--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -8681,9 +8681,9 @@
           <t>see model</t>
         </is>
       </c>
-      <c r="C21" s="89" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
+      <c r="C21" s="90" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D21" s="85" t="inlineStr">
@@ -8696,9 +8696,9 @@
           <t>Special Eurobarometer 525, Sport and Physical Activity, September 2022</t>
         </is>
       </c>
-      <c r="F21" s="86" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F21" s="88" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" s="85" t="inlineStr">

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -11707,12 +11707,12 @@
       </c>
       <c r="D38" s="96" t="inlineStr">
         <is>
-          <t>25%. The conventional range for pre-revenue to early-revenue venture is 20-35% and we sit mid-range. The sensitivity grid runs 18-30% precisely because this is arguable rather than knowable.</t>
+          <t>25%, against a published mature-company anchor of 6.01%. Damodaran's European cost of capital dataset puts Software (Internet) at 6.01% in euros across 23 listed firms, and the European market ex-financials at 6.59%. Those are costs of capital for mature listed companies; this is a pre-revenue venture, and the 19-point gap is the stage premium. It is stated rather than buried because it is the largest single judgement in the valuation. Damodaran publishes no dataset for venture-stage rates, so the premium itself is convention (20-35% is the usual range) and not a sourced figure. The sensitivity grid runs 18-30% because this is arguable rather than knowable.</t>
         </is>
       </c>
       <c r="E38" s="96" t="inlineStr">
         <is>
-          <t>Standard venture valuation practice</t>
+          <t>Aswath Damodaran, NYU Stern, Cost of Capital by Industry (Europe), updated 5 January 2026</t>
         </is>
       </c>
       <c r="F38" s="99" t="inlineStr">

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -207,12 +207,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001E7A3C"/>
+      <color rgb="00B3272D"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00B3272D"/>
+      <color rgb="001E7A3C"/>
       <sz val="9"/>
     </font>
     <font>
@@ -469,15 +469,15 @@
     <xf numFmtId="0" fontId="29" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="C4" s="30" t="n">
-        <v>600000</v>
+        <v>400000</v>
       </c>
       <c r="D4" s="30" t="n">
         <v>0</v>
@@ -6708,34 +6708,34 @@
         </is>
       </c>
       <c r="C20" s="30" t="n">
-        <v>106353.5810732172</v>
+        <v>87353.58107321717</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>246573.4630437107</v>
+        <v>220573.4630437107</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>571042.425977224</v>
+        <v>481042.4259772239</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>1170801.155460181</v>
+        <v>1010801.155460181</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>2038784.148591631</v>
+        <v>1774784.148591631</v>
       </c>
       <c r="H20" s="30" t="n">
-        <v>3055988.758048311</v>
+        <v>2647988.758048311</v>
       </c>
       <c r="I20" s="30" t="n">
-        <v>4326886.683956385</v>
+        <v>3696886.683956385</v>
       </c>
       <c r="J20" s="30" t="n">
-        <v>5336742.575015504</v>
+        <v>4616742.575015504</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>6074427.15237586</v>
+        <v>5334427.15237586</v>
       </c>
       <c r="L20" s="30" t="n">
-        <v>7093002.214343966</v>
+        <v>6333002.214343966</v>
       </c>
     </row>
     <row r="21">
@@ -6872,34 +6872,34 @@
         </is>
       </c>
       <c r="C25" s="30" t="n">
-        <v>-95025.0653449579</v>
+        <v>-76025.0653449579</v>
       </c>
       <c r="D25" s="30" t="n">
-        <v>-170545.7455848839</v>
+        <v>-144545.7455848839</v>
       </c>
       <c r="E25" s="30" t="n">
-        <v>-236868.3008951278</v>
+        <v>-146868.3008951277</v>
       </c>
       <c r="F25" s="30" t="n">
-        <v>-212822.9369717319</v>
+        <v>-52822.93697173183</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>156369.6728872678</v>
+        <v>420369.6728872678</v>
       </c>
       <c r="H25" s="30" t="n">
-        <v>1159572.48659347</v>
+        <v>1567572.48659347</v>
       </c>
       <c r="I25" s="30" t="n">
-        <v>2621573.878883271</v>
+        <v>3251573.878883271</v>
       </c>
       <c r="J25" s="30" t="n">
-        <v>4690028.521808989</v>
+        <v>5410028.521808989</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>6898861.25693799</v>
+        <v>7638861.25693799</v>
       </c>
       <c r="L25" s="30" t="n">
-        <v>9441189.914197091</v>
+        <v>10201189.91419709</v>
       </c>
     </row>
     <row r="26">
@@ -8035,19 +8035,19 @@
         <v>0</v>
       </c>
       <c r="H60" s="30" t="n">
-        <v>21027.01660260542</v>
+        <v>193392.0166026054</v>
       </c>
       <c r="I60" s="30" t="n">
-        <v>344936.0818324907</v>
+        <v>458966.0818324906</v>
       </c>
       <c r="J60" s="30" t="n">
-        <v>634864.2782713483</v>
+        <v>769234.2782713483</v>
       </c>
       <c r="K60" s="30" t="n">
-        <v>944859.1885406985</v>
+        <v>1087209.188540698</v>
       </c>
       <c r="L60" s="30" t="n">
-        <v>2176647.478549273</v>
+        <v>2422147.478549273</v>
       </c>
     </row>
     <row r="61">
@@ -8184,34 +8184,34 @@
         </is>
       </c>
       <c r="C65" s="30" t="n">
-        <v>-100725.0653449579</v>
+        <v>-79825.0653449579</v>
       </c>
       <c r="D65" s="30" t="n">
-        <v>-186645.7455848839</v>
+        <v>-156145.7455848839</v>
       </c>
       <c r="E65" s="30" t="n">
-        <v>-273968.3008951278</v>
+        <v>-170468.3008951277</v>
       </c>
       <c r="F65" s="30" t="n">
-        <v>-282622.9369717319</v>
+        <v>-95022.93697173183</v>
       </c>
       <c r="G65" s="30" t="n">
-        <v>30969.67288726778</v>
+        <v>346369.6728872678</v>
       </c>
       <c r="H65" s="30" t="n">
-        <v>932145.4699908645</v>
+        <v>1250980.469990865</v>
       </c>
       <c r="I65" s="30" t="n">
-        <v>1954637.797050781</v>
+        <v>2600807.797050781</v>
       </c>
       <c r="J65" s="30" t="n">
-        <v>3597564.243537641</v>
+        <v>4358994.243537641</v>
       </c>
       <c r="K65" s="30" t="n">
-        <v>5354202.068397291</v>
+        <v>6160852.068397291</v>
       </c>
       <c r="L65" s="30" t="n">
-        <v>6529942.435647818</v>
+        <v>7266442.435647818</v>
       </c>
     </row>
     <row r="66">
@@ -8348,34 +8348,34 @@
         </is>
       </c>
       <c r="C70" s="30" t="n">
-        <v>-95817.27587252646</v>
+        <v>-72678.9197081429</v>
       </c>
       <c r="D70" s="30" t="n">
-        <v>-163256.1042565819</v>
+        <v>-130031.4467223353</v>
       </c>
       <c r="E70" s="30" t="n">
-        <v>-188798.9540611985</v>
+        <v>-77059.22803380112</v>
       </c>
       <c r="F70" s="30" t="n">
-        <v>-60058.22952126013</v>
+        <v>142188.3458212058</v>
       </c>
       <c r="G70" s="30" t="n">
-        <v>484377.4431417021</v>
+        <v>819029.4979362227</v>
       </c>
       <c r="H70" s="30" t="n">
-        <v>1673919.564120663</v>
+        <v>2020118.947682307</v>
       </c>
       <c r="I70" s="30" t="n">
-        <v>2936196.927008493</v>
+        <v>3622920.351666027</v>
       </c>
       <c r="J70" s="30" t="n">
-        <v>4692204.487844148</v>
+        <v>5486437.227570175</v>
       </c>
       <c r="K70" s="30" t="n">
-        <v>6419322.362693556</v>
+        <v>7237328.527077117</v>
       </c>
       <c r="L70" s="30" t="n">
-        <v>7900590.191422299</v>
+        <v>8641446.355805861</v>
       </c>
     </row>
     <row r="71">
@@ -10573,7 +10573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -10688,11 +10688,11 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="95" t="inlineStr">
         <is>
-          <t>Take rate on sponsorship</t>
+          <t>Sponsorship commission, Scout Pro</t>
         </is>
       </c>
       <c r="B7" s="41">
-        <f>Assumptions!$C$41</f>
+        <f>Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="C7" s="96" t="inlineStr">
@@ -10702,12 +10702,12 @@
       </c>
       <c r="D7" s="97" t="inlineStr">
         <is>
-          <t>Sports agents take 10-20% of an endorsement and 4-10% of a playing contract. On OnlyFans, management agencies take a further 20-50% on top of the platform's 20%.</t>
+          <t>7% against a 10% base. A sponsor paying EUR 2,988 a year for the tooling is already paying for the relationship, and charging them the full headline rate on every deal as well is charging twice for it. Still comfortably inside the 10-20% an agent takes.</t>
         </is>
       </c>
       <c r="E7" s="97" t="inlineStr">
         <is>
-          <t>Oreate and Sapling agent-commission surveys; Aruna Talent agency rate guide 2026</t>
+          <t>Priced against the agent range; the discount itself is a pricing decision</t>
         </is>
       </c>
       <c r="F7" s="98" t="inlineStr">
@@ -10717,20 +10717,19 @@
       </c>
       <c r="G7" s="97" t="inlineStr">
         <is>
-          <t>Observed deal data once the marketplace is running.</t>
+          <t>Nothing to improve. This is a decision, not a measurement.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="95" t="inlineStr">
         <is>
-          <t>Suggested tiers 4.99 / 9.99 / 24.99</t>
-        </is>
-      </c>
-      <c r="B8" s="99" t="inlineStr">
-        <is>
-          <t>see model</t>
-        </is>
+          <t>Sponsorship commission, Scout Agency</t>
+        </is>
+      </c>
+      <c r="B8" s="41">
+        <f>Assumptions!$C$43</f>
+        <v/>
       </c>
       <c r="C8" s="96" t="inlineStr">
         <is>
@@ -10739,84 +10738,107 @@
       </c>
       <c r="D8" s="97" t="inlineStr">
         <is>
-          <t>Patreon's typical patronage is quoted at $8-12/month, so the EUR 9.99 anchor sits inside the observed band. EUR 4.99 retains only 54% of our take after payment fees, against 71% at EUR 9.99: which is why the floor matters more than the take rate.</t>
+          <t>5%, which is half the low end of what an agent charges and a quarter of the high end. The most committed tier pays EUR 11,988 a year, so the deal rate can fall furthest here.</t>
         </is>
       </c>
       <c r="E8" s="97" t="inlineStr">
         <is>
-          <t>Patreon 2024 Transparency Report; independent audits of ~1,200 creators</t>
-        </is>
-      </c>
-      <c r="F8" s="100" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Oreate and Sapling agent-commission surveys, 10-20%</t>
+        </is>
+      </c>
+      <c r="F8" s="98" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" s="97" t="inlineStr">
         <is>
-          <t>Our own tier mix after P1.</t>
+          <t>Nothing to improve. This is a decision, not a measurement.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="95" t="inlineStr">
         <is>
-          <t>Season pass / annual billing</t>
-        </is>
-      </c>
-      <c r="B9" s="99" t="inlineStr">
-        <is>
-          <t>see model</t>
-        </is>
-      </c>
-      <c r="C9" s="101" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
+          <t>Subscriber share of deal volume</t>
+        </is>
+      </c>
+      <c r="B9" s="41">
+        <f>Assumptions!$C$44</f>
+        <v/>
+      </c>
+      <c r="C9" s="99" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D9" s="97" t="inlineStr">
         <is>
-          <t>Patreon reports that annual patrons churn at ONE THIRD the rate of monthly patrons. This is the single strongest piece of evidence in the plan for pushing annual billing.</t>
+          <t>Subscribers are assumed to run 2.0x the deal volume of the average sponsor, which with a paid rate of 10-20% puts them at 20-40% of GMV. This is the ONLY estimate in the tiering and it is the one that sets the blended rate, which falls from 9.60% in Y1 to 8.56% by Y10. Deliberately conservative: Scout Pro buys five campaigns against the free tier's one, so 2.0x is well below what the campaign allowance alone would imply. Higher multiples lower the blend further.</t>
         </is>
       </c>
       <c r="E9" s="97" t="inlineStr">
         <is>
-          <t>Patreon 2024 Transparency Report</t>
-        </is>
-      </c>
-      <c r="F9" s="98" t="inlineStr">
+          <t>None. No tier-level deal volume exists yet, because no tier exists yet</t>
+        </is>
+      </c>
+      <c r="F9" s="100" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G9" s="97" t="inlineStr">
+        <is>
+          <t>The first year of billing settles it exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="95" t="inlineStr">
+        <is>
+          <t>Take rate on sponsorship</t>
+        </is>
+      </c>
+      <c r="B10" s="41">
+        <f>Assumptions!$C$41</f>
+        <v/>
+      </c>
+      <c r="C10" s="96" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D10" s="97" t="inlineStr">
+        <is>
+          <t>Sports agents take 10-20% of an endorsement and 4-10% of a playing contract. On OnlyFans, management agencies take a further 20-50% on top of the platform's 20%.</t>
+        </is>
+      </c>
+      <c r="E10" s="97" t="inlineStr">
+        <is>
+          <t>Oreate and Sapling agent-commission surveys; Aruna Talent agency rate guide 2026</t>
+        </is>
+      </c>
+      <c r="F10" s="98" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G9" s="97" t="inlineStr">
-        <is>
-          <t>Already strong. Confirm on our own cohorts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">: FAN ECONOMICS: </t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="20" t="n"/>
+      <c r="G10" s="97" t="inlineStr">
+        <is>
+          <t>Observed deal data once the marketplace is running.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="95" t="inlineStr">
         <is>
-          <t>Fan ARPU per month</t>
-        </is>
-      </c>
-      <c r="B11" s="41">
-        <f>Assumptions!$C$12</f>
-        <v/>
+          <t>Suggested tiers 4.99 / 9.99 / 24.99</t>
+        </is>
+      </c>
+      <c r="B11" s="101" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
       </c>
       <c r="C11" s="96" t="inlineStr">
         <is>
@@ -10825,824 +10847,825 @@
       </c>
       <c r="D11" s="97" t="inlineStr">
         <is>
-          <t>Patreon's average monthly support rose from $5.40 to $6.10 during 2024, with typical patronage quoted at $8-12. Our EUR 8.00-9.50 sits in the upper-middle of that range.</t>
+          <t>Patreon's typical patronage is quoted at $8-12/month, so the EUR 9.99 anchor sits inside the observed band. EUR 4.99 retains only 54% of our take after payment fees, against 71% at EUR 9.99: which is why the floor matters more than the take rate.</t>
         </is>
       </c>
       <c r="E11" s="97" t="inlineStr">
         <is>
-          <t>Patreon 2024 Transparency Report</t>
-        </is>
-      </c>
-      <c r="F11" s="100" t="inlineStr">
+          <t>Patreon 2024 Transparency Report; independent audits of ~1,200 creators</t>
+        </is>
+      </c>
+      <c r="F11" s="102" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="G11" s="97" t="inlineStr">
         <is>
-          <t>Actual ARPU by tier and sport after P1.</t>
+          <t>Our own tier mix after P1.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="95" t="inlineStr">
         <is>
-          <t>Fan churn per month</t>
-        </is>
-      </c>
-      <c r="B12" s="41">
-        <f>Assumptions!$C$13</f>
-        <v/>
-      </c>
-      <c r="C12" s="102" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
+          <t>Season pass / annual billing</t>
+        </is>
+      </c>
+      <c r="B12" s="101" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C12" s="103" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="D12" s="97" t="inlineStr">
         <is>
-          <t>OPTIMISTIC AGAINST BENCHMARK. Patreon runs 10-15% monthly. We assume 6-9% (niche) and 9-13% (popular), arguing that training content is habitual and that competitive seasons create natural renewal moments. That argument is currently untested.</t>
+          <t>Patreon reports that annual patrons churn at ONE THIRD the rate of monthly patrons. This is the single strongest piece of evidence in the plan for pushing annual billing.</t>
         </is>
       </c>
       <c r="E12" s="97" t="inlineStr">
         <is>
-          <t>Patreon 2024 Transparency Report (10-15%/month)</t>
-        </is>
-      </c>
-      <c r="F12" s="103" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Patreon 2024 Transparency Report</t>
+        </is>
+      </c>
+      <c r="F12" s="98" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G12" s="97" t="inlineStr">
         <is>
-          <t>THE most important number to measure in P1. Three months of real cohorts settles it. Until then the conservative case should be treated as the plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="95" t="inlineStr">
-        <is>
-          <t>Paying fans per monetising athlete</t>
-        </is>
-      </c>
-      <c r="B13" s="41">
-        <f>Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="C13" s="104" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="D13" s="97" t="inlineStr">
-        <is>
-          <t>20 rising to 48 over ten years. Cross-check: Patreon creators average $350/month and our modelled niche athlete at maturity earns about EUR 313/month, closely aligned, which is reassuring for an assumption built bottom-up rather than from a comparable.</t>
-        </is>
-      </c>
-      <c r="E13" s="97" t="inlineStr">
-        <is>
-          <t>Patreon 2024 Transparency Report (creator average $350/month)</t>
-        </is>
-      </c>
-      <c r="F13" s="100" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G13" s="97" t="inlineStr">
-        <is>
-          <t>Observed fans per athlete, banded by follower count.</t>
-        </is>
-      </c>
+          <t>Already strong. Confirm on our own cohorts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">: FAN ECONOMICS: </t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="95" t="inlineStr">
         <is>
-          <t>Share of athletes who monetise</t>
+          <t>Fan ARPU per month</t>
         </is>
       </c>
       <c r="B14" s="41">
-        <f>Assumptions!$C$10</f>
-        <v/>
-      </c>
-      <c r="C14" s="102" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
+        <f>Assumptions!$C$12</f>
+        <v/>
+      </c>
+      <c r="C14" s="96" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
         </is>
       </c>
       <c r="D14" s="97" t="inlineStr">
         <is>
-          <t>28% rising to 50% for niche sports. No direct comparable exists: neither Patreon nor OnlyFans publishes activation rates for creators who sign up but never charge.</t>
+          <t>Patreon's average monthly support rose from $5.40 to $6.10 during 2024, with typical patronage quoted at $8-12. Our EUR 8.00-9.50 sits in the upper-middle of that range.</t>
         </is>
       </c>
       <c r="E14" s="97" t="inlineStr">
         <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="F14" s="103" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Patreon 2024 Transparency Report</t>
+        </is>
+      </c>
+      <c r="F14" s="102" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G14" s="97" t="inlineStr">
         <is>
-          <t>Our own activation funnel, available from P1 onward.</t>
+          <t>Actual ARPU by tier and sport after P1.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="95" t="inlineStr">
         <is>
-          <t>Fan acquisition capacity</t>
-        </is>
-      </c>
-      <c r="B15" s="99" t="inlineStr">
-        <is>
-          <t>see model</t>
-        </is>
-      </c>
-      <c r="C15" s="102" t="inlineStr">
+          <t>Fan churn per month</t>
+        </is>
+      </c>
+      <c r="B15" s="41">
+        <f>Assumptions!$C$13</f>
+        <v/>
+      </c>
+      <c r="C15" s="99" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D15" s="97" t="inlineStr">
         <is>
-          <t>An athlete can recruit 30-69 new paying fans a year depending on segment. This ceiling is what makes churn bite in the model: without it, higher churn perversely RAISED revenue, because the year-end target was reachable at any churn rate.</t>
+          <t>OPTIMISTIC AGAINST BENCHMARK. Patreon runs 10-15% monthly. We assume 6-9% (niche) and 9-13% (popular), arguing that training content is habitual and that competitive seasons create natural renewal moments. That argument is currently untested.</t>
         </is>
       </c>
       <c r="E15" s="97" t="inlineStr">
         <is>
-          <t>None: introduced to fix a modelling flaw found by stress testing</t>
-        </is>
-      </c>
-      <c r="F15" s="103" t="inlineStr">
+          <t>Patreon 2024 Transparency Report (10-15%/month)</t>
+        </is>
+      </c>
+      <c r="F15" s="100" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
       <c r="G15" s="97" t="inlineStr">
         <is>
-          <t>Observed gross adds per athlete per year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">: PAYMENT RAILS: </t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
+          <t>THE most important number to measure in P1. Three months of real cohorts settles it. Until then the conservative case should be treated as the plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="95" t="inlineStr">
+        <is>
+          <t>Paying fans per monetising athlete</t>
+        </is>
+      </c>
+      <c r="B16" s="41">
+        <f>Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="C16" s="104" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D16" s="97" t="inlineStr">
+        <is>
+          <t>20 rising to 48 over ten years. Cross-check: Patreon creators average $350/month and our modelled niche athlete at maturity earns about EUR 313/month, closely aligned, which is reassuring for an assumption built bottom-up rather than from a comparable.</t>
+        </is>
+      </c>
+      <c r="E16" s="97" t="inlineStr">
+        <is>
+          <t>Patreon 2024 Transparency Report (creator average $350/month)</t>
+        </is>
+      </c>
+      <c r="F16" s="102" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G16" s="97" t="inlineStr">
+        <is>
+          <t>Observed fans per athlete, banded by follower count.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="95" t="inlineStr">
         <is>
-          <t>PSP percentage fee</t>
+          <t>Share of athletes who monetise</t>
         </is>
       </c>
       <c r="B17" s="41">
-        <f>Assumptions!$C$50</f>
-        <v/>
-      </c>
-      <c r="C17" s="101" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
+        <f>Assumptions!$C$10</f>
+        <v/>
+      </c>
+      <c r="C17" s="99" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D17" s="97" t="inlineStr">
         <is>
-          <t>Stripe for a Spanish entity: 1.5% + EUR 0.25 on EEA domestic cards, 2.5% on UK cards, 3.25% on non-EEA. 1.9% is the blend for a mostly-European fan base. CORRECTION: an earlier version of this model used the US headline of 2.9% and overstated the largest cost line in the business by about a third.</t>
+          <t>28% rising to 50% for niche sports. No direct comparable exists: neither Patreon nor OnlyFans publishes activation rates for creators who sign up but never charge.</t>
         </is>
       </c>
       <c r="E17" s="97" t="inlineStr">
         <is>
-          <t>Stripe published EU/EEA pricing, 2026</t>
-        </is>
-      </c>
-      <c r="F17" s="98" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="F17" s="100" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G17" s="97" t="inlineStr">
         <is>
-          <t>Interchange-plus terms become negotiable above roughly EUR 5M processed.</t>
+          <t>Our own activation funnel, available from P1 onward.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="95" t="inlineStr">
         <is>
-          <t>PSP fixed fee per transaction</t>
-        </is>
-      </c>
-      <c r="B18" s="41">
-        <f>Assumptions!$C$51</f>
-        <v/>
-      </c>
-      <c r="C18" s="101" t="inlineStr">
+          <t>Fan acquisition capacity</t>
+        </is>
+      </c>
+      <c r="B18" s="101" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C18" s="99" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="D18" s="97" t="inlineStr">
+        <is>
+          <t>An athlete can recruit 30-69 new paying fans a year depending on segment. This ceiling is what makes churn bite in the model: without it, higher churn perversely RAISED revenue, because the year-end target was reachable at any churn rate.</t>
+        </is>
+      </c>
+      <c r="E18" s="97" t="inlineStr">
+        <is>
+          <t>None: introduced to fix a modelling flaw found by stress testing</t>
+        </is>
+      </c>
+      <c r="F18" s="100" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G18" s="97" t="inlineStr">
+        <is>
+          <t>Observed gross adds per athlete per year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">: PAYMENT RAILS: </t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="20" t="n"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="95" t="inlineStr">
+        <is>
+          <t>PSP percentage fee</t>
+        </is>
+      </c>
+      <c r="B20" s="41">
+        <f>Assumptions!$C$50</f>
+        <v/>
+      </c>
+      <c r="C20" s="103" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D18" s="97" t="inlineStr">
-        <is>
-          <t>EUR 0.25 per transaction. On a EUR 4.99 tier that single fee is a third of our take, which is why the tier floor and annual billing move more margin than the take rate does.</t>
-        </is>
-      </c>
-      <c r="E18" s="97" t="inlineStr">
-        <is>
-          <t>Stripe published pricing, 2026</t>
-        </is>
-      </c>
-      <c r="F18" s="98" t="inlineStr">
+      <c r="D20" s="97" t="inlineStr">
+        <is>
+          <t>Stripe for a Spanish entity: 1.5% + EUR 0.25 on EEA domestic cards, 2.5% on UK cards, 3.25% on non-EEA. 1.9% is the blend for a mostly-European fan base. CORRECTION: an earlier version of this model used the US headline of 2.9% and overstated the largest cost line in the business by about a third.</t>
+        </is>
+      </c>
+      <c r="E20" s="97" t="inlineStr">
+        <is>
+          <t>Stripe published EU/EEA pricing, 2026</t>
+        </is>
+      </c>
+      <c r="F20" s="98" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G18" s="97" t="inlineStr">
-        <is>
-          <t>Volume renegotiation; annual billing turns twelve fees into one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="95" t="inlineStr">
-        <is>
-          <t>Payout fees</t>
-        </is>
-      </c>
-      <c r="B19" s="41">
-        <f>Assumptions!$C$52</f>
-        <v/>
-      </c>
-      <c r="C19" s="101" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
-        </is>
-      </c>
-      <c r="D19" s="97" t="inlineStr">
-        <is>
-          <t>Stripe Connect Express: roughly 0.25% + EUR 0.25 per payout, plus a monthly active-account fee that is not modelled as a separate line.</t>
-        </is>
-      </c>
-      <c r="E19" s="97" t="inlineStr">
-        <is>
-          <t>Stripe Connect pricing, 2026</t>
-        </is>
-      </c>
-      <c r="F19" s="100" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G19" s="97" t="inlineStr">
-        <is>
-          <t>Actual payout frequency once athletes are onboarded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">: MARKET SIZING: </t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
-      <c r="G20" s="20" t="n"/>
+      <c r="G20" s="97" t="inlineStr">
+        <is>
+          <t>Interchange-plus terms become negotiable above roughly EUR 5M processed.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="95" t="inlineStr">
         <is>
-          <t>Sport participation by country</t>
-        </is>
-      </c>
-      <c r="B21" s="99" t="inlineStr">
-        <is>
-          <t>see model</t>
-        </is>
-      </c>
-      <c r="C21" s="102" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
+          <t>PSP fixed fee per transaction</t>
+        </is>
+      </c>
+      <c r="B21" s="41">
+        <f>Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="C21" s="103" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="D21" s="97" t="inlineStr">
         <is>
-          <t>Eurobarometer 525, share who NEVER exercise: Finland 8%, Sweden 12%, Denmark 20%, Poland 65%, Greece 68%, Portugal 73%, EU-27 average 45%. Six of the 34 countries in the index are measured; the other 28 are estimates placed inside that distribution.</t>
+          <t>EUR 0.25 per transaction. On a EUR 4.99 tier that single fee is a third of our take, which is why the tier floor and annual billing move more margin than the take rate does.</t>
         </is>
       </c>
       <c r="E21" s="97" t="inlineStr">
         <is>
-          <t>Special Eurobarometer 525, Sport and Physical Activity, September 2022</t>
-        </is>
-      </c>
-      <c r="F21" s="100" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Stripe published pricing, 2026</t>
+        </is>
+      </c>
+      <c r="F21" s="98" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G21" s="97" t="inlineStr">
         <is>
-          <t>Federation licence counts, published annually and free (CSD in Spain).</t>
+          <t>Volume renegotiation; annual billing turns twelve fees into one.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="95" t="inlineStr">
         <is>
-          <t>Padel market size</t>
-        </is>
-      </c>
-      <c r="B22" s="99" t="inlineStr">
-        <is>
-          <t>see model</t>
-        </is>
-      </c>
-      <c r="C22" s="101" t="inlineStr">
+          <t>Payout fees</t>
+        </is>
+      </c>
+      <c r="B22" s="41">
+        <f>Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="C22" s="103" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
       <c r="D22" s="97" t="inlineStr">
         <is>
-          <t>Spain has ~6.0M active players (12.7% of the population), 109,040 federation licences and 17,300+ courts; globally 35M+ players and 77,000+ courts. This is the clearest case for weighting a sport regionally rather than globally, padel scores 77.7 in Spain and 45.1 worldwide.</t>
+          <t>Stripe Connect Express: roughly 0.25% + EUR 0.25 per payout, plus a monthly active-account fee that is not modelled as a separate line.</t>
         </is>
       </c>
       <c r="E22" s="97" t="inlineStr">
         <is>
-          <t>FIP World Padel Report 2025</t>
-        </is>
-      </c>
-      <c r="F22" s="98" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Stripe Connect pricing, 2026</t>
+        </is>
+      </c>
+      <c r="F22" s="102" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G22" s="97" t="inlineStr">
         <is>
-          <t>Annual FIP refresh.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="95" t="inlineStr">
-        <is>
-          <t>Sports fandom by country</t>
-        </is>
-      </c>
-      <c r="B23" s="99" t="inlineStr">
-        <is>
-          <t>see model</t>
-        </is>
-      </c>
-      <c r="C23" s="102" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="D23" s="97" t="inlineStr">
-        <is>
-          <t>The weakest layer of the sport index, and it drives both the `demand` and `appetite` signals. Commercial audience panels (Nielsen Sports, YouGov) cost more than the entire Y1-Y2 analytics budget.</t>
-        </is>
-      </c>
-      <c r="E23" s="97" t="inlineStr">
-        <is>
-          <t>None: reasoned estimates only</t>
-        </is>
-      </c>
-      <c r="F23" s="103" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G23" s="97" t="inlineStr">
-        <is>
-          <t>Our own engagement data per sport per country once connectors are live. This is what makes the index self-improving rather than something anyone could copy.</t>
-        </is>
-      </c>
+          <t>Actual payout frequency once athletes are onboarded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">: MARKET SIZING: </t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="20" t="n"/>
+      <c r="F23" s="20" t="n"/>
+      <c r="G23" s="20" t="n"/>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="95" t="inlineStr">
         <is>
-          <t>Athlete count trajectory</t>
-        </is>
-      </c>
-      <c r="B24" s="41">
-        <f>Assumptions!$C$5</f>
-        <v/>
-      </c>
-      <c r="C24" s="102" t="inlineStr">
+          <t>Sport participation by country</t>
+        </is>
+      </c>
+      <c r="B24" s="101" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C24" s="99" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D24" s="97" t="inlineStr">
         <is>
-          <t>400 rising to 40,000 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
+          <t>Eurobarometer 525, share who NEVER exercise: Finland 8%, Sweden 12%, Denmark 20%, Poland 65%, Greece 68%, Portugal 73%, EU-27 average 45%. Six of the 34 countries in the index are measured; the other 28 are estimates placed inside that distribution.</t>
         </is>
       </c>
       <c r="E24" s="97" t="inlineStr">
         <is>
-          <t>None: it is a target</t>
-        </is>
-      </c>
-      <c r="F24" s="103" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Special Eurobarometer 525, Sport and Physical Activity, September 2022</t>
+        </is>
+      </c>
+      <c r="F24" s="102" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G24" s="97" t="inlineStr">
         <is>
-          <t>The pre-seed gate tests it directly: 400 athletes and EUR 10k MRR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">: COSTS: </t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="20" t="n"/>
+          <t>Federation licence counts, published annually and free (CSD in Spain).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="95" t="inlineStr">
+        <is>
+          <t>Padel market size</t>
+        </is>
+      </c>
+      <c r="B25" s="101" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C25" s="103" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D25" s="97" t="inlineStr">
+        <is>
+          <t>Spain has ~6.0M active players (12.7% of the population), 109,040 federation licences and 17,300+ courts; globally 35M+ players and 77,000+ courts. This is the clearest case for weighting a sport regionally rather than globally, padel scores 77.7 in Spain and 45.1 worldwide.</t>
+        </is>
+      </c>
+      <c r="E25" s="97" t="inlineStr">
+        <is>
+          <t>FIP World Padel Report 2025</t>
+        </is>
+      </c>
+      <c r="F25" s="98" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G25" s="97" t="inlineStr">
+        <is>
+          <t>Annual FIP refresh.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="95" t="inlineStr">
         <is>
-          <t>Athlete CAC</t>
-        </is>
-      </c>
-      <c r="B26" s="41">
-        <f>Assumptions!$C$19</f>
-        <v/>
-      </c>
-      <c r="C26" s="102" t="inlineStr">
+          <t>Sports fandom by country</t>
+        </is>
+      </c>
+      <c r="B26" s="101" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C26" s="99" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D26" s="97" t="inlineStr">
         <is>
-          <t>EUR 16-36 for niche, EUR 40-88 for popular. The gap reflects displacing an existing agent relationship versus reaching someone with no representation at all. No published comparable exists for athlete acquisition in this segment.</t>
+          <t>The weakest layer of the sport index, and it drives both the `demand` and `appetite` signals. Commercial audience panels (Nielsen Sports, YouGov) cost more than the entire Y1-Y2 analytics budget.</t>
         </is>
       </c>
       <c r="E26" s="97" t="inlineStr">
         <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="F26" s="103" t="inlineStr">
+          <t>None: reasoned estimates only</t>
+        </is>
+      </c>
+      <c r="F26" s="100" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
       <c r="G26" s="97" t="inlineStr">
         <is>
-          <t>Measured CAC by channel from the first federation partnership.</t>
+          <t>Our own engagement data per sport per country once connectors are live. This is what makes the index self-improving rather than something anyone could copy.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="95" t="inlineStr">
         <is>
-          <t>Admission rate, direct applicants</t>
+          <t>Athlete count trajectory</t>
         </is>
       </c>
       <c r="B27" s="41">
-        <f>Assumptions!$C$82</f>
-        <v/>
-      </c>
-      <c r="C27" s="104" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+        <f>Assumptions!$C$5</f>
+        <v/>
+      </c>
+      <c r="C27" s="99" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D27" s="97" t="inlineStr">
         <is>
-          <t>20% of direct applicants are admitted, 25% go to a human, 40% are refused and 15% never finish the form. Not a judgement: it is the ops-load output of scripts/admission_stress.py run over the admission policy itself, so retuning a threshold moves this figure. The sweep asserts the model and the policy stay in step and fails if they drift.</t>
+          <t>400 rising to 40,000 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
         </is>
       </c>
       <c r="E27" s="97" t="inlineStr">
         <is>
-          <t>scripts/admission_stress.py, section 7, over a modelled applicant mix</t>
+          <t>None: it is a target</t>
         </is>
       </c>
       <c r="F27" s="100" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G27" s="97" t="inlineStr">
         <is>
-          <t>Real intake data. The mix the sweep assumes is the soft part, not the arithmetic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="95" t="inlineStr">
-        <is>
-          <t>Admission rate, club-nominated</t>
-        </is>
-      </c>
-      <c r="B28" s="41">
-        <f>Assumptions!$C$84</f>
-        <v/>
-      </c>
-      <c r="C28" s="102" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="D28" s="97" t="inlineStr">
-        <is>
-          <t>45% admitted against 20% direct. A verified club's nomination confers a credibility floor of 0.75 x its own legitimacy score, which carries a completed application over the admit line that would otherwise have gone to review. It cannot carry an empty one: no club can supply someone else's date of birth, so the uplift is real but bounded.</t>
-        </is>
-      </c>
-      <c r="E28" s="97" t="inlineStr">
-        <is>
-          <t>None: the mechanism is built and tested, the conversion is not yet measured</t>
-        </is>
-      </c>
-      <c r="F28" s="103" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G28" s="97" t="inlineStr">
-        <is>
-          <t>The first federation partnership: nominated applicants are tagged, so this is measurable from day one of it.</t>
-        </is>
-      </c>
+          <t>The pre-seed gate tests it directly: 400 athletes and EUR 10k MRR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">: COSTS: </t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="95" t="inlineStr">
         <is>
-          <t>Athlete verification cost</t>
+          <t>Athlete CAC</t>
         </is>
       </c>
       <c r="B29" s="41">
-        <f>Assumptions!$C$87</f>
-        <v/>
-      </c>
-      <c r="C29" s="104" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+        <f>Assumptions!$C$19</f>
+        <v/>
+      </c>
+      <c r="C29" s="99" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D29" s="97" t="inlineStr">
         <is>
-          <t>Four minutes per manual review, priced at the same loaded salary the People line uses, over 1,700 productive hours. Peaks at EUR 47k and 0.64 reviewer-FTE in Y10, which is the finding rather than the cost: verification is not a money problem at this scale. The reason to automate it is latency: an athlete sitting in the queue is not listed, not matchable and not earning.</t>
+          <t>EUR 16-36 for niche, EUR 40-88 for popular. The gap reflects displacing an existing agent relationship versus reaching someone with no representation at all. No published comparable exists for athlete acquisition in this segment.</t>
         </is>
       </c>
       <c r="E29" s="97" t="inlineStr">
         <is>
-          <t>Derived from the sweep's review volume and the model's own salary line</t>
+          <t>None found</t>
         </is>
       </c>
       <c r="F29" s="100" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G29" s="97" t="inlineStr">
         <is>
-          <t>Timing real reviews. Four minutes is an estimate of a mechanical task.</t>
+          <t>Measured CAC by channel from the first federation partnership.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="95" t="inlineStr">
         <is>
-          <t>Athlete CAC vs the funnel</t>
+          <t>Admission rate, direct applicants</t>
         </is>
       </c>
       <c r="B30" s="41">
-        <f>Assumptions!$C$19</f>
-        <v/>
-      </c>
-      <c r="C30" s="102" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
+        <f>Assumptions!$C$82</f>
+        <v/>
+      </c>
+      <c r="C30" s="104" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D30" s="97" t="inlineStr">
         <is>
-          <t>Deliberately NOT multiplied by the admission funnel. Segment CAC is defined as the cost of landing one athlete ON the platform, so scaling it by 1/admission-rate would charge the same money twice. The Costs sheet carries a memo line showing what that CAC works out to per application (EUR 3.40 in Y1 rising to EUR 22), the figure to hold against what a channel actually charges per name reached.</t>
+          <t>20% of direct applicants are admitted, 25% go to a human, 40% are refused and 15% never finish the form. Not a judgement: it is the ops-load output of scripts/admission_stress.py run over the admission policy itself, so retuning a threshold moves this figure. The sweep asserts the model and the policy stay in step and fails if they drift.</t>
         </is>
       </c>
       <c r="E30" s="97" t="inlineStr">
         <is>
-          <t>None: this is a definitional choice, made explicit so it is not silently reversed</t>
-        </is>
-      </c>
-      <c r="F30" s="103" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>scripts/admission_stress.py, section 7, over a modelled applicant mix</t>
+        </is>
+      </c>
+      <c r="F30" s="102" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G30" s="97" t="inlineStr">
         <is>
-          <t>Channel-level spend against applications, which the funnel now records.</t>
+          <t>Real intake data. The mix the sweep assumes is the soft part, not the arithmetic.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="95" t="inlineStr">
         <is>
-          <t>Loaded salary, Spain</t>
+          <t>Admission rate, club-nominated</t>
         </is>
       </c>
       <c r="B31" s="41">
-        <f>Assumptions!$C$67</f>
-        <v/>
-      </c>
-      <c r="C31" s="96" t="inlineStr">
-        <is>
-          <t>BENCHMARKED</t>
+        <f>Assumptions!$C$84</f>
+        <v/>
+      </c>
+      <c r="C31" s="99" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D31" s="97" t="inlineStr">
         <is>
-          <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k, around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
+          <t>45% admitted against 20% direct. A verified club's nomination confers a credibility floor of 0.75 x its own legitimacy score, which carries a completed application over the admit line that would otherwise have gone to review. It cannot carry an empty one: no club can supply someone else's date of birth, so the uplift is real but bounded.</t>
         </is>
       </c>
       <c r="E31" s="97" t="inlineStr">
         <is>
-          <t>Spanish Seguridad Social employer contribution rates</t>
+          <t>None: the mechanism is built and tested, the conversion is not yet measured</t>
         </is>
       </c>
       <c r="F31" s="100" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G31" s="97" t="inlineStr">
         <is>
-          <t>Actual offers accepted.</t>
+          <t>The first federation partnership: nominated applicants are tagged, so this is measurable from day one of it.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="95" t="inlineStr">
         <is>
-          <t>AWS infrastructure</t>
+          <t>Athlete verification cost</t>
         </is>
       </c>
       <c r="B32" s="41">
-        <f>Assumptions!$C$58</f>
-        <v/>
-      </c>
-      <c r="C32" s="96" t="inlineStr">
-        <is>
-          <t>BENCHMARKED</t>
+        <f>Assumptions!$C$87</f>
+        <v/>
+      </c>
+      <c r="C32" s="104" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D32" s="97" t="inlineStr">
         <is>
-          <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
+          <t>Four minutes per manual review, priced at the same loaded salary the People line uses, over 1,700 productive hours. Peaks at EUR 47k and 0.64 reviewer-FTE in Y10, which is the finding rather than the cost: verification is not a money problem at this scale. The reason to automate it is latency: an athlete sitting in the queue is not listed, not matchable and not earning.</t>
         </is>
       </c>
       <c r="E32" s="97" t="inlineStr">
         <is>
-          <t>AWS published list pricing, 2026</t>
-        </is>
-      </c>
-      <c r="F32" s="100" t="inlineStr">
+          <t>Derived from the sweep's review volume and the model's own salary line</t>
+        </is>
+      </c>
+      <c r="F32" s="102" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="G32" s="97" t="inlineStr">
         <is>
-          <t>Actual bills; commit to Savings Plans once usage is stable.</t>
+          <t>Timing real reviews. Four minutes is an estimate of a mechanical task.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="95" t="inlineStr">
         <is>
-          <t>Media egress</t>
+          <t>Athlete CAC vs the funnel</t>
         </is>
       </c>
       <c r="B33" s="41">
-        <f>Assumptions!$C$60</f>
-        <v/>
-      </c>
-      <c r="C33" s="101" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
+        <f>Assumptions!$C$19</f>
+        <v/>
+      </c>
+      <c r="C33" s="99" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D33" s="97" t="inlineStr">
         <is>
-          <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year, the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
+          <t>Deliberately NOT multiplied by the admission funnel. Segment CAC is defined as the cost of landing one athlete ON the platform, so scaling it by 1/admission-rate would charge the same money twice. The Costs sheet carries a memo line showing what that CAC works out to per application (EUR 3.40 in Y1 rising to EUR 22), the figure to hold against what a channel actually charges per name reached.</t>
         </is>
       </c>
       <c r="E33" s="97" t="inlineStr">
         <is>
-          <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
-        </is>
-      </c>
-      <c r="F33" s="98" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>None: this is a definitional choice, made explicit so it is not silently reversed</t>
+        </is>
+      </c>
+      <c r="F33" s="100" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G33" s="97" t="inlineStr">
         <is>
-          <t>Nothing. Both are published.</t>
+          <t>Channel-level spend against applications, which the funnel now records.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="95" t="inlineStr">
         <is>
-          <t>Moderation cost</t>
+          <t>Loaded salary, Spain</t>
         </is>
       </c>
       <c r="B34" s="41">
-        <f>Assumptions!$C$62</f>
-        <v/>
-      </c>
-      <c r="C34" s="102" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
+        <f>Assumptions!$C$67</f>
+        <v/>
+      </c>
+      <c r="C34" s="96" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
         </is>
       </c>
       <c r="D34" s="97" t="inlineStr">
         <is>
-          <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
+          <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k, around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
         </is>
       </c>
       <c r="E34" s="97" t="inlineStr">
         <is>
-          <t>None cited</t>
-        </is>
-      </c>
-      <c r="F34" s="103" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Spanish Seguridad Social employer contribution rates</t>
+        </is>
+      </c>
+      <c r="F34" s="102" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G34" s="97" t="inlineStr">
         <is>
-          <t>Vendor quotes once P2 scope is fixed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">: TAX, CAPITAL &amp; VALUATION: </t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="n"/>
-      <c r="C35" s="20" t="n"/>
-      <c r="D35" s="20" t="n"/>
-      <c r="E35" s="20" t="n"/>
-      <c r="F35" s="20" t="n"/>
-      <c r="G35" s="20" t="n"/>
+          <t>Actual offers accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="95" t="inlineStr">
+        <is>
+          <t>AWS infrastructure</t>
+        </is>
+      </c>
+      <c r="B35" s="41">
+        <f>Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="C35" s="96" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D35" s="97" t="inlineStr">
+        <is>
+          <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
+        </is>
+      </c>
+      <c r="E35" s="97" t="inlineStr">
+        <is>
+          <t>AWS published list pricing, 2026</t>
+        </is>
+      </c>
+      <c r="F35" s="102" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G35" s="97" t="inlineStr">
+        <is>
+          <t>Actual bills; commit to Savings Plans once usage is stable.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="95" t="inlineStr">
         <is>
-          <t>Corporate tax rates</t>
+          <t>Media egress</t>
         </is>
       </c>
       <c r="B36" s="41">
-        <f>Assumptions!$C$77</f>
-        <v/>
-      </c>
-      <c r="C36" s="101" t="inlineStr">
+        <f>Assumptions!$C$60</f>
+        <v/>
+      </c>
+      <c r="C36" s="103" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
       <c r="D36" s="97" t="inlineStr">
         <is>
-          <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
+          <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year, the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
         </is>
       </c>
       <c r="E36" s="97" t="inlineStr">
         <is>
-          <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
+          <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
         </is>
       </c>
       <c r="F36" s="98" t="inlineStr">
@@ -11652,274 +11675,359 @@
       </c>
       <c r="G36" s="97" t="inlineStr">
         <is>
-          <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
+          <t>Nothing. Both are published.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="95" t="inlineStr">
         <is>
-          <t>Risk-free rate</t>
+          <t>Moderation cost</t>
         </is>
       </c>
       <c r="B37" s="41">
-        <f>Assumptions!$C$94</f>
-        <v/>
-      </c>
-      <c r="C37" s="101" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
+        <f>Assumptions!$C$62</f>
+        <v/>
+      </c>
+      <c r="C37" s="99" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="D37" s="97" t="inlineStr">
         <is>
-          <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
+          <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
         </is>
       </c>
       <c r="E37" s="97" t="inlineStr">
         <is>
-          <t>Spanish 10Y government bond yield</t>
-        </is>
-      </c>
-      <c r="F37" s="98" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>None cited</t>
+        </is>
+      </c>
+      <c r="F37" s="100" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G37" s="97" t="inlineStr">
         <is>
-          <t>Refresh at the date of any raise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="95" t="inlineStr">
-        <is>
-          <t>WACC / discount rate</t>
-        </is>
-      </c>
-      <c r="B38" s="41">
-        <f>Assumptions!$C$91</f>
-        <v/>
-      </c>
-      <c r="C38" s="96" t="inlineStr">
-        <is>
-          <t>BENCHMARKED</t>
-        </is>
-      </c>
-      <c r="D38" s="97" t="inlineStr">
-        <is>
-          <t>25%, against a published mature-company anchor of 6.01%. Damodaran's European cost of capital dataset puts Software (Internet) at 6.01% in euros across 23 listed firms, and the European market ex-financials at 6.59%. Those are costs of capital for mature listed companies; this is a pre-revenue venture, and the 19-point gap is the stage premium. It is stated rather than buried because it is the largest single judgement in the valuation. Damodaran publishes no dataset for venture-stage rates, so the premium itself is convention (20-35% is the usual range) and not a sourced figure. The sensitivity grid runs 18-30% because this is arguable rather than knowable.</t>
-        </is>
-      </c>
-      <c r="E38" s="97" t="inlineStr">
-        <is>
-          <t>Aswath Damodaran, NYU Stern, Cost of Capital by Industry (Europe), updated 5 January 2026</t>
-        </is>
-      </c>
-      <c r="F38" s="100" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G38" s="97" t="inlineStr">
-        <is>
-          <t>An actual term sheet prices this for you.</t>
-        </is>
-      </c>
+          <t>Vendor quotes once P2 scope is fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">: TAX, CAPITAL &amp; VALUATION: </t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20" t="n"/>
+      <c r="F38" s="20" t="n"/>
+      <c r="G38" s="20" t="n"/>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="95" t="inlineStr">
         <is>
-          <t>Exit revenue multiple</t>
+          <t>Corporate tax rates</t>
         </is>
       </c>
       <c r="B39" s="41">
-        <f>Assumptions!$C$93</f>
-        <v/>
-      </c>
-      <c r="C39" s="96" t="inlineStr">
-        <is>
-          <t>BENCHMARKED</t>
+        <f>Assumptions!$C$77</f>
+        <v/>
+      </c>
+      <c r="C39" s="103" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="D39" s="97" t="inlineStr">
         <is>
-          <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
+          <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
         </is>
       </c>
       <c r="E39" s="97" t="inlineStr">
         <is>
-          <t>Public marketplace and SaaS trading multiples</t>
-        </is>
-      </c>
-      <c r="F39" s="100" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
+        </is>
+      </c>
+      <c r="F39" s="98" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G39" s="97" t="inlineStr">
         <is>
-          <t>Comparable private transactions nearer an exit.</t>
+          <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="95" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Risk-free rate</t>
         </is>
       </c>
       <c r="B40" s="41">
-        <f>Assumptions!$C$92</f>
-        <v/>
-      </c>
-      <c r="C40" s="96" t="inlineStr">
+        <f>Assumptions!$C$94</f>
+        <v/>
+      </c>
+      <c r="C40" s="103" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D40" s="97" t="inlineStr">
+        <is>
+          <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
+        </is>
+      </c>
+      <c r="E40" s="97" t="inlineStr">
+        <is>
+          <t>Spanish 10Y government bond yield</t>
+        </is>
+      </c>
+      <c r="F40" s="98" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G40" s="97" t="inlineStr">
+        <is>
+          <t>Refresh at the date of any raise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="95" t="inlineStr">
+        <is>
+          <t>WACC / discount rate</t>
+        </is>
+      </c>
+      <c r="B41" s="41">
+        <f>Assumptions!$C$91</f>
+        <v/>
+      </c>
+      <c r="C41" s="96" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D40" s="97" t="inlineStr">
-        <is>
-          <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
-        </is>
-      </c>
-      <c r="E40" s="97" t="inlineStr">
-        <is>
-          <t>Standard DCF convention</t>
-        </is>
-      </c>
-      <c r="F40" s="100" t="inlineStr">
+      <c r="D41" s="97" t="inlineStr">
+        <is>
+          <t>25%, against a published mature-company anchor of 6.01%. Damodaran's European cost of capital dataset puts Software (Internet) at 6.01% in euros across 23 listed firms, and the European market ex-financials at 6.59%. Those are costs of capital for mature listed companies; this is a pre-revenue venture, and the 19-point gap is the stage premium. It is stated rather than buried because it is the largest single judgement in the valuation. Damodaran publishes no dataset for venture-stage rates, so the premium itself is convention (20-35% is the usual range) and not a sourced figure. The sensitivity grid runs 18-30% because this is arguable rather than knowable.</t>
+        </is>
+      </c>
+      <c r="E41" s="97" t="inlineStr">
+        <is>
+          <t>Aswath Damodaran, NYU Stern, Cost of Capital by Industry (Europe), updated 5 January 2026</t>
+        </is>
+      </c>
+      <c r="F41" s="102" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G40" s="97" t="inlineStr">
-        <is>
-          <t>Nothing: it is a convention, and the grid shows its effect.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">: COMPLIANCE: </t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="n"/>
-      <c r="C41" s="20" t="n"/>
-      <c r="D41" s="20" t="n"/>
-      <c r="E41" s="20" t="n"/>
-      <c r="F41" s="20" t="n"/>
-      <c r="G41" s="20" t="n"/>
+      <c r="G41" s="97" t="inlineStr">
+        <is>
+          <t>An actual term sheet prices this for you.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="95" t="inlineStr">
         <is>
-          <t>Payout age floor</t>
-        </is>
-      </c>
-      <c r="B42" s="99" t="inlineStr">
-        <is>
-          <t>see model</t>
-        </is>
-      </c>
-      <c r="C42" s="101" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
+          <t>Exit revenue multiple</t>
+        </is>
+      </c>
+      <c r="B42" s="41">
+        <f>Assumptions!$C$93</f>
+        <v/>
+      </c>
+      <c r="C42" s="96" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
         </is>
       </c>
       <c r="D42" s="97" t="inlineStr">
         <is>
-          <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
+          <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
         </is>
       </c>
       <c r="E42" s="97" t="inlineStr">
         <is>
-          <t>Stripe Connect documentation</t>
-        </is>
-      </c>
-      <c r="F42" s="98" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Public marketplace and SaaS trading multiples</t>
+        </is>
+      </c>
+      <c r="F42" s="102" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G42" s="97" t="inlineStr">
         <is>
-          <t>Nothing: it is a hard platform rule.</t>
+          <t>Comparable private transactions nearer an exit.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="95" t="inlineStr">
         <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="B43" s="41">
+        <f>Assumptions!$C$92</f>
+        <v/>
+      </c>
+      <c r="C43" s="96" t="inlineStr">
+        <is>
+          <t>BENCHMARKED</t>
+        </is>
+      </c>
+      <c r="D43" s="97" t="inlineStr">
+        <is>
+          <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
+        </is>
+      </c>
+      <c r="E43" s="97" t="inlineStr">
+        <is>
+          <t>Standard DCF convention</t>
+        </is>
+      </c>
+      <c r="F43" s="102" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G43" s="97" t="inlineStr">
+        <is>
+          <t>Nothing: it is a convention, and the grid shows its effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">: COMPLIANCE: </t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="20" t="n"/>
+      <c r="F44" s="20" t="n"/>
+      <c r="G44" s="20" t="n"/>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="95" t="inlineStr">
+        <is>
+          <t>Payout age floor</t>
+        </is>
+      </c>
+      <c r="B45" s="101" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
+      </c>
+      <c r="C45" s="103" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D45" s="97" t="inlineStr">
+        <is>
+          <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
+        </is>
+      </c>
+      <c r="E45" s="97" t="inlineStr">
+        <is>
+          <t>Stripe Connect documentation</t>
+        </is>
+      </c>
+      <c r="F45" s="98" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G45" s="97" t="inlineStr">
+        <is>
+          <t>Nothing: it is a hard platform rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="95" t="inlineStr">
+        <is>
           <t>Digital consent age, Spain</t>
         </is>
       </c>
-      <c r="B43" s="99" t="inlineStr">
+      <c r="B46" s="101" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C43" s="101" t="inlineStr">
+      <c r="C46" s="103" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D43" s="97" t="inlineStr">
+      <c r="D46" s="97" t="inlineStr">
         <is>
           <t>14 today under LOPDGDD Art. 7. A draft Organic Law on the Protection of Minors in Digital Environments would raise it to 16 and make age verification mandatory, which is why 16 is the forward-compatible floor for an account.</t>
         </is>
       </c>
-      <c r="E43" s="97" t="inlineStr">
+      <c r="E46" s="97" t="inlineStr">
         <is>
           <t>LOPDGDD Art. 7; draft Organic Law, Council of Ministers, March 2025</t>
         </is>
       </c>
-      <c r="F43" s="98" t="inlineStr">
+      <c r="F46" s="98" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G43" s="97" t="inlineStr">
+      <c r="G46" s="97" t="inlineStr">
         <is>
           <t>Track the bill through Parliament.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="105" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="105" t="inlineStr">
         <is>
           <t>THE THREE ASSUMPTIONS MOST LIKELY TO BE WRONG</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="106" t="inlineStr">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="106" t="inlineStr">
         <is>
           <t>1. Fan churn. We assume 6-13%/month; Patreon reports 10-15%. If Patreon is right, Y10 revenue falls from about EUR 58M to EUR 51M and the capital requirement roughly doubles.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="106" t="inlineStr">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="106" t="inlineStr">
         <is>
           <t>2. Athlete count. The trajectory is a target, not a forecast, and everything scales off it.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="106" t="inlineStr">
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="106" t="inlineStr">
         <is>
           <t>3. Share of athletes who monetise. No published comparable exists at all.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="107" t="inlineStr"/>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="107" t="inlineStr">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="107" t="inlineStr"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="107" t="inlineStr">
         <is>
           <t>All three are answered by the same thing: three months of real cohort data from P1.</t>
         </is>
@@ -11927,11 +12035,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A53:G53"/>
     <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A52:G52"/>
     <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14560,34 +14668,34 @@
         </is>
       </c>
       <c r="C66" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="29" t="n">
         <v>1.5</v>
       </c>
-      <c r="D66" s="29" t="n">
+      <c r="E66" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="E66" s="29" t="n">
+      <c r="F66" s="29" t="n">
         <v>3.5</v>
       </c>
-      <c r="F66" s="29" t="n">
+      <c r="G66" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="G66" s="29" t="n">
-        <v>10</v>
-      </c>
       <c r="H66" s="29" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I66" s="29" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J66" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="K66" s="29" t="n">
+        <v>23</v>
+      </c>
+      <c r="L66" s="29" t="n">
         <v>28</v>
-      </c>
-      <c r="K66" s="29" t="n">
-        <v>33</v>
-      </c>
-      <c r="L66" s="29" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="67">

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -10702,7 +10702,7 @@
       </c>
       <c r="D7" s="97" t="inlineStr">
         <is>
-          <t>7% against a 10% base. A sponsor paying EUR 2,988 a year for the tooling is already paying for the relationship, and charging them the full headline rate on every deal as well is charging twice for it. Still comfortably inside the 10-20% an agent takes.</t>
+          <t>7% against a 10% base. A sponsor paying EUR 2,988 a year for the tooling is already paying for the relationship, and charging them the full headline rate on every deal as well is charging twice for it. Below the 10-20% an agent takes, which is the point: the sponsor who commits most pays least on each deal.</t>
         </is>
       </c>
       <c r="E7" s="97" t="inlineStr">

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -149,12 +149,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
@@ -404,36 +404,36 @@
     <xf numFmtId="1" fontId="15" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="18" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="18" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="20" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="20" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="20" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="19" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="20" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="19" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="21" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="20" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="19" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="20" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="21" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="22" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="20" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="20" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="19" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="19" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="15" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="20" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="20" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="20" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="20" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="19" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="20" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="20" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="19" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="19" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="21" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -1423,94 +1423,94 @@
         </is>
       </c>
       <c r="C5" s="41">
-        <f>1/(1+Assumptions!$C$91)^1</f>
+        <f>1/(1+Assumptions!$C$94)^1</f>
         <v/>
       </c>
       <c r="D5" s="41">
-        <f>1/(1+Assumptions!$C$91)^2</f>
+        <f>1/(1+Assumptions!$C$94)^2</f>
         <v/>
       </c>
       <c r="E5" s="41">
-        <f>1/(1+Assumptions!$C$91)^3</f>
+        <f>1/(1+Assumptions!$C$94)^3</f>
         <v/>
       </c>
       <c r="F5" s="41">
-        <f>1/(1+Assumptions!$C$91)^4</f>
+        <f>1/(1+Assumptions!$C$94)^4</f>
         <v/>
       </c>
       <c r="G5" s="41">
-        <f>1/(1+Assumptions!$C$91)^5</f>
+        <f>1/(1+Assumptions!$C$94)^5</f>
         <v/>
       </c>
       <c r="H5" s="41">
-        <f>1/(1+Assumptions!$C$91)^6</f>
+        <f>1/(1+Assumptions!$C$94)^6</f>
         <v/>
       </c>
       <c r="I5" s="41">
-        <f>1/(1+Assumptions!$C$91)^7</f>
+        <f>1/(1+Assumptions!$C$94)^7</f>
         <v/>
       </c>
       <c r="J5" s="41">
-        <f>1/(1+Assumptions!$C$91)^8</f>
+        <f>1/(1+Assumptions!$C$94)^8</f>
         <v/>
       </c>
       <c r="K5" s="41">
-        <f>1/(1+Assumptions!$C$91)^9</f>
+        <f>1/(1+Assumptions!$C$94)^9</f>
         <v/>
       </c>
       <c r="L5" s="41">
-        <f>1/(1+Assumptions!$C$91)^10</f>
+        <f>1/(1+Assumptions!$C$94)^10</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Discounted FCF</t>
         </is>
       </c>
-      <c r="B6" s="48" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="C6" s="51">
+      <c r="C6" s="52">
         <f>C4*C5</f>
         <v/>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="52">
         <f>D4*D5</f>
         <v/>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="52">
         <f>E4*E5</f>
         <v/>
       </c>
-      <c r="F6" s="51">
+      <c r="F6" s="52">
         <f>F4*F5</f>
         <v/>
       </c>
-      <c r="G6" s="51">
+      <c r="G6" s="52">
         <f>G4*G5</f>
         <v/>
       </c>
-      <c r="H6" s="51">
+      <c r="H6" s="52">
         <f>H4*H5</f>
         <v/>
       </c>
-      <c r="I6" s="51">
+      <c r="I6" s="52">
         <f>I4*I5</f>
         <v/>
       </c>
-      <c r="J6" s="51">
+      <c r="J6" s="52">
         <f>J4*J5</f>
         <v/>
       </c>
-      <c r="K6" s="51">
+      <c r="K6" s="52">
         <f>K4*K5</f>
         <v/>
       </c>
-      <c r="L6" s="51">
+      <c r="L6" s="52">
         <f>L4*L5</f>
         <v/>
       </c>
@@ -1526,43 +1526,43 @@
           <t>for the IRR below</t>
         </is>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="56">
         <f>C4+IF(1=10,$C$11,0)</f>
         <v/>
       </c>
-      <c r="D8" s="55">
+      <c r="D8" s="56">
         <f>D4+IF(2=10,$C$11,0)</f>
         <v/>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="56">
         <f>E4+IF(3=10,$C$11,0)</f>
         <v/>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="56">
         <f>F4+IF(4=10,$C$11,0)</f>
         <v/>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="56">
         <f>G4+IF(5=10,$C$11,0)</f>
         <v/>
       </c>
-      <c r="H8" s="55">
+      <c r="H8" s="56">
         <f>H4+IF(6=10,$C$11,0)</f>
         <v/>
       </c>
-      <c r="I8" s="55">
+      <c r="I8" s="56">
         <f>I4+IF(7=10,$C$11,0)</f>
         <v/>
       </c>
-      <c r="J8" s="55">
+      <c r="J8" s="56">
         <f>J4+IF(8=10,$C$11,0)</f>
         <v/>
       </c>
-      <c r="K8" s="55">
+      <c r="K8" s="56">
         <f>K4+IF(9=10,$C$11,0)</f>
         <v/>
       </c>
-      <c r="L8" s="55">
+      <c r="L8" s="56">
         <f>L4+IF(10=10,$C$11,0)</f>
         <v/>
       </c>
@@ -1591,7 +1591,7 @@
           <t>PV of explicit forecast</t>
         </is>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="60">
         <f>SUM(C6:L6)</f>
         <v/>
       </c>
@@ -1602,8 +1602,8 @@
           <t>Terminal value at Y10</t>
         </is>
       </c>
-      <c r="C11" s="59">
-        <f>L4*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)</f>
+      <c r="C11" s="60">
+        <f>L4*(1+Assumptions!$C$95)/(Assumptions!$C$94-Assumptions!$C$95)</f>
         <v/>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C12" s="59">
+      <c r="C12" s="60">
         <f>C11*L5</f>
         <v/>
       </c>
@@ -1624,7 +1624,7 @@
           <t>ENTERPRISE VALUE (DCF)</t>
         </is>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="60">
         <f>C10+C12</f>
         <v/>
       </c>
@@ -1653,8 +1653,8 @@
           <t>NPV of FCF at WACC</t>
         </is>
       </c>
-      <c r="C16" s="59">
-        <f>NPV(Assumptions!$C$91,C4:L4)</f>
+      <c r="C16" s="60">
+        <f>NPV(Assumptions!$C$94,C4:L4)</f>
         <v/>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
           <t>IRR of the plan</t>
         </is>
       </c>
-      <c r="C17" s="60">
+      <c r="C17" s="61">
         <f>IRR(C4:L4)</f>
         <v/>
       </c>
@@ -1675,7 +1675,7 @@
           <t>IRR incl. terminal value</t>
         </is>
       </c>
-      <c r="C18" s="60">
+      <c r="C18" s="61">
         <f>IRR(C8:L8,0.3)</f>
         <v/>
       </c>
@@ -1704,7 +1704,7 @@
           <t>Y10 net revenue</t>
         </is>
       </c>
-      <c r="C21" s="59">
+      <c r="C21" s="60">
         <f>Revenue!L26</f>
         <v/>
       </c>
@@ -1715,8 +1715,8 @@
           <t>Exit value at Y10</t>
         </is>
       </c>
-      <c r="C22" s="59">
-        <f>C21*Assumptions!$C$93</f>
+      <c r="C22" s="60">
+        <f>C21*Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
           <t>Discounted to today</t>
         </is>
       </c>
-      <c r="C23" s="59">
+      <c r="C23" s="60">
         <f>C22*L5</f>
         <v/>
       </c>
@@ -1755,166 +1755,166 @@
           <t>Terminal growth \ WACC</t>
         </is>
       </c>
-      <c r="C26" s="61" t="n">
+      <c r="C26" s="62" t="n">
         <v>0.18</v>
       </c>
-      <c r="D26" s="61" t="n">
+      <c r="D26" s="62" t="n">
         <v>0.2</v>
       </c>
-      <c r="E26" s="61" t="n">
+      <c r="E26" s="62" t="n">
         <v>0.22</v>
       </c>
-      <c r="F26" s="61" t="n">
+      <c r="F26" s="62" t="n">
         <v>0.25</v>
       </c>
-      <c r="G26" s="61" t="n">
+      <c r="G26" s="62" t="n">
         <v>0.28</v>
       </c>
-      <c r="H26" s="61" t="n">
+      <c r="H26" s="62" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="60" t="n">
+      <c r="A27" s="61" t="n">
         <v>0.01</v>
       </c>
-      <c r="C27" s="62">
+      <c r="C27" s="63">
         <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.01)/(0.18-0.01)/(1+0.18)^10</f>
         <v/>
       </c>
-      <c r="D27" s="62">
+      <c r="D27" s="63">
         <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.01)/(0.2-0.01)/(1+0.2)^10</f>
         <v/>
       </c>
-      <c r="E27" s="62">
+      <c r="E27" s="63">
         <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.01)/(0.22-0.01)/(1+0.22)^10</f>
         <v/>
       </c>
-      <c r="F27" s="62">
+      <c r="F27" s="63">
         <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.01)/(0.25-0.01)/(1+0.25)^10</f>
         <v/>
       </c>
-      <c r="G27" s="62">
+      <c r="G27" s="63">
         <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.01)/(0.28-0.01)/(1+0.28)^10</f>
         <v/>
       </c>
-      <c r="H27" s="62">
+      <c r="H27" s="63">
         <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.01)/(0.3-0.01)/(1+0.3)^10</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="60" t="n">
+      <c r="A28" s="61" t="n">
         <v>0.02</v>
       </c>
-      <c r="C28" s="62">
+      <c r="C28" s="63">
         <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.02)/(0.18-0.02)/(1+0.18)^10</f>
         <v/>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="63">
         <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.02)/(0.2-0.02)/(1+0.2)^10</f>
         <v/>
       </c>
-      <c r="E28" s="62">
+      <c r="E28" s="63">
         <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.02)/(0.22-0.02)/(1+0.22)^10</f>
         <v/>
       </c>
-      <c r="F28" s="62">
+      <c r="F28" s="63">
         <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.02)/(0.25-0.02)/(1+0.25)^10</f>
         <v/>
       </c>
-      <c r="G28" s="62">
+      <c r="G28" s="63">
         <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.02)/(0.28-0.02)/(1+0.28)^10</f>
         <v/>
       </c>
-      <c r="H28" s="62">
+      <c r="H28" s="63">
         <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.02)/(0.3-0.02)/(1+0.3)^10</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="60" t="n">
+      <c r="A29" s="61" t="n">
         <v>0.03</v>
       </c>
-      <c r="C29" s="62">
+      <c r="C29" s="63">
         <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.03)/(0.18-0.03)/(1+0.18)^10</f>
         <v/>
       </c>
-      <c r="D29" s="62">
+      <c r="D29" s="63">
         <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.03)/(0.2-0.03)/(1+0.2)^10</f>
         <v/>
       </c>
-      <c r="E29" s="62">
+      <c r="E29" s="63">
         <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.03)/(0.22-0.03)/(1+0.22)^10</f>
         <v/>
       </c>
-      <c r="F29" s="62">
+      <c r="F29" s="63">
         <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.03)/(0.25-0.03)/(1+0.25)^10</f>
         <v/>
       </c>
-      <c r="G29" s="62">
+      <c r="G29" s="63">
         <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.03)/(0.28-0.03)/(1+0.28)^10</f>
         <v/>
       </c>
-      <c r="H29" s="62">
+      <c r="H29" s="63">
         <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.03)/(0.3-0.03)/(1+0.3)^10</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="60" t="n">
+      <c r="A30" s="61" t="n">
         <v>0.04</v>
       </c>
-      <c r="C30" s="62">
+      <c r="C30" s="63">
         <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.04)/(0.18-0.04)/(1+0.18)^10</f>
         <v/>
       </c>
-      <c r="D30" s="62">
+      <c r="D30" s="63">
         <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.04)/(0.2-0.04)/(1+0.2)^10</f>
         <v/>
       </c>
-      <c r="E30" s="62">
+      <c r="E30" s="63">
         <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.04)/(0.22-0.04)/(1+0.22)^10</f>
         <v/>
       </c>
-      <c r="F30" s="62">
+      <c r="F30" s="63">
         <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.04)/(0.25-0.04)/(1+0.25)^10</f>
         <v/>
       </c>
-      <c r="G30" s="62">
+      <c r="G30" s="63">
         <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.04)/(0.28-0.04)/(1+0.28)^10</f>
         <v/>
       </c>
-      <c r="H30" s="62">
+      <c r="H30" s="63">
         <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.04)/(0.3-0.04)/(1+0.3)^10</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="60" t="n">
+      <c r="A31" s="61" t="n">
         <v>0.05</v>
       </c>
-      <c r="C31" s="62">
+      <c r="C31" s="63">
         <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.05)/(0.18-0.05)/(1+0.18)^10</f>
         <v/>
       </c>
-      <c r="D31" s="62">
+      <c r="D31" s="63">
         <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.05)/(0.2-0.05)/(1+0.2)^10</f>
         <v/>
       </c>
-      <c r="E31" s="62">
+      <c r="E31" s="63">
         <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.05)/(0.22-0.05)/(1+0.22)^10</f>
         <v/>
       </c>
-      <c r="F31" s="62">
+      <c r="F31" s="63">
         <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.05)/(0.25-0.05)/(1+0.25)^10</f>
         <v/>
       </c>
-      <c r="G31" s="62">
+      <c r="G31" s="63">
         <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.05)/(0.28-0.05)/(1+0.28)^10</f>
         <v/>
       </c>
-      <c r="H31" s="62">
+      <c r="H31" s="63">
         <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.05)/(0.3-0.05)/(1+0.3)^10</f>
         <v/>
       </c>
@@ -2150,43 +2150,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="56">
         <f>IF(C4=0,0,C5+C4)</f>
         <v/>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="56">
         <f>IF(D4=0,0,D5+D4)</f>
         <v/>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="56">
         <f>IF(E4=0,0,E5+E4)</f>
         <v/>
       </c>
-      <c r="F6" s="55">
+      <c r="F6" s="56">
         <f>IF(F4=0,0,F5+F4)</f>
         <v/>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="56">
         <f>IF(G4=0,0,G5+G4)</f>
         <v/>
       </c>
-      <c r="H6" s="55">
+      <c r="H6" s="56">
         <f>IF(H4=0,0,H5+H4)</f>
         <v/>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="56">
         <f>IF(I4=0,0,I5+I4)</f>
         <v/>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="56">
         <f>IF(J4=0,0,J5+J4)</f>
         <v/>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="56">
         <f>IF(K4=0,0,K5+K4)</f>
         <v/>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="56">
         <f>IF(L4=0,0,L5+L4)</f>
         <v/>
       </c>
@@ -2202,43 +2202,43 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="57">
         <f>IF(C6=0,0,C4/C6)</f>
         <v/>
       </c>
-      <c r="D7" s="56">
+      <c r="D7" s="57">
         <f>IF(D6=0,0,D4/D6)</f>
         <v/>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="57">
         <f>IF(E6=0,0,E4/E6)</f>
         <v/>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="57">
         <f>IF(F6=0,0,F4/F6)</f>
         <v/>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="57">
         <f>IF(G6=0,0,G4/G6)</f>
         <v/>
       </c>
-      <c r="H7" s="56">
+      <c r="H7" s="57">
         <f>IF(H6=0,0,H4/H6)</f>
         <v/>
       </c>
-      <c r="I7" s="56">
+      <c r="I7" s="57">
         <f>IF(I6=0,0,I4/I6)</f>
         <v/>
       </c>
-      <c r="J7" s="56">
+      <c r="J7" s="57">
         <f>IF(J6=0,0,J4/J6)</f>
         <v/>
       </c>
-      <c r="K7" s="56">
+      <c r="K7" s="57">
         <f>IF(K6=0,0,K4/K6)</f>
         <v/>
       </c>
-      <c r="L7" s="56">
+      <c r="L7" s="57">
         <f>IF(L6=0,0,L4/L6)</f>
         <v/>
       </c>
@@ -2328,53 +2328,53 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>Founders + team retained</t>
         </is>
       </c>
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C10" s="63">
+      <c r="C10" s="48">
         <f>(1-C7-C8)*(1-C9)</f>
         <v/>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="48">
         <f>(C10*(1-D7)-D8)*(1-D9)</f>
         <v/>
       </c>
-      <c r="E10" s="63">
+      <c r="E10" s="48">
         <f>(D10*(1-E7)-E8)*(1-E9)</f>
         <v/>
       </c>
-      <c r="F10" s="63">
+      <c r="F10" s="48">
         <f>(E10*(1-F7)-F8)*(1-F9)</f>
         <v/>
       </c>
-      <c r="G10" s="63">
+      <c r="G10" s="48">
         <f>(F10*(1-G7)-G8)*(1-G9)</f>
         <v/>
       </c>
-      <c r="H10" s="63">
+      <c r="H10" s="48">
         <f>(G10*(1-H7)-H8)*(1-H9)</f>
         <v/>
       </c>
-      <c r="I10" s="63">
+      <c r="I10" s="48">
         <f>(H10*(1-I7)-I8)*(1-I9)</f>
         <v/>
       </c>
-      <c r="J10" s="63">
+      <c r="J10" s="48">
         <f>(I10*(1-J7)-J8)*(1-J9)</f>
         <v/>
       </c>
-      <c r="K10" s="63">
+      <c r="K10" s="48">
         <f>(J10*(1-K7)-K8)*(1-K9)</f>
         <v/>
       </c>
-      <c r="L10" s="63">
+      <c r="L10" s="48">
         <f>(K10*(1-L7)-L8)*(1-L9)</f>
         <v/>
       </c>
@@ -2390,43 +2390,43 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C11" s="56">
+      <c r="C11" s="57">
         <f>1-C10</f>
         <v/>
       </c>
-      <c r="D11" s="56">
+      <c r="D11" s="57">
         <f>1-D10</f>
         <v/>
       </c>
-      <c r="E11" s="56">
+      <c r="E11" s="57">
         <f>1-E10</f>
         <v/>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="57">
         <f>1-F10</f>
         <v/>
       </c>
-      <c r="G11" s="56">
+      <c r="G11" s="57">
         <f>1-G10</f>
         <v/>
       </c>
-      <c r="H11" s="56">
+      <c r="H11" s="57">
         <f>1-H10</f>
         <v/>
       </c>
-      <c r="I11" s="56">
+      <c r="I11" s="57">
         <f>1-I10</f>
         <v/>
       </c>
-      <c r="J11" s="56">
+      <c r="J11" s="57">
         <f>1-J10</f>
         <v/>
       </c>
-      <c r="K11" s="56">
+      <c r="K11" s="57">
         <f>1-K10</f>
         <v/>
       </c>
-      <c r="L11" s="56">
+      <c r="L11" s="57">
         <f>1-L10</f>
         <v/>
       </c>
@@ -2880,12 +2880,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="53" t="inlineStr">
+      <c r="A12" s="54" t="inlineStr">
         <is>
           <t>TOTAL FTE</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
@@ -2984,12 +2984,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="46" t="inlineStr">
         <is>
           <t>CHECK</t>
         </is>
       </c>
-      <c r="B14" s="48" t="inlineStr">
+      <c r="B14" s="47" t="inlineStr">
         <is>
           <t>must be zero</t>
         </is>
@@ -3106,43 +3106,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C18" s="55">
+      <c r="C18" s="56">
         <f>C5*45000*(1+C17)</f>
         <v/>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="56">
         <f>D5*45000*(1+D17)</f>
         <v/>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="56">
         <f>E5*45000*(1+E17)</f>
         <v/>
       </c>
-      <c r="F18" s="55">
+      <c r="F18" s="56">
         <f>F5*45000*(1+F17)</f>
         <v/>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="56">
         <f>G5*45000*(1+G17)</f>
         <v/>
       </c>
-      <c r="H18" s="55">
+      <c r="H18" s="56">
         <f>H5*45000*(1+H17)</f>
         <v/>
       </c>
-      <c r="I18" s="55">
+      <c r="I18" s="56">
         <f>I5*45000*(1+I17)</f>
         <v/>
       </c>
-      <c r="J18" s="55">
+      <c r="J18" s="56">
         <f>J5*45000*(1+J17)</f>
         <v/>
       </c>
-      <c r="K18" s="55">
+      <c r="K18" s="56">
         <f>K5*45000*(1+K17)</f>
         <v/>
       </c>
-      <c r="L18" s="55">
+      <c r="L18" s="56">
         <f>L5*45000*(1+L17)</f>
         <v/>
       </c>
@@ -3158,43 +3158,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C19" s="55">
+      <c r="C19" s="56">
         <f>C6*55000*(1+C17)</f>
         <v/>
       </c>
-      <c r="D19" s="55">
+      <c r="D19" s="56">
         <f>D6*55000*(1+D17)</f>
         <v/>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="56">
         <f>E6*55000*(1+E17)</f>
         <v/>
       </c>
-      <c r="F19" s="55">
+      <c r="F19" s="56">
         <f>F6*55000*(1+F17)</f>
         <v/>
       </c>
-      <c r="G19" s="55">
+      <c r="G19" s="56">
         <f>G6*55000*(1+G17)</f>
         <v/>
       </c>
-      <c r="H19" s="55">
+      <c r="H19" s="56">
         <f>H6*55000*(1+H17)</f>
         <v/>
       </c>
-      <c r="I19" s="55">
+      <c r="I19" s="56">
         <f>I6*55000*(1+I17)</f>
         <v/>
       </c>
-      <c r="J19" s="55">
+      <c r="J19" s="56">
         <f>J6*55000*(1+J17)</f>
         <v/>
       </c>
-      <c r="K19" s="55">
+      <c r="K19" s="56">
         <f>K6*55000*(1+K17)</f>
         <v/>
       </c>
-      <c r="L19" s="55">
+      <c r="L19" s="56">
         <f>L6*55000*(1+L17)</f>
         <v/>
       </c>
@@ -3210,43 +3210,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C20" s="55">
+      <c r="C20" s="56">
         <f>C7*38000*(1+C17)</f>
         <v/>
       </c>
-      <c r="D20" s="55">
+      <c r="D20" s="56">
         <f>D7*38000*(1+D17)</f>
         <v/>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="56">
         <f>E7*38000*(1+E17)</f>
         <v/>
       </c>
-      <c r="F20" s="55">
+      <c r="F20" s="56">
         <f>F7*38000*(1+F17)</f>
         <v/>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="56">
         <f>G7*38000*(1+G17)</f>
         <v/>
       </c>
-      <c r="H20" s="55">
+      <c r="H20" s="56">
         <f>H7*38000*(1+H17)</f>
         <v/>
       </c>
-      <c r="I20" s="55">
+      <c r="I20" s="56">
         <f>I7*38000*(1+I17)</f>
         <v/>
       </c>
-      <c r="J20" s="55">
+      <c r="J20" s="56">
         <f>J7*38000*(1+J17)</f>
         <v/>
       </c>
-      <c r="K20" s="55">
+      <c r="K20" s="56">
         <f>K7*38000*(1+K17)</f>
         <v/>
       </c>
-      <c r="L20" s="55">
+      <c r="L20" s="56">
         <f>L7*38000*(1+L17)</f>
         <v/>
       </c>
@@ -3262,43 +3262,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C21" s="55">
+      <c r="C21" s="56">
         <f>C8*30000*(1+C17)</f>
         <v/>
       </c>
-      <c r="D21" s="55">
+      <c r="D21" s="56">
         <f>D8*30000*(1+D17)</f>
         <v/>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="56">
         <f>E8*30000*(1+E17)</f>
         <v/>
       </c>
-      <c r="F21" s="55">
+      <c r="F21" s="56">
         <f>F8*30000*(1+F17)</f>
         <v/>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="56">
         <f>G8*30000*(1+G17)</f>
         <v/>
       </c>
-      <c r="H21" s="55">
+      <c r="H21" s="56">
         <f>H8*30000*(1+H17)</f>
         <v/>
       </c>
-      <c r="I21" s="55">
+      <c r="I21" s="56">
         <f>I8*30000*(1+I17)</f>
         <v/>
       </c>
-      <c r="J21" s="55">
+      <c r="J21" s="56">
         <f>J8*30000*(1+J17)</f>
         <v/>
       </c>
-      <c r="K21" s="55">
+      <c r="K21" s="56">
         <f>K8*30000*(1+K17)</f>
         <v/>
       </c>
-      <c r="L21" s="55">
+      <c r="L21" s="56">
         <f>L8*30000*(1+L17)</f>
         <v/>
       </c>
@@ -3314,43 +3314,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C22" s="55">
+      <c r="C22" s="56">
         <f>C9*34000*(1+C17)</f>
         <v/>
       </c>
-      <c r="D22" s="55">
+      <c r="D22" s="56">
         <f>D9*34000*(1+D17)</f>
         <v/>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="56">
         <f>E9*34000*(1+E17)</f>
         <v/>
       </c>
-      <c r="F22" s="55">
+      <c r="F22" s="56">
         <f>F9*34000*(1+F17)</f>
         <v/>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="56">
         <f>G9*34000*(1+G17)</f>
         <v/>
       </c>
-      <c r="H22" s="55">
+      <c r="H22" s="56">
         <f>H9*34000*(1+H17)</f>
         <v/>
       </c>
-      <c r="I22" s="55">
+      <c r="I22" s="56">
         <f>I9*34000*(1+I17)</f>
         <v/>
       </c>
-      <c r="J22" s="55">
+      <c r="J22" s="56">
         <f>J9*34000*(1+J17)</f>
         <v/>
       </c>
-      <c r="K22" s="55">
+      <c r="K22" s="56">
         <f>K9*34000*(1+K17)</f>
         <v/>
       </c>
-      <c r="L22" s="55">
+      <c r="L22" s="56">
         <f>L9*34000*(1+L17)</f>
         <v/>
       </c>
@@ -3366,43 +3366,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C23" s="55">
+      <c r="C23" s="56">
         <f>C10*42000*(1+C17)</f>
         <v/>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="56">
         <f>D10*42000*(1+D17)</f>
         <v/>
       </c>
-      <c r="E23" s="55">
+      <c r="E23" s="56">
         <f>E10*42000*(1+E17)</f>
         <v/>
       </c>
-      <c r="F23" s="55">
+      <c r="F23" s="56">
         <f>F10*42000*(1+F17)</f>
         <v/>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="56">
         <f>G10*42000*(1+G17)</f>
         <v/>
       </c>
-      <c r="H23" s="55">
+      <c r="H23" s="56">
         <f>H10*42000*(1+H17)</f>
         <v/>
       </c>
-      <c r="I23" s="55">
+      <c r="I23" s="56">
         <f>I10*42000*(1+I17)</f>
         <v/>
       </c>
-      <c r="J23" s="55">
+      <c r="J23" s="56">
         <f>J10*42000*(1+J17)</f>
         <v/>
       </c>
-      <c r="K23" s="55">
+      <c r="K23" s="56">
         <f>K10*42000*(1+K17)</f>
         <v/>
       </c>
-      <c r="L23" s="55">
+      <c r="L23" s="56">
         <f>L10*42000*(1+L17)</f>
         <v/>
       </c>
@@ -3418,95 +3418,95 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C24" s="55">
+      <c r="C24" s="56">
         <f>C11*60000*(1+C17)</f>
         <v/>
       </c>
-      <c r="D24" s="55">
+      <c r="D24" s="56">
         <f>D11*60000*(1+D17)</f>
         <v/>
       </c>
-      <c r="E24" s="55">
+      <c r="E24" s="56">
         <f>E11*60000*(1+E17)</f>
         <v/>
       </c>
-      <c r="F24" s="55">
+      <c r="F24" s="56">
         <f>F11*60000*(1+F17)</f>
         <v/>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="56">
         <f>G11*60000*(1+G17)</f>
         <v/>
       </c>
-      <c r="H24" s="55">
+      <c r="H24" s="56">
         <f>H11*60000*(1+H17)</f>
         <v/>
       </c>
-      <c r="I24" s="55">
+      <c r="I24" s="56">
         <f>I11*60000*(1+I17)</f>
         <v/>
       </c>
-      <c r="J24" s="55">
+      <c r="J24" s="56">
         <f>J11*60000*(1+J17)</f>
         <v/>
       </c>
-      <c r="K24" s="55">
+      <c r="K24" s="56">
         <f>K11*60000*(1+K17)</f>
         <v/>
       </c>
-      <c r="L24" s="55">
+      <c r="L24" s="56">
         <f>L11*60000*(1+L17)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="53" t="inlineStr">
+      <c r="A25" s="54" t="inlineStr">
         <is>
           <t>TOTAL, role build-up</t>
         </is>
       </c>
-      <c r="B25" s="48" t="inlineStr">
+      <c r="B25" s="47" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="C25" s="54">
+      <c r="C25" s="55">
         <f>SUM(C18:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="54">
+      <c r="D25" s="55">
         <f>SUM(D18:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="54">
+      <c r="E25" s="55">
         <f>SUM(E18:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="54">
+      <c r="F25" s="55">
         <f>SUM(F18:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="54">
+      <c r="G25" s="55">
         <f>SUM(G18:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="54">
+      <c r="H25" s="55">
         <f>SUM(H18:H24)</f>
         <v/>
       </c>
-      <c r="I25" s="54">
+      <c r="I25" s="55">
         <f>SUM(I18:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="54">
+      <c r="J25" s="55">
         <f>SUM(J18:J24)</f>
         <v/>
       </c>
-      <c r="K25" s="54">
+      <c r="K25" s="55">
         <f>SUM(K18:K24)</f>
         <v/>
       </c>
-      <c r="L25" s="54">
+      <c r="L25" s="55">
         <f>SUM(L18:L24)</f>
         <v/>
       </c>
@@ -3574,43 +3574,43 @@
           <t>build-up less model</t>
         </is>
       </c>
-      <c r="C27" s="55">
+      <c r="C27" s="56">
         <f>C25-C26</f>
         <v/>
       </c>
-      <c r="D27" s="55">
+      <c r="D27" s="56">
         <f>D25-D26</f>
         <v/>
       </c>
-      <c r="E27" s="55">
+      <c r="E27" s="56">
         <f>E25-E26</f>
         <v/>
       </c>
-      <c r="F27" s="55">
+      <c r="F27" s="56">
         <f>F25-F26</f>
         <v/>
       </c>
-      <c r="G27" s="55">
+      <c r="G27" s="56">
         <f>G25-G26</f>
         <v/>
       </c>
-      <c r="H27" s="55">
+      <c r="H27" s="56">
         <f>H25-H26</f>
         <v/>
       </c>
-      <c r="I27" s="55">
+      <c r="I27" s="56">
         <f>I25-I26</f>
         <v/>
       </c>
-      <c r="J27" s="55">
+      <c r="J27" s="56">
         <f>J25-J26</f>
         <v/>
       </c>
-      <c r="K27" s="55">
+      <c r="K27" s="56">
         <f>K25-K26</f>
         <v/>
       </c>
-      <c r="L27" s="55">
+      <c r="L27" s="56">
         <f>L25-L26</f>
         <v/>
       </c>
@@ -4193,64 +4193,64 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="53" t="inlineStr">
+      <c r="A11" s="54" t="inlineStr">
         <is>
           <t>ATHLETE LTV</t>
         </is>
       </c>
-      <c r="B11" s="48" t="inlineStr">
+      <c r="B11" s="47" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="C11" s="54">
+      <c r="C11" s="55">
         <f>C10*C8</f>
         <v/>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="55">
         <f>D10*D8</f>
         <v/>
       </c>
-      <c r="E11" s="54">
+      <c r="E11" s="55">
         <f>E10*E8</f>
         <v/>
       </c>
-      <c r="F11" s="54">
+      <c r="F11" s="55">
         <f>F10*F8</f>
         <v/>
       </c>
-      <c r="G11" s="54">
+      <c r="G11" s="55">
         <f>G10*G8</f>
         <v/>
       </c>
-      <c r="H11" s="54">
+      <c r="H11" s="55">
         <f>H10*H8</f>
         <v/>
       </c>
-      <c r="I11" s="54">
+      <c r="I11" s="55">
         <f>I10*I8</f>
         <v/>
       </c>
-      <c r="J11" s="54">
+      <c r="J11" s="55">
         <f>J10*J8</f>
         <v/>
       </c>
-      <c r="K11" s="54">
+      <c r="K11" s="55">
         <f>K10*K8</f>
         <v/>
       </c>
-      <c r="L11" s="54">
+      <c r="L11" s="55">
         <f>L10*L8</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="47" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>LTV / CAC</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4794,12 +4794,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="53" t="inlineStr">
+      <c r="A27" s="54" t="inlineStr">
         <is>
           <t>FAN LTV</t>
         </is>
       </c>
-      <c r="B27" s="48" t="inlineStr">
+      <c r="B27" s="47" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -5079,43 +5079,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C36" s="55">
+      <c r="C36" s="56">
         <f>C34+C35</f>
         <v/>
       </c>
-      <c r="D36" s="55">
+      <c r="D36" s="56">
         <f>D34+D35</f>
         <v/>
       </c>
-      <c r="E36" s="55">
+      <c r="E36" s="56">
         <f>E34+E35</f>
         <v/>
       </c>
-      <c r="F36" s="55">
+      <c r="F36" s="56">
         <f>F34+F35</f>
         <v/>
       </c>
-      <c r="G36" s="55">
+      <c r="G36" s="56">
         <f>G34+G35</f>
         <v/>
       </c>
-      <c r="H36" s="55">
+      <c r="H36" s="56">
         <f>H34+H35</f>
         <v/>
       </c>
-      <c r="I36" s="55">
+      <c r="I36" s="56">
         <f>I34+I35</f>
         <v/>
       </c>
-      <c r="J36" s="55">
+      <c r="J36" s="56">
         <f>J34+J35</f>
         <v/>
       </c>
-      <c r="K36" s="55">
+      <c r="K36" s="56">
         <f>K34+K35</f>
         <v/>
       </c>
-      <c r="L36" s="55">
+      <c r="L36" s="56">
         <f>L34+L35</f>
         <v/>
       </c>
@@ -5173,12 +5173,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="53" t="inlineStr">
+      <c r="A38" s="54" t="inlineStr">
         <is>
           <t>CAC payback</t>
         </is>
       </c>
-      <c r="B38" s="48" t="inlineStr">
+      <c r="B38" s="47" t="inlineStr">
         <is>
           <t>months</t>
         </is>
@@ -6299,12 +6299,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B7" s="48" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -6463,12 +6463,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="47" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -6627,12 +6627,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="47" t="inlineStr">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B17" s="48" t="inlineStr">
+      <c r="B17" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -6791,12 +6791,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="47" t="inlineStr">
+      <c r="A22" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B22" s="48" t="inlineStr">
+      <c r="B22" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -6955,12 +6955,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="47" t="inlineStr">
+      <c r="A27" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B27" s="48" t="inlineStr">
+      <c r="B27" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -7119,12 +7119,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="47" t="inlineStr">
+      <c r="A32" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B32" s="48" t="inlineStr">
+      <c r="B32" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -7283,12 +7283,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="47" t="inlineStr">
+      <c r="A37" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B37" s="48" t="inlineStr">
+      <c r="B37" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -7447,12 +7447,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="47" t="inlineStr">
+      <c r="A42" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B42" s="48" t="inlineStr">
+      <c r="B42" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -7611,12 +7611,12 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="47" t="inlineStr">
+      <c r="A47" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B47" s="48" t="inlineStr">
+      <c r="B47" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -7775,12 +7775,12 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="47" t="inlineStr">
+      <c r="A52" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B52" s="48" t="inlineStr">
+      <c r="B52" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -7939,12 +7939,12 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="47" t="inlineStr">
+      <c r="A57" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B57" s="48" t="inlineStr">
+      <c r="B57" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -8103,12 +8103,12 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="47" t="inlineStr">
+      <c r="A62" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B62" s="48" t="inlineStr">
+      <c r="B62" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -8267,12 +8267,12 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="47" t="inlineStr">
+      <c r="A67" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B67" s="48" t="inlineStr">
+      <c r="B67" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -8431,12 +8431,12 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="47" t="inlineStr">
+      <c r="A72" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  VARIANCE</t>
         </is>
       </c>
-      <c r="B72" s="48" t="inlineStr">
+      <c r="B72" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -8490,12 +8490,12 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="47" t="inlineStr">
+      <c r="A75" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  Assets less liabilities and equity</t>
         </is>
       </c>
-      <c r="B75" s="48" t="inlineStr">
+      <c r="B75" s="47" t="inlineStr">
         <is>
           <t>must be 0</t>
         </is>
@@ -9969,7 +9969,7 @@
           <t>Mix check (must be 100%)</t>
         </is>
       </c>
-      <c r="B21" s="56">
+      <c r="B21" s="57">
         <f>B18+B19+B20</f>
         <v/>
       </c>
@@ -10101,7 +10101,7 @@
           <t>Benchmark midpoint</t>
         </is>
       </c>
-      <c r="B31" s="56">
+      <c r="B31" s="57">
         <f>(B29+B30)/2</f>
         <v/>
       </c>
@@ -10144,7 +10144,7 @@
           <t>Blended benchmark churn</t>
         </is>
       </c>
-      <c r="B34" s="56">
+      <c r="B34" s="57">
         <f>B31*(1-B33)+B31*B32*B33</f>
         <v/>
       </c>
@@ -10521,7 +10521,7 @@
           <t>Y10 athletes in the plan</t>
         </is>
       </c>
-      <c r="B60" s="46">
+      <c r="B60" s="49">
         <f>Assumptions!$L$5</f>
         <v/>
       </c>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="B40" s="41">
-        <f>Assumptions!$C$94</f>
+        <f>Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="C40" s="103" t="inlineStr">
@@ -11806,9 +11806,10 @@
           <t>WACC / discount rate</t>
         </is>
       </c>
-      <c r="B41" s="41">
-        <f>Assumptions!$C$91</f>
-        <v/>
+      <c r="B41" s="101" t="inlineStr">
+        <is>
+          <t>see model</t>
+        </is>
       </c>
       <c r="C41" s="96" t="inlineStr">
         <is>
@@ -11843,7 +11844,7 @@
         </is>
       </c>
       <c r="B42" s="41">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="C42" s="96" t="inlineStr">
@@ -11879,7 +11880,7 @@
         </is>
       </c>
       <c r="B43" s="41">
-        <f>Assumptions!$C$92</f>
+        <f>Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="C43" s="96" t="inlineStr">
@@ -12051,7 +12052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N95"/>
+  <dimension ref="A1:N98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -15696,7 +15697,7 @@
     <row r="91">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>WACC / discount rate</t>
+          <t xml:space="preserve">  Mature listed software, Europe, in EUR</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
@@ -15704,8 +15705,8 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C91" s="24" t="n">
-        <v>0.25</v>
+      <c r="C91" s="44" t="n">
+        <v>0.0601</v>
       </c>
       <c r="D91" s="31">
         <f>C91</f>
@@ -15745,14 +15746,14 @@
       </c>
       <c r="N91" s="26" t="inlineStr">
         <is>
-          <t>Early-stage venture hurdle</t>
+          <t>Damodaran, NYU Stern, Cost of Capital by Industry (Europe), 5 Jan 2026. 23 listed firms</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t xml:space="preserve">  Spain country risk premium</t>
         </is>
       </c>
       <c r="B92" s="22" t="inlineStr">
@@ -15760,8 +15761,8 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C92" s="24" t="n">
-        <v>0.03</v>
+      <c r="C92" s="44" t="n">
+        <v>0.0155</v>
       </c>
       <c r="D92" s="31">
         <f>C92</f>
@@ -15799,123 +15800,129 @@
         <f>C92</f>
         <v/>
       </c>
+      <c r="N92" s="26" t="inlineStr">
+        <is>
+          <t>Damodaran, country risk premiums, 5 Jan 2026. The sector figure above is pan-European; the company is Spanish</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t>Exit revenue multiple</t>
+          <t xml:space="preserve">  Size and stage premium</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C93" s="29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D93" s="39">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C93" s="24" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="D93" s="31">
         <f>C93</f>
         <v/>
       </c>
-      <c r="E93" s="39">
+      <c r="E93" s="31">
         <f>C93</f>
         <v/>
       </c>
-      <c r="F93" s="39">
+      <c r="F93" s="31">
         <f>C93</f>
         <v/>
       </c>
-      <c r="G93" s="39">
+      <c r="G93" s="31">
         <f>C93</f>
         <v/>
       </c>
-      <c r="H93" s="39">
+      <c r="H93" s="31">
         <f>C93</f>
         <v/>
       </c>
-      <c r="I93" s="39">
+      <c r="I93" s="31">
         <f>C93</f>
         <v/>
       </c>
-      <c r="J93" s="39">
+      <c r="J93" s="31">
         <f>C93</f>
         <v/>
       </c>
-      <c r="K93" s="39">
+      <c r="K93" s="31">
         <f>C93</f>
         <v/>
       </c>
-      <c r="L93" s="39">
+      <c r="L93" s="31">
         <f>C93</f>
         <v/>
       </c>
       <c r="N93" s="26" t="inlineStr">
         <is>
-          <t>Blended marketplace + SaaS comparables</t>
+          <t>NOT SOURCED. A pre-revenue company with one product and no operating history does not finance itself at a listed company's cost of capital. Convention puts early-stage venture at 20-35% all-in. The largest single judgement in the valuation</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="21" t="inlineStr">
-        <is>
-          <t>Risk-free rate (Spanish 10Y)</t>
-        </is>
-      </c>
-      <c r="B94" s="22" t="inlineStr">
+      <c r="A94" s="46" t="inlineStr">
+        <is>
+          <t>WACC / discount rate</t>
+        </is>
+      </c>
+      <c r="B94" s="47" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C94" s="44" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="D94" s="31">
-        <f>C94</f>
-        <v/>
-      </c>
-      <c r="E94" s="31">
-        <f>C94</f>
-        <v/>
-      </c>
-      <c r="F94" s="31">
-        <f>C94</f>
-        <v/>
-      </c>
-      <c r="G94" s="31">
-        <f>C94</f>
-        <v/>
-      </c>
-      <c r="H94" s="31">
-        <f>C94</f>
-        <v/>
-      </c>
-      <c r="I94" s="31">
-        <f>C94</f>
-        <v/>
-      </c>
-      <c r="J94" s="31">
-        <f>C94</f>
-        <v/>
-      </c>
-      <c r="K94" s="31">
-        <f>C94</f>
-        <v/>
-      </c>
-      <c r="L94" s="31">
-        <f>C94</f>
+      <c r="C94" s="48">
+        <f>C91+C92+C93</f>
+        <v/>
+      </c>
+      <c r="D94" s="48">
+        <f>D91+D92+D93</f>
+        <v/>
+      </c>
+      <c r="E94" s="48">
+        <f>E91+E92+E93</f>
+        <v/>
+      </c>
+      <c r="F94" s="48">
+        <f>F91+F92+F93</f>
+        <v/>
+      </c>
+      <c r="G94" s="48">
+        <f>G91+G92+G93</f>
+        <v/>
+      </c>
+      <c r="H94" s="48">
+        <f>H91+H92+H93</f>
+        <v/>
+      </c>
+      <c r="I94" s="48">
+        <f>I91+I92+I93</f>
+        <v/>
+      </c>
+      <c r="J94" s="48">
+        <f>J91+J92+J93</f>
+        <v/>
+      </c>
+      <c r="K94" s="48">
+        <f>K91+K92+K93</f>
+        <v/>
+      </c>
+      <c r="L94" s="48">
+        <f>L91+L92+L93</f>
         <v/>
       </c>
       <c r="N94" s="26" t="inlineStr">
         <is>
-          <t>Spanish 10Y government bond, mid-2026</t>
+          <t>The sum of the three rows above. Trace precedents from here to see which parts are published and which is judgement</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>Founder alternative return</t>
+          <t>Terminal growth</t>
         </is>
       </c>
       <c r="B95" s="22" t="inlineStr">
@@ -15924,7 +15931,7 @@
         </is>
       </c>
       <c r="C95" s="24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="D95" s="31">
         <f>C95</f>
@@ -15960,6 +15967,169 @@
       </c>
       <c r="L95" s="31">
         <f>C95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="21" t="inlineStr">
+        <is>
+          <t>Exit revenue multiple</t>
+        </is>
+      </c>
+      <c r="B96" s="22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C96" s="29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D96" s="39">
+        <f>C96</f>
+        <v/>
+      </c>
+      <c r="E96" s="39">
+        <f>C96</f>
+        <v/>
+      </c>
+      <c r="F96" s="39">
+        <f>C96</f>
+        <v/>
+      </c>
+      <c r="G96" s="39">
+        <f>C96</f>
+        <v/>
+      </c>
+      <c r="H96" s="39">
+        <f>C96</f>
+        <v/>
+      </c>
+      <c r="I96" s="39">
+        <f>C96</f>
+        <v/>
+      </c>
+      <c r="J96" s="39">
+        <f>C96</f>
+        <v/>
+      </c>
+      <c r="K96" s="39">
+        <f>C96</f>
+        <v/>
+      </c>
+      <c r="L96" s="39">
+        <f>C96</f>
+        <v/>
+      </c>
+      <c r="N96" s="26" t="inlineStr">
+        <is>
+          <t>Blended marketplace + SaaS comparables</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="21" t="inlineStr">
+        <is>
+          <t>Risk-free rate (Spanish 10Y)</t>
+        </is>
+      </c>
+      <c r="B97" s="22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C97" s="44" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="D97" s="31">
+        <f>C97</f>
+        <v/>
+      </c>
+      <c r="E97" s="31">
+        <f>C97</f>
+        <v/>
+      </c>
+      <c r="F97" s="31">
+        <f>C97</f>
+        <v/>
+      </c>
+      <c r="G97" s="31">
+        <f>C97</f>
+        <v/>
+      </c>
+      <c r="H97" s="31">
+        <f>C97</f>
+        <v/>
+      </c>
+      <c r="I97" s="31">
+        <f>C97</f>
+        <v/>
+      </c>
+      <c r="J97" s="31">
+        <f>C97</f>
+        <v/>
+      </c>
+      <c r="K97" s="31">
+        <f>C97</f>
+        <v/>
+      </c>
+      <c r="L97" s="31">
+        <f>C97</f>
+        <v/>
+      </c>
+      <c r="N97" s="26" t="inlineStr">
+        <is>
+          <t>Spanish 10Y government bond, mid-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="inlineStr">
+        <is>
+          <t>Founder alternative return</t>
+        </is>
+      </c>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C98" s="24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D98" s="31">
+        <f>C98</f>
+        <v/>
+      </c>
+      <c r="E98" s="31">
+        <f>C98</f>
+        <v/>
+      </c>
+      <c r="F98" s="31">
+        <f>C98</f>
+        <v/>
+      </c>
+      <c r="G98" s="31">
+        <f>C98</f>
+        <v/>
+      </c>
+      <c r="H98" s="31">
+        <f>C98</f>
+        <v/>
+      </c>
+      <c r="I98" s="31">
+        <f>C98</f>
+        <v/>
+      </c>
+      <c r="J98" s="31">
+        <f>C98</f>
+        <v/>
+      </c>
+      <c r="K98" s="31">
+        <f>C98</f>
+        <v/>
+      </c>
+      <c r="L98" s="31">
+        <f>C98</f>
         <v/>
       </c>
     </row>
@@ -16334,43 +16504,43 @@
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr"/>
-      <c r="C11" s="46">
+      <c r="C11" s="49">
         <f>MAX(0,C6-IF(1=1,0,C6)+C10)</f>
         <v/>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="49">
         <f>MAX(0,D6-IF(2=1,0,C6)+D10)</f>
         <v/>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="49">
         <f>MAX(0,E6-IF(3=1,0,D6)+E10)</f>
         <v/>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="49">
         <f>MAX(0,F6-IF(4=1,0,E6)+F10)</f>
         <v/>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="49">
         <f>MAX(0,G6-IF(5=1,0,F6)+G10)</f>
         <v/>
       </c>
-      <c r="H11" s="46">
+      <c r="H11" s="49">
         <f>MAX(0,H6-IF(6=1,0,G6)+H10)</f>
         <v/>
       </c>
-      <c r="I11" s="46">
+      <c r="I11" s="49">
         <f>MAX(0,I6-IF(7=1,0,H6)+I10)</f>
         <v/>
       </c>
-      <c r="J11" s="46">
+      <c r="J11" s="49">
         <f>MAX(0,J6-IF(8=1,0,I6)+J10)</f>
         <v/>
       </c>
-      <c r="K11" s="46">
+      <c r="K11" s="49">
         <f>MAX(0,K6-IF(9=1,0,J6)+K10)</f>
         <v/>
       </c>
-      <c r="L11" s="46">
+      <c r="L11" s="49">
         <f>MAX(0,L6-IF(10=1,0,K6)+L10)</f>
         <v/>
       </c>
@@ -16534,43 +16704,43 @@
           <t>open x r^12</t>
         </is>
       </c>
-      <c r="C15" s="46">
+      <c r="C15" s="49">
         <f>0</f>
         <v/>
       </c>
-      <c r="D15" s="46">
+      <c r="D15" s="49">
         <f>C17*D14^12</f>
         <v/>
       </c>
-      <c r="E15" s="46">
+      <c r="E15" s="49">
         <f>D17*E14^12</f>
         <v/>
       </c>
-      <c r="F15" s="46">
+      <c r="F15" s="49">
         <f>E17*F14^12</f>
         <v/>
       </c>
-      <c r="G15" s="46">
+      <c r="G15" s="49">
         <f>F17*G14^12</f>
         <v/>
       </c>
-      <c r="H15" s="46">
+      <c r="H15" s="49">
         <f>G17*H14^12</f>
         <v/>
       </c>
-      <c r="I15" s="46">
+      <c r="I15" s="49">
         <f>H17*I14^12</f>
         <v/>
       </c>
-      <c r="J15" s="46">
+      <c r="J15" s="49">
         <f>I17*J14^12</f>
         <v/>
       </c>
-      <c r="K15" s="46">
+      <c r="K15" s="49">
         <f>J17*K14^12</f>
         <v/>
       </c>
-      <c r="L15" s="46">
+      <c r="L15" s="49">
         <f>K17*L14^12</f>
         <v/>
       </c>
@@ -16628,53 +16798,53 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="47" t="inlineStr">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>Niche paying fans (year end)</t>
         </is>
       </c>
-      <c r="B17" s="48" t="inlineStr">
+      <c r="B17" s="47" t="inlineStr">
         <is>
           <t>survivors + capped adds</t>
         </is>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="50">
         <f>C15+C16*(1-C14^12)/(1-C14)</f>
         <v/>
       </c>
-      <c r="D17" s="49">
+      <c r="D17" s="50">
         <f>D15+D16*(1-D14^12)/(1-D14)</f>
         <v/>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="50">
         <f>E15+E16*(1-E14^12)/(1-E14)</f>
         <v/>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="50">
         <f>F15+F16*(1-F14^12)/(1-F14)</f>
         <v/>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="50">
         <f>G15+G16*(1-G14^12)/(1-G14)</f>
         <v/>
       </c>
-      <c r="H17" s="49">
+      <c r="H17" s="50">
         <f>H15+H16*(1-H14^12)/(1-H14)</f>
         <v/>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="50">
         <f>I15+I16*(1-I14^12)/(1-I14)</f>
         <v/>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="50">
         <f>J15+J16*(1-J14^12)/(1-J14)</f>
         <v/>
       </c>
-      <c r="K17" s="49">
+      <c r="K17" s="50">
         <f>K15+K16*(1-K14^12)/(1-K14)</f>
         <v/>
       </c>
-      <c r="L17" s="49">
+      <c r="L17" s="50">
         <f>L15+L16*(1-L14^12)/(1-L14)</f>
         <v/>
       </c>
@@ -16690,43 +16860,43 @@
           <t>x12 months</t>
         </is>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="49">
         <f>C16*12</f>
         <v/>
       </c>
-      <c r="D18" s="46">
+      <c r="D18" s="49">
         <f>D16*12</f>
         <v/>
       </c>
-      <c r="E18" s="46">
+      <c r="E18" s="49">
         <f>E16*12</f>
         <v/>
       </c>
-      <c r="F18" s="46">
+      <c r="F18" s="49">
         <f>F16*12</f>
         <v/>
       </c>
-      <c r="G18" s="46">
+      <c r="G18" s="49">
         <f>G16*12</f>
         <v/>
       </c>
-      <c r="H18" s="46">
+      <c r="H18" s="49">
         <f>H16*12</f>
         <v/>
       </c>
-      <c r="I18" s="46">
+      <c r="I18" s="49">
         <f>I16*12</f>
         <v/>
       </c>
-      <c r="J18" s="46">
+      <c r="J18" s="49">
         <f>J16*12</f>
         <v/>
       </c>
-      <c r="K18" s="46">
+      <c r="K18" s="49">
         <f>K16*12</f>
         <v/>
       </c>
-      <c r="L18" s="46">
+      <c r="L18" s="49">
         <f>L16*12</f>
         <v/>
       </c>
@@ -16742,95 +16912,95 @@
           <t>geometric sum</t>
         </is>
       </c>
-      <c r="C19" s="50">
+      <c r="C19" s="51">
         <f>C14*(1-C14^12)/(1-C14)</f>
         <v/>
       </c>
-      <c r="D19" s="50">
+      <c r="D19" s="51">
         <f>D14*(1-D14^12)/(1-D14)</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="51">
         <f>E14*(1-E14^12)/(1-E14)</f>
         <v/>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="51">
         <f>F14*(1-F14^12)/(1-F14)</f>
         <v/>
       </c>
-      <c r="G19" s="50">
+      <c r="G19" s="51">
         <f>G14*(1-G14^12)/(1-G14)</f>
         <v/>
       </c>
-      <c r="H19" s="50">
+      <c r="H19" s="51">
         <f>H14*(1-H14^12)/(1-H14)</f>
         <v/>
       </c>
-      <c r="I19" s="50">
+      <c r="I19" s="51">
         <f>I14*(1-I14^12)/(1-I14)</f>
         <v/>
       </c>
-      <c r="J19" s="50">
+      <c r="J19" s="51">
         <f>J14*(1-J14^12)/(1-J14)</f>
         <v/>
       </c>
-      <c r="K19" s="50">
+      <c r="K19" s="51">
         <f>K14*(1-K14^12)/(1-K14)</f>
         <v/>
       </c>
-      <c r="L19" s="50">
+      <c r="L19" s="51">
         <f>L14*(1-L14^12)/(1-L14)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="47" t="inlineStr">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>Niche average fans during year</t>
         </is>
       </c>
-      <c r="B20" s="48" t="inlineStr">
+      <c r="B20" s="47" t="inlineStr">
         <is>
           <t>exact mean, revenue basis</t>
         </is>
       </c>
-      <c r="C20" s="49">
+      <c r="C20" s="50">
         <f>(C16/(1-C14)*(12-C19))/12</f>
         <v/>
       </c>
-      <c r="D20" s="49">
+      <c r="D20" s="50">
         <f>(C17*D19+D16/(1-D14)*(12-D19))/12</f>
         <v/>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="50">
         <f>(D17*E19+E16/(1-E14)*(12-E19))/12</f>
         <v/>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="50">
         <f>(E17*F19+F16/(1-F14)*(12-F19))/12</f>
         <v/>
       </c>
-      <c r="G20" s="49">
+      <c r="G20" s="50">
         <f>(F17*G19+G16/(1-G14)*(12-G19))/12</f>
         <v/>
       </c>
-      <c r="H20" s="49">
+      <c r="H20" s="50">
         <f>(G17*H19+H16/(1-H14)*(12-H19))/12</f>
         <v/>
       </c>
-      <c r="I20" s="49">
+      <c r="I20" s="50">
         <f>(H17*I19+I16/(1-I14)*(12-I19))/12</f>
         <v/>
       </c>
-      <c r="J20" s="49">
+      <c r="J20" s="50">
         <f>(I17*J19+J16/(1-J14)*(12-J19))/12</f>
         <v/>
       </c>
-      <c r="K20" s="49">
+      <c r="K20" s="50">
         <f>(J17*K19+K16/(1-K14)*(12-K19))/12</f>
         <v/>
       </c>
-      <c r="L20" s="49">
+      <c r="L20" s="50">
         <f>(K17*L19+L16/(1-L14)*(12-L19))/12</f>
         <v/>
       </c>
@@ -16960,43 +17130,43 @@
         </is>
       </c>
       <c r="B25" s="22" t="inlineStr"/>
-      <c r="C25" s="46">
+      <c r="C25" s="49">
         <f>MAX(0,C7-IF(1=1,0,C7)+C24)</f>
         <v/>
       </c>
-      <c r="D25" s="46">
+      <c r="D25" s="49">
         <f>MAX(0,D7-IF(2=1,0,C7)+D24)</f>
         <v/>
       </c>
-      <c r="E25" s="46">
+      <c r="E25" s="49">
         <f>MAX(0,E7-IF(3=1,0,D7)+E24)</f>
         <v/>
       </c>
-      <c r="F25" s="46">
+      <c r="F25" s="49">
         <f>MAX(0,F7-IF(4=1,0,E7)+F24)</f>
         <v/>
       </c>
-      <c r="G25" s="46">
+      <c r="G25" s="49">
         <f>MAX(0,G7-IF(5=1,0,F7)+G24)</f>
         <v/>
       </c>
-      <c r="H25" s="46">
+      <c r="H25" s="49">
         <f>MAX(0,H7-IF(6=1,0,G7)+H24)</f>
         <v/>
       </c>
-      <c r="I25" s="46">
+      <c r="I25" s="49">
         <f>MAX(0,I7-IF(7=1,0,H7)+I24)</f>
         <v/>
       </c>
-      <c r="J25" s="46">
+      <c r="J25" s="49">
         <f>MAX(0,J7-IF(8=1,0,I7)+J24)</f>
         <v/>
       </c>
-      <c r="K25" s="46">
+      <c r="K25" s="49">
         <f>MAX(0,K7-IF(9=1,0,J7)+K24)</f>
         <v/>
       </c>
-      <c r="L25" s="46">
+      <c r="L25" s="49">
         <f>MAX(0,L7-IF(10=1,0,K7)+L24)</f>
         <v/>
       </c>
@@ -17160,43 +17330,43 @@
           <t>open x r^12</t>
         </is>
       </c>
-      <c r="C29" s="46">
+      <c r="C29" s="49">
         <f>0</f>
         <v/>
       </c>
-      <c r="D29" s="46">
+      <c r="D29" s="49">
         <f>C31*D28^12</f>
         <v/>
       </c>
-      <c r="E29" s="46">
+      <c r="E29" s="49">
         <f>D31*E28^12</f>
         <v/>
       </c>
-      <c r="F29" s="46">
+      <c r="F29" s="49">
         <f>E31*F28^12</f>
         <v/>
       </c>
-      <c r="G29" s="46">
+      <c r="G29" s="49">
         <f>F31*G28^12</f>
         <v/>
       </c>
-      <c r="H29" s="46">
+      <c r="H29" s="49">
         <f>G31*H28^12</f>
         <v/>
       </c>
-      <c r="I29" s="46">
+      <c r="I29" s="49">
         <f>H31*I28^12</f>
         <v/>
       </c>
-      <c r="J29" s="46">
+      <c r="J29" s="49">
         <f>I31*J28^12</f>
         <v/>
       </c>
-      <c r="K29" s="46">
+      <c r="K29" s="49">
         <f>J31*K28^12</f>
         <v/>
       </c>
-      <c r="L29" s="46">
+      <c r="L29" s="49">
         <f>K31*L28^12</f>
         <v/>
       </c>
@@ -17254,53 +17424,53 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="47" t="inlineStr">
+      <c r="A31" s="46" t="inlineStr">
         <is>
           <t>Popular paying fans (year end)</t>
         </is>
       </c>
-      <c r="B31" s="48" t="inlineStr">
+      <c r="B31" s="47" t="inlineStr">
         <is>
           <t>survivors + capped adds</t>
         </is>
       </c>
-      <c r="C31" s="49">
+      <c r="C31" s="50">
         <f>C29+C30*(1-C28^12)/(1-C28)</f>
         <v/>
       </c>
-      <c r="D31" s="49">
+      <c r="D31" s="50">
         <f>D29+D30*(1-D28^12)/(1-D28)</f>
         <v/>
       </c>
-      <c r="E31" s="49">
+      <c r="E31" s="50">
         <f>E29+E30*(1-E28^12)/(1-E28)</f>
         <v/>
       </c>
-      <c r="F31" s="49">
+      <c r="F31" s="50">
         <f>F29+F30*(1-F28^12)/(1-F28)</f>
         <v/>
       </c>
-      <c r="G31" s="49">
+      <c r="G31" s="50">
         <f>G29+G30*(1-G28^12)/(1-G28)</f>
         <v/>
       </c>
-      <c r="H31" s="49">
+      <c r="H31" s="50">
         <f>H29+H30*(1-H28^12)/(1-H28)</f>
         <v/>
       </c>
-      <c r="I31" s="49">
+      <c r="I31" s="50">
         <f>I29+I30*(1-I28^12)/(1-I28)</f>
         <v/>
       </c>
-      <c r="J31" s="49">
+      <c r="J31" s="50">
         <f>J29+J30*(1-J28^12)/(1-J28)</f>
         <v/>
       </c>
-      <c r="K31" s="49">
+      <c r="K31" s="50">
         <f>K29+K30*(1-K28^12)/(1-K28)</f>
         <v/>
       </c>
-      <c r="L31" s="49">
+      <c r="L31" s="50">
         <f>L29+L30*(1-L28^12)/(1-L28)</f>
         <v/>
       </c>
@@ -17316,43 +17486,43 @@
           <t>x12 months</t>
         </is>
       </c>
-      <c r="C32" s="46">
+      <c r="C32" s="49">
         <f>C30*12</f>
         <v/>
       </c>
-      <c r="D32" s="46">
+      <c r="D32" s="49">
         <f>D30*12</f>
         <v/>
       </c>
-      <c r="E32" s="46">
+      <c r="E32" s="49">
         <f>E30*12</f>
         <v/>
       </c>
-      <c r="F32" s="46">
+      <c r="F32" s="49">
         <f>F30*12</f>
         <v/>
       </c>
-      <c r="G32" s="46">
+      <c r="G32" s="49">
         <f>G30*12</f>
         <v/>
       </c>
-      <c r="H32" s="46">
+      <c r="H32" s="49">
         <f>H30*12</f>
         <v/>
       </c>
-      <c r="I32" s="46">
+      <c r="I32" s="49">
         <f>I30*12</f>
         <v/>
       </c>
-      <c r="J32" s="46">
+      <c r="J32" s="49">
         <f>J30*12</f>
         <v/>
       </c>
-      <c r="K32" s="46">
+      <c r="K32" s="49">
         <f>K30*12</f>
         <v/>
       </c>
-      <c r="L32" s="46">
+      <c r="L32" s="49">
         <f>L30*12</f>
         <v/>
       </c>
@@ -17368,95 +17538,95 @@
           <t>geometric sum</t>
         </is>
       </c>
-      <c r="C33" s="50">
+      <c r="C33" s="51">
         <f>C28*(1-C28^12)/(1-C28)</f>
         <v/>
       </c>
-      <c r="D33" s="50">
+      <c r="D33" s="51">
         <f>D28*(1-D28^12)/(1-D28)</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="51">
         <f>E28*(1-E28^12)/(1-E28)</f>
         <v/>
       </c>
-      <c r="F33" s="50">
+      <c r="F33" s="51">
         <f>F28*(1-F28^12)/(1-F28)</f>
         <v/>
       </c>
-      <c r="G33" s="50">
+      <c r="G33" s="51">
         <f>G28*(1-G28^12)/(1-G28)</f>
         <v/>
       </c>
-      <c r="H33" s="50">
+      <c r="H33" s="51">
         <f>H28*(1-H28^12)/(1-H28)</f>
         <v/>
       </c>
-      <c r="I33" s="50">
+      <c r="I33" s="51">
         <f>I28*(1-I28^12)/(1-I28)</f>
         <v/>
       </c>
-      <c r="J33" s="50">
+      <c r="J33" s="51">
         <f>J28*(1-J28^12)/(1-J28)</f>
         <v/>
       </c>
-      <c r="K33" s="50">
+      <c r="K33" s="51">
         <f>K28*(1-K28^12)/(1-K28)</f>
         <v/>
       </c>
-      <c r="L33" s="50">
+      <c r="L33" s="51">
         <f>L28*(1-L28^12)/(1-L28)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="47" t="inlineStr">
+      <c r="A34" s="46" t="inlineStr">
         <is>
           <t>Popular average fans during year</t>
         </is>
       </c>
-      <c r="B34" s="48" t="inlineStr">
+      <c r="B34" s="47" t="inlineStr">
         <is>
           <t>exact mean, revenue basis</t>
         </is>
       </c>
-      <c r="C34" s="49">
+      <c r="C34" s="50">
         <f>(C30/(1-C28)*(12-C33))/12</f>
         <v/>
       </c>
-      <c r="D34" s="49">
+      <c r="D34" s="50">
         <f>(C31*D33+D30/(1-D28)*(12-D33))/12</f>
         <v/>
       </c>
-      <c r="E34" s="49">
+      <c r="E34" s="50">
         <f>(D31*E33+E30/(1-E28)*(12-E33))/12</f>
         <v/>
       </c>
-      <c r="F34" s="49">
+      <c r="F34" s="50">
         <f>(E31*F33+F30/(1-F28)*(12-F33))/12</f>
         <v/>
       </c>
-      <c r="G34" s="49">
+      <c r="G34" s="50">
         <f>(F31*G33+G30/(1-G28)*(12-G33))/12</f>
         <v/>
       </c>
-      <c r="H34" s="49">
+      <c r="H34" s="50">
         <f>(G31*H33+H30/(1-H28)*(12-H33))/12</f>
         <v/>
       </c>
-      <c r="I34" s="49">
+      <c r="I34" s="50">
         <f>(H31*I33+I30/(1-I28)*(12-I33))/12</f>
         <v/>
       </c>
-      <c r="J34" s="49">
+      <c r="J34" s="50">
         <f>(I31*J33+J30/(1-J28)*(12-J33))/12</f>
         <v/>
       </c>
-      <c r="K34" s="49">
+      <c r="K34" s="50">
         <f>(J31*K33+K30/(1-K28)*(12-K33))/12</f>
         <v/>
       </c>
-      <c r="L34" s="49">
+      <c r="L34" s="50">
         <f>(K31*L33+L30/(1-L28)*(12-L33))/12</f>
         <v/>
       </c>
@@ -17532,97 +17702,97 @@
       <c r="L37" s="20" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="47" t="inlineStr">
+      <c r="A38" s="46" t="inlineStr">
         <is>
           <t>Paying fans (year end)</t>
         </is>
       </c>
-      <c r="B38" s="48" t="inlineStr"/>
-      <c r="C38" s="49">
+      <c r="B38" s="47" t="inlineStr"/>
+      <c r="C38" s="50">
         <f>C17+C31</f>
         <v/>
       </c>
-      <c r="D38" s="49">
+      <c r="D38" s="50">
         <f>D17+D31</f>
         <v/>
       </c>
-      <c r="E38" s="49">
+      <c r="E38" s="50">
         <f>E17+E31</f>
         <v/>
       </c>
-      <c r="F38" s="49">
+      <c r="F38" s="50">
         <f>F17+F31</f>
         <v/>
       </c>
-      <c r="G38" s="49">
+      <c r="G38" s="50">
         <f>G17+G31</f>
         <v/>
       </c>
-      <c r="H38" s="49">
+      <c r="H38" s="50">
         <f>H17+H31</f>
         <v/>
       </c>
-      <c r="I38" s="49">
+      <c r="I38" s="50">
         <f>I17+I31</f>
         <v/>
       </c>
-      <c r="J38" s="49">
+      <c r="J38" s="50">
         <f>J17+J31</f>
         <v/>
       </c>
-      <c r="K38" s="49">
+      <c r="K38" s="50">
         <f>K17+K31</f>
         <v/>
       </c>
-      <c r="L38" s="49">
+      <c r="L38" s="50">
         <f>L17+L31</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="47" t="inlineStr">
+      <c r="A39" s="46" t="inlineStr">
         <is>
           <t>Average paying fans</t>
         </is>
       </c>
-      <c r="B39" s="48" t="inlineStr"/>
-      <c r="C39" s="49">
+      <c r="B39" s="47" t="inlineStr"/>
+      <c r="C39" s="50">
         <f>C20+C34</f>
         <v/>
       </c>
-      <c r="D39" s="49">
+      <c r="D39" s="50">
         <f>D20+D34</f>
         <v/>
       </c>
-      <c r="E39" s="49">
+      <c r="E39" s="50">
         <f>E20+E34</f>
         <v/>
       </c>
-      <c r="F39" s="49">
+      <c r="F39" s="50">
         <f>F20+F34</f>
         <v/>
       </c>
-      <c r="G39" s="49">
+      <c r="G39" s="50">
         <f>G20+G34</f>
         <v/>
       </c>
-      <c r="H39" s="49">
+      <c r="H39" s="50">
         <f>H20+H34</f>
         <v/>
       </c>
-      <c r="I39" s="49">
+      <c r="I39" s="50">
         <f>I20+I34</f>
         <v/>
       </c>
-      <c r="J39" s="49">
+      <c r="J39" s="50">
         <f>J20+J34</f>
         <v/>
       </c>
-      <c r="K39" s="49">
+      <c r="K39" s="50">
         <f>K20+K34</f>
         <v/>
       </c>
-      <c r="L39" s="49">
+      <c r="L39" s="50">
         <f>L20+L34</f>
         <v/>
       </c>
@@ -17634,43 +17804,43 @@
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr"/>
-      <c r="C40" s="46">
+      <c r="C40" s="49">
         <f>C11+C25</f>
         <v/>
       </c>
-      <c r="D40" s="46">
+      <c r="D40" s="49">
         <f>D11+D25</f>
         <v/>
       </c>
-      <c r="E40" s="46">
+      <c r="E40" s="49">
         <f>E11+E25</f>
         <v/>
       </c>
-      <c r="F40" s="46">
+      <c r="F40" s="49">
         <f>F11+F25</f>
         <v/>
       </c>
-      <c r="G40" s="46">
+      <c r="G40" s="49">
         <f>G11+G25</f>
         <v/>
       </c>
-      <c r="H40" s="46">
+      <c r="H40" s="49">
         <f>H11+H25</f>
         <v/>
       </c>
-      <c r="I40" s="46">
+      <c r="I40" s="49">
         <f>I11+I25</f>
         <v/>
       </c>
-      <c r="J40" s="46">
+      <c r="J40" s="49">
         <f>J11+J25</f>
         <v/>
       </c>
-      <c r="K40" s="46">
+      <c r="K40" s="49">
         <f>K11+K25</f>
         <v/>
       </c>
-      <c r="L40" s="46">
+      <c r="L40" s="49">
         <f>L11+L25</f>
         <v/>
       </c>
@@ -17682,43 +17852,43 @@
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr"/>
-      <c r="C41" s="46">
+      <c r="C41" s="49">
         <f>C21+C35</f>
         <v/>
       </c>
-      <c r="D41" s="46">
+      <c r="D41" s="49">
         <f>D21+D35</f>
         <v/>
       </c>
-      <c r="E41" s="46">
+      <c r="E41" s="49">
         <f>E21+E35</f>
         <v/>
       </c>
-      <c r="F41" s="46">
+      <c r="F41" s="49">
         <f>F21+F35</f>
         <v/>
       </c>
-      <c r="G41" s="46">
+      <c r="G41" s="49">
         <f>G21+G35</f>
         <v/>
       </c>
-      <c r="H41" s="46">
+      <c r="H41" s="49">
         <f>H21+H35</f>
         <v/>
       </c>
-      <c r="I41" s="46">
+      <c r="I41" s="49">
         <f>I21+I35</f>
         <v/>
       </c>
-      <c r="J41" s="46">
+      <c r="J41" s="49">
         <f>J21+J35</f>
         <v/>
       </c>
-      <c r="K41" s="46">
+      <c r="K41" s="49">
         <f>K21+K35</f>
         <v/>
       </c>
-      <c r="L41" s="46">
+      <c r="L41" s="49">
         <f>L21+L35</f>
         <v/>
       </c>
@@ -17838,49 +18008,49 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="47" t="inlineStr">
+      <c r="A46" s="46" t="inlineStr">
         <is>
           <t>Total deals</t>
         </is>
       </c>
-      <c r="B46" s="48" t="inlineStr"/>
-      <c r="C46" s="49">
+      <c r="B46" s="47" t="inlineStr"/>
+      <c r="C46" s="50">
         <f>C44+C45</f>
         <v/>
       </c>
-      <c r="D46" s="49">
+      <c r="D46" s="50">
         <f>D44+D45</f>
         <v/>
       </c>
-      <c r="E46" s="49">
+      <c r="E46" s="50">
         <f>E44+E45</f>
         <v/>
       </c>
-      <c r="F46" s="49">
+      <c r="F46" s="50">
         <f>F44+F45</f>
         <v/>
       </c>
-      <c r="G46" s="49">
+      <c r="G46" s="50">
         <f>G44+G45</f>
         <v/>
       </c>
-      <c r="H46" s="49">
+      <c r="H46" s="50">
         <f>H44+H45</f>
         <v/>
       </c>
-      <c r="I46" s="49">
+      <c r="I46" s="50">
         <f>I44+I45</f>
         <v/>
       </c>
-      <c r="J46" s="49">
+      <c r="J46" s="50">
         <f>J44+J45</f>
         <v/>
       </c>
-      <c r="K46" s="49">
+      <c r="K46" s="50">
         <f>K44+K45</f>
         <v/>
       </c>
-      <c r="L46" s="49">
+      <c r="L46" s="50">
         <f>L44+L45</f>
         <v/>
       </c>
@@ -18166,43 +18336,43 @@
           <t>gross adds / admission rate</t>
         </is>
       </c>
-      <c r="C54" s="46">
+      <c r="C54" s="49">
         <f>C40/C52</f>
         <v/>
       </c>
-      <c r="D54" s="46">
+      <c r="D54" s="49">
         <f>D40/D52</f>
         <v/>
       </c>
-      <c r="E54" s="46">
+      <c r="E54" s="49">
         <f>E40/E52</f>
         <v/>
       </c>
-      <c r="F54" s="46">
+      <c r="F54" s="49">
         <f>F40/F52</f>
         <v/>
       </c>
-      <c r="G54" s="46">
+      <c r="G54" s="49">
         <f>G40/G52</f>
         <v/>
       </c>
-      <c r="H54" s="46">
+      <c r="H54" s="49">
         <f>H40/H52</f>
         <v/>
       </c>
-      <c r="I54" s="46">
+      <c r="I54" s="49">
         <f>I40/I52</f>
         <v/>
       </c>
-      <c r="J54" s="46">
+      <c r="J54" s="49">
         <f>J40/J52</f>
         <v/>
       </c>
-      <c r="K54" s="46">
+      <c r="K54" s="49">
         <f>K40/K52</f>
         <v/>
       </c>
-      <c r="L54" s="46">
+      <c r="L54" s="49">
         <f>L40/L52</f>
         <v/>
       </c>
@@ -18218,43 +18388,43 @@
           <t>applications x review rate</t>
         </is>
       </c>
-      <c r="C55" s="46">
+      <c r="C55" s="49">
         <f>C54*C53</f>
         <v/>
       </c>
-      <c r="D55" s="46">
+      <c r="D55" s="49">
         <f>D54*D53</f>
         <v/>
       </c>
-      <c r="E55" s="46">
+      <c r="E55" s="49">
         <f>E54*E53</f>
         <v/>
       </c>
-      <c r="F55" s="46">
+      <c r="F55" s="49">
         <f>F54*F53</f>
         <v/>
       </c>
-      <c r="G55" s="46">
+      <c r="G55" s="49">
         <f>G54*G53</f>
         <v/>
       </c>
-      <c r="H55" s="46">
+      <c r="H55" s="49">
         <f>H54*H53</f>
         <v/>
       </c>
-      <c r="I55" s="46">
+      <c r="I55" s="49">
         <f>I54*I53</f>
         <v/>
       </c>
-      <c r="J55" s="46">
+      <c r="J55" s="49">
         <f>J54*J53</f>
         <v/>
       </c>
-      <c r="K55" s="46">
+      <c r="K55" s="49">
         <f>K54*K53</f>
         <v/>
       </c>
-      <c r="L55" s="46">
+      <c r="L55" s="49">
         <f>L54*L53</f>
         <v/>
       </c>
@@ -18570,49 +18740,49 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>Subscription GMV</t>
         </is>
       </c>
-      <c r="B7" s="48" t="inlineStr"/>
-      <c r="C7" s="51">
+      <c r="B7" s="47" t="inlineStr"/>
+      <c r="C7" s="52">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="52">
         <f>D5+D6</f>
         <v/>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="52">
         <f>E5+E6</f>
         <v/>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="52">
         <f>F5+F6</f>
         <v/>
       </c>
-      <c r="G7" s="51">
+      <c r="G7" s="52">
         <f>G5+G6</f>
         <v/>
       </c>
-      <c r="H7" s="51">
+      <c r="H7" s="52">
         <f>H5+H6</f>
         <v/>
       </c>
-      <c r="I7" s="51">
+      <c r="I7" s="52">
         <f>I5+I6</f>
         <v/>
       </c>
-      <c r="J7" s="51">
+      <c r="J7" s="52">
         <f>J5+J6</f>
         <v/>
       </c>
-      <c r="K7" s="51">
+      <c r="K7" s="52">
         <f>K5+K6</f>
         <v/>
       </c>
-      <c r="L7" s="51">
+      <c r="L7" s="52">
         <f>L5+L6</f>
         <v/>
       </c>
@@ -18670,53 +18840,53 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>Total fan GMV</t>
         </is>
       </c>
-      <c r="B9" s="48" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>ex-VAT, the take base</t>
         </is>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="52">
         <f>C7+C8</f>
         <v/>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="52">
         <f>D7+D8</f>
         <v/>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="52">
         <f>E7+E8</f>
         <v/>
       </c>
-      <c r="F9" s="51">
+      <c r="F9" s="52">
         <f>F7+F8</f>
         <v/>
       </c>
-      <c r="G9" s="51">
+      <c r="G9" s="52">
         <f>G7+G8</f>
         <v/>
       </c>
-      <c r="H9" s="51">
+      <c r="H9" s="52">
         <f>H7+H8</f>
         <v/>
       </c>
-      <c r="I9" s="51">
+      <c r="I9" s="52">
         <f>I7+I8</f>
         <v/>
       </c>
-      <c r="J9" s="51">
+      <c r="J9" s="52">
         <f>J7+J8</f>
         <v/>
       </c>
-      <c r="K9" s="51">
+      <c r="K9" s="52">
         <f>K7+K8</f>
         <v/>
       </c>
-      <c r="L9" s="51">
+      <c r="L9" s="52">
         <f>L7+L8</f>
         <v/>
       </c>
@@ -18888,49 +19058,49 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>Total sponsorship GMV</t>
         </is>
       </c>
-      <c r="B15" s="48" t="inlineStr"/>
-      <c r="C15" s="51">
+      <c r="B15" s="47" t="inlineStr"/>
+      <c r="C15" s="52">
         <f>C13+C14</f>
         <v/>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="52">
         <f>D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="52">
         <f>E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="51">
+      <c r="F15" s="52">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="51">
+      <c r="G15" s="52">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="51">
+      <c r="H15" s="52">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="52">
         <f>I13+I14</f>
         <v/>
       </c>
-      <c r="J15" s="51">
+      <c r="J15" s="52">
         <f>J13+J14</f>
         <v/>
       </c>
-      <c r="K15" s="51">
+      <c r="K15" s="52">
         <f>K13+K14</f>
         <v/>
       </c>
-      <c r="L15" s="51">
+      <c r="L15" s="52">
         <f>L13+L14</f>
         <v/>
       </c>
@@ -19080,97 +19250,97 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="47" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>Effective sponsorship take</t>
         </is>
       </c>
-      <c r="B19" s="48" t="inlineStr"/>
-      <c r="C19" s="52">
+      <c r="B19" s="47" t="inlineStr"/>
+      <c r="C19" s="53">
         <f>(1-C18)*Assumptions!C41+C18*(C17*Assumptions!C41+(1-C17-C16)*Assumptions!C42+C16*Assumptions!C43)</f>
         <v/>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="53">
         <f>(1-D18)*Assumptions!D41+D18*(D17*Assumptions!D41+(1-D17-D16)*Assumptions!D42+D16*Assumptions!D43)</f>
         <v/>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="53">
         <f>(1-E18)*Assumptions!E41+E18*(E17*Assumptions!E41+(1-E17-E16)*Assumptions!E42+E16*Assumptions!E43)</f>
         <v/>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="53">
         <f>(1-F18)*Assumptions!F41+F18*(F17*Assumptions!F41+(1-F17-F16)*Assumptions!F42+F16*Assumptions!F43)</f>
         <v/>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="53">
         <f>(1-G18)*Assumptions!G41+G18*(G17*Assumptions!G41+(1-G17-G16)*Assumptions!G42+G16*Assumptions!G43)</f>
         <v/>
       </c>
-      <c r="H19" s="52">
+      <c r="H19" s="53">
         <f>(1-H18)*Assumptions!H41+H18*(H17*Assumptions!H41+(1-H17-H16)*Assumptions!H42+H16*Assumptions!H43)</f>
         <v/>
       </c>
-      <c r="I19" s="52">
+      <c r="I19" s="53">
         <f>(1-I18)*Assumptions!I41+I18*(I17*Assumptions!I41+(1-I17-I16)*Assumptions!I42+I16*Assumptions!I43)</f>
         <v/>
       </c>
-      <c r="J19" s="52">
+      <c r="J19" s="53">
         <f>(1-J18)*Assumptions!J41+J18*(J17*Assumptions!J41+(1-J17-J16)*Assumptions!J42+J16*Assumptions!J43)</f>
         <v/>
       </c>
-      <c r="K19" s="52">
+      <c r="K19" s="53">
         <f>(1-K18)*Assumptions!K41+K18*(K17*Assumptions!K41+(1-K17-K16)*Assumptions!K42+K16*Assumptions!K43)</f>
         <v/>
       </c>
-      <c r="L19" s="52">
+      <c r="L19" s="53">
         <f>(1-L18)*Assumptions!L41+L18*(L17*Assumptions!L41+(1-L17-L16)*Assumptions!L42+L16*Assumptions!L43)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="inlineStr">
+      <c r="A20" s="54" t="inlineStr">
         <is>
           <t>TOTAL GMV</t>
         </is>
       </c>
-      <c r="B20" s="48" t="inlineStr"/>
-      <c r="C20" s="54">
+      <c r="B20" s="47" t="inlineStr"/>
+      <c r="C20" s="55">
         <f>C9+C15</f>
         <v/>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="55">
         <f>D9+D15</f>
         <v/>
       </c>
-      <c r="E20" s="54">
+      <c r="E20" s="55">
         <f>E9+E15</f>
         <v/>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="55">
         <f>F9+F15</f>
         <v/>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="55">
         <f>G9+G15</f>
         <v/>
       </c>
-      <c r="H20" s="54">
+      <c r="H20" s="55">
         <f>H9+H15</f>
         <v/>
       </c>
-      <c r="I20" s="54">
+      <c r="I20" s="55">
         <f>I9+I15</f>
         <v/>
       </c>
-      <c r="J20" s="54">
+      <c r="J20" s="55">
         <f>J9+J15</f>
         <v/>
       </c>
-      <c r="K20" s="54">
+      <c r="K20" s="55">
         <f>K9+K15</f>
         <v/>
       </c>
-      <c r="L20" s="54">
+      <c r="L20" s="55">
         <f>L9+L15</f>
         <v/>
       </c>
@@ -19252,43 +19422,43 @@
         </is>
       </c>
       <c r="B24" s="22" t="inlineStr"/>
-      <c r="C24" s="55">
+      <c r="C24" s="56">
         <f>C15*C19</f>
         <v/>
       </c>
-      <c r="D24" s="55">
+      <c r="D24" s="56">
         <f>D15*D19</f>
         <v/>
       </c>
-      <c r="E24" s="55">
+      <c r="E24" s="56">
         <f>E15*E19</f>
         <v/>
       </c>
-      <c r="F24" s="55">
+      <c r="F24" s="56">
         <f>F15*F19</f>
         <v/>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="56">
         <f>G15*G19</f>
         <v/>
       </c>
-      <c r="H24" s="55">
+      <c r="H24" s="56">
         <f>H15*H19</f>
         <v/>
       </c>
-      <c r="I24" s="55">
+      <c r="I24" s="56">
         <f>I15*I19</f>
         <v/>
       </c>
-      <c r="J24" s="55">
+      <c r="J24" s="56">
         <f>J15*J19</f>
         <v/>
       </c>
-      <c r="K24" s="55">
+      <c r="K24" s="56">
         <f>K15*K19</f>
         <v/>
       </c>
-      <c r="L24" s="55">
+      <c r="L24" s="56">
         <f>L15*L19</f>
         <v/>
       </c>
@@ -19346,49 +19516,49 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="inlineStr">
+      <c r="A26" s="54" t="inlineStr">
         <is>
           <t>NET REVENUE</t>
         </is>
       </c>
-      <c r="B26" s="48" t="inlineStr"/>
-      <c r="C26" s="54">
+      <c r="B26" s="47" t="inlineStr"/>
+      <c r="C26" s="55">
         <f>SUM(C23:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="54">
+      <c r="D26" s="55">
         <f>SUM(D23:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="54">
+      <c r="E26" s="55">
         <f>SUM(E23:E25)</f>
         <v/>
       </c>
-      <c r="F26" s="54">
+      <c r="F26" s="55">
         <f>SUM(F23:F25)</f>
         <v/>
       </c>
-      <c r="G26" s="54">
+      <c r="G26" s="55">
         <f>SUM(G23:G25)</f>
         <v/>
       </c>
-      <c r="H26" s="54">
+      <c r="H26" s="55">
         <f>SUM(H23:H25)</f>
         <v/>
       </c>
-      <c r="I26" s="54">
+      <c r="I26" s="55">
         <f>SUM(I23:I25)</f>
         <v/>
       </c>
-      <c r="J26" s="54">
+      <c r="J26" s="55">
         <f>SUM(J23:J25)</f>
         <v/>
       </c>
-      <c r="K26" s="54">
+      <c r="K26" s="55">
         <f>SUM(K23:K25)</f>
         <v/>
       </c>
-      <c r="L26" s="54">
+      <c r="L26" s="55">
         <f>SUM(L23:L25)</f>
         <v/>
       </c>
@@ -19404,43 +19574,43 @@
           <t>% YoY</t>
         </is>
       </c>
-      <c r="C27" s="56">
+      <c r="C27" s="57">
         <f>IF(1=1,"",C26/C26-1)</f>
         <v/>
       </c>
-      <c r="D27" s="56">
+      <c r="D27" s="57">
         <f>IF(2=1,"",D26/C26-1)</f>
         <v/>
       </c>
-      <c r="E27" s="56">
+      <c r="E27" s="57">
         <f>IF(3=1,"",E26/D26-1)</f>
         <v/>
       </c>
-      <c r="F27" s="56">
+      <c r="F27" s="57">
         <f>IF(4=1,"",F26/E26-1)</f>
         <v/>
       </c>
-      <c r="G27" s="56">
+      <c r="G27" s="57">
         <f>IF(5=1,"",G26/F26-1)</f>
         <v/>
       </c>
-      <c r="H27" s="56">
+      <c r="H27" s="57">
         <f>IF(6=1,"",H26/G26-1)</f>
         <v/>
       </c>
-      <c r="I27" s="56">
+      <c r="I27" s="57">
         <f>IF(7=1,"",I26/H26-1)</f>
         <v/>
       </c>
-      <c r="J27" s="56">
+      <c r="J27" s="57">
         <f>IF(8=1,"",J26/I26-1)</f>
         <v/>
       </c>
-      <c r="K27" s="56">
+      <c r="K27" s="57">
         <f>IF(9=1,"",K26/J26-1)</f>
         <v/>
       </c>
-      <c r="L27" s="56">
+      <c r="L27" s="57">
         <f>IF(10=1,"",L26/K26-1)</f>
         <v/>
       </c>
@@ -19456,43 +19626,43 @@
           <t>blended</t>
         </is>
       </c>
-      <c r="C28" s="56">
+      <c r="C28" s="57">
         <f>C26/C20</f>
         <v/>
       </c>
-      <c r="D28" s="56">
+      <c r="D28" s="57">
         <f>D26/D20</f>
         <v/>
       </c>
-      <c r="E28" s="56">
+      <c r="E28" s="57">
         <f>E26/E20</f>
         <v/>
       </c>
-      <c r="F28" s="56">
+      <c r="F28" s="57">
         <f>F26/F20</f>
         <v/>
       </c>
-      <c r="G28" s="56">
+      <c r="G28" s="57">
         <f>G26/G20</f>
         <v/>
       </c>
-      <c r="H28" s="56">
+      <c r="H28" s="57">
         <f>H26/H20</f>
         <v/>
       </c>
-      <c r="I28" s="56">
+      <c r="I28" s="57">
         <f>I26/I20</f>
         <v/>
       </c>
-      <c r="J28" s="56">
+      <c r="J28" s="57">
         <f>J26/J20</f>
         <v/>
       </c>
-      <c r="K28" s="56">
+      <c r="K28" s="57">
         <f>K26/K20</f>
         <v/>
       </c>
-      <c r="L28" s="56">
+      <c r="L28" s="57">
         <f>L26/L20</f>
         <v/>
       </c>
@@ -20120,49 +20290,49 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="53" t="inlineStr">
+      <c r="A14" s="54" t="inlineStr">
         <is>
           <t>TOTAL COST OF SALES</t>
         </is>
       </c>
-      <c r="B14" s="48" t="inlineStr"/>
-      <c r="C14" s="54">
+      <c r="B14" s="47" t="inlineStr"/>
+      <c r="C14" s="55">
         <f>C7+C8+C10+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="55">
         <f>D7+D8+D10+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="55">
         <f>E7+E8+E10+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="54">
+      <c r="F14" s="55">
         <f>F7+F8+F10+F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="54">
+      <c r="G14" s="55">
         <f>G7+G8+G10+G12+G13</f>
         <v/>
       </c>
-      <c r="H14" s="54">
+      <c r="H14" s="55">
         <f>H7+H8+H10+H12+H13</f>
         <v/>
       </c>
-      <c r="I14" s="54">
+      <c r="I14" s="55">
         <f>I7+I8+I10+I12+I13</f>
         <v/>
       </c>
-      <c r="J14" s="54">
+      <c r="J14" s="55">
         <f>J7+J8+J10+J12+J13</f>
         <v/>
       </c>
-      <c r="K14" s="54">
+      <c r="K14" s="55">
         <f>K7+K8+K10+K12+K13</f>
         <v/>
       </c>
-      <c r="L14" s="54">
+      <c r="L14" s="55">
         <f>L7+L8+L10+L12+L13</f>
         <v/>
       </c>
@@ -20386,49 +20556,49 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="47" t="inlineStr">
+      <c r="A21" s="46" t="inlineStr">
         <is>
           <t>Total marketing / CAC</t>
         </is>
       </c>
-      <c r="B21" s="48" t="inlineStr"/>
-      <c r="C21" s="51">
+      <c r="B21" s="47" t="inlineStr"/>
+      <c r="C21" s="52">
         <f>SUM(C18:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="52">
         <f>SUM(D18:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="52">
         <f>SUM(E18:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="51">
+      <c r="F21" s="52">
         <f>SUM(F18:F20)</f>
         <v/>
       </c>
-      <c r="G21" s="51">
+      <c r="G21" s="52">
         <f>SUM(G18:G20)</f>
         <v/>
       </c>
-      <c r="H21" s="51">
+      <c r="H21" s="52">
         <f>SUM(H18:H20)</f>
         <v/>
       </c>
-      <c r="I21" s="51">
+      <c r="I21" s="52">
         <f>SUM(I18:I20)</f>
         <v/>
       </c>
-      <c r="J21" s="51">
+      <c r="J21" s="52">
         <f>SUM(J18:J20)</f>
         <v/>
       </c>
-      <c r="K21" s="51">
+      <c r="K21" s="52">
         <f>SUM(K18:K20)</f>
         <v/>
       </c>
-      <c r="L21" s="51">
+      <c r="L21" s="52">
         <f>SUM(L18:L20)</f>
         <v/>
       </c>
@@ -20586,49 +20756,49 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="53" t="inlineStr">
+      <c r="A25" s="54" t="inlineStr">
         <is>
           <t>TOTAL OPERATING COSTS</t>
         </is>
       </c>
-      <c r="B25" s="48" t="inlineStr"/>
-      <c r="C25" s="54">
+      <c r="B25" s="47" t="inlineStr"/>
+      <c r="C25" s="55">
         <f>C17+C21+C23+C24</f>
         <v/>
       </c>
-      <c r="D25" s="54">
+      <c r="D25" s="55">
         <f>D17+D21+D23+D24</f>
         <v/>
       </c>
-      <c r="E25" s="54">
+      <c r="E25" s="55">
         <f>E17+E21+E23+E24</f>
         <v/>
       </c>
-      <c r="F25" s="54">
+      <c r="F25" s="55">
         <f>F17+F21+F23+F24</f>
         <v/>
       </c>
-      <c r="G25" s="54">
+      <c r="G25" s="55">
         <f>G17+G21+G23+G24</f>
         <v/>
       </c>
-      <c r="H25" s="54">
+      <c r="H25" s="55">
         <f>H17+H21+H23+H24</f>
         <v/>
       </c>
-      <c r="I25" s="54">
+      <c r="I25" s="55">
         <f>I17+I21+I23+I24</f>
         <v/>
       </c>
-      <c r="J25" s="54">
+      <c r="J25" s="55">
         <f>J17+J21+J23+J24</f>
         <v/>
       </c>
-      <c r="K25" s="54">
+      <c r="K25" s="55">
         <f>K17+K21+K23+K24</f>
         <v/>
       </c>
-      <c r="L25" s="54">
+      <c r="L25" s="55">
         <f>L17+L21+L23+L24</f>
         <v/>
       </c>
@@ -20944,53 +21114,53 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>AR - float - AP</t>
         </is>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="52">
         <f>C5-C6-C7</f>
         <v/>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="52">
         <f>D5-D6-D7</f>
         <v/>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="52">
         <f>E5-E6-E7</f>
         <v/>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="52">
         <f>F5-F6-F7</f>
         <v/>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="52">
         <f>G5-G6-G7</f>
         <v/>
       </c>
-      <c r="H8" s="51">
+      <c r="H8" s="52">
         <f>H5-H6-H7</f>
         <v/>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="52">
         <f>I5-I6-I7</f>
         <v/>
       </c>
-      <c r="J8" s="51">
+      <c r="J8" s="52">
         <f>J5-J6-J7</f>
         <v/>
       </c>
-      <c r="K8" s="51">
+      <c r="K8" s="52">
         <f>K5-K6-K7</f>
         <v/>
       </c>
-      <c r="L8" s="51">
+      <c r="L8" s="52">
         <f>L5-L6-L7</f>
         <v/>
       </c>
@@ -21006,43 +21176,43 @@
           <t>cash impact</t>
         </is>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="56">
         <f>IF(1=1,C8,C8-C8)</f>
         <v/>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="56">
         <f>IF(2=1,D8,D8-C8)</f>
         <v/>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="56">
         <f>IF(3=1,E8,E8-D8)</f>
         <v/>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="56">
         <f>IF(4=1,F8,F8-E8)</f>
         <v/>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="56">
         <f>IF(5=1,G8,G8-F8)</f>
         <v/>
       </c>
-      <c r="H9" s="55">
+      <c r="H9" s="56">
         <f>IF(6=1,H8,H8-G8)</f>
         <v/>
       </c>
-      <c r="I9" s="55">
+      <c r="I9" s="56">
         <f>IF(7=1,I8,I8-H8)</f>
         <v/>
       </c>
-      <c r="J9" s="55">
+      <c r="J9" s="56">
         <f>IF(8=1,J8,J8-I8)</f>
         <v/>
       </c>
-      <c r="K9" s="55">
+      <c r="K9" s="56">
         <f>IF(9=1,K8,K8-J8)</f>
         <v/>
       </c>
-      <c r="L9" s="55">
+      <c r="L9" s="56">
         <f>IF(10=1,L8,L8-K8)</f>
         <v/>
       </c>
@@ -21180,43 +21350,43 @@
           <t>closing</t>
         </is>
       </c>
-      <c r="C14" s="55">
+      <c r="C14" s="56">
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="56">
         <f>C14+D12-D13</f>
         <v/>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="56">
         <f>D14+E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="55">
+      <c r="F14" s="56">
         <f>E14+F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="56">
         <f>F14+G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="55">
+      <c r="H14" s="56">
         <f>G14+H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="55">
+      <c r="I14" s="56">
         <f>H14+I12-I13</f>
         <v/>
       </c>
-      <c r="J14" s="55">
+      <c r="J14" s="56">
         <f>I14+J12-J13</f>
         <v/>
       </c>
-      <c r="K14" s="55">
+      <c r="K14" s="56">
         <f>J14+K12-K13</f>
         <v/>
       </c>
-      <c r="L14" s="55">
+      <c r="L14" s="56">
         <f>K14+L12-L13</f>
         <v/>
       </c>
@@ -21358,49 +21528,49 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="B4" s="48" t="inlineStr"/>
-      <c r="C4" s="57">
+      <c r="B4" s="47" t="inlineStr"/>
+      <c r="C4" s="58">
         <f>Revenue!C26</f>
         <v/>
       </c>
-      <c r="D4" s="57">
+      <c r="D4" s="58">
         <f>Revenue!D26</f>
         <v/>
       </c>
-      <c r="E4" s="57">
+      <c r="E4" s="58">
         <f>Revenue!E26</f>
         <v/>
       </c>
-      <c r="F4" s="57">
+      <c r="F4" s="58">
         <f>Revenue!F26</f>
         <v/>
       </c>
-      <c r="G4" s="57">
+      <c r="G4" s="58">
         <f>Revenue!G26</f>
         <v/>
       </c>
-      <c r="H4" s="57">
+      <c r="H4" s="58">
         <f>Revenue!H26</f>
         <v/>
       </c>
-      <c r="I4" s="57">
+      <c r="I4" s="58">
         <f>Revenue!I26</f>
         <v/>
       </c>
-      <c r="J4" s="57">
+      <c r="J4" s="58">
         <f>Revenue!J26</f>
         <v/>
       </c>
-      <c r="K4" s="57">
+      <c r="K4" s="58">
         <f>Revenue!K26</f>
         <v/>
       </c>
-      <c r="L4" s="57">
+      <c r="L4" s="58">
         <f>Revenue!L26</f>
         <v/>
       </c>
@@ -21454,49 +21624,49 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="53" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>GROSS PROFIT</t>
         </is>
       </c>
-      <c r="B6" s="48" t="inlineStr"/>
-      <c r="C6" s="54">
+      <c r="B6" s="47" t="inlineStr"/>
+      <c r="C6" s="55">
         <f>C4+C5</f>
         <v/>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="55">
         <f>D4+D5</f>
         <v/>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="55">
         <f>E4+E5</f>
         <v/>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="55">
         <f>F4+F5</f>
         <v/>
       </c>
-      <c r="G6" s="54">
+      <c r="G6" s="55">
         <f>G4+G5</f>
         <v/>
       </c>
-      <c r="H6" s="54">
+      <c r="H6" s="55">
         <f>H4+H5</f>
         <v/>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="55">
         <f>I4+I5</f>
         <v/>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="55">
         <f>J4+J5</f>
         <v/>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="55">
         <f>K4+K5</f>
         <v/>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="55">
         <f>L4+L5</f>
         <v/>
       </c>
@@ -21508,43 +21678,43 @@
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr"/>
-      <c r="C7" s="56">
+      <c r="C7" s="57">
         <f>C6/C4</f>
         <v/>
       </c>
-      <c r="D7" s="56">
+      <c r="D7" s="57">
         <f>D6/D4</f>
         <v/>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="57">
         <f>E6/E4</f>
         <v/>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="57">
         <f>F6/F4</f>
         <v/>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="57">
         <f>G6/G4</f>
         <v/>
       </c>
-      <c r="H7" s="56">
+      <c r="H7" s="57">
         <f>H6/H4</f>
         <v/>
       </c>
-      <c r="I7" s="56">
+      <c r="I7" s="57">
         <f>I6/I4</f>
         <v/>
       </c>
-      <c r="J7" s="56">
+      <c r="J7" s="57">
         <f>J6/J4</f>
         <v/>
       </c>
-      <c r="K7" s="56">
+      <c r="K7" s="57">
         <f>K6/K4</f>
         <v/>
       </c>
-      <c r="L7" s="56">
+      <c r="L7" s="57">
         <f>L6/L4</f>
         <v/>
       </c>
@@ -21598,49 +21768,49 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="53" t="inlineStr">
+      <c r="A10" s="54" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="48" t="inlineStr"/>
-      <c r="C10" s="54">
+      <c r="B10" s="47" t="inlineStr"/>
+      <c r="C10" s="55">
         <f>C6+C9</f>
         <v/>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="55">
         <f>D6+D9</f>
         <v/>
       </c>
-      <c r="E10" s="54">
+      <c r="E10" s="55">
         <f>E6+E9</f>
         <v/>
       </c>
-      <c r="F10" s="54">
+      <c r="F10" s="55">
         <f>F6+F9</f>
         <v/>
       </c>
-      <c r="G10" s="54">
+      <c r="G10" s="55">
         <f>G6+G9</f>
         <v/>
       </c>
-      <c r="H10" s="54">
+      <c r="H10" s="55">
         <f>H6+H9</f>
         <v/>
       </c>
-      <c r="I10" s="54">
+      <c r="I10" s="55">
         <f>I6+I9</f>
         <v/>
       </c>
-      <c r="J10" s="54">
+      <c r="J10" s="55">
         <f>J6+J9</f>
         <v/>
       </c>
-      <c r="K10" s="54">
+      <c r="K10" s="55">
         <f>K6+K9</f>
         <v/>
       </c>
-      <c r="L10" s="54">
+      <c r="L10" s="55">
         <f>L6+L9</f>
         <v/>
       </c>
@@ -21652,43 +21822,43 @@
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr"/>
-      <c r="C11" s="56">
+      <c r="C11" s="57">
         <f>C10/C4</f>
         <v/>
       </c>
-      <c r="D11" s="56">
+      <c r="D11" s="57">
         <f>D10/D4</f>
         <v/>
       </c>
-      <c r="E11" s="56">
+      <c r="E11" s="57">
         <f>E10/E4</f>
         <v/>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="57">
         <f>F10/F4</f>
         <v/>
       </c>
-      <c r="G11" s="56">
+      <c r="G11" s="57">
         <f>G10/G4</f>
         <v/>
       </c>
-      <c r="H11" s="56">
+      <c r="H11" s="57">
         <f>H10/H4</f>
         <v/>
       </c>
-      <c r="I11" s="56">
+      <c r="I11" s="57">
         <f>I10/I4</f>
         <v/>
       </c>
-      <c r="J11" s="56">
+      <c r="J11" s="57">
         <f>J10/J4</f>
         <v/>
       </c>
-      <c r="K11" s="56">
+      <c r="K11" s="57">
         <f>K10/K4</f>
         <v/>
       </c>
-      <c r="L11" s="56">
+      <c r="L11" s="57">
         <f>L10/L4</f>
         <v/>
       </c>
@@ -21742,49 +21912,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="47" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B13" s="48" t="inlineStr"/>
-      <c r="C13" s="51">
+      <c r="B13" s="47" t="inlineStr"/>
+      <c r="C13" s="52">
         <f>C10+C12</f>
         <v/>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="52">
         <f>D10+D12</f>
         <v/>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="52">
         <f>E10+E12</f>
         <v/>
       </c>
-      <c r="F13" s="51">
+      <c r="F13" s="52">
         <f>F10+F12</f>
         <v/>
       </c>
-      <c r="G13" s="51">
+      <c r="G13" s="52">
         <f>G10+G12</f>
         <v/>
       </c>
-      <c r="H13" s="51">
+      <c r="H13" s="52">
         <f>H10+H12</f>
         <v/>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="52">
         <f>I10+I12</f>
         <v/>
       </c>
-      <c r="J13" s="51">
+      <c r="J13" s="52">
         <f>J10+J12</f>
         <v/>
       </c>
-      <c r="K13" s="51">
+      <c r="K13" s="52">
         <f>K10+K12</f>
         <v/>
       </c>
-      <c r="L13" s="51">
+      <c r="L13" s="52">
         <f>L10+L12</f>
         <v/>
       </c>
@@ -21818,43 +21988,43 @@
           <t>accumulated</t>
         </is>
       </c>
-      <c r="C16" s="55">
+      <c r="C16" s="56">
         <f>IF(1=1,0,MIN(0,C18))</f>
         <v/>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="56">
         <f>IF(2=1,0,MIN(0,C18))</f>
         <v/>
       </c>
-      <c r="E16" s="55">
+      <c r="E16" s="56">
         <f>IF(3=1,0,MIN(0,D18))</f>
         <v/>
       </c>
-      <c r="F16" s="55">
+      <c r="F16" s="56">
         <f>IF(4=1,0,MIN(0,E18))</f>
         <v/>
       </c>
-      <c r="G16" s="55">
+      <c r="G16" s="56">
         <f>IF(5=1,0,MIN(0,F18))</f>
         <v/>
       </c>
-      <c r="H16" s="55">
+      <c r="H16" s="56">
         <f>IF(6=1,0,MIN(0,G18))</f>
         <v/>
       </c>
-      <c r="I16" s="55">
+      <c r="I16" s="56">
         <f>IF(7=1,0,MIN(0,H18))</f>
         <v/>
       </c>
-      <c r="J16" s="55">
+      <c r="J16" s="56">
         <f>IF(8=1,0,MIN(0,I18))</f>
         <v/>
       </c>
-      <c r="K16" s="55">
+      <c r="K16" s="56">
         <f>IF(9=1,0,MIN(0,J18))</f>
         <v/>
       </c>
-      <c r="L16" s="55">
+      <c r="L16" s="56">
         <f>IF(10=1,0,MIN(0,K18))</f>
         <v/>
       </c>
@@ -21870,43 +22040,43 @@
           <t>after offset</t>
         </is>
       </c>
-      <c r="C17" s="55">
+      <c r="C17" s="56">
         <f>MAX(0,C13+C16)</f>
         <v/>
       </c>
-      <c r="D17" s="55">
+      <c r="D17" s="56">
         <f>MAX(0,D13+D16)</f>
         <v/>
       </c>
-      <c r="E17" s="55">
+      <c r="E17" s="56">
         <f>MAX(0,E13+E16)</f>
         <v/>
       </c>
-      <c r="F17" s="55">
+      <c r="F17" s="56">
         <f>MAX(0,F13+F16)</f>
         <v/>
       </c>
-      <c r="G17" s="55">
+      <c r="G17" s="56">
         <f>MAX(0,G13+G16)</f>
         <v/>
       </c>
-      <c r="H17" s="55">
+      <c r="H17" s="56">
         <f>MAX(0,H13+H16)</f>
         <v/>
       </c>
-      <c r="I17" s="55">
+      <c r="I17" s="56">
         <f>MAX(0,I13+I16)</f>
         <v/>
       </c>
-      <c r="J17" s="55">
+      <c r="J17" s="56">
         <f>MAX(0,J13+J16)</f>
         <v/>
       </c>
-      <c r="K17" s="55">
+      <c r="K17" s="56">
         <f>MAX(0,K13+K16)</f>
         <v/>
       </c>
-      <c r="L17" s="55">
+      <c r="L17" s="56">
         <f>MAX(0,L13+L16)</f>
         <v/>
       </c>
@@ -21922,43 +22092,43 @@
           <t>running</t>
         </is>
       </c>
-      <c r="C18" s="55">
+      <c r="C18" s="56">
         <f>MIN(0,C13)</f>
         <v/>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="56">
         <f>MIN(0,D13+C18)</f>
         <v/>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="56">
         <f>MIN(0,E13+D18)</f>
         <v/>
       </c>
-      <c r="F18" s="55">
+      <c r="F18" s="56">
         <f>MIN(0,F13+E18)</f>
         <v/>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="56">
         <f>MIN(0,G13+F18)</f>
         <v/>
       </c>
-      <c r="H18" s="55">
+      <c r="H18" s="56">
         <f>MIN(0,H13+G18)</f>
         <v/>
       </c>
-      <c r="I18" s="55">
+      <c r="I18" s="56">
         <f>MIN(0,I13+H18)</f>
         <v/>
       </c>
-      <c r="J18" s="55">
+      <c r="J18" s="56">
         <f>MIN(0,J13+I18)</f>
         <v/>
       </c>
-      <c r="K18" s="55">
+      <c r="K18" s="56">
         <f>MIN(0,K13+J18)</f>
         <v/>
       </c>
-      <c r="L18" s="55">
+      <c r="L18" s="56">
         <f>MIN(0,L13+K18)</f>
         <v/>
       </c>
@@ -22022,91 +22192,91 @@
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr"/>
-      <c r="C20" s="55">
+      <c r="C20" s="56">
         <f>-C17*C19</f>
         <v/>
       </c>
-      <c r="D20" s="55">
+      <c r="D20" s="56">
         <f>-D17*D19</f>
         <v/>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="56">
         <f>-E17*E19</f>
         <v/>
       </c>
-      <c r="F20" s="55">
+      <c r="F20" s="56">
         <f>-F17*F19</f>
         <v/>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="56">
         <f>-G17*G19</f>
         <v/>
       </c>
-      <c r="H20" s="55">
+      <c r="H20" s="56">
         <f>-H17*H19</f>
         <v/>
       </c>
-      <c r="I20" s="55">
+      <c r="I20" s="56">
         <f>-I17*I19</f>
         <v/>
       </c>
-      <c r="J20" s="55">
+      <c r="J20" s="56">
         <f>-J17*J19</f>
         <v/>
       </c>
-      <c r="K20" s="55">
+      <c r="K20" s="56">
         <f>-K17*K19</f>
         <v/>
       </c>
-      <c r="L20" s="55">
+      <c r="L20" s="56">
         <f>-L17*L19</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="54" t="inlineStr">
         <is>
           <t>NET PROFIT</t>
         </is>
       </c>
-      <c r="B21" s="48" t="inlineStr"/>
-      <c r="C21" s="54">
+      <c r="B21" s="47" t="inlineStr"/>
+      <c r="C21" s="55">
         <f>C13+C20</f>
         <v/>
       </c>
-      <c r="D21" s="54">
+      <c r="D21" s="55">
         <f>D13+D20</f>
         <v/>
       </c>
-      <c r="E21" s="54">
+      <c r="E21" s="55">
         <f>E13+E20</f>
         <v/>
       </c>
-      <c r="F21" s="54">
+      <c r="F21" s="55">
         <f>F13+F20</f>
         <v/>
       </c>
-      <c r="G21" s="54">
+      <c r="G21" s="55">
         <f>G13+G20</f>
         <v/>
       </c>
-      <c r="H21" s="54">
+      <c r="H21" s="55">
         <f>H13+H20</f>
         <v/>
       </c>
-      <c r="I21" s="54">
+      <c r="I21" s="55">
         <f>I13+I20</f>
         <v/>
       </c>
-      <c r="J21" s="54">
+      <c r="J21" s="55">
         <f>J13+J20</f>
         <v/>
       </c>
-      <c r="K21" s="54">
+      <c r="K21" s="55">
         <f>K13+K20</f>
         <v/>
       </c>
-      <c r="L21" s="54">
+      <c r="L21" s="55">
         <f>L13+L20</f>
         <v/>
       </c>
@@ -22392,49 +22562,49 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="53" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>OPERATING CASH FLOW</t>
         </is>
       </c>
-      <c r="B7" s="48" t="inlineStr"/>
-      <c r="C7" s="54">
+      <c r="B7" s="47" t="inlineStr"/>
+      <c r="C7" s="55">
         <f>SUM(C4:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="55">
         <f>SUM(D4:D6)</f>
         <v/>
       </c>
-      <c r="E7" s="54">
+      <c r="E7" s="55">
         <f>SUM(E4:E6)</f>
         <v/>
       </c>
-      <c r="F7" s="54">
+      <c r="F7" s="55">
         <f>SUM(F4:F6)</f>
         <v/>
       </c>
-      <c r="G7" s="54">
+      <c r="G7" s="55">
         <f>SUM(G4:G6)</f>
         <v/>
       </c>
-      <c r="H7" s="54">
+      <c r="H7" s="55">
         <f>SUM(H4:H6)</f>
         <v/>
       </c>
-      <c r="I7" s="54">
+      <c r="I7" s="55">
         <f>SUM(I4:I6)</f>
         <v/>
       </c>
-      <c r="J7" s="54">
+      <c r="J7" s="55">
         <f>SUM(J4:J6)</f>
         <v/>
       </c>
-      <c r="K7" s="54">
+      <c r="K7" s="55">
         <f>SUM(K4:K6)</f>
         <v/>
       </c>
-      <c r="L7" s="54">
+      <c r="L7" s="55">
         <f>SUM(L4:L6)</f>
         <v/>
       </c>
@@ -22488,49 +22658,49 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="53" t="inlineStr">
+      <c r="A9" s="54" t="inlineStr">
         <is>
           <t>FREE CASH FLOW</t>
         </is>
       </c>
-      <c r="B9" s="48" t="inlineStr"/>
-      <c r="C9" s="54">
+      <c r="B9" s="47" t="inlineStr"/>
+      <c r="C9" s="55">
         <f>C7+C8</f>
         <v/>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="55">
         <f>D7+D8</f>
         <v/>
       </c>
-      <c r="E9" s="54">
+      <c r="E9" s="55">
         <f>E7+E8</f>
         <v/>
       </c>
-      <c r="F9" s="54">
+      <c r="F9" s="55">
         <f>F7+F8</f>
         <v/>
       </c>
-      <c r="G9" s="54">
+      <c r="G9" s="55">
         <f>G7+G8</f>
         <v/>
       </c>
-      <c r="H9" s="54">
+      <c r="H9" s="55">
         <f>H7+H8</f>
         <v/>
       </c>
-      <c r="I9" s="54">
+      <c r="I9" s="55">
         <f>I7+I8</f>
         <v/>
       </c>
-      <c r="J9" s="54">
+      <c r="J9" s="55">
         <f>J7+J8</f>
         <v/>
       </c>
-      <c r="K9" s="54">
+      <c r="K9" s="55">
         <f>K7+K8</f>
         <v/>
       </c>
-      <c r="L9" s="54">
+      <c r="L9" s="55">
         <f>L7+L8</f>
         <v/>
       </c>
@@ -22542,43 +22712,43 @@
         </is>
       </c>
       <c r="B10" s="22" t="inlineStr"/>
-      <c r="C10" s="55">
+      <c r="C10" s="56">
         <f>C9</f>
         <v/>
       </c>
-      <c r="D10" s="55">
+      <c r="D10" s="56">
         <f>C10+D9</f>
         <v/>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="56">
         <f>D10+E9</f>
         <v/>
       </c>
-      <c r="F10" s="55">
+      <c r="F10" s="56">
         <f>E10+F9</f>
         <v/>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="56">
         <f>F10+G9</f>
         <v/>
       </c>
-      <c r="H10" s="55">
+      <c r="H10" s="56">
         <f>G10+H9</f>
         <v/>
       </c>
-      <c r="I10" s="55">
+      <c r="I10" s="56">
         <f>H10+I9</f>
         <v/>
       </c>
-      <c r="J10" s="55">
+      <c r="J10" s="56">
         <f>I10+J9</f>
         <v/>
       </c>
-      <c r="K10" s="55">
+      <c r="K10" s="56">
         <f>J10+K9</f>
         <v/>
       </c>
-      <c r="L10" s="55">
+      <c r="L10" s="56">
         <f>K10+L9</f>
         <v/>
       </c>
@@ -22642,91 +22812,91 @@
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr"/>
-      <c r="C13" s="55">
+      <c r="C13" s="56">
         <f>0</f>
         <v/>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="56">
         <f>C14</f>
         <v/>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="56">
         <f>D14</f>
         <v/>
       </c>
-      <c r="F13" s="55">
+      <c r="F13" s="56">
         <f>E14</f>
         <v/>
       </c>
-      <c r="G13" s="55">
+      <c r="G13" s="56">
         <f>F14</f>
         <v/>
       </c>
-      <c r="H13" s="55">
+      <c r="H13" s="56">
         <f>G14</f>
         <v/>
       </c>
-      <c r="I13" s="55">
+      <c r="I13" s="56">
         <f>H14</f>
         <v/>
       </c>
-      <c r="J13" s="55">
+      <c r="J13" s="56">
         <f>I14</f>
         <v/>
       </c>
-      <c r="K13" s="55">
+      <c r="K13" s="56">
         <f>J14</f>
         <v/>
       </c>
-      <c r="L13" s="55">
+      <c r="L13" s="56">
         <f>K14</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="53" t="inlineStr">
+      <c r="A14" s="54" t="inlineStr">
         <is>
           <t>CLOSING CASH</t>
         </is>
       </c>
-      <c r="B14" s="48" t="inlineStr"/>
-      <c r="C14" s="54">
+      <c r="B14" s="47" t="inlineStr"/>
+      <c r="C14" s="55">
         <f>C13+C9+C12</f>
         <v/>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="55">
         <f>D13+D9+D12</f>
         <v/>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="55">
         <f>E13+E9+E12</f>
         <v/>
       </c>
-      <c r="F14" s="54">
+      <c r="F14" s="55">
         <f>F13+F9+F12</f>
         <v/>
       </c>
-      <c r="G14" s="54">
+      <c r="G14" s="55">
         <f>G13+G9+G12</f>
         <v/>
       </c>
-      <c r="H14" s="54">
+      <c r="H14" s="55">
         <f>H13+H9+H12</f>
         <v/>
       </c>
-      <c r="I14" s="54">
+      <c r="I14" s="55">
         <f>I13+I9+I12</f>
         <v/>
       </c>
-      <c r="J14" s="54">
+      <c r="J14" s="55">
         <f>J13+J9+J12</f>
         <v/>
       </c>
-      <c r="K14" s="54">
+      <c r="K14" s="55">
         <f>K13+K9+K12</f>
         <v/>
       </c>
-      <c r="L14" s="54">
+      <c r="L14" s="55">
         <f>L13+L9+L12</f>
         <v/>
       </c>
@@ -23030,49 +23200,49 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="53" t="inlineStr">
+      <c r="A8" s="54" t="inlineStr">
         <is>
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B8" s="48" t="inlineStr"/>
-      <c r="C8" s="54">
+      <c r="B8" s="47" t="inlineStr"/>
+      <c r="C8" s="55">
         <f>SUM(C5:C7)</f>
         <v/>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="55">
         <f>SUM(D5:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="55">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="55">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="54">
+      <c r="G8" s="55">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="54">
+      <c r="H8" s="55">
         <f>SUM(H5:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="54">
+      <c r="I8" s="55">
         <f>SUM(I5:I7)</f>
         <v/>
       </c>
-      <c r="J8" s="54">
+      <c r="J8" s="55">
         <f>SUM(J5:J7)</f>
         <v/>
       </c>
-      <c r="K8" s="54">
+      <c r="K8" s="55">
         <f>SUM(K5:K7)</f>
         <v/>
       </c>
-      <c r="L8" s="54">
+      <c r="L8" s="55">
         <f>SUM(L5:L7)</f>
         <v/>
       </c>
@@ -23192,49 +23362,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="53" t="inlineStr">
+      <c r="A13" s="54" t="inlineStr">
         <is>
           <t>TOTAL LIABILITIES</t>
         </is>
       </c>
-      <c r="B13" s="48" t="inlineStr"/>
-      <c r="C13" s="54">
+      <c r="B13" s="47" t="inlineStr"/>
+      <c r="C13" s="55">
         <f>C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="55">
         <f>D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="54">
+      <c r="E13" s="55">
         <f>E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="54">
+      <c r="F13" s="55">
         <f>F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="54">
+      <c r="G13" s="55">
         <f>G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="54">
+      <c r="H13" s="55">
         <f>H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="54">
+      <c r="I13" s="55">
         <f>I11+I12</f>
         <v/>
       </c>
-      <c r="J13" s="54">
+      <c r="J13" s="55">
         <f>J11+J12</f>
         <v/>
       </c>
-      <c r="K13" s="54">
+      <c r="K13" s="55">
         <f>K11+K12</f>
         <v/>
       </c>
-      <c r="L13" s="54">
+      <c r="L13" s="55">
         <f>L11+L12</f>
         <v/>
       </c>
@@ -23354,149 +23524,149 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t>TOTAL EQUITY</t>
         </is>
       </c>
-      <c r="B18" s="48" t="inlineStr"/>
-      <c r="C18" s="54">
+      <c r="B18" s="47" t="inlineStr"/>
+      <c r="C18" s="55">
         <f>C16+C17</f>
         <v/>
       </c>
-      <c r="D18" s="54">
+      <c r="D18" s="55">
         <f>D16+D17</f>
         <v/>
       </c>
-      <c r="E18" s="54">
+      <c r="E18" s="55">
         <f>E16+E17</f>
         <v/>
       </c>
-      <c r="F18" s="54">
+      <c r="F18" s="55">
         <f>F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="54">
+      <c r="G18" s="55">
         <f>G16+G17</f>
         <v/>
       </c>
-      <c r="H18" s="54">
+      <c r="H18" s="55">
         <f>H16+H17</f>
         <v/>
       </c>
-      <c r="I18" s="54">
+      <c r="I18" s="55">
         <f>I16+I17</f>
         <v/>
       </c>
-      <c r="J18" s="54">
+      <c r="J18" s="55">
         <f>J16+J17</f>
         <v/>
       </c>
-      <c r="K18" s="54">
+      <c r="K18" s="55">
         <f>K16+K17</f>
         <v/>
       </c>
-      <c r="L18" s="54">
+      <c r="L18" s="55">
         <f>L16+L17</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="47" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>Liabilities + equity</t>
         </is>
       </c>
-      <c r="B19" s="48" t="inlineStr"/>
-      <c r="C19" s="51">
+      <c r="B19" s="47" t="inlineStr"/>
+      <c r="C19" s="52">
         <f>C13+C18</f>
         <v/>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="52">
         <f>D13+D18</f>
         <v/>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="52">
         <f>E13+E18</f>
         <v/>
       </c>
-      <c r="F19" s="51">
+      <c r="F19" s="52">
         <f>F13+F18</f>
         <v/>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="52">
         <f>G13+G18</f>
         <v/>
       </c>
-      <c r="H19" s="51">
+      <c r="H19" s="52">
         <f>H13+H18</f>
         <v/>
       </c>
-      <c r="I19" s="51">
+      <c r="I19" s="52">
         <f>I13+I18</f>
         <v/>
       </c>
-      <c r="J19" s="51">
+      <c r="J19" s="52">
         <f>J13+J18</f>
         <v/>
       </c>
-      <c r="K19" s="51">
+      <c r="K19" s="52">
         <f>K13+K18</f>
         <v/>
       </c>
-      <c r="L19" s="51">
+      <c r="L19" s="52">
         <f>L13+L18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="inlineStr">
+      <c r="A20" s="54" t="inlineStr">
         <is>
           <t>BALANCE CHECK</t>
         </is>
       </c>
-      <c r="B20" s="48" t="inlineStr">
+      <c r="B20" s="47" t="inlineStr">
         <is>
           <t>must be zero</t>
         </is>
       </c>
-      <c r="C20" s="58">
+      <c r="C20" s="59">
         <f>ROUND(C8-C19,2)</f>
         <v/>
       </c>
-      <c r="D20" s="58">
+      <c r="D20" s="59">
         <f>ROUND(D8-D19,2)</f>
         <v/>
       </c>
-      <c r="E20" s="58">
+      <c r="E20" s="59">
         <f>ROUND(E8-E19,2)</f>
         <v/>
       </c>
-      <c r="F20" s="58">
+      <c r="F20" s="59">
         <f>ROUND(F8-F19,2)</f>
         <v/>
       </c>
-      <c r="G20" s="58">
+      <c r="G20" s="59">
         <f>ROUND(G8-G19,2)</f>
         <v/>
       </c>
-      <c r="H20" s="58">
+      <c r="H20" s="59">
         <f>ROUND(H8-H19,2)</f>
         <v/>
       </c>
-      <c r="I20" s="58">
+      <c r="I20" s="59">
         <f>ROUND(I8-I19,2)</f>
         <v/>
       </c>
-      <c r="J20" s="58">
+      <c r="J20" s="59">
         <f>ROUND(J8-J19,2)</f>
         <v/>
       </c>
-      <c r="K20" s="58">
+      <c r="K20" s="59">
         <f>ROUND(K8-K19,2)</f>
         <v/>
       </c>
-      <c r="L20" s="58">
+      <c r="L20" s="59">
         <f>ROUND(L8-L19,2)</f>
         <v/>
       </c>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -11818,7 +11818,7 @@
       </c>
       <c r="D41" s="97" t="inlineStr">
         <is>
-          <t>25%, against a published mature-company anchor of 6.01%. Damodaran's European cost of capital dataset puts Software (Internet) at 6.01% in euros across 23 listed firms, and the European market ex-financials at 6.59%. Those are costs of capital for mature listed companies; this is a pre-revenue venture, and the 19-point gap is the stage premium. It is stated rather than buried because it is the largest single judgement in the valuation. Damodaran publishes no dataset for venture-stage rates, so the premium itself is convention (20-35% is the usual range) and not a sourced figure. The sensitivity grid runs 18-30% because this is arguable rather than knowable.</t>
+          <t>25%, against a published mature-company anchor of 6.01%. Damodaran's European cost of capital dataset puts Software (Internet) at 6.01% in euros across 23 listed firms, and the European market ex-financials at 6.59%. Those are costs of capital for mature listed companies; this is a pre-revenue venture, and the 19-point gap is the stage premium. It is stated rather than buried because it is the largest single judgement in the valuation. Damodaran publishes no dataset for venture-stage rates, so the premium itself is convention (20-35% is the usual range) and not a sourced figure. The sensitivity grid runs 20-30% because this is arguable rather than knowable.</t>
         </is>
       </c>
       <c r="E41" s="97" t="inlineStr">

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -33,7 +33,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00)"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -42,6 +42,7 @@
     <numFmt numFmtId="169" formatCode="0.000%"/>
     <numFmt numFmtId="170" formatCode="#,##0.000"/>
     <numFmt numFmtId="171" formatCode="#,##0.0"/>
+    <numFmt numFmtId="172" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="36">
     <font>
@@ -345,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -433,6 +434,17 @@
     <xf numFmtId="164" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="14" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -451,9 +463,6 @@
     <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -462,7 +471,6 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -2006,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="24" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="G4" s="24" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>8000000</v>
+        <v>1500000</v>
       </c>
       <c r="I4" s="24" t="n">
         <v>0</v>
@@ -2039,22 +2047,22 @@
         </is>
       </c>
       <c r="C5" s="24" t="n">
-        <v>2500000</v>
+        <v>1800000</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>5000000</v>
+        <v>3500000</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="24" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>40000000</v>
+        <v>12000000</v>
       </c>
       <c r="I5" s="24" t="n">
         <v>0</v>
@@ -2530,34 +2538,34 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="F6" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="G6" s="23" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="23" t="n">
+      <c r="H6" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I6" s="23" t="n">
         <v>3.5</v>
       </c>
-      <c r="H6" s="23" t="n">
+      <c r="J6" s="23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K6" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="K6" s="23" t="n">
-        <v>11</v>
-      </c>
       <c r="L6" s="23" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -2578,28 +2586,28 @@
         <v>0</v>
       </c>
       <c r="E7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="H7" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="I7" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="23" t="n">
+      <c r="J7" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K7" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="K7" s="23" t="n">
-        <v>7</v>
-      </c>
       <c r="L7" s="23" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8">
@@ -2620,28 +2628,28 @@
         <v>0</v>
       </c>
       <c r="E8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="H8" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="23" t="n">
+      <c r="I8" s="23" t="n">
         <v>1.5</v>
       </c>
-      <c r="H8" s="23" t="n">
+      <c r="J8" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="23" t="n">
         <v>2.5</v>
       </c>
-      <c r="I8" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="K8" s="23" t="n">
-        <v>6</v>
-      </c>
       <c r="L8" s="23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -2665,25 +2673,25 @@
         <v>0</v>
       </c>
       <c r="F9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="H9" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="23" t="n">
+      <c r="I9" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L9" s="23" t="n">
         <v>2</v>
-      </c>
-      <c r="I9" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="L9" s="23" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -2707,25 +2715,25 @@
         <v>0</v>
       </c>
       <c r="F10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="I10" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="L10" s="23" t="n">
         <v>1</v>
-      </c>
-      <c r="I10" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="23" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2755,19 +2763,19 @@
         <v>0</v>
       </c>
       <c r="H11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="I11" s="23" t="n">
-        <v>1</v>
-      </c>
       <c r="J11" s="23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L11" s="23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -5985,34 +5993,34 @@
         </is>
       </c>
       <c r="C5" s="24" t="n">
-        <v>24669.76341521453</v>
+        <v>15209.65213450907</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>133178.2880463835</v>
+        <v>78186.9800289897</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>525298.3247152992</v>
+        <v>288002.6712945602</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>1461114.443252258</v>
+        <v>703679.007100631</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>3293651.857395386</v>
+        <v>1321353.147539588</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>6223273.225603884</v>
+        <v>2124049.313694932</v>
       </c>
       <c r="I5" s="24" t="n">
-        <v>10161583.54945481</v>
+        <v>3013163.386035815</v>
       </c>
       <c r="J5" s="24" t="n">
-        <v>14573482.1876938</v>
+        <v>3853438.128678631</v>
       </c>
       <c r="K5" s="24" t="n">
-        <v>18838964.40469826</v>
+        <v>4526655.053312617</v>
       </c>
       <c r="L5" s="24" t="n">
-        <v>23911467.67929958</v>
+        <v>5253768.632209034</v>
       </c>
     </row>
     <row r="6">
@@ -6149,34 +6157,34 @@
         </is>
       </c>
       <c r="C10" s="24" t="n">
-        <v>13341.24768695526</v>
+        <v>8788.279804347037</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>57150.57058755679</v>
+        <v>35884.10661722298</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>191124.199633203</v>
+        <v>107180.4277627578</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>503136.2247638087</v>
+        <v>235202.2755595208</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>1098498.035916488</v>
+        <v>421379.4560848573</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>2007711.980962103</v>
+        <v>658989.9166519806</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>3213122.986615158</v>
+        <v>923988.6616917688</v>
       </c>
       <c r="J10" s="24" t="n">
-        <v>4546711.090869308</v>
+        <v>1175852.257663428</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>5865675.995384405</v>
+        <v>1378200.045113646</v>
       </c>
       <c r="L10" s="24" t="n">
-        <v>7377275.550758523</v>
+        <v>1591699.099905172</v>
       </c>
     </row>
     <row r="11">
@@ -6313,34 +6321,34 @@
         </is>
       </c>
       <c r="C15" s="24" t="n">
-        <v>11328.51572825927</v>
+        <v>6421.372330162036</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>76027.71745882675</v>
+        <v>42302.87341176671</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>334174.1250820962</v>
+        <v>180822.2435318024</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>957978.2184884488</v>
+        <v>468476.7315411102</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>2195153.821478899</v>
+        <v>899973.6914547306</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>4215561.244641781</v>
+        <v>1465059.397042952</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>6948460.562839656</v>
+        <v>2089174.724344046</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>10026771.09682449</v>
+        <v>2677585.871015203</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>12973288.40931385</v>
+        <v>3148455.008198972</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>16534192.12854106</v>
+        <v>3662069.532303861</v>
       </c>
     </row>
     <row r="16">
@@ -6477,34 +6485,34 @@
         </is>
       </c>
       <c r="C20" s="24" t="n">
-        <v>87353.58107321717</v>
+        <v>77716.77217076073</v>
       </c>
       <c r="D20" s="24" t="n">
-        <v>220573.4630437107</v>
+        <v>153773.2084023192</v>
       </c>
       <c r="E20" s="24" t="n">
-        <v>481042.4259772239</v>
+        <v>320381.8137035648</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>1010801.155460181</v>
+        <v>554399.1205680504</v>
       </c>
       <c r="G20" s="24" t="n">
-        <v>1774784.148591631</v>
+        <v>882757.851803167</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>2647988.758048311</v>
+        <v>1225415.145095594</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>3696886.683956385</v>
+        <v>1554635.070882865</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>4616742.575015504</v>
+        <v>1825600.650294291</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>5334427.15237586</v>
+        <v>2067126.404265009</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>6333002.214343966</v>
+        <v>2257172.370576723</v>
       </c>
     </row>
     <row r="21">
@@ -6641,34 +6649,34 @@
         </is>
       </c>
       <c r="C25" s="24" t="n">
-        <v>-76025.0653449579</v>
+        <v>-71295.39984059869</v>
       </c>
       <c r="D25" s="24" t="n">
-        <v>-144545.7455848839</v>
+        <v>-111470.3349905525</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>-146868.3008951277</v>
+        <v>-139559.5701717624</v>
       </c>
       <c r="F25" s="24" t="n">
-        <v>-52822.93697173183</v>
+        <v>-85922.38902694022</v>
       </c>
       <c r="G25" s="24" t="n">
-        <v>420369.6728872678</v>
+        <v>17215.83965156355</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>1567572.48659347</v>
+        <v>239644.2519473576</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>3251573.878883271</v>
+        <v>534539.6534611809</v>
       </c>
       <c r="J25" s="24" t="n">
-        <v>5410028.521808989</v>
+        <v>851985.2207209126</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>7638861.25693799</v>
+        <v>1081328.603933963</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>10201189.91419709</v>
+        <v>1404897.161727139</v>
       </c>
     </row>
     <row r="26">
@@ -6805,34 +6813,34 @@
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>2057.84174041374</v>
+        <v>1286.151087758587</v>
       </c>
       <c r="D30" s="17" t="n">
-        <v>8148.23494677803</v>
+        <v>5092.646841736267</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>25287.70242113075</v>
+        <v>14334.42936888351</v>
       </c>
       <c r="F30" s="17" t="n">
-        <v>60196.82975290195</v>
+        <v>28169.28576456208</v>
       </c>
       <c r="G30" s="17" t="n">
-        <v>120075.7365173497</v>
+        <v>46066.06447500147</v>
       </c>
       <c r="H30" s="17" t="n">
-        <v>206657.9512122322</v>
+        <v>67882.20782167294</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>321288</v>
+        <v>92005.20000000001</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>434075.5999999999</v>
+        <v>111619.44</v>
       </c>
       <c r="K30" s="17" t="n">
-        <v>553628.8000000002</v>
+        <v>128637.28</v>
       </c>
       <c r="L30" s="17" t="n">
-        <v>665896</v>
+        <v>141502.9</v>
       </c>
     </row>
     <row r="31">
@@ -6969,34 +6977,34 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>1305.616369213765</v>
+        <v>816.010230758603</v>
       </c>
       <c r="D35" s="17" t="n">
-        <v>5897.122422019523</v>
+        <v>3685.701513762201</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>18938.52415509884</v>
+        <v>10913.21808130112</v>
       </c>
       <c r="F35" s="17" t="n">
-        <v>47228.17401009858</v>
+        <v>23047.08309296033</v>
       </c>
       <c r="G35" s="17" t="n">
-        <v>97836.51656978924</v>
+        <v>39464.36338620399</v>
       </c>
       <c r="H35" s="17" t="n">
-        <v>174457.6422218148</v>
+        <v>59832.18166912212</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>277910.9888438896</v>
+        <v>82914.56519122265</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>391108.4765464211</v>
+        <v>104177.5514465162</v>
       </c>
       <c r="K35" s="17" t="n">
-        <v>507748.2506421141</v>
+        <v>122123.9241028032</v>
       </c>
       <c r="L35" s="17" t="n">
-        <v>622730.6704958598</v>
+        <v>136573.6263141455</v>
       </c>
     </row>
     <row r="36">
@@ -7133,34 +7141,34 @@
         </is>
       </c>
       <c r="C40" s="24" t="n">
-        <v>166159.5694347635</v>
+        <v>103849.7308967272</v>
       </c>
       <c r="D40" s="24" t="n">
-        <v>809909.7202025568</v>
+        <v>506193.5751265979</v>
       </c>
       <c r="E40" s="24" t="n">
-        <v>3053787.536928662</v>
+        <v>1751195.741743291</v>
       </c>
       <c r="F40" s="24" t="n">
-        <v>9029784.503559049</v>
+        <v>4330016.769991406</v>
       </c>
       <c r="G40" s="24" t="n">
-        <v>21701556.20578258</v>
+        <v>8521278.947970588</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>43115734.33602589</v>
+        <v>14372383.76169955</v>
       </c>
       <c r="I40" s="24" t="n">
-        <v>71777410.04809876</v>
+        <v>20940263.82626543</v>
       </c>
       <c r="J40" s="24" t="n">
-        <v>104393238.5445187</v>
+        <v>27265422.25706821</v>
       </c>
       <c r="K40" s="24" t="n">
-        <v>135555526.5711262</v>
+        <v>31985041.56907789</v>
       </c>
       <c r="L40" s="24" t="n">
-        <v>175904826.0874194</v>
+        <v>37884320.54596245</v>
       </c>
     </row>
     <row r="41">
@@ -7297,34 +7305,34 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>24.54</v>
+        <v>15.3375</v>
       </c>
       <c r="D45" s="17" t="n">
-        <v>117.216</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="E45" s="17" t="n">
-        <v>484.8</v>
+        <v>274.72</v>
       </c>
       <c r="F45" s="17" t="n">
-        <v>1548.72</v>
+        <v>722.7359999999999</v>
       </c>
       <c r="G45" s="17" t="n">
-        <v>3767.190000000001</v>
+        <v>1435.12</v>
       </c>
       <c r="H45" s="17" t="n">
-        <v>7376</v>
+        <v>2397.2</v>
       </c>
       <c r="I45" s="17" t="n">
-        <v>11563.2</v>
+        <v>3311.28</v>
       </c>
       <c r="J45" s="17" t="n">
-        <v>16257.92</v>
+        <v>4180.608</v>
       </c>
       <c r="K45" s="17" t="n">
-        <v>19895.44</v>
+        <v>4622.764</v>
       </c>
       <c r="L45" s="17" t="n">
-        <v>25539.2</v>
+        <v>5427.08</v>
       </c>
     </row>
     <row r="46">
@@ -7461,34 +7469,34 @@
         </is>
       </c>
       <c r="C50" s="17" t="n">
-        <v>2000</v>
+        <v>1250</v>
       </c>
       <c r="D50" s="17" t="n">
-        <v>4040</v>
+        <v>2525</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>8375.039999999999</v>
+        <v>4534.399999999999</v>
       </c>
       <c r="F50" s="17" t="n">
-        <v>13666.66666666667</v>
+        <v>5522.222222222222</v>
       </c>
       <c r="G50" s="17" t="n">
-        <v>20336.84210526316</v>
+        <v>6332.631578947367</v>
       </c>
       <c r="H50" s="17" t="n">
-        <v>26004.74576271186</v>
+        <v>6871.864406779659</v>
       </c>
       <c r="I50" s="17" t="n">
-        <v>30163.9344262295</v>
+        <v>7016.39344262295</v>
       </c>
       <c r="J50" s="17" t="n">
-        <v>32980.64516129032</v>
+        <v>6805.16129032258</v>
       </c>
       <c r="K50" s="17" t="n">
-        <v>35803.17460317459</v>
+        <v>6530.793650793649</v>
       </c>
       <c r="L50" s="17" t="n">
-        <v>38515.90551181103</v>
+        <v>6448.125984251968</v>
       </c>
     </row>
     <row r="51">
@@ -7625,34 +7633,34 @@
         </is>
       </c>
       <c r="C55" s="24" t="n">
-        <v>745.0980392156863</v>
+        <v>465.6862745098039</v>
       </c>
       <c r="D55" s="24" t="n">
-        <v>2001.938823529412</v>
+        <v>1251.211764705882</v>
       </c>
       <c r="E55" s="24" t="n">
-        <v>4650.610447058823</v>
+        <v>2517.925647058823</v>
       </c>
       <c r="F55" s="24" t="n">
-        <v>7902.870588235294</v>
+        <v>3193.273725490196</v>
       </c>
       <c r="G55" s="24" t="n">
-        <v>11906.38365325077</v>
+        <v>3707.495034055726</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>15491.89387570621</v>
+        <v>4093.798689265535</v>
       </c>
       <c r="I55" s="24" t="n">
-        <v>18266.33236901318</v>
+        <v>4248.907746705239</v>
       </c>
       <c r="J55" s="24" t="n">
-        <v>20412.30330170778</v>
+        <v>4211.834413662239</v>
       </c>
       <c r="K55" s="24" t="n">
-        <v>22629.29120448179</v>
+        <v>4127.768918767506</v>
       </c>
       <c r="L55" s="24" t="n">
-        <v>24921.45233657558</v>
+        <v>4172.215666265246</v>
       </c>
     </row>
     <row r="56">
@@ -7804,19 +7812,19 @@
         <v>0</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>193392.0166026054</v>
+        <v>0</v>
       </c>
       <c r="I60" s="24" t="n">
-        <v>458966.0818324906</v>
+        <v>6952.807654537234</v>
       </c>
       <c r="J60" s="24" t="n">
-        <v>769234.2782713483</v>
+        <v>96657.78310813688</v>
       </c>
       <c r="K60" s="24" t="n">
-        <v>1087209.188540698</v>
+        <v>122104.2905900944</v>
       </c>
       <c r="L60" s="24" t="n">
-        <v>2422147.478549273</v>
+        <v>162899.5742590708</v>
       </c>
     </row>
     <row r="61">
@@ -7953,34 +7961,34 @@
         </is>
       </c>
       <c r="C65" s="24" t="n">
-        <v>-79825.0653449579</v>
+        <v>-75095.39984059869</v>
       </c>
       <c r="D65" s="24" t="n">
-        <v>-156145.7455848839</v>
+        <v>-120470.3349905525</v>
       </c>
       <c r="E65" s="24" t="n">
-        <v>-170468.3008951277</v>
+        <v>-157559.5701717624</v>
       </c>
       <c r="F65" s="24" t="n">
-        <v>-95022.93697173183</v>
+        <v>-112922.3890269402</v>
       </c>
       <c r="G65" s="24" t="n">
-        <v>346369.6728872678</v>
+        <v>-30984.16034843645</v>
       </c>
       <c r="H65" s="24" t="n">
-        <v>1250980.469990865</v>
+        <v>152844.2519473576</v>
       </c>
       <c r="I65" s="24" t="n">
-        <v>2600807.797050781</v>
+        <v>383586.8458066436</v>
       </c>
       <c r="J65" s="24" t="n">
-        <v>4358994.243537641</v>
+        <v>547727.4376127757</v>
       </c>
       <c r="K65" s="24" t="n">
-        <v>6160852.068397291</v>
+        <v>691924.3133438681</v>
       </c>
       <c r="L65" s="24" t="n">
-        <v>7266442.435647818</v>
+        <v>923097.587468068</v>
       </c>
     </row>
     <row r="66">
@@ -8117,34 +8125,34 @@
         </is>
       </c>
       <c r="C70" s="24" t="n">
-        <v>-72678.9197081429</v>
+        <v>-71552.95944772632</v>
       </c>
       <c r="D70" s="24" t="n">
-        <v>-130031.4467223353</v>
+        <v>-103369.3973795417</v>
       </c>
       <c r="E70" s="24" t="n">
-        <v>-77059.22803380112</v>
+        <v>-105070.5356489066</v>
       </c>
       <c r="F70" s="24" t="n">
-        <v>142188.3458212058</v>
+        <v>-12309.89736107869</v>
       </c>
       <c r="G70" s="24" t="n">
-        <v>819029.4979362227</v>
+        <v>113157.2481145281</v>
       </c>
       <c r="H70" s="24" t="n">
-        <v>2020118.947682307</v>
+        <v>329870.0623134766</v>
       </c>
       <c r="I70" s="24" t="n">
-        <v>3622920.351666027</v>
+        <v>577578.3683435448</v>
       </c>
       <c r="J70" s="24" t="n">
-        <v>5486437.227570175</v>
+        <v>732667.1546823786</v>
       </c>
       <c r="K70" s="24" t="n">
-        <v>7237328.527077117</v>
+        <v>828273.2012880694</v>
       </c>
       <c r="L70" s="24" t="n">
-        <v>8641446.355805861</v>
+        <v>1095992.583641871</v>
       </c>
     </row>
     <row r="71">
@@ -8321,7 +8329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -9230,227 +9238,566 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="77" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP MARKETPLACES - the direct competitor set</t>
+        </is>
+      </c>
+    </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A42" s="71" t="inlineStr">
+        <is>
+          <t>PitchBook company profiles retrieved 1 Oct 2026, reported in EUR. None of the four discloses revenue, so headcount and capital raised are the only scale measures available. Links at the bottom of this sheet.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="81" t="inlineStr">
-        <is>
-          <t>OnlyFans FY2024 filed accounts (Fenix International Ltd)</t>
-        </is>
-      </c>
-      <c r="B43" s="82" t="inlineStr">
-        <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/10354575/filing-history</t>
+      <c r="A43" s="72" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B43" s="72" t="inlineStr">
+        <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="C43" s="72" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="D43" s="72" t="inlineStr">
+        <is>
+          <t>Total raised</t>
+        </is>
+      </c>
+      <c r="E43" s="72" t="inlineStr">
+        <is>
+          <t>Largest round pre-money</t>
+        </is>
+      </c>
+      <c r="F43" s="72" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="81" t="inlineStr">
         <is>
-          <t>OnlyFans FY2024 as reported</t>
-        </is>
-      </c>
-      <c r="B44" s="82" t="inlineStr">
-        <is>
-          <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
+          <t>Sponsoo (Germany)</t>
+        </is>
+      </c>
+      <c r="B44" s="39" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C44" s="74" t="n">
+        <v>13</v>
+      </c>
+      <c r="D44" s="82" t="n">
+        <v>2170000</v>
+      </c>
+      <c r="E44" s="82" t="n">
+        <v>15900000</v>
+      </c>
+      <c r="F44" s="75" t="inlineStr">
+        <is>
+          <t>Privately held, venture backed. Series A 28 Jan 2021; pre-money is a PitchBook ESTIMATE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="81" t="inlineStr">
         <is>
-          <t>Patreon published take rate</t>
-        </is>
-      </c>
-      <c r="B45" s="82" t="inlineStr">
-        <is>
-          <t>https://www.patreon.com/pricing</t>
+          <t>OpenSponsorship (United States)</t>
+        </is>
+      </c>
+      <c r="B45" s="39" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C45" s="74" t="n">
+        <v>23</v>
+      </c>
+      <c r="D45" s="82" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="E45" s="82" t="n"/>
+      <c r="F45" s="75" t="inlineStr">
+        <is>
+          <t>Privately held, venture backed. Last priced round not disclosed</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="81" t="inlineStr">
         <is>
-          <t>Patreon creators</t>
-        </is>
-      </c>
-      <c r="B46" s="82" t="inlineStr">
-        <is>
-          <t>https://backlinko.com/patreon-users</t>
+          <t>SponsorUnited (United States)</t>
+        </is>
+      </c>
+      <c r="B46" s="39" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C46" s="74" t="n">
+        <v>355</v>
+      </c>
+      <c r="D46" s="82" t="n">
+        <v>38760000</v>
+      </c>
+      <c r="E46" s="82" t="n">
+        <v>89380000</v>
+      </c>
+      <c r="F46" s="75" t="inlineStr">
+        <is>
+          <t>Privately held, venture backed. Series A 21 Nov 2022</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="81" t="inlineStr">
         <is>
-          <t>Passes economics</t>
-        </is>
-      </c>
-      <c r="B47" s="82" t="inlineStr">
-        <is>
-          <t>https://sacra.com/c/passes/</t>
+          <t>Hookit (United States)</t>
+        </is>
+      </c>
+      <c r="B47" s="39" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C47" s="74" t="n">
+        <v>47</v>
+      </c>
+      <c r="D47" s="82" t="n">
+        <v>21470000</v>
+      </c>
+      <c r="E47" s="82" t="n">
+        <v>38400000</v>
+      </c>
+      <c r="F47" s="75" t="inlineStr">
+        <is>
+          <t>Acquired, operating subsidiary. Series C2 24 Feb 2020; pre-money is a PitchBook ESTIMATE</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="81" t="inlineStr">
         <is>
+          <t>Stride (this plan, at Y10)</t>
+        </is>
+      </c>
+      <c r="B48" s="83" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C48" s="84" t="n">
+        <v>16</v>
+      </c>
+      <c r="D48" s="85" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="E48" s="85" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F48" s="75" t="inlineStr">
+        <is>
+          <t>Deliberately sized near Sponsoo. Only EUR 400k of the total is capital the plan depends on; the growth round is optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="77" t="inlineStr">
+        <is>
+          <t>REVENUE PER EMPLOYEE - what the plan is tested against</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Benchmark</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>EUR per employee</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr"/>
+      <c r="D51" s="11" t="inlineStr"/>
+      <c r="E51" s="11" t="inlineStr"/>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>Median private B2B SaaS, all stages</t>
+        </is>
+      </c>
+      <c r="B52" s="86" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F52" s="87" t="inlineStr">
+        <is>
+          <t>SaaS Capital 2025 survey of ~1,000 private B2B SaaS companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Top quartile private B2B SaaS</t>
+        </is>
+      </c>
+      <c r="B53" s="86" t="n">
+        <v>215000</v>
+      </c>
+      <c r="F53" s="87" t="inlineStr">
+        <is>
+          <t>SaaS Capital 2025 survey, 75th percentile</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>Efficient public SaaS at scale</t>
+        </is>
+      </c>
+      <c r="B54" s="86" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F54" s="87" t="inlineStr">
+        <is>
+          <t>Public SaaS medians, widely reported range EUR 250-350k</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Stride (this plan, Y7)</t>
+        </is>
+      </c>
+      <c r="B55" s="88">
+        <f>KPIs!I14</f>
+        <v/>
+      </c>
+      <c r="F55" s="87" t="inlineStr">
+        <is>
+          <t>Above the top quartile. Defended in section 3.2.2: the fan side is self-serve and moderation is a variable cost, not headcount</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>Multiple of the top quartile</t>
+        </is>
+      </c>
+      <c r="B56" s="89">
+        <f>B55/B53</f>
+        <v/>
+      </c>
+      <c r="F56" s="80" t="inlineStr">
+        <is>
+          <t>The plan's second most aggressive assumption after fan churn</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="90" t="inlineStr">
+        <is>
+          <t>OnlyFans FY2024 filed accounts (Fenix International Ltd)</t>
+        </is>
+      </c>
+      <c r="B60" s="91" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/10354575/filing-history</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="90" t="inlineStr">
+        <is>
+          <t>OnlyFans FY2024 as reported</t>
+        </is>
+      </c>
+      <c r="B61" s="91" t="inlineStr">
+        <is>
+          <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="90" t="inlineStr">
+        <is>
+          <t>Patreon published take rate</t>
+        </is>
+      </c>
+      <c r="B62" s="91" t="inlineStr">
+        <is>
+          <t>https://www.patreon.com/pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="90" t="inlineStr">
+        <is>
+          <t>Patreon creators</t>
+        </is>
+      </c>
+      <c r="B63" s="91" t="inlineStr">
+        <is>
+          <t>https://backlinko.com/patreon-users</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="90" t="inlineStr">
+        <is>
+          <t>Passes economics</t>
+        </is>
+      </c>
+      <c r="B64" s="91" t="inlineStr">
+        <is>
+          <t>https://sacra.com/c/passes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="90" t="inlineStr">
+        <is>
           <t>Fanfix creator terms (states no take rate)</t>
         </is>
       </c>
-      <c r="B48" s="82" t="inlineStr">
+      <c r="B65" s="91" t="inlineStr">
         <is>
           <t>https://auth.fanfix.io/creator-terms-of-use</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="81" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="90" t="inlineStr">
         <is>
           <t>Agency commissions</t>
         </is>
       </c>
-      <c r="B49" s="82" t="inlineStr">
+      <c r="B66" s="91" t="inlineStr">
         <is>
           <t>https://arunatalent.com/blog/onlyfans-agency-commission-rates/</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="81" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="90" t="inlineStr">
         <is>
           <t>NBPA agent fee cap (amended Sept 2025)</t>
         </is>
       </c>
-      <c r="B50" s="82" t="inlineStr">
+      <c r="B67" s="91" t="inlineStr">
         <is>
           <t>https://imgix.cosmicjs.com/cd844850-97c7-11f0-91fa-d9e1671c2776-NBPA-REGULATIONS-GOVERNING-PLAYER-AGENTS-09-2025.pdf</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="81" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="90" t="inlineStr">
         <is>
           <t>FIFA Football Agent Regulations art. 15</t>
         </is>
       </c>
-      <c r="B51" s="82" t="inlineStr">
+      <c r="B68" s="91" t="inlineStr">
         <is>
           <t>https://digitalhub.fifa.com/m/1e7b741fa0fae779/original/FIFA-Football-Agent-Regulations.pdf</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="81" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="90" t="inlineStr">
         <is>
           <t>CJEU upholds the FIFA fee cap (16 Jul 2026)</t>
         </is>
       </c>
-      <c r="B52" s="82" t="inlineStr">
+      <c r="B69" s="91" t="inlineStr">
         <is>
           <t>https://inside.fifa.com/news/welcomes-court-of-justice-european-union-decision-football-agent-regulations</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="81" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="90" t="inlineStr">
         <is>
           <t>Eurobarometer 525</t>
         </is>
       </c>
-      <c r="B53" s="82" t="inlineStr">
+      <c r="B70" s="91" t="inlineStr">
         <is>
           <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="81" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="90" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="B54" s="82" t="inlineStr">
+      <c r="B71" s="91" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="81" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="90" t="inlineStr">
         <is>
           <t>Stripe EU pricing</t>
         </is>
       </c>
-      <c r="B55" s="82" t="inlineStr">
+      <c r="B72" s="91" t="inlineStr">
         <is>
           <t>https://stripe.com/es/pricing</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="81" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="90" t="inlineStr">
         <is>
           <t>TEKTA launch</t>
         </is>
       </c>
-      <c r="B56" s="82" t="inlineStr">
+      <c r="B73" s="91" t="inlineStr">
         <is>
           <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="81" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="90" t="inlineStr">
         <is>
           <t>Stripe Connect age</t>
         </is>
       </c>
-      <c r="B57" s="82" t="inlineStr">
+      <c r="B74" s="91" t="inlineStr">
         <is>
           <t>https://support.stripe.com/questions/age-requirement-to-create-a-stripe-account</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="90" t="inlineStr">
+        <is>
+          <t>PitchBook: Sponsoo GmbH</t>
+        </is>
+      </c>
+      <c r="B75" s="91" t="inlineStr">
+        <is>
+          <t>https://pitchbook.com/profiles/company/103066-39</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="90" t="inlineStr">
+        <is>
+          <t>PitchBook: OpenSponsorship</t>
+        </is>
+      </c>
+      <c r="B76" s="91" t="inlineStr">
+        <is>
+          <t>https://pitchbook.com/profiles/company/113575-96</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="90" t="inlineStr">
+        <is>
+          <t>PitchBook: SponsorUnited</t>
+        </is>
+      </c>
+      <c r="B77" s="91" t="inlineStr">
+        <is>
+          <t>https://pitchbook.com/profiles/company/169635-43</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="90" t="inlineStr">
+        <is>
+          <t>PitchBook: Hookit</t>
+        </is>
+      </c>
+      <c r="B78" s="91" t="inlineStr">
+        <is>
+          <t>https://pitchbook.com/profiles/company/55307-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="90" t="inlineStr">
+        <is>
+          <t>SaaS Capital revenue per employee benchmarks</t>
+        </is>
+      </c>
+      <c r="B79" s="91" t="inlineStr">
+        <is>
+          <t>https://www.saas-capital.com/blog-posts/revenue-per-employee-benchmarks-for-private-saas-companies/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B49:F49"/>
+  <mergeCells count="21">
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B79:F79"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9486,36 +9833,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="83" t="inlineStr">
+      <c r="C3" s="92" t="inlineStr">
         <is>
           <t>Input: change me</t>
         </is>
       </c>
-      <c r="D3" s="84" t="n"/>
-      <c r="E3" s="85" t="inlineStr">
+      <c r="D3" s="93" t="n"/>
+      <c r="E3" s="94" t="inlineStr">
         <is>
           <t>Sourced fact</t>
         </is>
       </c>
-      <c r="F3" s="84" t="n"/>
-      <c r="G3" s="86" t="inlineStr">
+      <c r="F3" s="93" t="n"/>
+      <c r="G3" s="95" t="inlineStr">
         <is>
           <t>Formula (this sheet)</t>
         </is>
       </c>
-      <c r="H3" s="84" t="n"/>
-      <c r="I3" s="87" t="inlineStr">
+      <c r="H3" s="93" t="n"/>
+      <c r="I3" s="96" t="inlineStr">
         <is>
           <t>Formula (other sheet)</t>
         </is>
       </c>
-      <c r="J3" s="84" t="n"/>
-      <c r="K3" s="88" t="inlineStr">
+      <c r="J3" s="93" t="n"/>
+      <c r="K3" s="97" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="L3" s="84" t="n"/>
+      <c r="L3" s="93" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -9537,7 +9884,7 @@
         <f>Comparables!B14</f>
         <v/>
       </c>
-      <c r="D6" s="89" t="inlineStr">
+      <c r="D6" s="87" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -9553,7 +9900,7 @@
         <f>Comparables!B12</f>
         <v/>
       </c>
-      <c r="D7" s="89" t="inlineStr">
+      <c r="D7" s="87" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -9569,7 +9916,7 @@
         <f>B6/B7</f>
         <v/>
       </c>
-      <c r="D8" s="89" t="inlineStr">
+      <c r="D8" s="87" t="inlineStr">
         <is>
           <t>The single most useful benchmark we found: it is measured, not modelled.</t>
         </is>
@@ -9585,7 +9932,7 @@
         <f>Comparables!B9/Comparables!B8</f>
         <v/>
       </c>
-      <c r="D9" s="89" t="inlineStr">
+      <c r="D9" s="87" t="inlineStr">
         <is>
           <t>Fan ACCOUNTS, not paying fans - most follow free. Shown as an upper bound only.</t>
         </is>
@@ -9600,7 +9947,7 @@
       <c r="B10" s="26" t="n">
         <v>1.06</v>
       </c>
-      <c r="D10" s="89" t="inlineStr">
+      <c r="D10" s="87" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +6% on the Patreon benchmark. Sport audiences are smaller but convert better, because the fan usually does the sport themselves.</t>
         </is>
@@ -9615,7 +9962,7 @@
       <c r="B11" s="26" t="n">
         <v>1.37</v>
       </c>
-      <c r="D11" s="89" t="inlineStr">
+      <c r="D11" s="87" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +37%. Much larger followings, much weaker conversion - more paying fans in absolute terms even though a smaller share converts.</t>
         </is>
@@ -9627,11 +9974,11 @@
           <t>→ Niche fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B12" s="90">
+      <c r="B12" s="98">
         <f>B8*B10</f>
         <v/>
       </c>
-      <c r="D12" s="89" t="inlineStr"/>
+      <c r="D12" s="87" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -9639,11 +9986,11 @@
           <t>→ Popular fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B13" s="90">
+      <c r="B13" s="98">
         <f>B8*B11</f>
         <v/>
       </c>
-      <c r="D13" s="89" t="inlineStr"/>
+      <c r="D13" s="87" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -9664,7 +10011,7 @@
       <c r="B15" s="22" t="n">
         <v>4.99</v>
       </c>
-      <c r="D15" s="89" t="inlineStr"/>
+      <c r="D15" s="87" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -9675,7 +10022,7 @@
       <c r="B16" s="22" t="n">
         <v>9.99</v>
       </c>
-      <c r="D16" s="89" t="inlineStr"/>
+      <c r="D16" s="87" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
@@ -9686,7 +10033,7 @@
       <c r="B17" s="22" t="n">
         <v>24.99</v>
       </c>
-      <c r="D17" s="89" t="inlineStr"/>
+      <c r="D17" s="87" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -9697,7 +10044,7 @@
       <c r="B18" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="D18" s="89" t="inlineStr">
+      <c r="D18" s="87" t="inlineStr">
         <is>
           <t>Assumed distribution; replace with the real tier mix after P1.</t>
         </is>
@@ -9712,7 +10059,7 @@
       <c r="B19" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="D19" s="89" t="inlineStr"/>
+      <c r="D19" s="87" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -9723,7 +10070,7 @@
       <c r="B20" s="18" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="89" t="inlineStr"/>
+      <c r="D20" s="87" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -9735,7 +10082,7 @@
         <f>B18+B19+B20</f>
         <v/>
       </c>
-      <c r="D21" s="89" t="inlineStr"/>
+      <c r="D21" s="87" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -9743,11 +10090,11 @@
           <t>→ Weighted ARPU per month</t>
         </is>
       </c>
-      <c r="B22" s="91">
+      <c r="B22" s="99">
         <f>B15*B18+B16*B19+B17*B20</f>
         <v/>
       </c>
-      <c r="D22" s="89" t="inlineStr">
+      <c r="D22" s="87" t="inlineStr">
         <is>
           <t>Cross-check: Patreon reports $6.10 average support and a $8-12 typical band. Landing inside that band from an independent tier build is a good sign.</t>
         </is>
@@ -9763,7 +10110,7 @@
         <f>Comparables!B16</f>
         <v/>
       </c>
-      <c r="D23" s="89" t="inlineStr">
+      <c r="D23" s="87" t="inlineStr">
         <is>
           <t>Published average - below our figure because Patreon's long tail includes many $1-3 tiers. Our EUR 9.49 sits inside their $8-12 typical band.</t>
         </is>
@@ -9778,7 +10125,7 @@
       <c r="B24" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="89" t="inlineStr">
+      <c r="D24" s="87" t="inlineStr">
         <is>
           <t>Niche fans buy knowledge and sit at the tier mix above.</t>
         </is>
@@ -9793,7 +10140,7 @@
       <c r="B25" s="26" t="n">
         <v>0.87</v>
       </c>
-      <c r="D25" s="89" t="inlineStr">
+      <c r="D25" s="87" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: -13%. Popular-sport fans skew to the cheapest tier.</t>
         </is>
@@ -9805,11 +10152,11 @@
           <t>→ Niche ARPU, mature</t>
         </is>
       </c>
-      <c r="B26" s="91">
+      <c r="B26" s="99">
         <f>B22*B24</f>
         <v/>
       </c>
-      <c r="D26" s="89" t="inlineStr"/>
+      <c r="D26" s="87" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -9817,11 +10164,11 @@
           <t>→ Popular ARPU, mature</t>
         </is>
       </c>
-      <c r="B27" s="91">
+      <c r="B27" s="99">
         <f>B22*B25</f>
         <v/>
       </c>
-      <c r="D27" s="89" t="inlineStr"/>
+      <c r="D27" s="87" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -9843,7 +10190,7 @@
         <f>Comparables!B19</f>
         <v/>
       </c>
-      <c r="D29" s="89" t="inlineStr"/>
+      <c r="D29" s="87" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
@@ -9855,7 +10202,7 @@
         <f>Comparables!B20</f>
         <v/>
       </c>
-      <c r="D30" s="89" t="inlineStr"/>
+      <c r="D30" s="87" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
@@ -9867,7 +10214,7 @@
         <f>(B29+B30)/2</f>
         <v/>
       </c>
-      <c r="D31" s="89" t="inlineStr"/>
+      <c r="D31" s="87" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -9879,7 +10226,7 @@
         <f>Comparables!B21</f>
         <v/>
       </c>
-      <c r="D32" s="89" t="inlineStr">
+      <c r="D32" s="87" t="inlineStr">
         <is>
           <t>Patreon: annual patrons churn at one third the monthly rate.</t>
         </is>
@@ -9894,7 +10241,7 @@
       <c r="B33" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="89" t="inlineStr">
+      <c r="D33" s="87" t="inlineStr">
         <is>
           <t>Our target for the season pass. This is the one lever that improves churn without changing the product.</t>
         </is>
@@ -9910,7 +10257,7 @@
         <f>B31*(1-B33)+B31*B32*B33</f>
         <v/>
       </c>
-      <c r="D34" s="89" t="inlineStr">
+      <c r="D34" s="87" t="inlineStr">
         <is>
           <t>What a Patreon-like platform would see with our annual mix.</t>
         </is>
@@ -9925,7 +10272,7 @@
       <c r="B35" s="26" t="n">
         <v>0.55</v>
       </c>
-      <c r="D35" s="89" t="inlineStr">
+      <c r="D35" s="87" t="inlineStr">
         <is>
           <t>OUR CLAIM, UNTESTED, AND THE MOST OPTIMISTIC JUDGEMENT IN THE MODEL: this says niche fans churn 45% SLOWER than the Patreon benchmark, because training content is habitual and competitive seasons create renewal moments. Nothing yet proves it. If it is wrong and we are merely at benchmark, Y10 revenue falls by roughly EUR 7M.</t>
         </is>
@@ -9940,7 +10287,7 @@
       <c r="B36" s="26" t="n">
         <v>0.85</v>
       </c>
-      <c r="D36" s="89" t="inlineStr">
+      <c r="D36" s="87" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: 15% better than benchmark. Impulse follows after a result, with many free substitutes - but still a sport fan rather than a general creator audience.</t>
         </is>
@@ -9952,11 +10299,11 @@
           <t>→ Niche churn, mature</t>
         </is>
       </c>
-      <c r="B37" s="92">
+      <c r="B37" s="100">
         <f>B34*B35</f>
         <v/>
       </c>
-      <c r="D37" s="89" t="inlineStr"/>
+      <c r="D37" s="87" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -9964,11 +10311,11 @@
           <t>→ Popular churn, mature</t>
         </is>
       </c>
-      <c r="B38" s="92">
+      <c r="B38" s="100">
         <f>B34*B36</f>
         <v/>
       </c>
-      <c r="D38" s="89" t="inlineStr"/>
+      <c r="D38" s="87" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
@@ -9990,7 +10337,7 @@
         <f>Comparables!B7/Comparables!B8/12</f>
         <v/>
       </c>
-      <c r="D40" s="89" t="inlineStr">
+      <c r="D40" s="87" t="inlineStr">
         <is>
           <t>Includes dormant accounts, so this is a floor.</t>
         </is>
@@ -10006,7 +10353,7 @@
         <f>Comparables!B15/Comparables!B12/12</f>
         <v/>
       </c>
-      <c r="D41" s="89" t="inlineStr">
+      <c r="D41" s="87" t="inlineStr">
         <is>
           <t>Denominator is creators WITH members, so this is a ceiling.</t>
         </is>
@@ -10018,11 +10365,11 @@
           <t>Stride: modelled niche athlete, mature</t>
         </is>
       </c>
-      <c r="B42" s="91">
+      <c r="B42" s="99">
         <f>B12*B22*(1-Assumptions!$C$40)</f>
         <v/>
       </c>
-      <c r="D42" s="89" t="inlineStr">
+      <c r="D42" s="87" t="inlineStr">
         <is>
           <t>Ours sits between the two, which is where a plausible figure should sit.</t>
         </is>
@@ -10038,7 +10385,7 @@
         <f>Comparables!B11</f>
         <v/>
       </c>
-      <c r="D43" s="89" t="inlineStr">
+      <c r="D43" s="87" t="inlineStr">
         <is>
           <t>THE CAVEAT ON EVERY AVERAGE ABOVE: earnings follow a power law. Totals are unaffected, but the median athlete earns far less than the mean. Do not pitch the mean to an athlete.</t>
         </is>
@@ -10063,7 +10410,7 @@
       <c r="B45" s="26" t="n">
         <v>0.92</v>
       </c>
-      <c r="D45" s="89" t="inlineStr">
+      <c r="D45" s="87" t="inlineStr">
         <is>
           <t>Comparables are published in USD; this model is in EUR. Applied to the per-transaction and monthly creator fees below.</t>
         </is>
@@ -10078,7 +10425,7 @@
       <c r="B46" s="22" t="n">
         <v>300</v>
       </c>
-      <c r="D46" s="89" t="inlineStr">
+      <c r="D46" s="87" t="inlineStr">
         <is>
           <t>Change this to see who is cheapest at any revenue level.</t>
         </is>
@@ -10094,7 +10441,7 @@
         <f>B46*(1-Comparables!B29)-B46/Assumptions!$C$54*Comparables!C29*B45-Comparables!D29*B45</f>
         <v/>
       </c>
-      <c r="D47" s="89" t="inlineStr">
+      <c r="D47" s="87" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -10110,7 +10457,7 @@
         <f>B46*(1-Comparables!B32)-B46/Assumptions!$C$54*Comparables!C32*B45-Comparables!D32*B45</f>
         <v/>
       </c>
-      <c r="D48" s="89" t="inlineStr">
+      <c r="D48" s="87" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -10126,7 +10473,7 @@
         <f>B46*(1-Comparables!B33)-B46/Assumptions!$C$54*Comparables!C33*B45-Comparables!D33*B45</f>
         <v/>
       </c>
-      <c r="D49" s="89" t="inlineStr">
+      <c r="D49" s="87" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -10142,7 +10489,7 @@
         <f>B46*(1-Comparables!B34)-B46/Assumptions!$C$54*Comparables!C34*B45-Comparables!D34*B45</f>
         <v/>
       </c>
-      <c r="D50" s="89" t="inlineStr">
+      <c r="D50" s="87" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -10158,7 +10505,7 @@
         <f>Comparables!D33*B45/((Comparables!B34-Comparables!B33)-Comparables!C33*B45/Assumptions!$C$54)</f>
         <v/>
       </c>
-      <c r="D51" s="89" t="inlineStr">
+      <c r="D51" s="87" t="inlineStr">
         <is>
           <t>Below this, our flat 15% pays the athlete more than Passes' 10% plus fees. Our modelled athlete earns far less than this, so the long tail is on our side of the line.</t>
         </is>
@@ -10180,10 +10527,10 @@
           <t>Population, 34 countries in scope</t>
         </is>
       </c>
-      <c r="B53" s="93" t="n">
+      <c r="B53" s="101" t="n">
         <v>2726.2</v>
       </c>
-      <c r="D53" s="89" t="inlineStr">
+      <c r="D53" s="87" t="inlineStr">
         <is>
           <t>Millions. Eurostat / national statistics offices.</t>
         </is>
@@ -10195,10 +10542,10 @@
           <t>Population, Spain</t>
         </is>
       </c>
-      <c r="B54" s="93" t="n">
+      <c r="B54" s="101" t="n">
         <v>48.6</v>
       </c>
-      <c r="D54" s="89" t="inlineStr">
+      <c r="D54" s="87" t="inlineStr">
         <is>
           <t>Millions.</t>
         </is>
@@ -10213,7 +10560,7 @@
       <c r="B55" s="18" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D55" s="89" t="inlineStr">
+      <c r="D55" s="87" t="inlineStr">
         <is>
           <t>Eurobarometer 525 - Spain sits near the EU average of 55% who exercise at all.</t>
         </is>
@@ -10228,7 +10575,7 @@
       <c r="B56" s="18" t="n">
         <v>0.02</v>
       </c>
-      <c r="D56" s="89" t="inlineStr">
+      <c r="D56" s="87" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: competes, posts publicly, has a following worth sponsoring.</t>
         </is>
@@ -10243,7 +10590,7 @@
       <c r="B57" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="D57" s="89" t="inlineStr">
+      <c r="D57" s="87" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: would monetise if the tooling existed.</t>
         </is>
@@ -10255,11 +10602,11 @@
           <t>→ Addressable athletes, Spain</t>
         </is>
       </c>
-      <c r="B58" s="94">
+      <c r="B58" s="102">
         <f>B54*1000000*B55*B56*B57</f>
         <v/>
       </c>
-      <c r="D58" s="89" t="inlineStr"/>
+      <c r="D58" s="87" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -10267,11 +10614,11 @@
           <t>→ Addressable athletes, all 34 countries</t>
         </is>
       </c>
-      <c r="B59" s="94">
+      <c r="B59" s="102">
         <f>B53*1000000*0.5*B56*B57</f>
         <v/>
       </c>
-      <c r="D59" s="89" t="inlineStr">
+      <c r="D59" s="87" t="inlineStr">
         <is>
           <t>Using a 50% blended participation rate across the 34 countries.</t>
         </is>
@@ -10287,7 +10634,7 @@
         <f>Assumptions!$L$5</f>
         <v/>
       </c>
-      <c r="D60" s="89" t="inlineStr"/>
+      <c r="D60" s="87" t="inlineStr"/>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -10295,11 +10642,11 @@
           <t>→ Y10 penetration of Spain SAM</t>
         </is>
       </c>
-      <c r="B61" s="92">
+      <c r="B61" s="100">
         <f>Assumptions!$L$5/B58</f>
         <v/>
       </c>
-      <c r="D61" s="89" t="inlineStr"/>
+      <c r="D61" s="87" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -10307,11 +10654,11 @@
           <t>→ Y10 penetration of full TAM</t>
         </is>
       </c>
-      <c r="B62" s="92">
+      <c r="B62" s="100">
         <f>Assumptions!$L$5/B59</f>
         <v/>
       </c>
-      <c r="D62" s="89" t="inlineStr">
+      <c r="D62" s="87" t="inlineStr">
         <is>
           <t>If this reads as implausibly high, the athlete trajectory is too aggressive - that is exactly what this block exists to reveal.</t>
         </is>
@@ -10362,37 +10709,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="95" t="inlineStr">
+      <c r="A4" s="103" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="103" t="inlineStr">
         <is>
           <t>Model value</t>
         </is>
       </c>
-      <c r="C4" s="95" t="inlineStr">
+      <c r="C4" s="103" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D4" s="95" t="inlineStr">
+      <c r="D4" s="103" t="inlineStr">
         <is>
           <t>Benchmark / comparable</t>
         </is>
       </c>
-      <c r="E4" s="95" t="inlineStr">
+      <c r="E4" s="103" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F4" s="95" t="inlineStr">
+      <c r="F4" s="103" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="G4" s="95" t="inlineStr">
+      <c r="G4" s="103" t="inlineStr">
         <is>
           <t>What would replace the estimate</t>
         </is>
@@ -10412,7 +10759,7 @@
       <c r="G5" s="14" t="n"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="96" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>Take rate on fan revenue</t>
         </is>
@@ -10421,34 +10768,34 @@
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="C6" s="97" t="inlineStr">
+      <c r="C6" s="104" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D6" s="98" t="inlineStr">
+      <c r="D6" s="105" t="inlineStr">
         <is>
           <t>Passes charges 10% but adds $0.30/txn and a $29/month creator fee; OnlyFans, Fansly and Fanfix are all 20%; Patreon 8-12%. A flat 15% with no monthly fee pays an athlete more than Passes for anyone under EUR 1,380/month of fan revenue.</t>
         </is>
       </c>
-      <c r="E6" s="98" t="inlineStr">
+      <c r="E6" s="105" t="inlineStr">
         <is>
           <t>Sacra company profile (Passes); Passes rebrand release, Apr 2026; MEXC platform comparison 2026</t>
         </is>
       </c>
-      <c r="F6" s="99" t="inlineStr">
+      <c r="F6" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G6" s="98" t="inlineStr">
+      <c r="G6" s="105" t="inlineStr">
         <is>
           <t>Nothing. This is a pricing decision and the comparables are public.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="96" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>Sponsorship commission, Scout Pro</t>
         </is>
@@ -10457,34 +10804,34 @@
         <f>Assumptions!$C$42</f>
         <v/>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="104" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D7" s="98" t="inlineStr">
+      <c r="D7" s="105" t="inlineStr">
         <is>
           <t>7% against a 10% base. A sponsor paying EUR 2,988 a year for the tooling is already paying for the relationship, and charging them the full headline rate on every deal as well is charging twice for it. Below the 10-20% an agent takes, which is the point: the sponsor who commits most pays least on each deal.</t>
         </is>
       </c>
-      <c r="E7" s="98" t="inlineStr">
+      <c r="E7" s="105" t="inlineStr">
         <is>
           <t>Priced against the agent range; the discount itself is a pricing decision</t>
         </is>
       </c>
-      <c r="F7" s="99" t="inlineStr">
+      <c r="F7" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G7" s="98" t="inlineStr">
+      <c r="G7" s="105" t="inlineStr">
         <is>
           <t>Nothing to improve. This is a decision, not a measurement.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="96" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>Sponsorship commission, Scout Agency</t>
         </is>
@@ -10493,34 +10840,34 @@
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
-      <c r="C8" s="97" t="inlineStr">
+      <c r="C8" s="104" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D8" s="98" t="inlineStr">
+      <c r="D8" s="105" t="inlineStr">
         <is>
           <t>5%, which is half the low end of what an agent charges and a quarter of the high end. The most committed tier pays EUR 11,988 a year, so the deal rate can fall furthest here.</t>
         </is>
       </c>
-      <c r="E8" s="98" t="inlineStr">
+      <c r="E8" s="105" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys, 10-20%</t>
         </is>
       </c>
-      <c r="F8" s="99" t="inlineStr">
+      <c r="F8" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G8" s="98" t="inlineStr">
+      <c r="G8" s="105" t="inlineStr">
         <is>
           <t>Nothing to improve. This is a decision, not a measurement.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="96" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Subscriber share of deal volume</t>
         </is>
@@ -10529,34 +10876,34 @@
         <f>Assumptions!$C$44</f>
         <v/>
       </c>
-      <c r="C9" s="100" t="inlineStr">
+      <c r="C9" s="107" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D9" s="98" t="inlineStr">
+      <c r="D9" s="105" t="inlineStr">
         <is>
           <t>Subscribers are assumed to run 2.0x the deal volume of the average sponsor, which with a paid rate of 10-20% puts them at 20-40% of GMV. This is the ONLY estimate in the tiering and it is the one that sets the blended rate, which falls from 9.60% in Y1 to 8.56% by Y10. Deliberately conservative: Scout Pro buys five campaigns against the free tier's one, so 2.0x is well below what the campaign allowance alone would imply. Higher multiples lower the blend further.</t>
         </is>
       </c>
-      <c r="E9" s="98" t="inlineStr">
+      <c r="E9" s="105" t="inlineStr">
         <is>
           <t>None. No tier-level deal volume exists yet, because no tier exists yet</t>
         </is>
       </c>
-      <c r="F9" s="101" t="inlineStr">
+      <c r="F9" s="108" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G9" s="98" t="inlineStr">
+      <c r="G9" s="105" t="inlineStr">
         <is>
           <t>The first year of billing settles it exactly.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="96" t="inlineStr">
+      <c r="A10" s="81" t="inlineStr">
         <is>
           <t>Take rate on sponsorship</t>
         </is>
@@ -10565,101 +10912,101 @@
         <f>Assumptions!$C$41</f>
         <v/>
       </c>
-      <c r="C10" s="97" t="inlineStr">
+      <c r="C10" s="104" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D10" s="98" t="inlineStr">
+      <c r="D10" s="105" t="inlineStr">
         <is>
           <t>Sports agents take 10-20% of an endorsement and 4-10% of a playing contract. On OnlyFans, management agencies take a further 20-50% on top of the platform's 20%.</t>
         </is>
       </c>
-      <c r="E10" s="98" t="inlineStr">
+      <c r="E10" s="105" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys; Aruna Talent agency rate guide 2026</t>
         </is>
       </c>
-      <c r="F10" s="99" t="inlineStr">
+      <c r="F10" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G10" s="98" t="inlineStr">
+      <c r="G10" s="105" t="inlineStr">
         <is>
           <t>Observed deal data once the marketplace is running.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="96" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
         <is>
           <t>Suggested tiers 4.99 / 9.99 / 24.99</t>
         </is>
       </c>
-      <c r="B11" s="102" t="inlineStr">
+      <c r="B11" s="109" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="104" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D11" s="98" t="inlineStr">
+      <c r="D11" s="105" t="inlineStr">
         <is>
           <t>Patreon's typical patronage is quoted at $8-12/month, so the EUR 9.99 anchor sits inside the observed band. EUR 4.99 retains only 54% of our take after payment fees, against 71% at EUR 9.99: which is why the floor matters more than the take rate.</t>
         </is>
       </c>
-      <c r="E11" s="98" t="inlineStr">
+      <c r="E11" s="105" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; independent audits of ~1,200 creators</t>
         </is>
       </c>
-      <c r="F11" s="103" t="inlineStr">
+      <c r="F11" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G11" s="98" t="inlineStr">
+      <c r="G11" s="105" t="inlineStr">
         <is>
           <t>Our own tier mix after P1.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="96" t="inlineStr">
+      <c r="A12" s="81" t="inlineStr">
         <is>
           <t>Season pass / annual billing</t>
         </is>
       </c>
-      <c r="B12" s="102" t="inlineStr">
+      <c r="B12" s="109" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C12" s="104" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D12" s="98" t="inlineStr">
+      <c r="D12" s="105" t="inlineStr">
         <is>
           <t>Patreon reports that annual patrons churn at ONE THIRD the rate of monthly patrons. This is the single strongest piece of evidence in the plan for pushing annual billing.</t>
         </is>
       </c>
-      <c r="E12" s="98" t="inlineStr">
+      <c r="E12" s="105" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F12" s="99" t="inlineStr">
+      <c r="F12" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G12" s="98" t="inlineStr">
+      <c r="G12" s="105" t="inlineStr">
         <is>
           <t>Already strong. Confirm on our own cohorts.</t>
         </is>
@@ -10679,7 +11026,7 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="96" t="inlineStr">
+      <c r="A14" s="81" t="inlineStr">
         <is>
           <t>Fan ARPU per month</t>
         </is>
@@ -10688,34 +11035,34 @@
         <f>Assumptions!$C$12</f>
         <v/>
       </c>
-      <c r="C14" s="97" t="inlineStr">
+      <c r="C14" s="104" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D14" s="98" t="inlineStr">
+      <c r="D14" s="105" t="inlineStr">
         <is>
           <t>Patreon's average monthly support rose from $5.40 to $6.10 during 2024, with typical patronage quoted at $8-12. Our EUR 8.00-9.50 sits in the upper-middle of that range.</t>
         </is>
       </c>
-      <c r="E14" s="98" t="inlineStr">
+      <c r="E14" s="105" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F14" s="103" t="inlineStr">
+      <c r="F14" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G14" s="98" t="inlineStr">
+      <c r="G14" s="105" t="inlineStr">
         <is>
           <t>Actual ARPU by tier and sport after P1.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="96" t="inlineStr">
+      <c r="A15" s="81" t="inlineStr">
         <is>
           <t>Fan churn per month</t>
         </is>
@@ -10724,34 +11071,34 @@
         <f>Assumptions!$C$13</f>
         <v/>
       </c>
-      <c r="C15" s="100" t="inlineStr">
+      <c r="C15" s="107" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D15" s="98" t="inlineStr">
+      <c r="D15" s="105" t="inlineStr">
         <is>
           <t>OPTIMISTIC AGAINST BENCHMARK. Patreon runs 10-15% monthly. We assume 6-9% (niche) and 9-13% (popular), arguing that training content is habitual and that competitive seasons create natural renewal moments. That argument is currently untested.</t>
         </is>
       </c>
-      <c r="E15" s="98" t="inlineStr">
+      <c r="E15" s="105" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (10-15%/month)</t>
         </is>
       </c>
-      <c r="F15" s="101" t="inlineStr">
+      <c r="F15" s="108" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G15" s="98" t="inlineStr">
+      <c r="G15" s="105" t="inlineStr">
         <is>
           <t>THE most important number to measure in P1. Three months of real cohorts settles it. Until then the conservative case should be treated as the plan.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="96" t="inlineStr">
+      <c r="A16" s="81" t="inlineStr">
         <is>
           <t>Paying fans per monetising athlete</t>
         </is>
@@ -10760,34 +11107,34 @@
         <f>Assumptions!$C$11</f>
         <v/>
       </c>
-      <c r="C16" s="105" t="inlineStr">
+      <c r="C16" s="112" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D16" s="98" t="inlineStr">
+      <c r="D16" s="105" t="inlineStr">
         <is>
           <t>20 rising to 48 over ten years. Cross-check: Patreon creators average $350/month and our modelled niche athlete at maturity earns about EUR 313/month, closely aligned, which is reassuring for an assumption built bottom-up rather than from a comparable.</t>
         </is>
       </c>
-      <c r="E16" s="98" t="inlineStr">
+      <c r="E16" s="105" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (creator average $350/month)</t>
         </is>
       </c>
-      <c r="F16" s="103" t="inlineStr">
+      <c r="F16" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G16" s="98" t="inlineStr">
+      <c r="G16" s="105" t="inlineStr">
         <is>
           <t>Observed fans per athlete, banded by follower count.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="96" t="inlineStr">
+      <c r="A17" s="81" t="inlineStr">
         <is>
           <t>Share of athletes who monetise</t>
         </is>
@@ -10796,64 +11143,64 @@
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="C17" s="100" t="inlineStr">
+      <c r="C17" s="107" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D17" s="98" t="inlineStr">
+      <c r="D17" s="105" t="inlineStr">
         <is>
           <t>28% rising to 50% for niche sports. No direct comparable exists: neither Patreon nor OnlyFans publishes activation rates for creators who sign up but never charge.</t>
         </is>
       </c>
-      <c r="E17" s="98" t="inlineStr">
+      <c r="E17" s="105" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F17" s="101" t="inlineStr">
+      <c r="F17" s="108" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G17" s="98" t="inlineStr">
+      <c r="G17" s="105" t="inlineStr">
         <is>
           <t>Our own activation funnel, available from P1 onward.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="96" t="inlineStr">
+      <c r="A18" s="81" t="inlineStr">
         <is>
           <t>Fan acquisition capacity</t>
         </is>
       </c>
-      <c r="B18" s="102" t="inlineStr">
+      <c r="B18" s="109" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C18" s="100" t="inlineStr">
+      <c r="C18" s="107" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D18" s="98" t="inlineStr">
+      <c r="D18" s="105" t="inlineStr">
         <is>
           <t>An athlete can recruit 30-69 new paying fans a year depending on segment. This ceiling is what makes churn bite in the model: without it, higher churn perversely RAISED revenue, because the year-end target was reachable at any churn rate.</t>
         </is>
       </c>
-      <c r="E18" s="98" t="inlineStr">
+      <c r="E18" s="105" t="inlineStr">
         <is>
           <t>None: introduced to fix a modelling flaw found by stress testing</t>
         </is>
       </c>
-      <c r="F18" s="101" t="inlineStr">
+      <c r="F18" s="108" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G18" s="98" t="inlineStr">
+      <c r="G18" s="105" t="inlineStr">
         <is>
           <t>Observed gross adds per athlete per year.</t>
         </is>
@@ -10873,7 +11220,7 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="96" t="inlineStr">
+      <c r="A20" s="81" t="inlineStr">
         <is>
           <t>PSP percentage fee</t>
         </is>
@@ -10882,34 +11229,34 @@
         <f>Assumptions!$C$50</f>
         <v/>
       </c>
-      <c r="C20" s="104" t="inlineStr">
+      <c r="C20" s="111" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D20" s="98" t="inlineStr">
+      <c r="D20" s="105" t="inlineStr">
         <is>
           <t>Stripe for a Spanish entity: 1.5% + EUR 0.25 on EEA domestic cards, 2.5% on UK cards, 3.25% on non-EEA. 1.9% is the blend for a mostly-European fan base. CORRECTION: an earlier version of this model used the US headline of 2.9% and overstated the largest cost line in the business by about a third.</t>
         </is>
       </c>
-      <c r="E20" s="98" t="inlineStr">
+      <c r="E20" s="105" t="inlineStr">
         <is>
           <t>Stripe published EU/EEA pricing, 2026</t>
         </is>
       </c>
-      <c r="F20" s="99" t="inlineStr">
+      <c r="F20" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G20" s="98" t="inlineStr">
+      <c r="G20" s="105" t="inlineStr">
         <is>
           <t>Interchange-plus terms become negotiable above roughly EUR 5M processed.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="96" t="inlineStr">
+      <c r="A21" s="81" t="inlineStr">
         <is>
           <t>PSP fixed fee per transaction</t>
         </is>
@@ -10918,34 +11265,34 @@
         <f>Assumptions!$C$51</f>
         <v/>
       </c>
-      <c r="C21" s="104" t="inlineStr">
+      <c r="C21" s="111" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D21" s="98" t="inlineStr">
+      <c r="D21" s="105" t="inlineStr">
         <is>
           <t>EUR 0.25 per transaction. On a EUR 4.99 tier that single fee is a third of our take, which is why the tier floor and annual billing move more margin than the take rate does.</t>
         </is>
       </c>
-      <c r="E21" s="98" t="inlineStr">
+      <c r="E21" s="105" t="inlineStr">
         <is>
           <t>Stripe published pricing, 2026</t>
         </is>
       </c>
-      <c r="F21" s="99" t="inlineStr">
+      <c r="F21" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G21" s="98" t="inlineStr">
+      <c r="G21" s="105" t="inlineStr">
         <is>
           <t>Volume renegotiation; annual billing turns twelve fees into one.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="96" t="inlineStr">
+      <c r="A22" s="81" t="inlineStr">
         <is>
           <t>Payout fees</t>
         </is>
@@ -10954,27 +11301,27 @@
         <f>Assumptions!$C$52</f>
         <v/>
       </c>
-      <c r="C22" s="104" t="inlineStr">
+      <c r="C22" s="111" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D22" s="98" t="inlineStr">
+      <c r="D22" s="105" t="inlineStr">
         <is>
           <t>Stripe Connect Express: roughly 0.25% + EUR 0.25 per payout, plus a monthly active-account fee that is not modelled as a separate line.</t>
         </is>
       </c>
-      <c r="E22" s="98" t="inlineStr">
+      <c r="E22" s="105" t="inlineStr">
         <is>
           <t>Stripe Connect pricing, 2026</t>
         </is>
       </c>
-      <c r="F22" s="103" t="inlineStr">
+      <c r="F22" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G22" s="98" t="inlineStr">
+      <c r="G22" s="105" t="inlineStr">
         <is>
           <t>Actual payout frequency once athletes are onboarded.</t>
         </is>
@@ -10994,118 +11341,118 @@
       <c r="G23" s="14" t="n"/>
     </row>
     <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="96" t="inlineStr">
+      <c r="A24" s="81" t="inlineStr">
         <is>
           <t>Sport participation by country</t>
         </is>
       </c>
-      <c r="B24" s="102" t="inlineStr">
+      <c r="B24" s="109" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C24" s="100" t="inlineStr">
+      <c r="C24" s="107" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D24" s="98" t="inlineStr">
+      <c r="D24" s="105" t="inlineStr">
         <is>
           <t>Eurobarometer 525, share who NEVER exercise: Finland 8%, Sweden 12%, Denmark 20%, Poland 65%, Greece 68%, Portugal 73%, EU-27 average 45%. Six of the 34 countries in the index are measured; the other 28 are estimates placed inside that distribution.</t>
         </is>
       </c>
-      <c r="E24" s="98" t="inlineStr">
+      <c r="E24" s="105" t="inlineStr">
         <is>
           <t>Special Eurobarometer 525, Sport and Physical Activity, September 2022</t>
         </is>
       </c>
-      <c r="F24" s="103" t="inlineStr">
+      <c r="F24" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G24" s="98" t="inlineStr">
+      <c r="G24" s="105" t="inlineStr">
         <is>
           <t>Federation licence counts, published annually and free (CSD in Spain).</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="96" t="inlineStr">
+      <c r="A25" s="81" t="inlineStr">
         <is>
           <t>Padel market size</t>
         </is>
       </c>
-      <c r="B25" s="102" t="inlineStr">
+      <c r="B25" s="109" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C25" s="104" t="inlineStr">
+      <c r="C25" s="111" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D25" s="98" t="inlineStr">
+      <c r="D25" s="105" t="inlineStr">
         <is>
           <t>Spain has ~6.0M active players (12.7% of the population), 109,040 federation licences and 17,300+ courts; globally 35M+ players and 77,000+ courts. This is the clearest case for weighting a sport regionally rather than globally, padel scores 77.7 in Spain and 45.1 worldwide.</t>
         </is>
       </c>
-      <c r="E25" s="98" t="inlineStr">
+      <c r="E25" s="105" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="F25" s="99" t="inlineStr">
+      <c r="F25" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G25" s="98" t="inlineStr">
+      <c r="G25" s="105" t="inlineStr">
         <is>
           <t>Annual FIP refresh.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="96" t="inlineStr">
+      <c r="A26" s="81" t="inlineStr">
         <is>
           <t>Sports fandom by country</t>
         </is>
       </c>
-      <c r="B26" s="102" t="inlineStr">
+      <c r="B26" s="109" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C26" s="100" t="inlineStr">
+      <c r="C26" s="107" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D26" s="98" t="inlineStr">
+      <c r="D26" s="105" t="inlineStr">
         <is>
           <t>The weakest layer of the sport index, and it drives both the `demand` and `appetite` signals. Commercial audience panels (Nielsen Sports, YouGov) cost more than the entire Y1-Y2 analytics budget.</t>
         </is>
       </c>
-      <c r="E26" s="98" t="inlineStr">
+      <c r="E26" s="105" t="inlineStr">
         <is>
           <t>None: reasoned estimates only</t>
         </is>
       </c>
-      <c r="F26" s="101" t="inlineStr">
+      <c r="F26" s="108" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G26" s="98" t="inlineStr">
+      <c r="G26" s="105" t="inlineStr">
         <is>
           <t>Our own engagement data per sport per country once connectors are live. This is what makes the index self-improving rather than something anyone could copy.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="96" t="inlineStr">
+      <c r="A27" s="81" t="inlineStr">
         <is>
           <t>Athlete count trajectory</t>
         </is>
@@ -11114,27 +11461,27 @@
         <f>Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="C27" s="100" t="inlineStr">
+      <c r="C27" s="107" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D27" s="98" t="inlineStr">
-        <is>
-          <t>400 rising to 40,000 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
-        </is>
-      </c>
-      <c r="E27" s="98" t="inlineStr">
+      <c r="D27" s="105" t="inlineStr">
+        <is>
+          <t>250 rising to 8,500 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
+        </is>
+      </c>
+      <c r="E27" s="105" t="inlineStr">
         <is>
           <t>None: it is a target</t>
         </is>
       </c>
-      <c r="F27" s="101" t="inlineStr">
+      <c r="F27" s="108" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G27" s="98" t="inlineStr">
+      <c r="G27" s="105" t="inlineStr">
         <is>
           <t>The pre-seed gate tests it directly: 400 athletes and EUR 10k MRR.</t>
         </is>
@@ -11154,7 +11501,7 @@
       <c r="G28" s="14" t="n"/>
     </row>
     <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="96" t="inlineStr">
+      <c r="A29" s="81" t="inlineStr">
         <is>
           <t>Athlete CAC</t>
         </is>
@@ -11163,34 +11510,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C29" s="100" t="inlineStr">
+      <c r="C29" s="107" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D29" s="98" t="inlineStr">
+      <c r="D29" s="105" t="inlineStr">
         <is>
           <t>EUR 16-36 for niche, EUR 40-88 for popular. The gap reflects displacing an existing agent relationship versus reaching someone with no representation at all. No published comparable exists for athlete acquisition in this segment.</t>
         </is>
       </c>
-      <c r="E29" s="98" t="inlineStr">
+      <c r="E29" s="105" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F29" s="101" t="inlineStr">
+      <c r="F29" s="108" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G29" s="98" t="inlineStr">
+      <c r="G29" s="105" t="inlineStr">
         <is>
           <t>Measured CAC by channel from the first federation partnership.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="96" t="inlineStr">
+      <c r="A30" s="81" t="inlineStr">
         <is>
           <t>Admission rate, direct applicants</t>
         </is>
@@ -11199,34 +11546,34 @@
         <f>Assumptions!$C$82</f>
         <v/>
       </c>
-      <c r="C30" s="105" t="inlineStr">
+      <c r="C30" s="112" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D30" s="98" t="inlineStr">
+      <c r="D30" s="105" t="inlineStr">
         <is>
           <t>20% of direct applicants are admitted, 25% go to a human, 40% are refused and 15% never finish the form. Not a judgement: it is the ops-load output of scripts/admission_stress.py run over the admission policy itself, so retuning a threshold moves this figure. The sweep asserts the model and the policy stay in step and fails if they drift.</t>
         </is>
       </c>
-      <c r="E30" s="98" t="inlineStr">
+      <c r="E30" s="105" t="inlineStr">
         <is>
           <t>scripts/admission_stress.py, section 7, over a modelled applicant mix</t>
         </is>
       </c>
-      <c r="F30" s="103" t="inlineStr">
+      <c r="F30" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G30" s="98" t="inlineStr">
+      <c r="G30" s="105" t="inlineStr">
         <is>
           <t>Real intake data. The mix the sweep assumes is the soft part, not the arithmetic.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="96" t="inlineStr">
+      <c r="A31" s="81" t="inlineStr">
         <is>
           <t>Admission rate, club-nominated</t>
         </is>
@@ -11235,34 +11582,34 @@
         <f>Assumptions!$C$84</f>
         <v/>
       </c>
-      <c r="C31" s="100" t="inlineStr">
+      <c r="C31" s="107" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D31" s="98" t="inlineStr">
+      <c r="D31" s="105" t="inlineStr">
         <is>
           <t>45% admitted against 20% direct. A verified club's nomination confers a credibility floor of 0.75 x its own legitimacy score, which carries a completed application over the admit line that would otherwise have gone to review. It cannot carry an empty one: no club can supply someone else's date of birth, so the uplift is real but bounded.</t>
         </is>
       </c>
-      <c r="E31" s="98" t="inlineStr">
+      <c r="E31" s="105" t="inlineStr">
         <is>
           <t>None: the mechanism is built and tested, the conversion is not yet measured</t>
         </is>
       </c>
-      <c r="F31" s="101" t="inlineStr">
+      <c r="F31" s="108" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G31" s="98" t="inlineStr">
+      <c r="G31" s="105" t="inlineStr">
         <is>
           <t>The first federation partnership: nominated applicants are tagged, so this is measurable from day one of it.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="96" t="inlineStr">
+      <c r="A32" s="81" t="inlineStr">
         <is>
           <t>Athlete verification cost</t>
         </is>
@@ -11271,34 +11618,34 @@
         <f>Assumptions!$C$87</f>
         <v/>
       </c>
-      <c r="C32" s="105" t="inlineStr">
+      <c r="C32" s="112" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D32" s="98" t="inlineStr">
+      <c r="D32" s="105" t="inlineStr">
         <is>
           <t>Four minutes per manual review, priced at the same loaded salary the People line uses, over 1,700 productive hours. Peaks at EUR 47k and 0.64 reviewer-FTE in Y10, which is the finding rather than the cost: verification is not a money problem at this scale. The reason to automate it is latency: an athlete sitting in the queue is not listed, not matchable and not earning.</t>
         </is>
       </c>
-      <c r="E32" s="98" t="inlineStr">
+      <c r="E32" s="105" t="inlineStr">
         <is>
           <t>Derived from the sweep's review volume and the model's own salary line</t>
         </is>
       </c>
-      <c r="F32" s="103" t="inlineStr">
+      <c r="F32" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G32" s="98" t="inlineStr">
+      <c r="G32" s="105" t="inlineStr">
         <is>
           <t>Timing real reviews. Four minutes is an estimate of a mechanical task.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="96" t="inlineStr">
+      <c r="A33" s="81" t="inlineStr">
         <is>
           <t>Athlete CAC vs the funnel</t>
         </is>
@@ -11307,34 +11654,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C33" s="100" t="inlineStr">
+      <c r="C33" s="107" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D33" s="98" t="inlineStr">
+      <c r="D33" s="105" t="inlineStr">
         <is>
           <t>Deliberately NOT multiplied by the admission funnel. Segment CAC is defined as the cost of landing one athlete ON the platform, so scaling it by 1/admission-rate would charge the same money twice. The Costs sheet carries a memo line showing what that CAC works out to per application (EUR 3.40 in Y1 rising to EUR 22), the figure to hold against what a channel actually charges per name reached.</t>
         </is>
       </c>
-      <c r="E33" s="98" t="inlineStr">
+      <c r="E33" s="105" t="inlineStr">
         <is>
           <t>None: this is a definitional choice, made explicit so it is not silently reversed</t>
         </is>
       </c>
-      <c r="F33" s="101" t="inlineStr">
+      <c r="F33" s="108" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G33" s="98" t="inlineStr">
+      <c r="G33" s="105" t="inlineStr">
         <is>
           <t>Channel-level spend against applications, which the funnel now records.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="96" t="inlineStr">
+      <c r="A34" s="81" t="inlineStr">
         <is>
           <t>Loaded salary, Spain</t>
         </is>
@@ -11343,34 +11690,34 @@
         <f>Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="C34" s="97" t="inlineStr">
+      <c r="C34" s="104" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D34" s="98" t="inlineStr">
+      <c r="D34" s="105" t="inlineStr">
         <is>
           <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k, around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
         </is>
       </c>
-      <c r="E34" s="98" t="inlineStr">
+      <c r="E34" s="105" t="inlineStr">
         <is>
           <t>Spanish Seguridad Social employer contribution rates</t>
         </is>
       </c>
-      <c r="F34" s="103" t="inlineStr">
+      <c r="F34" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G34" s="98" t="inlineStr">
+      <c r="G34" s="105" t="inlineStr">
         <is>
           <t>Actual offers accepted.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="96" t="inlineStr">
+      <c r="A35" s="81" t="inlineStr">
         <is>
           <t>AWS infrastructure</t>
         </is>
@@ -11379,34 +11726,34 @@
         <f>Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="C35" s="97" t="inlineStr">
+      <c r="C35" s="104" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D35" s="98" t="inlineStr">
+      <c r="D35" s="105" t="inlineStr">
         <is>
           <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
         </is>
       </c>
-      <c r="E35" s="98" t="inlineStr">
+      <c r="E35" s="105" t="inlineStr">
         <is>
           <t>AWS published list pricing, 2026</t>
         </is>
       </c>
-      <c r="F35" s="103" t="inlineStr">
+      <c r="F35" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G35" s="98" t="inlineStr">
+      <c r="G35" s="105" t="inlineStr">
         <is>
           <t>Actual bills; commit to Savings Plans once usage is stable.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="96" t="inlineStr">
+      <c r="A36" s="81" t="inlineStr">
         <is>
           <t>Media egress</t>
         </is>
@@ -11415,34 +11762,34 @@
         <f>Assumptions!$C$60</f>
         <v/>
       </c>
-      <c r="C36" s="104" t="inlineStr">
+      <c r="C36" s="111" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D36" s="98" t="inlineStr">
+      <c r="D36" s="105" t="inlineStr">
         <is>
           <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year, the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
         </is>
       </c>
-      <c r="E36" s="98" t="inlineStr">
+      <c r="E36" s="105" t="inlineStr">
         <is>
           <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
         </is>
       </c>
-      <c r="F36" s="99" t="inlineStr">
+      <c r="F36" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G36" s="98" t="inlineStr">
+      <c r="G36" s="105" t="inlineStr">
         <is>
           <t>Nothing. Both are published.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="96" t="inlineStr">
+      <c r="A37" s="81" t="inlineStr">
         <is>
           <t>Moderation cost</t>
         </is>
@@ -11451,27 +11798,27 @@
         <f>Assumptions!$C$62</f>
         <v/>
       </c>
-      <c r="C37" s="100" t="inlineStr">
+      <c r="C37" s="107" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D37" s="98" t="inlineStr">
+      <c r="D37" s="105" t="inlineStr">
         <is>
           <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
         </is>
       </c>
-      <c r="E37" s="98" t="inlineStr">
+      <c r="E37" s="105" t="inlineStr">
         <is>
           <t>None cited</t>
         </is>
       </c>
-      <c r="F37" s="101" t="inlineStr">
+      <c r="F37" s="108" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G37" s="98" t="inlineStr">
+      <c r="G37" s="105" t="inlineStr">
         <is>
           <t>Vendor quotes once P2 scope is fixed.</t>
         </is>
@@ -11491,7 +11838,7 @@
       <c r="G38" s="14" t="n"/>
     </row>
     <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="96" t="inlineStr">
+      <c r="A39" s="81" t="inlineStr">
         <is>
           <t>Corporate tax rates</t>
         </is>
@@ -11500,34 +11847,34 @@
         <f>Assumptions!$C$77</f>
         <v/>
       </c>
-      <c r="C39" s="104" t="inlineStr">
+      <c r="C39" s="111" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D39" s="98" t="inlineStr">
+      <c r="D39" s="105" t="inlineStr">
         <is>
           <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
         </is>
       </c>
-      <c r="E39" s="98" t="inlineStr">
+      <c r="E39" s="105" t="inlineStr">
         <is>
           <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
         </is>
       </c>
-      <c r="F39" s="99" t="inlineStr">
+      <c r="F39" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G39" s="98" t="inlineStr">
+      <c r="G39" s="105" t="inlineStr">
         <is>
           <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="96" t="inlineStr">
+      <c r="A40" s="81" t="inlineStr">
         <is>
           <t>Risk-free rate</t>
         </is>
@@ -11536,71 +11883,71 @@
         <f>Assumptions!$C$97</f>
         <v/>
       </c>
-      <c r="C40" s="104" t="inlineStr">
+      <c r="C40" s="111" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D40" s="98" t="inlineStr">
+      <c r="D40" s="105" t="inlineStr">
         <is>
           <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
         </is>
       </c>
-      <c r="E40" s="98" t="inlineStr">
+      <c r="E40" s="105" t="inlineStr">
         <is>
           <t>Spanish 10Y government bond yield</t>
         </is>
       </c>
-      <c r="F40" s="99" t="inlineStr">
+      <c r="F40" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G40" s="98" t="inlineStr">
+      <c r="G40" s="105" t="inlineStr">
         <is>
           <t>Refresh at the date of any raise.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="96" t="inlineStr">
+      <c r="A41" s="81" t="inlineStr">
         <is>
           <t>WACC / discount rate</t>
         </is>
       </c>
-      <c r="B41" s="102" t="inlineStr">
+      <c r="B41" s="109" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C41" s="97" t="inlineStr">
+      <c r="C41" s="104" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D41" s="98" t="inlineStr">
+      <c r="D41" s="105" t="inlineStr">
         <is>
           <t>25%, against a published mature-company anchor of 6.01%. Damodaran's European cost of capital dataset puts Software (Internet) at 6.01% in euros across 23 listed firms, and the European market ex-financials at 6.59%. Those are costs of capital for mature listed companies; this is a pre-revenue venture, and the 19-point gap is the stage premium. It is stated rather than buried because it is the largest single judgement in the valuation. Damodaran publishes no dataset for venture-stage rates, so the premium itself is convention (20-35% is the usual range) and not a sourced figure. The sensitivity grid runs 20-30% because this is arguable rather than knowable.</t>
         </is>
       </c>
-      <c r="E41" s="98" t="inlineStr">
+      <c r="E41" s="105" t="inlineStr">
         <is>
           <t>Aswath Damodaran, NYU Stern, Cost of Capital by Industry (Europe), updated 5 January 2026</t>
         </is>
       </c>
-      <c r="F41" s="103" t="inlineStr">
+      <c r="F41" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G41" s="98" t="inlineStr">
+      <c r="G41" s="105" t="inlineStr">
         <is>
           <t>An actual term sheet prices this for you.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="96" t="inlineStr">
+      <c r="A42" s="81" t="inlineStr">
         <is>
           <t>Exit revenue multiple</t>
         </is>
@@ -11609,34 +11956,34 @@
         <f>Assumptions!$C$96</f>
         <v/>
       </c>
-      <c r="C42" s="97" t="inlineStr">
+      <c r="C42" s="104" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D42" s="98" t="inlineStr">
+      <c r="D42" s="105" t="inlineStr">
         <is>
           <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
         </is>
       </c>
-      <c r="E42" s="98" t="inlineStr">
+      <c r="E42" s="105" t="inlineStr">
         <is>
           <t>Public marketplace and SaaS trading multiples</t>
         </is>
       </c>
-      <c r="F42" s="103" t="inlineStr">
+      <c r="F42" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G42" s="98" t="inlineStr">
+      <c r="G42" s="105" t="inlineStr">
         <is>
           <t>Comparable private transactions nearer an exit.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="96" t="inlineStr">
+      <c r="A43" s="81" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
@@ -11645,27 +11992,27 @@
         <f>Assumptions!$C$95</f>
         <v/>
       </c>
-      <c r="C43" s="97" t="inlineStr">
+      <c r="C43" s="104" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D43" s="98" t="inlineStr">
+      <c r="D43" s="105" t="inlineStr">
         <is>
           <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
         </is>
       </c>
-      <c r="E43" s="98" t="inlineStr">
+      <c r="E43" s="105" t="inlineStr">
         <is>
           <t>Standard DCF convention</t>
         </is>
       </c>
-      <c r="F43" s="103" t="inlineStr">
+      <c r="F43" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G43" s="98" t="inlineStr">
+      <c r="G43" s="105" t="inlineStr">
         <is>
           <t>Nothing: it is a convention, and the grid shows its effect.</t>
         </is>
@@ -11685,112 +12032,112 @@
       <c r="G44" s="14" t="n"/>
     </row>
     <row r="45" ht="58" customHeight="1">
-      <c r="A45" s="96" t="inlineStr">
+      <c r="A45" s="81" t="inlineStr">
         <is>
           <t>Payout age floor</t>
         </is>
       </c>
-      <c r="B45" s="102" t="inlineStr">
+      <c r="B45" s="109" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C45" s="104" t="inlineStr">
+      <c r="C45" s="111" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D45" s="98" t="inlineStr">
+      <c r="D45" s="105" t="inlineStr">
         <is>
           <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
         </is>
       </c>
-      <c r="E45" s="98" t="inlineStr">
+      <c r="E45" s="105" t="inlineStr">
         <is>
           <t>Stripe Connect documentation</t>
         </is>
       </c>
-      <c r="F45" s="99" t="inlineStr">
+      <c r="F45" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G45" s="98" t="inlineStr">
+      <c r="G45" s="105" t="inlineStr">
         <is>
           <t>Nothing: it is a hard platform rule.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
-      <c r="A46" s="96" t="inlineStr">
+      <c r="A46" s="81" t="inlineStr">
         <is>
           <t>Digital consent age, Spain</t>
         </is>
       </c>
-      <c r="B46" s="102" t="inlineStr">
+      <c r="B46" s="109" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C46" s="104" t="inlineStr">
+      <c r="C46" s="111" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D46" s="98" t="inlineStr">
+      <c r="D46" s="105" t="inlineStr">
         <is>
           <t>14 today under LOPDGDD Art. 7. A draft Organic Law on the Protection of Minors in Digital Environments would raise it to 16 and make age verification mandatory, which is why 16 is the forward-compatible floor for an account.</t>
         </is>
       </c>
-      <c r="E46" s="98" t="inlineStr">
+      <c r="E46" s="105" t="inlineStr">
         <is>
           <t>LOPDGDD Art. 7; draft Organic Law, Council of Ministers, March 2025</t>
         </is>
       </c>
-      <c r="F46" s="99" t="inlineStr">
+      <c r="F46" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G46" s="98" t="inlineStr">
+      <c r="G46" s="105" t="inlineStr">
         <is>
           <t>Track the bill through Parliament.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="106" t="inlineStr">
+      <c r="A48" s="113" t="inlineStr">
         <is>
           <t>THE THREE ASSUMPTIONS MOST LIKELY TO BE WRONG</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="107" t="inlineStr">
+      <c r="A49" s="114" t="inlineStr">
         <is>
           <t>1. Fan churn. We assume 6-13%/month; Patreon reports 10-15%. If Patreon is right, Y10 revenue falls from about EUR 58M to EUR 51M and the capital requirement roughly doubles.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="107" t="inlineStr">
+      <c r="A50" s="114" t="inlineStr">
         <is>
           <t>2. Athlete count. The trajectory is a target, not a forecast, and everything scales off it.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="107" t="inlineStr">
+      <c r="A51" s="114" t="inlineStr">
         <is>
           <t>3. Share of athletes who monetise. No published comparable exists at all.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="108" t="inlineStr"/>
+      <c r="A52" s="115" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="108" t="inlineStr">
+      <c r="A53" s="115" t="inlineStr">
         <is>
           <t>All three are answered by the same thing: three months of real cohort data from P1.</t>
         </is>
@@ -11930,34 +12277,34 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1200</v>
+        <v>750</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>3000</v>
+        <v>1700</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>6000</v>
+        <v>2800</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>10500</v>
+        <v>4000</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>16000</v>
+        <v>5200</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>22000</v>
+        <v>6300</v>
       </c>
       <c r="J5" s="17" t="n">
-        <v>28000</v>
+        <v>7200</v>
       </c>
       <c r="K5" s="17" t="n">
-        <v>34000</v>
+        <v>7900</v>
       </c>
       <c r="L5" s="17" t="n">
-        <v>40000</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="6">
@@ -13004,34 +13351,34 @@
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D34" s="17" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>230</v>
+        <v>125</v>
       </c>
       <c r="F34" s="17" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="G34" s="17" t="n">
-        <v>900</v>
+        <v>380</v>
       </c>
       <c r="H34" s="17" t="n">
-        <v>1400</v>
+        <v>510</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>2000</v>
+        <v>620</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>2600</v>
+        <v>710</v>
       </c>
       <c r="K34" s="17" t="n">
-        <v>3100</v>
+        <v>790</v>
       </c>
       <c r="L34" s="17" t="n">
-        <v>3600</v>
+        <v>850</v>
       </c>
     </row>
     <row r="35">
@@ -14074,34 +14421,34 @@
         </is>
       </c>
       <c r="C58" s="24" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D58" s="24" t="n">
-        <v>650</v>
+        <v>420</v>
       </c>
       <c r="E58" s="24" t="n">
-        <v>2100</v>
+        <v>1000</v>
       </c>
       <c r="F58" s="24" t="n">
-        <v>5400</v>
+        <v>2000</v>
       </c>
       <c r="G58" s="24" t="n">
-        <v>11000</v>
+        <v>3200</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>17000</v>
+        <v>4300</v>
       </c>
       <c r="I58" s="24" t="n">
-        <v>24000</v>
+        <v>5300</v>
       </c>
       <c r="J58" s="24" t="n">
-        <v>30000</v>
+        <v>6200</v>
       </c>
       <c r="K58" s="24" t="n">
-        <v>35000</v>
+        <v>7000</v>
       </c>
       <c r="L58" s="24" t="n">
-        <v>39000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="59">
@@ -14402,31 +14749,31 @@
         <v>1</v>
       </c>
       <c r="D66" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="23" t="n">
         <v>1.5</v>
       </c>
-      <c r="E66" s="23" t="n">
+      <c r="F66" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="F66" s="23" t="n">
-        <v>3.5</v>
-      </c>
       <c r="G66" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H66" s="23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I66" s="23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J66" s="23" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="K66" s="23" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="L66" s="23" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67">

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -14779,7 +14779,7 @@
     <row r="67">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>Loaded salary (incl. ~31% employer SS)</t>
+          <t>Loaded salary (incl. ~32% employer SS)</t>
         </is>
       </c>
       <c r="B67" s="16" t="inlineStr">

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -346,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -434,8 +434,9 @@
     <xf numFmtId="164" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="14" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="14" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8329,7 +8330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -9241,563 +9242,1197 @@
     <row r="41">
       <c r="A41" s="77" t="inlineStr">
         <is>
-          <t>SPONSORSHIP MARKETPLACES - the direct competitor set</t>
+          <t>SPONSORSHIP MARKET - top down, for context not for sizing</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="71" t="inlineStr">
         <is>
-          <t>PitchBook company profiles retrieved 1 Oct 2026, reported in EUR. None of the four discloses revenue, so headcount and capital raised are the only scale measures available. Links at the bottom of this sheet.</t>
+          <t>European Sponsorship Association, analysis by Nielsen Sports, published 12 Mar 2026. NOTE: none of it breaks below the professional tier, so it is context rather than our addressable market. The athlete funnel on Research is what sizes the business.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="72" t="inlineStr">
         <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B43" s="72" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C43" s="72" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D43" s="72" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="E43" s="72" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="F43" s="72" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="73" t="inlineStr">
+        <is>
+          <t>Total sponsorship market</t>
+        </is>
+      </c>
+      <c r="B44" s="81" t="n">
+        <v>34450000000</v>
+      </c>
+      <c r="C44" s="75" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D44" s="75" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="E44" s="75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F44" s="75" t="inlineStr">
+        <is>
+          <t>European Sponsorship Association, analysis by Nielsen Sports, 12 Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="73" t="inlineStr">
+        <is>
+          <t>Sport sponsorship market</t>
+        </is>
+      </c>
+      <c r="B45" s="81" t="n">
+        <v>24790000000</v>
+      </c>
+      <c r="C45" s="75" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D45" s="75" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="E45" s="75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F45" s="75" t="inlineStr">
+        <is>
+          <t>ESA / Nielsen Sports: 72% of the total, +5.9% YoY</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="73" t="inlineStr">
+        <is>
+          <t>Non-sport sponsorship</t>
+        </is>
+      </c>
+      <c r="B46" s="81" t="n">
+        <v>9660000000</v>
+      </c>
+      <c r="C46" s="75" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D46" s="75" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="E46" s="75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F46" s="75" t="inlineStr">
+        <is>
+          <t>ESA / Nielsen Sports: +1.8% YoY</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="73" t="inlineStr">
+        <is>
+          <t>Sport sponsorship market</t>
+        </is>
+      </c>
+      <c r="B47" s="81" t="n">
+        <v>2180000000</v>
+      </c>
+      <c r="C47" s="75" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D47" s="75" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E47" s="75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F47" s="75" t="inlineStr">
+        <is>
+          <t>ESA / Nielsen Sports: +14%, the fastest growing major European market</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="73" t="inlineStr">
+        <is>
+          <t>Sport sponsorship market</t>
+        </is>
+      </c>
+      <c r="B48" s="81" t="n">
+        <v>6260000000</v>
+      </c>
+      <c r="C48" s="75" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D48" s="75" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E48" s="75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F48" s="75" t="inlineStr">
+        <is>
+          <t>ESA / Nielsen Sports: the largest European market</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="73" t="inlineStr">
+        <is>
+          <t>Sport sponsorship market</t>
+        </is>
+      </c>
+      <c r="B49" s="81" t="n">
+        <v>6150000000</v>
+      </c>
+      <c r="C49" s="75" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D49" s="75" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E49" s="75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F49" s="75" t="inlineStr">
+        <is>
+          <t>ESA / Nielsen Sports: +10.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="73" t="inlineStr">
+        <is>
+          <t>Sport sponsorship market</t>
+        </is>
+      </c>
+      <c r="B50" s="81" t="n">
+        <v>2010000000</v>
+      </c>
+      <c r="C50" s="75" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D50" s="75" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E50" s="75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F50" s="75" t="inlineStr">
+        <is>
+          <t>ESA / Nielsen Sports: +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="73" t="inlineStr">
+        <is>
+          <t>Sport sponsorship market</t>
+        </is>
+      </c>
+      <c r="B51" s="81" t="n">
+        <v>1850000000</v>
+      </c>
+      <c r="C51" s="75" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D51" s="75" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E51" s="75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F51" s="75" t="inlineStr">
+        <is>
+          <t>ESA / Nielsen Sports: +10.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="77" t="inlineStr">
+        <is>
+          <t>European SPORT sponsorship by year, EUR bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B54" s="12" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="82" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="B55" s="82" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C55" s="82" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="D55" s="82" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="E55" s="82" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F55" s="82" t="n">
+        <v>24.79</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="71" t="inlineStr">
+        <is>
+          <t>2020 is not published in the ESA series. Source: ESA via Statista, retrieved 1 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="77" t="inlineStr">
+        <is>
+          <t>FAN DEMAND - published surveys bearing on the fan thesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="72" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B59" s="72" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C59" s="72" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D59" s="72" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="E59" s="72" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="F59" s="72" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="73" t="inlineStr">
+        <is>
+          <t>Weekly minutes, fan-generated content</t>
+        </is>
+      </c>
+      <c r="B60" s="74" t="n">
+        <v>115</v>
+      </c>
+      <c r="C60" s="75" t="inlineStr">
+        <is>
+          <t>minutes/week</t>
+        </is>
+      </c>
+      <c r="D60" s="75" t="inlineStr">
+        <is>
+          <t>FR DE IT ES UK US</t>
+        </is>
+      </c>
+      <c r="E60" s="75" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="F60" s="75" t="inlineStr">
+        <is>
+          <t>Altman Solon / IRIS Sport, 6,000 respondents who watch sports video monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="73" t="inlineStr">
+        <is>
+          <t>Weekly minutes, highlights and clips</t>
+        </is>
+      </c>
+      <c r="B61" s="74" t="n">
+        <v>115</v>
+      </c>
+      <c r="C61" s="75" t="inlineStr">
+        <is>
+          <t>minutes/week</t>
+        </is>
+      </c>
+      <c r="D61" s="75" t="inlineStr">
+        <is>
+          <t>FR DE IT ES UK US</t>
+        </is>
+      </c>
+      <c r="E61" s="75" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="F61" s="75" t="inlineStr">
+        <is>
+          <t>Altman Solon / IRIS Sport</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="73" t="inlineStr">
+        <is>
+          <t>Weekly minutes, live games and events</t>
+        </is>
+      </c>
+      <c r="B62" s="74" t="n">
+        <v>245</v>
+      </c>
+      <c r="C62" s="75" t="inlineStr">
+        <is>
+          <t>minutes/week</t>
+        </is>
+      </c>
+      <c r="D62" s="75" t="inlineStr">
+        <is>
+          <t>FR DE IT ES UK US</t>
+        </is>
+      </c>
+      <c r="E62" s="75" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="F62" s="75" t="inlineStr">
+        <is>
+          <t>Altman Solon / IRIS Sport</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="73" t="inlineStr">
+        <is>
+          <t>YouTube share of fan-generated viewing</t>
+        </is>
+      </c>
+      <c r="B63" s="38" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C63" s="75" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="D63" s="75" t="inlineStr">
+        <is>
+          <t>FR DE IT ES UK US</t>
+        </is>
+      </c>
+      <c r="E63" s="75" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="F63" s="75" t="inlineStr">
+        <is>
+          <t>Altman Solon / IRIS Sport: 40 of 115 minutes, more than linear TV or streaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="73" t="inlineStr">
+        <is>
+          <t>Subscribers watching MORE sport after subscribing</t>
+        </is>
+      </c>
+      <c r="B64" s="38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C64" s="75" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="D64" s="75" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="E64" s="75" t="inlineStr">
+        <is>
+          <t>Nov 2022</t>
+        </is>
+      </c>
+      <c r="F64" s="75" t="inlineStr">
+        <is>
+          <t>YouGov / Strive, 19,000 respondents: 38% much more + 32% somewhat more</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="73" t="inlineStr">
+        <is>
+          <t>Subscribers watching LESS sport after subscribing</t>
+        </is>
+      </c>
+      <c r="B65" s="38" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C65" s="75" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="D65" s="75" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="E65" s="75" t="inlineStr">
+        <is>
+          <t>Nov 2022</t>
+        </is>
+      </c>
+      <c r="F65" s="75" t="inlineStr">
+        <is>
+          <t>YouGov / Strive: 3% much less + 4% somewhat less</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="77" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP MARKETPLACES - the direct competitor set</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="71" t="inlineStr">
+        <is>
+          <t>PitchBook company profiles retrieved 1 Oct 2026, reported in EUR. None of the four discloses revenue, so headcount and capital raised are the only scale measures available. Links at the bottom of this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="72" t="inlineStr">
+        <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B43" s="72" t="inlineStr">
+      <c r="B69" s="72" t="inlineStr">
         <is>
           <t>Founded</t>
         </is>
       </c>
-      <c r="C43" s="72" t="inlineStr">
-        <is>
-          <t>Employees</t>
-        </is>
-      </c>
-      <c r="D43" s="72" t="inlineStr">
+      <c r="C69" s="72" t="inlineStr">
+        <is>
+          <t>Employees (as of)</t>
+        </is>
+      </c>
+      <c r="D69" s="72" t="inlineStr">
         <is>
           <t>Total raised</t>
         </is>
       </c>
-      <c r="E43" s="72" t="inlineStr">
+      <c r="E69" s="72" t="inlineStr">
         <is>
           <t>Largest round pre-money</t>
         </is>
       </c>
-      <c r="F43" s="72" t="inlineStr">
+      <c r="F69" s="72" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="81" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="83" t="inlineStr">
         <is>
           <t>Sponsoo (Germany)</t>
         </is>
       </c>
-      <c r="B44" s="39" t="n">
+      <c r="B70" s="39" t="n">
         <v>2014</v>
       </c>
-      <c r="C44" s="74" t="n">
+      <c r="C70" s="74" t="n">
         <v>13</v>
       </c>
-      <c r="D44" s="82" t="n">
+      <c r="D70" s="81" t="n">
         <v>2170000</v>
       </c>
-      <c r="E44" s="82" t="n">
+      <c r="E70" s="81" t="n">
         <v>15900000</v>
       </c>
-      <c r="F44" s="75" t="inlineStr">
-        <is>
-          <t>Privately held, venture backed. Series A 28 Jan 2021; pre-money is a PitchBook ESTIMATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="81" t="inlineStr">
+      <c r="F70" s="75" t="inlineStr">
+        <is>
+          <t>Headcount as of 14 Nov 2025. Privately held, venture backed. Series A 28 Jan 2021; pre-money is a PitchBook ESTIMATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="83" t="inlineStr">
         <is>
           <t>OpenSponsorship (United States)</t>
         </is>
       </c>
-      <c r="B45" s="39" t="n">
+      <c r="B71" s="39" t="n">
         <v>2014</v>
       </c>
-      <c r="C45" s="74" t="n">
+      <c r="C71" s="74" t="n">
         <v>23</v>
       </c>
-      <c r="D45" s="82" t="n">
+      <c r="D71" s="81" t="n">
         <v>5400000</v>
       </c>
-      <c r="E45" s="82" t="n"/>
-      <c r="F45" s="75" t="inlineStr">
-        <is>
-          <t>Privately held, venture backed. Last priced round not disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="81" t="inlineStr">
+      <c r="E71" s="81" t="n"/>
+      <c r="F71" s="75" t="inlineStr">
+        <is>
+          <t>Headcount as of 9 Mar 2026. Privately held, venture backed. Last priced round not disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="83" t="inlineStr">
         <is>
           <t>SponsorUnited (United States)</t>
         </is>
       </c>
-      <c r="B46" s="39" t="n">
+      <c r="B72" s="39" t="n">
         <v>2016</v>
       </c>
-      <c r="C46" s="74" t="n">
+      <c r="C72" s="74" t="n">
         <v>355</v>
       </c>
-      <c r="D46" s="82" t="n">
+      <c r="D72" s="81" t="n">
         <v>38760000</v>
       </c>
-      <c r="E46" s="82" t="n">
+      <c r="E72" s="81" t="n">
         <v>89380000</v>
       </c>
-      <c r="F46" s="75" t="inlineStr">
-        <is>
-          <t>Privately held, venture backed. Series A 21 Nov 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="81" t="inlineStr">
+      <c r="F72" s="75" t="inlineStr">
+        <is>
+          <t>Headcount as of 28 May 2026. Privately held, venture backed. Series A 21 Nov 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="83" t="inlineStr">
         <is>
           <t>Hookit (United States)</t>
         </is>
       </c>
-      <c r="B47" s="39" t="n">
+      <c r="B73" s="39" t="n">
         <v>2001</v>
       </c>
-      <c r="C47" s="74" t="n">
+      <c r="C73" s="74" t="n">
         <v>47</v>
       </c>
-      <c r="D47" s="82" t="n">
+      <c r="D73" s="81" t="n">
         <v>21470000</v>
       </c>
-      <c r="E47" s="82" t="n">
+      <c r="E73" s="81" t="n">
         <v>38400000</v>
       </c>
-      <c r="F47" s="75" t="inlineStr">
-        <is>
-          <t>Acquired, operating subsidiary. Series C2 24 Feb 2020; pre-money is a PitchBook ESTIMATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="81" t="inlineStr">
+      <c r="F73" s="75" t="inlineStr">
+        <is>
+          <t>Headcount as of 8 Feb 2022. Acquired, operating subsidiary. Series C2 24 Feb 2020; pre-money is a PitchBook ESTIMATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="83" t="inlineStr">
         <is>
           <t>Stride (this plan, at Y10)</t>
         </is>
       </c>
-      <c r="B48" s="83" t="n">
+      <c r="B74" s="84" t="n">
         <v>2026</v>
       </c>
-      <c r="C48" s="84" t="n">
-        <v>16</v>
-      </c>
-      <c r="D48" s="85" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="E48" s="85" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="F48" s="75" t="inlineStr">
+      <c r="C74" s="85">
+        <f>Assumptions!L66</f>
+        <v/>
+      </c>
+      <c r="D74" s="86">
+        <f>SUM(Funding!C4:L4)</f>
+        <v/>
+      </c>
+      <c r="E74" s="86">
+        <f>Funding!H5</f>
+        <v/>
+      </c>
+      <c r="F74" s="75" t="inlineStr">
         <is>
           <t>Deliberately sized near Sponsoo. Only EUR 400k of the total is capital the plan depends on; the growth round is optional</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="77" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="77" t="inlineStr">
         <is>
           <t>REVENUE PER EMPLOYEE - what the plan is tested against</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>Benchmark</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>EUR per employee</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr"/>
-      <c r="D51" s="11" t="inlineStr"/>
-      <c r="E51" s="11" t="inlineStr"/>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="C77" s="11" t="inlineStr"/>
+      <c r="D77" s="11" t="inlineStr"/>
+      <c r="E77" s="11" t="inlineStr"/>
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="15" t="inlineStr">
         <is>
           <t>Median private B2B SaaS, all stages</t>
         </is>
       </c>
-      <c r="B52" s="86" t="n">
+      <c r="B78" s="87" t="n">
         <v>135000</v>
       </c>
-      <c r="F52" s="87" t="inlineStr">
+      <c r="F78" s="88" t="inlineStr">
         <is>
           <t>SaaS Capital 2025 survey of ~1,000 private B2B SaaS companies</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="15" t="inlineStr">
         <is>
           <t>Top quartile private B2B SaaS</t>
         </is>
       </c>
-      <c r="B53" s="86" t="n">
+      <c r="B79" s="87" t="n">
         <v>215000</v>
       </c>
-      <c r="F53" s="87" t="inlineStr">
+      <c r="F79" s="88" t="inlineStr">
         <is>
           <t>SaaS Capital 2025 survey, 75th percentile</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="15" t="inlineStr">
         <is>
           <t>Efficient public SaaS at scale</t>
         </is>
       </c>
-      <c r="B54" s="86" t="n">
+      <c r="B80" s="87" t="n">
         <v>300000</v>
       </c>
-      <c r="F54" s="87" t="inlineStr">
+      <c r="F80" s="88" t="inlineStr">
         <is>
           <t>Public SaaS medians, widely reported range EUR 250-350k</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Stride (this plan, Y7)</t>
         </is>
       </c>
-      <c r="B55" s="88">
+      <c r="B81" s="89">
         <f>KPIs!I14</f>
         <v/>
       </c>
-      <c r="F55" s="87" t="inlineStr">
+      <c r="F81" s="88" t="inlineStr">
         <is>
           <t>Above the top quartile. Defended in section 3.2.2: the fan side is self-serve and moderation is a variable cost, not headcount</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="15" t="inlineStr">
         <is>
           <t>Multiple of the top quartile</t>
         </is>
       </c>
-      <c r="B56" s="89">
-        <f>B55/B53</f>
-        <v/>
-      </c>
-      <c r="F56" s="80" t="inlineStr">
+      <c r="B82" s="90">
+        <f>B81/B79</f>
+        <v/>
+      </c>
+      <c r="F82" s="80" t="inlineStr">
         <is>
           <t>The plan's second most aggressive assumption after fan churn</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>SOURCES</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="90" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="91" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 filed accounts (Fenix International Ltd)</t>
         </is>
       </c>
-      <c r="B60" s="91" t="inlineStr">
+      <c r="B86" s="92" t="inlineStr">
         <is>
           <t>https://find-and-update.company-information.service.gov.uk/company/10354575/filing-history</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="90" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="91" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 as reported</t>
         </is>
       </c>
-      <c r="B61" s="91" t="inlineStr">
+      <c r="B87" s="92" t="inlineStr">
         <is>
           <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="90" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="91" t="inlineStr">
         <is>
           <t>Patreon published take rate</t>
         </is>
       </c>
-      <c r="B62" s="91" t="inlineStr">
+      <c r="B88" s="92" t="inlineStr">
         <is>
           <t>https://www.patreon.com/pricing</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="90" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="91" t="inlineStr">
         <is>
           <t>Patreon creators</t>
         </is>
       </c>
-      <c r="B63" s="91" t="inlineStr">
+      <c r="B89" s="92" t="inlineStr">
         <is>
           <t>https://backlinko.com/patreon-users</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="90" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="91" t="inlineStr">
         <is>
           <t>Passes economics</t>
         </is>
       </c>
-      <c r="B64" s="91" t="inlineStr">
+      <c r="B90" s="92" t="inlineStr">
         <is>
           <t>https://sacra.com/c/passes/</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="90" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="91" t="inlineStr">
         <is>
           <t>Fanfix creator terms (states no take rate)</t>
         </is>
       </c>
-      <c r="B65" s="91" t="inlineStr">
+      <c r="B91" s="92" t="inlineStr">
         <is>
           <t>https://auth.fanfix.io/creator-terms-of-use</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="90" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="91" t="inlineStr">
         <is>
           <t>Agency commissions</t>
         </is>
       </c>
-      <c r="B66" s="91" t="inlineStr">
+      <c r="B92" s="92" t="inlineStr">
         <is>
           <t>https://arunatalent.com/blog/onlyfans-agency-commission-rates/</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="90" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="91" t="inlineStr">
         <is>
           <t>NBPA agent fee cap (amended Sept 2025)</t>
         </is>
       </c>
-      <c r="B67" s="91" t="inlineStr">
+      <c r="B93" s="92" t="inlineStr">
         <is>
           <t>https://imgix.cosmicjs.com/cd844850-97c7-11f0-91fa-d9e1671c2776-NBPA-REGULATIONS-GOVERNING-PLAYER-AGENTS-09-2025.pdf</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="90" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="91" t="inlineStr">
         <is>
           <t>FIFA Football Agent Regulations art. 15</t>
         </is>
       </c>
-      <c r="B68" s="91" t="inlineStr">
+      <c r="B94" s="92" t="inlineStr">
         <is>
           <t>https://digitalhub.fifa.com/m/1e7b741fa0fae779/original/FIFA-Football-Agent-Regulations.pdf</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="90" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="91" t="inlineStr">
         <is>
           <t>CJEU upholds the FIFA fee cap (16 Jul 2026)</t>
         </is>
       </c>
-      <c r="B69" s="91" t="inlineStr">
+      <c r="B95" s="92" t="inlineStr">
         <is>
           <t>https://inside.fifa.com/news/welcomes-court-of-justice-european-union-decision-football-agent-regulations</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="90" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="91" t="inlineStr">
         <is>
           <t>Eurobarometer 525</t>
         </is>
       </c>
-      <c r="B70" s="91" t="inlineStr">
+      <c r="B96" s="92" t="inlineStr">
         <is>
           <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="90" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="91" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="B71" s="91" t="inlineStr">
+      <c r="B97" s="92" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="90" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="91" t="inlineStr">
         <is>
           <t>Stripe EU pricing</t>
         </is>
       </c>
-      <c r="B72" s="91" t="inlineStr">
+      <c r="B98" s="92" t="inlineStr">
         <is>
           <t>https://stripe.com/es/pricing</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="90" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="91" t="inlineStr">
         <is>
           <t>TEKTA launch</t>
         </is>
       </c>
-      <c r="B73" s="91" t="inlineStr">
+      <c r="B99" s="92" t="inlineStr">
         <is>
           <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="90" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="91" t="inlineStr">
         <is>
           <t>Stripe Connect age</t>
         </is>
       </c>
-      <c r="B74" s="91" t="inlineStr">
+      <c r="B100" s="92" t="inlineStr">
         <is>
           <t>https://support.stripe.com/questions/age-requirement-to-create-a-stripe-account</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="90" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="91" t="inlineStr">
         <is>
           <t>PitchBook: Sponsoo GmbH</t>
         </is>
       </c>
-      <c r="B75" s="91" t="inlineStr">
+      <c r="B101" s="92" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/103066-39</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="90" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="91" t="inlineStr">
         <is>
           <t>PitchBook: OpenSponsorship</t>
         </is>
       </c>
-      <c r="B76" s="91" t="inlineStr">
+      <c r="B102" s="92" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/113575-96</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="90" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="91" t="inlineStr">
         <is>
           <t>PitchBook: SponsorUnited</t>
         </is>
       </c>
-      <c r="B77" s="91" t="inlineStr">
+      <c r="B103" s="92" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/169635-43</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="90" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="91" t="inlineStr">
         <is>
           <t>PitchBook: Hookit</t>
         </is>
       </c>
-      <c r="B78" s="91" t="inlineStr">
+      <c r="B104" s="92" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/55307-17</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="90" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="91" t="inlineStr">
+        <is>
+          <t>ESA European sponsorship market 2025</t>
+        </is>
+      </c>
+      <c r="B105" s="92" t="inlineStr">
+        <is>
+          <t>https://sponsorship.org/european-sponsorship-market-reaches-e34-45bn-in-2025-as-growth-continues-across-all-sectors/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="91" t="inlineStr">
+        <is>
+          <t>SportsPro on the ESA 2026 market overview</t>
+        </is>
+      </c>
+      <c r="B106" s="92" t="inlineStr">
+        <is>
+          <t>https://www.sportspro.com/news/sponsorship-marketing/sports-sponsorship-european-market-valuation-esa-march-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="91" t="inlineStr">
+        <is>
+          <t>European sport sponsorship 2019-2025 (ESA via Statista)</t>
+        </is>
+      </c>
+      <c r="B107" s="92" t="inlineStr">
+        <is>
+          <t>https://www.statista.com/statistics/1430225/sports-sponsorship-market-size-europe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="91" t="inlineStr">
+        <is>
+          <t>Sports content formats by channel (Altman Solon / IRIS Sport)</t>
+        </is>
+      </c>
+      <c r="B108" s="92" t="inlineStr">
+        <is>
+          <t>https://www.statista.com/statistics/1660170/time-spent-weekly-watching-sports-formats-by-channel/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="91" t="inlineStr">
+        <is>
+          <t>Impact of subscriptions on sports consumption (YouGov / Strive)</t>
+        </is>
+      </c>
+      <c r="B109" s="92" t="inlineStr">
+        <is>
+          <t>https://www.statista.com/statistics/1413187/impact-subscriptions-sports-content-consumption/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="91" t="inlineStr">
         <is>
           <t>SaaS Capital revenue per employee benchmarks</t>
         </is>
       </c>
-      <c r="B79" s="91" t="inlineStr">
+      <c r="B110" s="92" t="inlineStr">
         <is>
           <t>https://www.saas-capital.com/blog-posts/revenue-per-employee-benchmarks-for-private-saas-companies/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B71:F71"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B77:F77"/>
+  <mergeCells count="28">
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="B93:F93"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="B102:F102"/>
+    <mergeCell ref="B105:F105"/>
     <mergeCell ref="A42:F42"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B76:F76"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B97:F97"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9833,36 +10468,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="93" t="inlineStr">
         <is>
           <t>Input: change me</t>
         </is>
       </c>
-      <c r="D3" s="93" t="n"/>
-      <c r="E3" s="94" t="inlineStr">
+      <c r="D3" s="94" t="n"/>
+      <c r="E3" s="95" t="inlineStr">
         <is>
           <t>Sourced fact</t>
         </is>
       </c>
-      <c r="F3" s="93" t="n"/>
-      <c r="G3" s="95" t="inlineStr">
+      <c r="F3" s="94" t="n"/>
+      <c r="G3" s="96" t="inlineStr">
         <is>
           <t>Formula (this sheet)</t>
         </is>
       </c>
-      <c r="H3" s="93" t="n"/>
-      <c r="I3" s="96" t="inlineStr">
+      <c r="H3" s="94" t="n"/>
+      <c r="I3" s="97" t="inlineStr">
         <is>
           <t>Formula (other sheet)</t>
         </is>
       </c>
-      <c r="J3" s="93" t="n"/>
-      <c r="K3" s="97" t="inlineStr">
+      <c r="J3" s="94" t="n"/>
+      <c r="K3" s="98" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="L3" s="93" t="n"/>
+      <c r="L3" s="94" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -9884,7 +10519,7 @@
         <f>Comparables!B14</f>
         <v/>
       </c>
-      <c r="D6" s="87" t="inlineStr">
+      <c r="D6" s="88" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -9900,7 +10535,7 @@
         <f>Comparables!B12</f>
         <v/>
       </c>
-      <c r="D7" s="87" t="inlineStr">
+      <c r="D7" s="88" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -9916,7 +10551,7 @@
         <f>B6/B7</f>
         <v/>
       </c>
-      <c r="D8" s="87" t="inlineStr">
+      <c r="D8" s="88" t="inlineStr">
         <is>
           <t>The single most useful benchmark we found: it is measured, not modelled.</t>
         </is>
@@ -9932,7 +10567,7 @@
         <f>Comparables!B9/Comparables!B8</f>
         <v/>
       </c>
-      <c r="D9" s="87" t="inlineStr">
+      <c r="D9" s="88" t="inlineStr">
         <is>
           <t>Fan ACCOUNTS, not paying fans - most follow free. Shown as an upper bound only.</t>
         </is>
@@ -9947,7 +10582,7 @@
       <c r="B10" s="26" t="n">
         <v>1.06</v>
       </c>
-      <c r="D10" s="87" t="inlineStr">
+      <c r="D10" s="88" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +6% on the Patreon benchmark. Sport audiences are smaller but convert better, because the fan usually does the sport themselves.</t>
         </is>
@@ -9962,7 +10597,7 @@
       <c r="B11" s="26" t="n">
         <v>1.37</v>
       </c>
-      <c r="D11" s="87" t="inlineStr">
+      <c r="D11" s="88" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +37%. Much larger followings, much weaker conversion - more paying fans in absolute terms even though a smaller share converts.</t>
         </is>
@@ -9974,11 +10609,11 @@
           <t>→ Niche fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B12" s="98">
+      <c r="B12" s="99">
         <f>B8*B10</f>
         <v/>
       </c>
-      <c r="D12" s="87" t="inlineStr"/>
+      <c r="D12" s="88" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -9986,11 +10621,11 @@
           <t>→ Popular fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B13" s="98">
+      <c r="B13" s="99">
         <f>B8*B11</f>
         <v/>
       </c>
-      <c r="D13" s="87" t="inlineStr"/>
+      <c r="D13" s="88" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -10011,7 +10646,7 @@
       <c r="B15" s="22" t="n">
         <v>4.99</v>
       </c>
-      <c r="D15" s="87" t="inlineStr"/>
+      <c r="D15" s="88" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -10022,7 +10657,7 @@
       <c r="B16" s="22" t="n">
         <v>9.99</v>
       </c>
-      <c r="D16" s="87" t="inlineStr"/>
+      <c r="D16" s="88" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
@@ -10033,7 +10668,7 @@
       <c r="B17" s="22" t="n">
         <v>24.99</v>
       </c>
-      <c r="D17" s="87" t="inlineStr"/>
+      <c r="D17" s="88" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -10044,7 +10679,7 @@
       <c r="B18" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="D18" s="87" t="inlineStr">
+      <c r="D18" s="88" t="inlineStr">
         <is>
           <t>Assumed distribution; replace with the real tier mix after P1.</t>
         </is>
@@ -10059,7 +10694,7 @@
       <c r="B19" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="D19" s="87" t="inlineStr"/>
+      <c r="D19" s="88" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -10070,7 +10705,7 @@
       <c r="B20" s="18" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="87" t="inlineStr"/>
+      <c r="D20" s="88" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -10082,7 +10717,7 @@
         <f>B18+B19+B20</f>
         <v/>
       </c>
-      <c r="D21" s="87" t="inlineStr"/>
+      <c r="D21" s="88" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -10090,11 +10725,11 @@
           <t>→ Weighted ARPU per month</t>
         </is>
       </c>
-      <c r="B22" s="99">
+      <c r="B22" s="100">
         <f>B15*B18+B16*B19+B17*B20</f>
         <v/>
       </c>
-      <c r="D22" s="87" t="inlineStr">
+      <c r="D22" s="88" t="inlineStr">
         <is>
           <t>Cross-check: Patreon reports $6.10 average support and a $8-12 typical band. Landing inside that band from an independent tier build is a good sign.</t>
         </is>
@@ -10110,7 +10745,7 @@
         <f>Comparables!B16</f>
         <v/>
       </c>
-      <c r="D23" s="87" t="inlineStr">
+      <c r="D23" s="88" t="inlineStr">
         <is>
           <t>Published average - below our figure because Patreon's long tail includes many $1-3 tiers. Our EUR 9.49 sits inside their $8-12 typical band.</t>
         </is>
@@ -10125,7 +10760,7 @@
       <c r="B24" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="87" t="inlineStr">
+      <c r="D24" s="88" t="inlineStr">
         <is>
           <t>Niche fans buy knowledge and sit at the tier mix above.</t>
         </is>
@@ -10140,7 +10775,7 @@
       <c r="B25" s="26" t="n">
         <v>0.87</v>
       </c>
-      <c r="D25" s="87" t="inlineStr">
+      <c r="D25" s="88" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: -13%. Popular-sport fans skew to the cheapest tier.</t>
         </is>
@@ -10152,11 +10787,11 @@
           <t>→ Niche ARPU, mature</t>
         </is>
       </c>
-      <c r="B26" s="99">
+      <c r="B26" s="100">
         <f>B22*B24</f>
         <v/>
       </c>
-      <c r="D26" s="87" t="inlineStr"/>
+      <c r="D26" s="88" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -10164,11 +10799,11 @@
           <t>→ Popular ARPU, mature</t>
         </is>
       </c>
-      <c r="B27" s="99">
+      <c r="B27" s="100">
         <f>B22*B25</f>
         <v/>
       </c>
-      <c r="D27" s="87" t="inlineStr"/>
+      <c r="D27" s="88" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -10190,7 +10825,7 @@
         <f>Comparables!B19</f>
         <v/>
       </c>
-      <c r="D29" s="87" t="inlineStr"/>
+      <c r="D29" s="88" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
@@ -10202,7 +10837,7 @@
         <f>Comparables!B20</f>
         <v/>
       </c>
-      <c r="D30" s="87" t="inlineStr"/>
+      <c r="D30" s="88" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
@@ -10214,7 +10849,7 @@
         <f>(B29+B30)/2</f>
         <v/>
       </c>
-      <c r="D31" s="87" t="inlineStr"/>
+      <c r="D31" s="88" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -10226,7 +10861,7 @@
         <f>Comparables!B21</f>
         <v/>
       </c>
-      <c r="D32" s="87" t="inlineStr">
+      <c r="D32" s="88" t="inlineStr">
         <is>
           <t>Patreon: annual patrons churn at one third the monthly rate.</t>
         </is>
@@ -10241,7 +10876,7 @@
       <c r="B33" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="87" t="inlineStr">
+      <c r="D33" s="88" t="inlineStr">
         <is>
           <t>Our target for the season pass. This is the one lever that improves churn without changing the product.</t>
         </is>
@@ -10257,7 +10892,7 @@
         <f>B31*(1-B33)+B31*B32*B33</f>
         <v/>
       </c>
-      <c r="D34" s="87" t="inlineStr">
+      <c r="D34" s="88" t="inlineStr">
         <is>
           <t>What a Patreon-like platform would see with our annual mix.</t>
         </is>
@@ -10272,7 +10907,7 @@
       <c r="B35" s="26" t="n">
         <v>0.55</v>
       </c>
-      <c r="D35" s="87" t="inlineStr">
+      <c r="D35" s="88" t="inlineStr">
         <is>
           <t>OUR CLAIM, UNTESTED, AND THE MOST OPTIMISTIC JUDGEMENT IN THE MODEL: this says niche fans churn 45% SLOWER than the Patreon benchmark, because training content is habitual and competitive seasons create renewal moments. Nothing yet proves it. If it is wrong and we are merely at benchmark, Y10 revenue falls by roughly EUR 7M.</t>
         </is>
@@ -10287,7 +10922,7 @@
       <c r="B36" s="26" t="n">
         <v>0.85</v>
       </c>
-      <c r="D36" s="87" t="inlineStr">
+      <c r="D36" s="88" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: 15% better than benchmark. Impulse follows after a result, with many free substitutes - but still a sport fan rather than a general creator audience.</t>
         </is>
@@ -10299,11 +10934,11 @@
           <t>→ Niche churn, mature</t>
         </is>
       </c>
-      <c r="B37" s="100">
+      <c r="B37" s="101">
         <f>B34*B35</f>
         <v/>
       </c>
-      <c r="D37" s="87" t="inlineStr"/>
+      <c r="D37" s="88" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -10311,11 +10946,11 @@
           <t>→ Popular churn, mature</t>
         </is>
       </c>
-      <c r="B38" s="100">
+      <c r="B38" s="101">
         <f>B34*B36</f>
         <v/>
       </c>
-      <c r="D38" s="87" t="inlineStr"/>
+      <c r="D38" s="88" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
@@ -10337,7 +10972,7 @@
         <f>Comparables!B7/Comparables!B8/12</f>
         <v/>
       </c>
-      <c r="D40" s="87" t="inlineStr">
+      <c r="D40" s="88" t="inlineStr">
         <is>
           <t>Includes dormant accounts, so this is a floor.</t>
         </is>
@@ -10353,7 +10988,7 @@
         <f>Comparables!B15/Comparables!B12/12</f>
         <v/>
       </c>
-      <c r="D41" s="87" t="inlineStr">
+      <c r="D41" s="88" t="inlineStr">
         <is>
           <t>Denominator is creators WITH members, so this is a ceiling.</t>
         </is>
@@ -10365,11 +11000,11 @@
           <t>Stride: modelled niche athlete, mature</t>
         </is>
       </c>
-      <c r="B42" s="99">
+      <c r="B42" s="100">
         <f>B12*B22*(1-Assumptions!$C$40)</f>
         <v/>
       </c>
-      <c r="D42" s="87" t="inlineStr">
+      <c r="D42" s="88" t="inlineStr">
         <is>
           <t>Ours sits between the two, which is where a plausible figure should sit.</t>
         </is>
@@ -10385,7 +11020,7 @@
         <f>Comparables!B11</f>
         <v/>
       </c>
-      <c r="D43" s="87" t="inlineStr">
+      <c r="D43" s="88" t="inlineStr">
         <is>
           <t>THE CAVEAT ON EVERY AVERAGE ABOVE: earnings follow a power law. Totals are unaffected, but the median athlete earns far less than the mean. Do not pitch the mean to an athlete.</t>
         </is>
@@ -10410,7 +11045,7 @@
       <c r="B45" s="26" t="n">
         <v>0.92</v>
       </c>
-      <c r="D45" s="87" t="inlineStr">
+      <c r="D45" s="88" t="inlineStr">
         <is>
           <t>Comparables are published in USD; this model is in EUR. Applied to the per-transaction and monthly creator fees below.</t>
         </is>
@@ -10425,7 +11060,7 @@
       <c r="B46" s="22" t="n">
         <v>300</v>
       </c>
-      <c r="D46" s="87" t="inlineStr">
+      <c r="D46" s="88" t="inlineStr">
         <is>
           <t>Change this to see who is cheapest at any revenue level.</t>
         </is>
@@ -10441,7 +11076,7 @@
         <f>B46*(1-Comparables!B29)-B46/Assumptions!$C$54*Comparables!C29*B45-Comparables!D29*B45</f>
         <v/>
       </c>
-      <c r="D47" s="87" t="inlineStr">
+      <c r="D47" s="88" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -10457,7 +11092,7 @@
         <f>B46*(1-Comparables!B32)-B46/Assumptions!$C$54*Comparables!C32*B45-Comparables!D32*B45</f>
         <v/>
       </c>
-      <c r="D48" s="87" t="inlineStr">
+      <c r="D48" s="88" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -10473,7 +11108,7 @@
         <f>B46*(1-Comparables!B33)-B46/Assumptions!$C$54*Comparables!C33*B45-Comparables!D33*B45</f>
         <v/>
       </c>
-      <c r="D49" s="87" t="inlineStr">
+      <c r="D49" s="88" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -10489,7 +11124,7 @@
         <f>B46*(1-Comparables!B34)-B46/Assumptions!$C$54*Comparables!C34*B45-Comparables!D34*B45</f>
         <v/>
       </c>
-      <c r="D50" s="87" t="inlineStr">
+      <c r="D50" s="88" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -10505,7 +11140,7 @@
         <f>Comparables!D33*B45/((Comparables!B34-Comparables!B33)-Comparables!C33*B45/Assumptions!$C$54)</f>
         <v/>
       </c>
-      <c r="D51" s="87" t="inlineStr">
+      <c r="D51" s="88" t="inlineStr">
         <is>
           <t>Below this, our flat 15% pays the athlete more than Passes' 10% plus fees. Our modelled athlete earns far less than this, so the long tail is on our side of the line.</t>
         </is>
@@ -10527,10 +11162,10 @@
           <t>Population, 34 countries in scope</t>
         </is>
       </c>
-      <c r="B53" s="101" t="n">
+      <c r="B53" s="102" t="n">
         <v>2726.2</v>
       </c>
-      <c r="D53" s="87" t="inlineStr">
+      <c r="D53" s="88" t="inlineStr">
         <is>
           <t>Millions. Eurostat / national statistics offices.</t>
         </is>
@@ -10542,10 +11177,10 @@
           <t>Population, Spain</t>
         </is>
       </c>
-      <c r="B54" s="101" t="n">
+      <c r="B54" s="102" t="n">
         <v>48.6</v>
       </c>
-      <c r="D54" s="87" t="inlineStr">
+      <c r="D54" s="88" t="inlineStr">
         <is>
           <t>Millions.</t>
         </is>
@@ -10560,7 +11195,7 @@
       <c r="B55" s="18" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D55" s="87" t="inlineStr">
+      <c r="D55" s="88" t="inlineStr">
         <is>
           <t>Eurobarometer 525 - Spain sits near the EU average of 55% who exercise at all.</t>
         </is>
@@ -10575,7 +11210,7 @@
       <c r="B56" s="18" t="n">
         <v>0.02</v>
       </c>
-      <c r="D56" s="87" t="inlineStr">
+      <c r="D56" s="88" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: competes, posts publicly, has a following worth sponsoring.</t>
         </is>
@@ -10590,7 +11225,7 @@
       <c r="B57" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="D57" s="87" t="inlineStr">
+      <c r="D57" s="88" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: would monetise if the tooling existed.</t>
         </is>
@@ -10602,11 +11237,11 @@
           <t>→ Addressable athletes, Spain</t>
         </is>
       </c>
-      <c r="B58" s="102">
+      <c r="B58" s="103">
         <f>B54*1000000*B55*B56*B57</f>
         <v/>
       </c>
-      <c r="D58" s="87" t="inlineStr"/>
+      <c r="D58" s="88" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -10614,11 +11249,11 @@
           <t>→ Addressable athletes, all 34 countries</t>
         </is>
       </c>
-      <c r="B59" s="102">
+      <c r="B59" s="103">
         <f>B53*1000000*0.5*B56*B57</f>
         <v/>
       </c>
-      <c r="D59" s="87" t="inlineStr">
+      <c r="D59" s="88" t="inlineStr">
         <is>
           <t>Using a 50% blended participation rate across the 34 countries.</t>
         </is>
@@ -10634,7 +11269,7 @@
         <f>Assumptions!$L$5</f>
         <v/>
       </c>
-      <c r="D60" s="87" t="inlineStr"/>
+      <c r="D60" s="88" t="inlineStr"/>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -10642,11 +11277,11 @@
           <t>→ Y10 penetration of Spain SAM</t>
         </is>
       </c>
-      <c r="B61" s="100">
+      <c r="B61" s="101">
         <f>Assumptions!$L$5/B58</f>
         <v/>
       </c>
-      <c r="D61" s="87" t="inlineStr"/>
+      <c r="D61" s="88" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -10654,11 +11289,11 @@
           <t>→ Y10 penetration of full TAM</t>
         </is>
       </c>
-      <c r="B62" s="100">
+      <c r="B62" s="101">
         <f>Assumptions!$L$5/B59</f>
         <v/>
       </c>
-      <c r="D62" s="87" t="inlineStr">
+      <c r="D62" s="88" t="inlineStr">
         <is>
           <t>If this reads as implausibly high, the athlete trajectory is too aggressive - that is exactly what this block exists to reveal.</t>
         </is>
@@ -10709,37 +11344,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="103" t="inlineStr">
+      <c r="A4" s="104" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B4" s="103" t="inlineStr">
+      <c r="B4" s="104" t="inlineStr">
         <is>
           <t>Model value</t>
         </is>
       </c>
-      <c r="C4" s="103" t="inlineStr">
+      <c r="C4" s="104" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D4" s="103" t="inlineStr">
+      <c r="D4" s="104" t="inlineStr">
         <is>
           <t>Benchmark / comparable</t>
         </is>
       </c>
-      <c r="E4" s="103" t="inlineStr">
+      <c r="E4" s="104" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F4" s="103" t="inlineStr">
+      <c r="F4" s="104" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="G4" s="103" t="inlineStr">
+      <c r="G4" s="104" t="inlineStr">
         <is>
           <t>What would replace the estimate</t>
         </is>
@@ -10759,7 +11394,7 @@
       <c r="G5" s="14" t="n"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="81" t="inlineStr">
+      <c r="A6" s="83" t="inlineStr">
         <is>
           <t>Take rate on fan revenue</t>
         </is>
@@ -10768,34 +11403,34 @@
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="C6" s="104" t="inlineStr">
+      <c r="C6" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D6" s="105" t="inlineStr">
+      <c r="D6" s="106" t="inlineStr">
         <is>
           <t>Passes charges 10% but adds $0.30/txn and a $29/month creator fee; OnlyFans, Fansly and Fanfix are all 20%; Patreon 8-12%. A flat 15% with no monthly fee pays an athlete more than Passes for anyone under EUR 1,380/month of fan revenue.</t>
         </is>
       </c>
-      <c r="E6" s="105" t="inlineStr">
+      <c r="E6" s="106" t="inlineStr">
         <is>
           <t>Sacra company profile (Passes); Passes rebrand release, Apr 2026; MEXC platform comparison 2026</t>
         </is>
       </c>
-      <c r="F6" s="106" t="inlineStr">
+      <c r="F6" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G6" s="105" t="inlineStr">
+      <c r="G6" s="106" t="inlineStr">
         <is>
           <t>Nothing. This is a pricing decision and the comparables are public.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="81" t="inlineStr">
+      <c r="A7" s="83" t="inlineStr">
         <is>
           <t>Sponsorship commission, Scout Pro</t>
         </is>
@@ -10804,34 +11439,34 @@
         <f>Assumptions!$C$42</f>
         <v/>
       </c>
-      <c r="C7" s="104" t="inlineStr">
+      <c r="C7" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D7" s="105" t="inlineStr">
+      <c r="D7" s="106" t="inlineStr">
         <is>
           <t>7% against a 10% base. A sponsor paying EUR 2,988 a year for the tooling is already paying for the relationship, and charging them the full headline rate on every deal as well is charging twice for it. Below the 10-20% an agent takes, which is the point: the sponsor who commits most pays least on each deal.</t>
         </is>
       </c>
-      <c r="E7" s="105" t="inlineStr">
+      <c r="E7" s="106" t="inlineStr">
         <is>
           <t>Priced against the agent range; the discount itself is a pricing decision</t>
         </is>
       </c>
-      <c r="F7" s="106" t="inlineStr">
+      <c r="F7" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G7" s="105" t="inlineStr">
+      <c r="G7" s="106" t="inlineStr">
         <is>
           <t>Nothing to improve. This is a decision, not a measurement.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="81" t="inlineStr">
+      <c r="A8" s="83" t="inlineStr">
         <is>
           <t>Sponsorship commission, Scout Agency</t>
         </is>
@@ -10840,34 +11475,34 @@
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
-      <c r="C8" s="104" t="inlineStr">
+      <c r="C8" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D8" s="105" t="inlineStr">
+      <c r="D8" s="106" t="inlineStr">
         <is>
           <t>5%, which is half the low end of what an agent charges and a quarter of the high end. The most committed tier pays EUR 11,988 a year, so the deal rate can fall furthest here.</t>
         </is>
       </c>
-      <c r="E8" s="105" t="inlineStr">
+      <c r="E8" s="106" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys, 10-20%</t>
         </is>
       </c>
-      <c r="F8" s="106" t="inlineStr">
+      <c r="F8" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G8" s="105" t="inlineStr">
+      <c r="G8" s="106" t="inlineStr">
         <is>
           <t>Nothing to improve. This is a decision, not a measurement.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="81" t="inlineStr">
+      <c r="A9" s="83" t="inlineStr">
         <is>
           <t>Subscriber share of deal volume</t>
         </is>
@@ -10876,34 +11511,34 @@
         <f>Assumptions!$C$44</f>
         <v/>
       </c>
-      <c r="C9" s="107" t="inlineStr">
+      <c r="C9" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D9" s="105" t="inlineStr">
+      <c r="D9" s="106" t="inlineStr">
         <is>
           <t>Subscribers are assumed to run 2.0x the deal volume of the average sponsor, which with a paid rate of 10-20% puts them at 20-40% of GMV. This is the ONLY estimate in the tiering and it is the one that sets the blended rate, which falls from 9.60% in Y1 to 8.56% by Y10. Deliberately conservative: Scout Pro buys five campaigns against the free tier's one, so 2.0x is well below what the campaign allowance alone would imply. Higher multiples lower the blend further.</t>
         </is>
       </c>
-      <c r="E9" s="105" t="inlineStr">
+      <c r="E9" s="106" t="inlineStr">
         <is>
           <t>None. No tier-level deal volume exists yet, because no tier exists yet</t>
         </is>
       </c>
-      <c r="F9" s="108" t="inlineStr">
+      <c r="F9" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G9" s="105" t="inlineStr">
+      <c r="G9" s="106" t="inlineStr">
         <is>
           <t>The first year of billing settles it exactly.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="81" t="inlineStr">
+      <c r="A10" s="83" t="inlineStr">
         <is>
           <t>Take rate on sponsorship</t>
         </is>
@@ -10912,101 +11547,101 @@
         <f>Assumptions!$C$41</f>
         <v/>
       </c>
-      <c r="C10" s="104" t="inlineStr">
+      <c r="C10" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D10" s="105" t="inlineStr">
+      <c r="D10" s="106" t="inlineStr">
         <is>
           <t>Sports agents take 10-20% of an endorsement and 4-10% of a playing contract. On OnlyFans, management agencies take a further 20-50% on top of the platform's 20%.</t>
         </is>
       </c>
-      <c r="E10" s="105" t="inlineStr">
+      <c r="E10" s="106" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys; Aruna Talent agency rate guide 2026</t>
         </is>
       </c>
-      <c r="F10" s="106" t="inlineStr">
+      <c r="F10" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G10" s="105" t="inlineStr">
+      <c r="G10" s="106" t="inlineStr">
         <is>
           <t>Observed deal data once the marketplace is running.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="81" t="inlineStr">
+      <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Suggested tiers 4.99 / 9.99 / 24.99</t>
         </is>
       </c>
-      <c r="B11" s="109" t="inlineStr">
+      <c r="B11" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C11" s="104" t="inlineStr">
+      <c r="C11" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D11" s="105" t="inlineStr">
+      <c r="D11" s="106" t="inlineStr">
         <is>
           <t>Patreon's typical patronage is quoted at $8-12/month, so the EUR 9.99 anchor sits inside the observed band. EUR 4.99 retains only 54% of our take after payment fees, against 71% at EUR 9.99: which is why the floor matters more than the take rate.</t>
         </is>
       </c>
-      <c r="E11" s="105" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; independent audits of ~1,200 creators</t>
         </is>
       </c>
-      <c r="F11" s="110" t="inlineStr">
+      <c r="F11" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G11" s="105" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>Our own tier mix after P1.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="81" t="inlineStr">
+      <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Season pass / annual billing</t>
         </is>
       </c>
-      <c r="B12" s="109" t="inlineStr">
+      <c r="B12" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C12" s="111" t="inlineStr">
+      <c r="C12" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D12" s="105" t="inlineStr">
+      <c r="D12" s="106" t="inlineStr">
         <is>
           <t>Patreon reports that annual patrons churn at ONE THIRD the rate of monthly patrons. This is the single strongest piece of evidence in the plan for pushing annual billing.</t>
         </is>
       </c>
-      <c r="E12" s="105" t="inlineStr">
+      <c r="E12" s="106" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F12" s="106" t="inlineStr">
+      <c r="F12" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G12" s="105" t="inlineStr">
+      <c r="G12" s="106" t="inlineStr">
         <is>
           <t>Already strong. Confirm on our own cohorts.</t>
         </is>
@@ -11026,7 +11661,7 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="81" t="inlineStr">
+      <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Fan ARPU per month</t>
         </is>
@@ -11035,34 +11670,34 @@
         <f>Assumptions!$C$12</f>
         <v/>
       </c>
-      <c r="C14" s="104" t="inlineStr">
+      <c r="C14" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D14" s="105" t="inlineStr">
+      <c r="D14" s="106" t="inlineStr">
         <is>
           <t>Patreon's average monthly support rose from $5.40 to $6.10 during 2024, with typical patronage quoted at $8-12. Our EUR 8.00-9.50 sits in the upper-middle of that range.</t>
         </is>
       </c>
-      <c r="E14" s="105" t="inlineStr">
+      <c r="E14" s="106" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F14" s="110" t="inlineStr">
+      <c r="F14" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G14" s="105" t="inlineStr">
+      <c r="G14" s="106" t="inlineStr">
         <is>
           <t>Actual ARPU by tier and sport after P1.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="81" t="inlineStr">
+      <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Fan churn per month</t>
         </is>
@@ -11071,34 +11706,34 @@
         <f>Assumptions!$C$13</f>
         <v/>
       </c>
-      <c r="C15" s="107" t="inlineStr">
+      <c r="C15" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D15" s="105" t="inlineStr">
+      <c r="D15" s="106" t="inlineStr">
         <is>
           <t>OPTIMISTIC AGAINST BENCHMARK. Patreon runs 10-15% monthly. We assume 6-9% (niche) and 9-13% (popular), arguing that training content is habitual and that competitive seasons create natural renewal moments. That argument is currently untested.</t>
         </is>
       </c>
-      <c r="E15" s="105" t="inlineStr">
+      <c r="E15" s="106" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (10-15%/month)</t>
         </is>
       </c>
-      <c r="F15" s="108" t="inlineStr">
+      <c r="F15" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G15" s="105" t="inlineStr">
+      <c r="G15" s="106" t="inlineStr">
         <is>
           <t>THE most important number to measure in P1. Three months of real cohorts settles it. Until then the conservative case should be treated as the plan.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="81" t="inlineStr">
+      <c r="A16" s="83" t="inlineStr">
         <is>
           <t>Paying fans per monetising athlete</t>
         </is>
@@ -11107,34 +11742,34 @@
         <f>Assumptions!$C$11</f>
         <v/>
       </c>
-      <c r="C16" s="112" t="inlineStr">
+      <c r="C16" s="113" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D16" s="105" t="inlineStr">
+      <c r="D16" s="106" t="inlineStr">
         <is>
           <t>20 rising to 48 over ten years. Cross-check: Patreon creators average $350/month and our modelled niche athlete at maturity earns about EUR 313/month, closely aligned, which is reassuring for an assumption built bottom-up rather than from a comparable.</t>
         </is>
       </c>
-      <c r="E16" s="105" t="inlineStr">
+      <c r="E16" s="106" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (creator average $350/month)</t>
         </is>
       </c>
-      <c r="F16" s="110" t="inlineStr">
+      <c r="F16" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G16" s="105" t="inlineStr">
+      <c r="G16" s="106" t="inlineStr">
         <is>
           <t>Observed fans per athlete, banded by follower count.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="81" t="inlineStr">
+      <c r="A17" s="83" t="inlineStr">
         <is>
           <t>Share of athletes who monetise</t>
         </is>
@@ -11143,64 +11778,64 @@
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="C17" s="107" t="inlineStr">
+      <c r="C17" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D17" s="105" t="inlineStr">
+      <c r="D17" s="106" t="inlineStr">
         <is>
           <t>28% rising to 50% for niche sports. No direct comparable exists: neither Patreon nor OnlyFans publishes activation rates for creators who sign up but never charge.</t>
         </is>
       </c>
-      <c r="E17" s="105" t="inlineStr">
+      <c r="E17" s="106" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F17" s="108" t="inlineStr">
+      <c r="F17" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G17" s="105" t="inlineStr">
+      <c r="G17" s="106" t="inlineStr">
         <is>
           <t>Our own activation funnel, available from P1 onward.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="81" t="inlineStr">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t>Fan acquisition capacity</t>
         </is>
       </c>
-      <c r="B18" s="109" t="inlineStr">
+      <c r="B18" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C18" s="107" t="inlineStr">
+      <c r="C18" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D18" s="105" t="inlineStr">
+      <c r="D18" s="106" t="inlineStr">
         <is>
           <t>An athlete can recruit 30-69 new paying fans a year depending on segment. This ceiling is what makes churn bite in the model: without it, higher churn perversely RAISED revenue, because the year-end target was reachable at any churn rate.</t>
         </is>
       </c>
-      <c r="E18" s="105" t="inlineStr">
+      <c r="E18" s="106" t="inlineStr">
         <is>
           <t>None: introduced to fix a modelling flaw found by stress testing</t>
         </is>
       </c>
-      <c r="F18" s="108" t="inlineStr">
+      <c r="F18" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G18" s="105" t="inlineStr">
+      <c r="G18" s="106" t="inlineStr">
         <is>
           <t>Observed gross adds per athlete per year.</t>
         </is>
@@ -11220,7 +11855,7 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="81" t="inlineStr">
+      <c r="A20" s="83" t="inlineStr">
         <is>
           <t>PSP percentage fee</t>
         </is>
@@ -11229,34 +11864,34 @@
         <f>Assumptions!$C$50</f>
         <v/>
       </c>
-      <c r="C20" s="111" t="inlineStr">
+      <c r="C20" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D20" s="105" t="inlineStr">
+      <c r="D20" s="106" t="inlineStr">
         <is>
           <t>Stripe for a Spanish entity: 1.5% + EUR 0.25 on EEA domestic cards, 2.5% on UK cards, 3.25% on non-EEA. 1.9% is the blend for a mostly-European fan base. CORRECTION: an earlier version of this model used the US headline of 2.9% and overstated the largest cost line in the business by about a third.</t>
         </is>
       </c>
-      <c r="E20" s="105" t="inlineStr">
+      <c r="E20" s="106" t="inlineStr">
         <is>
           <t>Stripe published EU/EEA pricing, 2026</t>
         </is>
       </c>
-      <c r="F20" s="106" t="inlineStr">
+      <c r="F20" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G20" s="105" t="inlineStr">
+      <c r="G20" s="106" t="inlineStr">
         <is>
           <t>Interchange-plus terms become negotiable above roughly EUR 5M processed.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="81" t="inlineStr">
+      <c r="A21" s="83" t="inlineStr">
         <is>
           <t>PSP fixed fee per transaction</t>
         </is>
@@ -11265,34 +11900,34 @@
         <f>Assumptions!$C$51</f>
         <v/>
       </c>
-      <c r="C21" s="111" t="inlineStr">
+      <c r="C21" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D21" s="105" t="inlineStr">
+      <c r="D21" s="106" t="inlineStr">
         <is>
           <t>EUR 0.25 per transaction. On a EUR 4.99 tier that single fee is a third of our take, which is why the tier floor and annual billing move more margin than the take rate does.</t>
         </is>
       </c>
-      <c r="E21" s="105" t="inlineStr">
+      <c r="E21" s="106" t="inlineStr">
         <is>
           <t>Stripe published pricing, 2026</t>
         </is>
       </c>
-      <c r="F21" s="106" t="inlineStr">
+      <c r="F21" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G21" s="105" t="inlineStr">
+      <c r="G21" s="106" t="inlineStr">
         <is>
           <t>Volume renegotiation; annual billing turns twelve fees into one.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="81" t="inlineStr">
+      <c r="A22" s="83" t="inlineStr">
         <is>
           <t>Payout fees</t>
         </is>
@@ -11301,27 +11936,27 @@
         <f>Assumptions!$C$52</f>
         <v/>
       </c>
-      <c r="C22" s="111" t="inlineStr">
+      <c r="C22" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D22" s="105" t="inlineStr">
+      <c r="D22" s="106" t="inlineStr">
         <is>
           <t>Stripe Connect Express: roughly 0.25% + EUR 0.25 per payout, plus a monthly active-account fee that is not modelled as a separate line.</t>
         </is>
       </c>
-      <c r="E22" s="105" t="inlineStr">
+      <c r="E22" s="106" t="inlineStr">
         <is>
           <t>Stripe Connect pricing, 2026</t>
         </is>
       </c>
-      <c r="F22" s="110" t="inlineStr">
+      <c r="F22" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G22" s="105" t="inlineStr">
+      <c r="G22" s="106" t="inlineStr">
         <is>
           <t>Actual payout frequency once athletes are onboarded.</t>
         </is>
@@ -11341,118 +11976,118 @@
       <c r="G23" s="14" t="n"/>
     </row>
     <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="81" t="inlineStr">
+      <c r="A24" s="83" t="inlineStr">
         <is>
           <t>Sport participation by country</t>
         </is>
       </c>
-      <c r="B24" s="109" t="inlineStr">
+      <c r="B24" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C24" s="107" t="inlineStr">
+      <c r="C24" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D24" s="105" t="inlineStr">
+      <c r="D24" s="106" t="inlineStr">
         <is>
           <t>Eurobarometer 525, share who NEVER exercise: Finland 8%, Sweden 12%, Denmark 20%, Poland 65%, Greece 68%, Portugal 73%, EU-27 average 45%. Six of the 34 countries in the index are measured; the other 28 are estimates placed inside that distribution.</t>
         </is>
       </c>
-      <c r="E24" s="105" t="inlineStr">
+      <c r="E24" s="106" t="inlineStr">
         <is>
           <t>Special Eurobarometer 525, Sport and Physical Activity, September 2022</t>
         </is>
       </c>
-      <c r="F24" s="110" t="inlineStr">
+      <c r="F24" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G24" s="105" t="inlineStr">
+      <c r="G24" s="106" t="inlineStr">
         <is>
           <t>Federation licence counts, published annually and free (CSD in Spain).</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="81" t="inlineStr">
+      <c r="A25" s="83" t="inlineStr">
         <is>
           <t>Padel market size</t>
         </is>
       </c>
-      <c r="B25" s="109" t="inlineStr">
+      <c r="B25" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C25" s="111" t="inlineStr">
+      <c r="C25" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D25" s="105" t="inlineStr">
+      <c r="D25" s="106" t="inlineStr">
         <is>
           <t>Spain has ~6.0M active players (12.7% of the population), 109,040 federation licences and 17,300+ courts; globally 35M+ players and 77,000+ courts. This is the clearest case for weighting a sport regionally rather than globally, padel scores 77.7 in Spain and 45.1 worldwide.</t>
         </is>
       </c>
-      <c r="E25" s="105" t="inlineStr">
+      <c r="E25" s="106" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="F25" s="106" t="inlineStr">
+      <c r="F25" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G25" s="105" t="inlineStr">
+      <c r="G25" s="106" t="inlineStr">
         <is>
           <t>Annual FIP refresh.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="81" t="inlineStr">
+      <c r="A26" s="83" t="inlineStr">
         <is>
           <t>Sports fandom by country</t>
         </is>
       </c>
-      <c r="B26" s="109" t="inlineStr">
+      <c r="B26" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C26" s="107" t="inlineStr">
+      <c r="C26" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D26" s="105" t="inlineStr">
+      <c r="D26" s="106" t="inlineStr">
         <is>
           <t>The weakest layer of the sport index, and it drives both the `demand` and `appetite` signals. Commercial audience panels (Nielsen Sports, YouGov) cost more than the entire Y1-Y2 analytics budget.</t>
         </is>
       </c>
-      <c r="E26" s="105" t="inlineStr">
+      <c r="E26" s="106" t="inlineStr">
         <is>
           <t>None: reasoned estimates only</t>
         </is>
       </c>
-      <c r="F26" s="108" t="inlineStr">
+      <c r="F26" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G26" s="105" t="inlineStr">
+      <c r="G26" s="106" t="inlineStr">
         <is>
           <t>Our own engagement data per sport per country once connectors are live. This is what makes the index self-improving rather than something anyone could copy.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="81" t="inlineStr">
+      <c r="A27" s="83" t="inlineStr">
         <is>
           <t>Athlete count trajectory</t>
         </is>
@@ -11461,29 +12096,29 @@
         <f>Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="C27" s="107" t="inlineStr">
+      <c r="C27" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D27" s="105" t="inlineStr">
+      <c r="D27" s="106" t="inlineStr">
         <is>
           <t>250 rising to 8,500 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
         </is>
       </c>
-      <c r="E27" s="105" t="inlineStr">
+      <c r="E27" s="106" t="inlineStr">
         <is>
           <t>None: it is a target</t>
         </is>
       </c>
-      <c r="F27" s="108" t="inlineStr">
+      <c r="F27" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G27" s="105" t="inlineStr">
-        <is>
-          <t>The pre-seed gate tests it directly: 400 athletes and EUR 10k MRR.</t>
+      <c r="G27" s="106" t="inlineStr">
+        <is>
+          <t>The pre-seed gate tests it directly: 250 athletes and the first paying sponsors.</t>
         </is>
       </c>
     </row>
@@ -11501,7 +12136,7 @@
       <c r="G28" s="14" t="n"/>
     </row>
     <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="81" t="inlineStr">
+      <c r="A29" s="83" t="inlineStr">
         <is>
           <t>Athlete CAC</t>
         </is>
@@ -11510,34 +12145,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C29" s="107" t="inlineStr">
+      <c r="C29" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D29" s="105" t="inlineStr">
+      <c r="D29" s="106" t="inlineStr">
         <is>
           <t>EUR 16-36 for niche, EUR 40-88 for popular. The gap reflects displacing an existing agent relationship versus reaching someone with no representation at all. No published comparable exists for athlete acquisition in this segment.</t>
         </is>
       </c>
-      <c r="E29" s="105" t="inlineStr">
+      <c r="E29" s="106" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F29" s="108" t="inlineStr">
+      <c r="F29" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G29" s="105" t="inlineStr">
+      <c r="G29" s="106" t="inlineStr">
         <is>
           <t>Measured CAC by channel from the first federation partnership.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="81" t="inlineStr">
+      <c r="A30" s="83" t="inlineStr">
         <is>
           <t>Admission rate, direct applicants</t>
         </is>
@@ -11546,34 +12181,34 @@
         <f>Assumptions!$C$82</f>
         <v/>
       </c>
-      <c r="C30" s="112" t="inlineStr">
+      <c r="C30" s="113" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D30" s="105" t="inlineStr">
+      <c r="D30" s="106" t="inlineStr">
         <is>
           <t>20% of direct applicants are admitted, 25% go to a human, 40% are refused and 15% never finish the form. Not a judgement: it is the ops-load output of scripts/admission_stress.py run over the admission policy itself, so retuning a threshold moves this figure. The sweep asserts the model and the policy stay in step and fails if they drift.</t>
         </is>
       </c>
-      <c r="E30" s="105" t="inlineStr">
+      <c r="E30" s="106" t="inlineStr">
         <is>
           <t>scripts/admission_stress.py, section 7, over a modelled applicant mix</t>
         </is>
       </c>
-      <c r="F30" s="110" t="inlineStr">
+      <c r="F30" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G30" s="105" t="inlineStr">
+      <c r="G30" s="106" t="inlineStr">
         <is>
           <t>Real intake data. The mix the sweep assumes is the soft part, not the arithmetic.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="81" t="inlineStr">
+      <c r="A31" s="83" t="inlineStr">
         <is>
           <t>Admission rate, club-nominated</t>
         </is>
@@ -11582,34 +12217,34 @@
         <f>Assumptions!$C$84</f>
         <v/>
       </c>
-      <c r="C31" s="107" t="inlineStr">
+      <c r="C31" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D31" s="105" t="inlineStr">
+      <c r="D31" s="106" t="inlineStr">
         <is>
           <t>45% admitted against 20% direct. A verified club's nomination confers a credibility floor of 0.75 x its own legitimacy score, which carries a completed application over the admit line that would otherwise have gone to review. It cannot carry an empty one: no club can supply someone else's date of birth, so the uplift is real but bounded.</t>
         </is>
       </c>
-      <c r="E31" s="105" t="inlineStr">
+      <c r="E31" s="106" t="inlineStr">
         <is>
           <t>None: the mechanism is built and tested, the conversion is not yet measured</t>
         </is>
       </c>
-      <c r="F31" s="108" t="inlineStr">
+      <c r="F31" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G31" s="105" t="inlineStr">
+      <c r="G31" s="106" t="inlineStr">
         <is>
           <t>The first federation partnership: nominated applicants are tagged, so this is measurable from day one of it.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="81" t="inlineStr">
+      <c r="A32" s="83" t="inlineStr">
         <is>
           <t>Athlete verification cost</t>
         </is>
@@ -11618,34 +12253,34 @@
         <f>Assumptions!$C$87</f>
         <v/>
       </c>
-      <c r="C32" s="112" t="inlineStr">
+      <c r="C32" s="113" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D32" s="105" t="inlineStr">
+      <c r="D32" s="106" t="inlineStr">
         <is>
           <t>Four minutes per manual review, priced at the same loaded salary the People line uses, over 1,700 productive hours. Peaks at EUR 47k and 0.64 reviewer-FTE in Y10, which is the finding rather than the cost: verification is not a money problem at this scale. The reason to automate it is latency: an athlete sitting in the queue is not listed, not matchable and not earning.</t>
         </is>
       </c>
-      <c r="E32" s="105" t="inlineStr">
+      <c r="E32" s="106" t="inlineStr">
         <is>
           <t>Derived from the sweep's review volume and the model's own salary line</t>
         </is>
       </c>
-      <c r="F32" s="110" t="inlineStr">
+      <c r="F32" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G32" s="105" t="inlineStr">
+      <c r="G32" s="106" t="inlineStr">
         <is>
           <t>Timing real reviews. Four minutes is an estimate of a mechanical task.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="81" t="inlineStr">
+      <c r="A33" s="83" t="inlineStr">
         <is>
           <t>Athlete CAC vs the funnel</t>
         </is>
@@ -11654,34 +12289,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C33" s="107" t="inlineStr">
+      <c r="C33" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D33" s="105" t="inlineStr">
+      <c r="D33" s="106" t="inlineStr">
         <is>
           <t>Deliberately NOT multiplied by the admission funnel. Segment CAC is defined as the cost of landing one athlete ON the platform, so scaling it by 1/admission-rate would charge the same money twice. The Costs sheet carries a memo line showing what that CAC works out to per application (EUR 3.40 in Y1 rising to EUR 22), the figure to hold against what a channel actually charges per name reached.</t>
         </is>
       </c>
-      <c r="E33" s="105" t="inlineStr">
+      <c r="E33" s="106" t="inlineStr">
         <is>
           <t>None: this is a definitional choice, made explicit so it is not silently reversed</t>
         </is>
       </c>
-      <c r="F33" s="108" t="inlineStr">
+      <c r="F33" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G33" s="105" t="inlineStr">
+      <c r="G33" s="106" t="inlineStr">
         <is>
           <t>Channel-level spend against applications, which the funnel now records.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="81" t="inlineStr">
+      <c r="A34" s="83" t="inlineStr">
         <is>
           <t>Loaded salary, Spain</t>
         </is>
@@ -11690,34 +12325,34 @@
         <f>Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="C34" s="104" t="inlineStr">
+      <c r="C34" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D34" s="105" t="inlineStr">
+      <c r="D34" s="106" t="inlineStr">
         <is>
           <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k, around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
         </is>
       </c>
-      <c r="E34" s="105" t="inlineStr">
+      <c r="E34" s="106" t="inlineStr">
         <is>
           <t>Spanish Seguridad Social employer contribution rates</t>
         </is>
       </c>
-      <c r="F34" s="110" t="inlineStr">
+      <c r="F34" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G34" s="105" t="inlineStr">
+      <c r="G34" s="106" t="inlineStr">
         <is>
           <t>Actual offers accepted.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="81" t="inlineStr">
+      <c r="A35" s="83" t="inlineStr">
         <is>
           <t>AWS infrastructure</t>
         </is>
@@ -11726,34 +12361,34 @@
         <f>Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="C35" s="104" t="inlineStr">
+      <c r="C35" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D35" s="105" t="inlineStr">
+      <c r="D35" s="106" t="inlineStr">
         <is>
           <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
         </is>
       </c>
-      <c r="E35" s="105" t="inlineStr">
+      <c r="E35" s="106" t="inlineStr">
         <is>
           <t>AWS published list pricing, 2026</t>
         </is>
       </c>
-      <c r="F35" s="110" t="inlineStr">
+      <c r="F35" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G35" s="105" t="inlineStr">
+      <c r="G35" s="106" t="inlineStr">
         <is>
           <t>Actual bills; commit to Savings Plans once usage is stable.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="81" t="inlineStr">
+      <c r="A36" s="83" t="inlineStr">
         <is>
           <t>Media egress</t>
         </is>
@@ -11762,34 +12397,34 @@
         <f>Assumptions!$C$60</f>
         <v/>
       </c>
-      <c r="C36" s="111" t="inlineStr">
+      <c r="C36" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D36" s="105" t="inlineStr">
+      <c r="D36" s="106" t="inlineStr">
         <is>
           <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year, the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
         </is>
       </c>
-      <c r="E36" s="105" t="inlineStr">
+      <c r="E36" s="106" t="inlineStr">
         <is>
           <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
         </is>
       </c>
-      <c r="F36" s="106" t="inlineStr">
+      <c r="F36" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G36" s="105" t="inlineStr">
+      <c r="G36" s="106" t="inlineStr">
         <is>
           <t>Nothing. Both are published.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="81" t="inlineStr">
+      <c r="A37" s="83" t="inlineStr">
         <is>
           <t>Moderation cost</t>
         </is>
@@ -11798,27 +12433,27 @@
         <f>Assumptions!$C$62</f>
         <v/>
       </c>
-      <c r="C37" s="107" t="inlineStr">
+      <c r="C37" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D37" s="105" t="inlineStr">
+      <c r="D37" s="106" t="inlineStr">
         <is>
           <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
         </is>
       </c>
-      <c r="E37" s="105" t="inlineStr">
+      <c r="E37" s="106" t="inlineStr">
         <is>
           <t>None cited</t>
         </is>
       </c>
-      <c r="F37" s="108" t="inlineStr">
+      <c r="F37" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G37" s="105" t="inlineStr">
+      <c r="G37" s="106" t="inlineStr">
         <is>
           <t>Vendor quotes once P2 scope is fixed.</t>
         </is>
@@ -11838,7 +12473,7 @@
       <c r="G38" s="14" t="n"/>
     </row>
     <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="81" t="inlineStr">
+      <c r="A39" s="83" t="inlineStr">
         <is>
           <t>Corporate tax rates</t>
         </is>
@@ -11847,34 +12482,34 @@
         <f>Assumptions!$C$77</f>
         <v/>
       </c>
-      <c r="C39" s="111" t="inlineStr">
+      <c r="C39" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D39" s="105" t="inlineStr">
+      <c r="D39" s="106" t="inlineStr">
         <is>
           <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
         </is>
       </c>
-      <c r="E39" s="105" t="inlineStr">
+      <c r="E39" s="106" t="inlineStr">
         <is>
           <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
         </is>
       </c>
-      <c r="F39" s="106" t="inlineStr">
+      <c r="F39" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G39" s="105" t="inlineStr">
+      <c r="G39" s="106" t="inlineStr">
         <is>
           <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="81" t="inlineStr">
+      <c r="A40" s="83" t="inlineStr">
         <is>
           <t>Risk-free rate</t>
         </is>
@@ -11883,71 +12518,71 @@
         <f>Assumptions!$C$97</f>
         <v/>
       </c>
-      <c r="C40" s="111" t="inlineStr">
+      <c r="C40" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D40" s="105" t="inlineStr">
+      <c r="D40" s="106" t="inlineStr">
         <is>
           <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
         </is>
       </c>
-      <c r="E40" s="105" t="inlineStr">
+      <c r="E40" s="106" t="inlineStr">
         <is>
           <t>Spanish 10Y government bond yield</t>
         </is>
       </c>
-      <c r="F40" s="106" t="inlineStr">
+      <c r="F40" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G40" s="105" t="inlineStr">
+      <c r="G40" s="106" t="inlineStr">
         <is>
           <t>Refresh at the date of any raise.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="81" t="inlineStr">
+      <c r="A41" s="83" t="inlineStr">
         <is>
           <t>WACC / discount rate</t>
         </is>
       </c>
-      <c r="B41" s="109" t="inlineStr">
+      <c r="B41" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C41" s="104" t="inlineStr">
+      <c r="C41" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D41" s="105" t="inlineStr">
+      <c r="D41" s="106" t="inlineStr">
         <is>
           <t>25%, against a published mature-company anchor of 6.01%. Damodaran's European cost of capital dataset puts Software (Internet) at 6.01% in euros across 23 listed firms, and the European market ex-financials at 6.59%. Those are costs of capital for mature listed companies; this is a pre-revenue venture, and the 19-point gap is the stage premium. It is stated rather than buried because it is the largest single judgement in the valuation. Damodaran publishes no dataset for venture-stage rates, so the premium itself is convention (20-35% is the usual range) and not a sourced figure. The sensitivity grid runs 20-30% because this is arguable rather than knowable.</t>
         </is>
       </c>
-      <c r="E41" s="105" t="inlineStr">
+      <c r="E41" s="106" t="inlineStr">
         <is>
           <t>Aswath Damodaran, NYU Stern, Cost of Capital by Industry (Europe), updated 5 January 2026</t>
         </is>
       </c>
-      <c r="F41" s="110" t="inlineStr">
+      <c r="F41" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G41" s="105" t="inlineStr">
+      <c r="G41" s="106" t="inlineStr">
         <is>
           <t>An actual term sheet prices this for you.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="81" t="inlineStr">
+      <c r="A42" s="83" t="inlineStr">
         <is>
           <t>Exit revenue multiple</t>
         </is>
@@ -11956,34 +12591,34 @@
         <f>Assumptions!$C$96</f>
         <v/>
       </c>
-      <c r="C42" s="104" t="inlineStr">
+      <c r="C42" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D42" s="105" t="inlineStr">
+      <c r="D42" s="106" t="inlineStr">
         <is>
           <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
         </is>
       </c>
-      <c r="E42" s="105" t="inlineStr">
+      <c r="E42" s="106" t="inlineStr">
         <is>
           <t>Public marketplace and SaaS trading multiples</t>
         </is>
       </c>
-      <c r="F42" s="110" t="inlineStr">
+      <c r="F42" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G42" s="105" t="inlineStr">
+      <c r="G42" s="106" t="inlineStr">
         <is>
           <t>Comparable private transactions nearer an exit.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="81" t="inlineStr">
+      <c r="A43" s="83" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
@@ -11992,27 +12627,27 @@
         <f>Assumptions!$C$95</f>
         <v/>
       </c>
-      <c r="C43" s="104" t="inlineStr">
+      <c r="C43" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D43" s="105" t="inlineStr">
+      <c r="D43" s="106" t="inlineStr">
         <is>
           <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
         </is>
       </c>
-      <c r="E43" s="105" t="inlineStr">
+      <c r="E43" s="106" t="inlineStr">
         <is>
           <t>Standard DCF convention</t>
         </is>
       </c>
-      <c r="F43" s="110" t="inlineStr">
+      <c r="F43" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G43" s="105" t="inlineStr">
+      <c r="G43" s="106" t="inlineStr">
         <is>
           <t>Nothing: it is a convention, and the grid shows its effect.</t>
         </is>
@@ -12032,112 +12667,112 @@
       <c r="G44" s="14" t="n"/>
     </row>
     <row r="45" ht="58" customHeight="1">
-      <c r="A45" s="81" t="inlineStr">
+      <c r="A45" s="83" t="inlineStr">
         <is>
           <t>Payout age floor</t>
         </is>
       </c>
-      <c r="B45" s="109" t="inlineStr">
+      <c r="B45" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C45" s="111" t="inlineStr">
+      <c r="C45" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D45" s="105" t="inlineStr">
+      <c r="D45" s="106" t="inlineStr">
         <is>
           <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
         </is>
       </c>
-      <c r="E45" s="105" t="inlineStr">
+      <c r="E45" s="106" t="inlineStr">
         <is>
           <t>Stripe Connect documentation</t>
         </is>
       </c>
-      <c r="F45" s="106" t="inlineStr">
+      <c r="F45" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G45" s="105" t="inlineStr">
+      <c r="G45" s="106" t="inlineStr">
         <is>
           <t>Nothing: it is a hard platform rule.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
-      <c r="A46" s="81" t="inlineStr">
+      <c r="A46" s="83" t="inlineStr">
         <is>
           <t>Digital consent age, Spain</t>
         </is>
       </c>
-      <c r="B46" s="109" t="inlineStr">
+      <c r="B46" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C46" s="111" t="inlineStr">
+      <c r="C46" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D46" s="105" t="inlineStr">
+      <c r="D46" s="106" t="inlineStr">
         <is>
           <t>14 today under LOPDGDD Art. 7. A draft Organic Law on the Protection of Minors in Digital Environments would raise it to 16 and make age verification mandatory, which is why 16 is the forward-compatible floor for an account.</t>
         </is>
       </c>
-      <c r="E46" s="105" t="inlineStr">
+      <c r="E46" s="106" t="inlineStr">
         <is>
           <t>LOPDGDD Art. 7; draft Organic Law, Council of Ministers, March 2025</t>
         </is>
       </c>
-      <c r="F46" s="106" t="inlineStr">
+      <c r="F46" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G46" s="105" t="inlineStr">
+      <c r="G46" s="106" t="inlineStr">
         <is>
           <t>Track the bill through Parliament.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="113" t="inlineStr">
+      <c r="A48" s="114" t="inlineStr">
         <is>
           <t>THE THREE ASSUMPTIONS MOST LIKELY TO BE WRONG</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="114" t="inlineStr">
+      <c r="A49" s="115" t="inlineStr">
         <is>
           <t>1. Fan churn. We assume 6-13%/month; Patreon reports 10-15%. If Patreon is right, Y10 revenue falls from about EUR 58M to EUR 51M and the capital requirement roughly doubles.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="114" t="inlineStr">
+      <c r="A50" s="115" t="inlineStr">
         <is>
           <t>2. Athlete count. The trajectory is a target, not a forecast, and everything scales off it.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="114" t="inlineStr">
+      <c r="A51" s="115" t="inlineStr">
         <is>
           <t>3. Share of athletes who monetise. No published comparable exists at all.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="115" t="inlineStr"/>
+      <c r="A52" s="116" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="115" t="inlineStr">
+      <c r="A53" s="116" t="inlineStr">
         <is>
           <t>All three are answered by the same thing: three months of real cohort data from P1.</t>
         </is>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -234,7 +234,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -279,6 +279,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E4F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7E8EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2EDE2"/>
       </patternFill>
     </fill>
   </fills>
@@ -346,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -406,9 +421,12 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="16" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="15" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="14" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="11" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="16" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -420,7 +438,6 @@
     <xf numFmtId="167" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="17" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -434,7 +451,6 @@
     <xf numFmtId="164" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="14" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -476,15 +492,15 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -933,7 +949,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dependent value, pulled from another sheet</t>
+          <t>Dependent value, pulled from another sheet or from the one input at the head of its row</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1753,148 +1769,155 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="55" t="n">
+      <c r="A27" s="57" t="n">
         <v>0.01</v>
       </c>
-      <c r="C27" s="57">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.01)/(0.18-0.01)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D27" s="57">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.01)/(0.2-0.01)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E27" s="57">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.01)/(0.22-0.01)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F27" s="57">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.01)/(0.25-0.01)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G27" s="57">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.01)/(0.28-0.01)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H27" s="57">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.01)/(0.3-0.01)/(1+0.3)^10</f>
+      <c r="C27" s="58">
+        <f>CashFlow!C9/(1+C$26)^1+CashFlow!D9/(1+C$26)^2+CashFlow!E9/(1+C$26)^3+CashFlow!F9/(1+C$26)^4+CashFlow!G9/(1+C$26)^5+CashFlow!H9/(1+C$26)^6+CashFlow!I9/(1+C$26)^7+CashFlow!J9/(1+C$26)^8+CashFlow!K9/(1+C$26)^9+CashFlow!L9/(1+C$26)^10+CashFlow!L9*(1+$A27)/(C$26-$A27)/(1+C$26)^10</f>
+        <v/>
+      </c>
+      <c r="D27" s="58">
+        <f>CashFlow!C9/(1+D$26)^1+CashFlow!D9/(1+D$26)^2+CashFlow!E9/(1+D$26)^3+CashFlow!F9/(1+D$26)^4+CashFlow!G9/(1+D$26)^5+CashFlow!H9/(1+D$26)^6+CashFlow!I9/(1+D$26)^7+CashFlow!J9/(1+D$26)^8+CashFlow!K9/(1+D$26)^9+CashFlow!L9/(1+D$26)^10+CashFlow!L9*(1+$A27)/(D$26-$A27)/(1+D$26)^10</f>
+        <v/>
+      </c>
+      <c r="E27" s="58">
+        <f>CashFlow!C9/(1+E$26)^1+CashFlow!D9/(1+E$26)^2+CashFlow!E9/(1+E$26)^3+CashFlow!F9/(1+E$26)^4+CashFlow!G9/(1+E$26)^5+CashFlow!H9/(1+E$26)^6+CashFlow!I9/(1+E$26)^7+CashFlow!J9/(1+E$26)^8+CashFlow!K9/(1+E$26)^9+CashFlow!L9/(1+E$26)^10+CashFlow!L9*(1+$A27)/(E$26-$A27)/(1+E$26)^10</f>
+        <v/>
+      </c>
+      <c r="F27" s="58">
+        <f>CashFlow!C9/(1+F$26)^1+CashFlow!D9/(1+F$26)^2+CashFlow!E9/(1+F$26)^3+CashFlow!F9/(1+F$26)^4+CashFlow!G9/(1+F$26)^5+CashFlow!H9/(1+F$26)^6+CashFlow!I9/(1+F$26)^7+CashFlow!J9/(1+F$26)^8+CashFlow!K9/(1+F$26)^9+CashFlow!L9/(1+F$26)^10+CashFlow!L9*(1+$A27)/(F$26-$A27)/(1+F$26)^10</f>
+        <v/>
+      </c>
+      <c r="G27" s="58">
+        <f>CashFlow!C9/(1+G$26)^1+CashFlow!D9/(1+G$26)^2+CashFlow!E9/(1+G$26)^3+CashFlow!F9/(1+G$26)^4+CashFlow!G9/(1+G$26)^5+CashFlow!H9/(1+G$26)^6+CashFlow!I9/(1+G$26)^7+CashFlow!J9/(1+G$26)^8+CashFlow!K9/(1+G$26)^9+CashFlow!L9/(1+G$26)^10+CashFlow!L9*(1+$A27)/(G$26-$A27)/(1+G$26)^10</f>
+        <v/>
+      </c>
+      <c r="H27" s="58">
+        <f>CashFlow!C9/(1+H$26)^1+CashFlow!D9/(1+H$26)^2+CashFlow!E9/(1+H$26)^3+CashFlow!F9/(1+H$26)^4+CashFlow!G9/(1+H$26)^5+CashFlow!H9/(1+H$26)^6+CashFlow!I9/(1+H$26)^7+CashFlow!J9/(1+H$26)^8+CashFlow!K9/(1+H$26)^9+CashFlow!L9/(1+H$26)^10+CashFlow!L9*(1+$A27)/(H$26-$A27)/(1+H$26)^10</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="55" t="n">
+      <c r="A28" s="57" t="n">
         <v>0.02</v>
       </c>
-      <c r="C28" s="57">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.02)/(0.18-0.02)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D28" s="57">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.02)/(0.2-0.02)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E28" s="57">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.02)/(0.22-0.02)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F28" s="57">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.02)/(0.25-0.02)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G28" s="57">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.02)/(0.28-0.02)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H28" s="57">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.02)/(0.3-0.02)/(1+0.3)^10</f>
+      <c r="C28" s="58">
+        <f>CashFlow!C9/(1+C$26)^1+CashFlow!D9/(1+C$26)^2+CashFlow!E9/(1+C$26)^3+CashFlow!F9/(1+C$26)^4+CashFlow!G9/(1+C$26)^5+CashFlow!H9/(1+C$26)^6+CashFlow!I9/(1+C$26)^7+CashFlow!J9/(1+C$26)^8+CashFlow!K9/(1+C$26)^9+CashFlow!L9/(1+C$26)^10+CashFlow!L9*(1+$A28)/(C$26-$A28)/(1+C$26)^10</f>
+        <v/>
+      </c>
+      <c r="D28" s="58">
+        <f>CashFlow!C9/(1+D$26)^1+CashFlow!D9/(1+D$26)^2+CashFlow!E9/(1+D$26)^3+CashFlow!F9/(1+D$26)^4+CashFlow!G9/(1+D$26)^5+CashFlow!H9/(1+D$26)^6+CashFlow!I9/(1+D$26)^7+CashFlow!J9/(1+D$26)^8+CashFlow!K9/(1+D$26)^9+CashFlow!L9/(1+D$26)^10+CashFlow!L9*(1+$A28)/(D$26-$A28)/(1+D$26)^10</f>
+        <v/>
+      </c>
+      <c r="E28" s="58">
+        <f>CashFlow!C9/(1+E$26)^1+CashFlow!D9/(1+E$26)^2+CashFlow!E9/(1+E$26)^3+CashFlow!F9/(1+E$26)^4+CashFlow!G9/(1+E$26)^5+CashFlow!H9/(1+E$26)^6+CashFlow!I9/(1+E$26)^7+CashFlow!J9/(1+E$26)^8+CashFlow!K9/(1+E$26)^9+CashFlow!L9/(1+E$26)^10+CashFlow!L9*(1+$A28)/(E$26-$A28)/(1+E$26)^10</f>
+        <v/>
+      </c>
+      <c r="F28" s="58">
+        <f>CashFlow!C9/(1+F$26)^1+CashFlow!D9/(1+F$26)^2+CashFlow!E9/(1+F$26)^3+CashFlow!F9/(1+F$26)^4+CashFlow!G9/(1+F$26)^5+CashFlow!H9/(1+F$26)^6+CashFlow!I9/(1+F$26)^7+CashFlow!J9/(1+F$26)^8+CashFlow!K9/(1+F$26)^9+CashFlow!L9/(1+F$26)^10+CashFlow!L9*(1+$A28)/(F$26-$A28)/(1+F$26)^10</f>
+        <v/>
+      </c>
+      <c r="G28" s="58">
+        <f>CashFlow!C9/(1+G$26)^1+CashFlow!D9/(1+G$26)^2+CashFlow!E9/(1+G$26)^3+CashFlow!F9/(1+G$26)^4+CashFlow!G9/(1+G$26)^5+CashFlow!H9/(1+G$26)^6+CashFlow!I9/(1+G$26)^7+CashFlow!J9/(1+G$26)^8+CashFlow!K9/(1+G$26)^9+CashFlow!L9/(1+G$26)^10+CashFlow!L9*(1+$A28)/(G$26-$A28)/(1+G$26)^10</f>
+        <v/>
+      </c>
+      <c r="H28" s="58">
+        <f>CashFlow!C9/(1+H$26)^1+CashFlow!D9/(1+H$26)^2+CashFlow!E9/(1+H$26)^3+CashFlow!F9/(1+H$26)^4+CashFlow!G9/(1+H$26)^5+CashFlow!H9/(1+H$26)^6+CashFlow!I9/(1+H$26)^7+CashFlow!J9/(1+H$26)^8+CashFlow!K9/(1+H$26)^9+CashFlow!L9/(1+H$26)^10+CashFlow!L9*(1+$A28)/(H$26-$A28)/(1+H$26)^10</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="55" t="n">
+      <c r="A29" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="C29" s="57">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.03)/(0.18-0.03)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D29" s="57">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.03)/(0.2-0.03)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E29" s="57">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.03)/(0.22-0.03)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F29" s="57">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.03)/(0.25-0.03)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G29" s="57">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.03)/(0.28-0.03)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H29" s="57">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.03)/(0.3-0.03)/(1+0.3)^10</f>
+      <c r="C29" s="58">
+        <f>CashFlow!C9/(1+C$26)^1+CashFlow!D9/(1+C$26)^2+CashFlow!E9/(1+C$26)^3+CashFlow!F9/(1+C$26)^4+CashFlow!G9/(1+C$26)^5+CashFlow!H9/(1+C$26)^6+CashFlow!I9/(1+C$26)^7+CashFlow!J9/(1+C$26)^8+CashFlow!K9/(1+C$26)^9+CashFlow!L9/(1+C$26)^10+CashFlow!L9*(1+$A29)/(C$26-$A29)/(1+C$26)^10</f>
+        <v/>
+      </c>
+      <c r="D29" s="58">
+        <f>CashFlow!C9/(1+D$26)^1+CashFlow!D9/(1+D$26)^2+CashFlow!E9/(1+D$26)^3+CashFlow!F9/(1+D$26)^4+CashFlow!G9/(1+D$26)^5+CashFlow!H9/(1+D$26)^6+CashFlow!I9/(1+D$26)^7+CashFlow!J9/(1+D$26)^8+CashFlow!K9/(1+D$26)^9+CashFlow!L9/(1+D$26)^10+CashFlow!L9*(1+$A29)/(D$26-$A29)/(1+D$26)^10</f>
+        <v/>
+      </c>
+      <c r="E29" s="58">
+        <f>CashFlow!C9/(1+E$26)^1+CashFlow!D9/(1+E$26)^2+CashFlow!E9/(1+E$26)^3+CashFlow!F9/(1+E$26)^4+CashFlow!G9/(1+E$26)^5+CashFlow!H9/(1+E$26)^6+CashFlow!I9/(1+E$26)^7+CashFlow!J9/(1+E$26)^8+CashFlow!K9/(1+E$26)^9+CashFlow!L9/(1+E$26)^10+CashFlow!L9*(1+$A29)/(E$26-$A29)/(1+E$26)^10</f>
+        <v/>
+      </c>
+      <c r="F29" s="58">
+        <f>CashFlow!C9/(1+F$26)^1+CashFlow!D9/(1+F$26)^2+CashFlow!E9/(1+F$26)^3+CashFlow!F9/(1+F$26)^4+CashFlow!G9/(1+F$26)^5+CashFlow!H9/(1+F$26)^6+CashFlow!I9/(1+F$26)^7+CashFlow!J9/(1+F$26)^8+CashFlow!K9/(1+F$26)^9+CashFlow!L9/(1+F$26)^10+CashFlow!L9*(1+$A29)/(F$26-$A29)/(1+F$26)^10</f>
+        <v/>
+      </c>
+      <c r="G29" s="58">
+        <f>CashFlow!C9/(1+G$26)^1+CashFlow!D9/(1+G$26)^2+CashFlow!E9/(1+G$26)^3+CashFlow!F9/(1+G$26)^4+CashFlow!G9/(1+G$26)^5+CashFlow!H9/(1+G$26)^6+CashFlow!I9/(1+G$26)^7+CashFlow!J9/(1+G$26)^8+CashFlow!K9/(1+G$26)^9+CashFlow!L9/(1+G$26)^10+CashFlow!L9*(1+$A29)/(G$26-$A29)/(1+G$26)^10</f>
+        <v/>
+      </c>
+      <c r="H29" s="58">
+        <f>CashFlow!C9/(1+H$26)^1+CashFlow!D9/(1+H$26)^2+CashFlow!E9/(1+H$26)^3+CashFlow!F9/(1+H$26)^4+CashFlow!G9/(1+H$26)^5+CashFlow!H9/(1+H$26)^6+CashFlow!I9/(1+H$26)^7+CashFlow!J9/(1+H$26)^8+CashFlow!K9/(1+H$26)^9+CashFlow!L9/(1+H$26)^10+CashFlow!L9*(1+$A29)/(H$26-$A29)/(1+H$26)^10</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="55" t="n">
+      <c r="A30" s="57" t="n">
         <v>0.04</v>
       </c>
-      <c r="C30" s="57">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.04)/(0.18-0.04)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D30" s="57">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.04)/(0.2-0.04)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E30" s="57">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.04)/(0.22-0.04)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F30" s="57">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.04)/(0.25-0.04)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G30" s="57">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.04)/(0.28-0.04)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H30" s="57">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.04)/(0.3-0.04)/(1+0.3)^10</f>
+      <c r="C30" s="58">
+        <f>CashFlow!C9/(1+C$26)^1+CashFlow!D9/(1+C$26)^2+CashFlow!E9/(1+C$26)^3+CashFlow!F9/(1+C$26)^4+CashFlow!G9/(1+C$26)^5+CashFlow!H9/(1+C$26)^6+CashFlow!I9/(1+C$26)^7+CashFlow!J9/(1+C$26)^8+CashFlow!K9/(1+C$26)^9+CashFlow!L9/(1+C$26)^10+CashFlow!L9*(1+$A30)/(C$26-$A30)/(1+C$26)^10</f>
+        <v/>
+      </c>
+      <c r="D30" s="58">
+        <f>CashFlow!C9/(1+D$26)^1+CashFlow!D9/(1+D$26)^2+CashFlow!E9/(1+D$26)^3+CashFlow!F9/(1+D$26)^4+CashFlow!G9/(1+D$26)^5+CashFlow!H9/(1+D$26)^6+CashFlow!I9/(1+D$26)^7+CashFlow!J9/(1+D$26)^8+CashFlow!K9/(1+D$26)^9+CashFlow!L9/(1+D$26)^10+CashFlow!L9*(1+$A30)/(D$26-$A30)/(1+D$26)^10</f>
+        <v/>
+      </c>
+      <c r="E30" s="58">
+        <f>CashFlow!C9/(1+E$26)^1+CashFlow!D9/(1+E$26)^2+CashFlow!E9/(1+E$26)^3+CashFlow!F9/(1+E$26)^4+CashFlow!G9/(1+E$26)^5+CashFlow!H9/(1+E$26)^6+CashFlow!I9/(1+E$26)^7+CashFlow!J9/(1+E$26)^8+CashFlow!K9/(1+E$26)^9+CashFlow!L9/(1+E$26)^10+CashFlow!L9*(1+$A30)/(E$26-$A30)/(1+E$26)^10</f>
+        <v/>
+      </c>
+      <c r="F30" s="58">
+        <f>CashFlow!C9/(1+F$26)^1+CashFlow!D9/(1+F$26)^2+CashFlow!E9/(1+F$26)^3+CashFlow!F9/(1+F$26)^4+CashFlow!G9/(1+F$26)^5+CashFlow!H9/(1+F$26)^6+CashFlow!I9/(1+F$26)^7+CashFlow!J9/(1+F$26)^8+CashFlow!K9/(1+F$26)^9+CashFlow!L9/(1+F$26)^10+CashFlow!L9*(1+$A30)/(F$26-$A30)/(1+F$26)^10</f>
+        <v/>
+      </c>
+      <c r="G30" s="58">
+        <f>CashFlow!C9/(1+G$26)^1+CashFlow!D9/(1+G$26)^2+CashFlow!E9/(1+G$26)^3+CashFlow!F9/(1+G$26)^4+CashFlow!G9/(1+G$26)^5+CashFlow!H9/(1+G$26)^6+CashFlow!I9/(1+G$26)^7+CashFlow!J9/(1+G$26)^8+CashFlow!K9/(1+G$26)^9+CashFlow!L9/(1+G$26)^10+CashFlow!L9*(1+$A30)/(G$26-$A30)/(1+G$26)^10</f>
+        <v/>
+      </c>
+      <c r="H30" s="58">
+        <f>CashFlow!C9/(1+H$26)^1+CashFlow!D9/(1+H$26)^2+CashFlow!E9/(1+H$26)^3+CashFlow!F9/(1+H$26)^4+CashFlow!G9/(1+H$26)^5+CashFlow!H9/(1+H$26)^6+CashFlow!I9/(1+H$26)^7+CashFlow!J9/(1+H$26)^8+CashFlow!K9/(1+H$26)^9+CashFlow!L9/(1+H$26)^10+CashFlow!L9*(1+$A30)/(H$26-$A30)/(1+H$26)^10</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="55" t="n">
+      <c r="A31" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="C31" s="57">
-        <f>CashFlow!C9/(1+0.18)^1+CashFlow!D9/(1+0.18)^2+CashFlow!E9/(1+0.18)^3+CashFlow!F9/(1+0.18)^4+CashFlow!G9/(1+0.18)^5+CashFlow!H9/(1+0.18)^6+CashFlow!I9/(1+0.18)^7+CashFlow!J9/(1+0.18)^8+CashFlow!K9/(1+0.18)^9+CashFlow!L9/(1+0.18)^10+CashFlow!L9*(1+0.05)/(0.18-0.05)/(1+0.18)^10</f>
-        <v/>
-      </c>
-      <c r="D31" s="57">
-        <f>CashFlow!C9/(1+0.2)^1+CashFlow!D9/(1+0.2)^2+CashFlow!E9/(1+0.2)^3+CashFlow!F9/(1+0.2)^4+CashFlow!G9/(1+0.2)^5+CashFlow!H9/(1+0.2)^6+CashFlow!I9/(1+0.2)^7+CashFlow!J9/(1+0.2)^8+CashFlow!K9/(1+0.2)^9+CashFlow!L9/(1+0.2)^10+CashFlow!L9*(1+0.05)/(0.2-0.05)/(1+0.2)^10</f>
-        <v/>
-      </c>
-      <c r="E31" s="57">
-        <f>CashFlow!C9/(1+0.22)^1+CashFlow!D9/(1+0.22)^2+CashFlow!E9/(1+0.22)^3+CashFlow!F9/(1+0.22)^4+CashFlow!G9/(1+0.22)^5+CashFlow!H9/(1+0.22)^6+CashFlow!I9/(1+0.22)^7+CashFlow!J9/(1+0.22)^8+CashFlow!K9/(1+0.22)^9+CashFlow!L9/(1+0.22)^10+CashFlow!L9*(1+0.05)/(0.22-0.05)/(1+0.22)^10</f>
-        <v/>
-      </c>
-      <c r="F31" s="57">
-        <f>CashFlow!C9/(1+0.25)^1+CashFlow!D9/(1+0.25)^2+CashFlow!E9/(1+0.25)^3+CashFlow!F9/(1+0.25)^4+CashFlow!G9/(1+0.25)^5+CashFlow!H9/(1+0.25)^6+CashFlow!I9/(1+0.25)^7+CashFlow!J9/(1+0.25)^8+CashFlow!K9/(1+0.25)^9+CashFlow!L9/(1+0.25)^10+CashFlow!L9*(1+0.05)/(0.25-0.05)/(1+0.25)^10</f>
-        <v/>
-      </c>
-      <c r="G31" s="57">
-        <f>CashFlow!C9/(1+0.28)^1+CashFlow!D9/(1+0.28)^2+CashFlow!E9/(1+0.28)^3+CashFlow!F9/(1+0.28)^4+CashFlow!G9/(1+0.28)^5+CashFlow!H9/(1+0.28)^6+CashFlow!I9/(1+0.28)^7+CashFlow!J9/(1+0.28)^8+CashFlow!K9/(1+0.28)^9+CashFlow!L9/(1+0.28)^10+CashFlow!L9*(1+0.05)/(0.28-0.05)/(1+0.28)^10</f>
-        <v/>
-      </c>
-      <c r="H31" s="57">
-        <f>CashFlow!C9/(1+0.3)^1+CashFlow!D9/(1+0.3)^2+CashFlow!E9/(1+0.3)^3+CashFlow!F9/(1+0.3)^4+CashFlow!G9/(1+0.3)^5+CashFlow!H9/(1+0.3)^6+CashFlow!I9/(1+0.3)^7+CashFlow!J9/(1+0.3)^8+CashFlow!K9/(1+0.3)^9+CashFlow!L9/(1+0.3)^10+CashFlow!L9*(1+0.05)/(0.3-0.05)/(1+0.3)^10</f>
-        <v/>
+      <c r="C31" s="58">
+        <f>CashFlow!C9/(1+C$26)^1+CashFlow!D9/(1+C$26)^2+CashFlow!E9/(1+C$26)^3+CashFlow!F9/(1+C$26)^4+CashFlow!G9/(1+C$26)^5+CashFlow!H9/(1+C$26)^6+CashFlow!I9/(1+C$26)^7+CashFlow!J9/(1+C$26)^8+CashFlow!K9/(1+C$26)^9+CashFlow!L9/(1+C$26)^10+CashFlow!L9*(1+$A31)/(C$26-$A31)/(1+C$26)^10</f>
+        <v/>
+      </c>
+      <c r="D31" s="58">
+        <f>CashFlow!C9/(1+D$26)^1+CashFlow!D9/(1+D$26)^2+CashFlow!E9/(1+D$26)^3+CashFlow!F9/(1+D$26)^4+CashFlow!G9/(1+D$26)^5+CashFlow!H9/(1+D$26)^6+CashFlow!I9/(1+D$26)^7+CashFlow!J9/(1+D$26)^8+CashFlow!K9/(1+D$26)^9+CashFlow!L9/(1+D$26)^10+CashFlow!L9*(1+$A31)/(D$26-$A31)/(1+D$26)^10</f>
+        <v/>
+      </c>
+      <c r="E31" s="58">
+        <f>CashFlow!C9/(1+E$26)^1+CashFlow!D9/(1+E$26)^2+CashFlow!E9/(1+E$26)^3+CashFlow!F9/(1+E$26)^4+CashFlow!G9/(1+E$26)^5+CashFlow!H9/(1+E$26)^6+CashFlow!I9/(1+E$26)^7+CashFlow!J9/(1+E$26)^8+CashFlow!K9/(1+E$26)^9+CashFlow!L9/(1+E$26)^10+CashFlow!L9*(1+$A31)/(E$26-$A31)/(1+E$26)^10</f>
+        <v/>
+      </c>
+      <c r="F31" s="58">
+        <f>CashFlow!C9/(1+F$26)^1+CashFlow!D9/(1+F$26)^2+CashFlow!E9/(1+F$26)^3+CashFlow!F9/(1+F$26)^4+CashFlow!G9/(1+F$26)^5+CashFlow!H9/(1+F$26)^6+CashFlow!I9/(1+F$26)^7+CashFlow!J9/(1+F$26)^8+CashFlow!K9/(1+F$26)^9+CashFlow!L9/(1+F$26)^10+CashFlow!L9*(1+$A31)/(F$26-$A31)/(1+F$26)^10</f>
+        <v/>
+      </c>
+      <c r="G31" s="58">
+        <f>CashFlow!C9/(1+G$26)^1+CashFlow!D9/(1+G$26)^2+CashFlow!E9/(1+G$26)^3+CashFlow!F9/(1+G$26)^4+CashFlow!G9/(1+G$26)^5+CashFlow!H9/(1+G$26)^6+CashFlow!I9/(1+G$26)^7+CashFlow!J9/(1+G$26)^8+CashFlow!K9/(1+G$26)^9+CashFlow!L9/(1+G$26)^10+CashFlow!L9*(1+$A31)/(G$26-$A31)/(1+G$26)^10</f>
+        <v/>
+      </c>
+      <c r="H31" s="58">
+        <f>CashFlow!C9/(1+H$26)^1+CashFlow!D9/(1+H$26)^2+CashFlow!E9/(1+H$26)^3+CashFlow!F9/(1+H$26)^4+CashFlow!G9/(1+H$26)^5+CashFlow!H9/(1+H$26)^6+CashFlow!I9/(1+H$26)^7+CashFlow!J9/(1+H$26)^8+CashFlow!K9/(1+H$26)^9+CashFlow!L9/(1+H$26)^10+CashFlow!L9*(1+$A31)/(H$26-$A31)/(1+H$26)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="59" t="inlineStr">
+        <is>
+          <t>Both axes are live inputs: edit a WACC header or a growth label and the grid recomputes.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2381,7 +2404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2790,43 +2813,43 @@
           <t>FTE</t>
         </is>
       </c>
-      <c r="C12" s="58">
+      <c r="C12" s="60">
         <f>SUM(C5:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="60">
         <f>SUM(D5:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="58">
+      <c r="E12" s="60">
         <f>SUM(E5:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="58">
+      <c r="F12" s="60">
         <f>SUM(F5:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="58">
+      <c r="G12" s="60">
         <f>SUM(G5:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="58">
+      <c r="H12" s="60">
         <f>SUM(H5:H11)</f>
         <v/>
       </c>
-      <c r="I12" s="58">
+      <c r="I12" s="60">
         <f>SUM(I5:I11)</f>
         <v/>
       </c>
-      <c r="J12" s="58">
+      <c r="J12" s="60">
         <f>SUM(J5:J11)</f>
         <v/>
       </c>
-      <c r="K12" s="58">
+      <c r="K12" s="60">
         <f>SUM(K5:K11)</f>
         <v/>
       </c>
-      <c r="L12" s="58">
+      <c r="L12" s="60">
         <f>SUM(L5:L11)</f>
         <v/>
       </c>
@@ -2894,43 +2917,43 @@
           <t>must be zero</t>
         </is>
       </c>
-      <c r="C14" s="59">
+      <c r="C14" s="61">
         <f>ROUND(C12-C13,3)</f>
         <v/>
       </c>
-      <c r="D14" s="59">
+      <c r="D14" s="61">
         <f>ROUND(D12-D13,3)</f>
         <v/>
       </c>
-      <c r="E14" s="59">
+      <c r="E14" s="61">
         <f>ROUND(E12-E13,3)</f>
         <v/>
       </c>
-      <c r="F14" s="59">
+      <c r="F14" s="61">
         <f>ROUND(F12-F13,3)</f>
         <v/>
       </c>
-      <c r="G14" s="59">
+      <c r="G14" s="61">
         <f>ROUND(G12-G13,3)</f>
         <v/>
       </c>
-      <c r="H14" s="59">
+      <c r="H14" s="61">
         <f>ROUND(H12-H13,3)</f>
         <v/>
       </c>
-      <c r="I14" s="59">
+      <c r="I14" s="61">
         <f>ROUND(I12-I13,3)</f>
         <v/>
       </c>
-      <c r="J14" s="59">
+      <c r="J14" s="61">
         <f>ROUND(J12-J13,3)</f>
         <v/>
       </c>
-      <c r="K14" s="59">
+      <c r="K14" s="61">
         <f>ROUND(K12-K13,3)</f>
         <v/>
       </c>
-      <c r="L14" s="59">
+      <c r="L14" s="61">
         <f>ROUND(L12-L13,3)</f>
         <v/>
       </c>
@@ -2998,59 +3021,29 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Founder / CEO: loaded</t>
+          <t>GROSS SALARY BY ROLE</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C18" s="50">
-        <f>C5*45000*(1+C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="50">
-        <f>D5*45000*(1+D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="50">
-        <f>E5*45000*(1+E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="50">
-        <f>F5*45000*(1+F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="50">
-        <f>G5*45000*(1+G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="50">
-        <f>H5*45000*(1+H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="50">
-        <f>I5*45000*(1+I17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="50">
-        <f>J5*45000*(1+J17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="50">
-        <f>K5*45000*(1+K17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="50">
-        <f>L5*45000*(1+L17)</f>
-        <v/>
-      </c>
+          <t>EUR, before employer SS</t>
+        </is>
+      </c>
+      <c r="C18" s="50" t="n"/>
+      <c r="D18" s="50" t="n"/>
+      <c r="E18" s="50" t="n"/>
+      <c r="F18" s="50" t="n"/>
+      <c r="G18" s="50" t="n"/>
+      <c r="H18" s="50" t="n"/>
+      <c r="I18" s="50" t="n"/>
+      <c r="J18" s="50" t="n"/>
+      <c r="K18" s="50" t="n"/>
+      <c r="L18" s="50" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Engineering: loaded</t>
+          <t xml:space="preserve">  Founder / CEO</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
@@ -3058,51 +3051,50 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C19" s="50">
-        <f>C6*55000*(1+C17)</f>
-        <v/>
-      </c>
-      <c r="D19" s="50">
-        <f>D6*55000*(1+D17)</f>
-        <v/>
-      </c>
-      <c r="E19" s="50">
-        <f>E6*55000*(1+E17)</f>
-        <v/>
-      </c>
-      <c r="F19" s="50">
-        <f>F6*55000*(1+F17)</f>
-        <v/>
-      </c>
-      <c r="G19" s="50">
-        <f>G6*55000*(1+G17)</f>
-        <v/>
-      </c>
-      <c r="H19" s="50">
-        <f>H6*55000*(1+H17)</f>
-        <v/>
-      </c>
-      <c r="I19" s="50">
-        <f>I6*55000*(1+I17)</f>
-        <v/>
-      </c>
-      <c r="J19" s="50">
-        <f>J6*55000*(1+J17)</f>
-        <v/>
-      </c>
-      <c r="K19" s="50">
-        <f>K6*55000*(1+K17)</f>
-        <v/>
-      </c>
-      <c r="L19" s="50">
-        <f>L6*55000*(1+L17)</f>
+      <c r="C19" s="62" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D19" s="32">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="32">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="F19" s="32">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="G19" s="32">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="H19" s="32">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="I19" s="32">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="J19" s="32">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="K19" s="32">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="L19" s="32">
+        <f>C19</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>BD / partnerships: loaded</t>
+          <t xml:space="preserve">  Engineering</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
@@ -3110,51 +3102,50 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C20" s="50">
-        <f>C7*38000*(1+C17)</f>
-        <v/>
-      </c>
-      <c r="D20" s="50">
-        <f>D7*38000*(1+D17)</f>
-        <v/>
-      </c>
-      <c r="E20" s="50">
-        <f>E7*38000*(1+E17)</f>
-        <v/>
-      </c>
-      <c r="F20" s="50">
-        <f>F7*38000*(1+F17)</f>
-        <v/>
-      </c>
-      <c r="G20" s="50">
-        <f>G7*38000*(1+G17)</f>
-        <v/>
-      </c>
-      <c r="H20" s="50">
-        <f>H7*38000*(1+H17)</f>
-        <v/>
-      </c>
-      <c r="I20" s="50">
-        <f>I7*38000*(1+I17)</f>
-        <v/>
-      </c>
-      <c r="J20" s="50">
-        <f>J7*38000*(1+J17)</f>
-        <v/>
-      </c>
-      <c r="K20" s="50">
-        <f>K7*38000*(1+K17)</f>
-        <v/>
-      </c>
-      <c r="L20" s="50">
-        <f>L7*38000*(1+L17)</f>
+      <c r="C20" s="62" t="n">
+        <v>55000</v>
+      </c>
+      <c r="D20" s="32">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="32">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="F20" s="32">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="G20" s="32">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="H20" s="32">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="I20" s="32">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="J20" s="32">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="K20" s="32">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="L20" s="32">
+        <f>C20</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Athlete success: loaded</t>
+          <t xml:space="preserve">  BD / partnerships</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
@@ -3162,51 +3153,50 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C21" s="50">
-        <f>C8*30000*(1+C17)</f>
-        <v/>
-      </c>
-      <c r="D21" s="50">
-        <f>D8*30000*(1+D17)</f>
-        <v/>
-      </c>
-      <c r="E21" s="50">
-        <f>E8*30000*(1+E17)</f>
-        <v/>
-      </c>
-      <c r="F21" s="50">
-        <f>F8*30000*(1+F17)</f>
-        <v/>
-      </c>
-      <c r="G21" s="50">
-        <f>G8*30000*(1+G17)</f>
-        <v/>
-      </c>
-      <c r="H21" s="50">
-        <f>H8*30000*(1+H17)</f>
-        <v/>
-      </c>
-      <c r="I21" s="50">
-        <f>I8*30000*(1+I17)</f>
-        <v/>
-      </c>
-      <c r="J21" s="50">
-        <f>J8*30000*(1+J17)</f>
-        <v/>
-      </c>
-      <c r="K21" s="50">
-        <f>K8*30000*(1+K17)</f>
-        <v/>
-      </c>
-      <c r="L21" s="50">
-        <f>L8*30000*(1+L17)</f>
+      <c r="C21" s="62" t="n">
+        <v>38000</v>
+      </c>
+      <c r="D21" s="32">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="32">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="F21" s="32">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="G21" s="32">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="H21" s="32">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="I21" s="32">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="J21" s="32">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="K21" s="32">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="L21" s="32">
+        <f>C21</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Trust &amp; safety / review: loaded</t>
+          <t xml:space="preserve">  Athlete success</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
@@ -3214,51 +3204,50 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C22" s="50">
-        <f>C9*34000*(1+C17)</f>
-        <v/>
-      </c>
-      <c r="D22" s="50">
-        <f>D9*34000*(1+D17)</f>
-        <v/>
-      </c>
-      <c r="E22" s="50">
-        <f>E9*34000*(1+E17)</f>
-        <v/>
-      </c>
-      <c r="F22" s="50">
-        <f>F9*34000*(1+F17)</f>
-        <v/>
-      </c>
-      <c r="G22" s="50">
-        <f>G9*34000*(1+G17)</f>
-        <v/>
-      </c>
-      <c r="H22" s="50">
-        <f>H9*34000*(1+H17)</f>
-        <v/>
-      </c>
-      <c r="I22" s="50">
-        <f>I9*34000*(1+I17)</f>
-        <v/>
-      </c>
-      <c r="J22" s="50">
-        <f>J9*34000*(1+J17)</f>
-        <v/>
-      </c>
-      <c r="K22" s="50">
-        <f>K9*34000*(1+K17)</f>
-        <v/>
-      </c>
-      <c r="L22" s="50">
-        <f>L9*34000*(1+L17)</f>
+      <c r="C22" s="62" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D22" s="32">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="32">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="F22" s="32">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="G22" s="32">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="H22" s="32">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="I22" s="32">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="J22" s="32">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="K22" s="32">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="L22" s="32">
+        <f>C22</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Finance / operations: loaded</t>
+          <t xml:space="preserve">  Trust &amp; safety / review</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
@@ -3266,51 +3255,50 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C23" s="50">
-        <f>C10*42000*(1+C17)</f>
-        <v/>
-      </c>
-      <c r="D23" s="50">
-        <f>D10*42000*(1+D17)</f>
-        <v/>
-      </c>
-      <c r="E23" s="50">
-        <f>E10*42000*(1+E17)</f>
-        <v/>
-      </c>
-      <c r="F23" s="50">
-        <f>F10*42000*(1+F17)</f>
-        <v/>
-      </c>
-      <c r="G23" s="50">
-        <f>G10*42000*(1+G17)</f>
-        <v/>
-      </c>
-      <c r="H23" s="50">
-        <f>H10*42000*(1+H17)</f>
-        <v/>
-      </c>
-      <c r="I23" s="50">
-        <f>I10*42000*(1+I17)</f>
-        <v/>
-      </c>
-      <c r="J23" s="50">
-        <f>J10*42000*(1+J17)</f>
-        <v/>
-      </c>
-      <c r="K23" s="50">
-        <f>K10*42000*(1+K17)</f>
-        <v/>
-      </c>
-      <c r="L23" s="50">
-        <f>L10*42000*(1+L17)</f>
+      <c r="C23" s="62" t="n">
+        <v>34000</v>
+      </c>
+      <c r="D23" s="32">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="32">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="F23" s="32">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="G23" s="32">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="H23" s="32">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="I23" s="32">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="J23" s="32">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="K23" s="32">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="L23" s="32">
+        <f>C23</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Data protection officer: loaded</t>
+          <t xml:space="preserve">  Finance / operations</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
@@ -3318,207 +3306,153 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C24" s="50">
-        <f>C11*60000*(1+C17)</f>
-        <v/>
-      </c>
-      <c r="D24" s="50">
-        <f>D11*60000*(1+D17)</f>
-        <v/>
-      </c>
-      <c r="E24" s="50">
-        <f>E11*60000*(1+E17)</f>
-        <v/>
-      </c>
-      <c r="F24" s="50">
-        <f>F11*60000*(1+F17)</f>
-        <v/>
-      </c>
-      <c r="G24" s="50">
-        <f>G11*60000*(1+G17)</f>
-        <v/>
-      </c>
-      <c r="H24" s="50">
-        <f>H11*60000*(1+H17)</f>
-        <v/>
-      </c>
-      <c r="I24" s="50">
-        <f>I11*60000*(1+I17)</f>
-        <v/>
-      </c>
-      <c r="J24" s="50">
-        <f>J11*60000*(1+J17)</f>
-        <v/>
-      </c>
-      <c r="K24" s="50">
-        <f>K11*60000*(1+K17)</f>
-        <v/>
-      </c>
-      <c r="L24" s="50">
-        <f>L11*60000*(1+L17)</f>
+      <c r="C24" s="62" t="n">
+        <v>42000</v>
+      </c>
+      <c r="D24" s="32">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="32">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="F24" s="32">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="G24" s="32">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="H24" s="32">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="I24" s="32">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="J24" s="32">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="K24" s="32">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="L24" s="32">
+        <f>C24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="48" t="inlineStr">
-        <is>
-          <t>TOTAL, role build-up</t>
-        </is>
-      </c>
-      <c r="B25" s="41" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Data protection officer</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="C25" s="49">
-        <f>SUM(C18:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="49">
-        <f>SUM(D18:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="49">
-        <f>SUM(E18:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="49">
-        <f>SUM(F18:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="49">
-        <f>SUM(G18:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="49">
-        <f>SUM(H18:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="49">
-        <f>SUM(I18:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="49">
-        <f>SUM(J18:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="49">
-        <f>SUM(K18:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="49">
-        <f>SUM(L18:L24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>People cost in the model</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Costs</t>
-        </is>
-      </c>
-      <c r="C26" s="32">
-        <f>Costs!C17</f>
-        <v/>
-      </c>
-      <c r="D26" s="32">
-        <f>Costs!D17</f>
-        <v/>
-      </c>
-      <c r="E26" s="32">
-        <f>Costs!E17</f>
-        <v/>
-      </c>
-      <c r="F26" s="32">
-        <f>Costs!F17</f>
-        <v/>
-      </c>
-      <c r="G26" s="32">
-        <f>Costs!G17</f>
-        <v/>
-      </c>
-      <c r="H26" s="32">
-        <f>Costs!H17</f>
-        <v/>
-      </c>
-      <c r="I26" s="32">
-        <f>Costs!I17</f>
-        <v/>
-      </c>
-      <c r="J26" s="32">
-        <f>Costs!J17</f>
-        <v/>
-      </c>
-      <c r="K26" s="32">
-        <f>Costs!K17</f>
-        <v/>
-      </c>
-      <c r="L26" s="32">
-        <f>Costs!L17</f>
+      <c r="C25" s="62" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D25" s="32">
+        <f>C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="32">
+        <f>C25</f>
+        <v/>
+      </c>
+      <c r="F25" s="32">
+        <f>C25</f>
+        <v/>
+      </c>
+      <c r="G25" s="32">
+        <f>C25</f>
+        <v/>
+      </c>
+      <c r="H25" s="32">
+        <f>C25</f>
+        <v/>
+      </c>
+      <c r="I25" s="32">
+        <f>C25</f>
+        <v/>
+      </c>
+      <c r="J25" s="32">
+        <f>C25</f>
+        <v/>
+      </c>
+      <c r="K25" s="32">
+        <f>C25</f>
+        <v/>
+      </c>
+      <c r="L25" s="32">
+        <f>C25</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Difference: role mix</t>
+          <t>Founder / CEO: loaded</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>build-up less model</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="C27" s="50">
-        <f>C25-C26</f>
+        <f>C5*C$19*(1+C17)</f>
         <v/>
       </c>
       <c r="D27" s="50">
-        <f>D25-D26</f>
+        <f>D5*D$19*(1+D17)</f>
         <v/>
       </c>
       <c r="E27" s="50">
-        <f>E25-E26</f>
+        <f>E5*E$19*(1+E17)</f>
         <v/>
       </c>
       <c r="F27" s="50">
-        <f>F25-F26</f>
+        <f>F5*F$19*(1+F17)</f>
         <v/>
       </c>
       <c r="G27" s="50">
-        <f>G25-G26</f>
+        <f>G5*G$19*(1+G17)</f>
         <v/>
       </c>
       <c r="H27" s="50">
-        <f>H25-H26</f>
+        <f>H5*H$19*(1+H17)</f>
         <v/>
       </c>
       <c r="I27" s="50">
-        <f>I25-I26</f>
+        <f>I5*I$19*(1+I17)</f>
         <v/>
       </c>
       <c r="J27" s="50">
-        <f>J25-J26</f>
+        <f>J5*J$19*(1+J17)</f>
         <v/>
       </c>
       <c r="K27" s="50">
-        <f>K25-K26</f>
+        <f>K5*K$19*(1+K17)</f>
         <v/>
       </c>
       <c r="L27" s="50">
-        <f>L25-L26</f>
+        <f>L5*L$19*(1+L17)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  memo: build-up per FTE</t>
+          <t>Engineering: loaded</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
@@ -3526,101 +3460,569 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C28" s="60">
-        <f>IF(C12=0,0,C25/C12)</f>
-        <v/>
-      </c>
-      <c r="D28" s="60">
-        <f>IF(D12=0,0,D25/D12)</f>
-        <v/>
-      </c>
-      <c r="E28" s="60">
-        <f>IF(E12=0,0,E25/E12)</f>
-        <v/>
-      </c>
-      <c r="F28" s="60">
-        <f>IF(F12=0,0,F25/F12)</f>
-        <v/>
-      </c>
-      <c r="G28" s="60">
-        <f>IF(G12=0,0,G25/G12)</f>
-        <v/>
-      </c>
-      <c r="H28" s="60">
-        <f>IF(H12=0,0,H25/H12)</f>
-        <v/>
-      </c>
-      <c r="I28" s="60">
-        <f>IF(I12=0,0,I25/I12)</f>
-        <v/>
-      </c>
-      <c r="J28" s="60">
-        <f>IF(J12=0,0,J25/J12)</f>
-        <v/>
-      </c>
-      <c r="K28" s="60">
-        <f>IF(K12=0,0,K25/K12)</f>
-        <v/>
-      </c>
-      <c r="L28" s="60">
-        <f>IF(L12=0,0,L25/L12)</f>
+      <c r="C28" s="50">
+        <f>C6*C$20*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D28" s="50">
+        <f>D6*D$20*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E28" s="50">
+        <f>E6*E$20*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F28" s="50">
+        <f>F6*F$20*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G28" s="50">
+        <f>G6*G$20*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H28" s="50">
+        <f>H6*H$20*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I28" s="50">
+        <f>I6*I$20*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J28" s="50">
+        <f>J6*J$20*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K28" s="50">
+        <f>K6*K$20*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L28" s="50">
+        <f>L6*L$20*(1+L17)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
+          <t>BD / partnerships: loaded</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C29" s="50">
+        <f>C7*C$21*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D29" s="50">
+        <f>D7*D$21*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E29" s="50">
+        <f>E7*E$21*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F29" s="50">
+        <f>F7*F$21*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G29" s="50">
+        <f>G7*G$21*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H29" s="50">
+        <f>H7*H$21*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I29" s="50">
+        <f>I7*I$21*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J29" s="50">
+        <f>J7*J$21*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K29" s="50">
+        <f>K7*K$21*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L29" s="50">
+        <f>L7*L$21*(1+L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Athlete success: loaded</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C30" s="50">
+        <f>C8*C$22*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D30" s="50">
+        <f>D8*D$22*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E30" s="50">
+        <f>E8*E$22*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F30" s="50">
+        <f>F8*F$22*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G30" s="50">
+        <f>G8*G$22*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H30" s="50">
+        <f>H8*H$22*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I30" s="50">
+        <f>I8*I$22*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J30" s="50">
+        <f>J8*J$22*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K30" s="50">
+        <f>K8*K$22*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L30" s="50">
+        <f>L8*L$22*(1+L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Trust &amp; safety / review: loaded</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C31" s="50">
+        <f>C9*C$23*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D31" s="50">
+        <f>D9*D$23*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E31" s="50">
+        <f>E9*E$23*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F31" s="50">
+        <f>F9*F$23*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G31" s="50">
+        <f>G9*G$23*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H31" s="50">
+        <f>H9*H$23*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I31" s="50">
+        <f>I9*I$23*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J31" s="50">
+        <f>J9*J$23*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K31" s="50">
+        <f>K9*K$23*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L31" s="50">
+        <f>L9*L$23*(1+L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Finance / operations: loaded</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C32" s="50">
+        <f>C10*C$24*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D32" s="50">
+        <f>D10*D$24*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E32" s="50">
+        <f>E10*E$24*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F32" s="50">
+        <f>F10*F$24*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G32" s="50">
+        <f>G10*G$24*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H32" s="50">
+        <f>H10*H$24*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I32" s="50">
+        <f>I10*I$24*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J32" s="50">
+        <f>J10*J$24*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K32" s="50">
+        <f>K10*K$24*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L32" s="50">
+        <f>L10*L$24*(1+L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>Data protection officer: loaded</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C33" s="50">
+        <f>C11*C$25*(1+C17)</f>
+        <v/>
+      </c>
+      <c r="D33" s="50">
+        <f>D11*D$25*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E33" s="50">
+        <f>E11*E$25*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F33" s="50">
+        <f>F11*F$25*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G33" s="50">
+        <f>G11*G$25*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H33" s="50">
+        <f>H11*H$25*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I33" s="50">
+        <f>I11*I$25*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J33" s="50">
+        <f>J11*J$25*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K33" s="50">
+        <f>K11*K$25*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L33" s="50">
+        <f>L11*L$25*(1+L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL, role build-up</t>
+        </is>
+      </c>
+      <c r="B34" s="41" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C34" s="49">
+        <f>SUM(C27:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="49">
+        <f>SUM(D27:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="49">
+        <f>SUM(E27:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="49">
+        <f>SUM(F27:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="49">
+        <f>SUM(G27:G33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="49">
+        <f>SUM(H27:H33)</f>
+        <v/>
+      </c>
+      <c r="I34" s="49">
+        <f>SUM(I27:I33)</f>
+        <v/>
+      </c>
+      <c r="J34" s="49">
+        <f>SUM(J27:J33)</f>
+        <v/>
+      </c>
+      <c r="K34" s="49">
+        <f>SUM(K27:K33)</f>
+        <v/>
+      </c>
+      <c r="L34" s="49">
+        <f>SUM(L27:L33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>People cost in the model</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="C35" s="32">
+        <f>Costs!C17</f>
+        <v/>
+      </c>
+      <c r="D35" s="32">
+        <f>Costs!D17</f>
+        <v/>
+      </c>
+      <c r="E35" s="32">
+        <f>Costs!E17</f>
+        <v/>
+      </c>
+      <c r="F35" s="32">
+        <f>Costs!F17</f>
+        <v/>
+      </c>
+      <c r="G35" s="32">
+        <f>Costs!G17</f>
+        <v/>
+      </c>
+      <c r="H35" s="32">
+        <f>Costs!H17</f>
+        <v/>
+      </c>
+      <c r="I35" s="32">
+        <f>Costs!I17</f>
+        <v/>
+      </c>
+      <c r="J35" s="32">
+        <f>Costs!J17</f>
+        <v/>
+      </c>
+      <c r="K35" s="32">
+        <f>Costs!K17</f>
+        <v/>
+      </c>
+      <c r="L35" s="32">
+        <f>Costs!L17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>Difference: role mix</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>build-up less model</t>
+        </is>
+      </c>
+      <c r="C36" s="50">
+        <f>C34-C35</f>
+        <v/>
+      </c>
+      <c r="D36" s="50">
+        <f>D34-D35</f>
+        <v/>
+      </c>
+      <c r="E36" s="50">
+        <f>E34-E35</f>
+        <v/>
+      </c>
+      <c r="F36" s="50">
+        <f>F34-F35</f>
+        <v/>
+      </c>
+      <c r="G36" s="50">
+        <f>G34-G35</f>
+        <v/>
+      </c>
+      <c r="H36" s="50">
+        <f>H34-H35</f>
+        <v/>
+      </c>
+      <c r="I36" s="50">
+        <f>I34-I35</f>
+        <v/>
+      </c>
+      <c r="J36" s="50">
+        <f>J34-J35</f>
+        <v/>
+      </c>
+      <c r="K36" s="50">
+        <f>K34-K35</f>
+        <v/>
+      </c>
+      <c r="L36" s="50">
+        <f>L34-L35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: build-up per FTE</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C37" s="63">
+        <f>IF(C12=0,0,C34/C12)</f>
+        <v/>
+      </c>
+      <c r="D37" s="63">
+        <f>IF(D12=0,0,D34/D12)</f>
+        <v/>
+      </c>
+      <c r="E37" s="63">
+        <f>IF(E12=0,0,E34/E12)</f>
+        <v/>
+      </c>
+      <c r="F37" s="63">
+        <f>IF(F12=0,0,F34/F12)</f>
+        <v/>
+      </c>
+      <c r="G37" s="63">
+        <f>IF(G12=0,0,G34/G12)</f>
+        <v/>
+      </c>
+      <c r="H37" s="63">
+        <f>IF(H12=0,0,H34/H12)</f>
+        <v/>
+      </c>
+      <c r="I37" s="63">
+        <f>IF(I12=0,0,I34/I12)</f>
+        <v/>
+      </c>
+      <c r="J37" s="63">
+        <f>IF(J12=0,0,J34/J12)</f>
+        <v/>
+      </c>
+      <c r="K37" s="63">
+        <f>IF(K12=0,0,K34/K12)</f>
+        <v/>
+      </c>
+      <c r="L37" s="63">
+        <f>IF(L12=0,0,L34/L12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">  memo: model blended per FTE</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="C29" s="32">
+      <c r="C38" s="32">
         <f>Assumptions!C67</f>
         <v/>
       </c>
-      <c r="D29" s="32">
+      <c r="D38" s="32">
         <f>Assumptions!D67</f>
         <v/>
       </c>
-      <c r="E29" s="32">
+      <c r="E38" s="32">
         <f>Assumptions!E67</f>
         <v/>
       </c>
-      <c r="F29" s="32">
+      <c r="F38" s="32">
         <f>Assumptions!F67</f>
         <v/>
       </c>
-      <c r="G29" s="32">
+      <c r="G38" s="32">
         <f>Assumptions!G67</f>
         <v/>
       </c>
-      <c r="H29" s="32">
+      <c r="H38" s="32">
         <f>Assumptions!H67</f>
         <v/>
       </c>
-      <c r="I29" s="32">
+      <c r="I38" s="32">
         <f>Assumptions!I67</f>
         <v/>
       </c>
-      <c r="J29" s="32">
+      <c r="J38" s="32">
         <f>Assumptions!J67</f>
         <v/>
       </c>
-      <c r="K29" s="32">
+      <c r="K38" s="32">
         <f>Assumptions!K67</f>
         <v/>
       </c>
-      <c r="L29" s="32">
+      <c r="L38" s="32">
         <f>Assumptions!L67</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="61" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="64" t="inlineStr">
         <is>
           <t>The FTE block reconciles exactly and is the plan. The cost build-up prices those roles at their own salaries; the model prices the same headcount at a blended loaded average that rises from 38k to 76k over the plan, while the build-up holds today's salaries flat. The two cross over at Y4: the build-up is the higher figure in Y1-Y3, where one founder salary dominates a team of two or three, and the model is higher from Y4 as its blended rate climbs. The model is the one that reaches the P&amp;L either way. The memo rows below make the two rates comparable.</t>
         </is>
@@ -3908,43 +4310,43 @@
           <t>years</t>
         </is>
       </c>
-      <c r="C8" s="62">
+      <c r="C8" s="65">
         <f>IF(C7=0,0,1/C7)</f>
         <v/>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="65">
         <f>IF(D7=0,0,1/D7)</f>
         <v/>
       </c>
-      <c r="E8" s="62">
+      <c r="E8" s="65">
         <f>IF(E7=0,0,1/E7)</f>
         <v/>
       </c>
-      <c r="F8" s="62">
+      <c r="F8" s="65">
         <f>IF(F7=0,0,1/F7)</f>
         <v/>
       </c>
-      <c r="G8" s="62">
+      <c r="G8" s="65">
         <f>IF(G7=0,0,1/G7)</f>
         <v/>
       </c>
-      <c r="H8" s="62">
+      <c r="H8" s="65">
         <f>IF(H7=0,0,1/H7)</f>
         <v/>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="65">
         <f>IF(I7=0,0,1/I7)</f>
         <v/>
       </c>
-      <c r="J8" s="62">
+      <c r="J8" s="65">
         <f>IF(J7=0,0,1/J7)</f>
         <v/>
       </c>
-      <c r="K8" s="62">
+      <c r="K8" s="65">
         <f>IF(K7=0,0,1/K7)</f>
         <v/>
       </c>
-      <c r="L8" s="62">
+      <c r="L8" s="65">
         <f>IF(L7=0,0,1/L7)</f>
         <v/>
       </c>
@@ -4116,43 +4518,43 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C12" s="59">
+      <c r="C12" s="61">
         <f>IF(C6=0,0,C11/C6)</f>
         <v/>
       </c>
-      <c r="D12" s="59">
+      <c r="D12" s="61">
         <f>IF(D6=0,0,D11/D6)</f>
         <v/>
       </c>
-      <c r="E12" s="59">
+      <c r="E12" s="61">
         <f>IF(E6=0,0,E11/E6)</f>
         <v/>
       </c>
-      <c r="F12" s="59">
+      <c r="F12" s="61">
         <f>IF(F6=0,0,F11/F6)</f>
         <v/>
       </c>
-      <c r="G12" s="59">
+      <c r="G12" s="61">
         <f>IF(G6=0,0,G11/G6)</f>
         <v/>
       </c>
-      <c r="H12" s="59">
+      <c r="H12" s="61">
         <f>IF(H6=0,0,H11/H6)</f>
         <v/>
       </c>
-      <c r="I12" s="59">
+      <c r="I12" s="61">
         <f>IF(I6=0,0,I11/I6)</f>
         <v/>
       </c>
-      <c r="J12" s="59">
+      <c r="J12" s="61">
         <f>IF(J6=0,0,J11/J6)</f>
         <v/>
       </c>
-      <c r="K12" s="59">
+      <c r="K12" s="61">
         <f>IF(K6=0,0,K11/K6)</f>
         <v/>
       </c>
-      <c r="L12" s="59">
+      <c r="L12" s="61">
         <f>IF(L6=0,0,L11/L6)</f>
         <v/>
       </c>
@@ -4168,49 +4570,49 @@
           <t>months</t>
         </is>
       </c>
-      <c r="C13" s="63">
+      <c r="C13" s="66">
         <f>IF(C10&lt;=0,0,12*C6/C10)</f>
         <v/>
       </c>
-      <c r="D13" s="63">
+      <c r="D13" s="66">
         <f>IF(D10&lt;=0,0,12*D6/D10)</f>
         <v/>
       </c>
-      <c r="E13" s="63">
+      <c r="E13" s="66">
         <f>IF(E10&lt;=0,0,12*E6/E10)</f>
         <v/>
       </c>
-      <c r="F13" s="63">
+      <c r="F13" s="66">
         <f>IF(F10&lt;=0,0,12*F6/F10)</f>
         <v/>
       </c>
-      <c r="G13" s="63">
+      <c r="G13" s="66">
         <f>IF(G10&lt;=0,0,12*G6/G10)</f>
         <v/>
       </c>
-      <c r="H13" s="63">
+      <c r="H13" s="66">
         <f>IF(H10&lt;=0,0,12*H6/H10)</f>
         <v/>
       </c>
-      <c r="I13" s="63">
+      <c r="I13" s="66">
         <f>IF(I10&lt;=0,0,12*I6/I10)</f>
         <v/>
       </c>
-      <c r="J13" s="63">
+      <c r="J13" s="66">
         <f>IF(J10&lt;=0,0,12*J6/J10)</f>
         <v/>
       </c>
-      <c r="K13" s="63">
+      <c r="K13" s="66">
         <f>IF(K10&lt;=0,0,12*K6/K10)</f>
         <v/>
       </c>
-      <c r="L13" s="63">
+      <c r="L13" s="66">
         <f>IF(L10&lt;=0,0,12*L6/L10)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="61" t="inlineStr">
+      <c r="A15" s="64" t="inlineStr">
         <is>
           <t>The athlete LTV/CAC ratio is unusually high, and that is the thesis rather than an error: acquisition is cheap precisely because there is no incumbent agent to outbid in these sports. It should be read alongside the fan LTV below, which is small: the economics work on volume of athletes, not on the value of any one of them.</t>
         </is>
@@ -4224,7 +4626,7 @@
       </c>
       <c r="B18" s="14" t="n"/>
       <c r="C18" s="14" t="n"/>
-      <c r="D18" s="64" t="inlineStr">
+      <c r="D18" s="67" t="inlineStr">
         <is>
           <t>excludes PPV and tips, which the revenue model carries separately</t>
         </is>
@@ -4509,43 +4911,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C24" s="65">
+      <c r="C24" s="68">
         <f>C21-C22-C23</f>
         <v/>
       </c>
-      <c r="D24" s="65">
+      <c r="D24" s="68">
         <f>D21-D22-D23</f>
         <v/>
       </c>
-      <c r="E24" s="65">
+      <c r="E24" s="68">
         <f>E21-E22-E23</f>
         <v/>
       </c>
-      <c r="F24" s="65">
+      <c r="F24" s="68">
         <f>F21-F22-F23</f>
         <v/>
       </c>
-      <c r="G24" s="65">
+      <c r="G24" s="68">
         <f>G21-G22-G23</f>
         <v/>
       </c>
-      <c r="H24" s="65">
+      <c r="H24" s="68">
         <f>H21-H22-H23</f>
         <v/>
       </c>
-      <c r="I24" s="65">
+      <c r="I24" s="68">
         <f>I21-I22-I23</f>
         <v/>
       </c>
-      <c r="J24" s="65">
+      <c r="J24" s="68">
         <f>J21-J22-J23</f>
         <v/>
       </c>
-      <c r="K24" s="65">
+      <c r="K24" s="68">
         <f>K21-K22-K23</f>
         <v/>
       </c>
-      <c r="L24" s="65">
+      <c r="L24" s="68">
         <f>L21-L22-L23</f>
         <v/>
       </c>
@@ -4613,43 +5015,43 @@
           <t>months</t>
         </is>
       </c>
-      <c r="C26" s="63">
+      <c r="C26" s="66">
         <f>IF(C25=0,0,1/C25)</f>
         <v/>
       </c>
-      <c r="D26" s="63">
+      <c r="D26" s="66">
         <f>IF(D25=0,0,1/D25)</f>
         <v/>
       </c>
-      <c r="E26" s="63">
+      <c r="E26" s="66">
         <f>IF(E25=0,0,1/E25)</f>
         <v/>
       </c>
-      <c r="F26" s="63">
+      <c r="F26" s="66">
         <f>IF(F25=0,0,1/F25)</f>
         <v/>
       </c>
-      <c r="G26" s="63">
+      <c r="G26" s="66">
         <f>IF(G25=0,0,1/G25)</f>
         <v/>
       </c>
-      <c r="H26" s="63">
+      <c r="H26" s="66">
         <f>IF(H25=0,0,1/H25)</f>
         <v/>
       </c>
-      <c r="I26" s="63">
+      <c r="I26" s="66">
         <f>IF(I25=0,0,1/I25)</f>
         <v/>
       </c>
-      <c r="J26" s="63">
+      <c r="J26" s="66">
         <f>IF(J25=0,0,1/J25)</f>
         <v/>
       </c>
-      <c r="K26" s="63">
+      <c r="K26" s="66">
         <f>IF(K25=0,0,1/K25)</f>
         <v/>
       </c>
-      <c r="L26" s="63">
+      <c r="L26" s="66">
         <f>IF(L25=0,0,1/L25)</f>
         <v/>
       </c>
@@ -4665,43 +5067,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C27" s="66">
+      <c r="C27" s="69">
         <f>C24*C26</f>
         <v/>
       </c>
-      <c r="D27" s="66">
+      <c r="D27" s="69">
         <f>D24*D26</f>
         <v/>
       </c>
-      <c r="E27" s="66">
+      <c r="E27" s="69">
         <f>E24*E26</f>
         <v/>
       </c>
-      <c r="F27" s="66">
+      <c r="F27" s="69">
         <f>F24*F26</f>
         <v/>
       </c>
-      <c r="G27" s="66">
+      <c r="G27" s="69">
         <f>G24*G26</f>
         <v/>
       </c>
-      <c r="H27" s="66">
+      <c r="H27" s="69">
         <f>H24*H26</f>
         <v/>
       </c>
-      <c r="I27" s="66">
+      <c r="I27" s="69">
         <f>I24*I26</f>
         <v/>
       </c>
-      <c r="J27" s="66">
+      <c r="J27" s="69">
         <f>J24*J26</f>
         <v/>
       </c>
-      <c r="K27" s="66">
+      <c r="K27" s="69">
         <f>K24*K26</f>
         <v/>
       </c>
-      <c r="L27" s="66">
+      <c r="L27" s="69">
         <f>L24*L26</f>
         <v/>
       </c>
@@ -4749,7 +5151,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="61" t="inlineStr">
+      <c r="A30" s="64" t="inlineStr">
         <is>
           <t>Fan CAC is zero by construction: athletes bring their own audiences and the model spends nothing acquiring fans. That understates the risk rather than flattering the return, and the plan discloses it as such.</t>
         </is>
@@ -5044,49 +5446,49 @@
           <t>months</t>
         </is>
       </c>
-      <c r="C38" s="58">
+      <c r="C38" s="60">
         <f>IF(C37&lt;=0,0,12*C33/C37)</f>
         <v/>
       </c>
-      <c r="D38" s="58">
+      <c r="D38" s="60">
         <f>IF(D37&lt;=0,0,12*D33/D37)</f>
         <v/>
       </c>
-      <c r="E38" s="58">
+      <c r="E38" s="60">
         <f>IF(E37&lt;=0,0,12*E33/E37)</f>
         <v/>
       </c>
-      <c r="F38" s="58">
+      <c r="F38" s="60">
         <f>IF(F37&lt;=0,0,12*F33/F37)</f>
         <v/>
       </c>
-      <c r="G38" s="58">
+      <c r="G38" s="60">
         <f>IF(G37&lt;=0,0,12*G33/G37)</f>
         <v/>
       </c>
-      <c r="H38" s="58">
+      <c r="H38" s="60">
         <f>IF(H37&lt;=0,0,12*H33/H37)</f>
         <v/>
       </c>
-      <c r="I38" s="58">
+      <c r="I38" s="60">
         <f>IF(I37&lt;=0,0,12*I33/I37)</f>
         <v/>
       </c>
-      <c r="J38" s="58">
+      <c r="J38" s="60">
         <f>IF(J37&lt;=0,0,12*J33/J37)</f>
         <v/>
       </c>
-      <c r="K38" s="58">
+      <c r="K38" s="60">
         <f>IF(K37&lt;=0,0,12*K33/K37)</f>
         <v/>
       </c>
-      <c r="L38" s="58">
+      <c r="L38" s="60">
         <f>IF(L37&lt;=0,0,12*L33/L37)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="61" t="inlineStr">
+      <c r="A40" s="64" t="inlineStr">
         <is>
           <t>No sponsor LTV is shown. It needs a sponsor retention assumption the model does not make, and inventing one here would create a figure nothing else in the plan validates. Payback needs no such assumption, so payback is what is reported.</t>
         </is>
@@ -5903,7 +6305,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="70" t="inlineStr">
         <is>
           <t>Each pair is the Python model's figure and the workbook's own calculation. VARIANCE must be zero: if a formula is wrong, it shows up here on open.</t>
         </is>
@@ -6087,43 +6489,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C7" s="68">
+      <c r="C7" s="71">
         <f>ROUND(C6-C5,0)</f>
         <v/>
       </c>
-      <c r="D7" s="68">
+      <c r="D7" s="71">
         <f>ROUND(D6-D5,0)</f>
         <v/>
       </c>
-      <c r="E7" s="68">
+      <c r="E7" s="71">
         <f>ROUND(E6-E5,0)</f>
         <v/>
       </c>
-      <c r="F7" s="68">
+      <c r="F7" s="71">
         <f>ROUND(F6-F5,0)</f>
         <v/>
       </c>
-      <c r="G7" s="68">
+      <c r="G7" s="71">
         <f>ROUND(G6-G5,0)</f>
         <v/>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="71">
         <f>ROUND(H6-H5,0)</f>
         <v/>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="71">
         <f>ROUND(I6-I5,0)</f>
         <v/>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="71">
         <f>ROUND(J6-J5,0)</f>
         <v/>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="71">
         <f>ROUND(K6-K5,0)</f>
         <v/>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="71">
         <f>ROUND(L6-L5,0)</f>
         <v/>
       </c>
@@ -6251,43 +6653,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C12" s="68">
+      <c r="C12" s="71">
         <f>ROUND(C11-C10,0)</f>
         <v/>
       </c>
-      <c r="D12" s="68">
+      <c r="D12" s="71">
         <f>ROUND(D11-D10,0)</f>
         <v/>
       </c>
-      <c r="E12" s="68">
+      <c r="E12" s="71">
         <f>ROUND(E11-E10,0)</f>
         <v/>
       </c>
-      <c r="F12" s="68">
+      <c r="F12" s="71">
         <f>ROUND(F11-F10,0)</f>
         <v/>
       </c>
-      <c r="G12" s="68">
+      <c r="G12" s="71">
         <f>ROUND(G11-G10,0)</f>
         <v/>
       </c>
-      <c r="H12" s="68">
+      <c r="H12" s="71">
         <f>ROUND(H11-H10,0)</f>
         <v/>
       </c>
-      <c r="I12" s="68">
+      <c r="I12" s="71">
         <f>ROUND(I11-I10,0)</f>
         <v/>
       </c>
-      <c r="J12" s="68">
+      <c r="J12" s="71">
         <f>ROUND(J11-J10,0)</f>
         <v/>
       </c>
-      <c r="K12" s="68">
+      <c r="K12" s="71">
         <f>ROUND(K11-K10,0)</f>
         <v/>
       </c>
-      <c r="L12" s="68">
+      <c r="L12" s="71">
         <f>ROUND(L11-L10,0)</f>
         <v/>
       </c>
@@ -6415,43 +6817,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C17" s="68">
+      <c r="C17" s="71">
         <f>ROUND(C16-C15,0)</f>
         <v/>
       </c>
-      <c r="D17" s="68">
+      <c r="D17" s="71">
         <f>ROUND(D16-D15,0)</f>
         <v/>
       </c>
-      <c r="E17" s="68">
+      <c r="E17" s="71">
         <f>ROUND(E16-E15,0)</f>
         <v/>
       </c>
-      <c r="F17" s="68">
+      <c r="F17" s="71">
         <f>ROUND(F16-F15,0)</f>
         <v/>
       </c>
-      <c r="G17" s="68">
+      <c r="G17" s="71">
         <f>ROUND(G16-G15,0)</f>
         <v/>
       </c>
-      <c r="H17" s="68">
+      <c r="H17" s="71">
         <f>ROUND(H16-H15,0)</f>
         <v/>
       </c>
-      <c r="I17" s="68">
+      <c r="I17" s="71">
         <f>ROUND(I16-I15,0)</f>
         <v/>
       </c>
-      <c r="J17" s="68">
+      <c r="J17" s="71">
         <f>ROUND(J16-J15,0)</f>
         <v/>
       </c>
-      <c r="K17" s="68">
+      <c r="K17" s="71">
         <f>ROUND(K16-K15,0)</f>
         <v/>
       </c>
-      <c r="L17" s="68">
+      <c r="L17" s="71">
         <f>ROUND(L16-L15,0)</f>
         <v/>
       </c>
@@ -6579,43 +6981,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C22" s="68">
+      <c r="C22" s="71">
         <f>ROUND(C21-C20,0)</f>
         <v/>
       </c>
-      <c r="D22" s="68">
+      <c r="D22" s="71">
         <f>ROUND(D21-D20,0)</f>
         <v/>
       </c>
-      <c r="E22" s="68">
+      <c r="E22" s="71">
         <f>ROUND(E21-E20,0)</f>
         <v/>
       </c>
-      <c r="F22" s="68">
+      <c r="F22" s="71">
         <f>ROUND(F21-F20,0)</f>
         <v/>
       </c>
-      <c r="G22" s="68">
+      <c r="G22" s="71">
         <f>ROUND(G21-G20,0)</f>
         <v/>
       </c>
-      <c r="H22" s="68">
+      <c r="H22" s="71">
         <f>ROUND(H21-H20,0)</f>
         <v/>
       </c>
-      <c r="I22" s="68">
+      <c r="I22" s="71">
         <f>ROUND(I21-I20,0)</f>
         <v/>
       </c>
-      <c r="J22" s="68">
+      <c r="J22" s="71">
         <f>ROUND(J21-J20,0)</f>
         <v/>
       </c>
-      <c r="K22" s="68">
+      <c r="K22" s="71">
         <f>ROUND(K21-K20,0)</f>
         <v/>
       </c>
-      <c r="L22" s="68">
+      <c r="L22" s="71">
         <f>ROUND(L21-L20,0)</f>
         <v/>
       </c>
@@ -6743,43 +7145,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C27" s="68">
+      <c r="C27" s="71">
         <f>ROUND(C26-C25,0)</f>
         <v/>
       </c>
-      <c r="D27" s="68">
+      <c r="D27" s="71">
         <f>ROUND(D26-D25,0)</f>
         <v/>
       </c>
-      <c r="E27" s="68">
+      <c r="E27" s="71">
         <f>ROUND(E26-E25,0)</f>
         <v/>
       </c>
-      <c r="F27" s="68">
+      <c r="F27" s="71">
         <f>ROUND(F26-F25,0)</f>
         <v/>
       </c>
-      <c r="G27" s="68">
+      <c r="G27" s="71">
         <f>ROUND(G26-G25,0)</f>
         <v/>
       </c>
-      <c r="H27" s="68">
+      <c r="H27" s="71">
         <f>ROUND(H26-H25,0)</f>
         <v/>
       </c>
-      <c r="I27" s="68">
+      <c r="I27" s="71">
         <f>ROUND(I26-I25,0)</f>
         <v/>
       </c>
-      <c r="J27" s="68">
+      <c r="J27" s="71">
         <f>ROUND(J26-J25,0)</f>
         <v/>
       </c>
-      <c r="K27" s="68">
+      <c r="K27" s="71">
         <f>ROUND(K26-K25,0)</f>
         <v/>
       </c>
-      <c r="L27" s="68">
+      <c r="L27" s="71">
         <f>ROUND(L26-L25,0)</f>
         <v/>
       </c>
@@ -6907,43 +7309,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C32" s="69">
+      <c r="C32" s="72">
         <f>ROUND(C31-C30,0)</f>
         <v/>
       </c>
-      <c r="D32" s="69">
+      <c r="D32" s="72">
         <f>ROUND(D31-D30,0)</f>
         <v/>
       </c>
-      <c r="E32" s="69">
+      <c r="E32" s="72">
         <f>ROUND(E31-E30,0)</f>
         <v/>
       </c>
-      <c r="F32" s="69">
+      <c r="F32" s="72">
         <f>ROUND(F31-F30,0)</f>
         <v/>
       </c>
-      <c r="G32" s="69">
+      <c r="G32" s="72">
         <f>ROUND(G31-G30,0)</f>
         <v/>
       </c>
-      <c r="H32" s="69">
+      <c r="H32" s="72">
         <f>ROUND(H31-H30,0)</f>
         <v/>
       </c>
-      <c r="I32" s="69">
+      <c r="I32" s="72">
         <f>ROUND(I31-I30,0)</f>
         <v/>
       </c>
-      <c r="J32" s="69">
+      <c r="J32" s="72">
         <f>ROUND(J31-J30,0)</f>
         <v/>
       </c>
-      <c r="K32" s="69">
+      <c r="K32" s="72">
         <f>ROUND(K31-K30,0)</f>
         <v/>
       </c>
-      <c r="L32" s="69">
+      <c r="L32" s="72">
         <f>ROUND(L31-L30,0)</f>
         <v/>
       </c>
@@ -7071,43 +7473,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C37" s="69">
+      <c r="C37" s="72">
         <f>ROUND(C36-C35,0)</f>
         <v/>
       </c>
-      <c r="D37" s="69">
+      <c r="D37" s="72">
         <f>ROUND(D36-D35,0)</f>
         <v/>
       </c>
-      <c r="E37" s="69">
+      <c r="E37" s="72">
         <f>ROUND(E36-E35,0)</f>
         <v/>
       </c>
-      <c r="F37" s="69">
+      <c r="F37" s="72">
         <f>ROUND(F36-F35,0)</f>
         <v/>
       </c>
-      <c r="G37" s="69">
+      <c r="G37" s="72">
         <f>ROUND(G36-G35,0)</f>
         <v/>
       </c>
-      <c r="H37" s="69">
+      <c r="H37" s="72">
         <f>ROUND(H36-H35,0)</f>
         <v/>
       </c>
-      <c r="I37" s="69">
+      <c r="I37" s="72">
         <f>ROUND(I36-I35,0)</f>
         <v/>
       </c>
-      <c r="J37" s="69">
+      <c r="J37" s="72">
         <f>ROUND(J36-J35,0)</f>
         <v/>
       </c>
-      <c r="K37" s="69">
+      <c r="K37" s="72">
         <f>ROUND(K36-K35,0)</f>
         <v/>
       </c>
-      <c r="L37" s="69">
+      <c r="L37" s="72">
         <f>ROUND(L36-L35,0)</f>
         <v/>
       </c>
@@ -7235,43 +7637,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C42" s="68">
+      <c r="C42" s="71">
         <f>ROUND(C41-C40,0)</f>
         <v/>
       </c>
-      <c r="D42" s="68">
+      <c r="D42" s="71">
         <f>ROUND(D41-D40,0)</f>
         <v/>
       </c>
-      <c r="E42" s="68">
+      <c r="E42" s="71">
         <f>ROUND(E41-E40,0)</f>
         <v/>
       </c>
-      <c r="F42" s="68">
+      <c r="F42" s="71">
         <f>ROUND(F41-F40,0)</f>
         <v/>
       </c>
-      <c r="G42" s="68">
+      <c r="G42" s="71">
         <f>ROUND(G41-G40,0)</f>
         <v/>
       </c>
-      <c r="H42" s="68">
+      <c r="H42" s="71">
         <f>ROUND(H41-H40,0)</f>
         <v/>
       </c>
-      <c r="I42" s="68">
+      <c r="I42" s="71">
         <f>ROUND(I41-I40,0)</f>
         <v/>
       </c>
-      <c r="J42" s="68">
+      <c r="J42" s="71">
         <f>ROUND(J41-J40,0)</f>
         <v/>
       </c>
-      <c r="K42" s="68">
+      <c r="K42" s="71">
         <f>ROUND(K41-K40,0)</f>
         <v/>
       </c>
-      <c r="L42" s="68">
+      <c r="L42" s="71">
         <f>ROUND(L41-L40,0)</f>
         <v/>
       </c>
@@ -7399,43 +7801,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C47" s="69">
+      <c r="C47" s="72">
         <f>ROUND(C46-C45,0)</f>
         <v/>
       </c>
-      <c r="D47" s="69">
+      <c r="D47" s="72">
         <f>ROUND(D46-D45,0)</f>
         <v/>
       </c>
-      <c r="E47" s="69">
+      <c r="E47" s="72">
         <f>ROUND(E46-E45,0)</f>
         <v/>
       </c>
-      <c r="F47" s="69">
+      <c r="F47" s="72">
         <f>ROUND(F46-F45,0)</f>
         <v/>
       </c>
-      <c r="G47" s="69">
+      <c r="G47" s="72">
         <f>ROUND(G46-G45,0)</f>
         <v/>
       </c>
-      <c r="H47" s="69">
+      <c r="H47" s="72">
         <f>ROUND(H46-H45,0)</f>
         <v/>
       </c>
-      <c r="I47" s="69">
+      <c r="I47" s="72">
         <f>ROUND(I46-I45,0)</f>
         <v/>
       </c>
-      <c r="J47" s="69">
+      <c r="J47" s="72">
         <f>ROUND(J46-J45,0)</f>
         <v/>
       </c>
-      <c r="K47" s="69">
+      <c r="K47" s="72">
         <f>ROUND(K46-K45,0)</f>
         <v/>
       </c>
-      <c r="L47" s="69">
+      <c r="L47" s="72">
         <f>ROUND(L46-L45,0)</f>
         <v/>
       </c>
@@ -7563,43 +7965,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C52" s="69">
+      <c r="C52" s="72">
         <f>ROUND(C51-C50,0)</f>
         <v/>
       </c>
-      <c r="D52" s="69">
+      <c r="D52" s="72">
         <f>ROUND(D51-D50,0)</f>
         <v/>
       </c>
-      <c r="E52" s="69">
+      <c r="E52" s="72">
         <f>ROUND(E51-E50,0)</f>
         <v/>
       </c>
-      <c r="F52" s="69">
+      <c r="F52" s="72">
         <f>ROUND(F51-F50,0)</f>
         <v/>
       </c>
-      <c r="G52" s="69">
+      <c r="G52" s="72">
         <f>ROUND(G51-G50,0)</f>
         <v/>
       </c>
-      <c r="H52" s="69">
+      <c r="H52" s="72">
         <f>ROUND(H51-H50,0)</f>
         <v/>
       </c>
-      <c r="I52" s="69">
+      <c r="I52" s="72">
         <f>ROUND(I51-I50,0)</f>
         <v/>
       </c>
-      <c r="J52" s="69">
+      <c r="J52" s="72">
         <f>ROUND(J51-J50,0)</f>
         <v/>
       </c>
-      <c r="K52" s="69">
+      <c r="K52" s="72">
         <f>ROUND(K51-K50,0)</f>
         <v/>
       </c>
-      <c r="L52" s="69">
+      <c r="L52" s="72">
         <f>ROUND(L51-L50,0)</f>
         <v/>
       </c>
@@ -7727,43 +8129,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C57" s="68">
+      <c r="C57" s="71">
         <f>ROUND(C56-C55,0)</f>
         <v/>
       </c>
-      <c r="D57" s="68">
+      <c r="D57" s="71">
         <f>ROUND(D56-D55,0)</f>
         <v/>
       </c>
-      <c r="E57" s="68">
+      <c r="E57" s="71">
         <f>ROUND(E56-E55,0)</f>
         <v/>
       </c>
-      <c r="F57" s="68">
+      <c r="F57" s="71">
         <f>ROUND(F56-F55,0)</f>
         <v/>
       </c>
-      <c r="G57" s="68">
+      <c r="G57" s="71">
         <f>ROUND(G56-G55,0)</f>
         <v/>
       </c>
-      <c r="H57" s="68">
+      <c r="H57" s="71">
         <f>ROUND(H56-H55,0)</f>
         <v/>
       </c>
-      <c r="I57" s="68">
+      <c r="I57" s="71">
         <f>ROUND(I56-I55,0)</f>
         <v/>
       </c>
-      <c r="J57" s="68">
+      <c r="J57" s="71">
         <f>ROUND(J56-J55,0)</f>
         <v/>
       </c>
-      <c r="K57" s="68">
+      <c r="K57" s="71">
         <f>ROUND(K56-K55,0)</f>
         <v/>
       </c>
-      <c r="L57" s="68">
+      <c r="L57" s="71">
         <f>ROUND(L56-L55,0)</f>
         <v/>
       </c>
@@ -7891,43 +8293,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C62" s="68">
+      <c r="C62" s="71">
         <f>ROUND(C61-C60,0)</f>
         <v/>
       </c>
-      <c r="D62" s="68">
+      <c r="D62" s="71">
         <f>ROUND(D61-D60,0)</f>
         <v/>
       </c>
-      <c r="E62" s="68">
+      <c r="E62" s="71">
         <f>ROUND(E61-E60,0)</f>
         <v/>
       </c>
-      <c r="F62" s="68">
+      <c r="F62" s="71">
         <f>ROUND(F61-F60,0)</f>
         <v/>
       </c>
-      <c r="G62" s="68">
+      <c r="G62" s="71">
         <f>ROUND(G61-G60,0)</f>
         <v/>
       </c>
-      <c r="H62" s="68">
+      <c r="H62" s="71">
         <f>ROUND(H61-H60,0)</f>
         <v/>
       </c>
-      <c r="I62" s="68">
+      <c r="I62" s="71">
         <f>ROUND(I61-I60,0)</f>
         <v/>
       </c>
-      <c r="J62" s="68">
+      <c r="J62" s="71">
         <f>ROUND(J61-J60,0)</f>
         <v/>
       </c>
-      <c r="K62" s="68">
+      <c r="K62" s="71">
         <f>ROUND(K61-K60,0)</f>
         <v/>
       </c>
-      <c r="L62" s="68">
+      <c r="L62" s="71">
         <f>ROUND(L61-L60,0)</f>
         <v/>
       </c>
@@ -8055,43 +8457,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C67" s="68">
+      <c r="C67" s="71">
         <f>ROUND(C66-C65,0)</f>
         <v/>
       </c>
-      <c r="D67" s="68">
+      <c r="D67" s="71">
         <f>ROUND(D66-D65,0)</f>
         <v/>
       </c>
-      <c r="E67" s="68">
+      <c r="E67" s="71">
         <f>ROUND(E66-E65,0)</f>
         <v/>
       </c>
-      <c r="F67" s="68">
+      <c r="F67" s="71">
         <f>ROUND(F66-F65,0)</f>
         <v/>
       </c>
-      <c r="G67" s="68">
+      <c r="G67" s="71">
         <f>ROUND(G66-G65,0)</f>
         <v/>
       </c>
-      <c r="H67" s="68">
+      <c r="H67" s="71">
         <f>ROUND(H66-H65,0)</f>
         <v/>
       </c>
-      <c r="I67" s="68">
+      <c r="I67" s="71">
         <f>ROUND(I66-I65,0)</f>
         <v/>
       </c>
-      <c r="J67" s="68">
+      <c r="J67" s="71">
         <f>ROUND(J66-J65,0)</f>
         <v/>
       </c>
-      <c r="K67" s="68">
+      <c r="K67" s="71">
         <f>ROUND(K66-K65,0)</f>
         <v/>
       </c>
-      <c r="L67" s="68">
+      <c r="L67" s="71">
         <f>ROUND(L66-L65,0)</f>
         <v/>
       </c>
@@ -8219,43 +8621,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C72" s="68">
+      <c r="C72" s="71">
         <f>ROUND(C71-C70,0)</f>
         <v/>
       </c>
-      <c r="D72" s="68">
+      <c r="D72" s="71">
         <f>ROUND(D71-D70,0)</f>
         <v/>
       </c>
-      <c r="E72" s="68">
+      <c r="E72" s="71">
         <f>ROUND(E71-E70,0)</f>
         <v/>
       </c>
-      <c r="F72" s="68">
+      <c r="F72" s="71">
         <f>ROUND(F71-F70,0)</f>
         <v/>
       </c>
-      <c r="G72" s="68">
+      <c r="G72" s="71">
         <f>ROUND(G71-G70,0)</f>
         <v/>
       </c>
-      <c r="H72" s="68">
+      <c r="H72" s="71">
         <f>ROUND(H71-H70,0)</f>
         <v/>
       </c>
-      <c r="I72" s="68">
+      <c r="I72" s="71">
         <f>ROUND(I71-I70,0)</f>
         <v/>
       </c>
-      <c r="J72" s="68">
+      <c r="J72" s="71">
         <f>ROUND(J71-J70,0)</f>
         <v/>
       </c>
-      <c r="K72" s="68">
+      <c r="K72" s="71">
         <f>ROUND(K71-K70,0)</f>
         <v/>
       </c>
-      <c r="L72" s="68">
+      <c r="L72" s="71">
         <f>ROUND(L71-L70,0)</f>
         <v/>
       </c>
@@ -8278,43 +8680,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C75" s="70">
+      <c r="C75" s="73">
         <f>BalanceSheet!C20</f>
         <v/>
       </c>
-      <c r="D75" s="70">
+      <c r="D75" s="73">
         <f>BalanceSheet!D20</f>
         <v/>
       </c>
-      <c r="E75" s="70">
+      <c r="E75" s="73">
         <f>BalanceSheet!E20</f>
         <v/>
       </c>
-      <c r="F75" s="70">
+      <c r="F75" s="73">
         <f>BalanceSheet!F20</f>
         <v/>
       </c>
-      <c r="G75" s="70">
+      <c r="G75" s="73">
         <f>BalanceSheet!G20</f>
         <v/>
       </c>
-      <c r="H75" s="70">
+      <c r="H75" s="73">
         <f>BalanceSheet!H20</f>
         <v/>
       </c>
-      <c r="I75" s="70">
+      <c r="I75" s="73">
         <f>BalanceSheet!I20</f>
         <v/>
       </c>
-      <c r="J75" s="70">
+      <c r="J75" s="73">
         <f>BalanceSheet!J20</f>
         <v/>
       </c>
-      <c r="K75" s="70">
+      <c r="K75" s="73">
         <f>BalanceSheet!K20</f>
         <v/>
       </c>
-      <c r="L75" s="70">
+      <c r="L75" s="73">
         <f>BalanceSheet!L20</f>
         <v/>
       </c>
@@ -8349,676 +8751,676 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="59" t="inlineStr">
         <is>
           <t>Nothing on this sheet is our estimate. Every figure is published and cited, so it can be refreshed independently of anything we concluded from it. MarketModel derives our assumptions from these numbers; Assumptions then uses what MarketModel produces.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="72" t="inlineStr">
+      <c r="A4" s="74" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="72" t="inlineStr">
+      <c r="B4" s="74" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="72" t="inlineStr">
+      <c r="C4" s="74" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="72" t="inlineStr">
+      <c r="D4" s="74" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E4" s="72" t="inlineStr">
+      <c r="E4" s="74" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F4" s="72" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="73" t="inlineStr">
+      <c r="A5" s="75" t="inlineStr">
         <is>
           <t>Gross payments (GMV)</t>
         </is>
       </c>
-      <c r="B5" s="74" t="n">
+      <c r="B5" s="76" t="n">
         <v>7220000000</v>
       </c>
-      <c r="C5" s="75" t="inlineStr">
+      <c r="C5" s="77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D5" s="75" t="inlineStr">
+      <c r="D5" s="77" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E5" s="75" t="inlineStr">
+      <c r="E5" s="77" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F5" s="75" t="inlineStr">
+      <c r="F5" s="77" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="73" t="inlineStr">
+      <c r="A6" s="75" t="inlineStr">
         <is>
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="B6" s="74" t="n">
+      <c r="B6" s="76" t="n">
         <v>1410000000</v>
       </c>
-      <c r="C6" s="75" t="inlineStr">
+      <c r="C6" s="77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D6" s="75" t="inlineStr">
+      <c r="D6" s="77" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E6" s="75" t="inlineStr">
+      <c r="E6" s="77" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="77" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="73" t="inlineStr">
+      <c r="A7" s="75" t="inlineStr">
         <is>
           <t>Paid to creators</t>
         </is>
       </c>
-      <c r="B7" s="74" t="n">
+      <c r="B7" s="76" t="n">
         <v>5800000000</v>
       </c>
-      <c r="C7" s="75" t="inlineStr">
+      <c r="C7" s="77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D7" s="75" t="inlineStr">
+      <c r="D7" s="77" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E7" s="75" t="inlineStr">
+      <c r="E7" s="77" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F7" s="75" t="inlineStr">
+      <c r="F7" s="77" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts, 80.3% of gross</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="73" t="inlineStr">
+      <c r="A8" s="75" t="inlineStr">
         <is>
           <t>Creator accounts</t>
         </is>
       </c>
-      <c r="B8" s="74" t="n">
+      <c r="B8" s="76" t="n">
         <v>4634000</v>
       </c>
-      <c r="C8" s="75" t="inlineStr">
+      <c r="C8" s="77" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D8" s="75" t="inlineStr">
+      <c r="D8" s="77" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E8" s="75" t="inlineStr">
+      <c r="E8" s="77" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="77" t="inlineStr">
         <is>
           <t>Variety: +13% YoY</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="73" t="inlineStr">
+      <c r="A9" s="75" t="inlineStr">
         <is>
           <t>Fan accounts</t>
         </is>
       </c>
-      <c r="B9" s="74" t="n">
+      <c r="B9" s="76" t="n">
         <v>377500000</v>
       </c>
-      <c r="C9" s="75" t="inlineStr">
+      <c r="C9" s="77" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D9" s="75" t="inlineStr">
+      <c r="D9" s="77" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E9" s="75" t="inlineStr">
+      <c r="E9" s="77" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="77" t="inlineStr">
         <is>
           <t>Variety: +24% YoY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="73" t="inlineStr">
+      <c r="A10" s="75" t="inlineStr">
         <is>
           <t>Reported average creator earnings</t>
         </is>
       </c>
-      <c r="B10" s="74" t="n">
+      <c r="B10" s="76" t="n">
         <v>131</v>
       </c>
-      <c r="C10" s="75" t="inlineStr">
+      <c r="C10" s="77" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D10" s="75" t="inlineStr">
+      <c r="D10" s="77" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E10" s="75" t="inlineStr">
+      <c r="E10" s="77" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="77" t="inlineStr">
         <is>
           <t>Sci-Tech Today / ElectroIQ: after platform fees</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="73" t="inlineStr">
+      <c r="A11" s="75" t="inlineStr">
         <is>
           <t>Revenue concentration</t>
         </is>
       </c>
-      <c r="B11" s="76" t="n">
+      <c r="B11" s="78" t="n">
         <v>0.76</v>
       </c>
-      <c r="C11" s="75" t="inlineStr">
+      <c r="C11" s="77" t="inlineStr">
         <is>
           <t>share to top 0.1%</t>
         </is>
       </c>
-      <c r="D11" s="75" t="inlineStr">
+      <c r="D11" s="77" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E11" s="75" t="inlineStr">
+      <c r="E11" s="77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="77" t="inlineStr">
         <is>
           <t>ElectroIQ: power-law distribution</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="73" t="inlineStr">
+      <c r="A12" s="75" t="inlineStr">
         <is>
           <t>Creators with &gt;=1 paying member</t>
         </is>
       </c>
-      <c r="B12" s="74" t="n">
+      <c r="B12" s="76" t="n">
         <v>286287</v>
       </c>
-      <c r="C12" s="75" t="inlineStr">
+      <c r="C12" s="77" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D12" s="75" t="inlineStr">
+      <c r="D12" s="77" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E12" s="75" t="inlineStr">
+      <c r="E12" s="77" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="77" t="inlineStr">
         <is>
           <t>Graphtreon</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="73" t="inlineStr">
+      <c r="A13" s="75" t="inlineStr">
         <is>
           <t>Active creators</t>
         </is>
       </c>
-      <c r="B13" s="74" t="n">
+      <c r="B13" s="76" t="n">
         <v>300000</v>
       </c>
-      <c r="C13" s="75" t="inlineStr">
+      <c r="C13" s="77" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D13" s="75" t="inlineStr">
+      <c r="D13" s="77" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E13" s="75" t="inlineStr">
+      <c r="E13" s="77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F13" s="75" t="inlineStr">
+      <c r="F13" s="77" t="inlineStr">
         <is>
           <t>Jack Conte, Patreon</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="73" t="inlineStr">
+      <c r="A14" s="75" t="inlineStr">
         <is>
           <t>Active paying members</t>
         </is>
       </c>
-      <c r="B14" s="74" t="n">
+      <c r="B14" s="76" t="n">
         <v>10000000</v>
       </c>
-      <c r="C14" s="75" t="inlineStr">
+      <c r="C14" s="77" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D14" s="75" t="inlineStr">
+      <c r="D14" s="77" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E14" s="75" t="inlineStr">
+      <c r="E14" s="77" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F14" s="75" t="inlineStr">
+      <c r="F14" s="77" t="inlineStr">
         <is>
           <t>Patreon / Backlinko</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="73" t="inlineStr">
+      <c r="A15" s="75" t="inlineStr">
         <is>
           <t>Paid to creators annually</t>
         </is>
       </c>
-      <c r="B15" s="74" t="n">
+      <c r="B15" s="76" t="n">
         <v>2000000000</v>
       </c>
-      <c r="C15" s="75" t="inlineStr">
+      <c r="C15" s="77" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="D15" s="75" t="inlineStr">
+      <c r="D15" s="77" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E15" s="75" t="inlineStr">
+      <c r="E15" s="77" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F15" s="75" t="inlineStr">
+      <c r="F15" s="77" t="inlineStr">
         <is>
           <t>Patreon / Backlinko</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="73" t="inlineStr">
+      <c r="A16" s="75" t="inlineStr">
         <is>
           <t>Average monthly support per member</t>
         </is>
       </c>
-      <c r="B16" s="76" t="n">
+      <c r="B16" s="78" t="n">
         <v>6.1</v>
       </c>
-      <c r="C16" s="75" t="inlineStr">
+      <c r="C16" s="77" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D16" s="75" t="inlineStr">
+      <c r="D16" s="77" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E16" s="75" t="inlineStr">
+      <c r="E16" s="77" t="inlineStr">
         <is>
           <t>Aug 2024</t>
         </is>
       </c>
-      <c r="F16" s="75" t="inlineStr">
+      <c r="F16" s="77" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; audit of ~1,200 creators</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="73" t="inlineStr">
+      <c r="A17" s="75" t="inlineStr">
         <is>
           <t>Typical patronage band (low)</t>
         </is>
       </c>
-      <c r="B17" s="76" t="n">
+      <c r="B17" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="C17" s="75" t="inlineStr">
+      <c r="C17" s="77" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D17" s="75" t="inlineStr">
+      <c r="D17" s="77" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E17" s="75" t="inlineStr">
+      <c r="E17" s="77" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F17" s="75" t="inlineStr">
+      <c r="F17" s="77" t="inlineStr">
         <is>
           <t>Creator-economy benchmarks</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="73" t="inlineStr">
+      <c r="A18" s="75" t="inlineStr">
         <is>
           <t>Typical patronage band (high)</t>
         </is>
       </c>
-      <c r="B18" s="76" t="n">
+      <c r="B18" s="78" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="75" t="inlineStr">
+      <c r="C18" s="77" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D18" s="75" t="inlineStr">
+      <c r="D18" s="77" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E18" s="75" t="inlineStr">
+      <c r="E18" s="77" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="77" t="inlineStr">
         <is>
           <t>Creator-economy benchmarks</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="73" t="inlineStr">
+      <c r="A19" s="75" t="inlineStr">
         <is>
           <t>Monthly churn (low)</t>
         </is>
       </c>
-      <c r="B19" s="76" t="n">
+      <c r="B19" s="78" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="75" t="inlineStr">
+      <c r="C19" s="77" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D19" s="75" t="inlineStr">
+      <c r="D19" s="77" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E19" s="75" t="inlineStr">
+      <c r="E19" s="77" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F19" s="75" t="inlineStr">
+      <c r="F19" s="77" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="73" t="inlineStr">
+      <c r="A20" s="75" t="inlineStr">
         <is>
           <t>Monthly churn (high)</t>
         </is>
       </c>
-      <c r="B20" s="76" t="n">
+      <c r="B20" s="78" t="n">
         <v>0.15</v>
       </c>
-      <c r="C20" s="75" t="inlineStr">
+      <c r="C20" s="77" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D20" s="75" t="inlineStr">
+      <c r="D20" s="77" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E20" s="75" t="inlineStr">
+      <c r="E20" s="77" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F20" s="75" t="inlineStr">
+      <c r="F20" s="77" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="73" t="inlineStr">
+      <c r="A21" s="75" t="inlineStr">
         <is>
           <t>Annual-plan churn multiplier</t>
         </is>
       </c>
-      <c r="B21" s="76" t="n">
+      <c r="B21" s="78" t="n">
         <v>0.333</v>
       </c>
-      <c r="C21" s="75" t="inlineStr">
+      <c r="C21" s="77" t="inlineStr">
         <is>
           <t>x monthly churn</t>
         </is>
       </c>
-      <c r="D21" s="75" t="inlineStr">
+      <c r="D21" s="77" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E21" s="75" t="inlineStr">
+      <c r="E21" s="77" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F21" s="75" t="inlineStr">
+      <c r="F21" s="77" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report: annual patrons churn at 1/3 the rate</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="73" t="inlineStr">
+      <c r="A22" s="75" t="inlineStr">
         <is>
           <t>Creators with &gt;2,000 patrons</t>
         </is>
       </c>
-      <c r="B22" s="76" t="n">
+      <c r="B22" s="78" t="n">
         <v>0.003</v>
       </c>
-      <c r="C22" s="75" t="inlineStr">
+      <c r="C22" s="77" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D22" s="75" t="inlineStr">
+      <c r="D22" s="77" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E22" s="75" t="inlineStr">
+      <c r="E22" s="77" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F22" s="75" t="inlineStr">
+      <c r="F22" s="77" t="inlineStr">
         <is>
           <t>Graphtreon: power-law distribution</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="73" t="inlineStr">
+      <c r="A23" s="75" t="inlineStr">
         <is>
           <t>Division I athletes in network</t>
         </is>
       </c>
-      <c r="B23" s="74" t="n">
+      <c r="B23" s="76" t="n">
         <v>45000</v>
       </c>
-      <c r="C23" s="75" t="inlineStr">
+      <c r="C23" s="77" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D23" s="75" t="inlineStr">
+      <c r="D23" s="77" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E23" s="75" t="inlineStr">
+      <c r="E23" s="77" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F23" s="75" t="inlineStr">
+      <c r="F23" s="77" t="inlineStr">
         <is>
           <t>Publicis Groupe press release, 19 Aug 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="73" t="inlineStr">
+      <c r="A24" s="75" t="inlineStr">
         <is>
           <t>Power Four universities</t>
         </is>
       </c>
-      <c r="B24" s="74" t="n">
+      <c r="B24" s="76" t="n">
         <v>68</v>
       </c>
-      <c r="C24" s="75" t="inlineStr">
+      <c r="C24" s="77" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D24" s="75" t="inlineStr">
+      <c r="D24" s="77" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E24" s="75" t="inlineStr">
+      <c r="E24" s="77" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="77" t="inlineStr">
         <is>
           <t>Publicis Groupe press release</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="73" t="inlineStr">
+      <c r="A25" s="75" t="inlineStr">
         <is>
           <t>Claimed speed-to-market gain</t>
         </is>
       </c>
-      <c r="B25" s="76" t="n">
+      <c r="B25" s="78" t="n">
         <v>0.6</v>
       </c>
-      <c r="C25" s="75" t="inlineStr">
+      <c r="C25" s="77" t="inlineStr">
         <is>
           <t>share faster</t>
         </is>
       </c>
-      <c r="D25" s="75" t="inlineStr">
+      <c r="D25" s="77" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E25" s="75" t="inlineStr">
+      <c r="E25" s="77" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F25" s="75" t="inlineStr">
+      <c r="F25" s="77" t="inlineStr">
         <is>
           <t>Publicis: stated 50-70% vs a traditional agency process</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="77" t="inlineStr">
+      <c r="A27" s="79" t="inlineStr">
         <is>
           <t>TAKE RATES - what each platform costs a creator</t>
         </is>
@@ -9058,16 +9460,16 @@
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="B29" s="78" t="n">
+      <c r="B29" s="80" t="n">
         <v>0.2</v>
       </c>
-      <c r="C29" s="79" t="n">
+      <c r="C29" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="79" t="n">
+      <c r="D29" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="80" t="inlineStr">
+      <c r="F29" s="82" t="inlineStr">
         <is>
           <t>Derived: 1.41bn / 7.22bn = 19.5% (filed accounts)</t>
         </is>
@@ -9079,16 +9481,16 @@
           <t>Fansly</t>
         </is>
       </c>
-      <c r="B30" s="78" t="n">
+      <c r="B30" s="80" t="n">
         <v>0.2</v>
       </c>
-      <c r="C30" s="79" t="n">
+      <c r="C30" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="79" t="n">
+      <c r="D30" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="80" t="inlineStr">
+      <c r="F30" s="82" t="inlineStr">
         <is>
           <t>Not published in terms; widely reported</t>
         </is>
@@ -9100,16 +9502,16 @@
           <t>Fanfix</t>
         </is>
       </c>
-      <c r="B31" s="78" t="n">
+      <c r="B31" s="80" t="n">
         <v>0.2</v>
       </c>
-      <c r="C31" s="79" t="n">
+      <c r="C31" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="79" t="n">
+      <c r="D31" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="80" t="inlineStr">
+      <c r="F31" s="82" t="inlineStr">
         <is>
           <t>Not published in terms; widely reported</t>
         </is>
@@ -9121,16 +9523,16 @@
           <t>Patreon</t>
         </is>
       </c>
-      <c r="B32" s="78" t="n">
+      <c r="B32" s="80" t="n">
         <v>0.1</v>
       </c>
-      <c r="C32" s="79" t="n">
+      <c r="C32" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="79" t="n">
+      <c r="D32" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="80" t="inlineStr">
+      <c r="F32" s="82" t="inlineStr">
         <is>
           <t>Published: 10% all-in, processing included</t>
         </is>
@@ -9142,16 +9544,16 @@
           <t>Passes</t>
         </is>
       </c>
-      <c r="B33" s="78" t="n">
+      <c r="B33" s="80" t="n">
         <v>0.1</v>
       </c>
-      <c r="C33" s="79" t="n">
+      <c r="C33" s="81" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="79" t="n">
+      <c r="D33" s="81" t="n">
         <v>29</v>
       </c>
-      <c r="F33" s="80" t="inlineStr">
+      <c r="F33" s="82" t="inlineStr">
         <is>
           <t>Sacra; Passes rebrand release Apr 2026</t>
         </is>
@@ -9163,23 +9565,23 @@
           <t>Stride (proposed)</t>
         </is>
       </c>
-      <c r="B34" s="78" t="n">
+      <c r="B34" s="80" t="n">
         <v>0.15</v>
       </c>
-      <c r="C34" s="79" t="n">
+      <c r="C34" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="79" t="n">
+      <c r="D34" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="80" t="inlineStr">
+      <c r="F34" s="82" t="inlineStr">
         <is>
           <t>Our decision, see MarketModel</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="77" t="inlineStr">
+      <c r="A36" s="79" t="inlineStr">
         <is>
           <t>INTERMEDIARIES the athlete already pays</t>
         </is>
@@ -9191,13 +9593,13 @@
           <t>Sports agent: endorsement</t>
         </is>
       </c>
-      <c r="B37" s="78" t="n">
+      <c r="B37" s="80" t="n">
         <v>0.1</v>
       </c>
-      <c r="C37" s="78" t="n">
+      <c r="C37" s="80" t="n">
         <v>0.2</v>
       </c>
-      <c r="F37" s="80" t="inlineStr">
+      <c r="F37" s="82" t="inlineStr">
         <is>
           <t>Unregulated; widely reported, no primary source</t>
         </is>
@@ -9209,13 +9611,13 @@
           <t>Sports agent: playing contract</t>
         </is>
       </c>
-      <c r="B38" s="78" t="n">
+      <c r="B38" s="80" t="n">
         <v>0.02</v>
       </c>
-      <c r="C38" s="78" t="n">
+      <c r="C38" s="80" t="n">
         <v>0.05</v>
       </c>
-      <c r="F38" s="80" t="inlineStr">
+      <c r="F38" s="82" t="inlineStr">
         <is>
           <t>NBPA reg. 4.B (Sept 2025); FIFA FFAR art. 15</t>
         </is>
@@ -9227,306 +9629,306 @@
           <t>OnlyFans management agency</t>
         </is>
       </c>
-      <c r="B39" s="78" t="n">
+      <c r="B39" s="80" t="n">
         <v>0.2</v>
       </c>
-      <c r="C39" s="78" t="n">
+      <c r="C39" s="80" t="n">
         <v>0.5</v>
       </c>
-      <c r="F39" s="80" t="inlineStr">
+      <c r="F39" s="82" t="inlineStr">
         <is>
           <t>Aruna Talent rate guide 2026, on top of the 20%</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="77" t="inlineStr">
+      <c r="A41" s="79" t="inlineStr">
         <is>
           <t>SPONSORSHIP MARKET - top down, for context not for sizing</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="71" t="inlineStr">
+      <c r="A42" s="59" t="inlineStr">
         <is>
           <t>European Sponsorship Association, analysis by Nielsen Sports, published 12 Mar 2026. NOTE: none of it breaks below the professional tier, so it is context rather than our addressable market. The athlete funnel on Research is what sizes the business.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="72" t="inlineStr">
+      <c r="A43" s="74" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B43" s="72" t="inlineStr">
+      <c r="B43" s="74" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C43" s="72" t="inlineStr">
+      <c r="C43" s="74" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D43" s="72" t="inlineStr">
+      <c r="D43" s="74" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="E43" s="72" t="inlineStr">
+      <c r="E43" s="74" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F43" s="72" t="inlineStr">
+      <c r="F43" s="74" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="73" t="inlineStr">
+      <c r="A44" s="75" t="inlineStr">
         <is>
           <t>Total sponsorship market</t>
         </is>
       </c>
-      <c r="B44" s="81" t="n">
+      <c r="B44" s="62" t="n">
         <v>34450000000</v>
       </c>
-      <c r="C44" s="75" t="inlineStr">
+      <c r="C44" s="77" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D44" s="75" t="inlineStr">
+      <c r="D44" s="77" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="E44" s="75" t="inlineStr">
+      <c r="E44" s="77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F44" s="75" t="inlineStr">
+      <c r="F44" s="77" t="inlineStr">
         <is>
           <t>European Sponsorship Association, analysis by Nielsen Sports, 12 Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="73" t="inlineStr">
+      <c r="A45" s="75" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
       </c>
-      <c r="B45" s="81" t="n">
+      <c r="B45" s="62" t="n">
         <v>24790000000</v>
       </c>
-      <c r="C45" s="75" t="inlineStr">
+      <c r="C45" s="77" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D45" s="75" t="inlineStr">
+      <c r="D45" s="77" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="E45" s="75" t="inlineStr">
+      <c r="E45" s="77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F45" s="75" t="inlineStr">
+      <c r="F45" s="77" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: 72% of the total, +5.9% YoY</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="73" t="inlineStr">
+      <c r="A46" s="75" t="inlineStr">
         <is>
           <t>Non-sport sponsorship</t>
         </is>
       </c>
-      <c r="B46" s="81" t="n">
+      <c r="B46" s="62" t="n">
         <v>9660000000</v>
       </c>
-      <c r="C46" s="75" t="inlineStr">
+      <c r="C46" s="77" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D46" s="75" t="inlineStr">
+      <c r="D46" s="77" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="E46" s="75" t="inlineStr">
+      <c r="E46" s="77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F46" s="75" t="inlineStr">
+      <c r="F46" s="77" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +1.8% YoY</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="73" t="inlineStr">
+      <c r="A47" s="75" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
       </c>
-      <c r="B47" s="81" t="n">
+      <c r="B47" s="62" t="n">
         <v>2180000000</v>
       </c>
-      <c r="C47" s="75" t="inlineStr">
+      <c r="C47" s="77" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D47" s="75" t="inlineStr">
+      <c r="D47" s="77" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="E47" s="75" t="inlineStr">
+      <c r="E47" s="77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F47" s="75" t="inlineStr">
+      <c r="F47" s="77" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +14%, the fastest growing major European market</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="73" t="inlineStr">
+      <c r="A48" s="75" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
       </c>
-      <c r="B48" s="81" t="n">
+      <c r="B48" s="62" t="n">
         <v>6260000000</v>
       </c>
-      <c r="C48" s="75" t="inlineStr">
+      <c r="C48" s="77" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D48" s="75" t="inlineStr">
+      <c r="D48" s="77" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E48" s="75" t="inlineStr">
+      <c r="E48" s="77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F48" s="75" t="inlineStr">
+      <c r="F48" s="77" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: the largest European market</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="73" t="inlineStr">
+      <c r="A49" s="75" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
       </c>
-      <c r="B49" s="81" t="n">
+      <c r="B49" s="62" t="n">
         <v>6150000000</v>
       </c>
-      <c r="C49" s="75" t="inlineStr">
+      <c r="C49" s="77" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D49" s="75" t="inlineStr">
+      <c r="D49" s="77" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E49" s="75" t="inlineStr">
+      <c r="E49" s="77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F49" s="75" t="inlineStr">
+      <c r="F49" s="77" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +10.5%</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="73" t="inlineStr">
+      <c r="A50" s="75" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
       </c>
-      <c r="B50" s="81" t="n">
+      <c r="B50" s="62" t="n">
         <v>2010000000</v>
       </c>
-      <c r="C50" s="75" t="inlineStr">
+      <c r="C50" s="77" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D50" s="75" t="inlineStr">
+      <c r="D50" s="77" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="E50" s="75" t="inlineStr">
+      <c r="E50" s="77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F50" s="75" t="inlineStr">
+      <c r="F50" s="77" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +5%</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="73" t="inlineStr">
+      <c r="A51" s="75" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
       </c>
-      <c r="B51" s="81" t="n">
+      <c r="B51" s="62" t="n">
         <v>1850000000</v>
       </c>
-      <c r="C51" s="75" t="inlineStr">
+      <c r="C51" s="77" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D51" s="75" t="inlineStr">
+      <c r="D51" s="77" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="E51" s="75" t="inlineStr">
+      <c r="E51" s="77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F51" s="75" t="inlineStr">
+      <c r="F51" s="77" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +10.3%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="77" t="inlineStr">
+      <c r="A53" s="79" t="inlineStr">
         <is>
           <t>European SPORT sponsorship by year, EUR bn</t>
         </is>
@@ -9553,163 +9955,163 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="82" t="n">
+      <c r="A55" s="83" t="n">
         <v>20.26</v>
       </c>
-      <c r="B55" s="82" t="n">
+      <c r="B55" s="83" t="n">
         <v>19.8</v>
       </c>
-      <c r="C55" s="82" t="n">
+      <c r="C55" s="83" t="n">
         <v>20.69</v>
       </c>
-      <c r="D55" s="82" t="n">
+      <c r="D55" s="83" t="n">
         <v>21.98</v>
       </c>
-      <c r="E55" s="82" t="n">
+      <c r="E55" s="83" t="n">
         <v>23.41</v>
       </c>
-      <c r="F55" s="82" t="n">
+      <c r="F55" s="83" t="n">
         <v>24.79</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="71" t="inlineStr">
+      <c r="A56" s="59" t="inlineStr">
         <is>
           <t>2020 is not published in the ESA series. Source: ESA via Statista, retrieved 1 Oct 2026.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="77" t="inlineStr">
+      <c r="A58" s="79" t="inlineStr">
         <is>
           <t>FAN DEMAND - published surveys bearing on the fan thesis</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="72" t="inlineStr">
+      <c r="A59" s="74" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B59" s="72" t="inlineStr">
+      <c r="B59" s="74" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C59" s="72" t="inlineStr">
+      <c r="C59" s="74" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D59" s="72" t="inlineStr">
+      <c r="D59" s="74" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="E59" s="72" t="inlineStr">
+      <c r="E59" s="74" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F59" s="72" t="inlineStr">
+      <c r="F59" s="74" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="73" t="inlineStr">
+      <c r="A60" s="75" t="inlineStr">
         <is>
           <t>Weekly minutes, fan-generated content</t>
         </is>
       </c>
-      <c r="B60" s="74" t="n">
+      <c r="B60" s="76" t="n">
         <v>115</v>
       </c>
-      <c r="C60" s="75" t="inlineStr">
+      <c r="C60" s="77" t="inlineStr">
         <is>
           <t>minutes/week</t>
         </is>
       </c>
-      <c r="D60" s="75" t="inlineStr">
+      <c r="D60" s="77" t="inlineStr">
         <is>
           <t>FR DE IT ES UK US</t>
         </is>
       </c>
-      <c r="E60" s="75" t="inlineStr">
+      <c r="E60" s="77" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F60" s="75" t="inlineStr">
+      <c r="F60" s="77" t="inlineStr">
         <is>
           <t>Altman Solon / IRIS Sport, 6,000 respondents who watch sports video monthly</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="73" t="inlineStr">
+      <c r="A61" s="75" t="inlineStr">
         <is>
           <t>Weekly minutes, highlights and clips</t>
         </is>
       </c>
-      <c r="B61" s="74" t="n">
+      <c r="B61" s="76" t="n">
         <v>115</v>
       </c>
-      <c r="C61" s="75" t="inlineStr">
+      <c r="C61" s="77" t="inlineStr">
         <is>
           <t>minutes/week</t>
         </is>
       </c>
-      <c r="D61" s="75" t="inlineStr">
+      <c r="D61" s="77" t="inlineStr">
         <is>
           <t>FR DE IT ES UK US</t>
         </is>
       </c>
-      <c r="E61" s="75" t="inlineStr">
+      <c r="E61" s="77" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F61" s="75" t="inlineStr">
+      <c r="F61" s="77" t="inlineStr">
         <is>
           <t>Altman Solon / IRIS Sport</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="73" t="inlineStr">
+      <c r="A62" s="75" t="inlineStr">
         <is>
           <t>Weekly minutes, live games and events</t>
         </is>
       </c>
-      <c r="B62" s="74" t="n">
+      <c r="B62" s="76" t="n">
         <v>245</v>
       </c>
-      <c r="C62" s="75" t="inlineStr">
+      <c r="C62" s="77" t="inlineStr">
         <is>
           <t>minutes/week</t>
         </is>
       </c>
-      <c r="D62" s="75" t="inlineStr">
+      <c r="D62" s="77" t="inlineStr">
         <is>
           <t>FR DE IT ES UK US</t>
         </is>
       </c>
-      <c r="E62" s="75" t="inlineStr">
+      <c r="E62" s="77" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F62" s="75" t="inlineStr">
+      <c r="F62" s="77" t="inlineStr">
         <is>
           <t>Altman Solon / IRIS Sport</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="73" t="inlineStr">
+      <c r="A63" s="75" t="inlineStr">
         <is>
           <t>YouTube share of fan-generated viewing</t>
         </is>
@@ -9717,29 +10119,29 @@
       <c r="B63" s="38" t="n">
         <v>0.35</v>
       </c>
-      <c r="C63" s="75" t="inlineStr">
+      <c r="C63" s="77" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D63" s="75" t="inlineStr">
+      <c r="D63" s="77" t="inlineStr">
         <is>
           <t>FR DE IT ES UK US</t>
         </is>
       </c>
-      <c r="E63" s="75" t="inlineStr">
+      <c r="E63" s="77" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F63" s="75" t="inlineStr">
+      <c r="F63" s="77" t="inlineStr">
         <is>
           <t>Altman Solon / IRIS Sport: 40 of 115 minutes, more than linear TV or streaming</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="73" t="inlineStr">
+      <c r="A64" s="75" t="inlineStr">
         <is>
           <t>Subscribers watching MORE sport after subscribing</t>
         </is>
@@ -9747,29 +10149,29 @@
       <c r="B64" s="38" t="n">
         <v>0.7</v>
       </c>
-      <c r="C64" s="75" t="inlineStr">
+      <c r="C64" s="77" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D64" s="75" t="inlineStr">
+      <c r="D64" s="77" t="inlineStr">
         <is>
           <t>Worldwide</t>
         </is>
       </c>
-      <c r="E64" s="75" t="inlineStr">
+      <c r="E64" s="77" t="inlineStr">
         <is>
           <t>Nov 2022</t>
         </is>
       </c>
-      <c r="F64" s="75" t="inlineStr">
+      <c r="F64" s="77" t="inlineStr">
         <is>
           <t>YouGov / Strive, 19,000 respondents: 38% much more + 32% somewhat more</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="73" t="inlineStr">
+      <c r="A65" s="75" t="inlineStr">
         <is>
           <t>Subscribers watching LESS sport after subscribing</t>
         </is>
@@ -9777,75 +10179,75 @@
       <c r="B65" s="38" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C65" s="75" t="inlineStr">
+      <c r="C65" s="77" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D65" s="75" t="inlineStr">
+      <c r="D65" s="77" t="inlineStr">
         <is>
           <t>Worldwide</t>
         </is>
       </c>
-      <c r="E65" s="75" t="inlineStr">
+      <c r="E65" s="77" t="inlineStr">
         <is>
           <t>Nov 2022</t>
         </is>
       </c>
-      <c r="F65" s="75" t="inlineStr">
+      <c r="F65" s="77" t="inlineStr">
         <is>
           <t>YouGov / Strive: 3% much less + 4% somewhat less</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="77" t="inlineStr">
+      <c r="A67" s="79" t="inlineStr">
         <is>
           <t>SPONSORSHIP MARKETPLACES - the direct competitor set</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="71" t="inlineStr">
+      <c r="A68" s="59" t="inlineStr">
         <is>
           <t>PitchBook company profiles retrieved 1 Oct 2026, reported in EUR. None of the four discloses revenue, so headcount and capital raised are the only scale measures available. Links at the bottom of this sheet.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="72" t="inlineStr">
+      <c r="A69" s="74" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B69" s="72" t="inlineStr">
+      <c r="B69" s="74" t="inlineStr">
         <is>
           <t>Founded</t>
         </is>
       </c>
-      <c r="C69" s="72" t="inlineStr">
+      <c r="C69" s="74" t="inlineStr">
         <is>
           <t>Employees (as of)</t>
         </is>
       </c>
-      <c r="D69" s="72" t="inlineStr">
+      <c r="D69" s="74" t="inlineStr">
         <is>
           <t>Total raised</t>
         </is>
       </c>
-      <c r="E69" s="72" t="inlineStr">
+      <c r="E69" s="74" t="inlineStr">
         <is>
           <t>Largest round pre-money</t>
         </is>
       </c>
-      <c r="F69" s="72" t="inlineStr">
+      <c r="F69" s="74" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="83" t="inlineStr">
+      <c r="A70" s="84" t="inlineStr">
         <is>
           <t>Sponsoo (Germany)</t>
         </is>
@@ -9853,23 +10255,23 @@
       <c r="B70" s="39" t="n">
         <v>2014</v>
       </c>
-      <c r="C70" s="74" t="n">
+      <c r="C70" s="76" t="n">
         <v>13</v>
       </c>
-      <c r="D70" s="81" t="n">
+      <c r="D70" s="62" t="n">
         <v>2170000</v>
       </c>
-      <c r="E70" s="81" t="n">
+      <c r="E70" s="62" t="n">
         <v>15900000</v>
       </c>
-      <c r="F70" s="75" t="inlineStr">
+      <c r="F70" s="77" t="inlineStr">
         <is>
           <t>Headcount as of 14 Nov 2025. Privately held, venture backed. Series A 28 Jan 2021; pre-money is a PitchBook ESTIMATE</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="83" t="inlineStr">
+      <c r="A71" s="84" t="inlineStr">
         <is>
           <t>OpenSponsorship (United States)</t>
         </is>
@@ -9877,21 +10279,21 @@
       <c r="B71" s="39" t="n">
         <v>2014</v>
       </c>
-      <c r="C71" s="74" t="n">
+      <c r="C71" s="76" t="n">
         <v>23</v>
       </c>
-      <c r="D71" s="81" t="n">
+      <c r="D71" s="62" t="n">
         <v>5400000</v>
       </c>
-      <c r="E71" s="81" t="n"/>
-      <c r="F71" s="75" t="inlineStr">
+      <c r="E71" s="62" t="n"/>
+      <c r="F71" s="77" t="inlineStr">
         <is>
           <t>Headcount as of 9 Mar 2026. Privately held, venture backed. Last priced round not disclosed</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="83" t="inlineStr">
+      <c r="A72" s="84" t="inlineStr">
         <is>
           <t>SponsorUnited (United States)</t>
         </is>
@@ -9899,23 +10301,23 @@
       <c r="B72" s="39" t="n">
         <v>2016</v>
       </c>
-      <c r="C72" s="74" t="n">
+      <c r="C72" s="76" t="n">
         <v>355</v>
       </c>
-      <c r="D72" s="81" t="n">
+      <c r="D72" s="62" t="n">
         <v>38760000</v>
       </c>
-      <c r="E72" s="81" t="n">
+      <c r="E72" s="62" t="n">
         <v>89380000</v>
       </c>
-      <c r="F72" s="75" t="inlineStr">
+      <c r="F72" s="77" t="inlineStr">
         <is>
           <t>Headcount as of 28 May 2026. Privately held, venture backed. Series A 21 Nov 2022</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="83" t="inlineStr">
+      <c r="A73" s="84" t="inlineStr">
         <is>
           <t>Hookit (United States)</t>
         </is>
@@ -9923,50 +10325,50 @@
       <c r="B73" s="39" t="n">
         <v>2001</v>
       </c>
-      <c r="C73" s="74" t="n">
+      <c r="C73" s="76" t="n">
         <v>47</v>
       </c>
-      <c r="D73" s="81" t="n">
+      <c r="D73" s="62" t="n">
         <v>21470000</v>
       </c>
-      <c r="E73" s="81" t="n">
+      <c r="E73" s="62" t="n">
         <v>38400000</v>
       </c>
-      <c r="F73" s="75" t="inlineStr">
+      <c r="F73" s="77" t="inlineStr">
         <is>
           <t>Headcount as of 8 Feb 2022. Acquired, operating subsidiary. Series C2 24 Feb 2020; pre-money is a PitchBook ESTIMATE</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="83" t="inlineStr">
+      <c r="A74" s="84" t="inlineStr">
         <is>
           <t>Stride (this plan, at Y10)</t>
         </is>
       </c>
-      <c r="B74" s="84" t="n">
+      <c r="B74" s="85" t="n">
         <v>2026</v>
       </c>
-      <c r="C74" s="85">
+      <c r="C74" s="86">
         <f>Assumptions!L66</f>
         <v/>
       </c>
-      <c r="D74" s="86">
+      <c r="D74" s="87">
         <f>SUM(Funding!C4:L4)</f>
         <v/>
       </c>
-      <c r="E74" s="86">
+      <c r="E74" s="87">
         <f>Funding!H5</f>
         <v/>
       </c>
-      <c r="F74" s="75" t="inlineStr">
+      <c r="F74" s="77" t="inlineStr">
         <is>
           <t>Deliberately sized near Sponsoo. Only EUR 400k of the total is capital the plan depends on; the growth round is optional</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="77" t="inlineStr">
+      <c r="A76" s="79" t="inlineStr">
         <is>
           <t>REVENUE PER EMPLOYEE - what the plan is tested against</t>
         </is>
@@ -9998,10 +10400,10 @@
           <t>Median private B2B SaaS, all stages</t>
         </is>
       </c>
-      <c r="B78" s="87" t="n">
+      <c r="B78" s="88" t="n">
         <v>135000</v>
       </c>
-      <c r="F78" s="88" t="inlineStr">
+      <c r="F78" s="89" t="inlineStr">
         <is>
           <t>SaaS Capital 2025 survey of ~1,000 private B2B SaaS companies</t>
         </is>
@@ -10013,10 +10415,10 @@
           <t>Top quartile private B2B SaaS</t>
         </is>
       </c>
-      <c r="B79" s="87" t="n">
+      <c r="B79" s="88" t="n">
         <v>215000</v>
       </c>
-      <c r="F79" s="88" t="inlineStr">
+      <c r="F79" s="89" t="inlineStr">
         <is>
           <t>SaaS Capital 2025 survey, 75th percentile</t>
         </is>
@@ -10028,10 +10430,10 @@
           <t>Efficient public SaaS at scale</t>
         </is>
       </c>
-      <c r="B80" s="87" t="n">
+      <c r="B80" s="88" t="n">
         <v>300000</v>
       </c>
-      <c r="F80" s="88" t="inlineStr">
+      <c r="F80" s="89" t="inlineStr">
         <is>
           <t>Public SaaS medians, widely reported range EUR 250-350k</t>
         </is>
@@ -10043,11 +10445,11 @@
           <t>Stride (this plan, Y7)</t>
         </is>
       </c>
-      <c r="B81" s="89">
+      <c r="B81" s="90">
         <f>KPIs!I14</f>
         <v/>
       </c>
-      <c r="F81" s="88" t="inlineStr">
+      <c r="F81" s="89" t="inlineStr">
         <is>
           <t>Above the top quartile. Defended in section 3.2.2: the fan side is self-serve and moderation is a variable cost, not headcount</t>
         </is>
@@ -10059,11 +10461,11 @@
           <t>Multiple of the top quartile</t>
         </is>
       </c>
-      <c r="B82" s="90">
+      <c r="B82" s="91">
         <f>B81/B79</f>
         <v/>
       </c>
-      <c r="F82" s="80" t="inlineStr">
+      <c r="F82" s="82" t="inlineStr">
         <is>
           <t>The plan's second most aggressive assumption after fan churn</t>
         </is>
@@ -10077,300 +10479,300 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="91" t="inlineStr">
+      <c r="A86" s="92" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 filed accounts (Fenix International Ltd)</t>
         </is>
       </c>
-      <c r="B86" s="92" t="inlineStr">
+      <c r="B86" s="93" t="inlineStr">
         <is>
           <t>https://find-and-update.company-information.service.gov.uk/company/10354575/filing-history</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="91" t="inlineStr">
+      <c r="A87" s="92" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 as reported</t>
         </is>
       </c>
-      <c r="B87" s="92" t="inlineStr">
+      <c r="B87" s="93" t="inlineStr">
         <is>
           <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="91" t="inlineStr">
+      <c r="A88" s="92" t="inlineStr">
         <is>
           <t>Patreon published take rate</t>
         </is>
       </c>
-      <c r="B88" s="92" t="inlineStr">
+      <c r="B88" s="93" t="inlineStr">
         <is>
           <t>https://www.patreon.com/pricing</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="91" t="inlineStr">
+      <c r="A89" s="92" t="inlineStr">
         <is>
           <t>Patreon creators</t>
         </is>
       </c>
-      <c r="B89" s="92" t="inlineStr">
+      <c r="B89" s="93" t="inlineStr">
         <is>
           <t>https://backlinko.com/patreon-users</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="91" t="inlineStr">
+      <c r="A90" s="92" t="inlineStr">
         <is>
           <t>Passes economics</t>
         </is>
       </c>
-      <c r="B90" s="92" t="inlineStr">
+      <c r="B90" s="93" t="inlineStr">
         <is>
           <t>https://sacra.com/c/passes/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="91" t="inlineStr">
+      <c r="A91" s="92" t="inlineStr">
         <is>
           <t>Fanfix creator terms (states no take rate)</t>
         </is>
       </c>
-      <c r="B91" s="92" t="inlineStr">
+      <c r="B91" s="93" t="inlineStr">
         <is>
           <t>https://auth.fanfix.io/creator-terms-of-use</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="91" t="inlineStr">
+      <c r="A92" s="92" t="inlineStr">
         <is>
           <t>Agency commissions</t>
         </is>
       </c>
-      <c r="B92" s="92" t="inlineStr">
+      <c r="B92" s="93" t="inlineStr">
         <is>
           <t>https://arunatalent.com/blog/onlyfans-agency-commission-rates/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="91" t="inlineStr">
+      <c r="A93" s="92" t="inlineStr">
         <is>
           <t>NBPA agent fee cap (amended Sept 2025)</t>
         </is>
       </c>
-      <c r="B93" s="92" t="inlineStr">
+      <c r="B93" s="93" t="inlineStr">
         <is>
           <t>https://imgix.cosmicjs.com/cd844850-97c7-11f0-91fa-d9e1671c2776-NBPA-REGULATIONS-GOVERNING-PLAYER-AGENTS-09-2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="91" t="inlineStr">
+      <c r="A94" s="92" t="inlineStr">
         <is>
           <t>FIFA Football Agent Regulations art. 15</t>
         </is>
       </c>
-      <c r="B94" s="92" t="inlineStr">
+      <c r="B94" s="93" t="inlineStr">
         <is>
           <t>https://digitalhub.fifa.com/m/1e7b741fa0fae779/original/FIFA-Football-Agent-Regulations.pdf</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="91" t="inlineStr">
+      <c r="A95" s="92" t="inlineStr">
         <is>
           <t>CJEU upholds the FIFA fee cap (16 Jul 2026)</t>
         </is>
       </c>
-      <c r="B95" s="92" t="inlineStr">
+      <c r="B95" s="93" t="inlineStr">
         <is>
           <t>https://inside.fifa.com/news/welcomes-court-of-justice-european-union-decision-football-agent-regulations</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="91" t="inlineStr">
+      <c r="A96" s="92" t="inlineStr">
         <is>
           <t>Eurobarometer 525</t>
         </is>
       </c>
-      <c r="B96" s="92" t="inlineStr">
+      <c r="B96" s="93" t="inlineStr">
         <is>
           <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="91" t="inlineStr">
+      <c r="A97" s="92" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="B97" s="92" t="inlineStr">
+      <c r="B97" s="93" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="91" t="inlineStr">
+      <c r="A98" s="92" t="inlineStr">
         <is>
           <t>Stripe EU pricing</t>
         </is>
       </c>
-      <c r="B98" s="92" t="inlineStr">
+      <c r="B98" s="93" t="inlineStr">
         <is>
           <t>https://stripe.com/es/pricing</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="91" t="inlineStr">
+      <c r="A99" s="92" t="inlineStr">
         <is>
           <t>TEKTA launch</t>
         </is>
       </c>
-      <c r="B99" s="92" t="inlineStr">
+      <c r="B99" s="93" t="inlineStr">
         <is>
           <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="91" t="inlineStr">
+      <c r="A100" s="92" t="inlineStr">
         <is>
           <t>Stripe Connect age</t>
         </is>
       </c>
-      <c r="B100" s="92" t="inlineStr">
+      <c r="B100" s="93" t="inlineStr">
         <is>
           <t>https://support.stripe.com/questions/age-requirement-to-create-a-stripe-account</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="91" t="inlineStr">
+      <c r="A101" s="92" t="inlineStr">
         <is>
           <t>PitchBook: Sponsoo GmbH</t>
         </is>
       </c>
-      <c r="B101" s="92" t="inlineStr">
+      <c r="B101" s="93" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/103066-39</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="91" t="inlineStr">
+      <c r="A102" s="92" t="inlineStr">
         <is>
           <t>PitchBook: OpenSponsorship</t>
         </is>
       </c>
-      <c r="B102" s="92" t="inlineStr">
+      <c r="B102" s="93" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/113575-96</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="91" t="inlineStr">
+      <c r="A103" s="92" t="inlineStr">
         <is>
           <t>PitchBook: SponsorUnited</t>
         </is>
       </c>
-      <c r="B103" s="92" t="inlineStr">
+      <c r="B103" s="93" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/169635-43</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="91" t="inlineStr">
+      <c r="A104" s="92" t="inlineStr">
         <is>
           <t>PitchBook: Hookit</t>
         </is>
       </c>
-      <c r="B104" s="92" t="inlineStr">
+      <c r="B104" s="93" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/55307-17</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="91" t="inlineStr">
+      <c r="A105" s="92" t="inlineStr">
         <is>
           <t>ESA European sponsorship market 2025</t>
         </is>
       </c>
-      <c r="B105" s="92" t="inlineStr">
+      <c r="B105" s="93" t="inlineStr">
         <is>
           <t>https://sponsorship.org/european-sponsorship-market-reaches-e34-45bn-in-2025-as-growth-continues-across-all-sectors/</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="91" t="inlineStr">
+      <c r="A106" s="92" t="inlineStr">
         <is>
           <t>SportsPro on the ESA 2026 market overview</t>
         </is>
       </c>
-      <c r="B106" s="92" t="inlineStr">
+      <c r="B106" s="93" t="inlineStr">
         <is>
           <t>https://www.sportspro.com/news/sponsorship-marketing/sports-sponsorship-european-market-valuation-esa-march-2026/</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="91" t="inlineStr">
+      <c r="A107" s="92" t="inlineStr">
         <is>
           <t>European sport sponsorship 2019-2025 (ESA via Statista)</t>
         </is>
       </c>
-      <c r="B107" s="92" t="inlineStr">
+      <c r="B107" s="93" t="inlineStr">
         <is>
           <t>https://www.statista.com/statistics/1430225/sports-sponsorship-market-size-europe/</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="91" t="inlineStr">
+      <c r="A108" s="92" t="inlineStr">
         <is>
           <t>Sports content formats by channel (Altman Solon / IRIS Sport)</t>
         </is>
       </c>
-      <c r="B108" s="92" t="inlineStr">
+      <c r="B108" s="93" t="inlineStr">
         <is>
           <t>https://www.statista.com/statistics/1660170/time-spent-weekly-watching-sports-formats-by-channel/</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="91" t="inlineStr">
+      <c r="A109" s="92" t="inlineStr">
         <is>
           <t>Impact of subscriptions on sports consumption (YouGov / Strive)</t>
         </is>
       </c>
-      <c r="B109" s="92" t="inlineStr">
+      <c r="B109" s="93" t="inlineStr">
         <is>
           <t>https://www.statista.com/statistics/1413187/impact-subscriptions-sports-content-consumption/</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="91" t="inlineStr">
+      <c r="A110" s="92" t="inlineStr">
         <is>
           <t>SaaS Capital revenue per employee benchmarks</t>
         </is>
       </c>
-      <c r="B110" s="92" t="inlineStr">
+      <c r="B110" s="93" t="inlineStr">
         <is>
           <t>https://www.saas-capital.com/blog-posts/revenue-per-employee-benchmarks-for-private-saas-companies/</t>
         </is>
@@ -10461,43 +10863,43 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="59" t="inlineStr">
         <is>
           <t>Each block starts from a published figure on Comparables and ends in a number the Assumptions sheet uses. Adjustment factors are blue because they are our judgement; everything else is a formula you can trace.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="93" t="inlineStr">
+      <c r="C3" s="94" t="inlineStr">
         <is>
           <t>Input: change me</t>
         </is>
       </c>
-      <c r="D3" s="94" t="n"/>
-      <c r="E3" s="95" t="inlineStr">
+      <c r="D3" s="95" t="n"/>
+      <c r="E3" s="96" t="inlineStr">
         <is>
           <t>Sourced fact</t>
         </is>
       </c>
-      <c r="F3" s="94" t="n"/>
-      <c r="G3" s="96" t="inlineStr">
+      <c r="F3" s="95" t="n"/>
+      <c r="G3" s="97" t="inlineStr">
         <is>
           <t>Formula (this sheet)</t>
         </is>
       </c>
-      <c r="H3" s="94" t="n"/>
-      <c r="I3" s="97" t="inlineStr">
-        <is>
-          <t>Formula (other sheet)</t>
-        </is>
-      </c>
-      <c r="J3" s="94" t="n"/>
-      <c r="K3" s="98" t="inlineStr">
+      <c r="H3" s="95" t="n"/>
+      <c r="I3" s="98" t="inlineStr">
+        <is>
+          <t>Dependent value</t>
+        </is>
+      </c>
+      <c r="J3" s="95" t="n"/>
+      <c r="K3" s="99" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="L3" s="94" t="n"/>
+      <c r="L3" s="95" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -10519,7 +10921,7 @@
         <f>Comparables!B14</f>
         <v/>
       </c>
-      <c r="D6" s="88" t="inlineStr">
+      <c r="D6" s="89" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -10535,7 +10937,7 @@
         <f>Comparables!B12</f>
         <v/>
       </c>
-      <c r="D7" s="88" t="inlineStr">
+      <c r="D7" s="89" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -10547,11 +10949,11 @@
           <t>Members per paying creator</t>
         </is>
       </c>
-      <c r="B8" s="63">
+      <c r="B8" s="66">
         <f>B6/B7</f>
         <v/>
       </c>
-      <c r="D8" s="88" t="inlineStr">
+      <c r="D8" s="89" t="inlineStr">
         <is>
           <t>The single most useful benchmark we found: it is measured, not modelled.</t>
         </is>
@@ -10567,7 +10969,7 @@
         <f>Comparables!B9/Comparables!B8</f>
         <v/>
       </c>
-      <c r="D9" s="88" t="inlineStr">
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>Fan ACCOUNTS, not paying fans - most follow free. Shown as an upper bound only.</t>
         </is>
@@ -10582,7 +10984,7 @@
       <c r="B10" s="26" t="n">
         <v>1.06</v>
       </c>
-      <c r="D10" s="88" t="inlineStr">
+      <c r="D10" s="89" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +6% on the Patreon benchmark. Sport audiences are smaller but convert better, because the fan usually does the sport themselves.</t>
         </is>
@@ -10597,7 +10999,7 @@
       <c r="B11" s="26" t="n">
         <v>1.37</v>
       </c>
-      <c r="D11" s="88" t="inlineStr">
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +37%. Much larger followings, much weaker conversion - more paying fans in absolute terms even though a smaller share converts.</t>
         </is>
@@ -10609,11 +11011,11 @@
           <t>→ Niche fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B12" s="99">
+      <c r="B12" s="100">
         <f>B8*B10</f>
         <v/>
       </c>
-      <c r="D12" s="88" t="inlineStr"/>
+      <c r="D12" s="89" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -10621,11 +11023,11 @@
           <t>→ Popular fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B13" s="99">
+      <c r="B13" s="100">
         <f>B8*B11</f>
         <v/>
       </c>
-      <c r="D13" s="88" t="inlineStr"/>
+      <c r="D13" s="89" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -10646,7 +11048,7 @@
       <c r="B15" s="22" t="n">
         <v>4.99</v>
       </c>
-      <c r="D15" s="88" t="inlineStr"/>
+      <c r="D15" s="89" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -10657,7 +11059,7 @@
       <c r="B16" s="22" t="n">
         <v>9.99</v>
       </c>
-      <c r="D16" s="88" t="inlineStr"/>
+      <c r="D16" s="89" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
@@ -10668,7 +11070,7 @@
       <c r="B17" s="22" t="n">
         <v>24.99</v>
       </c>
-      <c r="D17" s="88" t="inlineStr"/>
+      <c r="D17" s="89" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -10679,7 +11081,7 @@
       <c r="B18" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="D18" s="88" t="inlineStr">
+      <c r="D18" s="89" t="inlineStr">
         <is>
           <t>Assumed distribution; replace with the real tier mix after P1.</t>
         </is>
@@ -10694,7 +11096,7 @@
       <c r="B19" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="D19" s="88" t="inlineStr"/>
+      <c r="D19" s="89" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -10705,7 +11107,7 @@
       <c r="B20" s="18" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="88" t="inlineStr"/>
+      <c r="D20" s="89" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -10717,7 +11119,7 @@
         <f>B18+B19+B20</f>
         <v/>
       </c>
-      <c r="D21" s="88" t="inlineStr"/>
+      <c r="D21" s="89" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -10725,11 +11127,11 @@
           <t>→ Weighted ARPU per month</t>
         </is>
       </c>
-      <c r="B22" s="100">
+      <c r="B22" s="101">
         <f>B15*B18+B16*B19+B17*B20</f>
         <v/>
       </c>
-      <c r="D22" s="88" t="inlineStr">
+      <c r="D22" s="89" t="inlineStr">
         <is>
           <t>Cross-check: Patreon reports $6.10 average support and a $8-12 typical band. Landing inside that band from an independent tier build is a good sign.</t>
         </is>
@@ -10745,7 +11147,7 @@
         <f>Comparables!B16</f>
         <v/>
       </c>
-      <c r="D23" s="88" t="inlineStr">
+      <c r="D23" s="89" t="inlineStr">
         <is>
           <t>Published average - below our figure because Patreon's long tail includes many $1-3 tiers. Our EUR 9.49 sits inside their $8-12 typical band.</t>
         </is>
@@ -10760,7 +11162,7 @@
       <c r="B24" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="88" t="inlineStr">
+      <c r="D24" s="89" t="inlineStr">
         <is>
           <t>Niche fans buy knowledge and sit at the tier mix above.</t>
         </is>
@@ -10775,7 +11177,7 @@
       <c r="B25" s="26" t="n">
         <v>0.87</v>
       </c>
-      <c r="D25" s="88" t="inlineStr">
+      <c r="D25" s="89" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: -13%. Popular-sport fans skew to the cheapest tier.</t>
         </is>
@@ -10787,11 +11189,11 @@
           <t>→ Niche ARPU, mature</t>
         </is>
       </c>
-      <c r="B26" s="100">
+      <c r="B26" s="101">
         <f>B22*B24</f>
         <v/>
       </c>
-      <c r="D26" s="88" t="inlineStr"/>
+      <c r="D26" s="89" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -10799,11 +11201,11 @@
           <t>→ Popular ARPU, mature</t>
         </is>
       </c>
-      <c r="B27" s="100">
+      <c r="B27" s="101">
         <f>B22*B25</f>
         <v/>
       </c>
-      <c r="D27" s="88" t="inlineStr"/>
+      <c r="D27" s="89" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -10825,7 +11227,7 @@
         <f>Comparables!B19</f>
         <v/>
       </c>
-      <c r="D29" s="88" t="inlineStr"/>
+      <c r="D29" s="89" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
@@ -10837,7 +11239,7 @@
         <f>Comparables!B20</f>
         <v/>
       </c>
-      <c r="D30" s="88" t="inlineStr"/>
+      <c r="D30" s="89" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
@@ -10849,7 +11251,7 @@
         <f>(B29+B30)/2</f>
         <v/>
       </c>
-      <c r="D31" s="88" t="inlineStr"/>
+      <c r="D31" s="89" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -10861,7 +11263,7 @@
         <f>Comparables!B21</f>
         <v/>
       </c>
-      <c r="D32" s="88" t="inlineStr">
+      <c r="D32" s="89" t="inlineStr">
         <is>
           <t>Patreon: annual patrons churn at one third the monthly rate.</t>
         </is>
@@ -10876,7 +11278,7 @@
       <c r="B33" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="88" t="inlineStr">
+      <c r="D33" s="89" t="inlineStr">
         <is>
           <t>Our target for the season pass. This is the one lever that improves churn without changing the product.</t>
         </is>
@@ -10892,7 +11294,7 @@
         <f>B31*(1-B33)+B31*B32*B33</f>
         <v/>
       </c>
-      <c r="D34" s="88" t="inlineStr">
+      <c r="D34" s="89" t="inlineStr">
         <is>
           <t>What a Patreon-like platform would see with our annual mix.</t>
         </is>
@@ -10907,7 +11309,7 @@
       <c r="B35" s="26" t="n">
         <v>0.55</v>
       </c>
-      <c r="D35" s="88" t="inlineStr">
+      <c r="D35" s="89" t="inlineStr">
         <is>
           <t>OUR CLAIM, UNTESTED, AND THE MOST OPTIMISTIC JUDGEMENT IN THE MODEL: this says niche fans churn 45% SLOWER than the Patreon benchmark, because training content is habitual and competitive seasons create renewal moments. Nothing yet proves it. If it is wrong and we are merely at benchmark, Y10 revenue falls by roughly EUR 7M.</t>
         </is>
@@ -10922,7 +11324,7 @@
       <c r="B36" s="26" t="n">
         <v>0.85</v>
       </c>
-      <c r="D36" s="88" t="inlineStr">
+      <c r="D36" s="89" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: 15% better than benchmark. Impulse follows after a result, with many free substitutes - but still a sport fan rather than a general creator audience.</t>
         </is>
@@ -10934,11 +11336,11 @@
           <t>→ Niche churn, mature</t>
         </is>
       </c>
-      <c r="B37" s="101">
+      <c r="B37" s="102">
         <f>B34*B35</f>
         <v/>
       </c>
-      <c r="D37" s="88" t="inlineStr"/>
+      <c r="D37" s="89" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -10946,11 +11348,11 @@
           <t>→ Popular churn, mature</t>
         </is>
       </c>
-      <c r="B38" s="101">
+      <c r="B38" s="102">
         <f>B34*B36</f>
         <v/>
       </c>
-      <c r="D38" s="88" t="inlineStr"/>
+      <c r="D38" s="89" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
@@ -10972,7 +11374,7 @@
         <f>Comparables!B7/Comparables!B8/12</f>
         <v/>
       </c>
-      <c r="D40" s="88" t="inlineStr">
+      <c r="D40" s="89" t="inlineStr">
         <is>
           <t>Includes dormant accounts, so this is a floor.</t>
         </is>
@@ -10988,7 +11390,7 @@
         <f>Comparables!B15/Comparables!B12/12</f>
         <v/>
       </c>
-      <c r="D41" s="88" t="inlineStr">
+      <c r="D41" s="89" t="inlineStr">
         <is>
           <t>Denominator is creators WITH members, so this is a ceiling.</t>
         </is>
@@ -11000,11 +11402,11 @@
           <t>Stride: modelled niche athlete, mature</t>
         </is>
       </c>
-      <c r="B42" s="100">
+      <c r="B42" s="101">
         <f>B12*B22*(1-Assumptions!$C$40)</f>
         <v/>
       </c>
-      <c r="D42" s="88" t="inlineStr">
+      <c r="D42" s="89" t="inlineStr">
         <is>
           <t>Ours sits between the two, which is where a plausible figure should sit.</t>
         </is>
@@ -11020,7 +11422,7 @@
         <f>Comparables!B11</f>
         <v/>
       </c>
-      <c r="D43" s="88" t="inlineStr">
+      <c r="D43" s="89" t="inlineStr">
         <is>
           <t>THE CAVEAT ON EVERY AVERAGE ABOVE: earnings follow a power law. Totals are unaffected, but the median athlete earns far less than the mean. Do not pitch the mean to an athlete.</t>
         </is>
@@ -11045,7 +11447,7 @@
       <c r="B45" s="26" t="n">
         <v>0.92</v>
       </c>
-      <c r="D45" s="88" t="inlineStr">
+      <c r="D45" s="89" t="inlineStr">
         <is>
           <t>Comparables are published in USD; this model is in EUR. Applied to the per-transaction and monthly creator fees below.</t>
         </is>
@@ -11060,7 +11462,7 @@
       <c r="B46" s="22" t="n">
         <v>300</v>
       </c>
-      <c r="D46" s="88" t="inlineStr">
+      <c r="D46" s="89" t="inlineStr">
         <is>
           <t>Change this to see who is cheapest at any revenue level.</t>
         </is>
@@ -11076,7 +11478,7 @@
         <f>B46*(1-Comparables!B29)-B46/Assumptions!$C$54*Comparables!C29*B45-Comparables!D29*B45</f>
         <v/>
       </c>
-      <c r="D47" s="88" t="inlineStr">
+      <c r="D47" s="89" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -11092,7 +11494,7 @@
         <f>B46*(1-Comparables!B32)-B46/Assumptions!$C$54*Comparables!C32*B45-Comparables!D32*B45</f>
         <v/>
       </c>
-      <c r="D48" s="88" t="inlineStr">
+      <c r="D48" s="89" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -11108,7 +11510,7 @@
         <f>B46*(1-Comparables!B33)-B46/Assumptions!$C$54*Comparables!C33*B45-Comparables!D33*B45</f>
         <v/>
       </c>
-      <c r="D49" s="88" t="inlineStr">
+      <c r="D49" s="89" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -11124,7 +11526,7 @@
         <f>B46*(1-Comparables!B34)-B46/Assumptions!$C$54*Comparables!C34*B45-Comparables!D34*B45</f>
         <v/>
       </c>
-      <c r="D50" s="88" t="inlineStr">
+      <c r="D50" s="89" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -11140,7 +11542,7 @@
         <f>Comparables!D33*B45/((Comparables!B34-Comparables!B33)-Comparables!C33*B45/Assumptions!$C$54)</f>
         <v/>
       </c>
-      <c r="D51" s="88" t="inlineStr">
+      <c r="D51" s="89" t="inlineStr">
         <is>
           <t>Below this, our flat 15% pays the athlete more than Passes' 10% plus fees. Our modelled athlete earns far less than this, so the long tail is on our side of the line.</t>
         </is>
@@ -11162,10 +11564,10 @@
           <t>Population, 34 countries in scope</t>
         </is>
       </c>
-      <c r="B53" s="102" t="n">
+      <c r="B53" s="103" t="n">
         <v>2726.2</v>
       </c>
-      <c r="D53" s="88" t="inlineStr">
+      <c r="D53" s="89" t="inlineStr">
         <is>
           <t>Millions. Eurostat / national statistics offices.</t>
         </is>
@@ -11177,10 +11579,10 @@
           <t>Population, Spain</t>
         </is>
       </c>
-      <c r="B54" s="102" t="n">
+      <c r="B54" s="103" t="n">
         <v>48.6</v>
       </c>
-      <c r="D54" s="88" t="inlineStr">
+      <c r="D54" s="89" t="inlineStr">
         <is>
           <t>Millions.</t>
         </is>
@@ -11195,7 +11597,7 @@
       <c r="B55" s="18" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D55" s="88" t="inlineStr">
+      <c r="D55" s="89" t="inlineStr">
         <is>
           <t>Eurobarometer 525 - Spain sits near the EU average of 55% who exercise at all.</t>
         </is>
@@ -11210,7 +11612,7 @@
       <c r="B56" s="18" t="n">
         <v>0.02</v>
       </c>
-      <c r="D56" s="88" t="inlineStr">
+      <c r="D56" s="89" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: competes, posts publicly, has a following worth sponsoring.</t>
         </is>
@@ -11225,7 +11627,7 @@
       <c r="B57" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="D57" s="88" t="inlineStr">
+      <c r="D57" s="89" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: would monetise if the tooling existed.</t>
         </is>
@@ -11237,11 +11639,11 @@
           <t>→ Addressable athletes, Spain</t>
         </is>
       </c>
-      <c r="B58" s="103">
+      <c r="B58" s="104">
         <f>B54*1000000*B55*B56*B57</f>
         <v/>
       </c>
-      <c r="D58" s="88" t="inlineStr"/>
+      <c r="D58" s="89" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -11249,11 +11651,11 @@
           <t>→ Addressable athletes, all 34 countries</t>
         </is>
       </c>
-      <c r="B59" s="103">
+      <c r="B59" s="104">
         <f>B53*1000000*0.5*B56*B57</f>
         <v/>
       </c>
-      <c r="D59" s="88" t="inlineStr">
+      <c r="D59" s="89" t="inlineStr">
         <is>
           <t>Using a 50% blended participation rate across the 34 countries.</t>
         </is>
@@ -11269,7 +11671,7 @@
         <f>Assumptions!$L$5</f>
         <v/>
       </c>
-      <c r="D60" s="88" t="inlineStr"/>
+      <c r="D60" s="89" t="inlineStr"/>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -11277,11 +11679,11 @@
           <t>→ Y10 penetration of Spain SAM</t>
         </is>
       </c>
-      <c r="B61" s="101">
+      <c r="B61" s="102">
         <f>Assumptions!$L$5/B58</f>
         <v/>
       </c>
-      <c r="D61" s="88" t="inlineStr"/>
+      <c r="D61" s="89" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -11289,11 +11691,11 @@
           <t>→ Y10 penetration of full TAM</t>
         </is>
       </c>
-      <c r="B62" s="101">
+      <c r="B62" s="102">
         <f>Assumptions!$L$5/B59</f>
         <v/>
       </c>
-      <c r="D62" s="88" t="inlineStr">
+      <c r="D62" s="89" t="inlineStr">
         <is>
           <t>If this reads as implausibly high, the athlete trajectory is too aggressive - that is exactly what this block exists to reveal.</t>
         </is>
@@ -11337,44 +11739,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="59" t="inlineStr">
         <is>
           <t>SOURCED = published figure | BENCHMARKED = set against named comparables | DERIVED = computed from other assumptions | ESTIMATE = judgement, no benchmark yet</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="104" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B4" s="104" t="inlineStr">
+      <c r="B4" s="105" t="inlineStr">
         <is>
           <t>Model value</t>
         </is>
       </c>
-      <c r="C4" s="104" t="inlineStr">
+      <c r="C4" s="105" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D4" s="104" t="inlineStr">
+      <c r="D4" s="105" t="inlineStr">
         <is>
           <t>Benchmark / comparable</t>
         </is>
       </c>
-      <c r="E4" s="104" t="inlineStr">
+      <c r="E4" s="105" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F4" s="104" t="inlineStr">
+      <c r="F4" s="105" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="G4" s="104" t="inlineStr">
+      <c r="G4" s="105" t="inlineStr">
         <is>
           <t>What would replace the estimate</t>
         </is>
@@ -11394,7 +11796,7 @@
       <c r="G5" s="14" t="n"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="83" t="inlineStr">
+      <c r="A6" s="84" t="inlineStr">
         <is>
           <t>Take rate on fan revenue</t>
         </is>
@@ -11403,34 +11805,34 @@
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="C6" s="105" t="inlineStr">
+      <c r="C6" s="106" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D6" s="106" t="inlineStr">
+      <c r="D6" s="107" t="inlineStr">
         <is>
           <t>Passes charges 10% but adds $0.30/txn and a $29/month creator fee; OnlyFans, Fansly and Fanfix are all 20%; Patreon 8-12%. A flat 15% with no monthly fee pays an athlete more than Passes for anyone under EUR 1,380/month of fan revenue.</t>
         </is>
       </c>
-      <c r="E6" s="106" t="inlineStr">
+      <c r="E6" s="107" t="inlineStr">
         <is>
           <t>Sacra company profile (Passes); Passes rebrand release, Apr 2026; MEXC platform comparison 2026</t>
         </is>
       </c>
-      <c r="F6" s="107" t="inlineStr">
+      <c r="F6" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G6" s="106" t="inlineStr">
+      <c r="G6" s="107" t="inlineStr">
         <is>
           <t>Nothing. This is a pricing decision and the comparables are public.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="83" t="inlineStr">
+      <c r="A7" s="84" t="inlineStr">
         <is>
           <t>Sponsorship commission, Scout Pro</t>
         </is>
@@ -11439,34 +11841,34 @@
         <f>Assumptions!$C$42</f>
         <v/>
       </c>
-      <c r="C7" s="105" t="inlineStr">
+      <c r="C7" s="106" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D7" s="106" t="inlineStr">
+      <c r="D7" s="107" t="inlineStr">
         <is>
           <t>7% against a 10% base. A sponsor paying EUR 2,988 a year for the tooling is already paying for the relationship, and charging them the full headline rate on every deal as well is charging twice for it. Below the 10-20% an agent takes, which is the point: the sponsor who commits most pays least on each deal.</t>
         </is>
       </c>
-      <c r="E7" s="106" t="inlineStr">
+      <c r="E7" s="107" t="inlineStr">
         <is>
           <t>Priced against the agent range; the discount itself is a pricing decision</t>
         </is>
       </c>
-      <c r="F7" s="107" t="inlineStr">
+      <c r="F7" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G7" s="106" t="inlineStr">
+      <c r="G7" s="107" t="inlineStr">
         <is>
           <t>Nothing to improve. This is a decision, not a measurement.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="83" t="inlineStr">
+      <c r="A8" s="84" t="inlineStr">
         <is>
           <t>Sponsorship commission, Scout Agency</t>
         </is>
@@ -11475,34 +11877,34 @@
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
-      <c r="C8" s="105" t="inlineStr">
+      <c r="C8" s="106" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D8" s="106" t="inlineStr">
+      <c r="D8" s="107" t="inlineStr">
         <is>
           <t>5%, which is half the low end of what an agent charges and a quarter of the high end. The most committed tier pays EUR 11,988 a year, so the deal rate can fall furthest here.</t>
         </is>
       </c>
-      <c r="E8" s="106" t="inlineStr">
+      <c r="E8" s="107" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys, 10-20%</t>
         </is>
       </c>
-      <c r="F8" s="107" t="inlineStr">
+      <c r="F8" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G8" s="106" t="inlineStr">
+      <c r="G8" s="107" t="inlineStr">
         <is>
           <t>Nothing to improve. This is a decision, not a measurement.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="83" t="inlineStr">
+      <c r="A9" s="84" t="inlineStr">
         <is>
           <t>Subscriber share of deal volume</t>
         </is>
@@ -11511,34 +11913,34 @@
         <f>Assumptions!$C$44</f>
         <v/>
       </c>
-      <c r="C9" s="108" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D9" s="106" t="inlineStr">
+      <c r="D9" s="107" t="inlineStr">
         <is>
           <t>Subscribers are assumed to run 2.0x the deal volume of the average sponsor, which with a paid rate of 10-20% puts them at 20-40% of GMV. This is the ONLY estimate in the tiering and it is the one that sets the blended rate, which falls from 9.60% in Y1 to 8.56% by Y10. Deliberately conservative: Scout Pro buys five campaigns against the free tier's one, so 2.0x is well below what the campaign allowance alone would imply. Higher multiples lower the blend further.</t>
         </is>
       </c>
-      <c r="E9" s="106" t="inlineStr">
+      <c r="E9" s="107" t="inlineStr">
         <is>
           <t>None. No tier-level deal volume exists yet, because no tier exists yet</t>
         </is>
       </c>
-      <c r="F9" s="109" t="inlineStr">
+      <c r="F9" s="110" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G9" s="106" t="inlineStr">
+      <c r="G9" s="107" t="inlineStr">
         <is>
           <t>The first year of billing settles it exactly.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="83" t="inlineStr">
+      <c r="A10" s="84" t="inlineStr">
         <is>
           <t>Take rate on sponsorship</t>
         </is>
@@ -11547,101 +11949,101 @@
         <f>Assumptions!$C$41</f>
         <v/>
       </c>
-      <c r="C10" s="105" t="inlineStr">
+      <c r="C10" s="106" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D10" s="106" t="inlineStr">
+      <c r="D10" s="107" t="inlineStr">
         <is>
           <t>Sports agents take 10-20% of an endorsement and 4-10% of a playing contract. On OnlyFans, management agencies take a further 20-50% on top of the platform's 20%.</t>
         </is>
       </c>
-      <c r="E10" s="106" t="inlineStr">
+      <c r="E10" s="107" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys; Aruna Talent agency rate guide 2026</t>
         </is>
       </c>
-      <c r="F10" s="107" t="inlineStr">
+      <c r="F10" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G10" s="106" t="inlineStr">
+      <c r="G10" s="107" t="inlineStr">
         <is>
           <t>Observed deal data once the marketplace is running.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="83" t="inlineStr">
+      <c r="A11" s="84" t="inlineStr">
         <is>
           <t>Suggested tiers 4.99 / 9.99 / 24.99</t>
         </is>
       </c>
-      <c r="B11" s="110" t="inlineStr">
+      <c r="B11" s="111" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C11" s="105" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D11" s="106" t="inlineStr">
+      <c r="D11" s="107" t="inlineStr">
         <is>
           <t>Patreon's typical patronage is quoted at $8-12/month, so the EUR 9.99 anchor sits inside the observed band. EUR 4.99 retains only 54% of our take after payment fees, against 71% at EUR 9.99: which is why the floor matters more than the take rate.</t>
         </is>
       </c>
-      <c r="E11" s="106" t="inlineStr">
+      <c r="E11" s="107" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; independent audits of ~1,200 creators</t>
         </is>
       </c>
-      <c r="F11" s="111" t="inlineStr">
+      <c r="F11" s="112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G11" s="106" t="inlineStr">
+      <c r="G11" s="107" t="inlineStr">
         <is>
           <t>Our own tier mix after P1.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="83" t="inlineStr">
+      <c r="A12" s="84" t="inlineStr">
         <is>
           <t>Season pass / annual billing</t>
         </is>
       </c>
-      <c r="B12" s="110" t="inlineStr">
+      <c r="B12" s="111" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C12" s="112" t="inlineStr">
+      <c r="C12" s="113" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D12" s="106" t="inlineStr">
+      <c r="D12" s="107" t="inlineStr">
         <is>
           <t>Patreon reports that annual patrons churn at ONE THIRD the rate of monthly patrons. This is the single strongest piece of evidence in the plan for pushing annual billing.</t>
         </is>
       </c>
-      <c r="E12" s="106" t="inlineStr">
+      <c r="E12" s="107" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F12" s="107" t="inlineStr">
+      <c r="F12" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G12" s="106" t="inlineStr">
+      <c r="G12" s="107" t="inlineStr">
         <is>
           <t>Already strong. Confirm on our own cohorts.</t>
         </is>
@@ -11661,7 +12063,7 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="83" t="inlineStr">
+      <c r="A14" s="84" t="inlineStr">
         <is>
           <t>Fan ARPU per month</t>
         </is>
@@ -11670,34 +12072,34 @@
         <f>Assumptions!$C$12</f>
         <v/>
       </c>
-      <c r="C14" s="105" t="inlineStr">
+      <c r="C14" s="106" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D14" s="106" t="inlineStr">
+      <c r="D14" s="107" t="inlineStr">
         <is>
           <t>Patreon's average monthly support rose from $5.40 to $6.10 during 2024, with typical patronage quoted at $8-12. Our EUR 8.00-9.50 sits in the upper-middle of that range.</t>
         </is>
       </c>
-      <c r="E14" s="106" t="inlineStr">
+      <c r="E14" s="107" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F14" s="111" t="inlineStr">
+      <c r="F14" s="112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G14" s="106" t="inlineStr">
+      <c r="G14" s="107" t="inlineStr">
         <is>
           <t>Actual ARPU by tier and sport after P1.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="83" t="inlineStr">
+      <c r="A15" s="84" t="inlineStr">
         <is>
           <t>Fan churn per month</t>
         </is>
@@ -11706,34 +12108,34 @@
         <f>Assumptions!$C$13</f>
         <v/>
       </c>
-      <c r="C15" s="108" t="inlineStr">
+      <c r="C15" s="109" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D15" s="106" t="inlineStr">
+      <c r="D15" s="107" t="inlineStr">
         <is>
           <t>OPTIMISTIC AGAINST BENCHMARK. Patreon runs 10-15% monthly. We assume 6-9% (niche) and 9-13% (popular), arguing that training content is habitual and that competitive seasons create natural renewal moments. That argument is currently untested.</t>
         </is>
       </c>
-      <c r="E15" s="106" t="inlineStr">
+      <c r="E15" s="107" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (10-15%/month)</t>
         </is>
       </c>
-      <c r="F15" s="109" t="inlineStr">
+      <c r="F15" s="110" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G15" s="106" t="inlineStr">
+      <c r="G15" s="107" t="inlineStr">
         <is>
           <t>THE most important number to measure in P1. Three months of real cohorts settles it. Until then the conservative case should be treated as the plan.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="83" t="inlineStr">
+      <c r="A16" s="84" t="inlineStr">
         <is>
           <t>Paying fans per monetising athlete</t>
         </is>
@@ -11742,34 +12144,34 @@
         <f>Assumptions!$C$11</f>
         <v/>
       </c>
-      <c r="C16" s="113" t="inlineStr">
+      <c r="C16" s="114" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D16" s="106" t="inlineStr">
+      <c r="D16" s="107" t="inlineStr">
         <is>
           <t>20 rising to 48 over ten years. Cross-check: Patreon creators average $350/month and our modelled niche athlete at maturity earns about EUR 313/month, closely aligned, which is reassuring for an assumption built bottom-up rather than from a comparable.</t>
         </is>
       </c>
-      <c r="E16" s="106" t="inlineStr">
+      <c r="E16" s="107" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (creator average $350/month)</t>
         </is>
       </c>
-      <c r="F16" s="111" t="inlineStr">
+      <c r="F16" s="112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G16" s="106" t="inlineStr">
+      <c r="G16" s="107" t="inlineStr">
         <is>
           <t>Observed fans per athlete, banded by follower count.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="83" t="inlineStr">
+      <c r="A17" s="84" t="inlineStr">
         <is>
           <t>Share of athletes who monetise</t>
         </is>
@@ -11778,64 +12180,64 @@
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="C17" s="108" t="inlineStr">
+      <c r="C17" s="109" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D17" s="106" t="inlineStr">
+      <c r="D17" s="107" t="inlineStr">
         <is>
           <t>28% rising to 50% for niche sports. No direct comparable exists: neither Patreon nor OnlyFans publishes activation rates for creators who sign up but never charge.</t>
         </is>
       </c>
-      <c r="E17" s="106" t="inlineStr">
+      <c r="E17" s="107" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F17" s="109" t="inlineStr">
+      <c r="F17" s="110" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G17" s="106" t="inlineStr">
+      <c r="G17" s="107" t="inlineStr">
         <is>
           <t>Our own activation funnel, available from P1 onward.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="83" t="inlineStr">
+      <c r="A18" s="84" t="inlineStr">
         <is>
           <t>Fan acquisition capacity</t>
         </is>
       </c>
-      <c r="B18" s="110" t="inlineStr">
+      <c r="B18" s="111" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C18" s="108" t="inlineStr">
+      <c r="C18" s="109" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D18" s="106" t="inlineStr">
+      <c r="D18" s="107" t="inlineStr">
         <is>
           <t>An athlete can recruit 30-69 new paying fans a year depending on segment. This ceiling is what makes churn bite in the model: without it, higher churn perversely RAISED revenue, because the year-end target was reachable at any churn rate.</t>
         </is>
       </c>
-      <c r="E18" s="106" t="inlineStr">
+      <c r="E18" s="107" t="inlineStr">
         <is>
           <t>None: introduced to fix a modelling flaw found by stress testing</t>
         </is>
       </c>
-      <c r="F18" s="109" t="inlineStr">
+      <c r="F18" s="110" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G18" s="106" t="inlineStr">
+      <c r="G18" s="107" t="inlineStr">
         <is>
           <t>Observed gross adds per athlete per year.</t>
         </is>
@@ -11855,7 +12257,7 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="83" t="inlineStr">
+      <c r="A20" s="84" t="inlineStr">
         <is>
           <t>PSP percentage fee</t>
         </is>
@@ -11864,34 +12266,34 @@
         <f>Assumptions!$C$50</f>
         <v/>
       </c>
-      <c r="C20" s="112" t="inlineStr">
+      <c r="C20" s="113" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D20" s="106" t="inlineStr">
+      <c r="D20" s="107" t="inlineStr">
         <is>
           <t>Stripe for a Spanish entity: 1.5% + EUR 0.25 on EEA domestic cards, 2.5% on UK cards, 3.25% on non-EEA. 1.9% is the blend for a mostly-European fan base. CORRECTION: an earlier version of this model used the US headline of 2.9% and overstated the largest cost line in the business by about a third.</t>
         </is>
       </c>
-      <c r="E20" s="106" t="inlineStr">
+      <c r="E20" s="107" t="inlineStr">
         <is>
           <t>Stripe published EU/EEA pricing, 2026</t>
         </is>
       </c>
-      <c r="F20" s="107" t="inlineStr">
+      <c r="F20" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G20" s="106" t="inlineStr">
+      <c r="G20" s="107" t="inlineStr">
         <is>
           <t>Interchange-plus terms become negotiable above roughly EUR 5M processed.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="83" t="inlineStr">
+      <c r="A21" s="84" t="inlineStr">
         <is>
           <t>PSP fixed fee per transaction</t>
         </is>
@@ -11900,34 +12302,34 @@
         <f>Assumptions!$C$51</f>
         <v/>
       </c>
-      <c r="C21" s="112" t="inlineStr">
+      <c r="C21" s="113" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D21" s="106" t="inlineStr">
+      <c r="D21" s="107" t="inlineStr">
         <is>
           <t>EUR 0.25 per transaction. On a EUR 4.99 tier that single fee is a third of our take, which is why the tier floor and annual billing move more margin than the take rate does.</t>
         </is>
       </c>
-      <c r="E21" s="106" t="inlineStr">
+      <c r="E21" s="107" t="inlineStr">
         <is>
           <t>Stripe published pricing, 2026</t>
         </is>
       </c>
-      <c r="F21" s="107" t="inlineStr">
+      <c r="F21" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G21" s="106" t="inlineStr">
+      <c r="G21" s="107" t="inlineStr">
         <is>
           <t>Volume renegotiation; annual billing turns twelve fees into one.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="83" t="inlineStr">
+      <c r="A22" s="84" t="inlineStr">
         <is>
           <t>Payout fees</t>
         </is>
@@ -11936,27 +12338,27 @@
         <f>Assumptions!$C$52</f>
         <v/>
       </c>
-      <c r="C22" s="112" t="inlineStr">
+      <c r="C22" s="113" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D22" s="106" t="inlineStr">
+      <c r="D22" s="107" t="inlineStr">
         <is>
           <t>Stripe Connect Express: roughly 0.25% + EUR 0.25 per payout, plus a monthly active-account fee that is not modelled as a separate line.</t>
         </is>
       </c>
-      <c r="E22" s="106" t="inlineStr">
+      <c r="E22" s="107" t="inlineStr">
         <is>
           <t>Stripe Connect pricing, 2026</t>
         </is>
       </c>
-      <c r="F22" s="111" t="inlineStr">
+      <c r="F22" s="112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G22" s="106" t="inlineStr">
+      <c r="G22" s="107" t="inlineStr">
         <is>
           <t>Actual payout frequency once athletes are onboarded.</t>
         </is>
@@ -11976,118 +12378,118 @@
       <c r="G23" s="14" t="n"/>
     </row>
     <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="83" t="inlineStr">
+      <c r="A24" s="84" t="inlineStr">
         <is>
           <t>Sport participation by country</t>
         </is>
       </c>
-      <c r="B24" s="110" t="inlineStr">
+      <c r="B24" s="111" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C24" s="108" t="inlineStr">
+      <c r="C24" s="109" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D24" s="106" t="inlineStr">
+      <c r="D24" s="107" t="inlineStr">
         <is>
           <t>Eurobarometer 525, share who NEVER exercise: Finland 8%, Sweden 12%, Denmark 20%, Poland 65%, Greece 68%, Portugal 73%, EU-27 average 45%. Six of the 34 countries in the index are measured; the other 28 are estimates placed inside that distribution.</t>
         </is>
       </c>
-      <c r="E24" s="106" t="inlineStr">
+      <c r="E24" s="107" t="inlineStr">
         <is>
           <t>Special Eurobarometer 525, Sport and Physical Activity, September 2022</t>
         </is>
       </c>
-      <c r="F24" s="111" t="inlineStr">
+      <c r="F24" s="112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G24" s="106" t="inlineStr">
+      <c r="G24" s="107" t="inlineStr">
         <is>
           <t>Federation licence counts, published annually and free (CSD in Spain).</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="83" t="inlineStr">
+      <c r="A25" s="84" t="inlineStr">
         <is>
           <t>Padel market size</t>
         </is>
       </c>
-      <c r="B25" s="110" t="inlineStr">
+      <c r="B25" s="111" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C25" s="112" t="inlineStr">
+      <c r="C25" s="113" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D25" s="106" t="inlineStr">
+      <c r="D25" s="107" t="inlineStr">
         <is>
           <t>Spain has ~6.0M active players (12.7% of the population), 109,040 federation licences and 17,300+ courts; globally 35M+ players and 77,000+ courts. This is the clearest case for weighting a sport regionally rather than globally, padel scores 77.7 in Spain and 45.1 worldwide.</t>
         </is>
       </c>
-      <c r="E25" s="106" t="inlineStr">
+      <c r="E25" s="107" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="F25" s="107" t="inlineStr">
+      <c r="F25" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G25" s="106" t="inlineStr">
+      <c r="G25" s="107" t="inlineStr">
         <is>
           <t>Annual FIP refresh.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="83" t="inlineStr">
+      <c r="A26" s="84" t="inlineStr">
         <is>
           <t>Sports fandom by country</t>
         </is>
       </c>
-      <c r="B26" s="110" t="inlineStr">
+      <c r="B26" s="111" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C26" s="108" t="inlineStr">
+      <c r="C26" s="109" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D26" s="106" t="inlineStr">
+      <c r="D26" s="107" t="inlineStr">
         <is>
           <t>The weakest layer of the sport index, and it drives both the `demand` and `appetite` signals. Commercial audience panels (Nielsen Sports, YouGov) cost more than the entire Y1-Y2 analytics budget.</t>
         </is>
       </c>
-      <c r="E26" s="106" t="inlineStr">
+      <c r="E26" s="107" t="inlineStr">
         <is>
           <t>None: reasoned estimates only</t>
         </is>
       </c>
-      <c r="F26" s="109" t="inlineStr">
+      <c r="F26" s="110" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G26" s="106" t="inlineStr">
+      <c r="G26" s="107" t="inlineStr">
         <is>
           <t>Our own engagement data per sport per country once connectors are live. This is what makes the index self-improving rather than something anyone could copy.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="83" t="inlineStr">
+      <c r="A27" s="84" t="inlineStr">
         <is>
           <t>Athlete count trajectory</t>
         </is>
@@ -12096,27 +12498,27 @@
         <f>Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="C27" s="108" t="inlineStr">
+      <c r="C27" s="109" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D27" s="106" t="inlineStr">
+      <c r="D27" s="107" t="inlineStr">
         <is>
           <t>250 rising to 8,500 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
         </is>
       </c>
-      <c r="E27" s="106" t="inlineStr">
+      <c r="E27" s="107" t="inlineStr">
         <is>
           <t>None: it is a target</t>
         </is>
       </c>
-      <c r="F27" s="109" t="inlineStr">
+      <c r="F27" s="110" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G27" s="106" t="inlineStr">
+      <c r="G27" s="107" t="inlineStr">
         <is>
           <t>The pre-seed gate tests it directly: 250 athletes and the first paying sponsors.</t>
         </is>
@@ -12136,7 +12538,7 @@
       <c r="G28" s="14" t="n"/>
     </row>
     <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="83" t="inlineStr">
+      <c r="A29" s="84" t="inlineStr">
         <is>
           <t>Athlete CAC</t>
         </is>
@@ -12145,34 +12547,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C29" s="108" t="inlineStr">
+      <c r="C29" s="109" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D29" s="106" t="inlineStr">
+      <c r="D29" s="107" t="inlineStr">
         <is>
           <t>EUR 16-36 for niche, EUR 40-88 for popular. The gap reflects displacing an existing agent relationship versus reaching someone with no representation at all. No published comparable exists for athlete acquisition in this segment.</t>
         </is>
       </c>
-      <c r="E29" s="106" t="inlineStr">
+      <c r="E29" s="107" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F29" s="109" t="inlineStr">
+      <c r="F29" s="110" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G29" s="106" t="inlineStr">
+      <c r="G29" s="107" t="inlineStr">
         <is>
           <t>Measured CAC by channel from the first federation partnership.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="83" t="inlineStr">
+      <c r="A30" s="84" t="inlineStr">
         <is>
           <t>Admission rate, direct applicants</t>
         </is>
@@ -12181,34 +12583,34 @@
         <f>Assumptions!$C$82</f>
         <v/>
       </c>
-      <c r="C30" s="113" t="inlineStr">
+      <c r="C30" s="114" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D30" s="106" t="inlineStr">
+      <c r="D30" s="107" t="inlineStr">
         <is>
           <t>20% of direct applicants are admitted, 25% go to a human, 40% are refused and 15% never finish the form. Not a judgement: it is the ops-load output of scripts/admission_stress.py run over the admission policy itself, so retuning a threshold moves this figure. The sweep asserts the model and the policy stay in step and fails if they drift.</t>
         </is>
       </c>
-      <c r="E30" s="106" t="inlineStr">
+      <c r="E30" s="107" t="inlineStr">
         <is>
           <t>scripts/admission_stress.py, section 7, over a modelled applicant mix</t>
         </is>
       </c>
-      <c r="F30" s="111" t="inlineStr">
+      <c r="F30" s="112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G30" s="106" t="inlineStr">
+      <c r="G30" s="107" t="inlineStr">
         <is>
           <t>Real intake data. The mix the sweep assumes is the soft part, not the arithmetic.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="83" t="inlineStr">
+      <c r="A31" s="84" t="inlineStr">
         <is>
           <t>Admission rate, club-nominated</t>
         </is>
@@ -12217,34 +12619,34 @@
         <f>Assumptions!$C$84</f>
         <v/>
       </c>
-      <c r="C31" s="108" t="inlineStr">
+      <c r="C31" s="109" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D31" s="106" t="inlineStr">
+      <c r="D31" s="107" t="inlineStr">
         <is>
           <t>45% admitted against 20% direct. A verified club's nomination confers a credibility floor of 0.75 x its own legitimacy score, which carries a completed application over the admit line that would otherwise have gone to review. It cannot carry an empty one: no club can supply someone else's date of birth, so the uplift is real but bounded.</t>
         </is>
       </c>
-      <c r="E31" s="106" t="inlineStr">
+      <c r="E31" s="107" t="inlineStr">
         <is>
           <t>None: the mechanism is built and tested, the conversion is not yet measured</t>
         </is>
       </c>
-      <c r="F31" s="109" t="inlineStr">
+      <c r="F31" s="110" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G31" s="106" t="inlineStr">
+      <c r="G31" s="107" t="inlineStr">
         <is>
           <t>The first federation partnership: nominated applicants are tagged, so this is measurable from day one of it.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="83" t="inlineStr">
+      <c r="A32" s="84" t="inlineStr">
         <is>
           <t>Athlete verification cost</t>
         </is>
@@ -12253,34 +12655,34 @@
         <f>Assumptions!$C$87</f>
         <v/>
       </c>
-      <c r="C32" s="113" t="inlineStr">
+      <c r="C32" s="114" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D32" s="106" t="inlineStr">
+      <c r="D32" s="107" t="inlineStr">
         <is>
           <t>Four minutes per manual review, priced at the same loaded salary the People line uses, over 1,700 productive hours. Peaks at EUR 47k and 0.64 reviewer-FTE in Y10, which is the finding rather than the cost: verification is not a money problem at this scale. The reason to automate it is latency: an athlete sitting in the queue is not listed, not matchable and not earning.</t>
         </is>
       </c>
-      <c r="E32" s="106" t="inlineStr">
+      <c r="E32" s="107" t="inlineStr">
         <is>
           <t>Derived from the sweep's review volume and the model's own salary line</t>
         </is>
       </c>
-      <c r="F32" s="111" t="inlineStr">
+      <c r="F32" s="112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G32" s="106" t="inlineStr">
+      <c r="G32" s="107" t="inlineStr">
         <is>
           <t>Timing real reviews. Four minutes is an estimate of a mechanical task.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="83" t="inlineStr">
+      <c r="A33" s="84" t="inlineStr">
         <is>
           <t>Athlete CAC vs the funnel</t>
         </is>
@@ -12289,34 +12691,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C33" s="108" t="inlineStr">
+      <c r="C33" s="109" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D33" s="106" t="inlineStr">
+      <c r="D33" s="107" t="inlineStr">
         <is>
           <t>Deliberately NOT multiplied by the admission funnel. Segment CAC is defined as the cost of landing one athlete ON the platform, so scaling it by 1/admission-rate would charge the same money twice. The Costs sheet carries a memo line showing what that CAC works out to per application (EUR 3.40 in Y1 rising to EUR 22), the figure to hold against what a channel actually charges per name reached.</t>
         </is>
       </c>
-      <c r="E33" s="106" t="inlineStr">
+      <c r="E33" s="107" t="inlineStr">
         <is>
           <t>None: this is a definitional choice, made explicit so it is not silently reversed</t>
         </is>
       </c>
-      <c r="F33" s="109" t="inlineStr">
+      <c r="F33" s="110" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G33" s="106" t="inlineStr">
+      <c r="G33" s="107" t="inlineStr">
         <is>
           <t>Channel-level spend against applications, which the funnel now records.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="83" t="inlineStr">
+      <c r="A34" s="84" t="inlineStr">
         <is>
           <t>Loaded salary, Spain</t>
         </is>
@@ -12325,34 +12727,34 @@
         <f>Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="C34" s="105" t="inlineStr">
+      <c r="C34" s="106" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D34" s="106" t="inlineStr">
+      <c r="D34" s="107" t="inlineStr">
         <is>
           <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k, around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
         </is>
       </c>
-      <c r="E34" s="106" t="inlineStr">
+      <c r="E34" s="107" t="inlineStr">
         <is>
           <t>Spanish Seguridad Social employer contribution rates</t>
         </is>
       </c>
-      <c r="F34" s="111" t="inlineStr">
+      <c r="F34" s="112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G34" s="106" t="inlineStr">
+      <c r="G34" s="107" t="inlineStr">
         <is>
           <t>Actual offers accepted.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="83" t="inlineStr">
+      <c r="A35" s="84" t="inlineStr">
         <is>
           <t>AWS infrastructure</t>
         </is>
@@ -12361,34 +12763,34 @@
         <f>Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="C35" s="105" t="inlineStr">
+      <c r="C35" s="106" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D35" s="106" t="inlineStr">
+      <c r="D35" s="107" t="inlineStr">
         <is>
           <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
         </is>
       </c>
-      <c r="E35" s="106" t="inlineStr">
+      <c r="E35" s="107" t="inlineStr">
         <is>
           <t>AWS published list pricing, 2026</t>
         </is>
       </c>
-      <c r="F35" s="111" t="inlineStr">
+      <c r="F35" s="112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G35" s="106" t="inlineStr">
+      <c r="G35" s="107" t="inlineStr">
         <is>
           <t>Actual bills; commit to Savings Plans once usage is stable.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="83" t="inlineStr">
+      <c r="A36" s="84" t="inlineStr">
         <is>
           <t>Media egress</t>
         </is>
@@ -12397,34 +12799,34 @@
         <f>Assumptions!$C$60</f>
         <v/>
       </c>
-      <c r="C36" s="112" t="inlineStr">
+      <c r="C36" s="113" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D36" s="106" t="inlineStr">
+      <c r="D36" s="107" t="inlineStr">
         <is>
           <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year, the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
         </is>
       </c>
-      <c r="E36" s="106" t="inlineStr">
+      <c r="E36" s="107" t="inlineStr">
         <is>
           <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
         </is>
       </c>
-      <c r="F36" s="107" t="inlineStr">
+      <c r="F36" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G36" s="106" t="inlineStr">
+      <c r="G36" s="107" t="inlineStr">
         <is>
           <t>Nothing. Both are published.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="83" t="inlineStr">
+      <c r="A37" s="84" t="inlineStr">
         <is>
           <t>Moderation cost</t>
         </is>
@@ -12433,27 +12835,27 @@
         <f>Assumptions!$C$62</f>
         <v/>
       </c>
-      <c r="C37" s="108" t="inlineStr">
+      <c r="C37" s="109" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D37" s="106" t="inlineStr">
+      <c r="D37" s="107" t="inlineStr">
         <is>
           <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
         </is>
       </c>
-      <c r="E37" s="106" t="inlineStr">
+      <c r="E37" s="107" t="inlineStr">
         <is>
           <t>None cited</t>
         </is>
       </c>
-      <c r="F37" s="109" t="inlineStr">
+      <c r="F37" s="110" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G37" s="106" t="inlineStr">
+      <c r="G37" s="107" t="inlineStr">
         <is>
           <t>Vendor quotes once P2 scope is fixed.</t>
         </is>
@@ -12473,7 +12875,7 @@
       <c r="G38" s="14" t="n"/>
     </row>
     <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="83" t="inlineStr">
+      <c r="A39" s="84" t="inlineStr">
         <is>
           <t>Corporate tax rates</t>
         </is>
@@ -12482,34 +12884,34 @@
         <f>Assumptions!$C$77</f>
         <v/>
       </c>
-      <c r="C39" s="112" t="inlineStr">
+      <c r="C39" s="113" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D39" s="106" t="inlineStr">
+      <c r="D39" s="107" t="inlineStr">
         <is>
           <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
         </is>
       </c>
-      <c r="E39" s="106" t="inlineStr">
+      <c r="E39" s="107" t="inlineStr">
         <is>
           <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
         </is>
       </c>
-      <c r="F39" s="107" t="inlineStr">
+      <c r="F39" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G39" s="106" t="inlineStr">
+      <c r="G39" s="107" t="inlineStr">
         <is>
           <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="83" t="inlineStr">
+      <c r="A40" s="84" t="inlineStr">
         <is>
           <t>Risk-free rate</t>
         </is>
@@ -12518,71 +12920,71 @@
         <f>Assumptions!$C$97</f>
         <v/>
       </c>
-      <c r="C40" s="112" t="inlineStr">
+      <c r="C40" s="113" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D40" s="106" t="inlineStr">
+      <c r="D40" s="107" t="inlineStr">
         <is>
           <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
         </is>
       </c>
-      <c r="E40" s="106" t="inlineStr">
+      <c r="E40" s="107" t="inlineStr">
         <is>
           <t>Spanish 10Y government bond yield</t>
         </is>
       </c>
-      <c r="F40" s="107" t="inlineStr">
+      <c r="F40" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G40" s="106" t="inlineStr">
+      <c r="G40" s="107" t="inlineStr">
         <is>
           <t>Refresh at the date of any raise.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="83" t="inlineStr">
+      <c r="A41" s="84" t="inlineStr">
         <is>
           <t>WACC / discount rate</t>
         </is>
       </c>
-      <c r="B41" s="110" t="inlineStr">
+      <c r="B41" s="111" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C41" s="105" t="inlineStr">
+      <c r="C41" s="106" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D41" s="106" t="inlineStr">
+      <c r="D41" s="107" t="inlineStr">
         <is>
           <t>25%, against a published mature-company anchor of 6.01%. Damodaran's European cost of capital dataset puts Software (Internet) at 6.01% in euros across 23 listed firms, and the European market ex-financials at 6.59%. Those are costs of capital for mature listed companies; this is a pre-revenue venture, and the 19-point gap is the stage premium. It is stated rather than buried because it is the largest single judgement in the valuation. Damodaran publishes no dataset for venture-stage rates, so the premium itself is convention (20-35% is the usual range) and not a sourced figure. The sensitivity grid runs 20-30% because this is arguable rather than knowable.</t>
         </is>
       </c>
-      <c r="E41" s="106" t="inlineStr">
+      <c r="E41" s="107" t="inlineStr">
         <is>
           <t>Aswath Damodaran, NYU Stern, Cost of Capital by Industry (Europe), updated 5 January 2026</t>
         </is>
       </c>
-      <c r="F41" s="111" t="inlineStr">
+      <c r="F41" s="112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G41" s="106" t="inlineStr">
+      <c r="G41" s="107" t="inlineStr">
         <is>
           <t>An actual term sheet prices this for you.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="83" t="inlineStr">
+      <c r="A42" s="84" t="inlineStr">
         <is>
           <t>Exit revenue multiple</t>
         </is>
@@ -12591,34 +12993,34 @@
         <f>Assumptions!$C$96</f>
         <v/>
       </c>
-      <c r="C42" s="105" t="inlineStr">
+      <c r="C42" s="106" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D42" s="106" t="inlineStr">
+      <c r="D42" s="107" t="inlineStr">
         <is>
           <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
         </is>
       </c>
-      <c r="E42" s="106" t="inlineStr">
+      <c r="E42" s="107" t="inlineStr">
         <is>
           <t>Public marketplace and SaaS trading multiples</t>
         </is>
       </c>
-      <c r="F42" s="111" t="inlineStr">
+      <c r="F42" s="112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G42" s="106" t="inlineStr">
+      <c r="G42" s="107" t="inlineStr">
         <is>
           <t>Comparable private transactions nearer an exit.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="83" t="inlineStr">
+      <c r="A43" s="84" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
@@ -12627,27 +13029,27 @@
         <f>Assumptions!$C$95</f>
         <v/>
       </c>
-      <c r="C43" s="105" t="inlineStr">
+      <c r="C43" s="106" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D43" s="106" t="inlineStr">
+      <c r="D43" s="107" t="inlineStr">
         <is>
           <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
         </is>
       </c>
-      <c r="E43" s="106" t="inlineStr">
+      <c r="E43" s="107" t="inlineStr">
         <is>
           <t>Standard DCF convention</t>
         </is>
       </c>
-      <c r="F43" s="111" t="inlineStr">
+      <c r="F43" s="112" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G43" s="106" t="inlineStr">
+      <c r="G43" s="107" t="inlineStr">
         <is>
           <t>Nothing: it is a convention, and the grid shows its effect.</t>
         </is>
@@ -12667,112 +13069,112 @@
       <c r="G44" s="14" t="n"/>
     </row>
     <row r="45" ht="58" customHeight="1">
-      <c r="A45" s="83" t="inlineStr">
+      <c r="A45" s="84" t="inlineStr">
         <is>
           <t>Payout age floor</t>
         </is>
       </c>
-      <c r="B45" s="110" t="inlineStr">
+      <c r="B45" s="111" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C45" s="112" t="inlineStr">
+      <c r="C45" s="113" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D45" s="106" t="inlineStr">
+      <c r="D45" s="107" t="inlineStr">
         <is>
           <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
         </is>
       </c>
-      <c r="E45" s="106" t="inlineStr">
+      <c r="E45" s="107" t="inlineStr">
         <is>
           <t>Stripe Connect documentation</t>
         </is>
       </c>
-      <c r="F45" s="107" t="inlineStr">
+      <c r="F45" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G45" s="106" t="inlineStr">
+      <c r="G45" s="107" t="inlineStr">
         <is>
           <t>Nothing: it is a hard platform rule.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
-      <c r="A46" s="83" t="inlineStr">
+      <c r="A46" s="84" t="inlineStr">
         <is>
           <t>Digital consent age, Spain</t>
         </is>
       </c>
-      <c r="B46" s="110" t="inlineStr">
+      <c r="B46" s="111" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C46" s="112" t="inlineStr">
+      <c r="C46" s="113" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D46" s="106" t="inlineStr">
+      <c r="D46" s="107" t="inlineStr">
         <is>
           <t>14 today under LOPDGDD Art. 7. A draft Organic Law on the Protection of Minors in Digital Environments would raise it to 16 and make age verification mandatory, which is why 16 is the forward-compatible floor for an account.</t>
         </is>
       </c>
-      <c r="E46" s="106" t="inlineStr">
+      <c r="E46" s="107" t="inlineStr">
         <is>
           <t>LOPDGDD Art. 7; draft Organic Law, Council of Ministers, March 2025</t>
         </is>
       </c>
-      <c r="F46" s="107" t="inlineStr">
+      <c r="F46" s="108" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G46" s="106" t="inlineStr">
+      <c r="G46" s="107" t="inlineStr">
         <is>
           <t>Track the bill through Parliament.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="114" t="inlineStr">
+      <c r="A48" s="115" t="inlineStr">
         <is>
           <t>THE THREE ASSUMPTIONS MOST LIKELY TO BE WRONG</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="115" t="inlineStr">
+      <c r="A49" s="116" t="inlineStr">
         <is>
           <t>1. Fan churn. We assume 6-13%/month; Patreon reports 10-15%. If Patreon is right, Y10 revenue falls from about EUR 58M to EUR 51M and the capital requirement roughly doubles.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="115" t="inlineStr">
+      <c r="A50" s="116" t="inlineStr">
         <is>
           <t>2. Athlete count. The trajectory is a target, not a forecast, and everything scales off it.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="115" t="inlineStr">
+      <c r="A51" s="116" t="inlineStr">
         <is>
           <t>3. Share of athletes who monetise. No published comparable exists at all.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="116" t="inlineStr"/>
+      <c r="A52" s="117" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="116" t="inlineStr">
+      <c r="A53" s="117" t="inlineStr">
         <is>
           <t>All three are answered by the same thing: three months of real cohort data from P1.</t>
         </is>
@@ -17686,47 +18088,47 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>avg x churn x 12</t>
-        </is>
-      </c>
-      <c r="C21" s="19">
-        <f>C20*12*Assumptions!C13</f>
-        <v/>
-      </c>
-      <c r="D21" s="19">
-        <f>D20*12*Assumptions!D13</f>
-        <v/>
-      </c>
-      <c r="E21" s="19">
-        <f>E20*12*Assumptions!E13</f>
-        <v/>
-      </c>
-      <c r="F21" s="19">
-        <f>F20*12*Assumptions!F13</f>
-        <v/>
-      </c>
-      <c r="G21" s="19">
-        <f>G20*12*Assumptions!G13</f>
-        <v/>
-      </c>
-      <c r="H21" s="19">
-        <f>H20*12*Assumptions!H13</f>
-        <v/>
-      </c>
-      <c r="I21" s="19">
-        <f>I20*12*Assumptions!I13</f>
-        <v/>
-      </c>
-      <c r="J21" s="19">
-        <f>J20*12*Assumptions!J13</f>
-        <v/>
-      </c>
-      <c r="K21" s="19">
-        <f>K20*12*Assumptions!K13</f>
-        <v/>
-      </c>
-      <c r="L21" s="19">
-        <f>L20*12*Assumptions!L13</f>
+          <t>opening + gross adds - closing</t>
+        </is>
+      </c>
+      <c r="C21" s="43">
+        <f>C18-C17</f>
+        <v/>
+      </c>
+      <c r="D21" s="43">
+        <f>C17+D18-D17</f>
+        <v/>
+      </c>
+      <c r="E21" s="43">
+        <f>D17+E18-E17</f>
+        <v/>
+      </c>
+      <c r="F21" s="43">
+        <f>E17+F18-F17</f>
+        <v/>
+      </c>
+      <c r="G21" s="43">
+        <f>F17+G18-G17</f>
+        <v/>
+      </c>
+      <c r="H21" s="43">
+        <f>G17+H18-H17</f>
+        <v/>
+      </c>
+      <c r="I21" s="43">
+        <f>H17+I18-I17</f>
+        <v/>
+      </c>
+      <c r="J21" s="43">
+        <f>I17+J18-J17</f>
+        <v/>
+      </c>
+      <c r="K21" s="43">
+        <f>J17+K18-K17</f>
+        <v/>
+      </c>
+      <c r="L21" s="43">
+        <f>K17+L18-L17</f>
         <v/>
       </c>
     </row>
@@ -18312,47 +18714,47 @@
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>avg x churn x 12</t>
-        </is>
-      </c>
-      <c r="C35" s="19">
-        <f>C34*12*Assumptions!C25</f>
-        <v/>
-      </c>
-      <c r="D35" s="19">
-        <f>D34*12*Assumptions!D25</f>
-        <v/>
-      </c>
-      <c r="E35" s="19">
-        <f>E34*12*Assumptions!E25</f>
-        <v/>
-      </c>
-      <c r="F35" s="19">
-        <f>F34*12*Assumptions!F25</f>
-        <v/>
-      </c>
-      <c r="G35" s="19">
-        <f>G34*12*Assumptions!G25</f>
-        <v/>
-      </c>
-      <c r="H35" s="19">
-        <f>H34*12*Assumptions!H25</f>
-        <v/>
-      </c>
-      <c r="I35" s="19">
-        <f>I34*12*Assumptions!I25</f>
-        <v/>
-      </c>
-      <c r="J35" s="19">
-        <f>J34*12*Assumptions!J25</f>
-        <v/>
-      </c>
-      <c r="K35" s="19">
-        <f>K34*12*Assumptions!K25</f>
-        <v/>
-      </c>
-      <c r="L35" s="19">
-        <f>L34*12*Assumptions!L25</f>
+          <t>opening + gross adds - closing</t>
+        </is>
+      </c>
+      <c r="C35" s="43">
+        <f>C32-C31</f>
+        <v/>
+      </c>
+      <c r="D35" s="43">
+        <f>C31+D32-D31</f>
+        <v/>
+      </c>
+      <c r="E35" s="43">
+        <f>D31+E32-E31</f>
+        <v/>
+      </c>
+      <c r="F35" s="43">
+        <f>E31+F32-F31</f>
+        <v/>
+      </c>
+      <c r="G35" s="43">
+        <f>F31+G32-G31</f>
+        <v/>
+      </c>
+      <c r="H35" s="43">
+        <f>G31+H32-H31</f>
+        <v/>
+      </c>
+      <c r="I35" s="43">
+        <f>H31+I32-I31</f>
+        <v/>
+      </c>
+      <c r="J35" s="43">
+        <f>I31+J32-J31</f>
+        <v/>
+      </c>
+      <c r="K35" s="43">
+        <f>J31+K32-K31</f>
+        <v/>
+      </c>
+      <c r="L35" s="43">
+        <f>K31+L32-L31</f>
         <v/>
       </c>
     </row>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -11785,7 +11785,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">: PRICING &amp; TAKE RATE: </t>
+          <t>PRICING &amp; TAKE RATE</t>
         </is>
       </c>
       <c r="B5" s="14" t="n"/>
@@ -12052,7 +12052,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">: FAN ECONOMICS: </t>
+          <t>FAN ECONOMICS</t>
         </is>
       </c>
       <c r="B13" s="14" t="n"/>
@@ -12246,7 +12246,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">: PAYMENT RAILS: </t>
+          <t>PAYMENT RAILS</t>
         </is>
       </c>
       <c r="B19" s="14" t="n"/>
@@ -12367,7 +12367,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">: MARKET SIZING: </t>
+          <t>MARKET SIZING</t>
         </is>
       </c>
       <c r="B23" s="14" t="n"/>
@@ -12527,7 +12527,7 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">: COSTS: </t>
+          <t>COSTS</t>
         </is>
       </c>
       <c r="B28" s="14" t="n"/>
@@ -12864,7 +12864,7 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">: TAX, CAPITAL &amp; VALUATION: </t>
+          <t>TAX, CAPITAL &amp; VALUATION</t>
         </is>
       </c>
       <c r="B38" s="14" t="n"/>
@@ -13058,7 +13058,7 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">: COMPLIANCE: </t>
+          <t>COMPLIANCE</t>
         </is>
       </c>
       <c r="B44" s="14" t="n"/>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -6396,25 +6396,25 @@
         </is>
       </c>
       <c r="C5" s="24" t="n">
-        <v>15209.65213450907</v>
+        <v>2146.380000000001</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>78186.9800289897</v>
+        <v>68373.78390534884</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>288002.6712945602</v>
+        <v>286818.7980145874</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>703679.007100631</v>
+        <v>703667.3557595818</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>1321353.147539588</v>
+        <v>1321350.106984068</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>2124049.313694932</v>
+        <v>2124048.476059291</v>
       </c>
       <c r="I5" s="24" t="n">
-        <v>3013163.386035815</v>
+        <v>3013163.222831439</v>
       </c>
       <c r="J5" s="24" t="n">
         <v>3853438.128678631</v>
@@ -6560,25 +6560,25 @@
         </is>
       </c>
       <c r="C10" s="24" t="n">
-        <v>8788.279804347037</v>
+        <v>3422.709052287581</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>35884.10661722298</v>
+        <v>31857.28686143998</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>107180.4277627578</v>
+        <v>106695.0205154586</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>235202.2755595208</v>
+        <v>235197.4837750249</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>421379.4560848573</v>
+        <v>421378.2064945769</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>658989.9166519806</v>
+        <v>658989.5725221956</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>923988.6616917688</v>
+        <v>923988.594663968</v>
       </c>
       <c r="J10" s="24" t="n">
         <v>1175852.257663428</v>
@@ -6724,25 +6724,25 @@
         </is>
       </c>
       <c r="C15" s="24" t="n">
-        <v>6421.372330162036</v>
+        <v>-1276.329052287581</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>42302.87341176671</v>
+        <v>36516.49704390886</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>180822.2435318024</v>
+        <v>180123.7774991288</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>468476.7315411102</v>
+        <v>468469.8719845568</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>899973.6914547306</v>
+        <v>899971.9004894909</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>1465059.397042952</v>
+        <v>1465058.903537095</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>2089174.724344046</v>
+        <v>2089174.628167471</v>
       </c>
       <c r="J15" s="24" t="n">
         <v>2677585.871015203</v>
@@ -6888,25 +6888,25 @@
         </is>
       </c>
       <c r="C20" s="24" t="n">
-        <v>77716.77217076073</v>
+        <v>76671.7104</v>
       </c>
       <c r="D20" s="24" t="n">
-        <v>153773.2084023192</v>
+        <v>152988.1527124279</v>
       </c>
       <c r="E20" s="24" t="n">
-        <v>320381.8137035648</v>
+        <v>320287.1038411669</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>554399.1205680504</v>
+        <v>554398.1884607666</v>
       </c>
       <c r="G20" s="24" t="n">
-        <v>882757.851803167</v>
+        <v>882757.6085587254</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>1225415.145095594</v>
+        <v>1225415.078084743</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>1554635.070882865</v>
+        <v>1554635.057826515</v>
       </c>
       <c r="J20" s="24" t="n">
         <v>1825600.650294291</v>
@@ -7052,25 +7052,25 @@
         </is>
       </c>
       <c r="C25" s="24" t="n">
-        <v>-71295.39984059869</v>
+        <v>-77948.03945228757</v>
       </c>
       <c r="D25" s="24" t="n">
-        <v>-111470.3349905525</v>
+        <v>-116471.655668519</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>-139559.5701717624</v>
+        <v>-140163.3263420382</v>
       </c>
       <c r="F25" s="24" t="n">
-        <v>-85922.38902694022</v>
+        <v>-85928.31647620973</v>
       </c>
       <c r="G25" s="24" t="n">
-        <v>17215.83965156355</v>
+        <v>17214.2919307655</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>239644.2519473576</v>
+        <v>239643.8254523519</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>534539.6534611809</v>
+        <v>534539.5703409559</v>
       </c>
       <c r="J25" s="24" t="n">
         <v>851985.2207209126</v>
@@ -7216,25 +7216,25 @@
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>1286.151087758587</v>
+        <v>0</v>
       </c>
       <c r="D30" s="17" t="n">
-        <v>5092.646841736267</v>
+        <v>4911.429846669657</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>14334.42936888351</v>
+        <v>14332.92579479482</v>
       </c>
       <c r="F30" s="17" t="n">
-        <v>28169.28576456208</v>
+        <v>28168.91439619112</v>
       </c>
       <c r="G30" s="17" t="n">
-        <v>46066.06447500147</v>
+        <v>46065.96637221651</v>
       </c>
       <c r="H30" s="17" t="n">
-        <v>67882.20782167294</v>
+        <v>67882.18011454886</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>92005.20000000001</v>
+        <v>92005.2</v>
       </c>
       <c r="J30" s="17" t="n">
         <v>111619.44</v>
@@ -7380,25 +7380,25 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>816.010230758603</v>
+        <v>0</v>
       </c>
       <c r="D35" s="17" t="n">
-        <v>3685.701513762201</v>
+        <v>3094.840947139147</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>10913.21808130112</v>
+        <v>10844.20522362626</v>
       </c>
       <c r="F35" s="17" t="n">
-        <v>23047.08309296033</v>
+        <v>23046.31971183246</v>
       </c>
       <c r="G35" s="17" t="n">
-        <v>39464.36338620399</v>
+        <v>39464.16928088696</v>
       </c>
       <c r="H35" s="17" t="n">
-        <v>59832.18166912212</v>
+        <v>59832.12887237647</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>82914.56519122265</v>
+        <v>82914.55503292556</v>
       </c>
       <c r="J35" s="17" t="n">
         <v>104177.5514465162</v>
@@ -7544,25 +7544,25 @@
         </is>
       </c>
       <c r="C40" s="24" t="n">
-        <v>103849.7308967272</v>
+        <v>16761.25</v>
       </c>
       <c r="D40" s="24" t="n">
-        <v>506193.5751265979</v>
+        <v>440772.267635659</v>
       </c>
       <c r="E40" s="24" t="n">
-        <v>1751195.741743291</v>
+        <v>1743303.253210139</v>
       </c>
       <c r="F40" s="24" t="n">
-        <v>4330016.769991406</v>
+        <v>4329939.094384411</v>
       </c>
       <c r="G40" s="24" t="n">
-        <v>8521278.947970588</v>
+        <v>8521258.677600455</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>14372383.76169955</v>
+        <v>14372378.17746194</v>
       </c>
       <c r="I40" s="24" t="n">
-        <v>20940263.82626543</v>
+        <v>20940262.73823626</v>
       </c>
       <c r="J40" s="24" t="n">
         <v>27265422.25706821</v>
@@ -8218,7 +8218,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="24" t="n">
-        <v>6952.807654537234</v>
+        <v>5112.952467752815</v>
       </c>
       <c r="J60" s="24" t="n">
         <v>96657.78310813688</v>
@@ -8364,25 +8364,25 @@
         </is>
       </c>
       <c r="C65" s="24" t="n">
-        <v>-75095.39984059869</v>
+        <v>-81748.03945228757</v>
       </c>
       <c r="D65" s="24" t="n">
-        <v>-120470.3349905525</v>
+        <v>-125471.655668519</v>
       </c>
       <c r="E65" s="24" t="n">
-        <v>-157559.5701717624</v>
+        <v>-158163.3263420382</v>
       </c>
       <c r="F65" s="24" t="n">
-        <v>-112922.3890269402</v>
+        <v>-112928.3164762097</v>
       </c>
       <c r="G65" s="24" t="n">
-        <v>-30984.16034843645</v>
+        <v>-30985.7080692345</v>
       </c>
       <c r="H65" s="24" t="n">
-        <v>152844.2519473576</v>
+        <v>152843.8254523519</v>
       </c>
       <c r="I65" s="24" t="n">
-        <v>383586.8458066436</v>
+        <v>385426.6178732031</v>
       </c>
       <c r="J65" s="24" t="n">
         <v>547727.4376127757</v>
@@ -8528,28 +8528,28 @@
         </is>
       </c>
       <c r="C70" s="24" t="n">
-        <v>-71552.95944772632</v>
+        <v>-82622.05873447936</v>
       </c>
       <c r="D70" s="24" t="n">
-        <v>-103369.3973795417</v>
+        <v>-107271.9252362997</v>
       </c>
       <c r="E70" s="24" t="n">
-        <v>-105070.5356489066</v>
+        <v>-102756.8714386108</v>
       </c>
       <c r="F70" s="24" t="n">
-        <v>-12309.89736107869</v>
+        <v>-11919.51744798329</v>
       </c>
       <c r="G70" s="24" t="n">
-        <v>113157.2481145281</v>
+        <v>113158.6115469746</v>
       </c>
       <c r="H70" s="24" t="n">
-        <v>329870.0623134766</v>
+        <v>329870.3805864519</v>
       </c>
       <c r="I70" s="24" t="n">
-        <v>577578.3683435448</v>
+        <v>579418.3684233045</v>
       </c>
       <c r="J70" s="24" t="n">
-        <v>732667.1546823786</v>
+        <v>732667.2098588719</v>
       </c>
       <c r="K70" s="24" t="n">
         <v>828273.2012880694</v>
@@ -13472,7 +13472,7 @@
         </is>
       </c>
       <c r="C10" s="18" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="D10" s="18" t="n">
         <v>0.32</v>
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="D22" s="18" t="n">
         <v>0.17</v>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -362,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -428,6 +428,9 @@
     <xf numFmtId="164" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="16" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="15" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="11" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1934,7 +1937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1949,6 +1952,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="64" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2103,6 +2107,11 @@
       <c r="L5" s="24" t="n">
         <v>0</v>
       </c>
+      <c r="M5" s="63" t="inlineStr">
+        <is>
+          <t>Both rounds are priced against Sponsoo, the closest comparable there is: our pre-seed at EUR 1.8M against their EUR 1.55M seed, and the growth round at EUR 12M against their EUR 15.9M Series A.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -2211,7 +2220,7 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>Advisory grant</t>
+          <t>Athlete partner equity</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
@@ -2220,7 +2229,7 @@
         </is>
       </c>
       <c r="C8" s="18" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D8" s="18" t="n">
         <v>0</v>
@@ -2249,6 +2258,11 @@
       <c r="L8" s="18" t="n">
         <v>0</v>
       </c>
+      <c r="M8" s="63" t="inlineStr">
+        <is>
+          <t>5% to an athlete partner at the pre-seed, paid in equity rather than cash. The anchor athlete the pre-seed gate depends on: they put their name and their audience behind a product that does not exist yet. Four-year vesting, one-year cliff.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -2290,6 +2304,11 @@
       </c>
       <c r="L9" s="18" t="n">
         <v>0</v>
+      </c>
+      <c r="M9" s="63" t="inlineStr">
+        <is>
+          <t>Employee Stock Option Pool: 10% reserved for employee options at the growth round, which is when there is institutional money and people worth keeping.</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -2568,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>0.5</v>
@@ -2816,43 +2835,43 @@
           <t>FTE</t>
         </is>
       </c>
-      <c r="C12" s="63">
+      <c r="C12" s="64">
         <f>SUM(C5:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="64">
         <f>SUM(D5:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="63">
+      <c r="E12" s="64">
         <f>SUM(E5:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="63">
+      <c r="F12" s="64">
         <f>SUM(F5:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="63">
+      <c r="G12" s="64">
         <f>SUM(G5:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="63">
+      <c r="H12" s="64">
         <f>SUM(H5:H11)</f>
         <v/>
       </c>
-      <c r="I12" s="63">
+      <c r="I12" s="64">
         <f>SUM(I5:I11)</f>
         <v/>
       </c>
-      <c r="J12" s="63">
+      <c r="J12" s="64">
         <f>SUM(J5:J11)</f>
         <v/>
       </c>
-      <c r="K12" s="63">
+      <c r="K12" s="64">
         <f>SUM(K5:K11)</f>
         <v/>
       </c>
-      <c r="L12" s="63">
+      <c r="L12" s="64">
         <f>SUM(L5:L11)</f>
         <v/>
       </c>
@@ -2917,46 +2936,46 @@
       </c>
       <c r="B14" s="43" t="inlineStr">
         <is>
-          <t>must be zero</t>
-        </is>
-      </c>
-      <c r="C14" s="64">
+          <t>sheet arithmetic, must be zero</t>
+        </is>
+      </c>
+      <c r="C14" s="65">
         <f>ROUND(C12-C13,3)</f>
         <v/>
       </c>
-      <c r="D14" s="64">
+      <c r="D14" s="65">
         <f>ROUND(D12-D13,3)</f>
         <v/>
       </c>
-      <c r="E14" s="64">
+      <c r="E14" s="65">
         <f>ROUND(E12-E13,3)</f>
         <v/>
       </c>
-      <c r="F14" s="64">
+      <c r="F14" s="65">
         <f>ROUND(F12-F13,3)</f>
         <v/>
       </c>
-      <c r="G14" s="64">
+      <c r="G14" s="65">
         <f>ROUND(G12-G13,3)</f>
         <v/>
       </c>
-      <c r="H14" s="64">
+      <c r="H14" s="65">
         <f>ROUND(H12-H13,3)</f>
         <v/>
       </c>
-      <c r="I14" s="64">
+      <c r="I14" s="65">
         <f>ROUND(I12-I13,3)</f>
         <v/>
       </c>
-      <c r="J14" s="64">
+      <c r="J14" s="65">
         <f>ROUND(J12-J13,3)</f>
         <v/>
       </c>
-      <c r="K14" s="64">
+      <c r="K14" s="65">
         <f>ROUND(K12-K13,3)</f>
         <v/>
       </c>
-      <c r="L14" s="64">
+      <c r="L14" s="65">
         <f>ROUND(L12-L13,3)</f>
         <v/>
       </c>
@@ -3931,43 +3950,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C37" s="65">
+      <c r="C37" s="66">
         <f>IF(C12=0,0,C34/C12)</f>
         <v/>
       </c>
-      <c r="D37" s="65">
+      <c r="D37" s="66">
         <f>IF(D12=0,0,D34/D12)</f>
         <v/>
       </c>
-      <c r="E37" s="65">
+      <c r="E37" s="66">
         <f>IF(E12=0,0,E34/E12)</f>
         <v/>
       </c>
-      <c r="F37" s="65">
+      <c r="F37" s="66">
         <f>IF(F12=0,0,F34/F12)</f>
         <v/>
       </c>
-      <c r="G37" s="65">
+      <c r="G37" s="66">
         <f>IF(G12=0,0,G34/G12)</f>
         <v/>
       </c>
-      <c r="H37" s="65">
+      <c r="H37" s="66">
         <f>IF(H12=0,0,H34/H12)</f>
         <v/>
       </c>
-      <c r="I37" s="65">
+      <c r="I37" s="66">
         <f>IF(I12=0,0,I34/I12)</f>
         <v/>
       </c>
-      <c r="J37" s="65">
+      <c r="J37" s="66">
         <f>IF(J12=0,0,J34/J12)</f>
         <v/>
       </c>
-      <c r="K37" s="65">
+      <c r="K37" s="66">
         <f>IF(K12=0,0,K34/K12)</f>
         <v/>
       </c>
-      <c r="L37" s="65">
+      <c r="L37" s="66">
         <f>IF(L12=0,0,L34/L12)</f>
         <v/>
       </c>
@@ -4025,7 +4044,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="66" t="inlineStr">
+      <c r="A40" s="67" t="inlineStr">
         <is>
           <t>The FTE block reconciles exactly and is the plan. The cost build-up prices those roles at their own salaries; the model prices the same headcount at a blended loaded average that rises from 38k to 76k over the plan, while the build-up holds today's salaries flat. The two cross over at Y4: the build-up is the higher figure in Y1-Y3, where one founder salary dominates a team of two or three, and the model is higher from Y4 as its blended rate climbs. The model is the one that reaches the P&amp;L either way. The memo rows below make the two rates comparable.</t>
         </is>
@@ -4313,43 +4332,43 @@
           <t>years</t>
         </is>
       </c>
-      <c r="C8" s="67">
+      <c r="C8" s="68">
         <f>IF(C7=0,0,1/C7)</f>
         <v/>
       </c>
-      <c r="D8" s="67">
+      <c r="D8" s="68">
         <f>IF(D7=0,0,1/D7)</f>
         <v/>
       </c>
-      <c r="E8" s="67">
+      <c r="E8" s="68">
         <f>IF(E7=0,0,1/E7)</f>
         <v/>
       </c>
-      <c r="F8" s="67">
+      <c r="F8" s="68">
         <f>IF(F7=0,0,1/F7)</f>
         <v/>
       </c>
-      <c r="G8" s="67">
+      <c r="G8" s="68">
         <f>IF(G7=0,0,1/G7)</f>
         <v/>
       </c>
-      <c r="H8" s="67">
+      <c r="H8" s="68">
         <f>IF(H7=0,0,1/H7)</f>
         <v/>
       </c>
-      <c r="I8" s="67">
+      <c r="I8" s="68">
         <f>IF(I7=0,0,1/I7)</f>
         <v/>
       </c>
-      <c r="J8" s="67">
+      <c r="J8" s="68">
         <f>IF(J7=0,0,1/J7)</f>
         <v/>
       </c>
-      <c r="K8" s="67">
+      <c r="K8" s="68">
         <f>IF(K7=0,0,1/K7)</f>
         <v/>
       </c>
-      <c r="L8" s="67">
+      <c r="L8" s="68">
         <f>IF(L7=0,0,1/L7)</f>
         <v/>
       </c>
@@ -4521,43 +4540,43 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C12" s="64">
+      <c r="C12" s="65">
         <f>IF(C6=0,0,C11/C6)</f>
         <v/>
       </c>
-      <c r="D12" s="64">
+      <c r="D12" s="65">
         <f>IF(D6=0,0,D11/D6)</f>
         <v/>
       </c>
-      <c r="E12" s="64">
+      <c r="E12" s="65">
         <f>IF(E6=0,0,E11/E6)</f>
         <v/>
       </c>
-      <c r="F12" s="64">
+      <c r="F12" s="65">
         <f>IF(F6=0,0,F11/F6)</f>
         <v/>
       </c>
-      <c r="G12" s="64">
+      <c r="G12" s="65">
         <f>IF(G6=0,0,G11/G6)</f>
         <v/>
       </c>
-      <c r="H12" s="64">
+      <c r="H12" s="65">
         <f>IF(H6=0,0,H11/H6)</f>
         <v/>
       </c>
-      <c r="I12" s="64">
+      <c r="I12" s="65">
         <f>IF(I6=0,0,I11/I6)</f>
         <v/>
       </c>
-      <c r="J12" s="64">
+      <c r="J12" s="65">
         <f>IF(J6=0,0,J11/J6)</f>
         <v/>
       </c>
-      <c r="K12" s="64">
+      <c r="K12" s="65">
         <f>IF(K6=0,0,K11/K6)</f>
         <v/>
       </c>
-      <c r="L12" s="64">
+      <c r="L12" s="65">
         <f>IF(L6=0,0,L11/L6)</f>
         <v/>
       </c>
@@ -4573,49 +4592,49 @@
           <t>months</t>
         </is>
       </c>
-      <c r="C13" s="68">
+      <c r="C13" s="69">
         <f>IF(C10&lt;=0,0,12*C6/C10)</f>
         <v/>
       </c>
-      <c r="D13" s="68">
+      <c r="D13" s="69">
         <f>IF(D10&lt;=0,0,12*D6/D10)</f>
         <v/>
       </c>
-      <c r="E13" s="68">
+      <c r="E13" s="69">
         <f>IF(E10&lt;=0,0,12*E6/E10)</f>
         <v/>
       </c>
-      <c r="F13" s="68">
+      <c r="F13" s="69">
         <f>IF(F10&lt;=0,0,12*F6/F10)</f>
         <v/>
       </c>
-      <c r="G13" s="68">
+      <c r="G13" s="69">
         <f>IF(G10&lt;=0,0,12*G6/G10)</f>
         <v/>
       </c>
-      <c r="H13" s="68">
+      <c r="H13" s="69">
         <f>IF(H10&lt;=0,0,12*H6/H10)</f>
         <v/>
       </c>
-      <c r="I13" s="68">
+      <c r="I13" s="69">
         <f>IF(I10&lt;=0,0,12*I6/I10)</f>
         <v/>
       </c>
-      <c r="J13" s="68">
+      <c r="J13" s="69">
         <f>IF(J10&lt;=0,0,12*J6/J10)</f>
         <v/>
       </c>
-      <c r="K13" s="68">
+      <c r="K13" s="69">
         <f>IF(K10&lt;=0,0,12*K6/K10)</f>
         <v/>
       </c>
-      <c r="L13" s="68">
+      <c r="L13" s="69">
         <f>IF(L10&lt;=0,0,12*L6/L10)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="66" t="inlineStr">
+      <c r="A15" s="67" t="inlineStr">
         <is>
           <t>The athlete LTV/CAC ratio is unusually high, and that is the thesis rather than an error: acquisition is cheap precisely because there is no incumbent agent to outbid in these sports. It should be read alongside the fan LTV below, which is small: the economics work on volume of athletes, not on the value of any one of them.</t>
         </is>
@@ -4629,7 +4648,7 @@
       </c>
       <c r="B18" s="14" t="n"/>
       <c r="C18" s="14" t="n"/>
-      <c r="D18" s="69" t="inlineStr">
+      <c r="D18" s="70" t="inlineStr">
         <is>
           <t>excludes PPV and tips, which the revenue model carries separately</t>
         </is>
@@ -4914,43 +4933,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C24" s="70">
+      <c r="C24" s="71">
         <f>C21-C22-C23</f>
         <v/>
       </c>
-      <c r="D24" s="70">
+      <c r="D24" s="71">
         <f>D21-D22-D23</f>
         <v/>
       </c>
-      <c r="E24" s="70">
+      <c r="E24" s="71">
         <f>E21-E22-E23</f>
         <v/>
       </c>
-      <c r="F24" s="70">
+      <c r="F24" s="71">
         <f>F21-F22-F23</f>
         <v/>
       </c>
-      <c r="G24" s="70">
+      <c r="G24" s="71">
         <f>G21-G22-G23</f>
         <v/>
       </c>
-      <c r="H24" s="70">
+      <c r="H24" s="71">
         <f>H21-H22-H23</f>
         <v/>
       </c>
-      <c r="I24" s="70">
+      <c r="I24" s="71">
         <f>I21-I22-I23</f>
         <v/>
       </c>
-      <c r="J24" s="70">
+      <c r="J24" s="71">
         <f>J21-J22-J23</f>
         <v/>
       </c>
-      <c r="K24" s="70">
+      <c r="K24" s="71">
         <f>K21-K22-K23</f>
         <v/>
       </c>
-      <c r="L24" s="70">
+      <c r="L24" s="71">
         <f>L21-L22-L23</f>
         <v/>
       </c>
@@ -5018,43 +5037,43 @@
           <t>months</t>
         </is>
       </c>
-      <c r="C26" s="68">
+      <c r="C26" s="69">
         <f>IF(C25=0,0,1/C25)</f>
         <v/>
       </c>
-      <c r="D26" s="68">
+      <c r="D26" s="69">
         <f>IF(D25=0,0,1/D25)</f>
         <v/>
       </c>
-      <c r="E26" s="68">
+      <c r="E26" s="69">
         <f>IF(E25=0,0,1/E25)</f>
         <v/>
       </c>
-      <c r="F26" s="68">
+      <c r="F26" s="69">
         <f>IF(F25=0,0,1/F25)</f>
         <v/>
       </c>
-      <c r="G26" s="68">
+      <c r="G26" s="69">
         <f>IF(G25=0,0,1/G25)</f>
         <v/>
       </c>
-      <c r="H26" s="68">
+      <c r="H26" s="69">
         <f>IF(H25=0,0,1/H25)</f>
         <v/>
       </c>
-      <c r="I26" s="68">
+      <c r="I26" s="69">
         <f>IF(I25=0,0,1/I25)</f>
         <v/>
       </c>
-      <c r="J26" s="68">
+      <c r="J26" s="69">
         <f>IF(J25=0,0,1/J25)</f>
         <v/>
       </c>
-      <c r="K26" s="68">
+      <c r="K26" s="69">
         <f>IF(K25=0,0,1/K25)</f>
         <v/>
       </c>
-      <c r="L26" s="68">
+      <c r="L26" s="69">
         <f>IF(L25=0,0,1/L25)</f>
         <v/>
       </c>
@@ -5070,43 +5089,43 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C27" s="71">
+      <c r="C27" s="72">
         <f>C24*C26</f>
         <v/>
       </c>
-      <c r="D27" s="71">
+      <c r="D27" s="72">
         <f>D24*D26</f>
         <v/>
       </c>
-      <c r="E27" s="71">
+      <c r="E27" s="72">
         <f>E24*E26</f>
         <v/>
       </c>
-      <c r="F27" s="71">
+      <c r="F27" s="72">
         <f>F24*F26</f>
         <v/>
       </c>
-      <c r="G27" s="71">
+      <c r="G27" s="72">
         <f>G24*G26</f>
         <v/>
       </c>
-      <c r="H27" s="71">
+      <c r="H27" s="72">
         <f>H24*H26</f>
         <v/>
       </c>
-      <c r="I27" s="71">
+      <c r="I27" s="72">
         <f>I24*I26</f>
         <v/>
       </c>
-      <c r="J27" s="71">
+      <c r="J27" s="72">
         <f>J24*J26</f>
         <v/>
       </c>
-      <c r="K27" s="71">
+      <c r="K27" s="72">
         <f>K24*K26</f>
         <v/>
       </c>
-      <c r="L27" s="71">
+      <c r="L27" s="72">
         <f>L24*L26</f>
         <v/>
       </c>
@@ -5154,7 +5173,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="66" t="inlineStr">
+      <c r="A30" s="67" t="inlineStr">
         <is>
           <t>Fan CAC is zero by construction: athletes bring their own audiences and the model spends nothing acquiring fans. That understates the risk rather than flattering the return, and the plan discloses it as such.</t>
         </is>
@@ -5449,49 +5468,49 @@
           <t>months</t>
         </is>
       </c>
-      <c r="C38" s="63">
+      <c r="C38" s="64">
         <f>IF(C37&lt;=0,0,12*C33/C37)</f>
         <v/>
       </c>
-      <c r="D38" s="63">
+      <c r="D38" s="64">
         <f>IF(D37&lt;=0,0,12*D33/D37)</f>
         <v/>
       </c>
-      <c r="E38" s="63">
+      <c r="E38" s="64">
         <f>IF(E37&lt;=0,0,12*E33/E37)</f>
         <v/>
       </c>
-      <c r="F38" s="63">
+      <c r="F38" s="64">
         <f>IF(F37&lt;=0,0,12*F33/F37)</f>
         <v/>
       </c>
-      <c r="G38" s="63">
+      <c r="G38" s="64">
         <f>IF(G37&lt;=0,0,12*G33/G37)</f>
         <v/>
       </c>
-      <c r="H38" s="63">
+      <c r="H38" s="64">
         <f>IF(H37&lt;=0,0,12*H33/H37)</f>
         <v/>
       </c>
-      <c r="I38" s="63">
+      <c r="I38" s="64">
         <f>IF(I37&lt;=0,0,12*I33/I37)</f>
         <v/>
       </c>
-      <c r="J38" s="63">
+      <c r="J38" s="64">
         <f>IF(J37&lt;=0,0,12*J33/J37)</f>
         <v/>
       </c>
-      <c r="K38" s="63">
+      <c r="K38" s="64">
         <f>IF(K37&lt;=0,0,12*K33/K37)</f>
         <v/>
       </c>
-      <c r="L38" s="63">
+      <c r="L38" s="64">
         <f>IF(L37&lt;=0,0,12*L33/L37)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="66" t="inlineStr">
+      <c r="A40" s="67" t="inlineStr">
         <is>
           <t>No sponsor LTV is shown. It needs a sponsor retention assumption the model does not make, and inventing one here would create a figure nothing else in the plan validates. Payback needs no such assumption, so payback is what is reported.</t>
         </is>
@@ -6308,7 +6327,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="72" t="inlineStr">
+      <c r="A2" s="73" t="inlineStr">
         <is>
           <t>Each pair is the Python model's figure and the workbook's own calculation. VARIANCE must be zero: if a formula is wrong, it shows up here on open.</t>
         </is>
@@ -6492,43 +6511,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C7" s="73">
+      <c r="C7" s="74">
         <f>ROUND(C6-C5,0)</f>
         <v/>
       </c>
-      <c r="D7" s="73">
+      <c r="D7" s="74">
         <f>ROUND(D6-D5,0)</f>
         <v/>
       </c>
-      <c r="E7" s="73">
+      <c r="E7" s="74">
         <f>ROUND(E6-E5,0)</f>
         <v/>
       </c>
-      <c r="F7" s="73">
+      <c r="F7" s="74">
         <f>ROUND(F6-F5,0)</f>
         <v/>
       </c>
-      <c r="G7" s="73">
+      <c r="G7" s="74">
         <f>ROUND(G6-G5,0)</f>
         <v/>
       </c>
-      <c r="H7" s="73">
+      <c r="H7" s="74">
         <f>ROUND(H6-H5,0)</f>
         <v/>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="74">
         <f>ROUND(I6-I5,0)</f>
         <v/>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="74">
         <f>ROUND(J6-J5,0)</f>
         <v/>
       </c>
-      <c r="K7" s="73">
+      <c r="K7" s="74">
         <f>ROUND(K6-K5,0)</f>
         <v/>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="74">
         <f>ROUND(L6-L5,0)</f>
         <v/>
       </c>
@@ -6656,43 +6675,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C12" s="73">
+      <c r="C12" s="74">
         <f>ROUND(C11-C10,0)</f>
         <v/>
       </c>
-      <c r="D12" s="73">
+      <c r="D12" s="74">
         <f>ROUND(D11-D10,0)</f>
         <v/>
       </c>
-      <c r="E12" s="73">
+      <c r="E12" s="74">
         <f>ROUND(E11-E10,0)</f>
         <v/>
       </c>
-      <c r="F12" s="73">
+      <c r="F12" s="74">
         <f>ROUND(F11-F10,0)</f>
         <v/>
       </c>
-      <c r="G12" s="73">
+      <c r="G12" s="74">
         <f>ROUND(G11-G10,0)</f>
         <v/>
       </c>
-      <c r="H12" s="73">
+      <c r="H12" s="74">
         <f>ROUND(H11-H10,0)</f>
         <v/>
       </c>
-      <c r="I12" s="73">
+      <c r="I12" s="74">
         <f>ROUND(I11-I10,0)</f>
         <v/>
       </c>
-      <c r="J12" s="73">
+      <c r="J12" s="74">
         <f>ROUND(J11-J10,0)</f>
         <v/>
       </c>
-      <c r="K12" s="73">
+      <c r="K12" s="74">
         <f>ROUND(K11-K10,0)</f>
         <v/>
       </c>
-      <c r="L12" s="73">
+      <c r="L12" s="74">
         <f>ROUND(L11-L10,0)</f>
         <v/>
       </c>
@@ -6820,43 +6839,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C17" s="73">
+      <c r="C17" s="74">
         <f>ROUND(C16-C15,0)</f>
         <v/>
       </c>
-      <c r="D17" s="73">
+      <c r="D17" s="74">
         <f>ROUND(D16-D15,0)</f>
         <v/>
       </c>
-      <c r="E17" s="73">
+      <c r="E17" s="74">
         <f>ROUND(E16-E15,0)</f>
         <v/>
       </c>
-      <c r="F17" s="73">
+      <c r="F17" s="74">
         <f>ROUND(F16-F15,0)</f>
         <v/>
       </c>
-      <c r="G17" s="73">
+      <c r="G17" s="74">
         <f>ROUND(G16-G15,0)</f>
         <v/>
       </c>
-      <c r="H17" s="73">
+      <c r="H17" s="74">
         <f>ROUND(H16-H15,0)</f>
         <v/>
       </c>
-      <c r="I17" s="73">
+      <c r="I17" s="74">
         <f>ROUND(I16-I15,0)</f>
         <v/>
       </c>
-      <c r="J17" s="73">
+      <c r="J17" s="74">
         <f>ROUND(J16-J15,0)</f>
         <v/>
       </c>
-      <c r="K17" s="73">
+      <c r="K17" s="74">
         <f>ROUND(K16-K15,0)</f>
         <v/>
       </c>
-      <c r="L17" s="73">
+      <c r="L17" s="74">
         <f>ROUND(L16-L15,0)</f>
         <v/>
       </c>
@@ -6894,10 +6913,10 @@
         <v>109392.49303125</v>
       </c>
       <c r="D20" s="24" t="n">
-        <v>151380.2191447622</v>
+        <v>178185.2191447622</v>
       </c>
       <c r="E20" s="24" t="n">
-        <v>252393.5434635245</v>
+        <v>252106.0434635245</v>
       </c>
       <c r="F20" s="24" t="n">
         <v>428374.5174483291</v>
@@ -6984,43 +7003,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C22" s="73">
+      <c r="C22" s="74">
         <f>ROUND(C21-C20,0)</f>
         <v/>
       </c>
-      <c r="D22" s="73">
+      <c r="D22" s="74">
         <f>ROUND(D21-D20,0)</f>
         <v/>
       </c>
-      <c r="E22" s="73">
+      <c r="E22" s="74">
         <f>ROUND(E21-E20,0)</f>
         <v/>
       </c>
-      <c r="F22" s="73">
+      <c r="F22" s="74">
         <f>ROUND(F21-F20,0)</f>
         <v/>
       </c>
-      <c r="G22" s="73">
+      <c r="G22" s="74">
         <f>ROUND(G21-G20,0)</f>
         <v/>
       </c>
-      <c r="H22" s="73">
+      <c r="H22" s="74">
         <f>ROUND(H21-H20,0)</f>
         <v/>
       </c>
-      <c r="I22" s="73">
+      <c r="I22" s="74">
         <f>ROUND(I21-I20,0)</f>
         <v/>
       </c>
-      <c r="J22" s="73">
+      <c r="J22" s="74">
         <f>ROUND(J21-J20,0)</f>
         <v/>
       </c>
-      <c r="K22" s="73">
+      <c r="K22" s="74">
         <f>ROUND(K21-K20,0)</f>
         <v/>
       </c>
-      <c r="L22" s="73">
+      <c r="L22" s="74">
         <f>ROUND(L21-L20,0)</f>
         <v/>
       </c>
@@ -7058,10 +7077,10 @@
         <v>-110668.8220835376</v>
       </c>
       <c r="D25" s="24" t="n">
-        <v>-114863.7221008533</v>
+        <v>-141668.7221008533</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>-72269.76596439572</v>
+        <v>-71982.26596439572</v>
       </c>
       <c r="F25" s="24" t="n">
         <v>40095.35453622771</v>
@@ -7148,43 +7167,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C27" s="73">
+      <c r="C27" s="74">
         <f>ROUND(C26-C25,0)</f>
         <v/>
       </c>
-      <c r="D27" s="73">
+      <c r="D27" s="74">
         <f>ROUND(D26-D25,0)</f>
         <v/>
       </c>
-      <c r="E27" s="73">
+      <c r="E27" s="74">
         <f>ROUND(E26-E25,0)</f>
         <v/>
       </c>
-      <c r="F27" s="73">
+      <c r="F27" s="74">
         <f>ROUND(F26-F25,0)</f>
         <v/>
       </c>
-      <c r="G27" s="73">
+      <c r="G27" s="74">
         <f>ROUND(G26-G25,0)</f>
         <v/>
       </c>
-      <c r="H27" s="73">
+      <c r="H27" s="74">
         <f>ROUND(H26-H25,0)</f>
         <v/>
       </c>
-      <c r="I27" s="73">
+      <c r="I27" s="74">
         <f>ROUND(I26-I25,0)</f>
         <v/>
       </c>
-      <c r="J27" s="73">
+      <c r="J27" s="74">
         <f>ROUND(J26-J25,0)</f>
         <v/>
       </c>
-      <c r="K27" s="73">
+      <c r="K27" s="74">
         <f>ROUND(K26-K25,0)</f>
         <v/>
       </c>
-      <c r="L27" s="73">
+      <c r="L27" s="74">
         <f>ROUND(L26-L25,0)</f>
         <v/>
       </c>
@@ -7312,43 +7331,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C32" s="74">
+      <c r="C32" s="75">
         <f>ROUND(C31-C30,0)</f>
         <v/>
       </c>
-      <c r="D32" s="74">
+      <c r="D32" s="75">
         <f>ROUND(D31-D30,0)</f>
         <v/>
       </c>
-      <c r="E32" s="74">
+      <c r="E32" s="75">
         <f>ROUND(E31-E30,0)</f>
         <v/>
       </c>
-      <c r="F32" s="74">
+      <c r="F32" s="75">
         <f>ROUND(F31-F30,0)</f>
         <v/>
       </c>
-      <c r="G32" s="74">
+      <c r="G32" s="75">
         <f>ROUND(G31-G30,0)</f>
         <v/>
       </c>
-      <c r="H32" s="74">
+      <c r="H32" s="75">
         <f>ROUND(H31-H30,0)</f>
         <v/>
       </c>
-      <c r="I32" s="74">
+      <c r="I32" s="75">
         <f>ROUND(I31-I30,0)</f>
         <v/>
       </c>
-      <c r="J32" s="74">
+      <c r="J32" s="75">
         <f>ROUND(J31-J30,0)</f>
         <v/>
       </c>
-      <c r="K32" s="74">
+      <c r="K32" s="75">
         <f>ROUND(K31-K30,0)</f>
         <v/>
       </c>
-      <c r="L32" s="74">
+      <c r="L32" s="75">
         <f>ROUND(L31-L30,0)</f>
         <v/>
       </c>
@@ -7476,43 +7495,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C37" s="74">
+      <c r="C37" s="75">
         <f>ROUND(C36-C35,0)</f>
         <v/>
       </c>
-      <c r="D37" s="74">
+      <c r="D37" s="75">
         <f>ROUND(D36-D35,0)</f>
         <v/>
       </c>
-      <c r="E37" s="74">
+      <c r="E37" s="75">
         <f>ROUND(E36-E35,0)</f>
         <v/>
       </c>
-      <c r="F37" s="74">
+      <c r="F37" s="75">
         <f>ROUND(F36-F35,0)</f>
         <v/>
       </c>
-      <c r="G37" s="74">
+      <c r="G37" s="75">
         <f>ROUND(G36-G35,0)</f>
         <v/>
       </c>
-      <c r="H37" s="74">
+      <c r="H37" s="75">
         <f>ROUND(H36-H35,0)</f>
         <v/>
       </c>
-      <c r="I37" s="74">
+      <c r="I37" s="75">
         <f>ROUND(I36-I35,0)</f>
         <v/>
       </c>
-      <c r="J37" s="74">
+      <c r="J37" s="75">
         <f>ROUND(J36-J35,0)</f>
         <v/>
       </c>
-      <c r="K37" s="74">
+      <c r="K37" s="75">
         <f>ROUND(K36-K35,0)</f>
         <v/>
       </c>
-      <c r="L37" s="74">
+      <c r="L37" s="75">
         <f>ROUND(L36-L35,0)</f>
         <v/>
       </c>
@@ -7640,43 +7659,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C42" s="73">
+      <c r="C42" s="74">
         <f>ROUND(C41-C40,0)</f>
         <v/>
       </c>
-      <c r="D42" s="73">
+      <c r="D42" s="74">
         <f>ROUND(D41-D40,0)</f>
         <v/>
       </c>
-      <c r="E42" s="73">
+      <c r="E42" s="74">
         <f>ROUND(E41-E40,0)</f>
         <v/>
       </c>
-      <c r="F42" s="73">
+      <c r="F42" s="74">
         <f>ROUND(F41-F40,0)</f>
         <v/>
       </c>
-      <c r="G42" s="73">
+      <c r="G42" s="74">
         <f>ROUND(G41-G40,0)</f>
         <v/>
       </c>
-      <c r="H42" s="73">
+      <c r="H42" s="74">
         <f>ROUND(H41-H40,0)</f>
         <v/>
       </c>
-      <c r="I42" s="73">
+      <c r="I42" s="74">
         <f>ROUND(I41-I40,0)</f>
         <v/>
       </c>
-      <c r="J42" s="73">
+      <c r="J42" s="74">
         <f>ROUND(J41-J40,0)</f>
         <v/>
       </c>
-      <c r="K42" s="73">
+      <c r="K42" s="74">
         <f>ROUND(K41-K40,0)</f>
         <v/>
       </c>
-      <c r="L42" s="73">
+      <c r="L42" s="74">
         <f>ROUND(L41-L40,0)</f>
         <v/>
       </c>
@@ -7804,43 +7823,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C47" s="74">
+      <c r="C47" s="75">
         <f>ROUND(C46-C45,0)</f>
         <v/>
       </c>
-      <c r="D47" s="74">
+      <c r="D47" s="75">
         <f>ROUND(D46-D45,0)</f>
         <v/>
       </c>
-      <c r="E47" s="74">
+      <c r="E47" s="75">
         <f>ROUND(E46-E45,0)</f>
         <v/>
       </c>
-      <c r="F47" s="74">
+      <c r="F47" s="75">
         <f>ROUND(F46-F45,0)</f>
         <v/>
       </c>
-      <c r="G47" s="74">
+      <c r="G47" s="75">
         <f>ROUND(G46-G45,0)</f>
         <v/>
       </c>
-      <c r="H47" s="74">
+      <c r="H47" s="75">
         <f>ROUND(H46-H45,0)</f>
         <v/>
       </c>
-      <c r="I47" s="74">
+      <c r="I47" s="75">
         <f>ROUND(I46-I45,0)</f>
         <v/>
       </c>
-      <c r="J47" s="74">
+      <c r="J47" s="75">
         <f>ROUND(J46-J45,0)</f>
         <v/>
       </c>
-      <c r="K47" s="74">
+      <c r="K47" s="75">
         <f>ROUND(K46-K45,0)</f>
         <v/>
       </c>
-      <c r="L47" s="74">
+      <c r="L47" s="75">
         <f>ROUND(L46-L45,0)</f>
         <v/>
       </c>
@@ -7968,43 +7987,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C52" s="74">
+      <c r="C52" s="75">
         <f>ROUND(C51-C50,0)</f>
         <v/>
       </c>
-      <c r="D52" s="74">
+      <c r="D52" s="75">
         <f>ROUND(D51-D50,0)</f>
         <v/>
       </c>
-      <c r="E52" s="74">
+      <c r="E52" s="75">
         <f>ROUND(E51-E50,0)</f>
         <v/>
       </c>
-      <c r="F52" s="74">
+      <c r="F52" s="75">
         <f>ROUND(F51-F50,0)</f>
         <v/>
       </c>
-      <c r="G52" s="74">
+      <c r="G52" s="75">
         <f>ROUND(G51-G50,0)</f>
         <v/>
       </c>
-      <c r="H52" s="74">
+      <c r="H52" s="75">
         <f>ROUND(H51-H50,0)</f>
         <v/>
       </c>
-      <c r="I52" s="74">
+      <c r="I52" s="75">
         <f>ROUND(I51-I50,0)</f>
         <v/>
       </c>
-      <c r="J52" s="74">
+      <c r="J52" s="75">
         <f>ROUND(J51-J50,0)</f>
         <v/>
       </c>
-      <c r="K52" s="74">
+      <c r="K52" s="75">
         <f>ROUND(K51-K50,0)</f>
         <v/>
       </c>
-      <c r="L52" s="74">
+      <c r="L52" s="75">
         <f>ROUND(L51-L50,0)</f>
         <v/>
       </c>
@@ -8132,43 +8151,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C57" s="73">
+      <c r="C57" s="74">
         <f>ROUND(C56-C55,0)</f>
         <v/>
       </c>
-      <c r="D57" s="73">
+      <c r="D57" s="74">
         <f>ROUND(D56-D55,0)</f>
         <v/>
       </c>
-      <c r="E57" s="73">
+      <c r="E57" s="74">
         <f>ROUND(E56-E55,0)</f>
         <v/>
       </c>
-      <c r="F57" s="73">
+      <c r="F57" s="74">
         <f>ROUND(F56-F55,0)</f>
         <v/>
       </c>
-      <c r="G57" s="73">
+      <c r="G57" s="74">
         <f>ROUND(G56-G55,0)</f>
         <v/>
       </c>
-      <c r="H57" s="73">
+      <c r="H57" s="74">
         <f>ROUND(H56-H55,0)</f>
         <v/>
       </c>
-      <c r="I57" s="73">
+      <c r="I57" s="74">
         <f>ROUND(I56-I55,0)</f>
         <v/>
       </c>
-      <c r="J57" s="73">
+      <c r="J57" s="74">
         <f>ROUND(J56-J55,0)</f>
         <v/>
       </c>
-      <c r="K57" s="73">
+      <c r="K57" s="74">
         <f>ROUND(K56-K55,0)</f>
         <v/>
       </c>
-      <c r="L57" s="73">
+      <c r="L57" s="74">
         <f>ROUND(L56-L55,0)</f>
         <v/>
       </c>
@@ -8218,7 +8237,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>17405.67855833427</v>
+        <v>12258.05355833427</v>
       </c>
       <c r="I60" s="24" t="n">
         <v>89855.27695443966</v>
@@ -8296,43 +8315,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C62" s="73">
+      <c r="C62" s="74">
         <f>ROUND(C61-C60,0)</f>
         <v/>
       </c>
-      <c r="D62" s="73">
+      <c r="D62" s="74">
         <f>ROUND(D61-D60,0)</f>
         <v/>
       </c>
-      <c r="E62" s="73">
+      <c r="E62" s="74">
         <f>ROUND(E61-E60,0)</f>
         <v/>
       </c>
-      <c r="F62" s="73">
+      <c r="F62" s="74">
         <f>ROUND(F61-F60,0)</f>
         <v/>
       </c>
-      <c r="G62" s="73">
+      <c r="G62" s="74">
         <f>ROUND(G61-G60,0)</f>
         <v/>
       </c>
-      <c r="H62" s="73">
+      <c r="H62" s="74">
         <f>ROUND(H61-H60,0)</f>
         <v/>
       </c>
-      <c r="I62" s="73">
+      <c r="I62" s="74">
         <f>ROUND(I61-I60,0)</f>
         <v/>
       </c>
-      <c r="J62" s="73">
+      <c r="J62" s="74">
         <f>ROUND(J61-J60,0)</f>
         <v/>
       </c>
-      <c r="K62" s="73">
+      <c r="K62" s="74">
         <f>ROUND(K61-K60,0)</f>
         <v/>
       </c>
-      <c r="L62" s="73">
+      <c r="L62" s="74">
         <f>ROUND(L61-L60,0)</f>
         <v/>
       </c>
@@ -8370,19 +8389,19 @@
         <v>-114468.8220835376</v>
       </c>
       <c r="D65" s="24" t="n">
-        <v>-123863.7221008533</v>
+        <v>-153268.7221008533</v>
       </c>
       <c r="E65" s="24" t="n">
-        <v>-90269.76596439572</v>
+        <v>-92582.26596439572</v>
       </c>
       <c r="F65" s="24" t="n">
-        <v>13095.35453622771</v>
+        <v>10495.35453622771</v>
       </c>
       <c r="G65" s="24" t="n">
         <v>125249.4576869933</v>
       </c>
       <c r="H65" s="24" t="n">
-        <v>288889.6764227932</v>
+        <v>294037.3014227932</v>
       </c>
       <c r="I65" s="24" t="n">
         <v>509179.9027418248</v>
@@ -8460,43 +8479,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C67" s="73">
+      <c r="C67" s="74">
         <f>ROUND(C66-C65,0)</f>
         <v/>
       </c>
-      <c r="D67" s="73">
+      <c r="D67" s="74">
         <f>ROUND(D66-D65,0)</f>
         <v/>
       </c>
-      <c r="E67" s="73">
+      <c r="E67" s="74">
         <f>ROUND(E66-E65,0)</f>
         <v/>
       </c>
-      <c r="F67" s="73">
+      <c r="F67" s="74">
         <f>ROUND(F66-F65,0)</f>
         <v/>
       </c>
-      <c r="G67" s="73">
+      <c r="G67" s="74">
         <f>ROUND(G66-G65,0)</f>
         <v/>
       </c>
-      <c r="H67" s="73">
+      <c r="H67" s="74">
         <f>ROUND(H66-H65,0)</f>
         <v/>
       </c>
-      <c r="I67" s="73">
+      <c r="I67" s="74">
         <f>ROUND(I66-I65,0)</f>
         <v/>
       </c>
-      <c r="J67" s="73">
+      <c r="J67" s="74">
         <f>ROUND(J66-J65,0)</f>
         <v/>
       </c>
-      <c r="K67" s="73">
+      <c r="K67" s="74">
         <f>ROUND(K66-K65,0)</f>
         <v/>
       </c>
-      <c r="L67" s="73">
+      <c r="L67" s="74">
         <f>ROUND(L66-L65,0)</f>
         <v/>
       </c>
@@ -8534,19 +8553,19 @@
         <v>-112653.46197138</v>
       </c>
       <c r="D70" s="24" t="n">
-        <v>-108485.5299863531</v>
+        <v>-140887.3793014216</v>
       </c>
       <c r="E70" s="24" t="n">
-        <v>-40311.44477137744</v>
+        <v>-42250.72559329525</v>
       </c>
       <c r="F70" s="24" t="n">
-        <v>109326.3362520052</v>
+        <v>109349.9663889915</v>
       </c>
       <c r="G70" s="24" t="n">
         <v>266910.6407489183</v>
       </c>
       <c r="H70" s="24" t="n">
-        <v>466145.0235755878</v>
+        <v>471292.6485755878</v>
       </c>
       <c r="I70" s="24" t="n">
         <v>698647.4823472798</v>
@@ -8624,43 +8643,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C72" s="73">
+      <c r="C72" s="74">
         <f>ROUND(C71-C70,0)</f>
         <v/>
       </c>
-      <c r="D72" s="73">
+      <c r="D72" s="74">
         <f>ROUND(D71-D70,0)</f>
         <v/>
       </c>
-      <c r="E72" s="73">
+      <c r="E72" s="74">
         <f>ROUND(E71-E70,0)</f>
         <v/>
       </c>
-      <c r="F72" s="73">
+      <c r="F72" s="74">
         <f>ROUND(F71-F70,0)</f>
         <v/>
       </c>
-      <c r="G72" s="73">
+      <c r="G72" s="74">
         <f>ROUND(G71-G70,0)</f>
         <v/>
       </c>
-      <c r="H72" s="73">
+      <c r="H72" s="74">
         <f>ROUND(H71-H70,0)</f>
         <v/>
       </c>
-      <c r="I72" s="73">
+      <c r="I72" s="74">
         <f>ROUND(I71-I70,0)</f>
         <v/>
       </c>
-      <c r="J72" s="73">
+      <c r="J72" s="74">
         <f>ROUND(J71-J70,0)</f>
         <v/>
       </c>
-      <c r="K72" s="73">
+      <c r="K72" s="74">
         <f>ROUND(K71-K70,0)</f>
         <v/>
       </c>
-      <c r="L72" s="73">
+      <c r="L72" s="74">
         <f>ROUND(L71-L70,0)</f>
         <v/>
       </c>
@@ -8683,43 +8702,43 @@
           <t>must be 0</t>
         </is>
       </c>
-      <c r="C75" s="75">
+      <c r="C75" s="76">
         <f>BalanceSheet!C20</f>
         <v/>
       </c>
-      <c r="D75" s="75">
+      <c r="D75" s="76">
         <f>BalanceSheet!D20</f>
         <v/>
       </c>
-      <c r="E75" s="75">
+      <c r="E75" s="76">
         <f>BalanceSheet!E20</f>
         <v/>
       </c>
-      <c r="F75" s="75">
+      <c r="F75" s="76">
         <f>BalanceSheet!F20</f>
         <v/>
       </c>
-      <c r="G75" s="75">
+      <c r="G75" s="76">
         <f>BalanceSheet!G20</f>
         <v/>
       </c>
-      <c r="H75" s="75">
+      <c r="H75" s="76">
         <f>BalanceSheet!H20</f>
         <v/>
       </c>
-      <c r="I75" s="75">
+      <c r="I75" s="76">
         <f>BalanceSheet!I20</f>
         <v/>
       </c>
-      <c r="J75" s="75">
+      <c r="J75" s="76">
         <f>BalanceSheet!J20</f>
         <v/>
       </c>
-      <c r="K75" s="75">
+      <c r="K75" s="76">
         <f>BalanceSheet!K20</f>
         <v/>
       </c>
-      <c r="L75" s="75">
+      <c r="L75" s="76">
         <f>BalanceSheet!L20</f>
         <v/>
       </c>
@@ -8761,669 +8780,669 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="76" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="76" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="76" t="inlineStr">
+      <c r="C4" s="77" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="76" t="inlineStr">
+      <c r="D4" s="77" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E4" s="76" t="inlineStr">
+      <c r="E4" s="77" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F4" s="76" t="inlineStr">
+      <c r="F4" s="77" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="78" t="inlineStr">
         <is>
           <t>Gross payments (GMV)</t>
         </is>
       </c>
-      <c r="B5" s="78" t="n">
+      <c r="B5" s="79" t="n">
         <v>7220000000</v>
       </c>
-      <c r="C5" s="79" t="inlineStr">
+      <c r="C5" s="80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D5" s="79" t="inlineStr">
+      <c r="D5" s="80" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E5" s="79" t="inlineStr">
+      <c r="E5" s="80" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F5" s="79" t="inlineStr">
+      <c r="F5" s="80" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="77" t="inlineStr">
+      <c r="A6" s="78" t="inlineStr">
         <is>
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="B6" s="78" t="n">
+      <c r="B6" s="79" t="n">
         <v>1410000000</v>
       </c>
-      <c r="C6" s="79" t="inlineStr">
+      <c r="C6" s="80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D6" s="79" t="inlineStr">
+      <c r="D6" s="80" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E6" s="79" t="inlineStr">
+      <c r="E6" s="80" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F6" s="79" t="inlineStr">
+      <c r="F6" s="80" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="77" t="inlineStr">
+      <c r="A7" s="78" t="inlineStr">
         <is>
           <t>Paid to creators</t>
         </is>
       </c>
-      <c r="B7" s="78" t="n">
+      <c r="B7" s="79" t="n">
         <v>5800000000</v>
       </c>
-      <c r="C7" s="79" t="inlineStr">
+      <c r="C7" s="80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D7" s="79" t="inlineStr">
+      <c r="D7" s="80" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E7" s="79" t="inlineStr">
+      <c r="E7" s="80" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F7" s="79" t="inlineStr">
+      <c r="F7" s="80" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts, 80.3% of gross</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="77" t="inlineStr">
+      <c r="A8" s="78" t="inlineStr">
         <is>
           <t>Creator accounts</t>
         </is>
       </c>
-      <c r="B8" s="78" t="n">
+      <c r="B8" s="79" t="n">
         <v>4634000</v>
       </c>
-      <c r="C8" s="79" t="inlineStr">
+      <c r="C8" s="80" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D8" s="79" t="inlineStr">
+      <c r="D8" s="80" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E8" s="79" t="inlineStr">
+      <c r="E8" s="80" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F8" s="79" t="inlineStr">
+      <c r="F8" s="80" t="inlineStr">
         <is>
           <t>Variety: +13% YoY</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="77" t="inlineStr">
+      <c r="A9" s="78" t="inlineStr">
         <is>
           <t>Fan accounts</t>
         </is>
       </c>
-      <c r="B9" s="78" t="n">
+      <c r="B9" s="79" t="n">
         <v>377500000</v>
       </c>
-      <c r="C9" s="79" t="inlineStr">
+      <c r="C9" s="80" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D9" s="79" t="inlineStr">
+      <c r="D9" s="80" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E9" s="79" t="inlineStr">
+      <c r="E9" s="80" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F9" s="79" t="inlineStr">
+      <c r="F9" s="80" t="inlineStr">
         <is>
           <t>Variety: +24% YoY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="77" t="inlineStr">
+      <c r="A10" s="78" t="inlineStr">
         <is>
           <t>Reported average creator earnings</t>
         </is>
       </c>
-      <c r="B10" s="78" t="n">
+      <c r="B10" s="79" t="n">
         <v>131</v>
       </c>
-      <c r="C10" s="79" t="inlineStr">
+      <c r="C10" s="80" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D10" s="79" t="inlineStr">
+      <c r="D10" s="80" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E10" s="79" t="inlineStr">
+      <c r="E10" s="80" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F10" s="79" t="inlineStr">
+      <c r="F10" s="80" t="inlineStr">
         <is>
           <t>Sci-Tech Today / ElectroIQ: after platform fees</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="77" t="inlineStr">
+      <c r="A11" s="78" t="inlineStr">
         <is>
           <t>Revenue concentration</t>
         </is>
       </c>
-      <c r="B11" s="80" t="n">
+      <c r="B11" s="81" t="n">
         <v>0.76</v>
       </c>
-      <c r="C11" s="79" t="inlineStr">
+      <c r="C11" s="80" t="inlineStr">
         <is>
           <t>share to top 0.1%</t>
         </is>
       </c>
-      <c r="D11" s="79" t="inlineStr">
+      <c r="D11" s="80" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E11" s="79" t="inlineStr">
+      <c r="E11" s="80" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F11" s="79" t="inlineStr">
+      <c r="F11" s="80" t="inlineStr">
         <is>
           <t>ElectroIQ: power-law distribution</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="77" t="inlineStr">
+      <c r="A12" s="78" t="inlineStr">
         <is>
           <t>Creators with &gt;=1 paying member</t>
         </is>
       </c>
-      <c r="B12" s="78" t="n">
+      <c r="B12" s="79" t="n">
         <v>286287</v>
       </c>
-      <c r="C12" s="79" t="inlineStr">
+      <c r="C12" s="80" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D12" s="79" t="inlineStr">
+      <c r="D12" s="80" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E12" s="79" t="inlineStr">
+      <c r="E12" s="80" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="F12" s="79" t="inlineStr">
+      <c r="F12" s="80" t="inlineStr">
         <is>
           <t>Graphtreon</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="77" t="inlineStr">
+      <c r="A13" s="78" t="inlineStr">
         <is>
           <t>Active creators</t>
         </is>
       </c>
-      <c r="B13" s="78" t="n">
+      <c r="B13" s="79" t="n">
         <v>300000</v>
       </c>
-      <c r="C13" s="79" t="inlineStr">
+      <c r="C13" s="80" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D13" s="79" t="inlineStr">
+      <c r="D13" s="80" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E13" s="79" t="inlineStr">
+      <c r="E13" s="80" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F13" s="79" t="inlineStr">
+      <c r="F13" s="80" t="inlineStr">
         <is>
           <t>Jack Conte, Patreon</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="77" t="inlineStr">
+      <c r="A14" s="78" t="inlineStr">
         <is>
           <t>Active paying members</t>
         </is>
       </c>
-      <c r="B14" s="78" t="n">
+      <c r="B14" s="79" t="n">
         <v>10000000</v>
       </c>
-      <c r="C14" s="79" t="inlineStr">
+      <c r="C14" s="80" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D14" s="79" t="inlineStr">
+      <c r="D14" s="80" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E14" s="79" t="inlineStr">
+      <c r="E14" s="80" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F14" s="79" t="inlineStr">
+      <c r="F14" s="80" t="inlineStr">
         <is>
           <t>Patreon / Backlinko</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="77" t="inlineStr">
+      <c r="A15" s="78" t="inlineStr">
         <is>
           <t>Paid to creators annually</t>
         </is>
       </c>
-      <c r="B15" s="78" t="n">
+      <c r="B15" s="79" t="n">
         <v>2000000000</v>
       </c>
-      <c r="C15" s="79" t="inlineStr">
+      <c r="C15" s="80" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="D15" s="79" t="inlineStr">
+      <c r="D15" s="80" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E15" s="79" t="inlineStr">
+      <c r="E15" s="80" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F15" s="79" t="inlineStr">
+      <c r="F15" s="80" t="inlineStr">
         <is>
           <t>Patreon / Backlinko</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="77" t="inlineStr">
+      <c r="A16" s="78" t="inlineStr">
         <is>
           <t>Average monthly support per member</t>
         </is>
       </c>
-      <c r="B16" s="80" t="n">
+      <c r="B16" s="81" t="n">
         <v>6.1</v>
       </c>
-      <c r="C16" s="79" t="inlineStr">
+      <c r="C16" s="80" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D16" s="79" t="inlineStr">
+      <c r="D16" s="80" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E16" s="79" t="inlineStr">
+      <c r="E16" s="80" t="inlineStr">
         <is>
           <t>Aug 2024</t>
         </is>
       </c>
-      <c r="F16" s="79" t="inlineStr">
+      <c r="F16" s="80" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; audit of ~1,200 creators</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="77" t="inlineStr">
+      <c r="A17" s="78" t="inlineStr">
         <is>
           <t>Typical patronage band (low)</t>
         </is>
       </c>
-      <c r="B17" s="80" t="n">
+      <c r="B17" s="81" t="n">
         <v>8</v>
       </c>
-      <c r="C17" s="79" t="inlineStr">
+      <c r="C17" s="80" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D17" s="79" t="inlineStr">
+      <c r="D17" s="80" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E17" s="79" t="inlineStr">
+      <c r="E17" s="80" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F17" s="79" t="inlineStr">
+      <c r="F17" s="80" t="inlineStr">
         <is>
           <t>Creator-economy benchmarks</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="77" t="inlineStr">
+      <c r="A18" s="78" t="inlineStr">
         <is>
           <t>Typical patronage band (high)</t>
         </is>
       </c>
-      <c r="B18" s="80" t="n">
+      <c r="B18" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="79" t="inlineStr">
+      <c r="C18" s="80" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D18" s="79" t="inlineStr">
+      <c r="D18" s="80" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E18" s="79" t="inlineStr">
+      <c r="E18" s="80" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F18" s="79" t="inlineStr">
+      <c r="F18" s="80" t="inlineStr">
         <is>
           <t>Creator-economy benchmarks</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="77" t="inlineStr">
+      <c r="A19" s="78" t="inlineStr">
         <is>
           <t>Monthly churn (low)</t>
         </is>
       </c>
-      <c r="B19" s="80" t="n">
+      <c r="B19" s="81" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="79" t="inlineStr">
+      <c r="C19" s="80" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D19" s="79" t="inlineStr">
+      <c r="D19" s="80" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E19" s="79" t="inlineStr">
+      <c r="E19" s="80" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F19" s="79" t="inlineStr">
+      <c r="F19" s="80" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="77" t="inlineStr">
+      <c r="A20" s="78" t="inlineStr">
         <is>
           <t>Monthly churn (high)</t>
         </is>
       </c>
-      <c r="B20" s="80" t="n">
+      <c r="B20" s="81" t="n">
         <v>0.15</v>
       </c>
-      <c r="C20" s="79" t="inlineStr">
+      <c r="C20" s="80" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D20" s="79" t="inlineStr">
+      <c r="D20" s="80" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E20" s="79" t="inlineStr">
+      <c r="E20" s="80" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F20" s="79" t="inlineStr">
+      <c r="F20" s="80" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="77" t="inlineStr">
+      <c r="A21" s="78" t="inlineStr">
         <is>
           <t>Annual-plan churn multiplier</t>
         </is>
       </c>
-      <c r="B21" s="80" t="n">
+      <c r="B21" s="81" t="n">
         <v>0.333</v>
       </c>
-      <c r="C21" s="79" t="inlineStr">
+      <c r="C21" s="80" t="inlineStr">
         <is>
           <t>x monthly churn</t>
         </is>
       </c>
-      <c r="D21" s="79" t="inlineStr">
+      <c r="D21" s="80" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E21" s="79" t="inlineStr">
+      <c r="E21" s="80" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F21" s="79" t="inlineStr">
+      <c r="F21" s="80" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report: annual patrons churn at 1/3 the rate</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="77" t="inlineStr">
+      <c r="A22" s="78" t="inlineStr">
         <is>
           <t>Creators with &gt;2,000 patrons</t>
         </is>
       </c>
-      <c r="B22" s="80" t="n">
+      <c r="B22" s="81" t="n">
         <v>0.003</v>
       </c>
-      <c r="C22" s="79" t="inlineStr">
+      <c r="C22" s="80" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D22" s="79" t="inlineStr">
+      <c r="D22" s="80" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E22" s="79" t="inlineStr">
+      <c r="E22" s="80" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F22" s="79" t="inlineStr">
+      <c r="F22" s="80" t="inlineStr">
         <is>
           <t>Graphtreon: power-law distribution</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="77" t="inlineStr">
+      <c r="A23" s="78" t="inlineStr">
         <is>
           <t>Division I athletes in network</t>
         </is>
       </c>
-      <c r="B23" s="78" t="n">
+      <c r="B23" s="79" t="n">
         <v>45000</v>
       </c>
-      <c r="C23" s="79" t="inlineStr">
+      <c r="C23" s="80" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D23" s="79" t="inlineStr">
+      <c r="D23" s="80" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E23" s="79" t="inlineStr">
+      <c r="E23" s="80" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F23" s="79" t="inlineStr">
+      <c r="F23" s="80" t="inlineStr">
         <is>
           <t>Publicis Groupe press release, 19 Aug 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="77" t="inlineStr">
+      <c r="A24" s="78" t="inlineStr">
         <is>
           <t>Power Four universities</t>
         </is>
       </c>
-      <c r="B24" s="78" t="n">
+      <c r="B24" s="79" t="n">
         <v>68</v>
       </c>
-      <c r="C24" s="79" t="inlineStr">
+      <c r="C24" s="80" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D24" s="79" t="inlineStr">
+      <c r="D24" s="80" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E24" s="79" t="inlineStr">
+      <c r="E24" s="80" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F24" s="79" t="inlineStr">
+      <c r="F24" s="80" t="inlineStr">
         <is>
           <t>Publicis Groupe press release</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="77" t="inlineStr">
+      <c r="A25" s="78" t="inlineStr">
         <is>
           <t>Claimed speed-to-market gain</t>
         </is>
       </c>
-      <c r="B25" s="80" t="n">
+      <c r="B25" s="81" t="n">
         <v>0.6</v>
       </c>
-      <c r="C25" s="79" t="inlineStr">
+      <c r="C25" s="80" t="inlineStr">
         <is>
           <t>share faster</t>
         </is>
       </c>
-      <c r="D25" s="79" t="inlineStr">
+      <c r="D25" s="80" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E25" s="79" t="inlineStr">
+      <c r="E25" s="80" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F25" s="79" t="inlineStr">
+      <c r="F25" s="80" t="inlineStr">
         <is>
           <t>Publicis: stated 50-70% vs a traditional agency process</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="81" t="inlineStr">
+      <c r="A27" s="82" t="inlineStr">
         <is>
           <t>TAKE RATES - what each platform costs a creator</t>
         </is>
@@ -9463,16 +9482,16 @@
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="B29" s="82" t="n">
+      <c r="B29" s="83" t="n">
         <v>0.2</v>
       </c>
-      <c r="C29" s="83" t="n">
+      <c r="C29" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="83" t="n">
+      <c r="D29" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="84" t="inlineStr">
+      <c r="F29" s="85" t="inlineStr">
         <is>
           <t>Derived: 1.41bn / 7.22bn = 19.5% (filed accounts)</t>
         </is>
@@ -9484,16 +9503,16 @@
           <t>Fansly</t>
         </is>
       </c>
-      <c r="B30" s="82" t="n">
+      <c r="B30" s="83" t="n">
         <v>0.2</v>
       </c>
-      <c r="C30" s="83" t="n">
+      <c r="C30" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="83" t="n">
+      <c r="D30" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="84" t="inlineStr">
+      <c r="F30" s="85" t="inlineStr">
         <is>
           <t>Not published in terms; widely reported</t>
         </is>
@@ -9505,16 +9524,16 @@
           <t>Fanfix</t>
         </is>
       </c>
-      <c r="B31" s="82" t="n">
+      <c r="B31" s="83" t="n">
         <v>0.2</v>
       </c>
-      <c r="C31" s="83" t="n">
+      <c r="C31" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="83" t="n">
+      <c r="D31" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="84" t="inlineStr">
+      <c r="F31" s="85" t="inlineStr">
         <is>
           <t>Not published in terms; widely reported</t>
         </is>
@@ -9526,16 +9545,16 @@
           <t>Patreon</t>
         </is>
       </c>
-      <c r="B32" s="82" t="n">
+      <c r="B32" s="83" t="n">
         <v>0.1</v>
       </c>
-      <c r="C32" s="83" t="n">
+      <c r="C32" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="83" t="n">
+      <c r="D32" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="84" t="inlineStr">
+      <c r="F32" s="85" t="inlineStr">
         <is>
           <t>Published: 10% all-in, processing included</t>
         </is>
@@ -9547,16 +9566,16 @@
           <t>Passes</t>
         </is>
       </c>
-      <c r="B33" s="82" t="n">
+      <c r="B33" s="83" t="n">
         <v>0.1</v>
       </c>
-      <c r="C33" s="83" t="n">
+      <c r="C33" s="84" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="83" t="n">
+      <c r="D33" s="84" t="n">
         <v>29</v>
       </c>
-      <c r="F33" s="84" t="inlineStr">
+      <c r="F33" s="85" t="inlineStr">
         <is>
           <t>Sacra; Passes rebrand release Apr 2026</t>
         </is>
@@ -9568,23 +9587,23 @@
           <t>Stride (proposed)</t>
         </is>
       </c>
-      <c r="B34" s="82" t="n">
+      <c r="B34" s="83" t="n">
         <v>0.15</v>
       </c>
-      <c r="C34" s="83" t="n">
+      <c r="C34" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="83" t="n">
+      <c r="D34" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="84" t="inlineStr">
+      <c r="F34" s="85" t="inlineStr">
         <is>
           <t>Our decision, see MarketModel</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="81" t="inlineStr">
+      <c r="A36" s="82" t="inlineStr">
         <is>
           <t>INTERMEDIARIES the athlete already pays</t>
         </is>
@@ -9596,13 +9615,13 @@
           <t>Sports agent: endorsement</t>
         </is>
       </c>
-      <c r="B37" s="82" t="n">
+      <c r="B37" s="83" t="n">
         <v>0.1</v>
       </c>
-      <c r="C37" s="82" t="n">
+      <c r="C37" s="83" t="n">
         <v>0.2</v>
       </c>
-      <c r="F37" s="84" t="inlineStr">
+      <c r="F37" s="85" t="inlineStr">
         <is>
           <t>Unregulated; widely reported, no primary source</t>
         </is>
@@ -9614,13 +9633,13 @@
           <t>Sports agent: playing contract</t>
         </is>
       </c>
-      <c r="B38" s="82" t="n">
+      <c r="B38" s="83" t="n">
         <v>0.02</v>
       </c>
-      <c r="C38" s="82" t="n">
+      <c r="C38" s="83" t="n">
         <v>0.05</v>
       </c>
-      <c r="F38" s="84" t="inlineStr">
+      <c r="F38" s="85" t="inlineStr">
         <is>
           <t>NBPA reg. 4.B (Sept 2025); FIFA FFAR art. 15</t>
         </is>
@@ -9632,20 +9651,20 @@
           <t>OnlyFans management agency</t>
         </is>
       </c>
-      <c r="B39" s="82" t="n">
+      <c r="B39" s="83" t="n">
         <v>0.2</v>
       </c>
-      <c r="C39" s="82" t="n">
+      <c r="C39" s="83" t="n">
         <v>0.5</v>
       </c>
-      <c r="F39" s="84" t="inlineStr">
+      <c r="F39" s="85" t="inlineStr">
         <is>
           <t>Aruna Talent rate guide 2026, on top of the 20%</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="81" t="inlineStr">
+      <c r="A41" s="82" t="inlineStr">
         <is>
           <t>SPONSORSHIP MARKET - top down, for context not for sizing</t>
         </is>
@@ -9659,39 +9678,39 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="76" t="inlineStr">
+      <c r="A43" s="77" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B43" s="76" t="inlineStr">
+      <c r="B43" s="77" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C43" s="76" t="inlineStr">
+      <c r="C43" s="77" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D43" s="76" t="inlineStr">
+      <c r="D43" s="77" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="E43" s="76" t="inlineStr">
+      <c r="E43" s="77" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F43" s="76" t="inlineStr">
+      <c r="F43" s="77" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="77" t="inlineStr">
+      <c r="A44" s="78" t="inlineStr">
         <is>
           <t>Total sponsorship market</t>
         </is>
@@ -9699,29 +9718,29 @@
       <c r="B44" s="36" t="n">
         <v>34450000000</v>
       </c>
-      <c r="C44" s="79" t="inlineStr">
+      <c r="C44" s="80" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D44" s="79" t="inlineStr">
+      <c r="D44" s="80" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="E44" s="79" t="inlineStr">
+      <c r="E44" s="80" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F44" s="79" t="inlineStr">
+      <c r="F44" s="80" t="inlineStr">
         <is>
           <t>European Sponsorship Association, analysis by Nielsen Sports, 12 Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="77" t="inlineStr">
+      <c r="A45" s="78" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
@@ -9729,29 +9748,29 @@
       <c r="B45" s="36" t="n">
         <v>24790000000</v>
       </c>
-      <c r="C45" s="79" t="inlineStr">
+      <c r="C45" s="80" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D45" s="79" t="inlineStr">
+      <c r="D45" s="80" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="E45" s="79" t="inlineStr">
+      <c r="E45" s="80" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F45" s="79" t="inlineStr">
+      <c r="F45" s="80" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: 72% of the total, +5.9% YoY</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="77" t="inlineStr">
+      <c r="A46" s="78" t="inlineStr">
         <is>
           <t>Non-sport sponsorship</t>
         </is>
@@ -9759,29 +9778,29 @@
       <c r="B46" s="36" t="n">
         <v>9660000000</v>
       </c>
-      <c r="C46" s="79" t="inlineStr">
+      <c r="C46" s="80" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D46" s="79" t="inlineStr">
+      <c r="D46" s="80" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="E46" s="79" t="inlineStr">
+      <c r="E46" s="80" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F46" s="79" t="inlineStr">
+      <c r="F46" s="80" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +1.8% YoY</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="77" t="inlineStr">
+      <c r="A47" s="78" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
@@ -9789,29 +9808,29 @@
       <c r="B47" s="36" t="n">
         <v>2180000000</v>
       </c>
-      <c r="C47" s="79" t="inlineStr">
+      <c r="C47" s="80" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D47" s="79" t="inlineStr">
+      <c r="D47" s="80" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="E47" s="79" t="inlineStr">
+      <c r="E47" s="80" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F47" s="79" t="inlineStr">
+      <c r="F47" s="80" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +14%, the fastest growing major European market</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="77" t="inlineStr">
+      <c r="A48" s="78" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
@@ -9819,29 +9838,29 @@
       <c r="B48" s="36" t="n">
         <v>6260000000</v>
       </c>
-      <c r="C48" s="79" t="inlineStr">
+      <c r="C48" s="80" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D48" s="79" t="inlineStr">
+      <c r="D48" s="80" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E48" s="79" t="inlineStr">
+      <c r="E48" s="80" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F48" s="79" t="inlineStr">
+      <c r="F48" s="80" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: the largest European market</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="77" t="inlineStr">
+      <c r="A49" s="78" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
@@ -9849,29 +9868,29 @@
       <c r="B49" s="36" t="n">
         <v>6150000000</v>
       </c>
-      <c r="C49" s="79" t="inlineStr">
+      <c r="C49" s="80" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D49" s="79" t="inlineStr">
+      <c r="D49" s="80" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E49" s="79" t="inlineStr">
+      <c r="E49" s="80" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F49" s="79" t="inlineStr">
+      <c r="F49" s="80" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +10.5%</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="77" t="inlineStr">
+      <c r="A50" s="78" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
@@ -9879,29 +9898,29 @@
       <c r="B50" s="36" t="n">
         <v>2010000000</v>
       </c>
-      <c r="C50" s="79" t="inlineStr">
+      <c r="C50" s="80" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D50" s="79" t="inlineStr">
+      <c r="D50" s="80" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="E50" s="79" t="inlineStr">
+      <c r="E50" s="80" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F50" s="79" t="inlineStr">
+      <c r="F50" s="80" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +5%</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="77" t="inlineStr">
+      <c r="A51" s="78" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
@@ -9909,29 +9928,29 @@
       <c r="B51" s="36" t="n">
         <v>1850000000</v>
       </c>
-      <c r="C51" s="79" t="inlineStr">
+      <c r="C51" s="80" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D51" s="79" t="inlineStr">
+      <c r="D51" s="80" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="E51" s="79" t="inlineStr">
+      <c r="E51" s="80" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F51" s="79" t="inlineStr">
+      <c r="F51" s="80" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +10.3%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="81" t="inlineStr">
+      <c r="A53" s="82" t="inlineStr">
         <is>
           <t>European SPORT sponsorship by year, EUR bn</t>
         </is>
@@ -9958,22 +9977,22 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="85" t="n">
+      <c r="A55" s="86" t="n">
         <v>20.26</v>
       </c>
-      <c r="B55" s="85" t="n">
+      <c r="B55" s="86" t="n">
         <v>19.8</v>
       </c>
-      <c r="C55" s="85" t="n">
+      <c r="C55" s="86" t="n">
         <v>20.69</v>
       </c>
-      <c r="D55" s="85" t="n">
+      <c r="D55" s="86" t="n">
         <v>21.98</v>
       </c>
-      <c r="E55" s="85" t="n">
+      <c r="E55" s="86" t="n">
         <v>23.41</v>
       </c>
-      <c r="F55" s="85" t="n">
+      <c r="F55" s="86" t="n">
         <v>24.79</v>
       </c>
     </row>
@@ -9985,136 +10004,136 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="81" t="inlineStr">
+      <c r="A58" s="82" t="inlineStr">
         <is>
           <t>FAN DEMAND - published surveys bearing on the fan thesis</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="76" t="inlineStr">
+      <c r="A59" s="77" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B59" s="76" t="inlineStr">
+      <c r="B59" s="77" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C59" s="76" t="inlineStr">
+      <c r="C59" s="77" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D59" s="76" t="inlineStr">
+      <c r="D59" s="77" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="E59" s="76" t="inlineStr">
+      <c r="E59" s="77" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F59" s="76" t="inlineStr">
+      <c r="F59" s="77" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="77" t="inlineStr">
+      <c r="A60" s="78" t="inlineStr">
         <is>
           <t>Weekly minutes, fan-generated content</t>
         </is>
       </c>
-      <c r="B60" s="78" t="n">
+      <c r="B60" s="79" t="n">
         <v>115</v>
       </c>
-      <c r="C60" s="79" t="inlineStr">
+      <c r="C60" s="80" t="inlineStr">
         <is>
           <t>minutes/week</t>
         </is>
       </c>
-      <c r="D60" s="79" t="inlineStr">
+      <c r="D60" s="80" t="inlineStr">
         <is>
           <t>FR DE IT ES UK US</t>
         </is>
       </c>
-      <c r="E60" s="79" t="inlineStr">
+      <c r="E60" s="80" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F60" s="79" t="inlineStr">
+      <c r="F60" s="80" t="inlineStr">
         <is>
           <t>Altman Solon / IRIS Sport, 6,000 respondents who watch sports video monthly</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="77" t="inlineStr">
+      <c r="A61" s="78" t="inlineStr">
         <is>
           <t>Weekly minutes, highlights and clips</t>
         </is>
       </c>
-      <c r="B61" s="78" t="n">
+      <c r="B61" s="79" t="n">
         <v>115</v>
       </c>
-      <c r="C61" s="79" t="inlineStr">
+      <c r="C61" s="80" t="inlineStr">
         <is>
           <t>minutes/week</t>
         </is>
       </c>
-      <c r="D61" s="79" t="inlineStr">
+      <c r="D61" s="80" t="inlineStr">
         <is>
           <t>FR DE IT ES UK US</t>
         </is>
       </c>
-      <c r="E61" s="79" t="inlineStr">
+      <c r="E61" s="80" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F61" s="79" t="inlineStr">
+      <c r="F61" s="80" t="inlineStr">
         <is>
           <t>Altman Solon / IRIS Sport</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="77" t="inlineStr">
+      <c r="A62" s="78" t="inlineStr">
         <is>
           <t>Weekly minutes, live games and events</t>
         </is>
       </c>
-      <c r="B62" s="78" t="n">
+      <c r="B62" s="79" t="n">
         <v>245</v>
       </c>
-      <c r="C62" s="79" t="inlineStr">
+      <c r="C62" s="80" t="inlineStr">
         <is>
           <t>minutes/week</t>
         </is>
       </c>
-      <c r="D62" s="79" t="inlineStr">
+      <c r="D62" s="80" t="inlineStr">
         <is>
           <t>FR DE IT ES UK US</t>
         </is>
       </c>
-      <c r="E62" s="79" t="inlineStr">
+      <c r="E62" s="80" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F62" s="79" t="inlineStr">
+      <c r="F62" s="80" t="inlineStr">
         <is>
           <t>Altman Solon / IRIS Sport</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="77" t="inlineStr">
+      <c r="A63" s="78" t="inlineStr">
         <is>
           <t>YouTube share of fan-generated viewing</t>
         </is>
@@ -10122,29 +10141,29 @@
       <c r="B63" s="40" t="n">
         <v>0.35</v>
       </c>
-      <c r="C63" s="79" t="inlineStr">
+      <c r="C63" s="80" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D63" s="79" t="inlineStr">
+      <c r="D63" s="80" t="inlineStr">
         <is>
           <t>FR DE IT ES UK US</t>
         </is>
       </c>
-      <c r="E63" s="79" t="inlineStr">
+      <c r="E63" s="80" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F63" s="79" t="inlineStr">
+      <c r="F63" s="80" t="inlineStr">
         <is>
           <t>Altman Solon / IRIS Sport: 40 of 115 minutes, more than linear TV or streaming</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="77" t="inlineStr">
+      <c r="A64" s="78" t="inlineStr">
         <is>
           <t>Subscribers watching MORE sport after subscribing</t>
         </is>
@@ -10152,29 +10171,29 @@
       <c r="B64" s="40" t="n">
         <v>0.7</v>
       </c>
-      <c r="C64" s="79" t="inlineStr">
+      <c r="C64" s="80" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D64" s="79" t="inlineStr">
+      <c r="D64" s="80" t="inlineStr">
         <is>
           <t>Worldwide</t>
         </is>
       </c>
-      <c r="E64" s="79" t="inlineStr">
+      <c r="E64" s="80" t="inlineStr">
         <is>
           <t>Nov 2022</t>
         </is>
       </c>
-      <c r="F64" s="79" t="inlineStr">
+      <c r="F64" s="80" t="inlineStr">
         <is>
           <t>YouGov / Strive, 19,000 respondents: 38% much more + 32% somewhat more</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="77" t="inlineStr">
+      <c r="A65" s="78" t="inlineStr">
         <is>
           <t>Subscribers watching LESS sport after subscribing</t>
         </is>
@@ -10182,29 +10201,29 @@
       <c r="B65" s="40" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C65" s="79" t="inlineStr">
+      <c r="C65" s="80" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D65" s="79" t="inlineStr">
+      <c r="D65" s="80" t="inlineStr">
         <is>
           <t>Worldwide</t>
         </is>
       </c>
-      <c r="E65" s="79" t="inlineStr">
+      <c r="E65" s="80" t="inlineStr">
         <is>
           <t>Nov 2022</t>
         </is>
       </c>
-      <c r="F65" s="79" t="inlineStr">
+      <c r="F65" s="80" t="inlineStr">
         <is>
           <t>YouGov / Strive: 3% much less + 4% somewhat less</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="81" t="inlineStr">
+      <c r="A67" s="82" t="inlineStr">
         <is>
           <t>SPONSORSHIP MARKETPLACES - the direct competitor set</t>
         </is>
@@ -10218,39 +10237,39 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="76" t="inlineStr">
+      <c r="A69" s="77" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B69" s="76" t="inlineStr">
+      <c r="B69" s="77" t="inlineStr">
         <is>
           <t>Founded</t>
         </is>
       </c>
-      <c r="C69" s="76" t="inlineStr">
+      <c r="C69" s="77" t="inlineStr">
         <is>
           <t>Employees (as of)</t>
         </is>
       </c>
-      <c r="D69" s="76" t="inlineStr">
+      <c r="D69" s="77" t="inlineStr">
         <is>
           <t>Total raised</t>
         </is>
       </c>
-      <c r="E69" s="76" t="inlineStr">
+      <c r="E69" s="77" t="inlineStr">
         <is>
           <t>Largest round pre-money</t>
         </is>
       </c>
-      <c r="F69" s="76" t="inlineStr">
+      <c r="F69" s="77" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="86" t="inlineStr">
+      <c r="A70" s="87" t="inlineStr">
         <is>
           <t>Sponsoo (Germany)</t>
         </is>
@@ -10258,7 +10277,7 @@
       <c r="B70" s="41" t="n">
         <v>2014</v>
       </c>
-      <c r="C70" s="78" t="n">
+      <c r="C70" s="79" t="n">
         <v>13</v>
       </c>
       <c r="D70" s="36" t="n">
@@ -10267,14 +10286,14 @@
       <c r="E70" s="36" t="n">
         <v>15900000</v>
       </c>
-      <c r="F70" s="79" t="inlineStr">
+      <c r="F70" s="80" t="inlineStr">
         <is>
           <t>Headcount as of 14 Nov 2025. Privately held, venture backed. Series A 28 Jan 2021; pre-money is a PitchBook ESTIMATE</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="86" t="inlineStr">
+      <c r="A71" s="87" t="inlineStr">
         <is>
           <t>OpenSponsorship (United States)</t>
         </is>
@@ -10282,21 +10301,21 @@
       <c r="B71" s="41" t="n">
         <v>2014</v>
       </c>
-      <c r="C71" s="78" t="n">
+      <c r="C71" s="79" t="n">
         <v>23</v>
       </c>
       <c r="D71" s="36" t="n">
         <v>5400000</v>
       </c>
       <c r="E71" s="36" t="n"/>
-      <c r="F71" s="79" t="inlineStr">
+      <c r="F71" s="80" t="inlineStr">
         <is>
           <t>Headcount as of 9 Mar 2026. Privately held, venture backed. Last priced round not disclosed</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="86" t="inlineStr">
+      <c r="A72" s="87" t="inlineStr">
         <is>
           <t>SponsorUnited (United States)</t>
         </is>
@@ -10304,7 +10323,7 @@
       <c r="B72" s="41" t="n">
         <v>2016</v>
       </c>
-      <c r="C72" s="78" t="n">
+      <c r="C72" s="79" t="n">
         <v>355</v>
       </c>
       <c r="D72" s="36" t="n">
@@ -10313,14 +10332,14 @@
       <c r="E72" s="36" t="n">
         <v>89380000</v>
       </c>
-      <c r="F72" s="79" t="inlineStr">
+      <c r="F72" s="80" t="inlineStr">
         <is>
           <t>Headcount as of 28 May 2026. Privately held, venture backed. Series A 21 Nov 2022</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="86" t="inlineStr">
+      <c r="A73" s="87" t="inlineStr">
         <is>
           <t>Hookit (United States)</t>
         </is>
@@ -10328,7 +10347,7 @@
       <c r="B73" s="41" t="n">
         <v>2001</v>
       </c>
-      <c r="C73" s="78" t="n">
+      <c r="C73" s="79" t="n">
         <v>47</v>
       </c>
       <c r="D73" s="36" t="n">
@@ -10337,41 +10356,41 @@
       <c r="E73" s="36" t="n">
         <v>38400000</v>
       </c>
-      <c r="F73" s="79" t="inlineStr">
+      <c r="F73" s="80" t="inlineStr">
         <is>
           <t>Headcount as of 8 Feb 2022. Acquired, operating subsidiary. Series C2 24 Feb 2020; pre-money is a PitchBook ESTIMATE</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="86" t="inlineStr">
+      <c r="A74" s="87" t="inlineStr">
         <is>
           <t>Stride (this plan, at Y10)</t>
         </is>
       </c>
-      <c r="B74" s="87" t="n">
+      <c r="B74" s="88" t="n">
         <v>2026</v>
       </c>
-      <c r="C74" s="88">
+      <c r="C74" s="89">
         <f>Assumptions!L66</f>
         <v/>
       </c>
-      <c r="D74" s="89">
+      <c r="D74" s="90">
         <f>SUM(Funding!C4:L4)</f>
         <v/>
       </c>
-      <c r="E74" s="89">
+      <c r="E74" s="90">
         <f>Funding!H5</f>
         <v/>
       </c>
-      <c r="F74" s="79" t="inlineStr">
+      <c r="F74" s="80" t="inlineStr">
         <is>
           <t>Deliberately sized near Sponsoo. Only EUR 400k of the total is capital the plan depends on; the growth round is optional</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="81" t="inlineStr">
+      <c r="A76" s="82" t="inlineStr">
         <is>
           <t>REVENUE PER EMPLOYEE - what the plan is tested against</t>
         </is>
@@ -10403,10 +10422,10 @@
           <t>Median private B2B SaaS, all stages</t>
         </is>
       </c>
-      <c r="B78" s="90" t="n">
+      <c r="B78" s="91" t="n">
         <v>135000</v>
       </c>
-      <c r="F78" s="91" t="inlineStr">
+      <c r="F78" s="92" t="inlineStr">
         <is>
           <t>SaaS Capital 2025 survey of ~1,000 private B2B SaaS companies</t>
         </is>
@@ -10418,10 +10437,10 @@
           <t>Top quartile private B2B SaaS</t>
         </is>
       </c>
-      <c r="B79" s="90" t="n">
+      <c r="B79" s="91" t="n">
         <v>215000</v>
       </c>
-      <c r="F79" s="91" t="inlineStr">
+      <c r="F79" s="92" t="inlineStr">
         <is>
           <t>SaaS Capital 2025 survey, 75th percentile</t>
         </is>
@@ -10433,10 +10452,10 @@
           <t>Efficient public SaaS at scale</t>
         </is>
       </c>
-      <c r="B80" s="90" t="n">
+      <c r="B80" s="91" t="n">
         <v>300000</v>
       </c>
-      <c r="F80" s="91" t="inlineStr">
+      <c r="F80" s="92" t="inlineStr">
         <is>
           <t>Public SaaS medians, widely reported range EUR 250-350k</t>
         </is>
@@ -10448,11 +10467,11 @@
           <t>Stride (this plan, Y7)</t>
         </is>
       </c>
-      <c r="B81" s="92">
+      <c r="B81" s="93">
         <f>KPIs!I14</f>
         <v/>
       </c>
-      <c r="F81" s="91" t="inlineStr">
+      <c r="F81" s="92" t="inlineStr">
         <is>
           <t>Above the top quartile. Defended in section 3.2.2: the fan side is self-serve and moderation is a variable cost, not headcount</t>
         </is>
@@ -10464,11 +10483,11 @@
           <t>Multiple of the top quartile</t>
         </is>
       </c>
-      <c r="B82" s="93">
+      <c r="B82" s="94">
         <f>B81/B79</f>
         <v/>
       </c>
-      <c r="F82" s="84" t="inlineStr">
+      <c r="F82" s="85" t="inlineStr">
         <is>
           <t>The plan's second most aggressive assumption after fan churn</t>
         </is>
@@ -10482,300 +10501,300 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="94" t="inlineStr">
+      <c r="A86" s="95" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 filed accounts (Fenix International Ltd)</t>
         </is>
       </c>
-      <c r="B86" s="95" t="inlineStr">
+      <c r="B86" s="96" t="inlineStr">
         <is>
           <t>https://find-and-update.company-information.service.gov.uk/company/10354575/filing-history</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="94" t="inlineStr">
+      <c r="A87" s="95" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 as reported</t>
         </is>
       </c>
-      <c r="B87" s="95" t="inlineStr">
+      <c r="B87" s="96" t="inlineStr">
         <is>
           <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="94" t="inlineStr">
+      <c r="A88" s="95" t="inlineStr">
         <is>
           <t>Patreon published take rate</t>
         </is>
       </c>
-      <c r="B88" s="95" t="inlineStr">
+      <c r="B88" s="96" t="inlineStr">
         <is>
           <t>https://www.patreon.com/pricing</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="94" t="inlineStr">
+      <c r="A89" s="95" t="inlineStr">
         <is>
           <t>Patreon creators</t>
         </is>
       </c>
-      <c r="B89" s="95" t="inlineStr">
+      <c r="B89" s="96" t="inlineStr">
         <is>
           <t>https://backlinko.com/patreon-users</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="94" t="inlineStr">
+      <c r="A90" s="95" t="inlineStr">
         <is>
           <t>Passes economics</t>
         </is>
       </c>
-      <c r="B90" s="95" t="inlineStr">
+      <c r="B90" s="96" t="inlineStr">
         <is>
           <t>https://sacra.com/c/passes/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="94" t="inlineStr">
+      <c r="A91" s="95" t="inlineStr">
         <is>
           <t>Fanfix creator terms (states no take rate)</t>
         </is>
       </c>
-      <c r="B91" s="95" t="inlineStr">
+      <c r="B91" s="96" t="inlineStr">
         <is>
           <t>https://auth.fanfix.io/creator-terms-of-use</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="94" t="inlineStr">
+      <c r="A92" s="95" t="inlineStr">
         <is>
           <t>Agency commissions</t>
         </is>
       </c>
-      <c r="B92" s="95" t="inlineStr">
+      <c r="B92" s="96" t="inlineStr">
         <is>
           <t>https://arunatalent.com/blog/onlyfans-agency-commission-rates/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="94" t="inlineStr">
+      <c r="A93" s="95" t="inlineStr">
         <is>
           <t>NBPA agent fee cap (amended Sept 2025)</t>
         </is>
       </c>
-      <c r="B93" s="95" t="inlineStr">
+      <c r="B93" s="96" t="inlineStr">
         <is>
           <t>https://imgix.cosmicjs.com/cd844850-97c7-11f0-91fa-d9e1671c2776-NBPA-REGULATIONS-GOVERNING-PLAYER-AGENTS-09-2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="94" t="inlineStr">
+      <c r="A94" s="95" t="inlineStr">
         <is>
           <t>FIFA Football Agent Regulations art. 15</t>
         </is>
       </c>
-      <c r="B94" s="95" t="inlineStr">
+      <c r="B94" s="96" t="inlineStr">
         <is>
           <t>https://digitalhub.fifa.com/m/1e7b741fa0fae779/original/FIFA-Football-Agent-Regulations.pdf</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="94" t="inlineStr">
+      <c r="A95" s="95" t="inlineStr">
         <is>
           <t>CJEU upholds the FIFA fee cap (16 Jul 2026)</t>
         </is>
       </c>
-      <c r="B95" s="95" t="inlineStr">
+      <c r="B95" s="96" t="inlineStr">
         <is>
           <t>https://inside.fifa.com/news/welcomes-court-of-justice-european-union-decision-football-agent-regulations</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="94" t="inlineStr">
+      <c r="A96" s="95" t="inlineStr">
         <is>
           <t>Eurobarometer 525</t>
         </is>
       </c>
-      <c r="B96" s="95" t="inlineStr">
+      <c r="B96" s="96" t="inlineStr">
         <is>
           <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="94" t="inlineStr">
+      <c r="A97" s="95" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="B97" s="95" t="inlineStr">
+      <c r="B97" s="96" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="94" t="inlineStr">
+      <c r="A98" s="95" t="inlineStr">
         <is>
           <t>Stripe EU pricing</t>
         </is>
       </c>
-      <c r="B98" s="95" t="inlineStr">
+      <c r="B98" s="96" t="inlineStr">
         <is>
           <t>https://stripe.com/es/pricing</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="94" t="inlineStr">
+      <c r="A99" s="95" t="inlineStr">
         <is>
           <t>TEKTA launch</t>
         </is>
       </c>
-      <c r="B99" s="95" t="inlineStr">
+      <c r="B99" s="96" t="inlineStr">
         <is>
           <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="94" t="inlineStr">
+      <c r="A100" s="95" t="inlineStr">
         <is>
           <t>Stripe Connect age</t>
         </is>
       </c>
-      <c r="B100" s="95" t="inlineStr">
+      <c r="B100" s="96" t="inlineStr">
         <is>
           <t>https://support.stripe.com/questions/age-requirement-to-create-a-stripe-account</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="94" t="inlineStr">
+      <c r="A101" s="95" t="inlineStr">
         <is>
           <t>PitchBook: Sponsoo GmbH</t>
         </is>
       </c>
-      <c r="B101" s="95" t="inlineStr">
+      <c r="B101" s="96" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/103066-39</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="94" t="inlineStr">
+      <c r="A102" s="95" t="inlineStr">
         <is>
           <t>PitchBook: OpenSponsorship</t>
         </is>
       </c>
-      <c r="B102" s="95" t="inlineStr">
+      <c r="B102" s="96" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/113575-96</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="94" t="inlineStr">
+      <c r="A103" s="95" t="inlineStr">
         <is>
           <t>PitchBook: SponsorUnited</t>
         </is>
       </c>
-      <c r="B103" s="95" t="inlineStr">
+      <c r="B103" s="96" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/169635-43</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="94" t="inlineStr">
+      <c r="A104" s="95" t="inlineStr">
         <is>
           <t>PitchBook: Hookit</t>
         </is>
       </c>
-      <c r="B104" s="95" t="inlineStr">
+      <c r="B104" s="96" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/55307-17</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="94" t="inlineStr">
+      <c r="A105" s="95" t="inlineStr">
         <is>
           <t>ESA European sponsorship market 2025</t>
         </is>
       </c>
-      <c r="B105" s="95" t="inlineStr">
+      <c r="B105" s="96" t="inlineStr">
         <is>
           <t>https://sponsorship.org/european-sponsorship-market-reaches-e34-45bn-in-2025-as-growth-continues-across-all-sectors/</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="94" t="inlineStr">
+      <c r="A106" s="95" t="inlineStr">
         <is>
           <t>SportsPro on the ESA 2026 market overview</t>
         </is>
       </c>
-      <c r="B106" s="95" t="inlineStr">
+      <c r="B106" s="96" t="inlineStr">
         <is>
           <t>https://www.sportspro.com/news/sponsorship-marketing/sports-sponsorship-european-market-valuation-esa-march-2026/</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="94" t="inlineStr">
+      <c r="A107" s="95" t="inlineStr">
         <is>
           <t>European sport sponsorship 2019-2025 (ESA via Statista)</t>
         </is>
       </c>
-      <c r="B107" s="95" t="inlineStr">
+      <c r="B107" s="96" t="inlineStr">
         <is>
           <t>https://www.statista.com/statistics/1430225/sports-sponsorship-market-size-europe/</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="94" t="inlineStr">
+      <c r="A108" s="95" t="inlineStr">
         <is>
           <t>Sports content formats by channel (Altman Solon / IRIS Sport)</t>
         </is>
       </c>
-      <c r="B108" s="95" t="inlineStr">
+      <c r="B108" s="96" t="inlineStr">
         <is>
           <t>https://www.statista.com/statistics/1660170/time-spent-weekly-watching-sports-formats-by-channel/</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="94" t="inlineStr">
+      <c r="A109" s="95" t="inlineStr">
         <is>
           <t>Impact of subscriptions on sports consumption (YouGov / Strive)</t>
         </is>
       </c>
-      <c r="B109" s="95" t="inlineStr">
+      <c r="B109" s="96" t="inlineStr">
         <is>
           <t>https://www.statista.com/statistics/1413187/impact-subscriptions-sports-content-consumption/</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="94" t="inlineStr">
+      <c r="A110" s="95" t="inlineStr">
         <is>
           <t>SaaS Capital revenue per employee benchmarks</t>
         </is>
       </c>
-      <c r="B110" s="95" t="inlineStr">
+      <c r="B110" s="96" t="inlineStr">
         <is>
           <t>https://www.saas-capital.com/blog-posts/revenue-per-employee-benchmarks-for-private-saas-companies/</t>
         </is>
@@ -10873,36 +10892,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="96" t="inlineStr">
+      <c r="C3" s="97" t="inlineStr">
         <is>
           <t>Input: change me</t>
         </is>
       </c>
-      <c r="D3" s="97" t="n"/>
-      <c r="E3" s="98" t="inlineStr">
+      <c r="D3" s="98" t="n"/>
+      <c r="E3" s="99" t="inlineStr">
         <is>
           <t>Sourced fact</t>
         </is>
       </c>
-      <c r="F3" s="97" t="n"/>
-      <c r="G3" s="99" t="inlineStr">
+      <c r="F3" s="98" t="n"/>
+      <c r="G3" s="100" t="inlineStr">
         <is>
           <t>Formula (this sheet)</t>
         </is>
       </c>
-      <c r="H3" s="97" t="n"/>
-      <c r="I3" s="100" t="inlineStr">
+      <c r="H3" s="98" t="n"/>
+      <c r="I3" s="101" t="inlineStr">
         <is>
           <t>Dependent value</t>
         </is>
       </c>
-      <c r="J3" s="97" t="n"/>
-      <c r="K3" s="101" t="inlineStr">
+      <c r="J3" s="98" t="n"/>
+      <c r="K3" s="102" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="L3" s="97" t="n"/>
+      <c r="L3" s="98" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -10924,7 +10943,7 @@
         <f>Comparables!B14</f>
         <v/>
       </c>
-      <c r="D6" s="91" t="inlineStr">
+      <c r="D6" s="92" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -10940,7 +10959,7 @@
         <f>Comparables!B12</f>
         <v/>
       </c>
-      <c r="D7" s="91" t="inlineStr">
+      <c r="D7" s="92" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -10952,11 +10971,11 @@
           <t>Members per paying creator</t>
         </is>
       </c>
-      <c r="B8" s="68">
+      <c r="B8" s="69">
         <f>B6/B7</f>
         <v/>
       </c>
-      <c r="D8" s="91" t="inlineStr">
+      <c r="D8" s="92" t="inlineStr">
         <is>
           <t>The single most useful benchmark we found: it is measured, not modelled.</t>
         </is>
@@ -10972,7 +10991,7 @@
         <f>Comparables!B9/Comparables!B8</f>
         <v/>
       </c>
-      <c r="D9" s="91" t="inlineStr">
+      <c r="D9" s="92" t="inlineStr">
         <is>
           <t>Fan ACCOUNTS, not paying fans - most follow free. Shown as an upper bound only.</t>
         </is>
@@ -10987,7 +11006,7 @@
       <c r="B10" s="26" t="n">
         <v>1.06</v>
       </c>
-      <c r="D10" s="91" t="inlineStr">
+      <c r="D10" s="92" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +6% on the Patreon benchmark. Sport audiences are smaller but convert better, because the fan usually does the sport themselves.</t>
         </is>
@@ -11002,7 +11021,7 @@
       <c r="B11" s="26" t="n">
         <v>1.37</v>
       </c>
-      <c r="D11" s="91" t="inlineStr">
+      <c r="D11" s="92" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +37%. Much larger followings, much weaker conversion - more paying fans in absolute terms even though a smaller share converts.</t>
         </is>
@@ -11014,11 +11033,11 @@
           <t>→ Niche fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B12" s="102">
+      <c r="B12" s="103">
         <f>B8*B10</f>
         <v/>
       </c>
-      <c r="D12" s="91" t="inlineStr"/>
+      <c r="D12" s="92" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -11026,11 +11045,11 @@
           <t>→ Popular fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B13" s="102">
+      <c r="B13" s="103">
         <f>B8*B11</f>
         <v/>
       </c>
-      <c r="D13" s="91" t="inlineStr"/>
+      <c r="D13" s="92" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -11051,7 +11070,7 @@
       <c r="B15" s="22" t="n">
         <v>4.99</v>
       </c>
-      <c r="D15" s="91" t="inlineStr"/>
+      <c r="D15" s="92" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -11062,7 +11081,7 @@
       <c r="B16" s="22" t="n">
         <v>9.99</v>
       </c>
-      <c r="D16" s="91" t="inlineStr"/>
+      <c r="D16" s="92" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
@@ -11073,7 +11092,7 @@
       <c r="B17" s="22" t="n">
         <v>24.99</v>
       </c>
-      <c r="D17" s="91" t="inlineStr"/>
+      <c r="D17" s="92" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -11084,7 +11103,7 @@
       <c r="B18" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="D18" s="91" t="inlineStr">
+      <c r="D18" s="92" t="inlineStr">
         <is>
           <t>Assumed distribution; replace with the real tier mix after P1.</t>
         </is>
@@ -11099,7 +11118,7 @@
       <c r="B19" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="D19" s="91" t="inlineStr"/>
+      <c r="D19" s="92" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -11110,7 +11129,7 @@
       <c r="B20" s="18" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="91" t="inlineStr"/>
+      <c r="D20" s="92" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -11122,7 +11141,7 @@
         <f>B18+B19+B20</f>
         <v/>
       </c>
-      <c r="D21" s="91" t="inlineStr"/>
+      <c r="D21" s="92" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -11130,11 +11149,11 @@
           <t>→ Weighted ARPU per month</t>
         </is>
       </c>
-      <c r="B22" s="103">
+      <c r="B22" s="104">
         <f>B15*B18+B16*B19+B17*B20</f>
         <v/>
       </c>
-      <c r="D22" s="91" t="inlineStr">
+      <c r="D22" s="92" t="inlineStr">
         <is>
           <t>Cross-check: Patreon reports $6.10 average support and a $8-12 typical band. Landing inside that band from an independent tier build is a good sign.</t>
         </is>
@@ -11150,7 +11169,7 @@
         <f>Comparables!B16</f>
         <v/>
       </c>
-      <c r="D23" s="91" t="inlineStr">
+      <c r="D23" s="92" t="inlineStr">
         <is>
           <t>Published average - below our figure because Patreon's long tail includes many $1-3 tiers. Our EUR 9.49 sits inside their $8-12 typical band.</t>
         </is>
@@ -11165,7 +11184,7 @@
       <c r="B24" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="91" t="inlineStr">
+      <c r="D24" s="92" t="inlineStr">
         <is>
           <t>Niche fans buy knowledge and sit at the tier mix above.</t>
         </is>
@@ -11180,7 +11199,7 @@
       <c r="B25" s="26" t="n">
         <v>0.87</v>
       </c>
-      <c r="D25" s="91" t="inlineStr">
+      <c r="D25" s="92" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: -13%. Popular-sport fans skew to the cheapest tier.</t>
         </is>
@@ -11192,11 +11211,11 @@
           <t>→ Niche ARPU, mature</t>
         </is>
       </c>
-      <c r="B26" s="103">
+      <c r="B26" s="104">
         <f>B22*B24</f>
         <v/>
       </c>
-      <c r="D26" s="91" t="inlineStr"/>
+      <c r="D26" s="92" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -11204,11 +11223,11 @@
           <t>→ Popular ARPU, mature</t>
         </is>
       </c>
-      <c r="B27" s="103">
+      <c r="B27" s="104">
         <f>B22*B25</f>
         <v/>
       </c>
-      <c r="D27" s="91" t="inlineStr"/>
+      <c r="D27" s="92" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -11230,7 +11249,7 @@
         <f>Comparables!B19</f>
         <v/>
       </c>
-      <c r="D29" s="91" t="inlineStr"/>
+      <c r="D29" s="92" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
@@ -11242,7 +11261,7 @@
         <f>Comparables!B20</f>
         <v/>
       </c>
-      <c r="D30" s="91" t="inlineStr"/>
+      <c r="D30" s="92" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
@@ -11254,7 +11273,7 @@
         <f>(B29+B30)/2</f>
         <v/>
       </c>
-      <c r="D31" s="91" t="inlineStr"/>
+      <c r="D31" s="92" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -11266,7 +11285,7 @@
         <f>Comparables!B21</f>
         <v/>
       </c>
-      <c r="D32" s="91" t="inlineStr">
+      <c r="D32" s="92" t="inlineStr">
         <is>
           <t>Patreon: annual patrons churn at one third the monthly rate.</t>
         </is>
@@ -11281,7 +11300,7 @@
       <c r="B33" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="91" t="inlineStr">
+      <c r="D33" s="92" t="inlineStr">
         <is>
           <t>Our target for the season pass. This is the one lever that improves churn without changing the product.</t>
         </is>
@@ -11297,7 +11316,7 @@
         <f>B31*(1-B33)+B31*B32*B33</f>
         <v/>
       </c>
-      <c r="D34" s="91" t="inlineStr">
+      <c r="D34" s="92" t="inlineStr">
         <is>
           <t>What a Patreon-like platform would see with our annual mix.</t>
         </is>
@@ -11312,7 +11331,7 @@
       <c r="B35" s="26" t="n">
         <v>0.55</v>
       </c>
-      <c r="D35" s="91" t="inlineStr">
+      <c r="D35" s="92" t="inlineStr">
         <is>
           <t>OUR CLAIM, UNTESTED, AND THE MOST OPTIMISTIC JUDGEMENT IN THE MODEL: this says niche fans churn 45% SLOWER than the Patreon benchmark, because training content is habitual and competitive seasons create renewal moments. Nothing yet proves it. If it is wrong and we are merely at benchmark, Y10 revenue falls by roughly EUR 7M.</t>
         </is>
@@ -11327,7 +11346,7 @@
       <c r="B36" s="26" t="n">
         <v>0.85</v>
       </c>
-      <c r="D36" s="91" t="inlineStr">
+      <c r="D36" s="92" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: 15% better than benchmark. Impulse follows after a result, with many free substitutes - but still a sport fan rather than a general creator audience.</t>
         </is>
@@ -11339,11 +11358,11 @@
           <t>→ Niche churn, mature</t>
         </is>
       </c>
-      <c r="B37" s="104">
+      <c r="B37" s="105">
         <f>B34*B35</f>
         <v/>
       </c>
-      <c r="D37" s="91" t="inlineStr"/>
+      <c r="D37" s="92" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -11351,11 +11370,11 @@
           <t>→ Popular churn, mature</t>
         </is>
       </c>
-      <c r="B38" s="104">
+      <c r="B38" s="105">
         <f>B34*B36</f>
         <v/>
       </c>
-      <c r="D38" s="91" t="inlineStr"/>
+      <c r="D38" s="92" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
@@ -11377,7 +11396,7 @@
         <f>Comparables!B7/Comparables!B8/12</f>
         <v/>
       </c>
-      <c r="D40" s="91" t="inlineStr">
+      <c r="D40" s="92" t="inlineStr">
         <is>
           <t>Includes dormant accounts, so this is a floor.</t>
         </is>
@@ -11393,7 +11412,7 @@
         <f>Comparables!B15/Comparables!B12/12</f>
         <v/>
       </c>
-      <c r="D41" s="91" t="inlineStr">
+      <c r="D41" s="92" t="inlineStr">
         <is>
           <t>Denominator is creators WITH members, so this is a ceiling.</t>
         </is>
@@ -11405,11 +11424,11 @@
           <t>Stride: modelled niche athlete, mature</t>
         </is>
       </c>
-      <c r="B42" s="103">
+      <c r="B42" s="104">
         <f>B12*B22*(1-Assumptions!$C$40)</f>
         <v/>
       </c>
-      <c r="D42" s="91" t="inlineStr">
+      <c r="D42" s="92" t="inlineStr">
         <is>
           <t>Ours sits between the two, which is where a plausible figure should sit.</t>
         </is>
@@ -11425,7 +11444,7 @@
         <f>Comparables!B11</f>
         <v/>
       </c>
-      <c r="D43" s="91" t="inlineStr">
+      <c r="D43" s="92" t="inlineStr">
         <is>
           <t>THE CAVEAT ON EVERY AVERAGE ABOVE: earnings follow a power law. Totals are unaffected, but the median athlete earns far less than the mean. Do not pitch the mean to an athlete.</t>
         </is>
@@ -11450,7 +11469,7 @@
       <c r="B45" s="26" t="n">
         <v>0.92</v>
       </c>
-      <c r="D45" s="91" t="inlineStr">
+      <c r="D45" s="92" t="inlineStr">
         <is>
           <t>Comparables are published in USD; this model is in EUR. Applied to the per-transaction and monthly creator fees below.</t>
         </is>
@@ -11465,7 +11484,7 @@
       <c r="B46" s="22" t="n">
         <v>300</v>
       </c>
-      <c r="D46" s="91" t="inlineStr">
+      <c r="D46" s="92" t="inlineStr">
         <is>
           <t>Change this to see who is cheapest at any revenue level.</t>
         </is>
@@ -11481,7 +11500,7 @@
         <f>B46*(1-Comparables!B29)-B46/Assumptions!$C$54*Comparables!C29*B45-Comparables!D29*B45</f>
         <v/>
       </c>
-      <c r="D47" s="91" t="inlineStr">
+      <c r="D47" s="92" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -11497,7 +11516,7 @@
         <f>B46*(1-Comparables!B32)-B46/Assumptions!$C$54*Comparables!C32*B45-Comparables!D32*B45</f>
         <v/>
       </c>
-      <c r="D48" s="91" t="inlineStr">
+      <c r="D48" s="92" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -11513,7 +11532,7 @@
         <f>B46*(1-Comparables!B33)-B46/Assumptions!$C$54*Comparables!C33*B45-Comparables!D33*B45</f>
         <v/>
       </c>
-      <c r="D49" s="91" t="inlineStr">
+      <c r="D49" s="92" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -11529,7 +11548,7 @@
         <f>B46*(1-Comparables!B34)-B46/Assumptions!$C$54*Comparables!C34*B45-Comparables!D34*B45</f>
         <v/>
       </c>
-      <c r="D50" s="91" t="inlineStr">
+      <c r="D50" s="92" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -11545,7 +11564,7 @@
         <f>Comparables!D33*B45/((Comparables!B34-Comparables!B33)-Comparables!C33*B45/Assumptions!$C$54)</f>
         <v/>
       </c>
-      <c r="D51" s="91" t="inlineStr">
+      <c r="D51" s="92" t="inlineStr">
         <is>
           <t>Below this, our flat 15% pays the athlete more than Passes' 10% plus fees. Our modelled athlete earns far less than this, so the long tail is on our side of the line.</t>
         </is>
@@ -11567,10 +11586,10 @@
           <t>Population, 34 countries in scope</t>
         </is>
       </c>
-      <c r="B53" s="105" t="n">
+      <c r="B53" s="106" t="n">
         <v>2726.2</v>
       </c>
-      <c r="D53" s="91" t="inlineStr">
+      <c r="D53" s="92" t="inlineStr">
         <is>
           <t>Millions. Eurostat / national statistics offices.</t>
         </is>
@@ -11582,10 +11601,10 @@
           <t>Population, Spain</t>
         </is>
       </c>
-      <c r="B54" s="105" t="n">
+      <c r="B54" s="106" t="n">
         <v>48.6</v>
       </c>
-      <c r="D54" s="91" t="inlineStr">
+      <c r="D54" s="92" t="inlineStr">
         <is>
           <t>Millions.</t>
         </is>
@@ -11600,7 +11619,7 @@
       <c r="B55" s="18" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D55" s="91" t="inlineStr">
+      <c r="D55" s="92" t="inlineStr">
         <is>
           <t>Eurobarometer 525 - Spain sits near the EU average of 55% who exercise at all.</t>
         </is>
@@ -11615,7 +11634,7 @@
       <c r="B56" s="18" t="n">
         <v>0.02</v>
       </c>
-      <c r="D56" s="91" t="inlineStr">
+      <c r="D56" s="92" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: competes, posts publicly, has a following worth sponsoring.</t>
         </is>
@@ -11630,7 +11649,7 @@
       <c r="B57" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="D57" s="91" t="inlineStr">
+      <c r="D57" s="92" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: would monetise if the tooling existed.</t>
         </is>
@@ -11642,11 +11661,11 @@
           <t>→ Addressable athletes, Spain</t>
         </is>
       </c>
-      <c r="B58" s="106">
+      <c r="B58" s="107">
         <f>B54*1000000*B55*B56*B57</f>
         <v/>
       </c>
-      <c r="D58" s="91" t="inlineStr"/>
+      <c r="D58" s="92" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -11654,11 +11673,11 @@
           <t>→ Addressable athletes, all 34 countries</t>
         </is>
       </c>
-      <c r="B59" s="106">
+      <c r="B59" s="107">
         <f>B53*1000000*0.5*B56*B57</f>
         <v/>
       </c>
-      <c r="D59" s="91" t="inlineStr">
+      <c r="D59" s="92" t="inlineStr">
         <is>
           <t>Using a 50% blended participation rate across the 34 countries.</t>
         </is>
@@ -11674,7 +11693,7 @@
         <f>Assumptions!$L$5</f>
         <v/>
       </c>
-      <c r="D60" s="91" t="inlineStr"/>
+      <c r="D60" s="92" t="inlineStr"/>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -11682,11 +11701,11 @@
           <t>→ Y10 penetration of Spain SAM</t>
         </is>
       </c>
-      <c r="B61" s="104">
+      <c r="B61" s="105">
         <f>Assumptions!$L$5/B58</f>
         <v/>
       </c>
-      <c r="D61" s="91" t="inlineStr"/>
+      <c r="D61" s="92" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -11694,11 +11713,11 @@
           <t>→ Y10 penetration of full TAM</t>
         </is>
       </c>
-      <c r="B62" s="104">
+      <c r="B62" s="105">
         <f>Assumptions!$L$5/B59</f>
         <v/>
       </c>
-      <c r="D62" s="91" t="inlineStr">
+      <c r="D62" s="92" t="inlineStr">
         <is>
           <t>If this reads as implausibly high, the athlete trajectory is too aggressive - that is exactly what this block exists to reveal.</t>
         </is>
@@ -11749,37 +11768,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="107" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B4" s="107" t="inlineStr">
+      <c r="B4" s="108" t="inlineStr">
         <is>
           <t>Model value</t>
         </is>
       </c>
-      <c r="C4" s="107" t="inlineStr">
+      <c r="C4" s="108" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D4" s="107" t="inlineStr">
+      <c r="D4" s="108" t="inlineStr">
         <is>
           <t>Benchmark / comparable</t>
         </is>
       </c>
-      <c r="E4" s="107" t="inlineStr">
+      <c r="E4" s="108" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F4" s="107" t="inlineStr">
+      <c r="F4" s="108" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="G4" s="107" t="inlineStr">
+      <c r="G4" s="108" t="inlineStr">
         <is>
           <t>What would replace the estimate</t>
         </is>
@@ -11799,7 +11818,7 @@
       <c r="G5" s="14" t="n"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="86" t="inlineStr">
+      <c r="A6" s="87" t="inlineStr">
         <is>
           <t>Take rate on fan revenue</t>
         </is>
@@ -11808,34 +11827,34 @@
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="C6" s="108" t="inlineStr">
+      <c r="C6" s="109" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D6" s="109" t="inlineStr">
+      <c r="D6" s="110" t="inlineStr">
         <is>
           <t>Passes charges 10% but adds $0.30/txn and a $29/month creator fee; OnlyFans, Fansly and Fanfix are all 20%; Patreon 8-12%. A flat 15% with no monthly fee pays an athlete more than Passes for anyone under EUR 1,380/month of fan revenue.</t>
         </is>
       </c>
-      <c r="E6" s="109" t="inlineStr">
+      <c r="E6" s="110" t="inlineStr">
         <is>
           <t>Sacra company profile (Passes); Passes rebrand release, Apr 2026; MEXC platform comparison 2026</t>
         </is>
       </c>
-      <c r="F6" s="110" t="inlineStr">
+      <c r="F6" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G6" s="109" t="inlineStr">
+      <c r="G6" s="110" t="inlineStr">
         <is>
           <t>Nothing. This is a pricing decision and the comparables are public.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="86" t="inlineStr">
+      <c r="A7" s="87" t="inlineStr">
         <is>
           <t>Sponsorship commission, Scout Pro</t>
         </is>
@@ -11844,34 +11863,34 @@
         <f>Assumptions!$C$42</f>
         <v/>
       </c>
-      <c r="C7" s="108" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D7" s="109" t="inlineStr">
+      <c r="D7" s="110" t="inlineStr">
         <is>
           <t>7% against a 10% base. A sponsor paying EUR 2,988 a year for the tooling is already paying for the relationship, and charging them the full headline rate on every deal as well is charging twice for it. Below the 10-20% an agent takes, which is the point: the sponsor who commits most pays least on each deal.</t>
         </is>
       </c>
-      <c r="E7" s="109" t="inlineStr">
+      <c r="E7" s="110" t="inlineStr">
         <is>
           <t>Priced against the agent range; the discount itself is a pricing decision</t>
         </is>
       </c>
-      <c r="F7" s="110" t="inlineStr">
+      <c r="F7" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G7" s="109" t="inlineStr">
+      <c r="G7" s="110" t="inlineStr">
         <is>
           <t>Nothing to improve. This is a decision, not a measurement.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="86" t="inlineStr">
+      <c r="A8" s="87" t="inlineStr">
         <is>
           <t>Sponsorship commission, Scout Agency</t>
         </is>
@@ -11880,34 +11899,34 @@
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
-      <c r="C8" s="108" t="inlineStr">
+      <c r="C8" s="109" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D8" s="109" t="inlineStr">
+      <c r="D8" s="110" t="inlineStr">
         <is>
           <t>5%, which is half the low end of what an agent charges and a quarter of the high end. The most committed tier pays EUR 11,988 a year, so the deal rate can fall furthest here.</t>
         </is>
       </c>
-      <c r="E8" s="109" t="inlineStr">
+      <c r="E8" s="110" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys, 10-20%</t>
         </is>
       </c>
-      <c r="F8" s="110" t="inlineStr">
+      <c r="F8" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G8" s="109" t="inlineStr">
+      <c r="G8" s="110" t="inlineStr">
         <is>
           <t>Nothing to improve. This is a decision, not a measurement.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="86" t="inlineStr">
+      <c r="A9" s="87" t="inlineStr">
         <is>
           <t>Subscriber share of deal volume</t>
         </is>
@@ -11916,34 +11935,34 @@
         <f>Assumptions!$C$44</f>
         <v/>
       </c>
-      <c r="C9" s="111" t="inlineStr">
+      <c r="C9" s="112" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D9" s="109" t="inlineStr">
+      <c r="D9" s="110" t="inlineStr">
         <is>
           <t>Subscribers are assumed to run 2.0x the deal volume of the average sponsor, which with a paid rate of 10-20% puts them at 20-40% of GMV. This is the ONLY estimate in the tiering and it is the one that sets the blended rate, which falls from 9.60% in Y1 to 8.56% by Y10. Deliberately conservative: Scout Pro buys five campaigns against the free tier's one, so 2.0x is well below what the campaign allowance alone would imply. Higher multiples lower the blend further.</t>
         </is>
       </c>
-      <c r="E9" s="109" t="inlineStr">
+      <c r="E9" s="110" t="inlineStr">
         <is>
           <t>None. No tier-level deal volume exists yet, because no tier exists yet</t>
         </is>
       </c>
-      <c r="F9" s="112" t="inlineStr">
+      <c r="F9" s="113" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G9" s="109" t="inlineStr">
+      <c r="G9" s="110" t="inlineStr">
         <is>
           <t>The first year of billing settles it exactly.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="86" t="inlineStr">
+      <c r="A10" s="87" t="inlineStr">
         <is>
           <t>Take rate on sponsorship</t>
         </is>
@@ -11952,101 +11971,101 @@
         <f>Assumptions!$C$41</f>
         <v/>
       </c>
-      <c r="C10" s="108" t="inlineStr">
+      <c r="C10" s="109" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D10" s="109" t="inlineStr">
+      <c r="D10" s="110" t="inlineStr">
         <is>
           <t>Sports agents take 10-20% of an endorsement and 4-10% of a playing contract. On OnlyFans, management agencies take a further 20-50% on top of the platform's 20%.</t>
         </is>
       </c>
-      <c r="E10" s="109" t="inlineStr">
+      <c r="E10" s="110" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys; Aruna Talent agency rate guide 2026</t>
         </is>
       </c>
-      <c r="F10" s="110" t="inlineStr">
+      <c r="F10" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G10" s="109" t="inlineStr">
+      <c r="G10" s="110" t="inlineStr">
         <is>
           <t>Observed deal data once the marketplace is running.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="86" t="inlineStr">
+      <c r="A11" s="87" t="inlineStr">
         <is>
           <t>Suggested tiers 4.99 / 9.99 / 24.99</t>
         </is>
       </c>
-      <c r="B11" s="113" t="inlineStr">
+      <c r="B11" s="114" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C11" s="108" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D11" s="109" t="inlineStr">
+      <c r="D11" s="110" t="inlineStr">
         <is>
           <t>Patreon's typical patronage is quoted at $8-12/month, so the EUR 9.99 anchor sits inside the observed band. EUR 4.99 retains only 54% of our take after payment fees, against 71% at EUR 9.99: which is why the floor matters more than the take rate.</t>
         </is>
       </c>
-      <c r="E11" s="109" t="inlineStr">
+      <c r="E11" s="110" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; independent audits of ~1,200 creators</t>
         </is>
       </c>
-      <c r="F11" s="114" t="inlineStr">
+      <c r="F11" s="115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G11" s="109" t="inlineStr">
+      <c r="G11" s="110" t="inlineStr">
         <is>
           <t>Our own tier mix after P1.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="86" t="inlineStr">
+      <c r="A12" s="87" t="inlineStr">
         <is>
           <t>Season pass / annual billing</t>
         </is>
       </c>
-      <c r="B12" s="113" t="inlineStr">
+      <c r="B12" s="114" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C12" s="115" t="inlineStr">
+      <c r="C12" s="116" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D12" s="109" t="inlineStr">
+      <c r="D12" s="110" t="inlineStr">
         <is>
           <t>Patreon reports that annual patrons churn at ONE THIRD the rate of monthly patrons. This is the single strongest piece of evidence in the plan for pushing annual billing.</t>
         </is>
       </c>
-      <c r="E12" s="109" t="inlineStr">
+      <c r="E12" s="110" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F12" s="110" t="inlineStr">
+      <c r="F12" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G12" s="109" t="inlineStr">
+      <c r="G12" s="110" t="inlineStr">
         <is>
           <t>Already strong. Confirm on our own cohorts.</t>
         </is>
@@ -12066,7 +12085,7 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="86" t="inlineStr">
+      <c r="A14" s="87" t="inlineStr">
         <is>
           <t>Fan ARPU per month</t>
         </is>
@@ -12075,34 +12094,34 @@
         <f>Assumptions!$C$12</f>
         <v/>
       </c>
-      <c r="C14" s="108" t="inlineStr">
+      <c r="C14" s="109" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D14" s="109" t="inlineStr">
+      <c r="D14" s="110" t="inlineStr">
         <is>
           <t>Patreon's average monthly support rose from $5.40 to $6.10 during 2024, with typical patronage quoted at $8-12. Our EUR 8.00-9.50 sits in the upper-middle of that range.</t>
         </is>
       </c>
-      <c r="E14" s="109" t="inlineStr">
+      <c r="E14" s="110" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F14" s="114" t="inlineStr">
+      <c r="F14" s="115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G14" s="109" t="inlineStr">
+      <c r="G14" s="110" t="inlineStr">
         <is>
           <t>Actual ARPU by tier and sport after P1.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="86" t="inlineStr">
+      <c r="A15" s="87" t="inlineStr">
         <is>
           <t>Fan churn per month</t>
         </is>
@@ -12111,34 +12130,34 @@
         <f>Assumptions!$C$13</f>
         <v/>
       </c>
-      <c r="C15" s="111" t="inlineStr">
+      <c r="C15" s="112" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D15" s="109" t="inlineStr">
+      <c r="D15" s="110" t="inlineStr">
         <is>
           <t>OPTIMISTIC AGAINST BENCHMARK. Patreon runs 10-15% monthly. We assume 6-9% (niche) and 9-13% (popular), arguing that training content is habitual and that competitive seasons create natural renewal moments. That argument is currently untested.</t>
         </is>
       </c>
-      <c r="E15" s="109" t="inlineStr">
+      <c r="E15" s="110" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (10-15%/month)</t>
         </is>
       </c>
-      <c r="F15" s="112" t="inlineStr">
+      <c r="F15" s="113" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G15" s="109" t="inlineStr">
+      <c r="G15" s="110" t="inlineStr">
         <is>
           <t>THE most important number to measure in P1. Three months of real cohorts settles it. Until then the conservative case should be treated as the plan.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="86" t="inlineStr">
+      <c r="A16" s="87" t="inlineStr">
         <is>
           <t>Paying fans per monetising athlete</t>
         </is>
@@ -12147,34 +12166,34 @@
         <f>Assumptions!$C$11</f>
         <v/>
       </c>
-      <c r="C16" s="116" t="inlineStr">
+      <c r="C16" s="117" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D16" s="109" t="inlineStr">
+      <c r="D16" s="110" t="inlineStr">
         <is>
           <t>20 rising to 48 over ten years. Cross-check: Patreon creators average $350/month and our modelled niche athlete at maturity earns about EUR 313/month, closely aligned, which is reassuring for an assumption built bottom-up rather than from a comparable.</t>
         </is>
       </c>
-      <c r="E16" s="109" t="inlineStr">
+      <c r="E16" s="110" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (creator average $350/month)</t>
         </is>
       </c>
-      <c r="F16" s="114" t="inlineStr">
+      <c r="F16" s="115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G16" s="109" t="inlineStr">
+      <c r="G16" s="110" t="inlineStr">
         <is>
           <t>Observed fans per athlete, banded by follower count.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="86" t="inlineStr">
+      <c r="A17" s="87" t="inlineStr">
         <is>
           <t>Share of athletes who monetise</t>
         </is>
@@ -12183,64 +12202,64 @@
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="C17" s="111" t="inlineStr">
+      <c r="C17" s="112" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D17" s="109" t="inlineStr">
+      <c r="D17" s="110" t="inlineStr">
         <is>
           <t>28% rising to 50% for niche sports. No direct comparable exists: neither Patreon nor OnlyFans publishes activation rates for creators who sign up but never charge.</t>
         </is>
       </c>
-      <c r="E17" s="109" t="inlineStr">
+      <c r="E17" s="110" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F17" s="112" t="inlineStr">
+      <c r="F17" s="113" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G17" s="109" t="inlineStr">
+      <c r="G17" s="110" t="inlineStr">
         <is>
           <t>Our own activation funnel, available from P1 onward.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="86" t="inlineStr">
+      <c r="A18" s="87" t="inlineStr">
         <is>
           <t>Fan acquisition capacity</t>
         </is>
       </c>
-      <c r="B18" s="113" t="inlineStr">
+      <c r="B18" s="114" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C18" s="111" t="inlineStr">
+      <c r="C18" s="112" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D18" s="109" t="inlineStr">
+      <c r="D18" s="110" t="inlineStr">
         <is>
           <t>An athlete can recruit 30-69 new paying fans a year depending on segment. This ceiling is what makes churn bite in the model: without it, higher churn perversely RAISED revenue, because the year-end target was reachable at any churn rate.</t>
         </is>
       </c>
-      <c r="E18" s="109" t="inlineStr">
+      <c r="E18" s="110" t="inlineStr">
         <is>
           <t>None: introduced to fix a modelling flaw found by stress testing</t>
         </is>
       </c>
-      <c r="F18" s="112" t="inlineStr">
+      <c r="F18" s="113" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G18" s="109" t="inlineStr">
+      <c r="G18" s="110" t="inlineStr">
         <is>
           <t>Observed gross adds per athlete per year.</t>
         </is>
@@ -12260,7 +12279,7 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="86" t="inlineStr">
+      <c r="A20" s="87" t="inlineStr">
         <is>
           <t>PSP percentage fee</t>
         </is>
@@ -12269,34 +12288,34 @@
         <f>Assumptions!$C$50</f>
         <v/>
       </c>
-      <c r="C20" s="115" t="inlineStr">
+      <c r="C20" s="116" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D20" s="109" t="inlineStr">
+      <c r="D20" s="110" t="inlineStr">
         <is>
           <t>Stripe for a Spanish entity: 1.5% + EUR 0.25 on EEA domestic cards, 2.5% on UK cards, 3.25% on non-EEA. 1.9% is the blend for a mostly-European fan base. CORRECTION: an earlier version of this model used the US headline of 2.9% and overstated the largest cost line in the business by about a third.</t>
         </is>
       </c>
-      <c r="E20" s="109" t="inlineStr">
+      <c r="E20" s="110" t="inlineStr">
         <is>
           <t>Stripe published EU/EEA pricing, 2026</t>
         </is>
       </c>
-      <c r="F20" s="110" t="inlineStr">
+      <c r="F20" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G20" s="109" t="inlineStr">
+      <c r="G20" s="110" t="inlineStr">
         <is>
           <t>Interchange-plus terms become negotiable above roughly EUR 5M processed.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="86" t="inlineStr">
+      <c r="A21" s="87" t="inlineStr">
         <is>
           <t>PSP fixed fee per transaction</t>
         </is>
@@ -12305,34 +12324,34 @@
         <f>Assumptions!$C$51</f>
         <v/>
       </c>
-      <c r="C21" s="115" t="inlineStr">
+      <c r="C21" s="116" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D21" s="109" t="inlineStr">
+      <c r="D21" s="110" t="inlineStr">
         <is>
           <t>EUR 0.25 per transaction. On a EUR 4.99 tier that single fee is a third of our take, which is why the tier floor and annual billing move more margin than the take rate does.</t>
         </is>
       </c>
-      <c r="E21" s="109" t="inlineStr">
+      <c r="E21" s="110" t="inlineStr">
         <is>
           <t>Stripe published pricing, 2026</t>
         </is>
       </c>
-      <c r="F21" s="110" t="inlineStr">
+      <c r="F21" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G21" s="109" t="inlineStr">
+      <c r="G21" s="110" t="inlineStr">
         <is>
           <t>Volume renegotiation; annual billing turns twelve fees into one.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="86" t="inlineStr">
+      <c r="A22" s="87" t="inlineStr">
         <is>
           <t>Payout fees</t>
         </is>
@@ -12341,27 +12360,27 @@
         <f>Assumptions!$C$52</f>
         <v/>
       </c>
-      <c r="C22" s="115" t="inlineStr">
+      <c r="C22" s="116" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D22" s="109" t="inlineStr">
+      <c r="D22" s="110" t="inlineStr">
         <is>
           <t>Stripe Connect Express: roughly 0.25% + EUR 0.25 per payout, plus a monthly active-account fee that is not modelled as a separate line.</t>
         </is>
       </c>
-      <c r="E22" s="109" t="inlineStr">
+      <c r="E22" s="110" t="inlineStr">
         <is>
           <t>Stripe Connect pricing, 2026</t>
         </is>
       </c>
-      <c r="F22" s="114" t="inlineStr">
+      <c r="F22" s="115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G22" s="109" t="inlineStr">
+      <c r="G22" s="110" t="inlineStr">
         <is>
           <t>Actual payout frequency once athletes are onboarded.</t>
         </is>
@@ -12381,118 +12400,118 @@
       <c r="G23" s="14" t="n"/>
     </row>
     <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="86" t="inlineStr">
+      <c r="A24" s="87" t="inlineStr">
         <is>
           <t>Sport participation by country</t>
         </is>
       </c>
-      <c r="B24" s="113" t="inlineStr">
+      <c r="B24" s="114" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C24" s="111" t="inlineStr">
+      <c r="C24" s="112" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D24" s="109" t="inlineStr">
+      <c r="D24" s="110" t="inlineStr">
         <is>
           <t>Eurobarometer 525, share who NEVER exercise: Finland 8%, Sweden 12%, Denmark 20%, Poland 65%, Greece 68%, Portugal 73%, EU-27 average 45%. Six of the 34 countries in the index are measured; the other 28 are estimates placed inside that distribution.</t>
         </is>
       </c>
-      <c r="E24" s="109" t="inlineStr">
+      <c r="E24" s="110" t="inlineStr">
         <is>
           <t>Special Eurobarometer 525, Sport and Physical Activity, September 2022</t>
         </is>
       </c>
-      <c r="F24" s="114" t="inlineStr">
+      <c r="F24" s="115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G24" s="109" t="inlineStr">
+      <c r="G24" s="110" t="inlineStr">
         <is>
           <t>Federation licence counts, published annually and free (CSD in Spain).</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="86" t="inlineStr">
+      <c r="A25" s="87" t="inlineStr">
         <is>
           <t>Padel market size</t>
         </is>
       </c>
-      <c r="B25" s="113" t="inlineStr">
+      <c r="B25" s="114" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C25" s="115" t="inlineStr">
+      <c r="C25" s="116" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D25" s="109" t="inlineStr">
+      <c r="D25" s="110" t="inlineStr">
         <is>
           <t>Spain has ~6.0M active players (12.7% of the population), 109,040 federation licences and 17,300+ courts; globally 35M+ players and 77,000+ courts. This is the clearest case for weighting a sport regionally rather than globally, padel scores 77.7 in Spain and 45.1 worldwide.</t>
         </is>
       </c>
-      <c r="E25" s="109" t="inlineStr">
+      <c r="E25" s="110" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="F25" s="110" t="inlineStr">
+      <c r="F25" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G25" s="109" t="inlineStr">
+      <c r="G25" s="110" t="inlineStr">
         <is>
           <t>Annual FIP refresh.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="86" t="inlineStr">
+      <c r="A26" s="87" t="inlineStr">
         <is>
           <t>Sports fandom by country</t>
         </is>
       </c>
-      <c r="B26" s="113" t="inlineStr">
+      <c r="B26" s="114" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C26" s="111" t="inlineStr">
+      <c r="C26" s="112" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D26" s="109" t="inlineStr">
+      <c r="D26" s="110" t="inlineStr">
         <is>
           <t>The weakest layer of the sport index, and it drives both the `demand` and `appetite` signals. Commercial audience panels (Nielsen Sports, YouGov) cost more than the entire Y1-Y2 analytics budget.</t>
         </is>
       </c>
-      <c r="E26" s="109" t="inlineStr">
+      <c r="E26" s="110" t="inlineStr">
         <is>
           <t>None: reasoned estimates only</t>
         </is>
       </c>
-      <c r="F26" s="112" t="inlineStr">
+      <c r="F26" s="113" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G26" s="109" t="inlineStr">
+      <c r="G26" s="110" t="inlineStr">
         <is>
           <t>Our own engagement data per sport per country once connectors are live. This is what makes the index self-improving rather than something anyone could copy.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="86" t="inlineStr">
+      <c r="A27" s="87" t="inlineStr">
         <is>
           <t>Athlete count trajectory</t>
         </is>
@@ -12501,27 +12520,27 @@
         <f>Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="C27" s="111" t="inlineStr">
+      <c r="C27" s="112" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D27" s="109" t="inlineStr">
+      <c r="D27" s="110" t="inlineStr">
         <is>
           <t>250 rising to 8,500 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
         </is>
       </c>
-      <c r="E27" s="109" t="inlineStr">
+      <c r="E27" s="110" t="inlineStr">
         <is>
           <t>None: it is a target</t>
         </is>
       </c>
-      <c r="F27" s="112" t="inlineStr">
+      <c r="F27" s="113" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G27" s="109" t="inlineStr">
+      <c r="G27" s="110" t="inlineStr">
         <is>
           <t>The pre-seed gate tests it directly: 250 athletes and the first paying sponsors.</t>
         </is>
@@ -12541,7 +12560,7 @@
       <c r="G28" s="14" t="n"/>
     </row>
     <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="86" t="inlineStr">
+      <c r="A29" s="87" t="inlineStr">
         <is>
           <t>Athlete CAC</t>
         </is>
@@ -12550,34 +12569,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C29" s="111" t="inlineStr">
+      <c r="C29" s="112" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D29" s="109" t="inlineStr">
+      <c r="D29" s="110" t="inlineStr">
         <is>
           <t>EUR 16-36 for niche, EUR 40-88 for popular. The gap reflects displacing an existing agent relationship versus reaching someone with no representation at all. No published comparable exists for athlete acquisition in this segment.</t>
         </is>
       </c>
-      <c r="E29" s="109" t="inlineStr">
+      <c r="E29" s="110" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F29" s="112" t="inlineStr">
+      <c r="F29" s="113" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G29" s="109" t="inlineStr">
+      <c r="G29" s="110" t="inlineStr">
         <is>
           <t>Measured CAC by channel from the first federation partnership.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="86" t="inlineStr">
+      <c r="A30" s="87" t="inlineStr">
         <is>
           <t>Admission rate, direct applicants</t>
         </is>
@@ -12586,34 +12605,34 @@
         <f>Assumptions!$C$98</f>
         <v/>
       </c>
-      <c r="C30" s="116" t="inlineStr">
+      <c r="C30" s="117" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D30" s="109" t="inlineStr">
+      <c r="D30" s="110" t="inlineStr">
         <is>
           <t>20% of direct applicants are admitted, 25% go to a human, 40% are refused and 15% never finish the form. Not a judgement: it is the ops-load output of scripts/admission_stress.py run over the admission policy itself, so retuning a threshold moves this figure. The sweep asserts the model and the policy stay in step and fails if they drift.</t>
         </is>
       </c>
-      <c r="E30" s="109" t="inlineStr">
+      <c r="E30" s="110" t="inlineStr">
         <is>
           <t>scripts/admission_stress.py, section 7, over a modelled applicant mix</t>
         </is>
       </c>
-      <c r="F30" s="114" t="inlineStr">
+      <c r="F30" s="115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G30" s="109" t="inlineStr">
+      <c r="G30" s="110" t="inlineStr">
         <is>
           <t>Real intake data. The mix the sweep assumes is the soft part, not the arithmetic.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="86" t="inlineStr">
+      <c r="A31" s="87" t="inlineStr">
         <is>
           <t>Admission rate, club-nominated</t>
         </is>
@@ -12622,34 +12641,34 @@
         <f>Assumptions!$C$100</f>
         <v/>
       </c>
-      <c r="C31" s="111" t="inlineStr">
+      <c r="C31" s="112" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D31" s="109" t="inlineStr">
+      <c r="D31" s="110" t="inlineStr">
         <is>
           <t>45% admitted against 20% direct. A verified club's nomination confers a credibility floor of 0.75 x its own legitimacy score, which carries a completed application over the admit line that would otherwise have gone to review. It cannot carry an empty one: no club can supply someone else's date of birth, so the uplift is real but bounded.</t>
         </is>
       </c>
-      <c r="E31" s="109" t="inlineStr">
+      <c r="E31" s="110" t="inlineStr">
         <is>
           <t>None: the mechanism is built and tested, the conversion is not yet measured</t>
         </is>
       </c>
-      <c r="F31" s="112" t="inlineStr">
+      <c r="F31" s="113" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G31" s="109" t="inlineStr">
+      <c r="G31" s="110" t="inlineStr">
         <is>
           <t>The first federation partnership: nominated applicants are tagged, so this is measurable from day one of it.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="86" t="inlineStr">
+      <c r="A32" s="87" t="inlineStr">
         <is>
           <t>Athlete verification cost</t>
         </is>
@@ -12658,34 +12677,34 @@
         <f>Assumptions!$C$103</f>
         <v/>
       </c>
-      <c r="C32" s="116" t="inlineStr">
+      <c r="C32" s="117" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D32" s="109" t="inlineStr">
+      <c r="D32" s="110" t="inlineStr">
         <is>
           <t>Four minutes per manual review, priced at the same loaded salary the People line uses, over 1,700 productive hours. Peaks at EUR 47k and 0.64 reviewer-FTE in Y10, which is the finding rather than the cost: verification is not a money problem at this scale. The reason to automate it is latency: an athlete sitting in the queue is not listed, not matchable and not earning.</t>
         </is>
       </c>
-      <c r="E32" s="109" t="inlineStr">
+      <c r="E32" s="110" t="inlineStr">
         <is>
           <t>Derived from the sweep's review volume and the model's own salary line</t>
         </is>
       </c>
-      <c r="F32" s="114" t="inlineStr">
+      <c r="F32" s="115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G32" s="109" t="inlineStr">
+      <c r="G32" s="110" t="inlineStr">
         <is>
           <t>Timing real reviews. Four minutes is an estimate of a mechanical task.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="86" t="inlineStr">
+      <c r="A33" s="87" t="inlineStr">
         <is>
           <t>Athlete CAC vs the funnel</t>
         </is>
@@ -12694,34 +12713,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C33" s="111" t="inlineStr">
+      <c r="C33" s="112" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D33" s="109" t="inlineStr">
+      <c r="D33" s="110" t="inlineStr">
         <is>
           <t>Deliberately NOT multiplied by the admission funnel. Segment CAC is defined as the cost of landing one athlete ON the platform, so scaling it by 1/admission-rate would charge the same money twice. The Costs sheet carries a memo line showing what that CAC works out to per application (EUR 3.40 in Y1 rising to EUR 22), the figure to hold against what a channel actually charges per name reached.</t>
         </is>
       </c>
-      <c r="E33" s="109" t="inlineStr">
+      <c r="E33" s="110" t="inlineStr">
         <is>
           <t>None: this is a definitional choice, made explicit so it is not silently reversed</t>
         </is>
       </c>
-      <c r="F33" s="112" t="inlineStr">
+      <c r="F33" s="113" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G33" s="109" t="inlineStr">
+      <c r="G33" s="110" t="inlineStr">
         <is>
           <t>Channel-level spend against applications, which the funnel now records.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="86" t="inlineStr">
+      <c r="A34" s="87" t="inlineStr">
         <is>
           <t>Loaded salary, Spain</t>
         </is>
@@ -12730,34 +12749,34 @@
         <f>Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="C34" s="108" t="inlineStr">
+      <c r="C34" s="109" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D34" s="109" t="inlineStr">
+      <c r="D34" s="110" t="inlineStr">
         <is>
           <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k, around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
         </is>
       </c>
-      <c r="E34" s="109" t="inlineStr">
+      <c r="E34" s="110" t="inlineStr">
         <is>
           <t>Spanish Seguridad Social employer contribution rates</t>
         </is>
       </c>
-      <c r="F34" s="114" t="inlineStr">
+      <c r="F34" s="115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G34" s="109" t="inlineStr">
+      <c r="G34" s="110" t="inlineStr">
         <is>
           <t>Actual offers accepted.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="86" t="inlineStr">
+      <c r="A35" s="87" t="inlineStr">
         <is>
           <t>AWS infrastructure</t>
         </is>
@@ -12766,34 +12785,34 @@
         <f>Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="C35" s="108" t="inlineStr">
+      <c r="C35" s="109" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D35" s="109" t="inlineStr">
+      <c r="D35" s="110" t="inlineStr">
         <is>
           <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
         </is>
       </c>
-      <c r="E35" s="109" t="inlineStr">
+      <c r="E35" s="110" t="inlineStr">
         <is>
           <t>AWS published list pricing, 2026</t>
         </is>
       </c>
-      <c r="F35" s="114" t="inlineStr">
+      <c r="F35" s="115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G35" s="109" t="inlineStr">
+      <c r="G35" s="110" t="inlineStr">
         <is>
           <t>Actual bills; commit to Savings Plans once usage is stable.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="86" t="inlineStr">
+      <c r="A36" s="87" t="inlineStr">
         <is>
           <t>Media egress</t>
         </is>
@@ -12802,34 +12821,34 @@
         <f>Assumptions!$C$60</f>
         <v/>
       </c>
-      <c r="C36" s="115" t="inlineStr">
+      <c r="C36" s="116" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D36" s="109" t="inlineStr">
+      <c r="D36" s="110" t="inlineStr">
         <is>
           <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year, the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
         </is>
       </c>
-      <c r="E36" s="109" t="inlineStr">
+      <c r="E36" s="110" t="inlineStr">
         <is>
           <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
         </is>
       </c>
-      <c r="F36" s="110" t="inlineStr">
+      <c r="F36" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G36" s="109" t="inlineStr">
+      <c r="G36" s="110" t="inlineStr">
         <is>
           <t>Nothing. Both are published.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="86" t="inlineStr">
+      <c r="A37" s="87" t="inlineStr">
         <is>
           <t>Moderation cost</t>
         </is>
@@ -12838,27 +12857,27 @@
         <f>Assumptions!$C$62</f>
         <v/>
       </c>
-      <c r="C37" s="111" t="inlineStr">
+      <c r="C37" s="112" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D37" s="109" t="inlineStr">
+      <c r="D37" s="110" t="inlineStr">
         <is>
           <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
         </is>
       </c>
-      <c r="E37" s="109" t="inlineStr">
+      <c r="E37" s="110" t="inlineStr">
         <is>
           <t>None cited</t>
         </is>
       </c>
-      <c r="F37" s="112" t="inlineStr">
+      <c r="F37" s="113" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G37" s="109" t="inlineStr">
+      <c r="G37" s="110" t="inlineStr">
         <is>
           <t>Vendor quotes once P2 scope is fixed.</t>
         </is>
@@ -12878,7 +12897,7 @@
       <c r="G38" s="14" t="n"/>
     </row>
     <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="86" t="inlineStr">
+      <c r="A39" s="87" t="inlineStr">
         <is>
           <t>Corporate tax rates</t>
         </is>
@@ -12887,34 +12906,34 @@
         <f>Assumptions!$C$93</f>
         <v/>
       </c>
-      <c r="C39" s="115" t="inlineStr">
+      <c r="C39" s="116" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D39" s="109" t="inlineStr">
+      <c r="D39" s="110" t="inlineStr">
         <is>
           <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
         </is>
       </c>
-      <c r="E39" s="109" t="inlineStr">
+      <c r="E39" s="110" t="inlineStr">
         <is>
           <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
         </is>
       </c>
-      <c r="F39" s="110" t="inlineStr">
+      <c r="F39" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G39" s="109" t="inlineStr">
+      <c r="G39" s="110" t="inlineStr">
         <is>
           <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="86" t="inlineStr">
+      <c r="A40" s="87" t="inlineStr">
         <is>
           <t>Risk-free rate</t>
         </is>
@@ -12923,71 +12942,71 @@
         <f>Assumptions!$C$113</f>
         <v/>
       </c>
-      <c r="C40" s="115" t="inlineStr">
+      <c r="C40" s="116" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D40" s="109" t="inlineStr">
+      <c r="D40" s="110" t="inlineStr">
         <is>
           <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
         </is>
       </c>
-      <c r="E40" s="109" t="inlineStr">
+      <c r="E40" s="110" t="inlineStr">
         <is>
           <t>Spanish 10Y government bond yield</t>
         </is>
       </c>
-      <c r="F40" s="110" t="inlineStr">
+      <c r="F40" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G40" s="109" t="inlineStr">
+      <c r="G40" s="110" t="inlineStr">
         <is>
           <t>Refresh at the date of any raise.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="86" t="inlineStr">
+      <c r="A41" s="87" t="inlineStr">
         <is>
           <t>WACC / discount rate</t>
         </is>
       </c>
-      <c r="B41" s="113" t="inlineStr">
+      <c r="B41" s="114" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C41" s="108" t="inlineStr">
+      <c r="C41" s="109" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D41" s="109" t="inlineStr">
+      <c r="D41" s="110" t="inlineStr">
         <is>
           <t>25%, against a published mature-company anchor of 6.01%. Damodaran's European cost of capital dataset puts Software (Internet) at 6.01% in euros across 23 listed firms, and the European market ex-financials at 6.59%. Those are costs of capital for mature listed companies; this is a pre-revenue venture, and the 19-point gap is the stage premium. It is stated rather than buried because it is the largest single judgement in the valuation. Damodaran publishes no dataset for venture-stage rates, so the premium itself is convention (20-35% is the usual range) and not a sourced figure. The sensitivity grid runs 20-30% because this is arguable rather than knowable.</t>
         </is>
       </c>
-      <c r="E41" s="109" t="inlineStr">
+      <c r="E41" s="110" t="inlineStr">
         <is>
           <t>Aswath Damodaran, NYU Stern, Cost of Capital by Industry (Europe), updated 5 January 2026</t>
         </is>
       </c>
-      <c r="F41" s="114" t="inlineStr">
+      <c r="F41" s="115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G41" s="109" t="inlineStr">
+      <c r="G41" s="110" t="inlineStr">
         <is>
           <t>An actual term sheet prices this for you.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="86" t="inlineStr">
+      <c r="A42" s="87" t="inlineStr">
         <is>
           <t>Exit revenue multiple</t>
         </is>
@@ -12996,34 +13015,34 @@
         <f>Assumptions!$C$112</f>
         <v/>
       </c>
-      <c r="C42" s="108" t="inlineStr">
+      <c r="C42" s="109" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D42" s="109" t="inlineStr">
+      <c r="D42" s="110" t="inlineStr">
         <is>
           <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
         </is>
       </c>
-      <c r="E42" s="109" t="inlineStr">
+      <c r="E42" s="110" t="inlineStr">
         <is>
           <t>Public marketplace and SaaS trading multiples</t>
         </is>
       </c>
-      <c r="F42" s="114" t="inlineStr">
+      <c r="F42" s="115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G42" s="109" t="inlineStr">
+      <c r="G42" s="110" t="inlineStr">
         <is>
           <t>Comparable private transactions nearer an exit.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="86" t="inlineStr">
+      <c r="A43" s="87" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
@@ -13032,27 +13051,27 @@
         <f>Assumptions!$C$111</f>
         <v/>
       </c>
-      <c r="C43" s="108" t="inlineStr">
+      <c r="C43" s="109" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D43" s="109" t="inlineStr">
+      <c r="D43" s="110" t="inlineStr">
         <is>
           <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
         </is>
       </c>
-      <c r="E43" s="109" t="inlineStr">
+      <c r="E43" s="110" t="inlineStr">
         <is>
           <t>Standard DCF convention</t>
         </is>
       </c>
-      <c r="F43" s="114" t="inlineStr">
+      <c r="F43" s="115" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G43" s="109" t="inlineStr">
+      <c r="G43" s="110" t="inlineStr">
         <is>
           <t>Nothing: it is a convention, and the grid shows its effect.</t>
         </is>
@@ -13072,112 +13091,112 @@
       <c r="G44" s="14" t="n"/>
     </row>
     <row r="45" ht="58" customHeight="1">
-      <c r="A45" s="86" t="inlineStr">
+      <c r="A45" s="87" t="inlineStr">
         <is>
           <t>Payout age floor</t>
         </is>
       </c>
-      <c r="B45" s="113" t="inlineStr">
+      <c r="B45" s="114" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C45" s="115" t="inlineStr">
+      <c r="C45" s="116" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D45" s="109" t="inlineStr">
+      <c r="D45" s="110" t="inlineStr">
         <is>
           <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
         </is>
       </c>
-      <c r="E45" s="109" t="inlineStr">
+      <c r="E45" s="110" t="inlineStr">
         <is>
           <t>Stripe Connect documentation</t>
         </is>
       </c>
-      <c r="F45" s="110" t="inlineStr">
+      <c r="F45" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G45" s="109" t="inlineStr">
+      <c r="G45" s="110" t="inlineStr">
         <is>
           <t>Nothing: it is a hard platform rule.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
-      <c r="A46" s="86" t="inlineStr">
+      <c r="A46" s="87" t="inlineStr">
         <is>
           <t>Digital consent age, Spain</t>
         </is>
       </c>
-      <c r="B46" s="113" t="inlineStr">
+      <c r="B46" s="114" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C46" s="115" t="inlineStr">
+      <c r="C46" s="116" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D46" s="109" t="inlineStr">
+      <c r="D46" s="110" t="inlineStr">
         <is>
           <t>14 today under LOPDGDD Art. 7. A draft Organic Law on the Protection of Minors in Digital Environments would raise it to 16 and make age verification mandatory, which is why 16 is the forward-compatible floor for an account.</t>
         </is>
       </c>
-      <c r="E46" s="109" t="inlineStr">
+      <c r="E46" s="110" t="inlineStr">
         <is>
           <t>LOPDGDD Art. 7; draft Organic Law, Council of Ministers, March 2025</t>
         </is>
       </c>
-      <c r="F46" s="110" t="inlineStr">
+      <c r="F46" s="111" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G46" s="109" t="inlineStr">
+      <c r="G46" s="110" t="inlineStr">
         <is>
           <t>Track the bill through Parliament.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="117" t="inlineStr">
+      <c r="A48" s="118" t="inlineStr">
         <is>
           <t>THE THREE ASSUMPTIONS MOST LIKELY TO BE WRONG</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="118" t="inlineStr">
+      <c r="A49" s="119" t="inlineStr">
         <is>
           <t>1. Fan churn. We assume 6-13%/month; Patreon reports 10-15%. If Patreon is right, Y10 revenue falls from about EUR 58M to EUR 51M and the capital requirement roughly doubles.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="118" t="inlineStr">
+      <c r="A50" s="119" t="inlineStr">
         <is>
           <t>2. Athlete count. The trajectory is a target, not a forecast, and everything scales off it.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="118" t="inlineStr">
+      <c r="A51" s="119" t="inlineStr">
         <is>
           <t>3. Share of athletes who monetise. No published comparable exists at all.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="119" t="inlineStr"/>
+      <c r="A52" s="120" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="119" t="inlineStr">
+      <c r="A53" s="120" t="inlineStr">
         <is>
           <t>All three are answered by the same thing: three months of real cohort data from P1.</t>
         </is>
@@ -15789,7 +15808,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E66" s="23" t="n">
         <v>1.5</v>

--- a/business-plan/Stride_Financial_Model.xlsx
+++ b/business-plan/Stride_Financial_Model.xlsx
@@ -21,10 +21,9 @@
     <sheet name="HiringPlan" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="CAC_CLV" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="KPIs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Check" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Comparables" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="MarketModel" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Research" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Comparables" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="MarketModel" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Research" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -362,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -432,18 +431,14 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="15" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="11" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="16" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="16" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="16" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="15" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="17" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -883,7 +878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -979,7 +974,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A check that must read zero</t>
+          <t>The balance-sheet check, which must read zero</t>
         </is>
       </c>
     </row>
@@ -1184,60 +1179,41 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>CONTROL</t>
+          <t>APPENDIX: RESEARCH AND MODELLING</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Comparables</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Internal quality checks. Every variance row must read zero</t>
+          <t>Published facts about Patreon, Passes and agents. The benchmarking source</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>MarketModel</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Modelled assumptions, per market dynamics</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>APPENDIX: RESEARCH AND MODELLING</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>Comparables</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Published facts about Patreon, Passes and agents. The benchmarking source</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>MarketModel</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Modelled assumptions, per market dynamics</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Where each baseline assumption came from, and how confident it is</t>
         </is>
@@ -1259,9 +1235,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2426,7 +2401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2876,196 +2851,194 @@
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Model headcount</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-      <c r="C13" s="33">
-        <f>Assumptions!C66</f>
-        <v/>
-      </c>
-      <c r="D13" s="33">
-        <f>Assumptions!D66</f>
-        <v/>
-      </c>
-      <c r="E13" s="33">
-        <f>Assumptions!E66</f>
-        <v/>
-      </c>
-      <c r="F13" s="33">
-        <f>Assumptions!F66</f>
-        <v/>
-      </c>
-      <c r="G13" s="33">
-        <f>Assumptions!G66</f>
-        <v/>
-      </c>
-      <c r="H13" s="33">
-        <f>Assumptions!H66</f>
-        <v/>
-      </c>
-      <c r="I13" s="33">
-        <f>Assumptions!I66</f>
-        <v/>
-      </c>
-      <c r="J13" s="33">
-        <f>Assumptions!J66</f>
-        <v/>
-      </c>
-      <c r="K13" s="33">
-        <f>Assumptions!K66</f>
-        <v/>
-      </c>
-      <c r="L13" s="33">
-        <f>Assumptions!L66</f>
-        <v/>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="42" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B14" s="43" t="inlineStr">
-        <is>
-          <t>sheet arithmetic, must be zero</t>
-        </is>
-      </c>
-      <c r="C14" s="65">
-        <f>ROUND(C12-C13,3)</f>
-        <v/>
-      </c>
-      <c r="D14" s="65">
-        <f>ROUND(D12-D13,3)</f>
-        <v/>
-      </c>
-      <c r="E14" s="65">
-        <f>ROUND(E12-E13,3)</f>
-        <v/>
-      </c>
-      <c r="F14" s="65">
-        <f>ROUND(F12-F13,3)</f>
-        <v/>
-      </c>
-      <c r="G14" s="65">
-        <f>ROUND(G12-G13,3)</f>
-        <v/>
-      </c>
-      <c r="H14" s="65">
-        <f>ROUND(H12-H13,3)</f>
-        <v/>
-      </c>
-      <c r="I14" s="65">
-        <f>ROUND(I12-I13,3)</f>
-        <v/>
-      </c>
-      <c r="J14" s="65">
-        <f>ROUND(J12-J13,3)</f>
-        <v/>
-      </c>
-      <c r="K14" s="65">
-        <f>ROUND(K12-K13,3)</f>
-        <v/>
-      </c>
-      <c r="L14" s="65">
-        <f>ROUND(L12-L13,3)</f>
-        <v/>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>COST: ROLE BUILD-UP AGAINST THE MODEL</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="14" t="n"/>
+      <c r="J14" s="14" t="n"/>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Employer social security</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>on gross</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D15" s="40" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E15" s="40" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F15" s="40" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G15" s="40" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H15" s="40" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I15" s="40" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J15" s="40" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K15" s="40" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L15" s="40" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>COST: ROLE BUILD-UP AGAINST THE MODEL</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="14" t="n"/>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>GROSS SALARY BY ROLE</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>EUR, before employer SS</t>
+        </is>
+      </c>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
+      <c r="E16" s="53" t="n"/>
+      <c r="F16" s="53" t="n"/>
+      <c r="G16" s="53" t="n"/>
+      <c r="H16" s="53" t="n"/>
+      <c r="I16" s="53" t="n"/>
+      <c r="J16" s="53" t="n"/>
+      <c r="K16" s="53" t="n"/>
+      <c r="L16" s="53" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Employer social security</t>
+          <t xml:space="preserve">  Founder / CEO</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>on gross</t>
-        </is>
-      </c>
-      <c r="C17" s="40" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="D17" s="40" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E17" s="40" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="F17" s="40" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G17" s="40" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H17" s="40" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I17" s="40" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="J17" s="40" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K17" s="40" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="L17" s="40" t="n">
-        <v>0.32</v>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D17" s="28">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="28">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="F17" s="28">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="G17" s="28">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="H17" s="28">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="I17" s="28">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="J17" s="28">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="K17" s="28">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="L17" s="28">
+        <f>C17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>GROSS SALARY BY ROLE</t>
+          <t xml:space="preserve">  Engineering</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>EUR, before employer SS</t>
-        </is>
-      </c>
-      <c r="C18" s="53" t="n"/>
-      <c r="D18" s="53" t="n"/>
-      <c r="E18" s="53" t="n"/>
-      <c r="F18" s="53" t="n"/>
-      <c r="G18" s="53" t="n"/>
-      <c r="H18" s="53" t="n"/>
-      <c r="I18" s="53" t="n"/>
-      <c r="J18" s="53" t="n"/>
-      <c r="K18" s="53" t="n"/>
-      <c r="L18" s="53" t="n"/>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>55000</v>
+      </c>
+      <c r="D18" s="28">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="28">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="F18" s="28">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="G18" s="28">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="H18" s="28">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="I18" s="28">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="J18" s="28">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="K18" s="28">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="L18" s="28">
+        <f>C18</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Founder / CEO</t>
+          <t xml:space="preserve">  BD / partnerships</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
@@ -3074,7 +3047,7 @@
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>45000</v>
+        <v>38000</v>
       </c>
       <c r="D19" s="28">
         <f>C19</f>
@@ -3116,7 +3089,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Engineering</t>
+          <t xml:space="preserve">  Athlete success</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
@@ -3125,7 +3098,7 @@
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>55000</v>
+        <v>30000</v>
       </c>
       <c r="D20" s="28">
         <f>C20</f>
@@ -3167,7 +3140,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BD / partnerships</t>
+          <t xml:space="preserve">  Trust &amp; safety / review</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
@@ -3176,7 +3149,7 @@
         </is>
       </c>
       <c r="C21" s="36" t="n">
-        <v>38000</v>
+        <v>34000</v>
       </c>
       <c r="D21" s="28">
         <f>C21</f>
@@ -3218,7 +3191,7 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Athlete success</t>
+          <t xml:space="preserve">  Finance / operations</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
@@ -3227,7 +3200,7 @@
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>30000</v>
+        <v>42000</v>
       </c>
       <c r="D22" s="28">
         <f>C22</f>
@@ -3269,7 +3242,7 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Trust &amp; safety / review</t>
+          <t xml:space="preserve">  Data protection officer</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
@@ -3278,7 +3251,7 @@
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>34000</v>
+        <v>60000</v>
       </c>
       <c r="D23" s="28">
         <f>C23</f>
@@ -3317,61 +3290,10 @@
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Finance / operations</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C24" s="36" t="n">
-        <v>42000</v>
-      </c>
-      <c r="D24" s="28">
-        <f>C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="28">
-        <f>C24</f>
-        <v/>
-      </c>
-      <c r="F24" s="28">
-        <f>C24</f>
-        <v/>
-      </c>
-      <c r="G24" s="28">
-        <f>C24</f>
-        <v/>
-      </c>
-      <c r="H24" s="28">
-        <f>C24</f>
-        <v/>
-      </c>
-      <c r="I24" s="28">
-        <f>C24</f>
-        <v/>
-      </c>
-      <c r="J24" s="28">
-        <f>C24</f>
-        <v/>
-      </c>
-      <c r="K24" s="28">
-        <f>C24</f>
-        <v/>
-      </c>
-      <c r="L24" s="28">
-        <f>C24</f>
-        <v/>
-      </c>
-    </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Data protection officer</t>
+          <t>Founder / CEO: loaded</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
@@ -3379,50 +3301,103 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C25" s="36" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D25" s="28">
-        <f>C25</f>
-        <v/>
-      </c>
-      <c r="E25" s="28">
-        <f>C25</f>
-        <v/>
-      </c>
-      <c r="F25" s="28">
-        <f>C25</f>
-        <v/>
-      </c>
-      <c r="G25" s="28">
-        <f>C25</f>
-        <v/>
-      </c>
-      <c r="H25" s="28">
-        <f>C25</f>
-        <v/>
-      </c>
-      <c r="I25" s="28">
-        <f>C25</f>
-        <v/>
-      </c>
-      <c r="J25" s="28">
-        <f>C25</f>
-        <v/>
-      </c>
-      <c r="K25" s="28">
-        <f>C25</f>
-        <v/>
-      </c>
-      <c r="L25" s="28">
-        <f>C25</f>
+      <c r="C25" s="53">
+        <f>C5*C$17*(1+C15)</f>
+        <v/>
+      </c>
+      <c r="D25" s="53">
+        <f>D5*D$17*(1+D15)</f>
+        <v/>
+      </c>
+      <c r="E25" s="53">
+        <f>E5*E$17*(1+E15)</f>
+        <v/>
+      </c>
+      <c r="F25" s="53">
+        <f>F5*F$17*(1+F15)</f>
+        <v/>
+      </c>
+      <c r="G25" s="53">
+        <f>G5*G$17*(1+G15)</f>
+        <v/>
+      </c>
+      <c r="H25" s="53">
+        <f>H5*H$17*(1+H15)</f>
+        <v/>
+      </c>
+      <c r="I25" s="53">
+        <f>I5*I$17*(1+I15)</f>
+        <v/>
+      </c>
+      <c r="J25" s="53">
+        <f>J5*J$17*(1+J15)</f>
+        <v/>
+      </c>
+      <c r="K25" s="53">
+        <f>K5*K$17*(1+K15)</f>
+        <v/>
+      </c>
+      <c r="L25" s="53">
+        <f>L5*L$17*(1+L15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Engineering: loaded</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C26" s="53">
+        <f>C6*C$18*(1+C15)</f>
+        <v/>
+      </c>
+      <c r="D26" s="53">
+        <f>D6*D$18*(1+D15)</f>
+        <v/>
+      </c>
+      <c r="E26" s="53">
+        <f>E6*E$18*(1+E15)</f>
+        <v/>
+      </c>
+      <c r="F26" s="53">
+        <f>F6*F$18*(1+F15)</f>
+        <v/>
+      </c>
+      <c r="G26" s="53">
+        <f>G6*G$18*(1+G15)</f>
+        <v/>
+      </c>
+      <c r="H26" s="53">
+        <f>H6*H$18*(1+H15)</f>
+        <v/>
+      </c>
+      <c r="I26" s="53">
+        <f>I6*I$18*(1+I15)</f>
+        <v/>
+      </c>
+      <c r="J26" s="53">
+        <f>J6*J$18*(1+J15)</f>
+        <v/>
+      </c>
+      <c r="K26" s="53">
+        <f>K6*K$18*(1+K15)</f>
+        <v/>
+      </c>
+      <c r="L26" s="53">
+        <f>L6*L$18*(1+L15)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Founder / CEO: loaded</t>
+          <t>BD / partnerships: loaded</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
@@ -3431,50 +3406,50 @@
         </is>
       </c>
       <c r="C27" s="53">
-        <f>C5*C$19*(1+C17)</f>
+        <f>C7*C$19*(1+C15)</f>
         <v/>
       </c>
       <c r="D27" s="53">
-        <f>D5*D$19*(1+D17)</f>
+        <f>D7*D$19*(1+D15)</f>
         <v/>
       </c>
       <c r="E27" s="53">
-        <f>E5*E$19*(1+E17)</f>
+        <f>E7*E$19*(1+E15)</f>
         <v/>
       </c>
       <c r="F27" s="53">
-        <f>F5*F$19*(1+F17)</f>
+        <f>F7*F$19*(1+F15)</f>
         <v/>
       </c>
       <c r="G27" s="53">
-        <f>G5*G$19*(1+G17)</f>
+        <f>G7*G$19*(1+G15)</f>
         <v/>
       </c>
       <c r="H27" s="53">
-        <f>H5*H$19*(1+H17)</f>
+        <f>H7*H$19*(1+H15)</f>
         <v/>
       </c>
       <c r="I27" s="53">
-        <f>I5*I$19*(1+I17)</f>
+        <f>I7*I$19*(1+I15)</f>
         <v/>
       </c>
       <c r="J27" s="53">
-        <f>J5*J$19*(1+J17)</f>
+        <f>J7*J$19*(1+J15)</f>
         <v/>
       </c>
       <c r="K27" s="53">
-        <f>K5*K$19*(1+K17)</f>
+        <f>K7*K$19*(1+K15)</f>
         <v/>
       </c>
       <c r="L27" s="53">
-        <f>L5*L$19*(1+L17)</f>
+        <f>L7*L$19*(1+L15)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Engineering: loaded</t>
+          <t>Athlete success: loaded</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
@@ -3483,50 +3458,50 @@
         </is>
       </c>
       <c r="C28" s="53">
-        <f>C6*C$20*(1+C17)</f>
+        <f>C8*C$20*(1+C15)</f>
         <v/>
       </c>
       <c r="D28" s="53">
-        <f>D6*D$20*(1+D17)</f>
+        <f>D8*D$20*(1+D15)</f>
         <v/>
       </c>
       <c r="E28" s="53">
-        <f>E6*E$20*(1+E17)</f>
+        <f>E8*E$20*(1+E15)</f>
         <v/>
       </c>
       <c r="F28" s="53">
-        <f>F6*F$20*(1+F17)</f>
+        <f>F8*F$20*(1+F15)</f>
         <v/>
       </c>
       <c r="G28" s="53">
-        <f>G6*G$20*(1+G17)</f>
+        <f>G8*G$20*(1+G15)</f>
         <v/>
       </c>
       <c r="H28" s="53">
-        <f>H6*H$20*(1+H17)</f>
+        <f>H8*H$20*(1+H15)</f>
         <v/>
       </c>
       <c r="I28" s="53">
-        <f>I6*I$20*(1+I17)</f>
+        <f>I8*I$20*(1+I15)</f>
         <v/>
       </c>
       <c r="J28" s="53">
-        <f>J6*J$20*(1+J17)</f>
+        <f>J8*J$20*(1+J15)</f>
         <v/>
       </c>
       <c r="K28" s="53">
-        <f>K6*K$20*(1+K17)</f>
+        <f>K8*K$20*(1+K15)</f>
         <v/>
       </c>
       <c r="L28" s="53">
-        <f>L6*L$20*(1+L17)</f>
+        <f>L8*L$20*(1+L15)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>BD / partnerships: loaded</t>
+          <t>Trust &amp; safety / review: loaded</t>
         </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
@@ -3535,50 +3510,50 @@
         </is>
       </c>
       <c r="C29" s="53">
-        <f>C7*C$21*(1+C17)</f>
+        <f>C9*C$21*(1+C15)</f>
         <v/>
       </c>
       <c r="D29" s="53">
-        <f>D7*D$21*(1+D17)</f>
+        <f>D9*D$21*(1+D15)</f>
         <v/>
       </c>
       <c r="E29" s="53">
-        <f>E7*E$21*(1+E17)</f>
+        <f>E9*E$21*(1+E15)</f>
         <v/>
       </c>
       <c r="F29" s="53">
-        <f>F7*F$21*(1+F17)</f>
+        <f>F9*F$21*(1+F15)</f>
         <v/>
       </c>
       <c r="G29" s="53">
-        <f>G7*G$21*(1+G17)</f>
+        <f>G9*G$21*(1+G15)</f>
         <v/>
       </c>
       <c r="H29" s="53">
-        <f>H7*H$21*(1+H17)</f>
+        <f>H9*H$21*(1+H15)</f>
         <v/>
       </c>
       <c r="I29" s="53">
-        <f>I7*I$21*(1+I17)</f>
+        <f>I9*I$21*(1+I15)</f>
         <v/>
       </c>
       <c r="J29" s="53">
-        <f>J7*J$21*(1+J17)</f>
+        <f>J9*J$21*(1+J15)</f>
         <v/>
       </c>
       <c r="K29" s="53">
-        <f>K7*K$21*(1+K17)</f>
+        <f>K9*K$21*(1+K15)</f>
         <v/>
       </c>
       <c r="L29" s="53">
-        <f>L7*L$21*(1+L17)</f>
+        <f>L9*L$21*(1+L15)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>Athlete success: loaded</t>
+          <t>Finance / operations: loaded</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
@@ -3587,50 +3562,50 @@
         </is>
       </c>
       <c r="C30" s="53">
-        <f>C8*C$22*(1+C17)</f>
+        <f>C10*C$22*(1+C15)</f>
         <v/>
       </c>
       <c r="D30" s="53">
-        <f>D8*D$22*(1+D17)</f>
+        <f>D10*D$22*(1+D15)</f>
         <v/>
       </c>
       <c r="E30" s="53">
-        <f>E8*E$22*(1+E17)</f>
+        <f>E10*E$22*(1+E15)</f>
         <v/>
       </c>
       <c r="F30" s="53">
-        <f>F8*F$22*(1+F17)</f>
+        <f>F10*F$22*(1+F15)</f>
         <v/>
       </c>
       <c r="G30" s="53">
-        <f>G8*G$22*(1+G17)</f>
+        <f>G10*G$22*(1+G15)</f>
         <v/>
       </c>
       <c r="H30" s="53">
-        <f>H8*H$22*(1+H17)</f>
+        <f>H10*H$22*(1+H15)</f>
         <v/>
       </c>
       <c r="I30" s="53">
-        <f>I8*I$22*(1+I17)</f>
+        <f>I10*I$22*(1+I15)</f>
         <v/>
       </c>
       <c r="J30" s="53">
-        <f>J8*J$22*(1+J17)</f>
+        <f>J10*J$22*(1+J15)</f>
         <v/>
       </c>
       <c r="K30" s="53">
-        <f>K8*K$22*(1+K17)</f>
+        <f>K10*K$22*(1+K15)</f>
         <v/>
       </c>
       <c r="L30" s="53">
-        <f>L8*L$22*(1+L17)</f>
+        <f>L10*L$22*(1+L15)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>Trust &amp; safety / review: loaded</t>
+          <t>Data protection officer: loaded</t>
         </is>
       </c>
       <c r="B31" s="16" t="inlineStr">
@@ -3639,412 +3614,308 @@
         </is>
       </c>
       <c r="C31" s="53">
-        <f>C9*C$23*(1+C17)</f>
+        <f>C11*C$23*(1+C15)</f>
         <v/>
       </c>
       <c r="D31" s="53">
-        <f>D9*D$23*(1+D17)</f>
+        <f>D11*D$23*(1+D15)</f>
         <v/>
       </c>
       <c r="E31" s="53">
-        <f>E9*E$23*(1+E17)</f>
+        <f>E11*E$23*(1+E15)</f>
         <v/>
       </c>
       <c r="F31" s="53">
-        <f>F9*F$23*(1+F17)</f>
+        <f>F11*F$23*(1+F15)</f>
         <v/>
       </c>
       <c r="G31" s="53">
-        <f>G9*G$23*(1+G17)</f>
+        <f>G11*G$23*(1+G15)</f>
         <v/>
       </c>
       <c r="H31" s="53">
-        <f>H9*H$23*(1+H17)</f>
+        <f>H11*H$23*(1+H15)</f>
         <v/>
       </c>
       <c r="I31" s="53">
-        <f>I9*I$23*(1+I17)</f>
+        <f>I11*I$23*(1+I15)</f>
         <v/>
       </c>
       <c r="J31" s="53">
-        <f>J9*J$23*(1+J17)</f>
+        <f>J11*J$23*(1+J15)</f>
         <v/>
       </c>
       <c r="K31" s="53">
-        <f>K9*K$23*(1+K17)</f>
+        <f>K11*K$23*(1+K15)</f>
         <v/>
       </c>
       <c r="L31" s="53">
-        <f>L9*L$23*(1+L17)</f>
+        <f>L11*L$23*(1+L15)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>Finance / operations: loaded</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>TOTAL, role build-up</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="C32" s="53">
-        <f>C10*C$24*(1+C17)</f>
-        <v/>
-      </c>
-      <c r="D32" s="53">
-        <f>D10*D$24*(1+D17)</f>
-        <v/>
-      </c>
-      <c r="E32" s="53">
-        <f>E10*E$24*(1+E17)</f>
-        <v/>
-      </c>
-      <c r="F32" s="53">
-        <f>F10*F$24*(1+F17)</f>
-        <v/>
-      </c>
-      <c r="G32" s="53">
-        <f>G10*G$24*(1+G17)</f>
-        <v/>
-      </c>
-      <c r="H32" s="53">
-        <f>H10*H$24*(1+H17)</f>
-        <v/>
-      </c>
-      <c r="I32" s="53">
-        <f>I10*I$24*(1+I17)</f>
-        <v/>
-      </c>
-      <c r="J32" s="53">
-        <f>J10*J$24*(1+J17)</f>
-        <v/>
-      </c>
-      <c r="K32" s="53">
-        <f>K10*K$24*(1+K17)</f>
-        <v/>
-      </c>
-      <c r="L32" s="53">
-        <f>L10*L$24*(1+L17)</f>
+      <c r="C32" s="52">
+        <f>SUM(C25:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="52">
+        <f>SUM(D25:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="52">
+        <f>SUM(E25:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="52">
+        <f>SUM(F25:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="52">
+        <f>SUM(G25:G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="52">
+        <f>SUM(H25:H31)</f>
+        <v/>
+      </c>
+      <c r="I32" s="52">
+        <f>SUM(I25:I31)</f>
+        <v/>
+      </c>
+      <c r="J32" s="52">
+        <f>SUM(J25:J31)</f>
+        <v/>
+      </c>
+      <c r="K32" s="52">
+        <f>SUM(K25:K31)</f>
+        <v/>
+      </c>
+      <c r="L32" s="52">
+        <f>SUM(L25:L31)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Data protection officer: loaded</t>
+          <t>People cost in the model</t>
         </is>
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C33" s="53">
-        <f>C11*C$25*(1+C17)</f>
-        <v/>
-      </c>
-      <c r="D33" s="53">
-        <f>D11*D$25*(1+D17)</f>
-        <v/>
-      </c>
-      <c r="E33" s="53">
-        <f>E11*E$25*(1+E17)</f>
-        <v/>
-      </c>
-      <c r="F33" s="53">
-        <f>F11*F$25*(1+F17)</f>
-        <v/>
-      </c>
-      <c r="G33" s="53">
-        <f>G11*G$25*(1+G17)</f>
-        <v/>
-      </c>
-      <c r="H33" s="53">
-        <f>H11*H$25*(1+H17)</f>
-        <v/>
-      </c>
-      <c r="I33" s="53">
-        <f>I11*I$25*(1+I17)</f>
-        <v/>
-      </c>
-      <c r="J33" s="53">
-        <f>J11*J$25*(1+J17)</f>
-        <v/>
-      </c>
-      <c r="K33" s="53">
-        <f>K11*K$25*(1+K17)</f>
-        <v/>
-      </c>
-      <c r="L33" s="53">
-        <f>L11*L$25*(1+L17)</f>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="C33" s="28">
+        <f>Costs!C17</f>
+        <v/>
+      </c>
+      <c r="D33" s="28">
+        <f>Costs!D17</f>
+        <v/>
+      </c>
+      <c r="E33" s="28">
+        <f>Costs!E17</f>
+        <v/>
+      </c>
+      <c r="F33" s="28">
+        <f>Costs!F17</f>
+        <v/>
+      </c>
+      <c r="G33" s="28">
+        <f>Costs!G17</f>
+        <v/>
+      </c>
+      <c r="H33" s="28">
+        <f>Costs!H17</f>
+        <v/>
+      </c>
+      <c r="I33" s="28">
+        <f>Costs!I17</f>
+        <v/>
+      </c>
+      <c r="J33" s="28">
+        <f>Costs!J17</f>
+        <v/>
+      </c>
+      <c r="K33" s="28">
+        <f>Costs!K17</f>
+        <v/>
+      </c>
+      <c r="L33" s="28">
+        <f>Costs!L17</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="51" t="inlineStr">
-        <is>
-          <t>TOTAL, role build-up</t>
-        </is>
-      </c>
-      <c r="B34" s="43" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C34" s="52">
-        <f>SUM(C27:C33)</f>
-        <v/>
-      </c>
-      <c r="D34" s="52">
-        <f>SUM(D27:D33)</f>
-        <v/>
-      </c>
-      <c r="E34" s="52">
-        <f>SUM(E27:E33)</f>
-        <v/>
-      </c>
-      <c r="F34" s="52">
-        <f>SUM(F27:F33)</f>
-        <v/>
-      </c>
-      <c r="G34" s="52">
-        <f>SUM(G27:G33)</f>
-        <v/>
-      </c>
-      <c r="H34" s="52">
-        <f>SUM(H27:H33)</f>
-        <v/>
-      </c>
-      <c r="I34" s="52">
-        <f>SUM(I27:I33)</f>
-        <v/>
-      </c>
-      <c r="J34" s="52">
-        <f>SUM(J27:J33)</f>
-        <v/>
-      </c>
-      <c r="K34" s="52">
-        <f>SUM(K27:K33)</f>
-        <v/>
-      </c>
-      <c r="L34" s="52">
-        <f>SUM(L27:L33)</f>
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Difference: role mix</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>build-up less model</t>
+        </is>
+      </c>
+      <c r="C34" s="53">
+        <f>C32-C33</f>
+        <v/>
+      </c>
+      <c r="D34" s="53">
+        <f>D32-D33</f>
+        <v/>
+      </c>
+      <c r="E34" s="53">
+        <f>E32-E33</f>
+        <v/>
+      </c>
+      <c r="F34" s="53">
+        <f>F32-F33</f>
+        <v/>
+      </c>
+      <c r="G34" s="53">
+        <f>G32-G33</f>
+        <v/>
+      </c>
+      <c r="H34" s="53">
+        <f>H32-H33</f>
+        <v/>
+      </c>
+      <c r="I34" s="53">
+        <f>I32-I33</f>
+        <v/>
+      </c>
+      <c r="J34" s="53">
+        <f>J32-J33</f>
+        <v/>
+      </c>
+      <c r="K34" s="53">
+        <f>K32-K33</f>
+        <v/>
+      </c>
+      <c r="L34" s="53">
+        <f>L32-L33</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>People cost in the model</t>
+          <t xml:space="preserve">  memo: build-up per FTE</t>
         </is>
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>Costs</t>
-        </is>
-      </c>
-      <c r="C35" s="28">
-        <f>Costs!C17</f>
-        <v/>
-      </c>
-      <c r="D35" s="28">
-        <f>Costs!D17</f>
-        <v/>
-      </c>
-      <c r="E35" s="28">
-        <f>Costs!E17</f>
-        <v/>
-      </c>
-      <c r="F35" s="28">
-        <f>Costs!F17</f>
-        <v/>
-      </c>
-      <c r="G35" s="28">
-        <f>Costs!G17</f>
-        <v/>
-      </c>
-      <c r="H35" s="28">
-        <f>Costs!H17</f>
-        <v/>
-      </c>
-      <c r="I35" s="28">
-        <f>Costs!I17</f>
-        <v/>
-      </c>
-      <c r="J35" s="28">
-        <f>Costs!J17</f>
-        <v/>
-      </c>
-      <c r="K35" s="28">
-        <f>Costs!K17</f>
-        <v/>
-      </c>
-      <c r="L35" s="28">
-        <f>Costs!L17</f>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C35" s="65">
+        <f>IF(C12=0,0,C32/C12)</f>
+        <v/>
+      </c>
+      <c r="D35" s="65">
+        <f>IF(D12=0,0,D32/D12)</f>
+        <v/>
+      </c>
+      <c r="E35" s="65">
+        <f>IF(E12=0,0,E32/E12)</f>
+        <v/>
+      </c>
+      <c r="F35" s="65">
+        <f>IF(F12=0,0,F32/F12)</f>
+        <v/>
+      </c>
+      <c r="G35" s="65">
+        <f>IF(G12=0,0,G32/G12)</f>
+        <v/>
+      </c>
+      <c r="H35" s="65">
+        <f>IF(H12=0,0,H32/H12)</f>
+        <v/>
+      </c>
+      <c r="I35" s="65">
+        <f>IF(I12=0,0,I32/I12)</f>
+        <v/>
+      </c>
+      <c r="J35" s="65">
+        <f>IF(J12=0,0,J32/J12)</f>
+        <v/>
+      </c>
+      <c r="K35" s="65">
+        <f>IF(K12=0,0,K32/K12)</f>
+        <v/>
+      </c>
+      <c r="L35" s="65">
+        <f>IF(L12=0,0,L32/L12)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>Difference: role mix</t>
+          <t xml:space="preserve">  memo: model blended per FTE</t>
         </is>
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>build-up less model</t>
-        </is>
-      </c>
-      <c r="C36" s="53">
-        <f>C34-C35</f>
-        <v/>
-      </c>
-      <c r="D36" s="53">
-        <f>D34-D35</f>
-        <v/>
-      </c>
-      <c r="E36" s="53">
-        <f>E34-E35</f>
-        <v/>
-      </c>
-      <c r="F36" s="53">
-        <f>F34-F35</f>
-        <v/>
-      </c>
-      <c r="G36" s="53">
-        <f>G34-G35</f>
-        <v/>
-      </c>
-      <c r="H36" s="53">
-        <f>H34-H35</f>
-        <v/>
-      </c>
-      <c r="I36" s="53">
-        <f>I34-I35</f>
-        <v/>
-      </c>
-      <c r="J36" s="53">
-        <f>J34-J35</f>
-        <v/>
-      </c>
-      <c r="K36" s="53">
-        <f>K34-K35</f>
-        <v/>
-      </c>
-      <c r="L36" s="53">
-        <f>L34-L35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  memo: build-up per FTE</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="C37" s="66">
-        <f>IF(C12=0,0,C34/C12)</f>
-        <v/>
-      </c>
-      <c r="D37" s="66">
-        <f>IF(D12=0,0,D34/D12)</f>
-        <v/>
-      </c>
-      <c r="E37" s="66">
-        <f>IF(E12=0,0,E34/E12)</f>
-        <v/>
-      </c>
-      <c r="F37" s="66">
-        <f>IF(F12=0,0,F34/F12)</f>
-        <v/>
-      </c>
-      <c r="G37" s="66">
-        <f>IF(G12=0,0,G34/G12)</f>
-        <v/>
-      </c>
-      <c r="H37" s="66">
-        <f>IF(H12=0,0,H34/H12)</f>
-        <v/>
-      </c>
-      <c r="I37" s="66">
-        <f>IF(I12=0,0,I34/I12)</f>
-        <v/>
-      </c>
-      <c r="J37" s="66">
-        <f>IF(J12=0,0,J34/J12)</f>
-        <v/>
-      </c>
-      <c r="K37" s="66">
-        <f>IF(K12=0,0,K34/K12)</f>
-        <v/>
-      </c>
-      <c r="L37" s="66">
-        <f>IF(L12=0,0,L34/L12)</f>
+      <c r="C36" s="28">
+        <f>Assumptions!C67</f>
+        <v/>
+      </c>
+      <c r="D36" s="28">
+        <f>Assumptions!D67</f>
+        <v/>
+      </c>
+      <c r="E36" s="28">
+        <f>Assumptions!E67</f>
+        <v/>
+      </c>
+      <c r="F36" s="28">
+        <f>Assumptions!F67</f>
+        <v/>
+      </c>
+      <c r="G36" s="28">
+        <f>Assumptions!G67</f>
+        <v/>
+      </c>
+      <c r="H36" s="28">
+        <f>Assumptions!H67</f>
+        <v/>
+      </c>
+      <c r="I36" s="28">
+        <f>Assumptions!I67</f>
+        <v/>
+      </c>
+      <c r="J36" s="28">
+        <f>Assumptions!J67</f>
+        <v/>
+      </c>
+      <c r="K36" s="28">
+        <f>Assumptions!K67</f>
+        <v/>
+      </c>
+      <c r="L36" s="28">
+        <f>Assumptions!L67</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  memo: model blended per FTE</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C38" s="28">
-        <f>Assumptions!C67</f>
-        <v/>
-      </c>
-      <c r="D38" s="28">
-        <f>Assumptions!D67</f>
-        <v/>
-      </c>
-      <c r="E38" s="28">
-        <f>Assumptions!E67</f>
-        <v/>
-      </c>
-      <c r="F38" s="28">
-        <f>Assumptions!F67</f>
-        <v/>
-      </c>
-      <c r="G38" s="28">
-        <f>Assumptions!G67</f>
-        <v/>
-      </c>
-      <c r="H38" s="28">
-        <f>Assumptions!H67</f>
-        <v/>
-      </c>
-      <c r="I38" s="28">
-        <f>Assumptions!I67</f>
-        <v/>
-      </c>
-      <c r="J38" s="28">
-        <f>Assumptions!J67</f>
-        <v/>
-      </c>
-      <c r="K38" s="28">
-        <f>Assumptions!K67</f>
-        <v/>
-      </c>
-      <c r="L38" s="28">
-        <f>Assumptions!L67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="67" t="inlineStr">
+      <c r="A38" s="66" t="inlineStr">
         <is>
           <t>The FTE block reconciles exactly and is the plan. The cost build-up prices those roles at their own salaries; the model prices the same headcount at a blended loaded average that rises from 38k to 76k over the plan, while the build-up holds today's salaries flat. The two cross over at Y4: the build-up is the higher figure in Y1-Y3, where one founder salary dominates a team of two or three, and the model is higher from Y4 as its blended rate climbs. The model is the one that reaches the P&amp;L either way. The memo rows below make the two rates comparable.</t>
         </is>
@@ -4332,43 +4203,43 @@
           <t>years</t>
         </is>
       </c>
-      <c r="C8" s="68">
+      <c r="C8" s="67">
         <f>IF(C7=0,0,1/C7)</f>
         <v/>
       </c>
-      <c r="D8" s="68">
+      <c r="D8" s="67">
         <f>IF(D7=0,0,1/D7)</f>
         <v/>
       </c>
-      <c r="E8" s="68">
+      <c r="E8" s="67">
         <f>IF(E7=0,0,1/E7)</f>
         <v/>
       </c>
-      <c r="F8" s="68">
+      <c r="F8" s="67">
         <f>IF(F7=0,0,1/F7)</f>
         <v/>
       </c>
-      <c r="G8" s="68">
+      <c r="G8" s="67">
         <f>IF(G7=0,0,1/G7)</f>
         <v/>
       </c>
-      <c r="H8" s="68">
+      <c r="H8" s="67">
         <f>IF(H7=0,0,1/H7)</f>
         <v/>
       </c>
-      <c r="I8" s="68">
+      <c r="I8" s="67">
         <f>IF(I7=0,0,1/I7)</f>
         <v/>
       </c>
-      <c r="J8" s="68">
+      <c r="J8" s="67">
         <f>IF(J7=0,0,1/J7)</f>
         <v/>
       </c>
-      <c r="K8" s="68">
+      <c r="K8" s="67">
         <f>IF(K7=0,0,1/K7)</f>
         <v/>
       </c>
-      <c r="L8" s="68">
+      <c r="L8" s="67">
         <f>IF(L7=0,0,1/L7)</f>
         <v/>
       </c>
@@ -4540,43 +4411,43 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C12" s="65">
+      <c r="C12" s="68">
         <f>IF(C6=0,0,C11/C6)</f>
         <v/>
       </c>
-      <c r="D12" s="65">
+      <c r="D12" s="68">
         <f>IF(D6=0,0,D11/D6)</f>
         <v/>
       </c>
-      <c r="E12" s="65">
+      <c r="E12" s="68">
         <f>IF(E6=0,0,E11/E6)</f>
         <v/>
       </c>
-      <c r="F12" s="65">
+      <c r="F12" s="68">
         <f>IF(F6=0,0,F11/F6)</f>
         <v/>
       </c>
-      <c r="G12" s="65">
+      <c r="G12" s="68">
         <f>IF(G6=0,0,G11/G6)</f>
         <v/>
       </c>
-      <c r="H12" s="65">
+      <c r="H12" s="68">
         <f>IF(H6=0,0,H11/H6)</f>
         <v/>
       </c>
-      <c r="I12" s="65">
+      <c r="I12" s="68">
         <f>IF(I6=0,0,I11/I6)</f>
         <v/>
       </c>
-      <c r="J12" s="65">
+      <c r="J12" s="68">
         <f>IF(J6=0,0,J11/J6)</f>
         <v/>
       </c>
-      <c r="K12" s="65">
+      <c r="K12" s="68">
         <f>IF(K6=0,0,K11/K6)</f>
         <v/>
       </c>
-      <c r="L12" s="65">
+      <c r="L12" s="68">
         <f>IF(L6=0,0,L11/L6)</f>
         <v/>
       </c>
@@ -4634,7 +4505,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="67" t="inlineStr">
+      <c r="A15" s="66" t="inlineStr">
         <is>
           <t>The athlete LTV/CAC ratio is unusually high, and that is the thesis rather than an error: acquisition is cheap precisely because there is no incumbent agent to outbid in these sports. It should be read alongside the fan LTV below, which is small: the economics work on volume of athletes, not on the value of any one of them.</t>
         </is>
@@ -5173,7 +5044,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="67" t="inlineStr">
+      <c r="A30" s="66" t="inlineStr">
         <is>
           <t>Fan CAC is zero by construction: athletes bring their own audiences and the model spends nothing acquiring fans. That understates the risk rather than flattering the return, and the plan discloses it as such.</t>
         </is>
@@ -5408,7 +5279,7 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  at gross margin</t>
+          <t>at gross margin</t>
         </is>
       </c>
       <c r="B37" s="16" t="inlineStr">
@@ -5510,7 +5381,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="67" t="inlineStr">
+      <c r="A40" s="66" t="inlineStr">
         <is>
           <t>No sponsor LTV is shown. It needs a sponsor retention assumption the model does not make, and inventing one here would create a figure nothing else in the plan validates. Payback needs no such assumption, so payback is what is reported.</t>
         </is>
@@ -5518,6 +5389,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -6302,2458 +6174,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Check: Excel's own answers against the Python model</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="73" t="inlineStr">
-        <is>
-          <t>Each pair is the Python model's figure and the workbook's own calculation. VARIANCE must be zero: if a formula is wrong, it shows up here on open.</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>Y7</t>
-        </is>
-      </c>
-      <c r="J2" s="12" t="inlineStr">
-        <is>
-          <t>Y8</t>
-        </is>
-      </c>
-      <c r="K2" s="12" t="inlineStr">
-        <is>
-          <t>Y9</t>
-        </is>
-      </c>
-      <c r="L2" s="12" t="inlineStr">
-        <is>
-          <t>Y10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>NET REVENUE</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="n"/>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="14" t="n"/>
-      <c r="G4" s="14" t="n"/>
-      <c r="H4" s="14" t="n"/>
-      <c r="I4" s="14" t="n"/>
-      <c r="J4" s="14" t="n"/>
-      <c r="K4" s="14" t="n"/>
-      <c r="L4" s="14" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="n">
-        <v>2146.380000000001</v>
-      </c>
-      <c r="D5" s="24" t="n">
-        <v>68373.78390534884</v>
-      </c>
-      <c r="E5" s="24" t="n">
-        <v>286818.7980145874</v>
-      </c>
-      <c r="F5" s="24" t="n">
-        <v>703667.3557595818</v>
-      </c>
-      <c r="G5" s="24" t="n">
-        <v>1321350.106984068</v>
-      </c>
-      <c r="H5" s="24" t="n">
-        <v>2124048.476059291</v>
-      </c>
-      <c r="I5" s="24" t="n">
-        <v>3013163.222831439</v>
-      </c>
-      <c r="J5" s="24" t="n">
-        <v>3853438.128678631</v>
-      </c>
-      <c r="K5" s="24" t="n">
-        <v>4526655.053312617</v>
-      </c>
-      <c r="L5" s="24" t="n">
-        <v>5253768.632209034</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C6" s="28">
-        <f>Revenue!C26</f>
-        <v/>
-      </c>
-      <c r="D6" s="28">
-        <f>Revenue!D26</f>
-        <v/>
-      </c>
-      <c r="E6" s="28">
-        <f>Revenue!E26</f>
-        <v/>
-      </c>
-      <c r="F6" s="28">
-        <f>Revenue!F26</f>
-        <v/>
-      </c>
-      <c r="G6" s="28">
-        <f>Revenue!G26</f>
-        <v/>
-      </c>
-      <c r="H6" s="28">
-        <f>Revenue!H26</f>
-        <v/>
-      </c>
-      <c r="I6" s="28">
-        <f>Revenue!I26</f>
-        <v/>
-      </c>
-      <c r="J6" s="28">
-        <f>Revenue!J26</f>
-        <v/>
-      </c>
-      <c r="K6" s="28">
-        <f>Revenue!K26</f>
-        <v/>
-      </c>
-      <c r="L6" s="28">
-        <f>Revenue!L26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B7" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C7" s="74">
-        <f>ROUND(C6-C5,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="74">
-        <f>ROUND(D6-D5,0)</f>
-        <v/>
-      </c>
-      <c r="E7" s="74">
-        <f>ROUND(E6-E5,0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="74">
-        <f>ROUND(F6-F5,0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="74">
-        <f>ROUND(G6-G5,0)</f>
-        <v/>
-      </c>
-      <c r="H7" s="74">
-        <f>ROUND(H6-H5,0)</f>
-        <v/>
-      </c>
-      <c r="I7" s="74">
-        <f>ROUND(I6-I5,0)</f>
-        <v/>
-      </c>
-      <c r="J7" s="74">
-        <f>ROUND(J6-J5,0)</f>
-        <v/>
-      </c>
-      <c r="K7" s="74">
-        <f>ROUND(K6-K5,0)</f>
-        <v/>
-      </c>
-      <c r="L7" s="74">
-        <f>ROUND(L6-L5,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>COST OF SALES</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
-      <c r="J9" s="14" t="n"/>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="14" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="n">
-        <v>3422.709052287581</v>
-      </c>
-      <c r="D10" s="24" t="n">
-        <v>31857.28686143998</v>
-      </c>
-      <c r="E10" s="24" t="n">
-        <v>106695.0205154586</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>235197.4837750249</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>421378.2064945769</v>
-      </c>
-      <c r="H10" s="24" t="n">
-        <v>658989.5725221956</v>
-      </c>
-      <c r="I10" s="24" t="n">
-        <v>923988.594663968</v>
-      </c>
-      <c r="J10" s="24" t="n">
-        <v>1175852.257663428</v>
-      </c>
-      <c r="K10" s="24" t="n">
-        <v>1378200.045113646</v>
-      </c>
-      <c r="L10" s="24" t="n">
-        <v>1591699.099905172</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C11" s="28">
-        <f>Costs!C14</f>
-        <v/>
-      </c>
-      <c r="D11" s="28">
-        <f>Costs!D14</f>
-        <v/>
-      </c>
-      <c r="E11" s="28">
-        <f>Costs!E14</f>
-        <v/>
-      </c>
-      <c r="F11" s="28">
-        <f>Costs!F14</f>
-        <v/>
-      </c>
-      <c r="G11" s="28">
-        <f>Costs!G14</f>
-        <v/>
-      </c>
-      <c r="H11" s="28">
-        <f>Costs!H14</f>
-        <v/>
-      </c>
-      <c r="I11" s="28">
-        <f>Costs!I14</f>
-        <v/>
-      </c>
-      <c r="J11" s="28">
-        <f>Costs!J14</f>
-        <v/>
-      </c>
-      <c r="K11" s="28">
-        <f>Costs!K14</f>
-        <v/>
-      </c>
-      <c r="L11" s="28">
-        <f>Costs!L14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B12" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C12" s="74">
-        <f>ROUND(C11-C10,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="74">
-        <f>ROUND(D11-D10,0)</f>
-        <v/>
-      </c>
-      <c r="E12" s="74">
-        <f>ROUND(E11-E10,0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="74">
-        <f>ROUND(F11-F10,0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="74">
-        <f>ROUND(G11-G10,0)</f>
-        <v/>
-      </c>
-      <c r="H12" s="74">
-        <f>ROUND(H11-H10,0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="74">
-        <f>ROUND(I11-I10,0)</f>
-        <v/>
-      </c>
-      <c r="J12" s="74">
-        <f>ROUND(J11-J10,0)</f>
-        <v/>
-      </c>
-      <c r="K12" s="74">
-        <f>ROUND(K11-K10,0)</f>
-        <v/>
-      </c>
-      <c r="L12" s="74">
-        <f>ROUND(L11-L10,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>GROSS PROFIT</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="14" t="n"/>
-      <c r="K14" s="14" t="n"/>
-      <c r="L14" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="n">
-        <v>-1276.329052287581</v>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>36516.49704390886</v>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>180123.7774991288</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>468469.8719845568</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>899971.9004894909</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>1465058.903537095</v>
-      </c>
-      <c r="I15" s="24" t="n">
-        <v>2089174.628167471</v>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>2677585.871015203</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>3148455.008198972</v>
-      </c>
-      <c r="L15" s="24" t="n">
-        <v>3662069.532303861</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C16" s="28">
-        <f>'P&amp;L'!C6</f>
-        <v/>
-      </c>
-      <c r="D16" s="28">
-        <f>'P&amp;L'!D6</f>
-        <v/>
-      </c>
-      <c r="E16" s="28">
-        <f>'P&amp;L'!E6</f>
-        <v/>
-      </c>
-      <c r="F16" s="28">
-        <f>'P&amp;L'!F6</f>
-        <v/>
-      </c>
-      <c r="G16" s="28">
-        <f>'P&amp;L'!G6</f>
-        <v/>
-      </c>
-      <c r="H16" s="28">
-        <f>'P&amp;L'!H6</f>
-        <v/>
-      </c>
-      <c r="I16" s="28">
-        <f>'P&amp;L'!I6</f>
-        <v/>
-      </c>
-      <c r="J16" s="28">
-        <f>'P&amp;L'!J6</f>
-        <v/>
-      </c>
-      <c r="K16" s="28">
-        <f>'P&amp;L'!K6</f>
-        <v/>
-      </c>
-      <c r="L16" s="28">
-        <f>'P&amp;L'!L6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B17" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C17" s="74">
-        <f>ROUND(C16-C15,0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="74">
-        <f>ROUND(D16-D15,0)</f>
-        <v/>
-      </c>
-      <c r="E17" s="74">
-        <f>ROUND(E16-E15,0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="74">
-        <f>ROUND(F16-F15,0)</f>
-        <v/>
-      </c>
-      <c r="G17" s="74">
-        <f>ROUND(G16-G15,0)</f>
-        <v/>
-      </c>
-      <c r="H17" s="74">
-        <f>ROUND(H16-H15,0)</f>
-        <v/>
-      </c>
-      <c r="I17" s="74">
-        <f>ROUND(I16-I15,0)</f>
-        <v/>
-      </c>
-      <c r="J17" s="74">
-        <f>ROUND(J16-J15,0)</f>
-        <v/>
-      </c>
-      <c r="K17" s="74">
-        <f>ROUND(K16-K15,0)</f>
-        <v/>
-      </c>
-      <c r="L17" s="74">
-        <f>ROUND(L16-L15,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>OPERATING COSTS</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-      <c r="H19" s="14" t="n"/>
-      <c r="I19" s="14" t="n"/>
-      <c r="J19" s="14" t="n"/>
-      <c r="K19" s="14" t="n"/>
-      <c r="L19" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="n">
-        <v>109392.49303125</v>
-      </c>
-      <c r="D20" s="24" t="n">
-        <v>178185.2191447622</v>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>252106.0434635245</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>428374.5174483291</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>726522.4428024977</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>1071963.548555968</v>
-      </c>
-      <c r="I20" s="24" t="n">
-        <v>1346139.448471206</v>
-      </c>
-      <c r="J20" s="24" t="n">
-        <v>1594922.220972979</v>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>1804968.743606341</v>
-      </c>
-      <c r="L20" s="24" t="n">
-        <v>1978774.96116508</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C21" s="28">
-        <f>Costs!C35</f>
-        <v/>
-      </c>
-      <c r="D21" s="28">
-        <f>Costs!D35</f>
-        <v/>
-      </c>
-      <c r="E21" s="28">
-        <f>Costs!E35</f>
-        <v/>
-      </c>
-      <c r="F21" s="28">
-        <f>Costs!F35</f>
-        <v/>
-      </c>
-      <c r="G21" s="28">
-        <f>Costs!G35</f>
-        <v/>
-      </c>
-      <c r="H21" s="28">
-        <f>Costs!H35</f>
-        <v/>
-      </c>
-      <c r="I21" s="28">
-        <f>Costs!I35</f>
-        <v/>
-      </c>
-      <c r="J21" s="28">
-        <f>Costs!J35</f>
-        <v/>
-      </c>
-      <c r="K21" s="28">
-        <f>Costs!K35</f>
-        <v/>
-      </c>
-      <c r="L21" s="28">
-        <f>Costs!L35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B22" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C22" s="74">
-        <f>ROUND(C21-C20,0)</f>
-        <v/>
-      </c>
-      <c r="D22" s="74">
-        <f>ROUND(D21-D20,0)</f>
-        <v/>
-      </c>
-      <c r="E22" s="74">
-        <f>ROUND(E21-E20,0)</f>
-        <v/>
-      </c>
-      <c r="F22" s="74">
-        <f>ROUND(F21-F20,0)</f>
-        <v/>
-      </c>
-      <c r="G22" s="74">
-        <f>ROUND(G21-G20,0)</f>
-        <v/>
-      </c>
-      <c r="H22" s="74">
-        <f>ROUND(H21-H20,0)</f>
-        <v/>
-      </c>
-      <c r="I22" s="74">
-        <f>ROUND(I21-I20,0)</f>
-        <v/>
-      </c>
-      <c r="J22" s="74">
-        <f>ROUND(J21-J20,0)</f>
-        <v/>
-      </c>
-      <c r="K22" s="74">
-        <f>ROUND(K21-K20,0)</f>
-        <v/>
-      </c>
-      <c r="L22" s="74">
-        <f>ROUND(L21-L20,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
-      <c r="J24" s="14" t="n"/>
-      <c r="K24" s="14" t="n"/>
-      <c r="L24" s="14" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="n">
-        <v>-110668.8220835376</v>
-      </c>
-      <c r="D25" s="24" t="n">
-        <v>-141668.7221008533</v>
-      </c>
-      <c r="E25" s="24" t="n">
-        <v>-71982.26596439572</v>
-      </c>
-      <c r="F25" s="24" t="n">
-        <v>40095.35453622771</v>
-      </c>
-      <c r="G25" s="24" t="n">
-        <v>173449.4576869933</v>
-      </c>
-      <c r="H25" s="24" t="n">
-        <v>393095.3549811274</v>
-      </c>
-      <c r="I25" s="24" t="n">
-        <v>743035.1796962644</v>
-      </c>
-      <c r="J25" s="24" t="n">
-        <v>1082663.650042224</v>
-      </c>
-      <c r="K25" s="24" t="n">
-        <v>1343486.264592631</v>
-      </c>
-      <c r="L25" s="24" t="n">
-        <v>1683294.571138782</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C26" s="28">
-        <f>'P&amp;L'!C10</f>
-        <v/>
-      </c>
-      <c r="D26" s="28">
-        <f>'P&amp;L'!D10</f>
-        <v/>
-      </c>
-      <c r="E26" s="28">
-        <f>'P&amp;L'!E10</f>
-        <v/>
-      </c>
-      <c r="F26" s="28">
-        <f>'P&amp;L'!F10</f>
-        <v/>
-      </c>
-      <c r="G26" s="28">
-        <f>'P&amp;L'!G10</f>
-        <v/>
-      </c>
-      <c r="H26" s="28">
-        <f>'P&amp;L'!H10</f>
-        <v/>
-      </c>
-      <c r="I26" s="28">
-        <f>'P&amp;L'!I10</f>
-        <v/>
-      </c>
-      <c r="J26" s="28">
-        <f>'P&amp;L'!J10</f>
-        <v/>
-      </c>
-      <c r="K26" s="28">
-        <f>'P&amp;L'!K10</f>
-        <v/>
-      </c>
-      <c r="L26" s="28">
-        <f>'P&amp;L'!L10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B27" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C27" s="74">
-        <f>ROUND(C26-C25,0)</f>
-        <v/>
-      </c>
-      <c r="D27" s="74">
-        <f>ROUND(D26-D25,0)</f>
-        <v/>
-      </c>
-      <c r="E27" s="74">
-        <f>ROUND(E26-E25,0)</f>
-        <v/>
-      </c>
-      <c r="F27" s="74">
-        <f>ROUND(F26-F25,0)</f>
-        <v/>
-      </c>
-      <c r="G27" s="74">
-        <f>ROUND(G26-G25,0)</f>
-        <v/>
-      </c>
-      <c r="H27" s="74">
-        <f>ROUND(H26-H25,0)</f>
-        <v/>
-      </c>
-      <c r="I27" s="74">
-        <f>ROUND(I26-I25,0)</f>
-        <v/>
-      </c>
-      <c r="J27" s="74">
-        <f>ROUND(J26-J25,0)</f>
-        <v/>
-      </c>
-      <c r="K27" s="74">
-        <f>ROUND(K26-K25,0)</f>
-        <v/>
-      </c>
-      <c r="L27" s="74">
-        <f>ROUND(L26-L25,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>PAYING FANS (YEAR END)</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="14" t="n"/>
-      <c r="E29" s="14" t="n"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="14" t="n"/>
-      <c r="H29" s="14" t="n"/>
-      <c r="I29" s="14" t="n"/>
-      <c r="J29" s="14" t="n"/>
-      <c r="K29" s="14" t="n"/>
-      <c r="L29" s="14" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="17" t="n">
-        <v>4911.429846669657</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>14332.92579479482</v>
-      </c>
-      <c r="F30" s="17" t="n">
-        <v>28168.91439619112</v>
-      </c>
-      <c r="G30" s="17" t="n">
-        <v>46065.96637221651</v>
-      </c>
-      <c r="H30" s="17" t="n">
-        <v>67882.18011454886</v>
-      </c>
-      <c r="I30" s="17" t="n">
-        <v>92005.2</v>
-      </c>
-      <c r="J30" s="17" t="n">
-        <v>111619.44</v>
-      </c>
-      <c r="K30" s="17" t="n">
-        <v>128637.28</v>
-      </c>
-      <c r="L30" s="17" t="n">
-        <v>141502.9</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C31" s="19">
-        <f>Drivers!C38</f>
-        <v/>
-      </c>
-      <c r="D31" s="19">
-        <f>Drivers!D38</f>
-        <v/>
-      </c>
-      <c r="E31" s="19">
-        <f>Drivers!E38</f>
-        <v/>
-      </c>
-      <c r="F31" s="19">
-        <f>Drivers!F38</f>
-        <v/>
-      </c>
-      <c r="G31" s="19">
-        <f>Drivers!G38</f>
-        <v/>
-      </c>
-      <c r="H31" s="19">
-        <f>Drivers!H38</f>
-        <v/>
-      </c>
-      <c r="I31" s="19">
-        <f>Drivers!I38</f>
-        <v/>
-      </c>
-      <c r="J31" s="19">
-        <f>Drivers!J38</f>
-        <v/>
-      </c>
-      <c r="K31" s="19">
-        <f>Drivers!K38</f>
-        <v/>
-      </c>
-      <c r="L31" s="19">
-        <f>Drivers!L38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B32" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C32" s="75">
-        <f>ROUND(C31-C30,0)</f>
-        <v/>
-      </c>
-      <c r="D32" s="75">
-        <f>ROUND(D31-D30,0)</f>
-        <v/>
-      </c>
-      <c r="E32" s="75">
-        <f>ROUND(E31-E30,0)</f>
-        <v/>
-      </c>
-      <c r="F32" s="75">
-        <f>ROUND(F31-F30,0)</f>
-        <v/>
-      </c>
-      <c r="G32" s="75">
-        <f>ROUND(G31-G30,0)</f>
-        <v/>
-      </c>
-      <c r="H32" s="75">
-        <f>ROUND(H31-H30,0)</f>
-        <v/>
-      </c>
-      <c r="I32" s="75">
-        <f>ROUND(I31-I30,0)</f>
-        <v/>
-      </c>
-      <c r="J32" s="75">
-        <f>ROUND(J31-J30,0)</f>
-        <v/>
-      </c>
-      <c r="K32" s="75">
-        <f>ROUND(K31-K30,0)</f>
-        <v/>
-      </c>
-      <c r="L32" s="75">
-        <f>ROUND(L31-L30,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>AVERAGE PAYING FANS</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="14" t="n"/>
-      <c r="H34" s="14" t="n"/>
-      <c r="I34" s="14" t="n"/>
-      <c r="J34" s="14" t="n"/>
-      <c r="K34" s="14" t="n"/>
-      <c r="L34" s="14" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="17" t="n">
-        <v>3094.840947139147</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>10844.20522362626</v>
-      </c>
-      <c r="F35" s="17" t="n">
-        <v>23046.31971183246</v>
-      </c>
-      <c r="G35" s="17" t="n">
-        <v>39464.16928088696</v>
-      </c>
-      <c r="H35" s="17" t="n">
-        <v>59832.12887237647</v>
-      </c>
-      <c r="I35" s="17" t="n">
-        <v>82914.55503292556</v>
-      </c>
-      <c r="J35" s="17" t="n">
-        <v>104177.5514465162</v>
-      </c>
-      <c r="K35" s="17" t="n">
-        <v>122123.9241028032</v>
-      </c>
-      <c r="L35" s="17" t="n">
-        <v>136573.6263141455</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C36" s="19">
-        <f>Drivers!C39</f>
-        <v/>
-      </c>
-      <c r="D36" s="19">
-        <f>Drivers!D39</f>
-        <v/>
-      </c>
-      <c r="E36" s="19">
-        <f>Drivers!E39</f>
-        <v/>
-      </c>
-      <c r="F36" s="19">
-        <f>Drivers!F39</f>
-        <v/>
-      </c>
-      <c r="G36" s="19">
-        <f>Drivers!G39</f>
-        <v/>
-      </c>
-      <c r="H36" s="19">
-        <f>Drivers!H39</f>
-        <v/>
-      </c>
-      <c r="I36" s="19">
-        <f>Drivers!I39</f>
-        <v/>
-      </c>
-      <c r="J36" s="19">
-        <f>Drivers!J39</f>
-        <v/>
-      </c>
-      <c r="K36" s="19">
-        <f>Drivers!K39</f>
-        <v/>
-      </c>
-      <c r="L36" s="19">
-        <f>Drivers!L39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B37" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C37" s="75">
-        <f>ROUND(C36-C35,0)</f>
-        <v/>
-      </c>
-      <c r="D37" s="75">
-        <f>ROUND(D36-D35,0)</f>
-        <v/>
-      </c>
-      <c r="E37" s="75">
-        <f>ROUND(E36-E35,0)</f>
-        <v/>
-      </c>
-      <c r="F37" s="75">
-        <f>ROUND(F36-F35,0)</f>
-        <v/>
-      </c>
-      <c r="G37" s="75">
-        <f>ROUND(G36-G35,0)</f>
-        <v/>
-      </c>
-      <c r="H37" s="75">
-        <f>ROUND(H36-H35,0)</f>
-        <v/>
-      </c>
-      <c r="I37" s="75">
-        <f>ROUND(I36-I35,0)</f>
-        <v/>
-      </c>
-      <c r="J37" s="75">
-        <f>ROUND(J36-J35,0)</f>
-        <v/>
-      </c>
-      <c r="K37" s="75">
-        <f>ROUND(K36-K35,0)</f>
-        <v/>
-      </c>
-      <c r="L37" s="75">
-        <f>ROUND(L36-L35,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL GMV</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="n"/>
-      <c r="C39" s="14" t="n"/>
-      <c r="D39" s="14" t="n"/>
-      <c r="E39" s="14" t="n"/>
-      <c r="F39" s="14" t="n"/>
-      <c r="G39" s="14" t="n"/>
-      <c r="H39" s="14" t="n"/>
-      <c r="I39" s="14" t="n"/>
-      <c r="J39" s="14" t="n"/>
-      <c r="K39" s="14" t="n"/>
-      <c r="L39" s="14" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="n">
-        <v>16761.25</v>
-      </c>
-      <c r="D40" s="24" t="n">
-        <v>440772.267635659</v>
-      </c>
-      <c r="E40" s="24" t="n">
-        <v>1743303.253210139</v>
-      </c>
-      <c r="F40" s="24" t="n">
-        <v>4329939.094384411</v>
-      </c>
-      <c r="G40" s="24" t="n">
-        <v>8521258.677600455</v>
-      </c>
-      <c r="H40" s="24" t="n">
-        <v>14372378.17746194</v>
-      </c>
-      <c r="I40" s="24" t="n">
-        <v>20940262.73823626</v>
-      </c>
-      <c r="J40" s="24" t="n">
-        <v>27265422.25706821</v>
-      </c>
-      <c r="K40" s="24" t="n">
-        <v>31985041.56907789</v>
-      </c>
-      <c r="L40" s="24" t="n">
-        <v>37884320.54596245</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C41" s="28">
-        <f>Revenue!C20</f>
-        <v/>
-      </c>
-      <c r="D41" s="28">
-        <f>Revenue!D20</f>
-        <v/>
-      </c>
-      <c r="E41" s="28">
-        <f>Revenue!E20</f>
-        <v/>
-      </c>
-      <c r="F41" s="28">
-        <f>Revenue!F20</f>
-        <v/>
-      </c>
-      <c r="G41" s="28">
-        <f>Revenue!G20</f>
-        <v/>
-      </c>
-      <c r="H41" s="28">
-        <f>Revenue!H20</f>
-        <v/>
-      </c>
-      <c r="I41" s="28">
-        <f>Revenue!I20</f>
-        <v/>
-      </c>
-      <c r="J41" s="28">
-        <f>Revenue!J20</f>
-        <v/>
-      </c>
-      <c r="K41" s="28">
-        <f>Revenue!K20</f>
-        <v/>
-      </c>
-      <c r="L41" s="28">
-        <f>Revenue!L20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B42" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C42" s="74">
-        <f>ROUND(C41-C40,0)</f>
-        <v/>
-      </c>
-      <c r="D42" s="74">
-        <f>ROUND(D41-D40,0)</f>
-        <v/>
-      </c>
-      <c r="E42" s="74">
-        <f>ROUND(E41-E40,0)</f>
-        <v/>
-      </c>
-      <c r="F42" s="74">
-        <f>ROUND(F41-F40,0)</f>
-        <v/>
-      </c>
-      <c r="G42" s="74">
-        <f>ROUND(G41-G40,0)</f>
-        <v/>
-      </c>
-      <c r="H42" s="74">
-        <f>ROUND(H41-H40,0)</f>
-        <v/>
-      </c>
-      <c r="I42" s="74">
-        <f>ROUND(I41-I40,0)</f>
-        <v/>
-      </c>
-      <c r="J42" s="74">
-        <f>ROUND(J41-J40,0)</f>
-        <v/>
-      </c>
-      <c r="K42" s="74">
-        <f>ROUND(K41-K40,0)</f>
-        <v/>
-      </c>
-      <c r="L42" s="74">
-        <f>ROUND(L41-L40,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>DEALS</t>
-        </is>
-      </c>
-      <c r="B44" s="14" t="n"/>
-      <c r="C44" s="14" t="n"/>
-      <c r="D44" s="14" t="n"/>
-      <c r="E44" s="14" t="n"/>
-      <c r="F44" s="14" t="n"/>
-      <c r="G44" s="14" t="n"/>
-      <c r="H44" s="14" t="n"/>
-      <c r="I44" s="14" t="n"/>
-      <c r="J44" s="14" t="n"/>
-      <c r="K44" s="14" t="n"/>
-      <c r="L44" s="14" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="n">
-        <v>15.3375</v>
-      </c>
-      <c r="D45" s="17" t="n">
-        <v>73.26000000000001</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>274.72</v>
-      </c>
-      <c r="F45" s="17" t="n">
-        <v>722.7359999999999</v>
-      </c>
-      <c r="G45" s="17" t="n">
-        <v>1435.12</v>
-      </c>
-      <c r="H45" s="17" t="n">
-        <v>2397.2</v>
-      </c>
-      <c r="I45" s="17" t="n">
-        <v>3311.28</v>
-      </c>
-      <c r="J45" s="17" t="n">
-        <v>4180.608</v>
-      </c>
-      <c r="K45" s="17" t="n">
-        <v>4622.764</v>
-      </c>
-      <c r="L45" s="17" t="n">
-        <v>5427.08</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C46" s="19">
-        <f>Drivers!C46</f>
-        <v/>
-      </c>
-      <c r="D46" s="19">
-        <f>Drivers!D46</f>
-        <v/>
-      </c>
-      <c r="E46" s="19">
-        <f>Drivers!E46</f>
-        <v/>
-      </c>
-      <c r="F46" s="19">
-        <f>Drivers!F46</f>
-        <v/>
-      </c>
-      <c r="G46" s="19">
-        <f>Drivers!G46</f>
-        <v/>
-      </c>
-      <c r="H46" s="19">
-        <f>Drivers!H46</f>
-        <v/>
-      </c>
-      <c r="I46" s="19">
-        <f>Drivers!I46</f>
-        <v/>
-      </c>
-      <c r="J46" s="19">
-        <f>Drivers!J46</f>
-        <v/>
-      </c>
-      <c r="K46" s="19">
-        <f>Drivers!K46</f>
-        <v/>
-      </c>
-      <c r="L46" s="19">
-        <f>Drivers!L46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B47" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C47" s="75">
-        <f>ROUND(C46-C45,0)</f>
-        <v/>
-      </c>
-      <c r="D47" s="75">
-        <f>ROUND(D46-D45,0)</f>
-        <v/>
-      </c>
-      <c r="E47" s="75">
-        <f>ROUND(E46-E45,0)</f>
-        <v/>
-      </c>
-      <c r="F47" s="75">
-        <f>ROUND(F46-F45,0)</f>
-        <v/>
-      </c>
-      <c r="G47" s="75">
-        <f>ROUND(G46-G45,0)</f>
-        <v/>
-      </c>
-      <c r="H47" s="75">
-        <f>ROUND(H46-H45,0)</f>
-        <v/>
-      </c>
-      <c r="I47" s="75">
-        <f>ROUND(I46-I45,0)</f>
-        <v/>
-      </c>
-      <c r="J47" s="75">
-        <f>ROUND(J46-J45,0)</f>
-        <v/>
-      </c>
-      <c r="K47" s="75">
-        <f>ROUND(K46-K45,0)</f>
-        <v/>
-      </c>
-      <c r="L47" s="75">
-        <f>ROUND(L46-L45,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>APPLICATIONS REQUIRED</t>
-        </is>
-      </c>
-      <c r="B49" s="14" t="n"/>
-      <c r="C49" s="14" t="n"/>
-      <c r="D49" s="14" t="n"/>
-      <c r="E49" s="14" t="n"/>
-      <c r="F49" s="14" t="n"/>
-      <c r="G49" s="14" t="n"/>
-      <c r="H49" s="14" t="n"/>
-      <c r="I49" s="14" t="n"/>
-      <c r="J49" s="14" t="n"/>
-      <c r="K49" s="14" t="n"/>
-      <c r="L49" s="14" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="n">
-        <v>1250</v>
-      </c>
-      <c r="D50" s="17" t="n">
-        <v>2525</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>4534.399999999999</v>
-      </c>
-      <c r="F50" s="17" t="n">
-        <v>5522.222222222222</v>
-      </c>
-      <c r="G50" s="17" t="n">
-        <v>6332.631578947367</v>
-      </c>
-      <c r="H50" s="17" t="n">
-        <v>6871.864406779659</v>
-      </c>
-      <c r="I50" s="17" t="n">
-        <v>7016.39344262295</v>
-      </c>
-      <c r="J50" s="17" t="n">
-        <v>6805.16129032258</v>
-      </c>
-      <c r="K50" s="17" t="n">
-        <v>6530.793650793649</v>
-      </c>
-      <c r="L50" s="17" t="n">
-        <v>6448.125984251968</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C51" s="19">
-        <f>Drivers!C54</f>
-        <v/>
-      </c>
-      <c r="D51" s="19">
-        <f>Drivers!D54</f>
-        <v/>
-      </c>
-      <c r="E51" s="19">
-        <f>Drivers!E54</f>
-        <v/>
-      </c>
-      <c r="F51" s="19">
-        <f>Drivers!F54</f>
-        <v/>
-      </c>
-      <c r="G51" s="19">
-        <f>Drivers!G54</f>
-        <v/>
-      </c>
-      <c r="H51" s="19">
-        <f>Drivers!H54</f>
-        <v/>
-      </c>
-      <c r="I51" s="19">
-        <f>Drivers!I54</f>
-        <v/>
-      </c>
-      <c r="J51" s="19">
-        <f>Drivers!J54</f>
-        <v/>
-      </c>
-      <c r="K51" s="19">
-        <f>Drivers!K54</f>
-        <v/>
-      </c>
-      <c r="L51" s="19">
-        <f>Drivers!L54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B52" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C52" s="75">
-        <f>ROUND(C51-C50,0)</f>
-        <v/>
-      </c>
-      <c r="D52" s="75">
-        <f>ROUND(D51-D50,0)</f>
-        <v/>
-      </c>
-      <c r="E52" s="75">
-        <f>ROUND(E51-E50,0)</f>
-        <v/>
-      </c>
-      <c r="F52" s="75">
-        <f>ROUND(F51-F50,0)</f>
-        <v/>
-      </c>
-      <c r="G52" s="75">
-        <f>ROUND(G51-G50,0)</f>
-        <v/>
-      </c>
-      <c r="H52" s="75">
-        <f>ROUND(H51-H50,0)</f>
-        <v/>
-      </c>
-      <c r="I52" s="75">
-        <f>ROUND(I51-I50,0)</f>
-        <v/>
-      </c>
-      <c r="J52" s="75">
-        <f>ROUND(J51-J50,0)</f>
-        <v/>
-      </c>
-      <c r="K52" s="75">
-        <f>ROUND(K51-K50,0)</f>
-        <v/>
-      </c>
-      <c r="L52" s="75">
-        <f>ROUND(L51-L50,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>ATHLETE VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B54" s="14" t="n"/>
-      <c r="C54" s="14" t="n"/>
-      <c r="D54" s="14" t="n"/>
-      <c r="E54" s="14" t="n"/>
-      <c r="F54" s="14" t="n"/>
-      <c r="G54" s="14" t="n"/>
-      <c r="H54" s="14" t="n"/>
-      <c r="I54" s="14" t="n"/>
-      <c r="J54" s="14" t="n"/>
-      <c r="K54" s="14" t="n"/>
-      <c r="L54" s="14" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C55" s="24" t="n">
-        <v>465.6862745098039</v>
-      </c>
-      <c r="D55" s="24" t="n">
-        <v>1251.211764705882</v>
-      </c>
-      <c r="E55" s="24" t="n">
-        <v>2517.925647058823</v>
-      </c>
-      <c r="F55" s="24" t="n">
-        <v>3193.273725490196</v>
-      </c>
-      <c r="G55" s="24" t="n">
-        <v>3707.495034055726</v>
-      </c>
-      <c r="H55" s="24" t="n">
-        <v>4093.798689265535</v>
-      </c>
-      <c r="I55" s="24" t="n">
-        <v>4248.907746705239</v>
-      </c>
-      <c r="J55" s="24" t="n">
-        <v>4211.834413662239</v>
-      </c>
-      <c r="K55" s="24" t="n">
-        <v>4127.768918767506</v>
-      </c>
-      <c r="L55" s="24" t="n">
-        <v>4172.215666265246</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C56" s="28">
-        <f>Costs!C13</f>
-        <v/>
-      </c>
-      <c r="D56" s="28">
-        <f>Costs!D13</f>
-        <v/>
-      </c>
-      <c r="E56" s="28">
-        <f>Costs!E13</f>
-        <v/>
-      </c>
-      <c r="F56" s="28">
-        <f>Costs!F13</f>
-        <v/>
-      </c>
-      <c r="G56" s="28">
-        <f>Costs!G13</f>
-        <v/>
-      </c>
-      <c r="H56" s="28">
-        <f>Costs!H13</f>
-        <v/>
-      </c>
-      <c r="I56" s="28">
-        <f>Costs!I13</f>
-        <v/>
-      </c>
-      <c r="J56" s="28">
-        <f>Costs!J13</f>
-        <v/>
-      </c>
-      <c r="K56" s="28">
-        <f>Costs!K13</f>
-        <v/>
-      </c>
-      <c r="L56" s="28">
-        <f>Costs!L13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B57" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C57" s="74">
-        <f>ROUND(C56-C55,0)</f>
-        <v/>
-      </c>
-      <c r="D57" s="74">
-        <f>ROUND(D56-D55,0)</f>
-        <v/>
-      </c>
-      <c r="E57" s="74">
-        <f>ROUND(E56-E55,0)</f>
-        <v/>
-      </c>
-      <c r="F57" s="74">
-        <f>ROUND(F56-F55,0)</f>
-        <v/>
-      </c>
-      <c r="G57" s="74">
-        <f>ROUND(G56-G55,0)</f>
-        <v/>
-      </c>
-      <c r="H57" s="74">
-        <f>ROUND(H56-H55,0)</f>
-        <v/>
-      </c>
-      <c r="I57" s="74">
-        <f>ROUND(I56-I55,0)</f>
-        <v/>
-      </c>
-      <c r="J57" s="74">
-        <f>ROUND(J56-J55,0)</f>
-        <v/>
-      </c>
-      <c r="K57" s="74">
-        <f>ROUND(K56-K55,0)</f>
-        <v/>
-      </c>
-      <c r="L57" s="74">
-        <f>ROUND(L56-L55,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>TAX CHARGE</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="n"/>
-      <c r="C59" s="14" t="n"/>
-      <c r="D59" s="14" t="n"/>
-      <c r="E59" s="14" t="n"/>
-      <c r="F59" s="14" t="n"/>
-      <c r="G59" s="14" t="n"/>
-      <c r="H59" s="14" t="n"/>
-      <c r="I59" s="14" t="n"/>
-      <c r="J59" s="14" t="n"/>
-      <c r="K59" s="14" t="n"/>
-      <c r="L59" s="14" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C60" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="24" t="n">
-        <v>12258.05355833427</v>
-      </c>
-      <c r="I60" s="24" t="n">
-        <v>89855.27695443966</v>
-      </c>
-      <c r="J60" s="24" t="n">
-        <v>131259.5475063336</v>
-      </c>
-      <c r="K60" s="24" t="n">
-        <v>161427.9396888946</v>
-      </c>
-      <c r="L60" s="24" t="n">
-        <v>341098.6427846954</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B61" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C61" s="28">
-        <f>-'P&amp;L'!C20</f>
-        <v/>
-      </c>
-      <c r="D61" s="28">
-        <f>-'P&amp;L'!D20</f>
-        <v/>
-      </c>
-      <c r="E61" s="28">
-        <f>-'P&amp;L'!E20</f>
-        <v/>
-      </c>
-      <c r="F61" s="28">
-        <f>-'P&amp;L'!F20</f>
-        <v/>
-      </c>
-      <c r="G61" s="28">
-        <f>-'P&amp;L'!G20</f>
-        <v/>
-      </c>
-      <c r="H61" s="28">
-        <f>-'P&amp;L'!H20</f>
-        <v/>
-      </c>
-      <c r="I61" s="28">
-        <f>-'P&amp;L'!I20</f>
-        <v/>
-      </c>
-      <c r="J61" s="28">
-        <f>-'P&amp;L'!J20</f>
-        <v/>
-      </c>
-      <c r="K61" s="28">
-        <f>-'P&amp;L'!K20</f>
-        <v/>
-      </c>
-      <c r="L61" s="28">
-        <f>-'P&amp;L'!L20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B62" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C62" s="74">
-        <f>ROUND(C61-C60,0)</f>
-        <v/>
-      </c>
-      <c r="D62" s="74">
-        <f>ROUND(D61-D60,0)</f>
-        <v/>
-      </c>
-      <c r="E62" s="74">
-        <f>ROUND(E61-E60,0)</f>
-        <v/>
-      </c>
-      <c r="F62" s="74">
-        <f>ROUND(F61-F60,0)</f>
-        <v/>
-      </c>
-      <c r="G62" s="74">
-        <f>ROUND(G61-G60,0)</f>
-        <v/>
-      </c>
-      <c r="H62" s="74">
-        <f>ROUND(H61-H60,0)</f>
-        <v/>
-      </c>
-      <c r="I62" s="74">
-        <f>ROUND(I61-I60,0)</f>
-        <v/>
-      </c>
-      <c r="J62" s="74">
-        <f>ROUND(J61-J60,0)</f>
-        <v/>
-      </c>
-      <c r="K62" s="74">
-        <f>ROUND(K61-K60,0)</f>
-        <v/>
-      </c>
-      <c r="L62" s="74">
-        <f>ROUND(L61-L60,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>NET PROFIT</t>
-        </is>
-      </c>
-      <c r="B64" s="14" t="n"/>
-      <c r="C64" s="14" t="n"/>
-      <c r="D64" s="14" t="n"/>
-      <c r="E64" s="14" t="n"/>
-      <c r="F64" s="14" t="n"/>
-      <c r="G64" s="14" t="n"/>
-      <c r="H64" s="14" t="n"/>
-      <c r="I64" s="14" t="n"/>
-      <c r="J64" s="14" t="n"/>
-      <c r="K64" s="14" t="n"/>
-      <c r="L64" s="14" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C65" s="24" t="n">
-        <v>-114468.8220835376</v>
-      </c>
-      <c r="D65" s="24" t="n">
-        <v>-153268.7221008533</v>
-      </c>
-      <c r="E65" s="24" t="n">
-        <v>-92582.26596439572</v>
-      </c>
-      <c r="F65" s="24" t="n">
-        <v>10495.35453622771</v>
-      </c>
-      <c r="G65" s="24" t="n">
-        <v>125249.4576869933</v>
-      </c>
-      <c r="H65" s="24" t="n">
-        <v>294037.3014227932</v>
-      </c>
-      <c r="I65" s="24" t="n">
-        <v>509179.9027418248</v>
-      </c>
-      <c r="J65" s="24" t="n">
-        <v>743804.1025358904</v>
-      </c>
-      <c r="K65" s="24" t="n">
-        <v>914758.324903736</v>
-      </c>
-      <c r="L65" s="24" t="n">
-        <v>1023295.928354086</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C66" s="28">
-        <f>'P&amp;L'!C21</f>
-        <v/>
-      </c>
-      <c r="D66" s="28">
-        <f>'P&amp;L'!D21</f>
-        <v/>
-      </c>
-      <c r="E66" s="28">
-        <f>'P&amp;L'!E21</f>
-        <v/>
-      </c>
-      <c r="F66" s="28">
-        <f>'P&amp;L'!F21</f>
-        <v/>
-      </c>
-      <c r="G66" s="28">
-        <f>'P&amp;L'!G21</f>
-        <v/>
-      </c>
-      <c r="H66" s="28">
-        <f>'P&amp;L'!H21</f>
-        <v/>
-      </c>
-      <c r="I66" s="28">
-        <f>'P&amp;L'!I21</f>
-        <v/>
-      </c>
-      <c r="J66" s="28">
-        <f>'P&amp;L'!J21</f>
-        <v/>
-      </c>
-      <c r="K66" s="28">
-        <f>'P&amp;L'!K21</f>
-        <v/>
-      </c>
-      <c r="L66" s="28">
-        <f>'P&amp;L'!L21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B67" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C67" s="74">
-        <f>ROUND(C66-C65,0)</f>
-        <v/>
-      </c>
-      <c r="D67" s="74">
-        <f>ROUND(D66-D65,0)</f>
-        <v/>
-      </c>
-      <c r="E67" s="74">
-        <f>ROUND(E66-E65,0)</f>
-        <v/>
-      </c>
-      <c r="F67" s="74">
-        <f>ROUND(F66-F65,0)</f>
-        <v/>
-      </c>
-      <c r="G67" s="74">
-        <f>ROUND(G66-G65,0)</f>
-        <v/>
-      </c>
-      <c r="H67" s="74">
-        <f>ROUND(H66-H65,0)</f>
-        <v/>
-      </c>
-      <c r="I67" s="74">
-        <f>ROUND(I66-I65,0)</f>
-        <v/>
-      </c>
-      <c r="J67" s="74">
-        <f>ROUND(J66-J65,0)</f>
-        <v/>
-      </c>
-      <c r="K67" s="74">
-        <f>ROUND(K66-K65,0)</f>
-        <v/>
-      </c>
-      <c r="L67" s="74">
-        <f>ROUND(L66-L65,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="13" t="inlineStr">
-        <is>
-          <t>FREE CASH FLOW</t>
-        </is>
-      </c>
-      <c r="B69" s="14" t="n"/>
-      <c r="C69" s="14" t="n"/>
-      <c r="D69" s="14" t="n"/>
-      <c r="E69" s="14" t="n"/>
-      <c r="F69" s="14" t="n"/>
-      <c r="G69" s="14" t="n"/>
-      <c r="H69" s="14" t="n"/>
-      <c r="I69" s="14" t="n"/>
-      <c r="J69" s="14" t="n"/>
-      <c r="K69" s="14" t="n"/>
-      <c r="L69" s="14" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Python model</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="inlineStr">
-        <is>
-          <t>model.py</t>
-        </is>
-      </c>
-      <c r="C70" s="24" t="n">
-        <v>-112653.46197138</v>
-      </c>
-      <c r="D70" s="24" t="n">
-        <v>-140887.3793014216</v>
-      </c>
-      <c r="E70" s="24" t="n">
-        <v>-42250.72559329525</v>
-      </c>
-      <c r="F70" s="24" t="n">
-        <v>109349.9663889915</v>
-      </c>
-      <c r="G70" s="24" t="n">
-        <v>266910.6407489183</v>
-      </c>
-      <c r="H70" s="24" t="n">
-        <v>471292.6485755878</v>
-      </c>
-      <c r="I70" s="24" t="n">
-        <v>698647.4823472798</v>
-      </c>
-      <c r="J70" s="24" t="n">
-        <v>926920.6293053289</v>
-      </c>
-      <c r="K70" s="24" t="n">
-        <v>1048519.878765414</v>
-      </c>
-      <c r="L70" s="24" t="n">
-        <v>1194856.150657782</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook</t>
-        </is>
-      </c>
-      <c r="B71" s="16" t="inlineStr">
-        <is>
-          <t>recalculated</t>
-        </is>
-      </c>
-      <c r="C71" s="28">
-        <f>CashFlow!C9</f>
-        <v/>
-      </c>
-      <c r="D71" s="28">
-        <f>CashFlow!D9</f>
-        <v/>
-      </c>
-      <c r="E71" s="28">
-        <f>CashFlow!E9</f>
-        <v/>
-      </c>
-      <c r="F71" s="28">
-        <f>CashFlow!F9</f>
-        <v/>
-      </c>
-      <c r="G71" s="28">
-        <f>CashFlow!G9</f>
-        <v/>
-      </c>
-      <c r="H71" s="28">
-        <f>CashFlow!H9</f>
-        <v/>
-      </c>
-      <c r="I71" s="28">
-        <f>CashFlow!I9</f>
-        <v/>
-      </c>
-      <c r="J71" s="28">
-        <f>CashFlow!J9</f>
-        <v/>
-      </c>
-      <c r="K71" s="28">
-        <f>CashFlow!K9</f>
-        <v/>
-      </c>
-      <c r="L71" s="28">
-        <f>CashFlow!L9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VARIANCE</t>
-        </is>
-      </c>
-      <c r="B72" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C72" s="74">
-        <f>ROUND(C71-C70,0)</f>
-        <v/>
-      </c>
-      <c r="D72" s="74">
-        <f>ROUND(D71-D70,0)</f>
-        <v/>
-      </c>
-      <c r="E72" s="74">
-        <f>ROUND(E71-E70,0)</f>
-        <v/>
-      </c>
-      <c r="F72" s="74">
-        <f>ROUND(F71-F70,0)</f>
-        <v/>
-      </c>
-      <c r="G72" s="74">
-        <f>ROUND(G71-G70,0)</f>
-        <v/>
-      </c>
-      <c r="H72" s="74">
-        <f>ROUND(H71-H70,0)</f>
-        <v/>
-      </c>
-      <c r="I72" s="74">
-        <f>ROUND(I71-I70,0)</f>
-        <v/>
-      </c>
-      <c r="J72" s="74">
-        <f>ROUND(J71-J70,0)</f>
-        <v/>
-      </c>
-      <c r="K72" s="74">
-        <f>ROUND(K71-K70,0)</f>
-        <v/>
-      </c>
-      <c r="L72" s="74">
-        <f>ROUND(L71-L70,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Balance sheet check (from BalanceSheet, must be zero):</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Assets less liabilities and equity</t>
-        </is>
-      </c>
-      <c r="B75" s="43" t="inlineStr">
-        <is>
-          <t>must be 0</t>
-        </is>
-      </c>
-      <c r="C75" s="76">
-        <f>BalanceSheet!C20</f>
-        <v/>
-      </c>
-      <c r="D75" s="76">
-        <f>BalanceSheet!D20</f>
-        <v/>
-      </c>
-      <c r="E75" s="76">
-        <f>BalanceSheet!E20</f>
-        <v/>
-      </c>
-      <c r="F75" s="76">
-        <f>BalanceSheet!F20</f>
-        <v/>
-      </c>
-      <c r="G75" s="76">
-        <f>BalanceSheet!G20</f>
-        <v/>
-      </c>
-      <c r="H75" s="76">
-        <f>BalanceSheet!H20</f>
-        <v/>
-      </c>
-      <c r="I75" s="76">
-        <f>BalanceSheet!I20</f>
-        <v/>
-      </c>
-      <c r="J75" s="76">
-        <f>BalanceSheet!J20</f>
-        <v/>
-      </c>
-      <c r="K75" s="76">
-        <f>BalanceSheet!K20</f>
-        <v/>
-      </c>
-      <c r="L75" s="76">
-        <f>BalanceSheet!L20</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8780,669 +6200,669 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="A4" s="73" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="77" t="inlineStr">
+      <c r="B4" s="73" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="77" t="inlineStr">
+      <c r="C4" s="73" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="77" t="inlineStr">
+      <c r="D4" s="73" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E4" s="77" t="inlineStr">
+      <c r="E4" s="73" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F4" s="77" t="inlineStr">
+      <c r="F4" s="73" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="inlineStr">
+      <c r="A5" s="74" t="inlineStr">
         <is>
           <t>Gross payments (GMV)</t>
         </is>
       </c>
-      <c r="B5" s="79" t="n">
+      <c r="B5" s="75" t="n">
         <v>7220000000</v>
       </c>
-      <c r="C5" s="80" t="inlineStr">
+      <c r="C5" s="76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D5" s="80" t="inlineStr">
+      <c r="D5" s="76" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E5" s="80" t="inlineStr">
+      <c r="E5" s="76" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F5" s="80" t="inlineStr">
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="78" t="inlineStr">
+      <c r="A6" s="74" t="inlineStr">
         <is>
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="B6" s="79" t="n">
+      <c r="B6" s="75" t="n">
         <v>1410000000</v>
       </c>
-      <c r="C6" s="80" t="inlineStr">
+      <c r="C6" s="76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D6" s="80" t="inlineStr">
+      <c r="D6" s="76" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E6" s="80" t="inlineStr">
+      <c r="E6" s="76" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F6" s="80" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts (Companies House 10354575)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="78" t="inlineStr">
+      <c r="A7" s="74" t="inlineStr">
         <is>
           <t>Paid to creators</t>
         </is>
       </c>
-      <c r="B7" s="79" t="n">
+      <c r="B7" s="75" t="n">
         <v>5800000000</v>
       </c>
-      <c r="C7" s="80" t="inlineStr">
+      <c r="C7" s="76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D7" s="80" t="inlineStr">
+      <c r="D7" s="76" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E7" s="80" t="inlineStr">
+      <c r="E7" s="76" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F7" s="80" t="inlineStr">
+      <c r="F7" s="76" t="inlineStr">
         <is>
           <t>Fenix International Ltd filed accounts, 80.3% of gross</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="78" t="inlineStr">
+      <c r="A8" s="74" t="inlineStr">
         <is>
           <t>Creator accounts</t>
         </is>
       </c>
-      <c r="B8" s="79" t="n">
+      <c r="B8" s="75" t="n">
         <v>4634000</v>
       </c>
-      <c r="C8" s="80" t="inlineStr">
+      <c r="C8" s="76" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D8" s="80" t="inlineStr">
+      <c r="D8" s="76" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E8" s="80" t="inlineStr">
+      <c r="E8" s="76" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F8" s="80" t="inlineStr">
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>Variety: +13% YoY</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="78" t="inlineStr">
+      <c r="A9" s="74" t="inlineStr">
         <is>
           <t>Fan accounts</t>
         </is>
       </c>
-      <c r="B9" s="79" t="n">
+      <c r="B9" s="75" t="n">
         <v>377500000</v>
       </c>
-      <c r="C9" s="80" t="inlineStr">
+      <c r="C9" s="76" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D9" s="80" t="inlineStr">
+      <c r="D9" s="76" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E9" s="80" t="inlineStr">
+      <c r="E9" s="76" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F9" s="80" t="inlineStr">
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>Variety: +24% YoY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="78" t="inlineStr">
+      <c r="A10" s="74" t="inlineStr">
         <is>
           <t>Reported average creator earnings</t>
         </is>
       </c>
-      <c r="B10" s="79" t="n">
+      <c r="B10" s="75" t="n">
         <v>131</v>
       </c>
-      <c r="C10" s="80" t="inlineStr">
+      <c r="C10" s="76" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D10" s="80" t="inlineStr">
+      <c r="D10" s="76" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E10" s="80" t="inlineStr">
+      <c r="E10" s="76" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F10" s="80" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>Sci-Tech Today / ElectroIQ: after platform fees</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="78" t="inlineStr">
+      <c r="A11" s="74" t="inlineStr">
         <is>
           <t>Revenue concentration</t>
         </is>
       </c>
-      <c r="B11" s="81" t="n">
+      <c r="B11" s="77" t="n">
         <v>0.76</v>
       </c>
-      <c r="C11" s="80" t="inlineStr">
+      <c r="C11" s="76" t="inlineStr">
         <is>
           <t>share to top 0.1%</t>
         </is>
       </c>
-      <c r="D11" s="80" t="inlineStr">
+      <c r="D11" s="76" t="inlineStr">
         <is>
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="E11" s="80" t="inlineStr">
+      <c r="E11" s="76" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F11" s="80" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>ElectroIQ: power-law distribution</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="78" t="inlineStr">
+      <c r="A12" s="74" t="inlineStr">
         <is>
           <t>Creators with &gt;=1 paying member</t>
         </is>
       </c>
-      <c r="B12" s="79" t="n">
+      <c r="B12" s="75" t="n">
         <v>286287</v>
       </c>
-      <c r="C12" s="80" t="inlineStr">
+      <c r="C12" s="76" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D12" s="80" t="inlineStr">
+      <c r="D12" s="76" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E12" s="80" t="inlineStr">
+      <c r="E12" s="76" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="F12" s="80" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>Graphtreon</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="78" t="inlineStr">
+      <c r="A13" s="74" t="inlineStr">
         <is>
           <t>Active creators</t>
         </is>
       </c>
-      <c r="B13" s="79" t="n">
+      <c r="B13" s="75" t="n">
         <v>300000</v>
       </c>
-      <c r="C13" s="80" t="inlineStr">
+      <c r="C13" s="76" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D13" s="80" t="inlineStr">
+      <c r="D13" s="76" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E13" s="80" t="inlineStr">
+      <c r="E13" s="76" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F13" s="80" t="inlineStr">
+      <c r="F13" s="76" t="inlineStr">
         <is>
           <t>Jack Conte, Patreon</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="78" t="inlineStr">
+      <c r="A14" s="74" t="inlineStr">
         <is>
           <t>Active paying members</t>
         </is>
       </c>
-      <c r="B14" s="79" t="n">
+      <c r="B14" s="75" t="n">
         <v>10000000</v>
       </c>
-      <c r="C14" s="80" t="inlineStr">
+      <c r="C14" s="76" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D14" s="80" t="inlineStr">
+      <c r="D14" s="76" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E14" s="80" t="inlineStr">
+      <c r="E14" s="76" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F14" s="80" t="inlineStr">
+      <c r="F14" s="76" t="inlineStr">
         <is>
           <t>Patreon / Backlinko</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="78" t="inlineStr">
+      <c r="A15" s="74" t="inlineStr">
         <is>
           <t>Paid to creators annually</t>
         </is>
       </c>
-      <c r="B15" s="79" t="n">
+      <c r="B15" s="75" t="n">
         <v>2000000000</v>
       </c>
-      <c r="C15" s="80" t="inlineStr">
+      <c r="C15" s="76" t="inlineStr">
         <is>
           <t>USD/year</t>
         </is>
       </c>
-      <c r="D15" s="80" t="inlineStr">
+      <c r="D15" s="76" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E15" s="80" t="inlineStr">
+      <c r="E15" s="76" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F15" s="80" t="inlineStr">
+      <c r="F15" s="76" t="inlineStr">
         <is>
           <t>Patreon / Backlinko</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="78" t="inlineStr">
+      <c r="A16" s="74" t="inlineStr">
         <is>
           <t>Average monthly support per member</t>
         </is>
       </c>
-      <c r="B16" s="81" t="n">
+      <c r="B16" s="77" t="n">
         <v>6.1</v>
       </c>
-      <c r="C16" s="80" t="inlineStr">
+      <c r="C16" s="76" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D16" s="80" t="inlineStr">
+      <c r="D16" s="76" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E16" s="80" t="inlineStr">
+      <c r="E16" s="76" t="inlineStr">
         <is>
           <t>Aug 2024</t>
         </is>
       </c>
-      <c r="F16" s="80" t="inlineStr">
+      <c r="F16" s="76" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; audit of ~1,200 creators</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="78" t="inlineStr">
+      <c r="A17" s="74" t="inlineStr">
         <is>
           <t>Typical patronage band (low)</t>
         </is>
       </c>
-      <c r="B17" s="81" t="n">
+      <c r="B17" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="C17" s="80" t="inlineStr">
+      <c r="C17" s="76" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D17" s="80" t="inlineStr">
+      <c r="D17" s="76" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E17" s="80" t="inlineStr">
+      <c r="E17" s="76" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F17" s="80" t="inlineStr">
+      <c r="F17" s="76" t="inlineStr">
         <is>
           <t>Creator-economy benchmarks</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="78" t="inlineStr">
+      <c r="A18" s="74" t="inlineStr">
         <is>
           <t>Typical patronage band (high)</t>
         </is>
       </c>
-      <c r="B18" s="81" t="n">
+      <c r="B18" s="77" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="80" t="inlineStr">
+      <c r="C18" s="76" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="D18" s="80" t="inlineStr">
+      <c r="D18" s="76" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E18" s="80" t="inlineStr">
+      <c r="E18" s="76" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F18" s="80" t="inlineStr">
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>Creator-economy benchmarks</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="78" t="inlineStr">
+      <c r="A19" s="74" t="inlineStr">
         <is>
           <t>Monthly churn (low)</t>
         </is>
       </c>
-      <c r="B19" s="81" t="n">
+      <c r="B19" s="77" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="80" t="inlineStr">
+      <c r="C19" s="76" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D19" s="80" t="inlineStr">
+      <c r="D19" s="76" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E19" s="80" t="inlineStr">
+      <c r="E19" s="76" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F19" s="80" t="inlineStr">
+      <c r="F19" s="76" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="78" t="inlineStr">
+      <c r="A20" s="74" t="inlineStr">
         <is>
           <t>Monthly churn (high)</t>
         </is>
       </c>
-      <c r="B20" s="81" t="n">
+      <c r="B20" s="77" t="n">
         <v>0.15</v>
       </c>
-      <c r="C20" s="80" t="inlineStr">
+      <c r="C20" s="76" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D20" s="80" t="inlineStr">
+      <c r="D20" s="76" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E20" s="80" t="inlineStr">
+      <c r="E20" s="76" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F20" s="80" t="inlineStr">
+      <c r="F20" s="76" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="78" t="inlineStr">
+      <c r="A21" s="74" t="inlineStr">
         <is>
           <t>Annual-plan churn multiplier</t>
         </is>
       </c>
-      <c r="B21" s="81" t="n">
+      <c r="B21" s="77" t="n">
         <v>0.333</v>
       </c>
-      <c r="C21" s="80" t="inlineStr">
+      <c r="C21" s="76" t="inlineStr">
         <is>
           <t>x monthly churn</t>
         </is>
       </c>
-      <c r="D21" s="80" t="inlineStr">
+      <c r="D21" s="76" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E21" s="80" t="inlineStr">
+      <c r="E21" s="76" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F21" s="80" t="inlineStr">
+      <c r="F21" s="76" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report: annual patrons churn at 1/3 the rate</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="78" t="inlineStr">
+      <c r="A22" s="74" t="inlineStr">
         <is>
           <t>Creators with &gt;2,000 patrons</t>
         </is>
       </c>
-      <c r="B22" s="81" t="n">
+      <c r="B22" s="77" t="n">
         <v>0.003</v>
       </c>
-      <c r="C22" s="80" t="inlineStr">
+      <c r="C22" s="76" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D22" s="80" t="inlineStr">
+      <c r="D22" s="76" t="inlineStr">
         <is>
           <t>Patreon</t>
         </is>
       </c>
-      <c r="E22" s="80" t="inlineStr">
+      <c r="E22" s="76" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F22" s="80" t="inlineStr">
+      <c r="F22" s="76" t="inlineStr">
         <is>
           <t>Graphtreon: power-law distribution</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="78" t="inlineStr">
+      <c r="A23" s="74" t="inlineStr">
         <is>
           <t>Division I athletes in network</t>
         </is>
       </c>
-      <c r="B23" s="79" t="n">
+      <c r="B23" s="75" t="n">
         <v>45000</v>
       </c>
-      <c r="C23" s="80" t="inlineStr">
+      <c r="C23" s="76" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D23" s="80" t="inlineStr">
+      <c r="D23" s="76" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E23" s="80" t="inlineStr">
+      <c r="E23" s="76" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F23" s="80" t="inlineStr">
+      <c r="F23" s="76" t="inlineStr">
         <is>
           <t>Publicis Groupe press release, 19 Aug 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="78" t="inlineStr">
+      <c r="A24" s="74" t="inlineStr">
         <is>
           <t>Power Four universities</t>
         </is>
       </c>
-      <c r="B24" s="79" t="n">
+      <c r="B24" s="75" t="n">
         <v>68</v>
       </c>
-      <c r="C24" s="80" t="inlineStr">
+      <c r="C24" s="76" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D24" s="80" t="inlineStr">
+      <c r="D24" s="76" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E24" s="80" t="inlineStr">
+      <c r="E24" s="76" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F24" s="80" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>Publicis Groupe press release</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="78" t="inlineStr">
+      <c r="A25" s="74" t="inlineStr">
         <is>
           <t>Claimed speed-to-market gain</t>
         </is>
       </c>
-      <c r="B25" s="81" t="n">
+      <c r="B25" s="77" t="n">
         <v>0.6</v>
       </c>
-      <c r="C25" s="80" t="inlineStr">
+      <c r="C25" s="76" t="inlineStr">
         <is>
           <t>share faster</t>
         </is>
       </c>
-      <c r="D25" s="80" t="inlineStr">
+      <c r="D25" s="76" t="inlineStr">
         <is>
           <t>TEKTA</t>
         </is>
       </c>
-      <c r="E25" s="80" t="inlineStr">
+      <c r="E25" s="76" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
       </c>
-      <c r="F25" s="80" t="inlineStr">
+      <c r="F25" s="76" t="inlineStr">
         <is>
           <t>Publicis: stated 50-70% vs a traditional agency process</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="82" t="inlineStr">
+      <c r="A27" s="78" t="inlineStr">
         <is>
           <t>TAKE RATES - what each platform costs a creator</t>
         </is>
@@ -9482,16 +6902,16 @@
           <t>OnlyFans</t>
         </is>
       </c>
-      <c r="B29" s="83" t="n">
+      <c r="B29" s="79" t="n">
         <v>0.2</v>
       </c>
-      <c r="C29" s="84" t="n">
+      <c r="C29" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="84" t="n">
+      <c r="D29" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="85" t="inlineStr">
+      <c r="F29" s="81" t="inlineStr">
         <is>
           <t>Derived: 1.41bn / 7.22bn = 19.5% (filed accounts)</t>
         </is>
@@ -9503,16 +6923,16 @@
           <t>Fansly</t>
         </is>
       </c>
-      <c r="B30" s="83" t="n">
+      <c r="B30" s="79" t="n">
         <v>0.2</v>
       </c>
-      <c r="C30" s="84" t="n">
+      <c r="C30" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="84" t="n">
+      <c r="D30" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="85" t="inlineStr">
+      <c r="F30" s="81" t="inlineStr">
         <is>
           <t>Not published in terms; widely reported</t>
         </is>
@@ -9524,16 +6944,16 @@
           <t>Fanfix</t>
         </is>
       </c>
-      <c r="B31" s="83" t="n">
+      <c r="B31" s="79" t="n">
         <v>0.2</v>
       </c>
-      <c r="C31" s="84" t="n">
+      <c r="C31" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="84" t="n">
+      <c r="D31" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="85" t="inlineStr">
+      <c r="F31" s="81" t="inlineStr">
         <is>
           <t>Not published in terms; widely reported</t>
         </is>
@@ -9545,16 +6965,16 @@
           <t>Patreon</t>
         </is>
       </c>
-      <c r="B32" s="83" t="n">
+      <c r="B32" s="79" t="n">
         <v>0.1</v>
       </c>
-      <c r="C32" s="84" t="n">
+      <c r="C32" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="84" t="n">
+      <c r="D32" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="85" t="inlineStr">
+      <c r="F32" s="81" t="inlineStr">
         <is>
           <t>Published: 10% all-in, processing included</t>
         </is>
@@ -9566,16 +6986,16 @@
           <t>Passes</t>
         </is>
       </c>
-      <c r="B33" s="83" t="n">
+      <c r="B33" s="79" t="n">
         <v>0.1</v>
       </c>
-      <c r="C33" s="84" t="n">
+      <c r="C33" s="80" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="84" t="n">
+      <c r="D33" s="80" t="n">
         <v>29</v>
       </c>
-      <c r="F33" s="85" t="inlineStr">
+      <c r="F33" s="81" t="inlineStr">
         <is>
           <t>Sacra; Passes rebrand release Apr 2026</t>
         </is>
@@ -9587,23 +7007,23 @@
           <t>Stride (proposed)</t>
         </is>
       </c>
-      <c r="B34" s="83" t="n">
+      <c r="B34" s="79" t="n">
         <v>0.15</v>
       </c>
-      <c r="C34" s="84" t="n">
+      <c r="C34" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="84" t="n">
+      <c r="D34" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="85" t="inlineStr">
+      <c r="F34" s="81" t="inlineStr">
         <is>
           <t>Our decision, see MarketModel</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="82" t="inlineStr">
+      <c r="A36" s="78" t="inlineStr">
         <is>
           <t>INTERMEDIARIES the athlete already pays</t>
         </is>
@@ -9615,13 +7035,13 @@
           <t>Sports agent: endorsement</t>
         </is>
       </c>
-      <c r="B37" s="83" t="n">
+      <c r="B37" s="79" t="n">
         <v>0.1</v>
       </c>
-      <c r="C37" s="83" t="n">
+      <c r="C37" s="79" t="n">
         <v>0.2</v>
       </c>
-      <c r="F37" s="85" t="inlineStr">
+      <c r="F37" s="81" t="inlineStr">
         <is>
           <t>Unregulated; widely reported, no primary source</t>
         </is>
@@ -9633,13 +7053,13 @@
           <t>Sports agent: playing contract</t>
         </is>
       </c>
-      <c r="B38" s="83" t="n">
+      <c r="B38" s="79" t="n">
         <v>0.02</v>
       </c>
-      <c r="C38" s="83" t="n">
+      <c r="C38" s="79" t="n">
         <v>0.05</v>
       </c>
-      <c r="F38" s="85" t="inlineStr">
+      <c r="F38" s="81" t="inlineStr">
         <is>
           <t>NBPA reg. 4.B (Sept 2025); FIFA FFAR art. 15</t>
         </is>
@@ -9651,20 +7071,20 @@
           <t>OnlyFans management agency</t>
         </is>
       </c>
-      <c r="B39" s="83" t="n">
+      <c r="B39" s="79" t="n">
         <v>0.2</v>
       </c>
-      <c r="C39" s="83" t="n">
+      <c r="C39" s="79" t="n">
         <v>0.5</v>
       </c>
-      <c r="F39" s="85" t="inlineStr">
+      <c r="F39" s="81" t="inlineStr">
         <is>
           <t>Aruna Talent rate guide 2026, on top of the 20%</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="82" t="inlineStr">
+      <c r="A41" s="78" t="inlineStr">
         <is>
           <t>SPONSORSHIP MARKET - top down, for context not for sizing</t>
         </is>
@@ -9678,39 +7098,39 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="77" t="inlineStr">
+      <c r="A43" s="73" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B43" s="77" t="inlineStr">
+      <c r="B43" s="73" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C43" s="77" t="inlineStr">
+      <c r="C43" s="73" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D43" s="77" t="inlineStr">
+      <c r="D43" s="73" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="E43" s="77" t="inlineStr">
+      <c r="E43" s="73" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F43" s="77" t="inlineStr">
+      <c r="F43" s="73" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="78" t="inlineStr">
+      <c r="A44" s="74" t="inlineStr">
         <is>
           <t>Total sponsorship market</t>
         </is>
@@ -9718,29 +7138,29 @@
       <c r="B44" s="36" t="n">
         <v>34450000000</v>
       </c>
-      <c r="C44" s="80" t="inlineStr">
+      <c r="C44" s="76" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D44" s="80" t="inlineStr">
+      <c r="D44" s="76" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="E44" s="80" t="inlineStr">
+      <c r="E44" s="76" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F44" s="80" t="inlineStr">
+      <c r="F44" s="76" t="inlineStr">
         <is>
           <t>European Sponsorship Association, analysis by Nielsen Sports, 12 Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="78" t="inlineStr">
+      <c r="A45" s="74" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
@@ -9748,29 +7168,29 @@
       <c r="B45" s="36" t="n">
         <v>24790000000</v>
       </c>
-      <c r="C45" s="80" t="inlineStr">
+      <c r="C45" s="76" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D45" s="80" t="inlineStr">
+      <c r="D45" s="76" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="E45" s="80" t="inlineStr">
+      <c r="E45" s="76" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F45" s="80" t="inlineStr">
+      <c r="F45" s="76" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: 72% of the total, +5.9% YoY</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="78" t="inlineStr">
+      <c r="A46" s="74" t="inlineStr">
         <is>
           <t>Non-sport sponsorship</t>
         </is>
@@ -9778,29 +7198,29 @@
       <c r="B46" s="36" t="n">
         <v>9660000000</v>
       </c>
-      <c r="C46" s="80" t="inlineStr">
+      <c r="C46" s="76" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D46" s="80" t="inlineStr">
+      <c r="D46" s="76" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="E46" s="80" t="inlineStr">
+      <c r="E46" s="76" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F46" s="80" t="inlineStr">
+      <c r="F46" s="76" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +1.8% YoY</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="78" t="inlineStr">
+      <c r="A47" s="74" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
@@ -9808,29 +7228,29 @@
       <c r="B47" s="36" t="n">
         <v>2180000000</v>
       </c>
-      <c r="C47" s="80" t="inlineStr">
+      <c r="C47" s="76" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D47" s="80" t="inlineStr">
+      <c r="D47" s="76" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="E47" s="80" t="inlineStr">
+      <c r="E47" s="76" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F47" s="80" t="inlineStr">
+      <c r="F47" s="76" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +14%, the fastest growing major European market</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="78" t="inlineStr">
+      <c r="A48" s="74" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
@@ -9838,29 +7258,29 @@
       <c r="B48" s="36" t="n">
         <v>6260000000</v>
       </c>
-      <c r="C48" s="80" t="inlineStr">
+      <c r="C48" s="76" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D48" s="80" t="inlineStr">
+      <c r="D48" s="76" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E48" s="80" t="inlineStr">
+      <c r="E48" s="76" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F48" s="80" t="inlineStr">
+      <c r="F48" s="76" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: the largest European market</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="78" t="inlineStr">
+      <c r="A49" s="74" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
@@ -9868,29 +7288,29 @@
       <c r="B49" s="36" t="n">
         <v>6150000000</v>
       </c>
-      <c r="C49" s="80" t="inlineStr">
+      <c r="C49" s="76" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D49" s="80" t="inlineStr">
+      <c r="D49" s="76" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E49" s="80" t="inlineStr">
+      <c r="E49" s="76" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F49" s="80" t="inlineStr">
+      <c r="F49" s="76" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +10.5%</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="78" t="inlineStr">
+      <c r="A50" s="74" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
@@ -9898,29 +7318,29 @@
       <c r="B50" s="36" t="n">
         <v>2010000000</v>
       </c>
-      <c r="C50" s="80" t="inlineStr">
+      <c r="C50" s="76" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D50" s="80" t="inlineStr">
+      <c r="D50" s="76" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="E50" s="80" t="inlineStr">
+      <c r="E50" s="76" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F50" s="80" t="inlineStr">
+      <c r="F50" s="76" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +5%</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="78" t="inlineStr">
+      <c r="A51" s="74" t="inlineStr">
         <is>
           <t>Sport sponsorship market</t>
         </is>
@@ -9928,29 +7348,29 @@
       <c r="B51" s="36" t="n">
         <v>1850000000</v>
       </c>
-      <c r="C51" s="80" t="inlineStr">
+      <c r="C51" s="76" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D51" s="80" t="inlineStr">
+      <c r="D51" s="76" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="E51" s="80" t="inlineStr">
+      <c r="E51" s="76" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F51" s="80" t="inlineStr">
+      <c r="F51" s="76" t="inlineStr">
         <is>
           <t>ESA / Nielsen Sports: +10.3%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="82" t="inlineStr">
+      <c r="A53" s="78" t="inlineStr">
         <is>
           <t>European SPORT sponsorship by year, EUR bn</t>
         </is>
@@ -9977,22 +7397,22 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="86" t="n">
+      <c r="A55" s="82" t="n">
         <v>20.26</v>
       </c>
-      <c r="B55" s="86" t="n">
+      <c r="B55" s="82" t="n">
         <v>19.8</v>
       </c>
-      <c r="C55" s="86" t="n">
+      <c r="C55" s="82" t="n">
         <v>20.69</v>
       </c>
-      <c r="D55" s="86" t="n">
+      <c r="D55" s="82" t="n">
         <v>21.98</v>
       </c>
-      <c r="E55" s="86" t="n">
+      <c r="E55" s="82" t="n">
         <v>23.41</v>
       </c>
-      <c r="F55" s="86" t="n">
+      <c r="F55" s="82" t="n">
         <v>24.79</v>
       </c>
     </row>
@@ -10004,136 +7424,136 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="82" t="inlineStr">
+      <c r="A58" s="78" t="inlineStr">
         <is>
           <t>FAN DEMAND - published surveys bearing on the fan thesis</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="77" t="inlineStr">
+      <c r="A59" s="73" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B59" s="77" t="inlineStr">
+      <c r="B59" s="73" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C59" s="77" t="inlineStr">
+      <c r="C59" s="73" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D59" s="77" t="inlineStr">
+      <c r="D59" s="73" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="E59" s="77" t="inlineStr">
+      <c r="E59" s="73" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F59" s="77" t="inlineStr">
+      <c r="F59" s="73" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="78" t="inlineStr">
+      <c r="A60" s="74" t="inlineStr">
         <is>
           <t>Weekly minutes, fan-generated content</t>
         </is>
       </c>
-      <c r="B60" s="79" t="n">
+      <c r="B60" s="75" t="n">
         <v>115</v>
       </c>
-      <c r="C60" s="80" t="inlineStr">
+      <c r="C60" s="76" t="inlineStr">
         <is>
           <t>minutes/week</t>
         </is>
       </c>
-      <c r="D60" s="80" t="inlineStr">
+      <c r="D60" s="76" t="inlineStr">
         <is>
           <t>FR DE IT ES UK US</t>
         </is>
       </c>
-      <c r="E60" s="80" t="inlineStr">
+      <c r="E60" s="76" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F60" s="80" t="inlineStr">
+      <c r="F60" s="76" t="inlineStr">
         <is>
           <t>Altman Solon / IRIS Sport, 6,000 respondents who watch sports video monthly</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="78" t="inlineStr">
+      <c r="A61" s="74" t="inlineStr">
         <is>
           <t>Weekly minutes, highlights and clips</t>
         </is>
       </c>
-      <c r="B61" s="79" t="n">
+      <c r="B61" s="75" t="n">
         <v>115</v>
       </c>
-      <c r="C61" s="80" t="inlineStr">
+      <c r="C61" s="76" t="inlineStr">
         <is>
           <t>minutes/week</t>
         </is>
       </c>
-      <c r="D61" s="80" t="inlineStr">
+      <c r="D61" s="76" t="inlineStr">
         <is>
           <t>FR DE IT ES UK US</t>
         </is>
       </c>
-      <c r="E61" s="80" t="inlineStr">
+      <c r="E61" s="76" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F61" s="80" t="inlineStr">
+      <c r="F61" s="76" t="inlineStr">
         <is>
           <t>Altman Solon / IRIS Sport</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="78" t="inlineStr">
+      <c r="A62" s="74" t="inlineStr">
         <is>
           <t>Weekly minutes, live games and events</t>
         </is>
       </c>
-      <c r="B62" s="79" t="n">
+      <c r="B62" s="75" t="n">
         <v>245</v>
       </c>
-      <c r="C62" s="80" t="inlineStr">
+      <c r="C62" s="76" t="inlineStr">
         <is>
           <t>minutes/week</t>
         </is>
       </c>
-      <c r="D62" s="80" t="inlineStr">
+      <c r="D62" s="76" t="inlineStr">
         <is>
           <t>FR DE IT ES UK US</t>
         </is>
       </c>
-      <c r="E62" s="80" t="inlineStr">
+      <c r="E62" s="76" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F62" s="80" t="inlineStr">
+      <c r="F62" s="76" t="inlineStr">
         <is>
           <t>Altman Solon / IRIS Sport</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="78" t="inlineStr">
+      <c r="A63" s="74" t="inlineStr">
         <is>
           <t>YouTube share of fan-generated viewing</t>
         </is>
@@ -10141,29 +7561,29 @@
       <c r="B63" s="40" t="n">
         <v>0.35</v>
       </c>
-      <c r="C63" s="80" t="inlineStr">
+      <c r="C63" s="76" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D63" s="80" t="inlineStr">
+      <c r="D63" s="76" t="inlineStr">
         <is>
           <t>FR DE IT ES UK US</t>
         </is>
       </c>
-      <c r="E63" s="80" t="inlineStr">
+      <c r="E63" s="76" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F63" s="80" t="inlineStr">
+      <c r="F63" s="76" t="inlineStr">
         <is>
           <t>Altman Solon / IRIS Sport: 40 of 115 minutes, more than linear TV or streaming</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="78" t="inlineStr">
+      <c r="A64" s="74" t="inlineStr">
         <is>
           <t>Subscribers watching MORE sport after subscribing</t>
         </is>
@@ -10171,29 +7591,29 @@
       <c r="B64" s="40" t="n">
         <v>0.7</v>
       </c>
-      <c r="C64" s="80" t="inlineStr">
+      <c r="C64" s="76" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D64" s="80" t="inlineStr">
+      <c r="D64" s="76" t="inlineStr">
         <is>
           <t>Worldwide</t>
         </is>
       </c>
-      <c r="E64" s="80" t="inlineStr">
+      <c r="E64" s="76" t="inlineStr">
         <is>
           <t>Nov 2022</t>
         </is>
       </c>
-      <c r="F64" s="80" t="inlineStr">
+      <c r="F64" s="76" t="inlineStr">
         <is>
           <t>YouGov / Strive, 19,000 respondents: 38% much more + 32% somewhat more</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="78" t="inlineStr">
+      <c r="A65" s="74" t="inlineStr">
         <is>
           <t>Subscribers watching LESS sport after subscribing</t>
         </is>
@@ -10201,29 +7621,29 @@
       <c r="B65" s="40" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C65" s="80" t="inlineStr">
+      <c r="C65" s="76" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="D65" s="80" t="inlineStr">
+      <c r="D65" s="76" t="inlineStr">
         <is>
           <t>Worldwide</t>
         </is>
       </c>
-      <c r="E65" s="80" t="inlineStr">
+      <c r="E65" s="76" t="inlineStr">
         <is>
           <t>Nov 2022</t>
         </is>
       </c>
-      <c r="F65" s="80" t="inlineStr">
+      <c r="F65" s="76" t="inlineStr">
         <is>
           <t>YouGov / Strive: 3% much less + 4% somewhat less</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="82" t="inlineStr">
+      <c r="A67" s="78" t="inlineStr">
         <is>
           <t>SPONSORSHIP MARKETPLACES - the direct competitor set</t>
         </is>
@@ -10237,39 +7657,39 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="77" t="inlineStr">
+      <c r="A69" s="73" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B69" s="77" t="inlineStr">
+      <c r="B69" s="73" t="inlineStr">
         <is>
           <t>Founded</t>
         </is>
       </c>
-      <c r="C69" s="77" t="inlineStr">
+      <c r="C69" s="73" t="inlineStr">
         <is>
           <t>Employees (as of)</t>
         </is>
       </c>
-      <c r="D69" s="77" t="inlineStr">
+      <c r="D69" s="73" t="inlineStr">
         <is>
           <t>Total raised</t>
         </is>
       </c>
-      <c r="E69" s="77" t="inlineStr">
+      <c r="E69" s="73" t="inlineStr">
         <is>
           <t>Largest round pre-money</t>
         </is>
       </c>
-      <c r="F69" s="77" t="inlineStr">
+      <c r="F69" s="73" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="87" t="inlineStr">
+      <c r="A70" s="83" t="inlineStr">
         <is>
           <t>Sponsoo (Germany)</t>
         </is>
@@ -10277,7 +7697,7 @@
       <c r="B70" s="41" t="n">
         <v>2014</v>
       </c>
-      <c r="C70" s="79" t="n">
+      <c r="C70" s="75" t="n">
         <v>13</v>
       </c>
       <c r="D70" s="36" t="n">
@@ -10286,14 +7706,14 @@
       <c r="E70" s="36" t="n">
         <v>15900000</v>
       </c>
-      <c r="F70" s="80" t="inlineStr">
+      <c r="F70" s="76" t="inlineStr">
         <is>
           <t>Headcount as of 14 Nov 2025. Privately held, venture backed. Series A 28 Jan 2021; pre-money is a PitchBook ESTIMATE</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="87" t="inlineStr">
+      <c r="A71" s="83" t="inlineStr">
         <is>
           <t>OpenSponsorship (United States)</t>
         </is>
@@ -10301,21 +7721,21 @@
       <c r="B71" s="41" t="n">
         <v>2014</v>
       </c>
-      <c r="C71" s="79" t="n">
+      <c r="C71" s="75" t="n">
         <v>23</v>
       </c>
       <c r="D71" s="36" t="n">
         <v>5400000</v>
       </c>
       <c r="E71" s="36" t="n"/>
-      <c r="F71" s="80" t="inlineStr">
+      <c r="F71" s="76" t="inlineStr">
         <is>
           <t>Headcount as of 9 Mar 2026. Privately held, venture backed. Last priced round not disclosed</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="87" t="inlineStr">
+      <c r="A72" s="83" t="inlineStr">
         <is>
           <t>SponsorUnited (United States)</t>
         </is>
@@ -10323,7 +7743,7 @@
       <c r="B72" s="41" t="n">
         <v>2016</v>
       </c>
-      <c r="C72" s="79" t="n">
+      <c r="C72" s="75" t="n">
         <v>355</v>
       </c>
       <c r="D72" s="36" t="n">
@@ -10332,14 +7752,14 @@
       <c r="E72" s="36" t="n">
         <v>89380000</v>
       </c>
-      <c r="F72" s="80" t="inlineStr">
+      <c r="F72" s="76" t="inlineStr">
         <is>
           <t>Headcount as of 28 May 2026. Privately held, venture backed. Series A 21 Nov 2022</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="87" t="inlineStr">
+      <c r="A73" s="83" t="inlineStr">
         <is>
           <t>Hookit (United States)</t>
         </is>
@@ -10347,7 +7767,7 @@
       <c r="B73" s="41" t="n">
         <v>2001</v>
       </c>
-      <c r="C73" s="79" t="n">
+      <c r="C73" s="75" t="n">
         <v>47</v>
       </c>
       <c r="D73" s="36" t="n">
@@ -10356,41 +7776,41 @@
       <c r="E73" s="36" t="n">
         <v>38400000</v>
       </c>
-      <c r="F73" s="80" t="inlineStr">
+      <c r="F73" s="76" t="inlineStr">
         <is>
           <t>Headcount as of 8 Feb 2022. Acquired, operating subsidiary. Series C2 24 Feb 2020; pre-money is a PitchBook ESTIMATE</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="87" t="inlineStr">
+      <c r="A74" s="83" t="inlineStr">
         <is>
           <t>Stride (this plan, at Y10)</t>
         </is>
       </c>
-      <c r="B74" s="88" t="n">
+      <c r="B74" s="84" t="n">
         <v>2026</v>
       </c>
-      <c r="C74" s="89">
+      <c r="C74" s="85">
         <f>Assumptions!L66</f>
         <v/>
       </c>
-      <c r="D74" s="90">
+      <c r="D74" s="86">
         <f>SUM(Funding!C4:L4)</f>
         <v/>
       </c>
-      <c r="E74" s="90">
+      <c r="E74" s="86">
         <f>Funding!H5</f>
         <v/>
       </c>
-      <c r="F74" s="80" t="inlineStr">
+      <c r="F74" s="76" t="inlineStr">
         <is>
           <t>Deliberately sized near Sponsoo. Only EUR 400k of the total is capital the plan depends on; the growth round is optional</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="82" t="inlineStr">
+      <c r="A76" s="78" t="inlineStr">
         <is>
           <t>REVENUE PER EMPLOYEE - what the plan is tested against</t>
         </is>
@@ -10422,10 +7842,10 @@
           <t>Median private B2B SaaS, all stages</t>
         </is>
       </c>
-      <c r="B78" s="91" t="n">
+      <c r="B78" s="87" t="n">
         <v>135000</v>
       </c>
-      <c r="F78" s="92" t="inlineStr">
+      <c r="F78" s="88" t="inlineStr">
         <is>
           <t>SaaS Capital 2025 survey of ~1,000 private B2B SaaS companies</t>
         </is>
@@ -10437,10 +7857,10 @@
           <t>Top quartile private B2B SaaS</t>
         </is>
       </c>
-      <c r="B79" s="91" t="n">
+      <c r="B79" s="87" t="n">
         <v>215000</v>
       </c>
-      <c r="F79" s="92" t="inlineStr">
+      <c r="F79" s="88" t="inlineStr">
         <is>
           <t>SaaS Capital 2025 survey, 75th percentile</t>
         </is>
@@ -10452,10 +7872,10 @@
           <t>Efficient public SaaS at scale</t>
         </is>
       </c>
-      <c r="B80" s="91" t="n">
+      <c r="B80" s="87" t="n">
         <v>300000</v>
       </c>
-      <c r="F80" s="92" t="inlineStr">
+      <c r="F80" s="88" t="inlineStr">
         <is>
           <t>Public SaaS medians, widely reported range EUR 250-350k</t>
         </is>
@@ -10467,11 +7887,11 @@
           <t>Stride (this plan, Y7)</t>
         </is>
       </c>
-      <c r="B81" s="93">
+      <c r="B81" s="89">
         <f>KPIs!I14</f>
         <v/>
       </c>
-      <c r="F81" s="92" t="inlineStr">
+      <c r="F81" s="88" t="inlineStr">
         <is>
           <t>Above the top quartile. Defended in section 3.2.2: the fan side is self-serve and moderation is a variable cost, not headcount</t>
         </is>
@@ -10483,11 +7903,11 @@
           <t>Multiple of the top quartile</t>
         </is>
       </c>
-      <c r="B82" s="94">
+      <c r="B82" s="90">
         <f>B81/B79</f>
         <v/>
       </c>
-      <c r="F82" s="85" t="inlineStr">
+      <c r="F82" s="81" t="inlineStr">
         <is>
           <t>The plan's second most aggressive assumption after fan churn</t>
         </is>
@@ -10501,300 +7921,300 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="95" t="inlineStr">
+      <c r="A86" s="91" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 filed accounts (Fenix International Ltd)</t>
         </is>
       </c>
-      <c r="B86" s="96" t="inlineStr">
+      <c r="B86" s="92" t="inlineStr">
         <is>
           <t>https://find-and-update.company-information.service.gov.uk/company/10354575/filing-history</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="95" t="inlineStr">
+      <c r="A87" s="91" t="inlineStr">
         <is>
           <t>OnlyFans FY2024 as reported</t>
         </is>
       </c>
-      <c r="B87" s="96" t="inlineStr">
+      <c r="B87" s="92" t="inlineStr">
         <is>
           <t>https://variety.com/2025/digital/news/onlyfans-fiscal-2024-revenue-earnings-1236495750/</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="95" t="inlineStr">
+      <c r="A88" s="91" t="inlineStr">
         <is>
           <t>Patreon published take rate</t>
         </is>
       </c>
-      <c r="B88" s="96" t="inlineStr">
+      <c r="B88" s="92" t="inlineStr">
         <is>
           <t>https://www.patreon.com/pricing</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="95" t="inlineStr">
+      <c r="A89" s="91" t="inlineStr">
         <is>
           <t>Patreon creators</t>
         </is>
       </c>
-      <c r="B89" s="96" t="inlineStr">
+      <c r="B89" s="92" t="inlineStr">
         <is>
           <t>https://backlinko.com/patreon-users</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="95" t="inlineStr">
+      <c r="A90" s="91" t="inlineStr">
         <is>
           <t>Passes economics</t>
         </is>
       </c>
-      <c r="B90" s="96" t="inlineStr">
+      <c r="B90" s="92" t="inlineStr">
         <is>
           <t>https://sacra.com/c/passes/</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="95" t="inlineStr">
+      <c r="A91" s="91" t="inlineStr">
         <is>
           <t>Fanfix creator terms (states no take rate)</t>
         </is>
       </c>
-      <c r="B91" s="96" t="inlineStr">
+      <c r="B91" s="92" t="inlineStr">
         <is>
           <t>https://auth.fanfix.io/creator-terms-of-use</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="95" t="inlineStr">
+      <c r="A92" s="91" t="inlineStr">
         <is>
           <t>Agency commissions</t>
         </is>
       </c>
-      <c r="B92" s="96" t="inlineStr">
+      <c r="B92" s="92" t="inlineStr">
         <is>
           <t>https://arunatalent.com/blog/onlyfans-agency-commission-rates/</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="95" t="inlineStr">
+      <c r="A93" s="91" t="inlineStr">
         <is>
           <t>NBPA agent fee cap (amended Sept 2025)</t>
         </is>
       </c>
-      <c r="B93" s="96" t="inlineStr">
+      <c r="B93" s="92" t="inlineStr">
         <is>
           <t>https://imgix.cosmicjs.com/cd844850-97c7-11f0-91fa-d9e1671c2776-NBPA-REGULATIONS-GOVERNING-PLAYER-AGENTS-09-2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="95" t="inlineStr">
+      <c r="A94" s="91" t="inlineStr">
         <is>
           <t>FIFA Football Agent Regulations art. 15</t>
         </is>
       </c>
-      <c r="B94" s="96" t="inlineStr">
+      <c r="B94" s="92" t="inlineStr">
         <is>
           <t>https://digitalhub.fifa.com/m/1e7b741fa0fae779/original/FIFA-Football-Agent-Regulations.pdf</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="95" t="inlineStr">
+      <c r="A95" s="91" t="inlineStr">
         <is>
           <t>CJEU upholds the FIFA fee cap (16 Jul 2026)</t>
         </is>
       </c>
-      <c r="B95" s="96" t="inlineStr">
+      <c r="B95" s="92" t="inlineStr">
         <is>
           <t>https://inside.fifa.com/news/welcomes-court-of-justice-european-union-decision-football-agent-regulations</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="95" t="inlineStr">
+      <c r="A96" s="91" t="inlineStr">
         <is>
           <t>Eurobarometer 525</t>
         </is>
       </c>
-      <c r="B96" s="96" t="inlineStr">
+      <c r="B96" s="92" t="inlineStr">
         <is>
           <t>https://europa.eu/eurobarometer/surveys/detail/2668</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="95" t="inlineStr">
+      <c r="A97" s="91" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="B97" s="96" t="inlineStr">
+      <c r="B97" s="92" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/2025/12/online-the-fip-world-padel-report-2025-a-comprehensive-analysis-of-a-sport-in-constant-growth/</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="95" t="inlineStr">
+      <c r="A98" s="91" t="inlineStr">
         <is>
           <t>Stripe EU pricing</t>
         </is>
       </c>
-      <c r="B98" s="96" t="inlineStr">
+      <c r="B98" s="92" t="inlineStr">
         <is>
           <t>https://stripe.com/es/pricing</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="95" t="inlineStr">
+      <c r="A99" s="91" t="inlineStr">
         <is>
           <t>TEKTA launch</t>
         </is>
       </c>
-      <c r="B99" s="96" t="inlineStr">
+      <c r="B99" s="92" t="inlineStr">
         <is>
           <t>https://www.publicisgroupe.com/en/news/press-releases/publicis-sports-and-travis-kelce-s-tekta-join-forces-to-reimagine-the-future-of-nil-marketing</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="95" t="inlineStr">
+      <c r="A100" s="91" t="inlineStr">
         <is>
           <t>Stripe Connect age</t>
         </is>
       </c>
-      <c r="B100" s="96" t="inlineStr">
+      <c r="B100" s="92" t="inlineStr">
         <is>
           <t>https://support.stripe.com/questions/age-requirement-to-create-a-stripe-account</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="95" t="inlineStr">
+      <c r="A101" s="91" t="inlineStr">
         <is>
           <t>PitchBook: Sponsoo GmbH</t>
         </is>
       </c>
-      <c r="B101" s="96" t="inlineStr">
+      <c r="B101" s="92" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/103066-39</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="95" t="inlineStr">
+      <c r="A102" s="91" t="inlineStr">
         <is>
           <t>PitchBook: OpenSponsorship</t>
         </is>
       </c>
-      <c r="B102" s="96" t="inlineStr">
+      <c r="B102" s="92" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/113575-96</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="95" t="inlineStr">
+      <c r="A103" s="91" t="inlineStr">
         <is>
           <t>PitchBook: SponsorUnited</t>
         </is>
       </c>
-      <c r="B103" s="96" t="inlineStr">
+      <c r="B103" s="92" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/169635-43</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="95" t="inlineStr">
+      <c r="A104" s="91" t="inlineStr">
         <is>
           <t>PitchBook: Hookit</t>
         </is>
       </c>
-      <c r="B104" s="96" t="inlineStr">
+      <c r="B104" s="92" t="inlineStr">
         <is>
           <t>https://pitchbook.com/profiles/company/55307-17</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="95" t="inlineStr">
+      <c r="A105" s="91" t="inlineStr">
         <is>
           <t>ESA European sponsorship market 2025</t>
         </is>
       </c>
-      <c r="B105" s="96" t="inlineStr">
+      <c r="B105" s="92" t="inlineStr">
         <is>
           <t>https://sponsorship.org/european-sponsorship-market-reaches-e34-45bn-in-2025-as-growth-continues-across-all-sectors/</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="95" t="inlineStr">
+      <c r="A106" s="91" t="inlineStr">
         <is>
           <t>SportsPro on the ESA 2026 market overview</t>
         </is>
       </c>
-      <c r="B106" s="96" t="inlineStr">
+      <c r="B106" s="92" t="inlineStr">
         <is>
           <t>https://www.sportspro.com/news/sponsorship-marketing/sports-sponsorship-european-market-valuation-esa-march-2026/</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="95" t="inlineStr">
+      <c r="A107" s="91" t="inlineStr">
         <is>
           <t>European sport sponsorship 2019-2025 (ESA via Statista)</t>
         </is>
       </c>
-      <c r="B107" s="96" t="inlineStr">
+      <c r="B107" s="92" t="inlineStr">
         <is>
           <t>https://www.statista.com/statistics/1430225/sports-sponsorship-market-size-europe/</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="95" t="inlineStr">
+      <c r="A108" s="91" t="inlineStr">
         <is>
           <t>Sports content formats by channel (Altman Solon / IRIS Sport)</t>
         </is>
       </c>
-      <c r="B108" s="96" t="inlineStr">
+      <c r="B108" s="92" t="inlineStr">
         <is>
           <t>https://www.statista.com/statistics/1660170/time-spent-weekly-watching-sports-formats-by-channel/</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="95" t="inlineStr">
+      <c r="A109" s="91" t="inlineStr">
         <is>
           <t>Impact of subscriptions on sports consumption (YouGov / Strive)</t>
         </is>
       </c>
-      <c r="B109" s="96" t="inlineStr">
+      <c r="B109" s="92" t="inlineStr">
         <is>
           <t>https://www.statista.com/statistics/1413187/impact-subscriptions-sports-content-consumption/</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="95" t="inlineStr">
+      <c r="A110" s="91" t="inlineStr">
         <is>
           <t>SaaS Capital revenue per employee benchmarks</t>
         </is>
       </c>
-      <c r="B110" s="96" t="inlineStr">
+      <c r="B110" s="92" t="inlineStr">
         <is>
           <t>https://www.saas-capital.com/blog-posts/revenue-per-employee-benchmarks-for-private-saas-companies/</t>
         </is>
@@ -10862,7 +8282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10892,36 +8312,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="93" t="inlineStr">
         <is>
           <t>Input: change me</t>
         </is>
       </c>
-      <c r="D3" s="98" t="n"/>
-      <c r="E3" s="99" t="inlineStr">
+      <c r="D3" s="94" t="n"/>
+      <c r="E3" s="95" t="inlineStr">
         <is>
           <t>Sourced fact</t>
         </is>
       </c>
-      <c r="F3" s="98" t="n"/>
-      <c r="G3" s="100" t="inlineStr">
+      <c r="F3" s="94" t="n"/>
+      <c r="G3" s="96" t="inlineStr">
         <is>
           <t>Formula (this sheet)</t>
         </is>
       </c>
-      <c r="H3" s="98" t="n"/>
-      <c r="I3" s="101" t="inlineStr">
+      <c r="H3" s="94" t="n"/>
+      <c r="I3" s="97" t="inlineStr">
         <is>
           <t>Dependent value</t>
         </is>
       </c>
-      <c r="J3" s="98" t="n"/>
-      <c r="K3" s="102" t="inlineStr">
+      <c r="J3" s="94" t="n"/>
+      <c r="K3" s="98" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="L3" s="98" t="n"/>
+      <c r="L3" s="94" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -10943,7 +8363,7 @@
         <f>Comparables!B14</f>
         <v/>
       </c>
-      <c r="D6" s="92" t="inlineStr">
+      <c r="D6" s="88" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -10959,7 +8379,7 @@
         <f>Comparables!B12</f>
         <v/>
       </c>
-      <c r="D7" s="92" t="inlineStr">
+      <c r="D7" s="88" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -10975,7 +8395,7 @@
         <f>B6/B7</f>
         <v/>
       </c>
-      <c r="D8" s="92" t="inlineStr">
+      <c r="D8" s="88" t="inlineStr">
         <is>
           <t>The single most useful benchmark we found: it is measured, not modelled.</t>
         </is>
@@ -10991,7 +8411,7 @@
         <f>Comparables!B9/Comparables!B8</f>
         <v/>
       </c>
-      <c r="D9" s="92" t="inlineStr">
+      <c r="D9" s="88" t="inlineStr">
         <is>
           <t>Fan ACCOUNTS, not paying fans - most follow free. Shown as an upper bound only.</t>
         </is>
@@ -11006,7 +8426,7 @@
       <c r="B10" s="26" t="n">
         <v>1.06</v>
       </c>
-      <c r="D10" s="92" t="inlineStr">
+      <c r="D10" s="88" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +6% on the Patreon benchmark. Sport audiences are smaller but convert better, because the fan usually does the sport themselves.</t>
         </is>
@@ -11021,7 +8441,7 @@
       <c r="B11" s="26" t="n">
         <v>1.37</v>
       </c>
-      <c r="D11" s="92" t="inlineStr">
+      <c r="D11" s="88" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: +37%. Much larger followings, much weaker conversion - more paying fans in absolute terms even though a smaller share converts.</t>
         </is>
@@ -11033,11 +8453,11 @@
           <t>→ Niche fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B12" s="103">
+      <c r="B12" s="99">
         <f>B8*B10</f>
         <v/>
       </c>
-      <c r="D12" s="92" t="inlineStr"/>
+      <c r="D12" s="88" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -11045,11 +8465,11 @@
           <t>→ Popular fans per athlete, mature</t>
         </is>
       </c>
-      <c r="B13" s="103">
+      <c r="B13" s="99">
         <f>B8*B11</f>
         <v/>
       </c>
-      <c r="D13" s="92" t="inlineStr"/>
+      <c r="D13" s="88" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -11070,7 +8490,7 @@
       <c r="B15" s="22" t="n">
         <v>4.99</v>
       </c>
-      <c r="D15" s="92" t="inlineStr"/>
+      <c r="D15" s="88" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -11081,7 +8501,7 @@
       <c r="B16" s="22" t="n">
         <v>9.99</v>
       </c>
-      <c r="D16" s="92" t="inlineStr"/>
+      <c r="D16" s="88" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
@@ -11092,7 +8512,7 @@
       <c r="B17" s="22" t="n">
         <v>24.99</v>
       </c>
-      <c r="D17" s="92" t="inlineStr"/>
+      <c r="D17" s="88" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -11103,7 +8523,7 @@
       <c r="B18" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="D18" s="92" t="inlineStr">
+      <c r="D18" s="88" t="inlineStr">
         <is>
           <t>Assumed distribution; replace with the real tier mix after P1.</t>
         </is>
@@ -11118,7 +8538,7 @@
       <c r="B19" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="D19" s="92" t="inlineStr"/>
+      <c r="D19" s="88" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -11129,7 +8549,7 @@
       <c r="B20" s="18" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="92" t="inlineStr"/>
+      <c r="D20" s="88" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -11141,7 +8561,7 @@
         <f>B18+B19+B20</f>
         <v/>
       </c>
-      <c r="D21" s="92" t="inlineStr"/>
+      <c r="D21" s="88" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -11149,11 +8569,11 @@
           <t>→ Weighted ARPU per month</t>
         </is>
       </c>
-      <c r="B22" s="104">
+      <c r="B22" s="100">
         <f>B15*B18+B16*B19+B17*B20</f>
         <v/>
       </c>
-      <c r="D22" s="92" t="inlineStr">
+      <c r="D22" s="88" t="inlineStr">
         <is>
           <t>Cross-check: Patreon reports $6.10 average support and a $8-12 typical band. Landing inside that band from an independent tier build is a good sign.</t>
         </is>
@@ -11169,7 +8589,7 @@
         <f>Comparables!B16</f>
         <v/>
       </c>
-      <c r="D23" s="92" t="inlineStr">
+      <c r="D23" s="88" t="inlineStr">
         <is>
           <t>Published average - below our figure because Patreon's long tail includes many $1-3 tiers. Our EUR 9.49 sits inside their $8-12 typical band.</t>
         </is>
@@ -11184,7 +8604,7 @@
       <c r="B24" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="92" t="inlineStr">
+      <c r="D24" s="88" t="inlineStr">
         <is>
           <t>Niche fans buy knowledge and sit at the tier mix above.</t>
         </is>
@@ -11199,7 +8619,7 @@
       <c r="B25" s="26" t="n">
         <v>0.87</v>
       </c>
-      <c r="D25" s="92" t="inlineStr">
+      <c r="D25" s="88" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: -13%. Popular-sport fans skew to the cheapest tier.</t>
         </is>
@@ -11211,11 +8631,11 @@
           <t>→ Niche ARPU, mature</t>
         </is>
       </c>
-      <c r="B26" s="104">
+      <c r="B26" s="100">
         <f>B22*B24</f>
         <v/>
       </c>
-      <c r="D26" s="92" t="inlineStr"/>
+      <c r="D26" s="88" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -11223,11 +8643,11 @@
           <t>→ Popular ARPU, mature</t>
         </is>
       </c>
-      <c r="B27" s="104">
+      <c r="B27" s="100">
         <f>B22*B25</f>
         <v/>
       </c>
-      <c r="D27" s="92" t="inlineStr"/>
+      <c r="D27" s="88" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -11249,7 +8669,7 @@
         <f>Comparables!B19</f>
         <v/>
       </c>
-      <c r="D29" s="92" t="inlineStr"/>
+      <c r="D29" s="88" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
@@ -11261,7 +8681,7 @@
         <f>Comparables!B20</f>
         <v/>
       </c>
-      <c r="D30" s="92" t="inlineStr"/>
+      <c r="D30" s="88" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
@@ -11273,7 +8693,7 @@
         <f>(B29+B30)/2</f>
         <v/>
       </c>
-      <c r="D31" s="92" t="inlineStr"/>
+      <c r="D31" s="88" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -11285,7 +8705,7 @@
         <f>Comparables!B21</f>
         <v/>
       </c>
-      <c r="D32" s="92" t="inlineStr">
+      <c r="D32" s="88" t="inlineStr">
         <is>
           <t>Patreon: annual patrons churn at one third the monthly rate.</t>
         </is>
@@ -11300,7 +8720,7 @@
       <c r="B33" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="D33" s="92" t="inlineStr">
+      <c r="D33" s="88" t="inlineStr">
         <is>
           <t>Our target for the season pass. This is the one lever that improves churn without changing the product.</t>
         </is>
@@ -11316,7 +8736,7 @@
         <f>B31*(1-B33)+B31*B32*B33</f>
         <v/>
       </c>
-      <c r="D34" s="92" t="inlineStr">
+      <c r="D34" s="88" t="inlineStr">
         <is>
           <t>What a Patreon-like platform would see with our annual mix.</t>
         </is>
@@ -11331,7 +8751,7 @@
       <c r="B35" s="26" t="n">
         <v>0.55</v>
       </c>
-      <c r="D35" s="92" t="inlineStr">
+      <c r="D35" s="88" t="inlineStr">
         <is>
           <t>OUR CLAIM, UNTESTED, AND THE MOST OPTIMISTIC JUDGEMENT IN THE MODEL: this says niche fans churn 45% SLOWER than the Patreon benchmark, because training content is habitual and competitive seasons create renewal moments. Nothing yet proves it. If it is wrong and we are merely at benchmark, Y10 revenue falls by roughly EUR 7M.</t>
         </is>
@@ -11346,7 +8766,7 @@
       <c r="B36" s="26" t="n">
         <v>0.85</v>
       </c>
-      <c r="D36" s="92" t="inlineStr">
+      <c r="D36" s="88" t="inlineStr">
         <is>
           <t>OUR JUDGEMENT: 15% better than benchmark. Impulse follows after a result, with many free substitutes - but still a sport fan rather than a general creator audience.</t>
         </is>
@@ -11358,11 +8778,11 @@
           <t>→ Niche churn, mature</t>
         </is>
       </c>
-      <c r="B37" s="105">
+      <c r="B37" s="101">
         <f>B34*B35</f>
         <v/>
       </c>
-      <c r="D37" s="92" t="inlineStr"/>
+      <c r="D37" s="88" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -11370,11 +8790,11 @@
           <t>→ Popular churn, mature</t>
         </is>
       </c>
-      <c r="B38" s="105">
+      <c r="B38" s="101">
         <f>B34*B36</f>
         <v/>
       </c>
-      <c r="D38" s="92" t="inlineStr"/>
+      <c r="D38" s="88" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
@@ -11396,7 +8816,7 @@
         <f>Comparables!B7/Comparables!B8/12</f>
         <v/>
       </c>
-      <c r="D40" s="92" t="inlineStr">
+      <c r="D40" s="88" t="inlineStr">
         <is>
           <t>Includes dormant accounts, so this is a floor.</t>
         </is>
@@ -11412,7 +8832,7 @@
         <f>Comparables!B15/Comparables!B12/12</f>
         <v/>
       </c>
-      <c r="D41" s="92" t="inlineStr">
+      <c r="D41" s="88" t="inlineStr">
         <is>
           <t>Denominator is creators WITH members, so this is a ceiling.</t>
         </is>
@@ -11424,11 +8844,11 @@
           <t>Stride: modelled niche athlete, mature</t>
         </is>
       </c>
-      <c r="B42" s="104">
+      <c r="B42" s="100">
         <f>B12*B22*(1-Assumptions!$C$40)</f>
         <v/>
       </c>
-      <c r="D42" s="92" t="inlineStr">
+      <c r="D42" s="88" t="inlineStr">
         <is>
           <t>Ours sits between the two, which is where a plausible figure should sit.</t>
         </is>
@@ -11444,7 +8864,7 @@
         <f>Comparables!B11</f>
         <v/>
       </c>
-      <c r="D43" s="92" t="inlineStr">
+      <c r="D43" s="88" t="inlineStr">
         <is>
           <t>THE CAVEAT ON EVERY AVERAGE ABOVE: earnings follow a power law. Totals are unaffected, but the median athlete earns far less than the mean. Do not pitch the mean to an athlete.</t>
         </is>
@@ -11469,7 +8889,7 @@
       <c r="B45" s="26" t="n">
         <v>0.92</v>
       </c>
-      <c r="D45" s="92" t="inlineStr">
+      <c r="D45" s="88" t="inlineStr">
         <is>
           <t>Comparables are published in USD; this model is in EUR. Applied to the per-transaction and monthly creator fees below.</t>
         </is>
@@ -11484,7 +8904,7 @@
       <c r="B46" s="22" t="n">
         <v>300</v>
       </c>
-      <c r="D46" s="92" t="inlineStr">
+      <c r="D46" s="88" t="inlineStr">
         <is>
           <t>Change this to see who is cheapest at any revenue level.</t>
         </is>
@@ -11500,7 +8920,7 @@
         <f>B46*(1-Comparables!B29)-B46/Assumptions!$C$54*Comparables!C29*B45-Comparables!D29*B45</f>
         <v/>
       </c>
-      <c r="D47" s="92" t="inlineStr">
+      <c r="D47" s="88" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -11516,7 +8936,7 @@
         <f>B46*(1-Comparables!B32)-B46/Assumptions!$C$54*Comparables!C32*B45-Comparables!D32*B45</f>
         <v/>
       </c>
-      <c r="D48" s="92" t="inlineStr">
+      <c r="D48" s="88" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -11532,7 +8952,7 @@
         <f>B46*(1-Comparables!B33)-B46/Assumptions!$C$54*Comparables!C33*B45-Comparables!D33*B45</f>
         <v/>
       </c>
-      <c r="D49" s="92" t="inlineStr">
+      <c r="D49" s="88" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -11548,7 +8968,7 @@
         <f>B46*(1-Comparables!B34)-B46/Assumptions!$C$54*Comparables!C34*B45-Comparables!D34*B45</f>
         <v/>
       </c>
-      <c r="D50" s="92" t="inlineStr">
+      <c r="D50" s="88" t="inlineStr">
         <is>
           <t>Headline take, plus per-transaction and monthly creator fees where they exist.</t>
         </is>
@@ -11564,7 +8984,7 @@
         <f>Comparables!D33*B45/((Comparables!B34-Comparables!B33)-Comparables!C33*B45/Assumptions!$C$54)</f>
         <v/>
       </c>
-      <c r="D51" s="92" t="inlineStr">
+      <c r="D51" s="88" t="inlineStr">
         <is>
           <t>Below this, our flat 15% pays the athlete more than Passes' 10% plus fees. Our modelled athlete earns far less than this, so the long tail is on our side of the line.</t>
         </is>
@@ -11586,10 +9006,10 @@
           <t>Population, 34 countries in scope</t>
         </is>
       </c>
-      <c r="B53" s="106" t="n">
+      <c r="B53" s="102" t="n">
         <v>2726.2</v>
       </c>
-      <c r="D53" s="92" t="inlineStr">
+      <c r="D53" s="88" t="inlineStr">
         <is>
           <t>Millions. Eurostat / national statistics offices.</t>
         </is>
@@ -11601,10 +9021,10 @@
           <t>Population, Spain</t>
         </is>
       </c>
-      <c r="B54" s="106" t="n">
+      <c r="B54" s="102" t="n">
         <v>48.6</v>
       </c>
-      <c r="D54" s="92" t="inlineStr">
+      <c r="D54" s="88" t="inlineStr">
         <is>
           <t>Millions.</t>
         </is>
@@ -11619,7 +9039,7 @@
       <c r="B55" s="18" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D55" s="92" t="inlineStr">
+      <c r="D55" s="88" t="inlineStr">
         <is>
           <t>Eurobarometer 525 - Spain sits near the EU average of 55% who exercise at all.</t>
         </is>
@@ -11634,7 +9054,7 @@
       <c r="B56" s="18" t="n">
         <v>0.02</v>
       </c>
-      <c r="D56" s="92" t="inlineStr">
+      <c r="D56" s="88" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: competes, posts publicly, has a following worth sponsoring.</t>
         </is>
@@ -11649,7 +9069,7 @@
       <c r="B57" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="D57" s="92" t="inlineStr">
+      <c r="D57" s="88" t="inlineStr">
         <is>
           <t>OUR ESTIMATE: would monetise if the tooling existed.</t>
         </is>
@@ -11661,11 +9081,11 @@
           <t>→ Addressable athletes, Spain</t>
         </is>
       </c>
-      <c r="B58" s="107">
+      <c r="B58" s="103">
         <f>B54*1000000*B55*B56*B57</f>
         <v/>
       </c>
-      <c r="D58" s="92" t="inlineStr"/>
+      <c r="D58" s="88" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -11673,11 +9093,11 @@
           <t>→ Addressable athletes, all 34 countries</t>
         </is>
       </c>
-      <c r="B59" s="107">
+      <c r="B59" s="103">
         <f>B53*1000000*0.5*B56*B57</f>
         <v/>
       </c>
-      <c r="D59" s="92" t="inlineStr">
+      <c r="D59" s="88" t="inlineStr">
         <is>
           <t>Using a 50% blended participation rate across the 34 countries.</t>
         </is>
@@ -11693,7 +9113,7 @@
         <f>Assumptions!$L$5</f>
         <v/>
       </c>
-      <c r="D60" s="92" t="inlineStr"/>
+      <c r="D60" s="88" t="inlineStr"/>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -11701,11 +9121,11 @@
           <t>→ Y10 penetration of Spain SAM</t>
         </is>
       </c>
-      <c r="B61" s="105">
+      <c r="B61" s="101">
         <f>Assumptions!$L$5/B58</f>
         <v/>
       </c>
-      <c r="D61" s="92" t="inlineStr"/>
+      <c r="D61" s="88" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -11713,11 +9133,11 @@
           <t>→ Y10 penetration of full TAM</t>
         </is>
       </c>
-      <c r="B62" s="105">
+      <c r="B62" s="101">
         <f>Assumptions!$L$5/B59</f>
         <v/>
       </c>
-      <c r="D62" s="92" t="inlineStr">
+      <c r="D62" s="88" t="inlineStr">
         <is>
           <t>If this reads as implausibly high, the athlete trajectory is too aggressive - that is exactly what this block exists to reveal.</t>
         </is>
@@ -11735,7 +9155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11768,37 +9188,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="108" t="inlineStr">
+      <c r="A4" s="104" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B4" s="108" t="inlineStr">
+      <c r="B4" s="104" t="inlineStr">
         <is>
           <t>Model value</t>
         </is>
       </c>
-      <c r="C4" s="108" t="inlineStr">
+      <c r="C4" s="104" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D4" s="108" t="inlineStr">
+      <c r="D4" s="104" t="inlineStr">
         <is>
           <t>Benchmark / comparable</t>
         </is>
       </c>
-      <c r="E4" s="108" t="inlineStr">
+      <c r="E4" s="104" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F4" s="108" t="inlineStr">
+      <c r="F4" s="104" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="G4" s="108" t="inlineStr">
+      <c r="G4" s="104" t="inlineStr">
         <is>
           <t>What would replace the estimate</t>
         </is>
@@ -11818,7 +9238,7 @@
       <c r="G5" s="14" t="n"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="87" t="inlineStr">
+      <c r="A6" s="83" t="inlineStr">
         <is>
           <t>Take rate on fan revenue</t>
         </is>
@@ -11827,34 +9247,34 @@
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="C6" s="109" t="inlineStr">
+      <c r="C6" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D6" s="110" t="inlineStr">
+      <c r="D6" s="106" t="inlineStr">
         <is>
           <t>Passes charges 10% but adds $0.30/txn and a $29/month creator fee; OnlyFans, Fansly and Fanfix are all 20%; Patreon 8-12%. A flat 15% with no monthly fee pays an athlete more than Passes for anyone under EUR 1,380/month of fan revenue.</t>
         </is>
       </c>
-      <c r="E6" s="110" t="inlineStr">
+      <c r="E6" s="106" t="inlineStr">
         <is>
           <t>Sacra company profile (Passes); Passes rebrand release, Apr 2026; MEXC platform comparison 2026</t>
         </is>
       </c>
-      <c r="F6" s="111" t="inlineStr">
+      <c r="F6" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G6" s="110" t="inlineStr">
+      <c r="G6" s="106" t="inlineStr">
         <is>
           <t>Nothing. This is a pricing decision and the comparables are public.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="87" t="inlineStr">
+      <c r="A7" s="83" t="inlineStr">
         <is>
           <t>Sponsorship commission, Scout Pro</t>
         </is>
@@ -11863,34 +9283,34 @@
         <f>Assumptions!$C$42</f>
         <v/>
       </c>
-      <c r="C7" s="109" t="inlineStr">
+      <c r="C7" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D7" s="110" t="inlineStr">
+      <c r="D7" s="106" t="inlineStr">
         <is>
           <t>7% against a 10% base. A sponsor paying EUR 2,988 a year for the tooling is already paying for the relationship, and charging them the full headline rate on every deal as well is charging twice for it. Below the 10-20% an agent takes, which is the point: the sponsor who commits most pays least on each deal.</t>
         </is>
       </c>
-      <c r="E7" s="110" t="inlineStr">
+      <c r="E7" s="106" t="inlineStr">
         <is>
           <t>Priced against the agent range; the discount itself is a pricing decision</t>
         </is>
       </c>
-      <c r="F7" s="111" t="inlineStr">
+      <c r="F7" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G7" s="110" t="inlineStr">
+      <c r="G7" s="106" t="inlineStr">
         <is>
           <t>Nothing to improve. This is a decision, not a measurement.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="87" t="inlineStr">
+      <c r="A8" s="83" t="inlineStr">
         <is>
           <t>Sponsorship commission, Scout Agency</t>
         </is>
@@ -11899,34 +9319,34 @@
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
-      <c r="C8" s="109" t="inlineStr">
+      <c r="C8" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D8" s="110" t="inlineStr">
+      <c r="D8" s="106" t="inlineStr">
         <is>
           <t>5%, which is half the low end of what an agent charges and a quarter of the high end. The most committed tier pays EUR 11,988 a year, so the deal rate can fall furthest here.</t>
         </is>
       </c>
-      <c r="E8" s="110" t="inlineStr">
+      <c r="E8" s="106" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys, 10-20%</t>
         </is>
       </c>
-      <c r="F8" s="111" t="inlineStr">
+      <c r="F8" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G8" s="110" t="inlineStr">
+      <c r="G8" s="106" t="inlineStr">
         <is>
           <t>Nothing to improve. This is a decision, not a measurement.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="87" t="inlineStr">
+      <c r="A9" s="83" t="inlineStr">
         <is>
           <t>Subscriber share of deal volume</t>
         </is>
@@ -11935,34 +9355,34 @@
         <f>Assumptions!$C$44</f>
         <v/>
       </c>
-      <c r="C9" s="112" t="inlineStr">
+      <c r="C9" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D9" s="110" t="inlineStr">
+      <c r="D9" s="106" t="inlineStr">
         <is>
           <t>Subscribers are assumed to run 2.0x the deal volume of the average sponsor, which with a paid rate of 10-20% puts them at 20-40% of GMV. This is the ONLY estimate in the tiering and it is the one that sets the blended rate, which falls from 9.60% in Y1 to 8.56% by Y10. Deliberately conservative: Scout Pro buys five campaigns against the free tier's one, so 2.0x is well below what the campaign allowance alone would imply. Higher multiples lower the blend further.</t>
         </is>
       </c>
-      <c r="E9" s="110" t="inlineStr">
+      <c r="E9" s="106" t="inlineStr">
         <is>
           <t>None. No tier-level deal volume exists yet, because no tier exists yet</t>
         </is>
       </c>
-      <c r="F9" s="113" t="inlineStr">
+      <c r="F9" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G9" s="110" t="inlineStr">
+      <c r="G9" s="106" t="inlineStr">
         <is>
           <t>The first year of billing settles it exactly.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="87" t="inlineStr">
+      <c r="A10" s="83" t="inlineStr">
         <is>
           <t>Take rate on sponsorship</t>
         </is>
@@ -11971,101 +9391,101 @@
         <f>Assumptions!$C$41</f>
         <v/>
       </c>
-      <c r="C10" s="109" t="inlineStr">
+      <c r="C10" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D10" s="110" t="inlineStr">
+      <c r="D10" s="106" t="inlineStr">
         <is>
           <t>Sports agents take 10-20% of an endorsement and 4-10% of a playing contract. On OnlyFans, management agencies take a further 20-50% on top of the platform's 20%.</t>
         </is>
       </c>
-      <c r="E10" s="110" t="inlineStr">
+      <c r="E10" s="106" t="inlineStr">
         <is>
           <t>Oreate and Sapling agent-commission surveys; Aruna Talent agency rate guide 2026</t>
         </is>
       </c>
-      <c r="F10" s="111" t="inlineStr">
+      <c r="F10" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G10" s="110" t="inlineStr">
+      <c r="G10" s="106" t="inlineStr">
         <is>
           <t>Observed deal data once the marketplace is running.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="87" t="inlineStr">
+      <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Suggested tiers 4.99 / 9.99 / 24.99</t>
         </is>
       </c>
-      <c r="B11" s="114" t="inlineStr">
+      <c r="B11" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C11" s="109" t="inlineStr">
+      <c r="C11" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D11" s="110" t="inlineStr">
+      <c r="D11" s="106" t="inlineStr">
         <is>
           <t>Patreon's typical patronage is quoted at $8-12/month, so the EUR 9.99 anchor sits inside the observed band. EUR 4.99 retains only 54% of our take after payment fees, against 71% at EUR 9.99: which is why the floor matters more than the take rate.</t>
         </is>
       </c>
-      <c r="E11" s="110" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report; independent audits of ~1,200 creators</t>
         </is>
       </c>
-      <c r="F11" s="115" t="inlineStr">
+      <c r="F11" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G11" s="110" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>Our own tier mix after P1.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="87" t="inlineStr">
+      <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Season pass / annual billing</t>
         </is>
       </c>
-      <c r="B12" s="114" t="inlineStr">
+      <c r="B12" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C12" s="116" t="inlineStr">
+      <c r="C12" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D12" s="110" t="inlineStr">
+      <c r="D12" s="106" t="inlineStr">
         <is>
           <t>Patreon reports that annual patrons churn at ONE THIRD the rate of monthly patrons. This is the single strongest piece of evidence in the plan for pushing annual billing.</t>
         </is>
       </c>
-      <c r="E12" s="110" t="inlineStr">
+      <c r="E12" s="106" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F12" s="111" t="inlineStr">
+      <c r="F12" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G12" s="110" t="inlineStr">
+      <c r="G12" s="106" t="inlineStr">
         <is>
           <t>Already strong. Confirm on our own cohorts.</t>
         </is>
@@ -12085,7 +9505,7 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="87" t="inlineStr">
+      <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Fan ARPU per month</t>
         </is>
@@ -12094,34 +9514,34 @@
         <f>Assumptions!$C$12</f>
         <v/>
       </c>
-      <c r="C14" s="109" t="inlineStr">
+      <c r="C14" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D14" s="110" t="inlineStr">
+      <c r="D14" s="106" t="inlineStr">
         <is>
           <t>Patreon's average monthly support rose from $5.40 to $6.10 during 2024, with typical patronage quoted at $8-12. Our EUR 8.00-9.50 sits in the upper-middle of that range.</t>
         </is>
       </c>
-      <c r="E14" s="110" t="inlineStr">
+      <c r="E14" s="106" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report</t>
         </is>
       </c>
-      <c r="F14" s="115" t="inlineStr">
+      <c r="F14" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G14" s="110" t="inlineStr">
+      <c r="G14" s="106" t="inlineStr">
         <is>
           <t>Actual ARPU by tier and sport after P1.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="87" t="inlineStr">
+      <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Fan churn per month</t>
         </is>
@@ -12130,34 +9550,34 @@
         <f>Assumptions!$C$13</f>
         <v/>
       </c>
-      <c r="C15" s="112" t="inlineStr">
+      <c r="C15" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D15" s="110" t="inlineStr">
+      <c r="D15" s="106" t="inlineStr">
         <is>
           <t>OPTIMISTIC AGAINST BENCHMARK. Patreon runs 10-15% monthly. We assume 6-9% (niche) and 9-13% (popular), arguing that training content is habitual and that competitive seasons create natural renewal moments. That argument is currently untested.</t>
         </is>
       </c>
-      <c r="E15" s="110" t="inlineStr">
+      <c r="E15" s="106" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (10-15%/month)</t>
         </is>
       </c>
-      <c r="F15" s="113" t="inlineStr">
+      <c r="F15" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G15" s="110" t="inlineStr">
+      <c r="G15" s="106" t="inlineStr">
         <is>
           <t>THE most important number to measure in P1. Three months of real cohorts settles it. Until then the conservative case should be treated as the plan.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="87" t="inlineStr">
+      <c r="A16" s="83" t="inlineStr">
         <is>
           <t>Paying fans per monetising athlete</t>
         </is>
@@ -12166,34 +9586,34 @@
         <f>Assumptions!$C$11</f>
         <v/>
       </c>
-      <c r="C16" s="117" t="inlineStr">
+      <c r="C16" s="113" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D16" s="110" t="inlineStr">
+      <c r="D16" s="106" t="inlineStr">
         <is>
           <t>20 rising to 48 over ten years. Cross-check: Patreon creators average $350/month and our modelled niche athlete at maturity earns about EUR 313/month, closely aligned, which is reassuring for an assumption built bottom-up rather than from a comparable.</t>
         </is>
       </c>
-      <c r="E16" s="110" t="inlineStr">
+      <c r="E16" s="106" t="inlineStr">
         <is>
           <t>Patreon 2024 Transparency Report (creator average $350/month)</t>
         </is>
       </c>
-      <c r="F16" s="115" t="inlineStr">
+      <c r="F16" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G16" s="110" t="inlineStr">
+      <c r="G16" s="106" t="inlineStr">
         <is>
           <t>Observed fans per athlete, banded by follower count.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="87" t="inlineStr">
+      <c r="A17" s="83" t="inlineStr">
         <is>
           <t>Share of athletes who monetise</t>
         </is>
@@ -12202,64 +9622,64 @@
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="C17" s="112" t="inlineStr">
+      <c r="C17" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D17" s="110" t="inlineStr">
+      <c r="D17" s="106" t="inlineStr">
         <is>
           <t>28% rising to 50% for niche sports. No direct comparable exists: neither Patreon nor OnlyFans publishes activation rates for creators who sign up but never charge.</t>
         </is>
       </c>
-      <c r="E17" s="110" t="inlineStr">
+      <c r="E17" s="106" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F17" s="113" t="inlineStr">
+      <c r="F17" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G17" s="110" t="inlineStr">
+      <c r="G17" s="106" t="inlineStr">
         <is>
           <t>Our own activation funnel, available from P1 onward.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="87" t="inlineStr">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t>Fan acquisition capacity</t>
         </is>
       </c>
-      <c r="B18" s="114" t="inlineStr">
+      <c r="B18" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C18" s="112" t="inlineStr">
+      <c r="C18" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D18" s="110" t="inlineStr">
+      <c r="D18" s="106" t="inlineStr">
         <is>
           <t>An athlete can recruit 30-69 new paying fans a year depending on segment. This ceiling is what makes churn bite in the model: without it, higher churn perversely RAISED revenue, because the year-end target was reachable at any churn rate.</t>
         </is>
       </c>
-      <c r="E18" s="110" t="inlineStr">
+      <c r="E18" s="106" t="inlineStr">
         <is>
           <t>None: introduced to fix a modelling flaw found by stress testing</t>
         </is>
       </c>
-      <c r="F18" s="113" t="inlineStr">
+      <c r="F18" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G18" s="110" t="inlineStr">
+      <c r="G18" s="106" t="inlineStr">
         <is>
           <t>Observed gross adds per athlete per year.</t>
         </is>
@@ -12279,7 +9699,7 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="87" t="inlineStr">
+      <c r="A20" s="83" t="inlineStr">
         <is>
           <t>PSP percentage fee</t>
         </is>
@@ -12288,34 +9708,34 @@
         <f>Assumptions!$C$50</f>
         <v/>
       </c>
-      <c r="C20" s="116" t="inlineStr">
+      <c r="C20" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D20" s="110" t="inlineStr">
+      <c r="D20" s="106" t="inlineStr">
         <is>
           <t>Stripe for a Spanish entity: 1.5% + EUR 0.25 on EEA domestic cards, 2.5% on UK cards, 3.25% on non-EEA. 1.9% is the blend for a mostly-European fan base. CORRECTION: an earlier version of this model used the US headline of 2.9% and overstated the largest cost line in the business by about a third.</t>
         </is>
       </c>
-      <c r="E20" s="110" t="inlineStr">
+      <c r="E20" s="106" t="inlineStr">
         <is>
           <t>Stripe published EU/EEA pricing, 2026</t>
         </is>
       </c>
-      <c r="F20" s="111" t="inlineStr">
+      <c r="F20" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G20" s="110" t="inlineStr">
+      <c r="G20" s="106" t="inlineStr">
         <is>
           <t>Interchange-plus terms become negotiable above roughly EUR 5M processed.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="87" t="inlineStr">
+      <c r="A21" s="83" t="inlineStr">
         <is>
           <t>PSP fixed fee per transaction</t>
         </is>
@@ -12324,34 +9744,34 @@
         <f>Assumptions!$C$51</f>
         <v/>
       </c>
-      <c r="C21" s="116" t="inlineStr">
+      <c r="C21" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D21" s="110" t="inlineStr">
+      <c r="D21" s="106" t="inlineStr">
         <is>
           <t>EUR 0.25 per transaction. On a EUR 4.99 tier that single fee is a third of our take, which is why the tier floor and annual billing move more margin than the take rate does.</t>
         </is>
       </c>
-      <c r="E21" s="110" t="inlineStr">
+      <c r="E21" s="106" t="inlineStr">
         <is>
           <t>Stripe published pricing, 2026</t>
         </is>
       </c>
-      <c r="F21" s="111" t="inlineStr">
+      <c r="F21" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G21" s="110" t="inlineStr">
+      <c r="G21" s="106" t="inlineStr">
         <is>
           <t>Volume renegotiation; annual billing turns twelve fees into one.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="87" t="inlineStr">
+      <c r="A22" s="83" t="inlineStr">
         <is>
           <t>Payout fees</t>
         </is>
@@ -12360,27 +9780,27 @@
         <f>Assumptions!$C$52</f>
         <v/>
       </c>
-      <c r="C22" s="116" t="inlineStr">
+      <c r="C22" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D22" s="110" t="inlineStr">
+      <c r="D22" s="106" t="inlineStr">
         <is>
           <t>Stripe Connect Express: roughly 0.25% + EUR 0.25 per payout, plus a monthly active-account fee that is not modelled as a separate line.</t>
         </is>
       </c>
-      <c r="E22" s="110" t="inlineStr">
+      <c r="E22" s="106" t="inlineStr">
         <is>
           <t>Stripe Connect pricing, 2026</t>
         </is>
       </c>
-      <c r="F22" s="115" t="inlineStr">
+      <c r="F22" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G22" s="110" t="inlineStr">
+      <c r="G22" s="106" t="inlineStr">
         <is>
           <t>Actual payout frequency once athletes are onboarded.</t>
         </is>
@@ -12400,118 +9820,118 @@
       <c r="G23" s="14" t="n"/>
     </row>
     <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="87" t="inlineStr">
+      <c r="A24" s="83" t="inlineStr">
         <is>
           <t>Sport participation by country</t>
         </is>
       </c>
-      <c r="B24" s="114" t="inlineStr">
+      <c r="B24" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C24" s="112" t="inlineStr">
+      <c r="C24" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D24" s="110" t="inlineStr">
+      <c r="D24" s="106" t="inlineStr">
         <is>
           <t>Eurobarometer 525, share who NEVER exercise: Finland 8%, Sweden 12%, Denmark 20%, Poland 65%, Greece 68%, Portugal 73%, EU-27 average 45%. Six of the 34 countries in the index are measured; the other 28 are estimates placed inside that distribution.</t>
         </is>
       </c>
-      <c r="E24" s="110" t="inlineStr">
+      <c r="E24" s="106" t="inlineStr">
         <is>
           <t>Special Eurobarometer 525, Sport and Physical Activity, September 2022</t>
         </is>
       </c>
-      <c r="F24" s="115" t="inlineStr">
+      <c r="F24" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G24" s="110" t="inlineStr">
+      <c r="G24" s="106" t="inlineStr">
         <is>
           <t>Federation licence counts, published annually and free (CSD in Spain).</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="87" t="inlineStr">
+      <c r="A25" s="83" t="inlineStr">
         <is>
           <t>Padel market size</t>
         </is>
       </c>
-      <c r="B25" s="114" t="inlineStr">
+      <c r="B25" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C25" s="116" t="inlineStr">
+      <c r="C25" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D25" s="110" t="inlineStr">
+      <c r="D25" s="106" t="inlineStr">
         <is>
           <t>Spain has ~6.0M active players (12.7% of the population), 109,040 federation licences and 17,300+ courts; globally 35M+ players and 77,000+ courts. This is the clearest case for weighting a sport regionally rather than globally, padel scores 77.7 in Spain and 45.1 worldwide.</t>
         </is>
       </c>
-      <c r="E25" s="110" t="inlineStr">
+      <c r="E25" s="106" t="inlineStr">
         <is>
           <t>FIP World Padel Report 2025</t>
         </is>
       </c>
-      <c r="F25" s="111" t="inlineStr">
+      <c r="F25" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G25" s="110" t="inlineStr">
+      <c r="G25" s="106" t="inlineStr">
         <is>
           <t>Annual FIP refresh.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="87" t="inlineStr">
+      <c r="A26" s="83" t="inlineStr">
         <is>
           <t>Sports fandom by country</t>
         </is>
       </c>
-      <c r="B26" s="114" t="inlineStr">
+      <c r="B26" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C26" s="112" t="inlineStr">
+      <c r="C26" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D26" s="110" t="inlineStr">
+      <c r="D26" s="106" t="inlineStr">
         <is>
           <t>The weakest layer of the sport index, and it drives both the `demand` and `appetite` signals. Commercial audience panels (Nielsen Sports, YouGov) cost more than the entire Y1-Y2 analytics budget.</t>
         </is>
       </c>
-      <c r="E26" s="110" t="inlineStr">
+      <c r="E26" s="106" t="inlineStr">
         <is>
           <t>None: reasoned estimates only</t>
         </is>
       </c>
-      <c r="F26" s="113" t="inlineStr">
+      <c r="F26" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G26" s="110" t="inlineStr">
+      <c r="G26" s="106" t="inlineStr">
         <is>
           <t>Our own engagement data per sport per country once connectors are live. This is what makes the index self-improving rather than something anyone could copy.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="87" t="inlineStr">
+      <c r="A27" s="83" t="inlineStr">
         <is>
           <t>Athlete count trajectory</t>
         </is>
@@ -12520,27 +9940,27 @@
         <f>Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="C27" s="112" t="inlineStr">
+      <c r="C27" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D27" s="110" t="inlineStr">
+      <c r="D27" s="106" t="inlineStr">
         <is>
           <t>250 rising to 8,500 over ten years. This is the PLAN, not a benchmark: marketing spend is derived from it at segment CAC, not the other way round. Everything in the model scales off this line.</t>
         </is>
       </c>
-      <c r="E27" s="110" t="inlineStr">
+      <c r="E27" s="106" t="inlineStr">
         <is>
           <t>None: it is a target</t>
         </is>
       </c>
-      <c r="F27" s="113" t="inlineStr">
+      <c r="F27" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G27" s="110" t="inlineStr">
+      <c r="G27" s="106" t="inlineStr">
         <is>
           <t>The pre-seed gate tests it directly: 250 athletes and the first paying sponsors.</t>
         </is>
@@ -12560,7 +9980,7 @@
       <c r="G28" s="14" t="n"/>
     </row>
     <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="87" t="inlineStr">
+      <c r="A29" s="83" t="inlineStr">
         <is>
           <t>Athlete CAC</t>
         </is>
@@ -12569,34 +9989,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C29" s="112" t="inlineStr">
+      <c r="C29" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D29" s="110" t="inlineStr">
+      <c r="D29" s="106" t="inlineStr">
         <is>
           <t>EUR 16-36 for niche, EUR 40-88 for popular. The gap reflects displacing an existing agent relationship versus reaching someone with no representation at all. No published comparable exists for athlete acquisition in this segment.</t>
         </is>
       </c>
-      <c r="E29" s="110" t="inlineStr">
+      <c r="E29" s="106" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="F29" s="113" t="inlineStr">
+      <c r="F29" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G29" s="110" t="inlineStr">
+      <c r="G29" s="106" t="inlineStr">
         <is>
           <t>Measured CAC by channel from the first federation partnership.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="87" t="inlineStr">
+      <c r="A30" s="83" t="inlineStr">
         <is>
           <t>Admission rate, direct applicants</t>
         </is>
@@ -12605,34 +10025,34 @@
         <f>Assumptions!$C$98</f>
         <v/>
       </c>
-      <c r="C30" s="117" t="inlineStr">
+      <c r="C30" s="113" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D30" s="110" t="inlineStr">
-        <is>
-          <t>20% of direct applicants are admitted, 25% go to a human, 40% are refused and 15% never finish the form. Not a judgement: it is the ops-load output of scripts/admission_stress.py run over the admission policy itself, so retuning a threshold moves this figure. The sweep asserts the model and the policy stay in step and fails if they drift.</t>
-        </is>
-      </c>
-      <c r="E30" s="110" t="inlineStr">
-        <is>
-          <t>scripts/admission_stress.py, section 7, over a modelled applicant mix</t>
-        </is>
-      </c>
-      <c r="F30" s="115" t="inlineStr">
+      <c r="D30" s="106" t="inlineStr">
+        <is>
+          <t>20% of direct applicants are admitted, 25% go to a human, 40% are refused and 15% never finish the form. Not a judgement: it is what the admission policy itself produces when the stress test is run over a modelled applicant mix, so retuning a threshold moves this figure. The sweep holds the model and the policy in step.</t>
+        </is>
+      </c>
+      <c r="E30" s="106" t="inlineStr">
+        <is>
+          <t>Admission stress test, section 7, over a modelled applicant mix</t>
+        </is>
+      </c>
+      <c r="F30" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G30" s="110" t="inlineStr">
+      <c r="G30" s="106" t="inlineStr">
         <is>
           <t>Real intake data. The mix the sweep assumes is the soft part, not the arithmetic.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="87" t="inlineStr">
+      <c r="A31" s="83" t="inlineStr">
         <is>
           <t>Admission rate, club-nominated</t>
         </is>
@@ -12641,34 +10061,34 @@
         <f>Assumptions!$C$100</f>
         <v/>
       </c>
-      <c r="C31" s="112" t="inlineStr">
+      <c r="C31" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D31" s="110" t="inlineStr">
+      <c r="D31" s="106" t="inlineStr">
         <is>
           <t>45% admitted against 20% direct. A verified club's nomination confers a credibility floor of 0.75 x its own legitimacy score, which carries a completed application over the admit line that would otherwise have gone to review. It cannot carry an empty one: no club can supply someone else's date of birth, so the uplift is real but bounded.</t>
         </is>
       </c>
-      <c r="E31" s="110" t="inlineStr">
+      <c r="E31" s="106" t="inlineStr">
         <is>
           <t>None: the mechanism is built and tested, the conversion is not yet measured</t>
         </is>
       </c>
-      <c r="F31" s="113" t="inlineStr">
+      <c r="F31" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G31" s="110" t="inlineStr">
+      <c r="G31" s="106" t="inlineStr">
         <is>
           <t>The first federation partnership: nominated applicants are tagged, so this is measurable from day one of it.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="87" t="inlineStr">
+      <c r="A32" s="83" t="inlineStr">
         <is>
           <t>Athlete verification cost</t>
         </is>
@@ -12677,34 +10097,34 @@
         <f>Assumptions!$C$103</f>
         <v/>
       </c>
-      <c r="C32" s="117" t="inlineStr">
+      <c r="C32" s="113" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="D32" s="110" t="inlineStr">
+      <c r="D32" s="106" t="inlineStr">
         <is>
           <t>Four minutes per manual review, priced at the same loaded salary the People line uses, over 1,700 productive hours. Peaks at EUR 47k and 0.64 reviewer-FTE in Y10, which is the finding rather than the cost: verification is not a money problem at this scale. The reason to automate it is latency: an athlete sitting in the queue is not listed, not matchable and not earning.</t>
         </is>
       </c>
-      <c r="E32" s="110" t="inlineStr">
+      <c r="E32" s="106" t="inlineStr">
         <is>
           <t>Derived from the sweep's review volume and the model's own salary line</t>
         </is>
       </c>
-      <c r="F32" s="115" t="inlineStr">
+      <c r="F32" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G32" s="110" t="inlineStr">
+      <c r="G32" s="106" t="inlineStr">
         <is>
           <t>Timing real reviews. Four minutes is an estimate of a mechanical task.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="87" t="inlineStr">
+      <c r="A33" s="83" t="inlineStr">
         <is>
           <t>Athlete CAC vs the funnel</t>
         </is>
@@ -12713,34 +10133,34 @@
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="C33" s="112" t="inlineStr">
+      <c r="C33" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D33" s="110" t="inlineStr">
+      <c r="D33" s="106" t="inlineStr">
         <is>
           <t>Deliberately NOT multiplied by the admission funnel. Segment CAC is defined as the cost of landing one athlete ON the platform, so scaling it by 1/admission-rate would charge the same money twice. The Costs sheet carries a memo line showing what that CAC works out to per application (EUR 3.40 in Y1 rising to EUR 22), the figure to hold against what a channel actually charges per name reached.</t>
         </is>
       </c>
-      <c r="E33" s="110" t="inlineStr">
+      <c r="E33" s="106" t="inlineStr">
         <is>
           <t>None: this is a definitional choice, made explicit so it is not silently reversed</t>
         </is>
       </c>
-      <c r="F33" s="113" t="inlineStr">
+      <c r="F33" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G33" s="110" t="inlineStr">
+      <c r="G33" s="106" t="inlineStr">
         <is>
           <t>Channel-level spend against applications, which the funnel now records.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="87" t="inlineStr">
+      <c r="A34" s="83" t="inlineStr">
         <is>
           <t>Loaded salary, Spain</t>
         </is>
@@ -12749,34 +10169,34 @@
         <f>Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="C34" s="109" t="inlineStr">
+      <c r="C34" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D34" s="110" t="inlineStr">
+      <c r="D34" s="106" t="inlineStr">
         <is>
           <t>EUR 38k-76k loaded. Spanish employer social security adds roughly 31% on top of gross, so a senior engineer at ~EUR 55k gross costs ~EUR 72k, around half the London equivalent, which is a real argument for being in Spain rather than an accident of geography.</t>
         </is>
       </c>
-      <c r="E34" s="110" t="inlineStr">
+      <c r="E34" s="106" t="inlineStr">
         <is>
           <t>Spanish Seguridad Social employer contribution rates</t>
         </is>
       </c>
-      <c r="F34" s="115" t="inlineStr">
+      <c r="F34" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G34" s="110" t="inlineStr">
+      <c r="G34" s="106" t="inlineStr">
         <is>
           <t>Actual offers accepted.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="87" t="inlineStr">
+      <c r="A35" s="83" t="inlineStr">
         <is>
           <t>AWS infrastructure</t>
         </is>
@@ -12785,34 +10205,34 @@
         <f>Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="C35" s="109" t="inlineStr">
+      <c r="C35" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D35" s="110" t="inlineStr">
+      <c r="D35" s="106" t="inlineStr">
         <is>
           <t>Built up per stage from list prices: Fargate, RDS then Aurora, ElastiCache, S3, MediaConvert, CloudWatch. Reserved capacity and Savings Plans (25-40%) are deliberately excluded and treated as upside.</t>
         </is>
       </c>
-      <c r="E35" s="110" t="inlineStr">
+      <c r="E35" s="106" t="inlineStr">
         <is>
           <t>AWS published list pricing, 2026</t>
         </is>
       </c>
-      <c r="F35" s="115" t="inlineStr">
+      <c r="F35" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G35" s="110" t="inlineStr">
+      <c r="G35" s="106" t="inlineStr">
         <is>
           <t>Actual bills; commit to Savings Plans once usage is stable.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="87" t="inlineStr">
+      <c r="A36" s="83" t="inlineStr">
         <is>
           <t>Media egress</t>
         </is>
@@ -12821,34 +10241,34 @@
         <f>Assumptions!$C$60</f>
         <v/>
       </c>
-      <c r="C36" s="116" t="inlineStr">
+      <c r="C36" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D36" s="110" t="inlineStr">
+      <c r="D36" s="106" t="inlineStr">
         <is>
           <t>EUR 0.008/GB behind a zero-egress object store versus EUR 0.075/GB at CloudFront list price. At Y10 volumes that single architectural choice is worth over EUR 1M a year, the largest cost decision in the plan that is settled by engineering rather than negotiation.</t>
         </is>
       </c>
-      <c r="E36" s="110" t="inlineStr">
+      <c r="E36" s="106" t="inlineStr">
         <is>
           <t>Cloudflare R2 and Backblaze B2 pricing; AWS CloudFront list price</t>
         </is>
       </c>
-      <c r="F36" s="111" t="inlineStr">
+      <c r="F36" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G36" s="110" t="inlineStr">
+      <c r="G36" s="106" t="inlineStr">
         <is>
           <t>Nothing. Both are published.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="87" t="inlineStr">
+      <c r="A37" s="83" t="inlineStr">
         <is>
           <t>Moderation cost</t>
         </is>
@@ -12857,27 +10277,27 @@
         <f>Assumptions!$C$62</f>
         <v/>
       </c>
-      <c r="C37" s="112" t="inlineStr">
+      <c r="C37" s="108" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
       </c>
-      <c r="D37" s="110" t="inlineStr">
+      <c r="D37" s="106" t="inlineStr">
         <is>
           <t>EUR 22 per 1,000 items reviewed, on a hybrid of automated classification and human review. Vendor pricing varies widely with SLA and content type.</t>
         </is>
       </c>
-      <c r="E37" s="110" t="inlineStr">
+      <c r="E37" s="106" t="inlineStr">
         <is>
           <t>None cited</t>
         </is>
       </c>
-      <c r="F37" s="113" t="inlineStr">
+      <c r="F37" s="109" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G37" s="110" t="inlineStr">
+      <c r="G37" s="106" t="inlineStr">
         <is>
           <t>Vendor quotes once P2 scope is fixed.</t>
         </is>
@@ -12897,7 +10317,7 @@
       <c r="G38" s="14" t="n"/>
     </row>
     <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="87" t="inlineStr">
+      <c r="A39" s="83" t="inlineStr">
         <is>
           <t>Corporate tax rates</t>
         </is>
@@ -12906,34 +10326,34 @@
         <f>Assumptions!$C$93</f>
         <v/>
       </c>
-      <c r="C39" s="116" t="inlineStr">
+      <c r="C39" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D39" s="110" t="inlineStr">
+      <c r="D39" s="106" t="inlineStr">
         <is>
           <t>15% for the first four profitable years under the Spanish Startup Law, then the 25% standard rate. Modelled with loss carryforward against the Y1-Y4 losses.</t>
         </is>
       </c>
-      <c r="E39" s="110" t="inlineStr">
+      <c r="E39" s="106" t="inlineStr">
         <is>
           <t>Ley de Startups (Spain); Impuesto sobre Sociedades</t>
         </is>
       </c>
-      <c r="F39" s="111" t="inlineStr">
+      <c r="F39" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G39" s="110" t="inlineStr">
+      <c r="G39" s="106" t="inlineStr">
         <is>
           <t>Confirm eligibility with a Spanish tax adviser before filing.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="87" t="inlineStr">
+      <c r="A40" s="83" t="inlineStr">
         <is>
           <t>Risk-free rate</t>
         </is>
@@ -12942,71 +10362,71 @@
         <f>Assumptions!$C$113</f>
         <v/>
       </c>
-      <c r="C40" s="116" t="inlineStr">
+      <c r="C40" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D40" s="110" t="inlineStr">
+      <c r="D40" s="106" t="inlineStr">
         <is>
           <t>Spanish 10-year sovereign yield, ~3.2% in mid-2026. Used as the floor for the founder opportunity-cost calculation rather than as the discount rate.</t>
         </is>
       </c>
-      <c r="E40" s="110" t="inlineStr">
+      <c r="E40" s="106" t="inlineStr">
         <is>
           <t>Spanish 10Y government bond yield</t>
         </is>
       </c>
-      <c r="F40" s="111" t="inlineStr">
+      <c r="F40" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G40" s="110" t="inlineStr">
+      <c r="G40" s="106" t="inlineStr">
         <is>
           <t>Refresh at the date of any raise.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="87" t="inlineStr">
+      <c r="A41" s="83" t="inlineStr">
         <is>
           <t>WACC / discount rate</t>
         </is>
       </c>
-      <c r="B41" s="114" t="inlineStr">
+      <c r="B41" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C41" s="109" t="inlineStr">
+      <c r="C41" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D41" s="110" t="inlineStr">
+      <c r="D41" s="106" t="inlineStr">
         <is>
           <t>25%, against a published mature-company anchor of 6.01%. Damodaran's European cost of capital dataset puts Software (Internet) at 6.01% in euros across 23 listed firms, and the European market ex-financials at 6.59%. Those are costs of capital for mature listed companies; this is a pre-revenue venture, and the 19-point gap is the stage premium. It is stated rather than buried because it is the largest single judgement in the valuation. Damodaran publishes no dataset for venture-stage rates, so the premium itself is convention (20-35% is the usual range) and not a sourced figure. The sensitivity grid runs 20-30% because this is arguable rather than knowable.</t>
         </is>
       </c>
-      <c r="E41" s="110" t="inlineStr">
+      <c r="E41" s="106" t="inlineStr">
         <is>
           <t>Aswath Damodaran, NYU Stern, Cost of Capital by Industry (Europe), updated 5 January 2026</t>
         </is>
       </c>
-      <c r="F41" s="115" t="inlineStr">
+      <c r="F41" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G41" s="110" t="inlineStr">
+      <c r="G41" s="106" t="inlineStr">
         <is>
           <t>An actual term sheet prices this for you.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="87" t="inlineStr">
+      <c r="A42" s="83" t="inlineStr">
         <is>
           <t>Exit revenue multiple</t>
         </is>
@@ -13015,34 +10435,34 @@
         <f>Assumptions!$C$112</f>
         <v/>
       </c>
-      <c r="C42" s="109" t="inlineStr">
+      <c r="C42" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D42" s="110" t="inlineStr">
+      <c r="D42" s="106" t="inlineStr">
         <is>
           <t>6.5x blended. Marketplace comparables trade around 4x revenue and high-growth SaaS around 9x; our Y10 mix is roughly 55% marketplace take and 12% SaaS.</t>
         </is>
       </c>
-      <c r="E42" s="110" t="inlineStr">
+      <c r="E42" s="106" t="inlineStr">
         <is>
           <t>Public marketplace and SaaS trading multiples</t>
         </is>
       </c>
-      <c r="F42" s="115" t="inlineStr">
+      <c r="F42" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G42" s="110" t="inlineStr">
+      <c r="G42" s="106" t="inlineStr">
         <is>
           <t>Comparable private transactions nearer an exit.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="87" t="inlineStr">
+      <c r="A43" s="83" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
@@ -13051,27 +10471,27 @@
         <f>Assumptions!$C$111</f>
         <v/>
       </c>
-      <c r="C43" s="109" t="inlineStr">
+      <c r="C43" s="105" t="inlineStr">
         <is>
           <t>BENCHMARKED</t>
         </is>
       </c>
-      <c r="D43" s="110" t="inlineStr">
+      <c r="D43" s="106" t="inlineStr">
         <is>
           <t>3%, approximating long-run nominal GDP. Ten explicit forecast years were chosen partly so this assumption carries less of the valuation than it would at Y7.</t>
         </is>
       </c>
-      <c r="E43" s="110" t="inlineStr">
+      <c r="E43" s="106" t="inlineStr">
         <is>
           <t>Standard DCF convention</t>
         </is>
       </c>
-      <c r="F43" s="115" t="inlineStr">
+      <c r="F43" s="111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G43" s="110" t="inlineStr">
+      <c r="G43" s="106" t="inlineStr">
         <is>
           <t>Nothing: it is a convention, and the grid shows its effect.</t>
         </is>
@@ -13091,112 +10511,112 @@
       <c r="G44" s="14" t="n"/>
     </row>
     <row r="45" ht="58" customHeight="1">
-      <c r="A45" s="87" t="inlineStr">
+      <c r="A45" s="83" t="inlineStr">
         <is>
           <t>Payout age floor</t>
         </is>
       </c>
-      <c r="B45" s="114" t="inlineStr">
+      <c r="B45" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C45" s="116" t="inlineStr">
+      <c r="C45" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D45" s="110" t="inlineStr">
+      <c r="D45" s="106" t="inlineStr">
         <is>
           <t>Stripe Express and Custom Connect require 18. Standard Connect allows 13+, but a legal guardian must own the account and hold the bank account the money lands in.</t>
         </is>
       </c>
-      <c r="E45" s="110" t="inlineStr">
+      <c r="E45" s="106" t="inlineStr">
         <is>
           <t>Stripe Connect documentation</t>
         </is>
       </c>
-      <c r="F45" s="111" t="inlineStr">
+      <c r="F45" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G45" s="110" t="inlineStr">
+      <c r="G45" s="106" t="inlineStr">
         <is>
           <t>Nothing: it is a hard platform rule.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
-      <c r="A46" s="87" t="inlineStr">
+      <c r="A46" s="83" t="inlineStr">
         <is>
           <t>Digital consent age, Spain</t>
         </is>
       </c>
-      <c r="B46" s="114" t="inlineStr">
+      <c r="B46" s="110" t="inlineStr">
         <is>
           <t>see model</t>
         </is>
       </c>
-      <c r="C46" s="116" t="inlineStr">
+      <c r="C46" s="112" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D46" s="110" t="inlineStr">
+      <c r="D46" s="106" t="inlineStr">
         <is>
           <t>14 today under LOPDGDD Art. 7. A draft Organic Law on the Protection of Minors in Digital Environments would raise it to 16 and make age verification mandatory, which is why 16 is the forward-compatible floor for an account.</t>
         </is>
       </c>
-      <c r="E46" s="110" t="inlineStr">
+      <c r="E46" s="106" t="inlineStr">
         <is>
           <t>LOPDGDD Art. 7; draft Organic Law, Council of Ministers, March 2025</t>
         </is>
       </c>
-      <c r="F46" s="111" t="inlineStr">
+      <c r="F46" s="107" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G46" s="110" t="inlineStr">
+      <c r="G46" s="106" t="inlineStr">
         <is>
           <t>Track the bill through Parliament.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="118" t="inlineStr">
+      <c r="A48" s="114" t="inlineStr">
         <is>
           <t>THE THREE ASSUMPTIONS MOST LIKELY TO BE WRONG</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="119" t="inlineStr">
+      <c r="A49" s="115" t="inlineStr">
         <is>
           <t>1. Fan churn. We assume 6-13%/month; Patreon reports 10-15%. If Patreon is right, Y10 revenue falls from about EUR 58M to EUR 51M and the capital requirement roughly doubles.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="119" t="inlineStr">
+      <c r="A50" s="115" t="inlineStr">
         <is>
           <t>2. Athlete count. The trajectory is a target, not a forecast, and everything scales off it.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="119" t="inlineStr">
+      <c r="A51" s="115" t="inlineStr">
         <is>
           <t>3. Share of athletes who monetise. No published comparable exists at all.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="120" t="inlineStr"/>
+      <c r="A52" s="116" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="120" t="inlineStr">
+      <c r="A53" s="116" t="inlineStr">
         <is>
           <t>All three are answered by the same thing: three months of real cohort data from P1.</t>
         </is>
@@ -15804,35 +13224,45 @@
           <t>FTE</t>
         </is>
       </c>
-      <c r="C66" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" s="23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E66" s="23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F66" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G66" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H66" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="I66" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="J66" s="23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K66" s="23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L66" s="23" t="n">
-        <v>16</v>
+      <c r="C66" s="33">
+        <f>HiringPlan!C12</f>
+        <v/>
+      </c>
+      <c r="D66" s="33">
+        <f>HiringPlan!D12</f>
+        <v/>
+      </c>
+      <c r="E66" s="33">
+        <f>HiringPlan!E12</f>
+        <v/>
+      </c>
+      <c r="F66" s="33">
+        <f>HiringPlan!F12</f>
+        <v/>
+      </c>
+      <c r="G66" s="33">
+        <f>HiringPlan!G12</f>
+        <v/>
+      </c>
+      <c r="H66" s="33">
+        <f>HiringPlan!H12</f>
+        <v/>
+      </c>
+      <c r="I66" s="33">
+        <f>HiringPlan!I12</f>
+        <v/>
+      </c>
+      <c r="J66" s="33">
+        <f>HiringPlan!J12</f>
+        <v/>
+      </c>
+      <c r="K66" s="33">
+        <f>HiringPlan!K12</f>
+        <v/>
+      </c>
+      <c r="L66" s="33">
+        <f>HiringPlan!L12</f>
+        <v/>
       </c>
     </row>
     <row r="67">
